--- a/Mine/logs/mine_signal_logs.xlsx
+++ b/Mine/logs/mine_signal_logs.xlsx
@@ -464,7 +464,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P53"/>
+  <dimension ref="A1:P58"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -3140,6 +3140,232 @@
       <c r="P53" s="2" t="inlineStr">
         <is>
           <t>Low Strike Check</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="2" t="inlineStr">
+        <is>
+          <t>2026-02-09 13:40:00</t>
+        </is>
+      </c>
+      <c r="B54" s="2" t="inlineStr">
+        <is>
+          <t>13:40:00</t>
+        </is>
+      </c>
+      <c r="C54" s="2" t="inlineStr">
+        <is>
+          <t>13:40</t>
+        </is>
+      </c>
+      <c r="D54" s="2" t="inlineStr">
+        <is>
+          <t>78.25</t>
+        </is>
+      </c>
+      <c r="E54" s="2" t="inlineStr"/>
+      <c r="F54" s="2" t="inlineStr">
+        <is>
+          <t>198.95</t>
+        </is>
+      </c>
+      <c r="G54" s="2" t="inlineStr"/>
+      <c r="H54" s="2" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="I54" s="2" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="J54" s="2" t="inlineStr"/>
+      <c r="K54" s="2" t="inlineStr"/>
+      <c r="L54" s="2" t="inlineStr"/>
+      <c r="M54" s="2" t="inlineStr"/>
+      <c r="N54" s="2" t="inlineStr"/>
+      <c r="O54" s="2" t="inlineStr"/>
+      <c r="P54" s="2" t="inlineStr">
+        <is>
+          <t>High Strike Check</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="2" t="inlineStr">
+        <is>
+          <t>2026-02-09 13:40:00</t>
+        </is>
+      </c>
+      <c r="B55" s="2" t="inlineStr">
+        <is>
+          <t>13:40:00</t>
+        </is>
+      </c>
+      <c r="C55" s="2" t="inlineStr">
+        <is>
+          <t>13:40</t>
+        </is>
+      </c>
+      <c r="D55" s="2" t="inlineStr">
+        <is>
+          <t>155.00</t>
+        </is>
+      </c>
+      <c r="E55" s="2" t="inlineStr"/>
+      <c r="F55" s="2" t="inlineStr">
+        <is>
+          <t>99.00</t>
+        </is>
+      </c>
+      <c r="G55" s="2" t="inlineStr"/>
+      <c r="H55" s="2" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="I55" s="2" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="J55" s="2" t="inlineStr"/>
+      <c r="K55" s="2" t="inlineStr"/>
+      <c r="L55" s="2" t="inlineStr"/>
+      <c r="M55" s="2" t="inlineStr"/>
+      <c r="N55" s="2" t="inlineStr"/>
+      <c r="O55" s="2" t="inlineStr"/>
+      <c r="P55" s="2" t="inlineStr">
+        <is>
+          <t>Low Strike Check</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="2" t="inlineStr">
+        <is>
+          <t>2026-02-09 13:45:00</t>
+        </is>
+      </c>
+      <c r="B56" s="2" t="inlineStr">
+        <is>
+          <t>13:45:00</t>
+        </is>
+      </c>
+      <c r="C56" s="2" t="inlineStr">
+        <is>
+          <t>13:45</t>
+        </is>
+      </c>
+      <c r="D56" s="2" t="inlineStr"/>
+      <c r="E56" s="2" t="inlineStr"/>
+      <c r="F56" s="2" t="inlineStr"/>
+      <c r="G56" s="2" t="inlineStr"/>
+      <c r="H56" s="2" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="I56" s="2" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="J56" s="2" t="inlineStr"/>
+      <c r="K56" s="2" t="inlineStr"/>
+      <c r="L56" s="2" t="inlineStr"/>
+      <c r="M56" s="2" t="inlineStr"/>
+      <c r="N56" s="2" t="inlineStr"/>
+      <c r="O56" s="2" t="inlineStr"/>
+      <c r="P56" s="2" t="inlineStr">
+        <is>
+          <t>Failed to fetch data: Live data fetch timed out after 10s</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="2" t="inlineStr">
+        <is>
+          <t>2026-02-09 13:50:00</t>
+        </is>
+      </c>
+      <c r="B57" s="2" t="inlineStr">
+        <is>
+          <t>13:50:00</t>
+        </is>
+      </c>
+      <c r="C57" s="2" t="inlineStr">
+        <is>
+          <t>13:50</t>
+        </is>
+      </c>
+      <c r="D57" s="2" t="inlineStr"/>
+      <c r="E57" s="2" t="inlineStr"/>
+      <c r="F57" s="2" t="inlineStr"/>
+      <c r="G57" s="2" t="inlineStr"/>
+      <c r="H57" s="2" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="I57" s="2" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="J57" s="2" t="inlineStr"/>
+      <c r="K57" s="2" t="inlineStr"/>
+      <c r="L57" s="2" t="inlineStr"/>
+      <c r="M57" s="2" t="inlineStr"/>
+      <c r="N57" s="2" t="inlineStr"/>
+      <c r="O57" s="2" t="inlineStr"/>
+      <c r="P57" s="2" t="inlineStr">
+        <is>
+          <t>Failed to fetch data: Live data fetch timed out after 10s</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="2" t="inlineStr">
+        <is>
+          <t>2026-02-09 13:55:00</t>
+        </is>
+      </c>
+      <c r="B58" s="2" t="inlineStr">
+        <is>
+          <t>13:55:00</t>
+        </is>
+      </c>
+      <c r="C58" s="2" t="inlineStr">
+        <is>
+          <t>13:55</t>
+        </is>
+      </c>
+      <c r="D58" s="2" t="inlineStr"/>
+      <c r="E58" s="2" t="inlineStr"/>
+      <c r="F58" s="2" t="inlineStr"/>
+      <c r="G58" s="2" t="inlineStr"/>
+      <c r="H58" s="2" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="I58" s="2" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="J58" s="2" t="inlineStr"/>
+      <c r="K58" s="2" t="inlineStr"/>
+      <c r="L58" s="2" t="inlineStr"/>
+      <c r="M58" s="2" t="inlineStr"/>
+      <c r="N58" s="2" t="inlineStr"/>
+      <c r="O58" s="2" t="inlineStr"/>
+      <c r="P58" s="2" t="inlineStr">
+        <is>
+          <t>Failed to fetch data: Live data fetch timed out after 10s</t>
         </is>
       </c>
     </row>

--- a/Mine/logs/mine_signal_logs.xlsx
+++ b/Mine/logs/mine_signal_logs.xlsx
@@ -464,7 +464,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P58"/>
+  <dimension ref="A1:P60"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -3366,6 +3366,106 @@
       <c r="P58" s="2" t="inlineStr">
         <is>
           <t>Failed to fetch data: Live data fetch timed out after 10s</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="2" t="inlineStr">
+        <is>
+          <t>2026-02-09 14:00:00</t>
+        </is>
+      </c>
+      <c r="B59" s="2" t="inlineStr">
+        <is>
+          <t>14:00:00</t>
+        </is>
+      </c>
+      <c r="C59" s="2" t="inlineStr">
+        <is>
+          <t>14:00</t>
+        </is>
+      </c>
+      <c r="D59" s="2" t="inlineStr">
+        <is>
+          <t>78.25</t>
+        </is>
+      </c>
+      <c r="E59" s="2" t="inlineStr"/>
+      <c r="F59" s="2" t="inlineStr">
+        <is>
+          <t>198.95</t>
+        </is>
+      </c>
+      <c r="G59" s="2" t="inlineStr"/>
+      <c r="H59" s="2" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="I59" s="2" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="J59" s="2" t="inlineStr"/>
+      <c r="K59" s="2" t="inlineStr"/>
+      <c r="L59" s="2" t="inlineStr"/>
+      <c r="M59" s="2" t="inlineStr"/>
+      <c r="N59" s="2" t="inlineStr"/>
+      <c r="O59" s="2" t="inlineStr"/>
+      <c r="P59" s="2" t="inlineStr">
+        <is>
+          <t>High Strike Check</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="2" t="inlineStr">
+        <is>
+          <t>2026-02-09 14:00:00</t>
+        </is>
+      </c>
+      <c r="B60" s="2" t="inlineStr">
+        <is>
+          <t>14:00:00</t>
+        </is>
+      </c>
+      <c r="C60" s="2" t="inlineStr">
+        <is>
+          <t>14:00</t>
+        </is>
+      </c>
+      <c r="D60" s="2" t="inlineStr">
+        <is>
+          <t>155.00</t>
+        </is>
+      </c>
+      <c r="E60" s="2" t="inlineStr"/>
+      <c r="F60" s="2" t="inlineStr">
+        <is>
+          <t>99.00</t>
+        </is>
+      </c>
+      <c r="G60" s="2" t="inlineStr"/>
+      <c r="H60" s="2" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="I60" s="2" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="J60" s="2" t="inlineStr"/>
+      <c r="K60" s="2" t="inlineStr"/>
+      <c r="L60" s="2" t="inlineStr"/>
+      <c r="M60" s="2" t="inlineStr"/>
+      <c r="N60" s="2" t="inlineStr"/>
+      <c r="O60" s="2" t="inlineStr"/>
+      <c r="P60" s="2" t="inlineStr">
+        <is>
+          <t>Low Strike Check</t>
         </is>
       </c>
     </row>

--- a/Mine/logs/mine_signal_logs.xlsx
+++ b/Mine/logs/mine_signal_logs.xlsx
@@ -464,7 +464,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P60"/>
+  <dimension ref="A1:P61"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -3466,6 +3466,48 @@
       <c r="P60" s="2" t="inlineStr">
         <is>
           <t>Low Strike Check</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="2" t="inlineStr">
+        <is>
+          <t>2026-02-09 14:05:00</t>
+        </is>
+      </c>
+      <c r="B61" s="2" t="inlineStr">
+        <is>
+          <t>14:05:00</t>
+        </is>
+      </c>
+      <c r="C61" s="2" t="inlineStr">
+        <is>
+          <t>14:05</t>
+        </is>
+      </c>
+      <c r="D61" s="2" t="inlineStr"/>
+      <c r="E61" s="2" t="inlineStr"/>
+      <c r="F61" s="2" t="inlineStr"/>
+      <c r="G61" s="2" t="inlineStr"/>
+      <c r="H61" s="2" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="I61" s="2" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="J61" s="2" t="inlineStr"/>
+      <c r="K61" s="2" t="inlineStr"/>
+      <c r="L61" s="2" t="inlineStr"/>
+      <c r="M61" s="2" t="inlineStr"/>
+      <c r="N61" s="2" t="inlineStr"/>
+      <c r="O61" s="2" t="inlineStr"/>
+      <c r="P61" s="2" t="inlineStr">
+        <is>
+          <t>Failed to fetch data: Live data fetch timed out after 10s</t>
         </is>
       </c>
     </row>

--- a/Mine/logs/mine_signal_logs.xlsx
+++ b/Mine/logs/mine_signal_logs.xlsx
@@ -483,7 +483,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P21"/>
+  <dimension ref="A1:P26"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -1543,6 +1543,248 @@
       <c r="P21" s="6" t="inlineStr">
         <is>
           <t>Failed to fetch data: Live data fetch timed out after 10s</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="6" t="inlineStr">
+        <is>
+          <t>2026-02-10 09:30:00</t>
+        </is>
+      </c>
+      <c r="B22" s="6" t="inlineStr">
+        <is>
+          <t>09:30:00</t>
+        </is>
+      </c>
+      <c r="C22" s="6" t="inlineStr">
+        <is>
+          <t>09:30</t>
+        </is>
+      </c>
+      <c r="D22" s="6" t="inlineStr">
+        <is>
+          <t>83.70</t>
+        </is>
+      </c>
+      <c r="E22" s="6" t="inlineStr"/>
+      <c r="F22" s="6" t="inlineStr">
+        <is>
+          <t>111.75</t>
+        </is>
+      </c>
+      <c r="G22" s="6" t="inlineStr"/>
+      <c r="H22" s="6" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="I22" s="6" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="J22" s="6" t="inlineStr"/>
+      <c r="K22" s="6" t="inlineStr"/>
+      <c r="L22" s="6" t="inlineStr"/>
+      <c r="M22" s="6" t="inlineStr"/>
+      <c r="N22" s="6" t="inlineStr"/>
+      <c r="O22" s="6" t="inlineStr"/>
+      <c r="P22" s="6" t="inlineStr">
+        <is>
+          <t>High Strike Check</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="6" t="inlineStr">
+        <is>
+          <t>2026-02-10 09:30:00</t>
+        </is>
+      </c>
+      <c r="B23" s="6" t="inlineStr">
+        <is>
+          <t>09:30:00</t>
+        </is>
+      </c>
+      <c r="C23" s="6" t="inlineStr">
+        <is>
+          <t>09:30</t>
+        </is>
+      </c>
+      <c r="D23" s="6" t="inlineStr">
+        <is>
+          <t>102.00</t>
+        </is>
+      </c>
+      <c r="E23" s="6" t="inlineStr"/>
+      <c r="F23" s="6" t="inlineStr">
+        <is>
+          <t>79.00</t>
+        </is>
+      </c>
+      <c r="G23" s="6" t="inlineStr"/>
+      <c r="H23" s="6" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="I23" s="6" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="J23" s="6" t="inlineStr"/>
+      <c r="K23" s="6" t="inlineStr"/>
+      <c r="L23" s="6" t="inlineStr"/>
+      <c r="M23" s="6" t="inlineStr"/>
+      <c r="N23" s="6" t="inlineStr"/>
+      <c r="O23" s="6" t="inlineStr"/>
+      <c r="P23" s="6" t="inlineStr">
+        <is>
+          <t>Low Strike Check</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="6" t="inlineStr">
+        <is>
+          <t>2026-02-10 09:35:00</t>
+        </is>
+      </c>
+      <c r="B24" s="6" t="inlineStr">
+        <is>
+          <t>09:35:00</t>
+        </is>
+      </c>
+      <c r="C24" s="6" t="inlineStr">
+        <is>
+          <t>09:35</t>
+        </is>
+      </c>
+      <c r="D24" s="6" t="inlineStr"/>
+      <c r="E24" s="6" t="inlineStr"/>
+      <c r="F24" s="6" t="inlineStr"/>
+      <c r="G24" s="6" t="inlineStr"/>
+      <c r="H24" s="6" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="I24" s="6" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="J24" s="6" t="inlineStr"/>
+      <c r="K24" s="6" t="inlineStr"/>
+      <c r="L24" s="6" t="inlineStr"/>
+      <c r="M24" s="6" t="inlineStr"/>
+      <c r="N24" s="6" t="inlineStr"/>
+      <c r="O24" s="6" t="inlineStr"/>
+      <c r="P24" s="6" t="inlineStr">
+        <is>
+          <t>Failed to fetch data: Live data fetch timed out after 10s</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="6" t="inlineStr">
+        <is>
+          <t>2026-02-10 09:35:00</t>
+        </is>
+      </c>
+      <c r="B25" s="6" t="inlineStr">
+        <is>
+          <t>09:35:00</t>
+        </is>
+      </c>
+      <c r="C25" s="6" t="inlineStr">
+        <is>
+          <t>09:35</t>
+        </is>
+      </c>
+      <c r="D25" s="6" t="inlineStr">
+        <is>
+          <t>83.70</t>
+        </is>
+      </c>
+      <c r="E25" s="6" t="inlineStr"/>
+      <c r="F25" s="6" t="inlineStr">
+        <is>
+          <t>111.75</t>
+        </is>
+      </c>
+      <c r="G25" s="6" t="inlineStr"/>
+      <c r="H25" s="6" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="I25" s="6" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="J25" s="6" t="inlineStr"/>
+      <c r="K25" s="6" t="inlineStr"/>
+      <c r="L25" s="6" t="inlineStr"/>
+      <c r="M25" s="6" t="inlineStr"/>
+      <c r="N25" s="6" t="inlineStr"/>
+      <c r="O25" s="6" t="inlineStr"/>
+      <c r="P25" s="6" t="inlineStr">
+        <is>
+          <t>High Strike Check</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="6" t="inlineStr">
+        <is>
+          <t>2026-02-10 09:35:00</t>
+        </is>
+      </c>
+      <c r="B26" s="6" t="inlineStr">
+        <is>
+          <t>09:35:00</t>
+        </is>
+      </c>
+      <c r="C26" s="6" t="inlineStr">
+        <is>
+          <t>09:35</t>
+        </is>
+      </c>
+      <c r="D26" s="6" t="inlineStr">
+        <is>
+          <t>102.00</t>
+        </is>
+      </c>
+      <c r="E26" s="6" t="inlineStr"/>
+      <c r="F26" s="6" t="inlineStr">
+        <is>
+          <t>79.00</t>
+        </is>
+      </c>
+      <c r="G26" s="6" t="inlineStr"/>
+      <c r="H26" s="6" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="I26" s="6" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="J26" s="6" t="inlineStr"/>
+      <c r="K26" s="6" t="inlineStr"/>
+      <c r="L26" s="6" t="inlineStr"/>
+      <c r="M26" s="6" t="inlineStr"/>
+      <c r="N26" s="6" t="inlineStr"/>
+      <c r="O26" s="6" t="inlineStr"/>
+      <c r="P26" s="6" t="inlineStr">
+        <is>
+          <t>Low Strike Check</t>
         </is>
       </c>
     </row>

--- a/Mine/logs/mine_signal_logs.xlsx
+++ b/Mine/logs/mine_signal_logs.xlsx
@@ -483,7 +483,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P26"/>
+  <dimension ref="A1:P42"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -1783,6 +1783,774 @@
       <c r="N26" s="6" t="inlineStr"/>
       <c r="O26" s="6" t="inlineStr"/>
       <c r="P26" s="6" t="inlineStr">
+        <is>
+          <t>Low Strike Check</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="6" t="inlineStr">
+        <is>
+          <t>2026-02-10 09:40:00</t>
+        </is>
+      </c>
+      <c r="B27" s="6" t="inlineStr">
+        <is>
+          <t>09:40:00</t>
+        </is>
+      </c>
+      <c r="C27" s="6" t="inlineStr">
+        <is>
+          <t>09:40</t>
+        </is>
+      </c>
+      <c r="D27" s="6" t="inlineStr"/>
+      <c r="E27" s="6" t="inlineStr"/>
+      <c r="F27" s="6" t="inlineStr"/>
+      <c r="G27" s="6" t="inlineStr"/>
+      <c r="H27" s="6" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="I27" s="6" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="J27" s="6" t="inlineStr"/>
+      <c r="K27" s="6" t="inlineStr"/>
+      <c r="L27" s="6" t="inlineStr"/>
+      <c r="M27" s="6" t="inlineStr"/>
+      <c r="N27" s="6" t="inlineStr"/>
+      <c r="O27" s="6" t="inlineStr"/>
+      <c r="P27" s="6" t="inlineStr">
+        <is>
+          <t>Failed to fetch data: Live data fetch timed out after 10s</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="6" t="inlineStr">
+        <is>
+          <t>2026-02-10 09:45:00</t>
+        </is>
+      </c>
+      <c r="B28" s="6" t="inlineStr">
+        <is>
+          <t>09:45:00</t>
+        </is>
+      </c>
+      <c r="C28" s="6" t="inlineStr">
+        <is>
+          <t>09:45</t>
+        </is>
+      </c>
+      <c r="D28" s="6" t="inlineStr"/>
+      <c r="E28" s="6" t="inlineStr"/>
+      <c r="F28" s="6" t="inlineStr"/>
+      <c r="G28" s="6" t="inlineStr"/>
+      <c r="H28" s="6" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="I28" s="6" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="J28" s="6" t="inlineStr"/>
+      <c r="K28" s="6" t="inlineStr"/>
+      <c r="L28" s="6" t="inlineStr"/>
+      <c r="M28" s="6" t="inlineStr"/>
+      <c r="N28" s="6" t="inlineStr"/>
+      <c r="O28" s="6" t="inlineStr"/>
+      <c r="P28" s="6" t="inlineStr">
+        <is>
+          <t>Failed to fetch data: Live data fetch timed out after 10s</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="6" t="inlineStr">
+        <is>
+          <t>2026-02-10 09:50:00</t>
+        </is>
+      </c>
+      <c r="B29" s="6" t="inlineStr">
+        <is>
+          <t>09:50:00</t>
+        </is>
+      </c>
+      <c r="C29" s="6" t="inlineStr">
+        <is>
+          <t>09:50</t>
+        </is>
+      </c>
+      <c r="D29" s="6" t="inlineStr">
+        <is>
+          <t>83.70</t>
+        </is>
+      </c>
+      <c r="E29" s="6" t="inlineStr"/>
+      <c r="F29" s="6" t="inlineStr">
+        <is>
+          <t>111.75</t>
+        </is>
+      </c>
+      <c r="G29" s="6" t="inlineStr"/>
+      <c r="H29" s="6" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="I29" s="6" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="J29" s="6" t="inlineStr"/>
+      <c r="K29" s="6" t="inlineStr"/>
+      <c r="L29" s="6" t="inlineStr"/>
+      <c r="M29" s="6" t="inlineStr"/>
+      <c r="N29" s="6" t="inlineStr"/>
+      <c r="O29" s="6" t="inlineStr"/>
+      <c r="P29" s="6" t="inlineStr">
+        <is>
+          <t>High Strike Check</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="6" t="inlineStr">
+        <is>
+          <t>2026-02-10 09:50:00</t>
+        </is>
+      </c>
+      <c r="B30" s="6" t="inlineStr">
+        <is>
+          <t>09:50:00</t>
+        </is>
+      </c>
+      <c r="C30" s="6" t="inlineStr">
+        <is>
+          <t>09:50</t>
+        </is>
+      </c>
+      <c r="D30" s="6" t="inlineStr">
+        <is>
+          <t>102.00</t>
+        </is>
+      </c>
+      <c r="E30" s="6" t="inlineStr"/>
+      <c r="F30" s="6" t="inlineStr">
+        <is>
+          <t>79.00</t>
+        </is>
+      </c>
+      <c r="G30" s="6" t="inlineStr"/>
+      <c r="H30" s="6" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="I30" s="6" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="J30" s="6" t="inlineStr"/>
+      <c r="K30" s="6" t="inlineStr"/>
+      <c r="L30" s="6" t="inlineStr"/>
+      <c r="M30" s="6" t="inlineStr"/>
+      <c r="N30" s="6" t="inlineStr"/>
+      <c r="O30" s="6" t="inlineStr"/>
+      <c r="P30" s="6" t="inlineStr">
+        <is>
+          <t>Low Strike Check</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="6" t="inlineStr">
+        <is>
+          <t>2026-02-10 09:55:00</t>
+        </is>
+      </c>
+      <c r="B31" s="6" t="inlineStr">
+        <is>
+          <t>09:55:00</t>
+        </is>
+      </c>
+      <c r="C31" s="6" t="inlineStr">
+        <is>
+          <t>09:55</t>
+        </is>
+      </c>
+      <c r="D31" s="6" t="inlineStr">
+        <is>
+          <t>83.70</t>
+        </is>
+      </c>
+      <c r="E31" s="6" t="inlineStr"/>
+      <c r="F31" s="6" t="inlineStr">
+        <is>
+          <t>111.75</t>
+        </is>
+      </c>
+      <c r="G31" s="6" t="inlineStr"/>
+      <c r="H31" s="6" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="I31" s="6" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="J31" s="6" t="inlineStr"/>
+      <c r="K31" s="6" t="inlineStr"/>
+      <c r="L31" s="6" t="inlineStr"/>
+      <c r="M31" s="6" t="inlineStr"/>
+      <c r="N31" s="6" t="inlineStr"/>
+      <c r="O31" s="6" t="inlineStr"/>
+      <c r="P31" s="6" t="inlineStr">
+        <is>
+          <t>High Strike Check</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="6" t="inlineStr">
+        <is>
+          <t>2026-02-10 09:55:00</t>
+        </is>
+      </c>
+      <c r="B32" s="6" t="inlineStr">
+        <is>
+          <t>09:55:00</t>
+        </is>
+      </c>
+      <c r="C32" s="6" t="inlineStr">
+        <is>
+          <t>09:55</t>
+        </is>
+      </c>
+      <c r="D32" s="6" t="inlineStr">
+        <is>
+          <t>102.00</t>
+        </is>
+      </c>
+      <c r="E32" s="6" t="inlineStr"/>
+      <c r="F32" s="6" t="inlineStr">
+        <is>
+          <t>79.00</t>
+        </is>
+      </c>
+      <c r="G32" s="6" t="inlineStr"/>
+      <c r="H32" s="6" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="I32" s="6" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="J32" s="6" t="inlineStr"/>
+      <c r="K32" s="6" t="inlineStr"/>
+      <c r="L32" s="6" t="inlineStr"/>
+      <c r="M32" s="6" t="inlineStr"/>
+      <c r="N32" s="6" t="inlineStr"/>
+      <c r="O32" s="6" t="inlineStr"/>
+      <c r="P32" s="6" t="inlineStr">
+        <is>
+          <t>Low Strike Check</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="6" t="inlineStr">
+        <is>
+          <t>2026-02-10 10:00:00</t>
+        </is>
+      </c>
+      <c r="B33" s="6" t="inlineStr">
+        <is>
+          <t>10:00:00</t>
+        </is>
+      </c>
+      <c r="C33" s="6" t="inlineStr">
+        <is>
+          <t>10:00</t>
+        </is>
+      </c>
+      <c r="D33" s="6" t="inlineStr"/>
+      <c r="E33" s="6" t="inlineStr"/>
+      <c r="F33" s="6" t="inlineStr"/>
+      <c r="G33" s="6" t="inlineStr"/>
+      <c r="H33" s="6" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="I33" s="6" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="J33" s="6" t="inlineStr"/>
+      <c r="K33" s="6" t="inlineStr"/>
+      <c r="L33" s="6" t="inlineStr"/>
+      <c r="M33" s="6" t="inlineStr"/>
+      <c r="N33" s="6" t="inlineStr"/>
+      <c r="O33" s="6" t="inlineStr"/>
+      <c r="P33" s="6" t="inlineStr">
+        <is>
+          <t>Failed to fetch data: Live data fetch timed out after 10s</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="6" t="inlineStr">
+        <is>
+          <t>2026-02-10 10:05:00</t>
+        </is>
+      </c>
+      <c r="B34" s="6" t="inlineStr">
+        <is>
+          <t>10:05:00</t>
+        </is>
+      </c>
+      <c r="C34" s="6" t="inlineStr">
+        <is>
+          <t>10:05</t>
+        </is>
+      </c>
+      <c r="D34" s="6" t="inlineStr"/>
+      <c r="E34" s="6" t="inlineStr"/>
+      <c r="F34" s="6" t="inlineStr"/>
+      <c r="G34" s="6" t="inlineStr"/>
+      <c r="H34" s="6" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="I34" s="6" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="J34" s="6" t="inlineStr"/>
+      <c r="K34" s="6" t="inlineStr"/>
+      <c r="L34" s="6" t="inlineStr"/>
+      <c r="M34" s="6" t="inlineStr"/>
+      <c r="N34" s="6" t="inlineStr"/>
+      <c r="O34" s="6" t="inlineStr"/>
+      <c r="P34" s="6" t="inlineStr">
+        <is>
+          <t>Failed to fetch data: Error fetching quote: ('Connection aborted.', ConnectionResetError(54, 'Connection reset by peer'))</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="6" t="inlineStr">
+        <is>
+          <t>2026-02-10 10:10:00</t>
+        </is>
+      </c>
+      <c r="B35" s="6" t="inlineStr">
+        <is>
+          <t>10:10:00</t>
+        </is>
+      </c>
+      <c r="C35" s="6" t="inlineStr">
+        <is>
+          <t>10:10</t>
+        </is>
+      </c>
+      <c r="D35" s="6" t="inlineStr">
+        <is>
+          <t>83.70</t>
+        </is>
+      </c>
+      <c r="E35" s="6" t="inlineStr"/>
+      <c r="F35" s="6" t="inlineStr">
+        <is>
+          <t>111.75</t>
+        </is>
+      </c>
+      <c r="G35" s="6" t="inlineStr"/>
+      <c r="H35" s="6" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="I35" s="6" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="J35" s="6" t="inlineStr"/>
+      <c r="K35" s="6" t="inlineStr"/>
+      <c r="L35" s="6" t="inlineStr"/>
+      <c r="M35" s="6" t="inlineStr"/>
+      <c r="N35" s="6" t="inlineStr"/>
+      <c r="O35" s="6" t="inlineStr"/>
+      <c r="P35" s="6" t="inlineStr">
+        <is>
+          <t>High Strike Check</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="6" t="inlineStr">
+        <is>
+          <t>2026-02-10 10:10:00</t>
+        </is>
+      </c>
+      <c r="B36" s="6" t="inlineStr">
+        <is>
+          <t>10:10:00</t>
+        </is>
+      </c>
+      <c r="C36" s="6" t="inlineStr">
+        <is>
+          <t>10:10</t>
+        </is>
+      </c>
+      <c r="D36" s="6" t="inlineStr">
+        <is>
+          <t>102.00</t>
+        </is>
+      </c>
+      <c r="E36" s="6" t="inlineStr"/>
+      <c r="F36" s="6" t="inlineStr">
+        <is>
+          <t>79.00</t>
+        </is>
+      </c>
+      <c r="G36" s="6" t="inlineStr"/>
+      <c r="H36" s="6" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="I36" s="6" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="J36" s="6" t="inlineStr"/>
+      <c r="K36" s="6" t="inlineStr"/>
+      <c r="L36" s="6" t="inlineStr"/>
+      <c r="M36" s="6" t="inlineStr"/>
+      <c r="N36" s="6" t="inlineStr"/>
+      <c r="O36" s="6" t="inlineStr"/>
+      <c r="P36" s="6" t="inlineStr">
+        <is>
+          <t>Low Strike Check</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="6" t="inlineStr">
+        <is>
+          <t>2026-02-10 10:15:00</t>
+        </is>
+      </c>
+      <c r="B37" s="6" t="inlineStr">
+        <is>
+          <t>10:15:00</t>
+        </is>
+      </c>
+      <c r="C37" s="6" t="inlineStr">
+        <is>
+          <t>10:15</t>
+        </is>
+      </c>
+      <c r="D37" s="6" t="inlineStr">
+        <is>
+          <t>83.70</t>
+        </is>
+      </c>
+      <c r="E37" s="6" t="inlineStr"/>
+      <c r="F37" s="6" t="inlineStr">
+        <is>
+          <t>111.75</t>
+        </is>
+      </c>
+      <c r="G37" s="6" t="inlineStr"/>
+      <c r="H37" s="6" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="I37" s="6" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="J37" s="6" t="inlineStr"/>
+      <c r="K37" s="6" t="inlineStr"/>
+      <c r="L37" s="6" t="inlineStr"/>
+      <c r="M37" s="6" t="inlineStr"/>
+      <c r="N37" s="6" t="inlineStr"/>
+      <c r="O37" s="6" t="inlineStr"/>
+      <c r="P37" s="6" t="inlineStr">
+        <is>
+          <t>High Strike Check</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="6" t="inlineStr">
+        <is>
+          <t>2026-02-10 10:15:00</t>
+        </is>
+      </c>
+      <c r="B38" s="6" t="inlineStr">
+        <is>
+          <t>10:15:00</t>
+        </is>
+      </c>
+      <c r="C38" s="6" t="inlineStr">
+        <is>
+          <t>10:15</t>
+        </is>
+      </c>
+      <c r="D38" s="6" t="inlineStr">
+        <is>
+          <t>102.00</t>
+        </is>
+      </c>
+      <c r="E38" s="6" t="inlineStr"/>
+      <c r="F38" s="6" t="inlineStr">
+        <is>
+          <t>79.00</t>
+        </is>
+      </c>
+      <c r="G38" s="6" t="inlineStr"/>
+      <c r="H38" s="6" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="I38" s="6" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="J38" s="6" t="inlineStr"/>
+      <c r="K38" s="6" t="inlineStr"/>
+      <c r="L38" s="6" t="inlineStr"/>
+      <c r="M38" s="6" t="inlineStr"/>
+      <c r="N38" s="6" t="inlineStr"/>
+      <c r="O38" s="6" t="inlineStr"/>
+      <c r="P38" s="6" t="inlineStr">
+        <is>
+          <t>Low Strike Check</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="6" t="inlineStr">
+        <is>
+          <t>2026-02-10 10:20:00</t>
+        </is>
+      </c>
+      <c r="B39" s="6" t="inlineStr">
+        <is>
+          <t>10:20:00</t>
+        </is>
+      </c>
+      <c r="C39" s="6" t="inlineStr">
+        <is>
+          <t>10:20</t>
+        </is>
+      </c>
+      <c r="D39" s="6" t="inlineStr">
+        <is>
+          <t>83.70</t>
+        </is>
+      </c>
+      <c r="E39" s="6" t="inlineStr"/>
+      <c r="F39" s="6" t="inlineStr">
+        <is>
+          <t>111.75</t>
+        </is>
+      </c>
+      <c r="G39" s="6" t="inlineStr"/>
+      <c r="H39" s="6" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="I39" s="6" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="J39" s="6" t="inlineStr"/>
+      <c r="K39" s="6" t="inlineStr"/>
+      <c r="L39" s="6" t="inlineStr"/>
+      <c r="M39" s="6" t="inlineStr"/>
+      <c r="N39" s="6" t="inlineStr"/>
+      <c r="O39" s="6" t="inlineStr"/>
+      <c r="P39" s="6" t="inlineStr">
+        <is>
+          <t>High Strike Check</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="6" t="inlineStr">
+        <is>
+          <t>2026-02-10 10:20:00</t>
+        </is>
+      </c>
+      <c r="B40" s="6" t="inlineStr">
+        <is>
+          <t>10:20:00</t>
+        </is>
+      </c>
+      <c r="C40" s="6" t="inlineStr">
+        <is>
+          <t>10:20</t>
+        </is>
+      </c>
+      <c r="D40" s="6" t="inlineStr">
+        <is>
+          <t>102.00</t>
+        </is>
+      </c>
+      <c r="E40" s="6" t="inlineStr"/>
+      <c r="F40" s="6" t="inlineStr">
+        <is>
+          <t>79.00</t>
+        </is>
+      </c>
+      <c r="G40" s="6" t="inlineStr"/>
+      <c r="H40" s="6" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="I40" s="6" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="J40" s="6" t="inlineStr"/>
+      <c r="K40" s="6" t="inlineStr"/>
+      <c r="L40" s="6" t="inlineStr"/>
+      <c r="M40" s="6" t="inlineStr"/>
+      <c r="N40" s="6" t="inlineStr"/>
+      <c r="O40" s="6" t="inlineStr"/>
+      <c r="P40" s="6" t="inlineStr">
+        <is>
+          <t>Low Strike Check</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="6" t="inlineStr">
+        <is>
+          <t>2026-02-10 10:25:00</t>
+        </is>
+      </c>
+      <c r="B41" s="6" t="inlineStr">
+        <is>
+          <t>10:25:00</t>
+        </is>
+      </c>
+      <c r="C41" s="6" t="inlineStr">
+        <is>
+          <t>10:25</t>
+        </is>
+      </c>
+      <c r="D41" s="6" t="inlineStr">
+        <is>
+          <t>83.70</t>
+        </is>
+      </c>
+      <c r="E41" s="6" t="inlineStr"/>
+      <c r="F41" s="6" t="inlineStr">
+        <is>
+          <t>111.75</t>
+        </is>
+      </c>
+      <c r="G41" s="6" t="inlineStr"/>
+      <c r="H41" s="6" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="I41" s="6" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="J41" s="6" t="inlineStr"/>
+      <c r="K41" s="6" t="inlineStr"/>
+      <c r="L41" s="6" t="inlineStr"/>
+      <c r="M41" s="6" t="inlineStr"/>
+      <c r="N41" s="6" t="inlineStr"/>
+      <c r="O41" s="6" t="inlineStr"/>
+      <c r="P41" s="6" t="inlineStr">
+        <is>
+          <t>High Strike Check</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="6" t="inlineStr">
+        <is>
+          <t>2026-02-10 10:25:00</t>
+        </is>
+      </c>
+      <c r="B42" s="6" t="inlineStr">
+        <is>
+          <t>10:25:00</t>
+        </is>
+      </c>
+      <c r="C42" s="6" t="inlineStr">
+        <is>
+          <t>10:25</t>
+        </is>
+      </c>
+      <c r="D42" s="6" t="inlineStr">
+        <is>
+          <t>102.00</t>
+        </is>
+      </c>
+      <c r="E42" s="6" t="inlineStr"/>
+      <c r="F42" s="6" t="inlineStr">
+        <is>
+          <t>79.00</t>
+        </is>
+      </c>
+      <c r="G42" s="6" t="inlineStr"/>
+      <c r="H42" s="6" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="I42" s="6" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="J42" s="6" t="inlineStr"/>
+      <c r="K42" s="6" t="inlineStr"/>
+      <c r="L42" s="6" t="inlineStr"/>
+      <c r="M42" s="6" t="inlineStr"/>
+      <c r="N42" s="6" t="inlineStr"/>
+      <c r="O42" s="6" t="inlineStr"/>
+      <c r="P42" s="6" t="inlineStr">
         <is>
           <t>Low Strike Check</t>
         </is>

--- a/Mine/logs/mine_signal_logs.xlsx
+++ b/Mine/logs/mine_signal_logs.xlsx
@@ -483,7 +483,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P42"/>
+  <dimension ref="A1:P44"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -2551,6 +2551,106 @@
       <c r="N42" s="6" t="inlineStr"/>
       <c r="O42" s="6" t="inlineStr"/>
       <c r="P42" s="6" t="inlineStr">
+        <is>
+          <t>Low Strike Check</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="6" t="inlineStr">
+        <is>
+          <t>2026-02-10 10:30:00</t>
+        </is>
+      </c>
+      <c r="B43" s="6" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="C43" s="6" t="inlineStr">
+        <is>
+          <t>10:30</t>
+        </is>
+      </c>
+      <c r="D43" s="6" t="inlineStr">
+        <is>
+          <t>83.70</t>
+        </is>
+      </c>
+      <c r="E43" s="6" t="inlineStr"/>
+      <c r="F43" s="6" t="inlineStr">
+        <is>
+          <t>111.75</t>
+        </is>
+      </c>
+      <c r="G43" s="6" t="inlineStr"/>
+      <c r="H43" s="6" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="I43" s="6" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="J43" s="6" t="inlineStr"/>
+      <c r="K43" s="6" t="inlineStr"/>
+      <c r="L43" s="6" t="inlineStr"/>
+      <c r="M43" s="6" t="inlineStr"/>
+      <c r="N43" s="6" t="inlineStr"/>
+      <c r="O43" s="6" t="inlineStr"/>
+      <c r="P43" s="6" t="inlineStr">
+        <is>
+          <t>High Strike Check</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="6" t="inlineStr">
+        <is>
+          <t>2026-02-10 10:30:00</t>
+        </is>
+      </c>
+      <c r="B44" s="6" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="C44" s="6" t="inlineStr">
+        <is>
+          <t>10:30</t>
+        </is>
+      </c>
+      <c r="D44" s="6" t="inlineStr">
+        <is>
+          <t>102.00</t>
+        </is>
+      </c>
+      <c r="E44" s="6" t="inlineStr"/>
+      <c r="F44" s="6" t="inlineStr">
+        <is>
+          <t>79.00</t>
+        </is>
+      </c>
+      <c r="G44" s="6" t="inlineStr"/>
+      <c r="H44" s="6" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="I44" s="6" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="J44" s="6" t="inlineStr"/>
+      <c r="K44" s="6" t="inlineStr"/>
+      <c r="L44" s="6" t="inlineStr"/>
+      <c r="M44" s="6" t="inlineStr"/>
+      <c r="N44" s="6" t="inlineStr"/>
+      <c r="O44" s="6" t="inlineStr"/>
+      <c r="P44" s="6" t="inlineStr">
         <is>
           <t>Low Strike Check</t>
         </is>

--- a/Mine/logs/mine_signal_logs.xlsx
+++ b/Mine/logs/mine_signal_logs.xlsx
@@ -33,7 +33,7 @@
       <sz val="11"/>
     </font>
   </fonts>
-  <fills count="6">
+  <fills count="5">
     <fill>
       <patternFill/>
     </fill>
@@ -58,19 +58,28 @@
         <bgColor rgb="FFFFFFFF"/>
       </patternFill>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor rgb="FFC6EFCE"/>
-      </patternFill>
-    </fill>
   </fills>
-  <borders count="3">
+  <borders count="4">
     <border>
       <left/>
       <right/>
       <top/>
       <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -112,10 +121,10 @@
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -483,7 +492,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P44"/>
+  <dimension ref="A1:P53"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -579,950 +588,982 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>2026-02-09 13:05:00</t>
-        </is>
-      </c>
-      <c r="B2" s="2" t="inlineStr">
-        <is>
-          <t>13:05:00</t>
-        </is>
-      </c>
-      <c r="C2" s="2" t="inlineStr">
-        <is>
-          <t>13:05</t>
-        </is>
-      </c>
-      <c r="D2" s="2" t="inlineStr">
-        <is>
-          <t>155.00</t>
-        </is>
-      </c>
-      <c r="E2" s="2" t="n"/>
-      <c r="F2" s="2" t="inlineStr">
-        <is>
-          <t>99.00</t>
-        </is>
-      </c>
-      <c r="G2" s="2" t="n"/>
-      <c r="H2" s="2" t="inlineStr">
-        <is>
-          <t>✗ NO</t>
-        </is>
-      </c>
-      <c r="I2" s="2" t="inlineStr">
-        <is>
-          <t>✗ NO</t>
-        </is>
-      </c>
-      <c r="J2" s="2" t="n"/>
-      <c r="K2" s="2" t="n"/>
-      <c r="L2" s="2" t="n"/>
-      <c r="M2" s="2" t="n"/>
-      <c r="N2" s="2" t="n"/>
-      <c r="O2" s="2" t="n"/>
-      <c r="P2" s="2" t="inlineStr">
+      <c r="A2" s="5" t="inlineStr">
+        <is>
+          <t>2026-02-10 10:50:00</t>
+        </is>
+      </c>
+      <c r="B2" s="5" t="inlineStr">
+        <is>
+          <t>10:50:00</t>
+        </is>
+      </c>
+      <c r="C2" s="5" t="inlineStr">
+        <is>
+          <t>10:50</t>
+        </is>
+      </c>
+      <c r="D2" s="5" t="inlineStr">
+        <is>
+          <t>83.70</t>
+        </is>
+      </c>
+      <c r="E2" s="5" t="n"/>
+      <c r="F2" s="5" t="inlineStr">
+        <is>
+          <t>111.75</t>
+        </is>
+      </c>
+      <c r="G2" s="5" t="n"/>
+      <c r="H2" s="5" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="I2" s="5" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="J2" s="5" t="n"/>
+      <c r="K2" s="5" t="n"/>
+      <c r="L2" s="5" t="n"/>
+      <c r="M2" s="5" t="n"/>
+      <c r="N2" s="5" t="n"/>
+      <c r="O2" s="5" t="n"/>
+      <c r="P2" s="5" t="inlineStr">
+        <is>
+          <t>High Strike Check</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="5" t="inlineStr">
+        <is>
+          <t>2026-02-10 10:50:00</t>
+        </is>
+      </c>
+      <c r="B3" s="5" t="inlineStr">
+        <is>
+          <t>10:50:00</t>
+        </is>
+      </c>
+      <c r="C3" s="5" t="inlineStr">
+        <is>
+          <t>10:50</t>
+        </is>
+      </c>
+      <c r="D3" s="5" t="inlineStr">
+        <is>
+          <t>102.00</t>
+        </is>
+      </c>
+      <c r="E3" s="5" t="n"/>
+      <c r="F3" s="5" t="inlineStr">
+        <is>
+          <t>79.00</t>
+        </is>
+      </c>
+      <c r="G3" s="5" t="n"/>
+      <c r="H3" s="5" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="I3" s="5" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="J3" s="5" t="n"/>
+      <c r="K3" s="5" t="n"/>
+      <c r="L3" s="5" t="n"/>
+      <c r="M3" s="5" t="n"/>
+      <c r="N3" s="5" t="n"/>
+      <c r="O3" s="5" t="n"/>
+      <c r="P3" s="5" t="inlineStr">
         <is>
           <t>Low Strike Check</t>
         </is>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" s="2" t="inlineStr">
-        <is>
-          <t>2026-02-09 13:10:00</t>
-        </is>
-      </c>
-      <c r="B3" s="2" t="inlineStr">
-        <is>
-          <t>13:10:00</t>
-        </is>
-      </c>
-      <c r="C3" s="2" t="inlineStr">
-        <is>
-          <t>13:10</t>
-        </is>
-      </c>
-      <c r="D3" s="2" t="inlineStr">
-        <is>
-          <t>78.25</t>
-        </is>
-      </c>
-      <c r="E3" s="2" t="n"/>
-      <c r="F3" s="2" t="inlineStr">
-        <is>
-          <t>198.95</t>
-        </is>
-      </c>
-      <c r="G3" s="2" t="n"/>
-      <c r="H3" s="2" t="inlineStr">
-        <is>
-          <t>✗ NO</t>
-        </is>
-      </c>
-      <c r="I3" s="2" t="inlineStr">
-        <is>
-          <t>✗ NO</t>
-        </is>
-      </c>
-      <c r="J3" s="2" t="n"/>
-      <c r="K3" s="2" t="n"/>
-      <c r="L3" s="2" t="n"/>
-      <c r="M3" s="2" t="n"/>
-      <c r="N3" s="2" t="n"/>
-      <c r="O3" s="2" t="n"/>
-      <c r="P3" s="2" t="inlineStr">
+    <row r="4">
+      <c r="A4" s="6" t="inlineStr">
+        <is>
+          <t>2026-02-10 10:55:00</t>
+        </is>
+      </c>
+      <c r="B4" s="6" t="inlineStr">
+        <is>
+          <t>10:55:00</t>
+        </is>
+      </c>
+      <c r="C4" s="6" t="inlineStr">
+        <is>
+          <t>10:55</t>
+        </is>
+      </c>
+      <c r="D4" s="6" t="inlineStr">
+        <is>
+          <t>83.70</t>
+        </is>
+      </c>
+      <c r="E4" s="6" t="inlineStr"/>
+      <c r="F4" s="6" t="inlineStr">
+        <is>
+          <t>111.75</t>
+        </is>
+      </c>
+      <c r="G4" s="6" t="inlineStr"/>
+      <c r="H4" s="6" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="I4" s="6" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="J4" s="6" t="inlineStr"/>
+      <c r="K4" s="6" t="inlineStr"/>
+      <c r="L4" s="6" t="inlineStr"/>
+      <c r="M4" s="6" t="inlineStr"/>
+      <c r="N4" s="6" t="inlineStr"/>
+      <c r="O4" s="6" t="inlineStr"/>
+      <c r="P4" s="6" t="inlineStr">
         <is>
           <t>High Strike Check</t>
         </is>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" s="2" t="inlineStr">
-        <is>
-          <t>2026-02-09 13:10:00</t>
-        </is>
-      </c>
-      <c r="B4" s="2" t="inlineStr">
-        <is>
-          <t>13:10:00</t>
-        </is>
-      </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>13:10</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>155.00</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="n"/>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>99.00</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="n"/>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>✗ NO</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>✗ NO</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="n"/>
-      <c r="K4" s="2" t="n"/>
-      <c r="L4" s="2" t="n"/>
-      <c r="M4" s="2" t="n"/>
-      <c r="N4" s="2" t="n"/>
-      <c r="O4" s="2" t="n"/>
-      <c r="P4" s="2" t="inlineStr">
+    <row r="5">
+      <c r="A5" s="6" t="inlineStr">
+        <is>
+          <t>2026-02-10 10:55:00</t>
+        </is>
+      </c>
+      <c r="B5" s="6" t="inlineStr">
+        <is>
+          <t>10:55:00</t>
+        </is>
+      </c>
+      <c r="C5" s="6" t="inlineStr">
+        <is>
+          <t>10:55</t>
+        </is>
+      </c>
+      <c r="D5" s="6" t="inlineStr">
+        <is>
+          <t>102.00</t>
+        </is>
+      </c>
+      <c r="E5" s="6" t="inlineStr"/>
+      <c r="F5" s="6" t="inlineStr">
+        <is>
+          <t>79.00</t>
+        </is>
+      </c>
+      <c r="G5" s="6" t="inlineStr"/>
+      <c r="H5" s="6" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="I5" s="6" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="J5" s="6" t="inlineStr"/>
+      <c r="K5" s="6" t="inlineStr"/>
+      <c r="L5" s="6" t="inlineStr"/>
+      <c r="M5" s="6" t="inlineStr"/>
+      <c r="N5" s="6" t="inlineStr"/>
+      <c r="O5" s="6" t="inlineStr"/>
+      <c r="P5" s="6" t="inlineStr">
         <is>
           <t>Low Strike Check</t>
         </is>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" s="2" t="inlineStr">
-        <is>
-          <t>2026-02-09 13:15:00</t>
-        </is>
-      </c>
-      <c r="B5" s="2" t="inlineStr">
-        <is>
-          <t>13:15:00</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>13:15</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>78.25</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="n"/>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>198.95</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="n"/>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>✗ NO</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>✗ NO</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="n"/>
-      <c r="K5" s="2" t="n"/>
-      <c r="L5" s="2" t="n"/>
-      <c r="M5" s="2" t="n"/>
-      <c r="N5" s="2" t="n"/>
-      <c r="O5" s="2" t="n"/>
-      <c r="P5" s="2" t="inlineStr">
+    <row r="6">
+      <c r="A6" s="6" t="inlineStr">
+        <is>
+          <t>2026-02-10 11:00:00</t>
+        </is>
+      </c>
+      <c r="B6" s="6" t="inlineStr">
+        <is>
+          <t>11:00:00</t>
+        </is>
+      </c>
+      <c r="C6" s="6" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
+      <c r="D6" s="6" t="inlineStr">
+        <is>
+          <t>83.70</t>
+        </is>
+      </c>
+      <c r="E6" s="6" t="inlineStr"/>
+      <c r="F6" s="6" t="inlineStr">
+        <is>
+          <t>111.75</t>
+        </is>
+      </c>
+      <c r="G6" s="6" t="inlineStr"/>
+      <c r="H6" s="6" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="I6" s="6" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="J6" s="6" t="inlineStr"/>
+      <c r="K6" s="6" t="inlineStr"/>
+      <c r="L6" s="6" t="inlineStr"/>
+      <c r="M6" s="6" t="inlineStr"/>
+      <c r="N6" s="6" t="inlineStr"/>
+      <c r="O6" s="6" t="inlineStr"/>
+      <c r="P6" s="6" t="inlineStr">
         <is>
           <t>High Strike Check</t>
         </is>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" s="2" t="inlineStr">
-        <is>
-          <t>2026-02-09 13:15:00</t>
-        </is>
-      </c>
-      <c r="B6" s="2" t="inlineStr">
-        <is>
-          <t>13:15:00</t>
-        </is>
-      </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>13:15</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>155.00</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="n"/>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>99.00</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="n"/>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>✗ NO</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>✗ NO</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="n"/>
-      <c r="K6" s="2" t="n"/>
-      <c r="L6" s="2" t="n"/>
-      <c r="M6" s="2" t="n"/>
-      <c r="N6" s="2" t="n"/>
-      <c r="O6" s="2" t="n"/>
-      <c r="P6" s="2" t="inlineStr">
+    <row r="7">
+      <c r="A7" s="6" t="inlineStr">
+        <is>
+          <t>2026-02-10 11:00:00</t>
+        </is>
+      </c>
+      <c r="B7" s="6" t="inlineStr">
+        <is>
+          <t>11:00:00</t>
+        </is>
+      </c>
+      <c r="C7" s="6" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
+      <c r="D7" s="6" t="inlineStr">
+        <is>
+          <t>102.00</t>
+        </is>
+      </c>
+      <c r="E7" s="6" t="inlineStr"/>
+      <c r="F7" s="6" t="inlineStr">
+        <is>
+          <t>79.00</t>
+        </is>
+      </c>
+      <c r="G7" s="6" t="inlineStr"/>
+      <c r="H7" s="6" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="I7" s="6" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="J7" s="6" t="inlineStr"/>
+      <c r="K7" s="6" t="inlineStr"/>
+      <c r="L7" s="6" t="inlineStr"/>
+      <c r="M7" s="6" t="inlineStr"/>
+      <c r="N7" s="6" t="inlineStr"/>
+      <c r="O7" s="6" t="inlineStr"/>
+      <c r="P7" s="6" t="inlineStr">
         <is>
           <t>Low Strike Check</t>
         </is>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" s="2" t="inlineStr">
-        <is>
-          <t>2026-02-09 13:20:00</t>
-        </is>
-      </c>
-      <c r="B7" s="2" t="inlineStr">
-        <is>
-          <t>13:20:00</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>13:20</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="n"/>
-      <c r="E7" s="2" t="n"/>
-      <c r="F7" s="2" t="n"/>
-      <c r="G7" s="2" t="n"/>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>✗ NO</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>✗ NO</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="n"/>
-      <c r="K7" s="2" t="n"/>
-      <c r="L7" s="2" t="n"/>
-      <c r="M7" s="2" t="n"/>
-      <c r="N7" s="2" t="n"/>
-      <c r="O7" s="2" t="n"/>
-      <c r="P7" s="2" t="inlineStr">
-        <is>
-          <t>Failed to fetch data: Live data fetch timed out after 10s</t>
-        </is>
-      </c>
-    </row>
     <row r="8">
-      <c r="A8" s="2" t="inlineStr">
-        <is>
-          <t>2026-02-09 13:35:00</t>
-        </is>
-      </c>
-      <c r="B8" s="2" t="inlineStr">
-        <is>
-          <t>13:35:00</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>13:35</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>155.00</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="n"/>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>198.95</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="n"/>
-      <c r="H8" s="5" t="inlineStr">
-        <is>
-          <t>✓ YES</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>✗ NO</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>104.80</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="n"/>
-      <c r="L8" s="2" t="inlineStr">
+      <c r="A8" s="6" t="inlineStr">
+        <is>
+          <t>2026-02-10 11:05:00</t>
+        </is>
+      </c>
+      <c r="B8" s="6" t="inlineStr">
+        <is>
+          <t>11:05:00</t>
+        </is>
+      </c>
+      <c r="C8" s="6" t="inlineStr">
+        <is>
+          <t>11:05</t>
+        </is>
+      </c>
+      <c r="D8" s="6" t="inlineStr">
+        <is>
+          <t>83.70</t>
+        </is>
+      </c>
+      <c r="E8" s="6" t="inlineStr"/>
+      <c r="F8" s="6" t="inlineStr">
+        <is>
+          <t>111.75</t>
+        </is>
+      </c>
+      <c r="G8" s="6" t="inlineStr"/>
+      <c r="H8" s="6" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="I8" s="6" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="J8" s="6" t="inlineStr"/>
+      <c r="K8" s="6" t="inlineStr"/>
+      <c r="L8" s="6" t="inlineStr"/>
+      <c r="M8" s="6" t="inlineStr"/>
+      <c r="N8" s="6" t="inlineStr"/>
+      <c r="O8" s="6" t="inlineStr"/>
+      <c r="P8" s="6" t="inlineStr">
+        <is>
+          <t>High Strike Check</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="6" t="inlineStr">
+        <is>
+          <t>2026-02-10 11:05:00</t>
+        </is>
+      </c>
+      <c r="B9" s="6" t="inlineStr">
+        <is>
+          <t>11:05:00</t>
+        </is>
+      </c>
+      <c r="C9" s="6" t="inlineStr">
+        <is>
+          <t>11:05</t>
+        </is>
+      </c>
+      <c r="D9" s="6" t="inlineStr">
+        <is>
+          <t>102.00</t>
+        </is>
+      </c>
+      <c r="E9" s="6" t="inlineStr"/>
+      <c r="F9" s="6" t="inlineStr">
         <is>
           <t>79.00</t>
         </is>
       </c>
-      <c r="M8" s="2" t="n"/>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>156.40</t>
-        </is>
-      </c>
-      <c r="O8" s="2" t="n"/>
-      <c r="P8" s="2" t="inlineStr">
+      <c r="G9" s="6" t="inlineStr"/>
+      <c r="H9" s="6" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="I9" s="6" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="J9" s="6" t="inlineStr"/>
+      <c r="K9" s="6" t="inlineStr"/>
+      <c r="L9" s="6" t="inlineStr"/>
+      <c r="M9" s="6" t="inlineStr"/>
+      <c r="N9" s="6" t="inlineStr"/>
+      <c r="O9" s="6" t="inlineStr"/>
+      <c r="P9" s="6" t="inlineStr">
+        <is>
+          <t>Low Strike Check</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="6" t="inlineStr">
+        <is>
+          <t>2026-02-10 11:10:00</t>
+        </is>
+      </c>
+      <c r="B10" s="6" t="inlineStr">
+        <is>
+          <t>11:10:00</t>
+        </is>
+      </c>
+      <c r="C10" s="6" t="inlineStr">
+        <is>
+          <t>11:10</t>
+        </is>
+      </c>
+      <c r="D10" s="6" t="inlineStr">
+        <is>
+          <t>83.70</t>
+        </is>
+      </c>
+      <c r="E10" s="6" t="inlineStr"/>
+      <c r="F10" s="6" t="inlineStr">
+        <is>
+          <t>111.75</t>
+        </is>
+      </c>
+      <c r="G10" s="6" t="inlineStr"/>
+      <c r="H10" s="6" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="I10" s="6" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="J10" s="6" t="inlineStr"/>
+      <c r="K10" s="6" t="inlineStr"/>
+      <c r="L10" s="6" t="inlineStr"/>
+      <c r="M10" s="6" t="inlineStr"/>
+      <c r="N10" s="6" t="inlineStr"/>
+      <c r="O10" s="6" t="inlineStr"/>
+      <c r="P10" s="6" t="inlineStr">
         <is>
           <t>High Strike Check</t>
         </is>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" s="2" t="inlineStr">
-        <is>
-          <t>2026-02-09 13:35:00</t>
-        </is>
-      </c>
-      <c r="B9" s="2" t="inlineStr">
-        <is>
-          <t>13:35:00</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>13:35</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>155.00</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="n"/>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>99.00</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="n"/>
-      <c r="H9" s="5" t="inlineStr">
-        <is>
-          <t>✓ YES</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>✗ NO</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>104.80</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="n"/>
-      <c r="L9" s="2" t="inlineStr">
+    <row r="11">
+      <c r="A11" s="6" t="inlineStr">
+        <is>
+          <t>2026-02-10 11:10:00</t>
+        </is>
+      </c>
+      <c r="B11" s="6" t="inlineStr">
+        <is>
+          <t>11:10:00</t>
+        </is>
+      </c>
+      <c r="C11" s="6" t="inlineStr">
+        <is>
+          <t>11:10</t>
+        </is>
+      </c>
+      <c r="D11" s="6" t="inlineStr">
+        <is>
+          <t>102.00</t>
+        </is>
+      </c>
+      <c r="E11" s="6" t="inlineStr"/>
+      <c r="F11" s="6" t="inlineStr">
         <is>
           <t>79.00</t>
         </is>
       </c>
-      <c r="M9" s="2" t="n"/>
-      <c r="N9" s="2" t="inlineStr">
-        <is>
-          <t>156.40</t>
-        </is>
-      </c>
-      <c r="O9" s="2" t="n"/>
-      <c r="P9" s="2" t="inlineStr">
+      <c r="G11" s="6" t="inlineStr"/>
+      <c r="H11" s="6" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="I11" s="6" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="J11" s="6" t="inlineStr"/>
+      <c r="K11" s="6" t="inlineStr"/>
+      <c r="L11" s="6" t="inlineStr"/>
+      <c r="M11" s="6" t="inlineStr"/>
+      <c r="N11" s="6" t="inlineStr"/>
+      <c r="O11" s="6" t="inlineStr"/>
+      <c r="P11" s="6" t="inlineStr">
         <is>
           <t>Low Strike Check</t>
         </is>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" s="2" t="inlineStr">
-        <is>
-          <t>2026-02-09 13:40:00</t>
-        </is>
-      </c>
-      <c r="B10" s="2" t="inlineStr">
-        <is>
-          <t>13:40:00</t>
-        </is>
-      </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>13:40</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>78.25</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="n"/>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>198.95</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="n"/>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>✗ NO</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>✗ NO</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="n"/>
-      <c r="K10" s="2" t="n"/>
-      <c r="L10" s="2" t="n"/>
-      <c r="M10" s="2" t="n"/>
-      <c r="N10" s="2" t="n"/>
-      <c r="O10" s="2" t="n"/>
-      <c r="P10" s="2" t="inlineStr">
+    <row r="12">
+      <c r="A12" s="6" t="inlineStr">
+        <is>
+          <t>2026-02-10 11:15:00</t>
+        </is>
+      </c>
+      <c r="B12" s="6" t="inlineStr">
+        <is>
+          <t>11:15:00</t>
+        </is>
+      </c>
+      <c r="C12" s="6" t="inlineStr">
+        <is>
+          <t>11:15</t>
+        </is>
+      </c>
+      <c r="D12" s="6" t="inlineStr">
+        <is>
+          <t>83.70</t>
+        </is>
+      </c>
+      <c r="E12" s="6" t="inlineStr"/>
+      <c r="F12" s="6" t="inlineStr">
+        <is>
+          <t>111.75</t>
+        </is>
+      </c>
+      <c r="G12" s="6" t="inlineStr"/>
+      <c r="H12" s="6" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="I12" s="6" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="J12" s="6" t="inlineStr"/>
+      <c r="K12" s="6" t="inlineStr"/>
+      <c r="L12" s="6" t="inlineStr"/>
+      <c r="M12" s="6" t="inlineStr"/>
+      <c r="N12" s="6" t="inlineStr"/>
+      <c r="O12" s="6" t="inlineStr"/>
+      <c r="P12" s="6" t="inlineStr">
         <is>
           <t>High Strike Check</t>
         </is>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" s="2" t="inlineStr">
-        <is>
-          <t>2026-02-09 13:40:00</t>
-        </is>
-      </c>
-      <c r="B11" s="2" t="inlineStr">
-        <is>
-          <t>13:40:00</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>13:40</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>155.00</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="n"/>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>99.00</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="n"/>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>✗ NO</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>✗ NO</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="n"/>
-      <c r="K11" s="2" t="n"/>
-      <c r="L11" s="2" t="n"/>
-      <c r="M11" s="2" t="n"/>
-      <c r="N11" s="2" t="n"/>
-      <c r="O11" s="2" t="n"/>
-      <c r="P11" s="2" t="inlineStr">
+    <row r="13">
+      <c r="A13" s="6" t="inlineStr">
+        <is>
+          <t>2026-02-10 11:15:00</t>
+        </is>
+      </c>
+      <c r="B13" s="6" t="inlineStr">
+        <is>
+          <t>11:15:00</t>
+        </is>
+      </c>
+      <c r="C13" s="6" t="inlineStr">
+        <is>
+          <t>11:15</t>
+        </is>
+      </c>
+      <c r="D13" s="6" t="inlineStr">
+        <is>
+          <t>102.00</t>
+        </is>
+      </c>
+      <c r="E13" s="6" t="inlineStr"/>
+      <c r="F13" s="6" t="inlineStr">
+        <is>
+          <t>79.00</t>
+        </is>
+      </c>
+      <c r="G13" s="6" t="inlineStr"/>
+      <c r="H13" s="6" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="I13" s="6" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="J13" s="6" t="inlineStr"/>
+      <c r="K13" s="6" t="inlineStr"/>
+      <c r="L13" s="6" t="inlineStr"/>
+      <c r="M13" s="6" t="inlineStr"/>
+      <c r="N13" s="6" t="inlineStr"/>
+      <c r="O13" s="6" t="inlineStr"/>
+      <c r="P13" s="6" t="inlineStr">
         <is>
           <t>Low Strike Check</t>
         </is>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" s="2" t="inlineStr">
-        <is>
-          <t>2026-02-09 13:45:00</t>
-        </is>
-      </c>
-      <c r="B12" s="2" t="inlineStr">
-        <is>
-          <t>13:45:00</t>
-        </is>
-      </c>
-      <c r="C12" s="2" t="inlineStr">
-        <is>
-          <t>13:45</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="n"/>
-      <c r="E12" s="2" t="n"/>
-      <c r="F12" s="2" t="n"/>
-      <c r="G12" s="2" t="n"/>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>✗ NO</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>✗ NO</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="n"/>
-      <c r="K12" s="2" t="n"/>
-      <c r="L12" s="2" t="n"/>
-      <c r="M12" s="2" t="n"/>
-      <c r="N12" s="2" t="n"/>
-      <c r="O12" s="2" t="n"/>
-      <c r="P12" s="2" t="inlineStr">
-        <is>
-          <t>Failed to fetch data: Live data fetch timed out after 10s</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="2" t="inlineStr">
-        <is>
-          <t>2026-02-09 13:50:00</t>
-        </is>
-      </c>
-      <c r="B13" s="2" t="inlineStr">
-        <is>
-          <t>13:50:00</t>
-        </is>
-      </c>
-      <c r="C13" s="2" t="inlineStr">
-        <is>
-          <t>13:50</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="n"/>
-      <c r="E13" s="2" t="n"/>
-      <c r="F13" s="2" t="n"/>
-      <c r="G13" s="2" t="n"/>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>✗ NO</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>✗ NO</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="n"/>
-      <c r="K13" s="2" t="n"/>
-      <c r="L13" s="2" t="n"/>
-      <c r="M13" s="2" t="n"/>
-      <c r="N13" s="2" t="n"/>
-      <c r="O13" s="2" t="n"/>
-      <c r="P13" s="2" t="inlineStr">
-        <is>
-          <t>Failed to fetch data: Live data fetch timed out after 10s</t>
-        </is>
-      </c>
-    </row>
     <row r="14">
-      <c r="A14" s="2" t="inlineStr">
-        <is>
-          <t>2026-02-09 13:55:00</t>
-        </is>
-      </c>
-      <c r="B14" s="2" t="inlineStr">
-        <is>
-          <t>13:55:00</t>
-        </is>
-      </c>
-      <c r="C14" s="2" t="inlineStr">
-        <is>
-          <t>13:55</t>
-        </is>
-      </c>
-      <c r="D14" s="2" t="n"/>
-      <c r="E14" s="2" t="n"/>
-      <c r="F14" s="2" t="n"/>
-      <c r="G14" s="2" t="n"/>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>✗ NO</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>✗ NO</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="n"/>
-      <c r="K14" s="2" t="n"/>
-      <c r="L14" s="2" t="n"/>
-      <c r="M14" s="2" t="n"/>
-      <c r="N14" s="2" t="n"/>
-      <c r="O14" s="2" t="n"/>
-      <c r="P14" s="2" t="inlineStr">
-        <is>
-          <t>Failed to fetch data: Live data fetch timed out after 10s</t>
+      <c r="A14" s="6" t="inlineStr">
+        <is>
+          <t>2026-02-10 11:20:00</t>
+        </is>
+      </c>
+      <c r="B14" s="6" t="inlineStr">
+        <is>
+          <t>11:20:00</t>
+        </is>
+      </c>
+      <c r="C14" s="6" t="inlineStr">
+        <is>
+          <t>11:20</t>
+        </is>
+      </c>
+      <c r="D14" s="6" t="inlineStr">
+        <is>
+          <t>83.70</t>
+        </is>
+      </c>
+      <c r="E14" s="6" t="inlineStr"/>
+      <c r="F14" s="6" t="inlineStr">
+        <is>
+          <t>111.75</t>
+        </is>
+      </c>
+      <c r="G14" s="6" t="inlineStr"/>
+      <c r="H14" s="6" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="I14" s="6" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="J14" s="6" t="inlineStr"/>
+      <c r="K14" s="6" t="inlineStr"/>
+      <c r="L14" s="6" t="inlineStr"/>
+      <c r="M14" s="6" t="inlineStr"/>
+      <c r="N14" s="6" t="inlineStr"/>
+      <c r="O14" s="6" t="inlineStr"/>
+      <c r="P14" s="6" t="inlineStr">
+        <is>
+          <t>High Strike Check</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="2" t="inlineStr">
-        <is>
-          <t>2026-02-09 14:00:00</t>
-        </is>
-      </c>
-      <c r="B15" s="2" t="inlineStr">
-        <is>
-          <t>14:00:00</t>
-        </is>
-      </c>
-      <c r="C15" s="2" t="inlineStr">
-        <is>
-          <t>14:00</t>
-        </is>
-      </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>78.25</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="n"/>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>198.95</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="n"/>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>✗ NO</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>✗ NO</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="n"/>
-      <c r="K15" s="2" t="n"/>
-      <c r="L15" s="2" t="n"/>
-      <c r="M15" s="2" t="n"/>
-      <c r="N15" s="2" t="n"/>
-      <c r="O15" s="2" t="n"/>
-      <c r="P15" s="2" t="inlineStr">
+      <c r="A15" s="6" t="inlineStr">
+        <is>
+          <t>2026-02-10 11:20:00</t>
+        </is>
+      </c>
+      <c r="B15" s="6" t="inlineStr">
+        <is>
+          <t>11:20:00</t>
+        </is>
+      </c>
+      <c r="C15" s="6" t="inlineStr">
+        <is>
+          <t>11:20</t>
+        </is>
+      </c>
+      <c r="D15" s="6" t="inlineStr">
+        <is>
+          <t>102.00</t>
+        </is>
+      </c>
+      <c r="E15" s="6" t="inlineStr"/>
+      <c r="F15" s="6" t="inlineStr">
+        <is>
+          <t>79.00</t>
+        </is>
+      </c>
+      <c r="G15" s="6" t="inlineStr"/>
+      <c r="H15" s="6" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="I15" s="6" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="J15" s="6" t="inlineStr"/>
+      <c r="K15" s="6" t="inlineStr"/>
+      <c r="L15" s="6" t="inlineStr"/>
+      <c r="M15" s="6" t="inlineStr"/>
+      <c r="N15" s="6" t="inlineStr"/>
+      <c r="O15" s="6" t="inlineStr"/>
+      <c r="P15" s="6" t="inlineStr">
+        <is>
+          <t>Low Strike Check</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="6" t="inlineStr">
+        <is>
+          <t>2026-02-10 11:25:00</t>
+        </is>
+      </c>
+      <c r="B16" s="6" t="inlineStr">
+        <is>
+          <t>11:25:00</t>
+        </is>
+      </c>
+      <c r="C16" s="6" t="inlineStr">
+        <is>
+          <t>11:25</t>
+        </is>
+      </c>
+      <c r="D16" s="6" t="inlineStr">
+        <is>
+          <t>83.70</t>
+        </is>
+      </c>
+      <c r="E16" s="6" t="inlineStr"/>
+      <c r="F16" s="6" t="inlineStr">
+        <is>
+          <t>111.75</t>
+        </is>
+      </c>
+      <c r="G16" s="6" t="inlineStr"/>
+      <c r="H16" s="6" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="I16" s="6" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="J16" s="6" t="inlineStr"/>
+      <c r="K16" s="6" t="inlineStr"/>
+      <c r="L16" s="6" t="inlineStr"/>
+      <c r="M16" s="6" t="inlineStr"/>
+      <c r="N16" s="6" t="inlineStr"/>
+      <c r="O16" s="6" t="inlineStr"/>
+      <c r="P16" s="6" t="inlineStr">
         <is>
           <t>High Strike Check</t>
         </is>
       </c>
     </row>
-    <row r="16">
-      <c r="A16" s="2" t="inlineStr">
-        <is>
-          <t>2026-02-09 14:00:00</t>
-        </is>
-      </c>
-      <c r="B16" s="2" t="inlineStr">
-        <is>
-          <t>14:00:00</t>
-        </is>
-      </c>
-      <c r="C16" s="2" t="inlineStr">
-        <is>
-          <t>14:00</t>
-        </is>
-      </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>155.00</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="n"/>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>99.00</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="n"/>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>✗ NO</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>✗ NO</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="n"/>
-      <c r="K16" s="2" t="n"/>
-      <c r="L16" s="2" t="n"/>
-      <c r="M16" s="2" t="n"/>
-      <c r="N16" s="2" t="n"/>
-      <c r="O16" s="2" t="n"/>
-      <c r="P16" s="2" t="inlineStr">
+    <row r="17">
+      <c r="A17" s="6" t="inlineStr">
+        <is>
+          <t>2026-02-10 11:25:00</t>
+        </is>
+      </c>
+      <c r="B17" s="6" t="inlineStr">
+        <is>
+          <t>11:25:00</t>
+        </is>
+      </c>
+      <c r="C17" s="6" t="inlineStr">
+        <is>
+          <t>11:25</t>
+        </is>
+      </c>
+      <c r="D17" s="6" t="inlineStr">
+        <is>
+          <t>102.00</t>
+        </is>
+      </c>
+      <c r="E17" s="6" t="inlineStr"/>
+      <c r="F17" s="6" t="inlineStr">
+        <is>
+          <t>79.00</t>
+        </is>
+      </c>
+      <c r="G17" s="6" t="inlineStr"/>
+      <c r="H17" s="6" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="I17" s="6" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="J17" s="6" t="inlineStr"/>
+      <c r="K17" s="6" t="inlineStr"/>
+      <c r="L17" s="6" t="inlineStr"/>
+      <c r="M17" s="6" t="inlineStr"/>
+      <c r="N17" s="6" t="inlineStr"/>
+      <c r="O17" s="6" t="inlineStr"/>
+      <c r="P17" s="6" t="inlineStr">
         <is>
           <t>Low Strike Check</t>
         </is>
       </c>
     </row>
-    <row r="17">
-      <c r="A17" s="2" t="inlineStr">
-        <is>
-          <t>2026-02-09 14:05:00</t>
-        </is>
-      </c>
-      <c r="B17" s="2" t="inlineStr">
-        <is>
-          <t>14:05:00</t>
-        </is>
-      </c>
-      <c r="C17" s="2" t="inlineStr">
-        <is>
-          <t>14:05</t>
-        </is>
-      </c>
-      <c r="D17" s="2" t="n"/>
-      <c r="E17" s="2" t="n"/>
-      <c r="F17" s="2" t="n"/>
-      <c r="G17" s="2" t="n"/>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>✗ NO</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>✗ NO</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="n"/>
-      <c r="K17" s="2" t="n"/>
-      <c r="L17" s="2" t="n"/>
-      <c r="M17" s="2" t="n"/>
-      <c r="N17" s="2" t="n"/>
-      <c r="O17" s="2" t="n"/>
-      <c r="P17" s="2" t="inlineStr">
-        <is>
-          <t>Failed to fetch data: Live data fetch timed out after 10s</t>
-        </is>
-      </c>
-    </row>
     <row r="18">
-      <c r="A18" s="2" t="inlineStr">
-        <is>
-          <t>2026-02-10 09:15:00</t>
-        </is>
-      </c>
-      <c r="B18" s="2" t="inlineStr">
-        <is>
-          <t>09:15:00</t>
-        </is>
-      </c>
-      <c r="C18" s="2" t="inlineStr">
-        <is>
-          <t>09:15</t>
-        </is>
-      </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="A18" s="6" t="inlineStr">
+        <is>
+          <t>2026-02-10 11:30:00</t>
+        </is>
+      </c>
+      <c r="B18" s="6" t="inlineStr">
+        <is>
+          <t>11:30:00</t>
+        </is>
+      </c>
+      <c r="C18" s="6" t="inlineStr">
+        <is>
+          <t>11:30</t>
+        </is>
+      </c>
+      <c r="D18" s="6" t="inlineStr">
         <is>
           <t>83.70</t>
         </is>
       </c>
-      <c r="E18" s="2" t="n"/>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>111.10</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="n"/>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>✗ NO</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>✗ NO</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="n"/>
-      <c r="K18" s="2" t="n"/>
-      <c r="L18" s="2" t="n"/>
-      <c r="M18" s="2" t="n"/>
-      <c r="N18" s="2" t="n"/>
-      <c r="O18" s="2" t="n"/>
-      <c r="P18" s="2" t="inlineStr">
+      <c r="E18" s="6" t="inlineStr"/>
+      <c r="F18" s="6" t="inlineStr">
+        <is>
+          <t>111.75</t>
+        </is>
+      </c>
+      <c r="G18" s="6" t="inlineStr"/>
+      <c r="H18" s="6" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="I18" s="6" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="J18" s="6" t="inlineStr"/>
+      <c r="K18" s="6" t="inlineStr"/>
+      <c r="L18" s="6" t="inlineStr"/>
+      <c r="M18" s="6" t="inlineStr"/>
+      <c r="N18" s="6" t="inlineStr"/>
+      <c r="O18" s="6" t="inlineStr"/>
+      <c r="P18" s="6" t="inlineStr">
         <is>
           <t>High Strike Check</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="2" t="inlineStr">
-        <is>
-          <t>2026-02-10 09:15:00</t>
-        </is>
-      </c>
-      <c r="B19" s="2" t="inlineStr">
-        <is>
-          <t>09:15:00</t>
-        </is>
-      </c>
-      <c r="C19" s="2" t="inlineStr">
-        <is>
-          <t>09:15</t>
-        </is>
-      </c>
-      <c r="D19" s="2" t="inlineStr">
-        <is>
-          <t>130.00</t>
-        </is>
-      </c>
-      <c r="E19" s="2" t="n"/>
-      <c r="F19" s="2" t="inlineStr">
-        <is>
-          <t>34.00</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="n"/>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t>✗ NO</t>
-        </is>
-      </c>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>✗ NO</t>
-        </is>
-      </c>
-      <c r="J19" s="2" t="n"/>
-      <c r="K19" s="2" t="n"/>
-      <c r="L19" s="2" t="n"/>
-      <c r="M19" s="2" t="n"/>
-      <c r="N19" s="2" t="n"/>
-      <c r="O19" s="2" t="n"/>
-      <c r="P19" s="2" t="inlineStr">
+      <c r="A19" s="6" t="inlineStr">
+        <is>
+          <t>2026-02-10 11:30:00</t>
+        </is>
+      </c>
+      <c r="B19" s="6" t="inlineStr">
+        <is>
+          <t>11:30:00</t>
+        </is>
+      </c>
+      <c r="C19" s="6" t="inlineStr">
+        <is>
+          <t>11:30</t>
+        </is>
+      </c>
+      <c r="D19" s="6" t="inlineStr">
+        <is>
+          <t>102.00</t>
+        </is>
+      </c>
+      <c r="E19" s="6" t="inlineStr"/>
+      <c r="F19" s="6" t="inlineStr">
+        <is>
+          <t>79.00</t>
+        </is>
+      </c>
+      <c r="G19" s="6" t="inlineStr"/>
+      <c r="H19" s="6" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="I19" s="6" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="J19" s="6" t="inlineStr"/>
+      <c r="K19" s="6" t="inlineStr"/>
+      <c r="L19" s="6" t="inlineStr"/>
+      <c r="M19" s="6" t="inlineStr"/>
+      <c r="N19" s="6" t="inlineStr"/>
+      <c r="O19" s="6" t="inlineStr"/>
+      <c r="P19" s="6" t="inlineStr">
         <is>
           <t>Low Strike Check</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="2" t="inlineStr">
-        <is>
-          <t>2026-02-10 09:20:00</t>
-        </is>
-      </c>
-      <c r="B20" s="2" t="inlineStr">
-        <is>
-          <t>09:20:00</t>
-        </is>
-      </c>
-      <c r="C20" s="2" t="inlineStr">
-        <is>
-          <t>09:20</t>
-        </is>
-      </c>
-      <c r="D20" s="2" t="n"/>
-      <c r="E20" s="2" t="n"/>
-      <c r="F20" s="2" t="n"/>
-      <c r="G20" s="2" t="n"/>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>✗ NO</t>
-        </is>
-      </c>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>✗ NO</t>
-        </is>
-      </c>
-      <c r="J20" s="2" t="n"/>
-      <c r="K20" s="2" t="n"/>
-      <c r="L20" s="2" t="n"/>
-      <c r="M20" s="2" t="n"/>
-      <c r="N20" s="2" t="n"/>
-      <c r="O20" s="2" t="n"/>
-      <c r="P20" s="2" t="inlineStr">
-        <is>
-          <t>Failed to fetch data: Error fetching quote: ('Connection aborted.', ConnectionResetError(54, 'Connection reset by peer'))</t>
+      <c r="A20" s="6" t="inlineStr">
+        <is>
+          <t>2026-02-10 11:35:00</t>
+        </is>
+      </c>
+      <c r="B20" s="6" t="inlineStr">
+        <is>
+          <t>11:35:00</t>
+        </is>
+      </c>
+      <c r="C20" s="6" t="inlineStr">
+        <is>
+          <t>11:35</t>
+        </is>
+      </c>
+      <c r="D20" s="6" t="inlineStr">
+        <is>
+          <t>83.70</t>
+        </is>
+      </c>
+      <c r="E20" s="6" t="inlineStr"/>
+      <c r="F20" s="6" t="inlineStr">
+        <is>
+          <t>111.75</t>
+        </is>
+      </c>
+      <c r="G20" s="6" t="inlineStr"/>
+      <c r="H20" s="6" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="I20" s="6" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="J20" s="6" t="inlineStr"/>
+      <c r="K20" s="6" t="inlineStr"/>
+      <c r="L20" s="6" t="inlineStr"/>
+      <c r="M20" s="6" t="inlineStr"/>
+      <c r="N20" s="6" t="inlineStr"/>
+      <c r="O20" s="6" t="inlineStr"/>
+      <c r="P20" s="6" t="inlineStr">
+        <is>
+          <t>High Strike Check</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="6" t="inlineStr">
         <is>
-          <t>2026-02-10 09:25:00</t>
+          <t>2026-02-10 11:35:00</t>
         </is>
       </c>
       <c r="B21" s="6" t="inlineStr">
         <is>
-          <t>09:25:00</t>
+          <t>11:35:00</t>
         </is>
       </c>
       <c r="C21" s="6" t="inlineStr">
         <is>
-          <t>09:25</t>
-        </is>
-      </c>
-      <c r="D21" s="6" t="inlineStr"/>
+          <t>11:35</t>
+        </is>
+      </c>
+      <c r="D21" s="6" t="inlineStr">
+        <is>
+          <t>102.00</t>
+        </is>
+      </c>
       <c r="E21" s="6" t="inlineStr"/>
-      <c r="F21" s="6" t="inlineStr"/>
+      <c r="F21" s="6" t="inlineStr">
+        <is>
+          <t>79.00</t>
+        </is>
+      </c>
       <c r="G21" s="6" t="inlineStr"/>
       <c r="H21" s="6" t="inlineStr">
         <is>
@@ -1542,24 +1583,24 @@
       <c r="O21" s="6" t="inlineStr"/>
       <c r="P21" s="6" t="inlineStr">
         <is>
-          <t>Failed to fetch data: Live data fetch timed out after 10s</t>
+          <t>Low Strike Check</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="6" t="inlineStr">
         <is>
-          <t>2026-02-10 09:30:00</t>
+          <t>2026-02-10 11:40:00</t>
         </is>
       </c>
       <c r="B22" s="6" t="inlineStr">
         <is>
-          <t>09:30:00</t>
+          <t>11:40:00</t>
         </is>
       </c>
       <c r="C22" s="6" t="inlineStr">
         <is>
-          <t>09:30</t>
+          <t>11:40</t>
         </is>
       </c>
       <c r="D22" s="6" t="inlineStr">
@@ -1599,17 +1640,17 @@
     <row r="23">
       <c r="A23" s="6" t="inlineStr">
         <is>
-          <t>2026-02-10 09:30:00</t>
+          <t>2026-02-10 11:40:00</t>
         </is>
       </c>
       <c r="B23" s="6" t="inlineStr">
         <is>
-          <t>09:30:00</t>
+          <t>11:40:00</t>
         </is>
       </c>
       <c r="C23" s="6" t="inlineStr">
         <is>
-          <t>09:30</t>
+          <t>11:40</t>
         </is>
       </c>
       <c r="D23" s="6" t="inlineStr">
@@ -1649,22 +1690,30 @@
     <row r="24">
       <c r="A24" s="6" t="inlineStr">
         <is>
-          <t>2026-02-10 09:35:00</t>
+          <t>2026-02-10 11:45:00</t>
         </is>
       </c>
       <c r="B24" s="6" t="inlineStr">
         <is>
-          <t>09:35:00</t>
+          <t>11:45:00</t>
         </is>
       </c>
       <c r="C24" s="6" t="inlineStr">
         <is>
-          <t>09:35</t>
-        </is>
-      </c>
-      <c r="D24" s="6" t="inlineStr"/>
+          <t>11:45</t>
+        </is>
+      </c>
+      <c r="D24" s="6" t="inlineStr">
+        <is>
+          <t>83.70</t>
+        </is>
+      </c>
       <c r="E24" s="6" t="inlineStr"/>
-      <c r="F24" s="6" t="inlineStr"/>
+      <c r="F24" s="6" t="inlineStr">
+        <is>
+          <t>111.75</t>
+        </is>
+      </c>
       <c r="G24" s="6" t="inlineStr"/>
       <c r="H24" s="6" t="inlineStr">
         <is>
@@ -1684,35 +1733,35 @@
       <c r="O24" s="6" t="inlineStr"/>
       <c r="P24" s="6" t="inlineStr">
         <is>
-          <t>Failed to fetch data: Live data fetch timed out after 10s</t>
+          <t>High Strike Check</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="6" t="inlineStr">
         <is>
-          <t>2026-02-10 09:35:00</t>
+          <t>2026-02-10 11:45:00</t>
         </is>
       </c>
       <c r="B25" s="6" t="inlineStr">
         <is>
-          <t>09:35:00</t>
+          <t>11:45:00</t>
         </is>
       </c>
       <c r="C25" s="6" t="inlineStr">
         <is>
-          <t>09:35</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="D25" s="6" t="inlineStr">
         <is>
-          <t>83.70</t>
+          <t>102.00</t>
         </is>
       </c>
       <c r="E25" s="6" t="inlineStr"/>
       <c r="F25" s="6" t="inlineStr">
         <is>
-          <t>111.75</t>
+          <t>79.00</t>
         </is>
       </c>
       <c r="G25" s="6" t="inlineStr"/>
@@ -1734,35 +1783,35 @@
       <c r="O25" s="6" t="inlineStr"/>
       <c r="P25" s="6" t="inlineStr">
         <is>
-          <t>High Strike Check</t>
+          <t>Low Strike Check</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="6" t="inlineStr">
         <is>
-          <t>2026-02-10 09:35:00</t>
+          <t>2026-02-10 11:50:00</t>
         </is>
       </c>
       <c r="B26" s="6" t="inlineStr">
         <is>
-          <t>09:35:00</t>
+          <t>11:50:00</t>
         </is>
       </c>
       <c r="C26" s="6" t="inlineStr">
         <is>
-          <t>09:35</t>
+          <t>11:50</t>
         </is>
       </c>
       <c r="D26" s="6" t="inlineStr">
         <is>
-          <t>102.00</t>
+          <t>83.70</t>
         </is>
       </c>
       <c r="E26" s="6" t="inlineStr"/>
       <c r="F26" s="6" t="inlineStr">
         <is>
-          <t>79.00</t>
+          <t>111.75</t>
         </is>
       </c>
       <c r="G26" s="6" t="inlineStr"/>
@@ -1784,29 +1833,37 @@
       <c r="O26" s="6" t="inlineStr"/>
       <c r="P26" s="6" t="inlineStr">
         <is>
-          <t>Low Strike Check</t>
+          <t>High Strike Check</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="6" t="inlineStr">
         <is>
-          <t>2026-02-10 09:40:00</t>
+          <t>2026-02-10 11:50:00</t>
         </is>
       </c>
       <c r="B27" s="6" t="inlineStr">
         <is>
-          <t>09:40:00</t>
+          <t>11:50:00</t>
         </is>
       </c>
       <c r="C27" s="6" t="inlineStr">
         <is>
-          <t>09:40</t>
-        </is>
-      </c>
-      <c r="D27" s="6" t="inlineStr"/>
+          <t>11:50</t>
+        </is>
+      </c>
+      <c r="D27" s="6" t="inlineStr">
+        <is>
+          <t>102.00</t>
+        </is>
+      </c>
       <c r="E27" s="6" t="inlineStr"/>
-      <c r="F27" s="6" t="inlineStr"/>
+      <c r="F27" s="6" t="inlineStr">
+        <is>
+          <t>79.00</t>
+        </is>
+      </c>
       <c r="G27" s="6" t="inlineStr"/>
       <c r="H27" s="6" t="inlineStr">
         <is>
@@ -1826,29 +1883,37 @@
       <c r="O27" s="6" t="inlineStr"/>
       <c r="P27" s="6" t="inlineStr">
         <is>
-          <t>Failed to fetch data: Live data fetch timed out after 10s</t>
+          <t>Low Strike Check</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="6" t="inlineStr">
         <is>
-          <t>2026-02-10 09:45:00</t>
+          <t>2026-02-10 11:55:00</t>
         </is>
       </c>
       <c r="B28" s="6" t="inlineStr">
         <is>
-          <t>09:45:00</t>
+          <t>11:55:00</t>
         </is>
       </c>
       <c r="C28" s="6" t="inlineStr">
         <is>
-          <t>09:45</t>
-        </is>
-      </c>
-      <c r="D28" s="6" t="inlineStr"/>
+          <t>11:55</t>
+        </is>
+      </c>
+      <c r="D28" s="6" t="inlineStr">
+        <is>
+          <t>83.70</t>
+        </is>
+      </c>
       <c r="E28" s="6" t="inlineStr"/>
-      <c r="F28" s="6" t="inlineStr"/>
+      <c r="F28" s="6" t="inlineStr">
+        <is>
+          <t>111.75</t>
+        </is>
+      </c>
       <c r="G28" s="6" t="inlineStr"/>
       <c r="H28" s="6" t="inlineStr">
         <is>
@@ -1868,35 +1933,35 @@
       <c r="O28" s="6" t="inlineStr"/>
       <c r="P28" s="6" t="inlineStr">
         <is>
-          <t>Failed to fetch data: Live data fetch timed out after 10s</t>
+          <t>High Strike Check</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="6" t="inlineStr">
         <is>
-          <t>2026-02-10 09:50:00</t>
+          <t>2026-02-10 11:55:00</t>
         </is>
       </c>
       <c r="B29" s="6" t="inlineStr">
         <is>
-          <t>09:50:00</t>
+          <t>11:55:00</t>
         </is>
       </c>
       <c r="C29" s="6" t="inlineStr">
         <is>
-          <t>09:50</t>
+          <t>11:55</t>
         </is>
       </c>
       <c r="D29" s="6" t="inlineStr">
         <is>
-          <t>83.70</t>
+          <t>102.00</t>
         </is>
       </c>
       <c r="E29" s="6" t="inlineStr"/>
       <c r="F29" s="6" t="inlineStr">
         <is>
-          <t>111.75</t>
+          <t>79.00</t>
         </is>
       </c>
       <c r="G29" s="6" t="inlineStr"/>
@@ -1918,35 +1983,35 @@
       <c r="O29" s="6" t="inlineStr"/>
       <c r="P29" s="6" t="inlineStr">
         <is>
-          <t>High Strike Check</t>
+          <t>Low Strike Check</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="6" t="inlineStr">
         <is>
-          <t>2026-02-10 09:50:00</t>
+          <t>2026-02-10 12:00:00</t>
         </is>
       </c>
       <c r="B30" s="6" t="inlineStr">
         <is>
-          <t>09:50:00</t>
+          <t>12:00:00</t>
         </is>
       </c>
       <c r="C30" s="6" t="inlineStr">
         <is>
-          <t>09:50</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="D30" s="6" t="inlineStr">
         <is>
-          <t>102.00</t>
+          <t>83.70</t>
         </is>
       </c>
       <c r="E30" s="6" t="inlineStr"/>
       <c r="F30" s="6" t="inlineStr">
         <is>
-          <t>79.00</t>
+          <t>111.75</t>
         </is>
       </c>
       <c r="G30" s="6" t="inlineStr"/>
@@ -1968,35 +2033,35 @@
       <c r="O30" s="6" t="inlineStr"/>
       <c r="P30" s="6" t="inlineStr">
         <is>
-          <t>Low Strike Check</t>
+          <t>High Strike Check</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="6" t="inlineStr">
         <is>
-          <t>2026-02-10 09:55:00</t>
+          <t>2026-02-10 12:00:00</t>
         </is>
       </c>
       <c r="B31" s="6" t="inlineStr">
         <is>
-          <t>09:55:00</t>
+          <t>12:00:00</t>
         </is>
       </c>
       <c r="C31" s="6" t="inlineStr">
         <is>
-          <t>09:55</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="D31" s="6" t="inlineStr">
         <is>
-          <t>83.70</t>
+          <t>102.00</t>
         </is>
       </c>
       <c r="E31" s="6" t="inlineStr"/>
       <c r="F31" s="6" t="inlineStr">
         <is>
-          <t>111.75</t>
+          <t>79.00</t>
         </is>
       </c>
       <c r="G31" s="6" t="inlineStr"/>
@@ -2018,37 +2083,29 @@
       <c r="O31" s="6" t="inlineStr"/>
       <c r="P31" s="6" t="inlineStr">
         <is>
-          <t>High Strike Check</t>
+          <t>Low Strike Check</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="6" t="inlineStr">
         <is>
-          <t>2026-02-10 09:55:00</t>
+          <t>2026-02-10 12:05:00</t>
         </is>
       </c>
       <c r="B32" s="6" t="inlineStr">
         <is>
-          <t>09:55:00</t>
+          <t>12:05:00</t>
         </is>
       </c>
       <c r="C32" s="6" t="inlineStr">
         <is>
-          <t>09:55</t>
-        </is>
-      </c>
-      <c r="D32" s="6" t="inlineStr">
-        <is>
-          <t>102.00</t>
-        </is>
-      </c>
+          <t>12:05</t>
+        </is>
+      </c>
+      <c r="D32" s="6" t="inlineStr"/>
       <c r="E32" s="6" t="inlineStr"/>
-      <c r="F32" s="6" t="inlineStr">
-        <is>
-          <t>79.00</t>
-        </is>
-      </c>
+      <c r="F32" s="6" t="inlineStr"/>
       <c r="G32" s="6" t="inlineStr"/>
       <c r="H32" s="6" t="inlineStr">
         <is>
@@ -2068,29 +2125,37 @@
       <c r="O32" s="6" t="inlineStr"/>
       <c r="P32" s="6" t="inlineStr">
         <is>
-          <t>Low Strike Check</t>
+          <t>Failed to fetch data: Live data fetch timed out after 20s - possible API or network issue</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="6" t="inlineStr">
         <is>
-          <t>2026-02-10 10:00:00</t>
+          <t>2026-02-10 12:10:00</t>
         </is>
       </c>
       <c r="B33" s="6" t="inlineStr">
         <is>
-          <t>10:00:00</t>
+          <t>12:10:00</t>
         </is>
       </c>
       <c r="C33" s="6" t="inlineStr">
         <is>
-          <t>10:00</t>
-        </is>
-      </c>
-      <c r="D33" s="6" t="inlineStr"/>
+          <t>12:10</t>
+        </is>
+      </c>
+      <c r="D33" s="6" t="inlineStr">
+        <is>
+          <t>83.70</t>
+        </is>
+      </c>
       <c r="E33" s="6" t="inlineStr"/>
-      <c r="F33" s="6" t="inlineStr"/>
+      <c r="F33" s="6" t="inlineStr">
+        <is>
+          <t>111.75</t>
+        </is>
+      </c>
       <c r="G33" s="6" t="inlineStr"/>
       <c r="H33" s="6" t="inlineStr">
         <is>
@@ -2110,29 +2175,37 @@
       <c r="O33" s="6" t="inlineStr"/>
       <c r="P33" s="6" t="inlineStr">
         <is>
-          <t>Failed to fetch data: Live data fetch timed out after 10s</t>
+          <t>High Strike Check</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="6" t="inlineStr">
         <is>
-          <t>2026-02-10 10:05:00</t>
+          <t>2026-02-10 12:10:00</t>
         </is>
       </c>
       <c r="B34" s="6" t="inlineStr">
         <is>
-          <t>10:05:00</t>
+          <t>12:10:00</t>
         </is>
       </c>
       <c r="C34" s="6" t="inlineStr">
         <is>
-          <t>10:05</t>
-        </is>
-      </c>
-      <c r="D34" s="6" t="inlineStr"/>
+          <t>12:10</t>
+        </is>
+      </c>
+      <c r="D34" s="6" t="inlineStr">
+        <is>
+          <t>102.00</t>
+        </is>
+      </c>
       <c r="E34" s="6" t="inlineStr"/>
-      <c r="F34" s="6" t="inlineStr"/>
+      <c r="F34" s="6" t="inlineStr">
+        <is>
+          <t>79.00</t>
+        </is>
+      </c>
       <c r="G34" s="6" t="inlineStr"/>
       <c r="H34" s="6" t="inlineStr">
         <is>
@@ -2152,37 +2225,29 @@
       <c r="O34" s="6" t="inlineStr"/>
       <c r="P34" s="6" t="inlineStr">
         <is>
-          <t>Failed to fetch data: Error fetching quote: ('Connection aborted.', ConnectionResetError(54, 'Connection reset by peer'))</t>
+          <t>Low Strike Check</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="6" t="inlineStr">
         <is>
-          <t>2026-02-10 10:10:00</t>
+          <t>2026-02-10 12:15:00</t>
         </is>
       </c>
       <c r="B35" s="6" t="inlineStr">
         <is>
-          <t>10:10:00</t>
+          <t>12:15:00</t>
         </is>
       </c>
       <c r="C35" s="6" t="inlineStr">
         <is>
-          <t>10:10</t>
-        </is>
-      </c>
-      <c r="D35" s="6" t="inlineStr">
-        <is>
-          <t>83.70</t>
-        </is>
-      </c>
+          <t>12:15</t>
+        </is>
+      </c>
+      <c r="D35" s="6" t="inlineStr"/>
       <c r="E35" s="6" t="inlineStr"/>
-      <c r="F35" s="6" t="inlineStr">
-        <is>
-          <t>111.75</t>
-        </is>
-      </c>
+      <c r="F35" s="6" t="inlineStr"/>
       <c r="G35" s="6" t="inlineStr"/>
       <c r="H35" s="6" t="inlineStr">
         <is>
@@ -2202,35 +2267,35 @@
       <c r="O35" s="6" t="inlineStr"/>
       <c r="P35" s="6" t="inlineStr">
         <is>
-          <t>High Strike Check</t>
+          <t>Failed to fetch data: Live data fetch timed out after 20s - possible API or network issue</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="6" t="inlineStr">
         <is>
-          <t>2026-02-10 10:10:00</t>
+          <t>2026-02-10 12:20:00</t>
         </is>
       </c>
       <c r="B36" s="6" t="inlineStr">
         <is>
-          <t>10:10:00</t>
+          <t>12:20:00</t>
         </is>
       </c>
       <c r="C36" s="6" t="inlineStr">
         <is>
-          <t>10:10</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="D36" s="6" t="inlineStr">
         <is>
-          <t>102.00</t>
+          <t>83.70</t>
         </is>
       </c>
       <c r="E36" s="6" t="inlineStr"/>
       <c r="F36" s="6" t="inlineStr">
         <is>
-          <t>79.00</t>
+          <t>111.75</t>
         </is>
       </c>
       <c r="G36" s="6" t="inlineStr"/>
@@ -2252,35 +2317,35 @@
       <c r="O36" s="6" t="inlineStr"/>
       <c r="P36" s="6" t="inlineStr">
         <is>
-          <t>Low Strike Check</t>
+          <t>High Strike Check</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="6" t="inlineStr">
         <is>
-          <t>2026-02-10 10:15:00</t>
+          <t>2026-02-10 12:20:00</t>
         </is>
       </c>
       <c r="B37" s="6" t="inlineStr">
         <is>
-          <t>10:15:00</t>
+          <t>12:20:00</t>
         </is>
       </c>
       <c r="C37" s="6" t="inlineStr">
         <is>
-          <t>10:15</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="D37" s="6" t="inlineStr">
         <is>
-          <t>83.70</t>
+          <t>102.00</t>
         </is>
       </c>
       <c r="E37" s="6" t="inlineStr"/>
       <c r="F37" s="6" t="inlineStr">
         <is>
-          <t>111.75</t>
+          <t>79.00</t>
         </is>
       </c>
       <c r="G37" s="6" t="inlineStr"/>
@@ -2302,35 +2367,35 @@
       <c r="O37" s="6" t="inlineStr"/>
       <c r="P37" s="6" t="inlineStr">
         <is>
-          <t>High Strike Check</t>
+          <t>Low Strike Check</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="6" t="inlineStr">
         <is>
-          <t>2026-02-10 10:15:00</t>
+          <t>2026-02-10 12:50:00</t>
         </is>
       </c>
       <c r="B38" s="6" t="inlineStr">
         <is>
-          <t>10:15:00</t>
+          <t>12:50:00</t>
         </is>
       </c>
       <c r="C38" s="6" t="inlineStr">
         <is>
-          <t>10:15</t>
+          <t>12:50</t>
         </is>
       </c>
       <c r="D38" s="6" t="inlineStr">
         <is>
-          <t>102.00</t>
+          <t>83.70</t>
         </is>
       </c>
       <c r="E38" s="6" t="inlineStr"/>
       <c r="F38" s="6" t="inlineStr">
         <is>
-          <t>79.00</t>
+          <t>111.75</t>
         </is>
       </c>
       <c r="G38" s="6" t="inlineStr"/>
@@ -2352,35 +2417,35 @@
       <c r="O38" s="6" t="inlineStr"/>
       <c r="P38" s="6" t="inlineStr">
         <is>
-          <t>Low Strike Check</t>
+          <t>High Strike Check</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="6" t="inlineStr">
         <is>
-          <t>2026-02-10 10:20:00</t>
+          <t>2026-02-10 12:50:00</t>
         </is>
       </c>
       <c r="B39" s="6" t="inlineStr">
         <is>
-          <t>10:20:00</t>
+          <t>12:50:00</t>
         </is>
       </c>
       <c r="C39" s="6" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>12:50</t>
         </is>
       </c>
       <c r="D39" s="6" t="inlineStr">
         <is>
-          <t>83.70</t>
+          <t>102.00</t>
         </is>
       </c>
       <c r="E39" s="6" t="inlineStr"/>
       <c r="F39" s="6" t="inlineStr">
         <is>
-          <t>111.75</t>
+          <t>79.00</t>
         </is>
       </c>
       <c r="G39" s="6" t="inlineStr"/>
@@ -2402,37 +2467,29 @@
       <c r="O39" s="6" t="inlineStr"/>
       <c r="P39" s="6" t="inlineStr">
         <is>
-          <t>High Strike Check</t>
+          <t>Low Strike Check</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="6" t="inlineStr">
         <is>
-          <t>2026-02-10 10:20:00</t>
+          <t>2026-02-10 13:05:00</t>
         </is>
       </c>
       <c r="B40" s="6" t="inlineStr">
         <is>
-          <t>10:20:00</t>
+          <t>13:05:00</t>
         </is>
       </c>
       <c r="C40" s="6" t="inlineStr">
         <is>
-          <t>10:20</t>
-        </is>
-      </c>
-      <c r="D40" s="6" t="inlineStr">
-        <is>
-          <t>102.00</t>
-        </is>
-      </c>
+          <t>13:05</t>
+        </is>
+      </c>
+      <c r="D40" s="6" t="inlineStr"/>
       <c r="E40" s="6" t="inlineStr"/>
-      <c r="F40" s="6" t="inlineStr">
-        <is>
-          <t>79.00</t>
-        </is>
-      </c>
+      <c r="F40" s="6" t="inlineStr"/>
       <c r="G40" s="6" t="inlineStr"/>
       <c r="H40" s="6" t="inlineStr">
         <is>
@@ -2452,24 +2509,24 @@
       <c r="O40" s="6" t="inlineStr"/>
       <c r="P40" s="6" t="inlineStr">
         <is>
-          <t>Low Strike Check</t>
+          <t>Failed to fetch data: Live data fetch timed out after 20s - possible API or network issue</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="6" t="inlineStr">
         <is>
-          <t>2026-02-10 10:25:00</t>
+          <t>2026-02-10 13:10:00</t>
         </is>
       </c>
       <c r="B41" s="6" t="inlineStr">
         <is>
-          <t>10:25:00</t>
+          <t>13:10:00</t>
         </is>
       </c>
       <c r="C41" s="6" t="inlineStr">
         <is>
-          <t>10:25</t>
+          <t>13:10</t>
         </is>
       </c>
       <c r="D41" s="6" t="inlineStr">
@@ -2509,17 +2566,17 @@
     <row r="42">
       <c r="A42" s="6" t="inlineStr">
         <is>
-          <t>2026-02-10 10:25:00</t>
+          <t>2026-02-10 13:10:00</t>
         </is>
       </c>
       <c r="B42" s="6" t="inlineStr">
         <is>
-          <t>10:25:00</t>
+          <t>13:10:00</t>
         </is>
       </c>
       <c r="C42" s="6" t="inlineStr">
         <is>
-          <t>10:25</t>
+          <t>13:10</t>
         </is>
       </c>
       <c r="D42" s="6" t="inlineStr">
@@ -2559,17 +2616,17 @@
     <row r="43">
       <c r="A43" s="6" t="inlineStr">
         <is>
-          <t>2026-02-10 10:30:00</t>
+          <t>2026-02-10 13:15:00</t>
         </is>
       </c>
       <c r="B43" s="6" t="inlineStr">
         <is>
-          <t>10:30:00</t>
+          <t>13:15:00</t>
         </is>
       </c>
       <c r="C43" s="6" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="D43" s="6" t="inlineStr">
@@ -2609,17 +2666,17 @@
     <row r="44">
       <c r="A44" s="6" t="inlineStr">
         <is>
-          <t>2026-02-10 10:30:00</t>
+          <t>2026-02-10 13:15:00</t>
         </is>
       </c>
       <c r="B44" s="6" t="inlineStr">
         <is>
-          <t>10:30:00</t>
+          <t>13:15:00</t>
         </is>
       </c>
       <c r="C44" s="6" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="D44" s="6" t="inlineStr">
@@ -2653,6 +2710,432 @@
       <c r="P44" s="6" t="inlineStr">
         <is>
           <t>Low Strike Check</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="6" t="inlineStr">
+        <is>
+          <t>2026-02-10 13:20:00</t>
+        </is>
+      </c>
+      <c r="B45" s="6" t="inlineStr">
+        <is>
+          <t>13:20:00</t>
+        </is>
+      </c>
+      <c r="C45" s="6" t="inlineStr">
+        <is>
+          <t>13:20</t>
+        </is>
+      </c>
+      <c r="D45" s="6" t="inlineStr">
+        <is>
+          <t>83.70</t>
+        </is>
+      </c>
+      <c r="E45" s="6" t="inlineStr"/>
+      <c r="F45" s="6" t="inlineStr">
+        <is>
+          <t>111.75</t>
+        </is>
+      </c>
+      <c r="G45" s="6" t="inlineStr"/>
+      <c r="H45" s="6" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="I45" s="6" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="J45" s="6" t="inlineStr"/>
+      <c r="K45" s="6" t="inlineStr"/>
+      <c r="L45" s="6" t="inlineStr"/>
+      <c r="M45" s="6" t="inlineStr"/>
+      <c r="N45" s="6" t="inlineStr"/>
+      <c r="O45" s="6" t="inlineStr"/>
+      <c r="P45" s="6" t="inlineStr">
+        <is>
+          <t>High Strike Check</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="6" t="inlineStr">
+        <is>
+          <t>2026-02-10 13:20:00</t>
+        </is>
+      </c>
+      <c r="B46" s="6" t="inlineStr">
+        <is>
+          <t>13:20:00</t>
+        </is>
+      </c>
+      <c r="C46" s="6" t="inlineStr">
+        <is>
+          <t>13:20</t>
+        </is>
+      </c>
+      <c r="D46" s="6" t="inlineStr">
+        <is>
+          <t>102.00</t>
+        </is>
+      </c>
+      <c r="E46" s="6" t="inlineStr"/>
+      <c r="F46" s="6" t="inlineStr">
+        <is>
+          <t>79.00</t>
+        </is>
+      </c>
+      <c r="G46" s="6" t="inlineStr"/>
+      <c r="H46" s="6" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="I46" s="6" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="J46" s="6" t="inlineStr"/>
+      <c r="K46" s="6" t="inlineStr"/>
+      <c r="L46" s="6" t="inlineStr"/>
+      <c r="M46" s="6" t="inlineStr"/>
+      <c r="N46" s="6" t="inlineStr"/>
+      <c r="O46" s="6" t="inlineStr"/>
+      <c r="P46" s="6" t="inlineStr">
+        <is>
+          <t>Low Strike Check</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="6" t="inlineStr">
+        <is>
+          <t>2026-02-10 13:25:00</t>
+        </is>
+      </c>
+      <c r="B47" s="6" t="inlineStr">
+        <is>
+          <t>13:25:00</t>
+        </is>
+      </c>
+      <c r="C47" s="6" t="inlineStr">
+        <is>
+          <t>13:25</t>
+        </is>
+      </c>
+      <c r="D47" s="6" t="inlineStr"/>
+      <c r="E47" s="6" t="inlineStr"/>
+      <c r="F47" s="6" t="inlineStr"/>
+      <c r="G47" s="6" t="inlineStr"/>
+      <c r="H47" s="6" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="I47" s="6" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="J47" s="6" t="inlineStr"/>
+      <c r="K47" s="6" t="inlineStr"/>
+      <c r="L47" s="6" t="inlineStr"/>
+      <c r="M47" s="6" t="inlineStr"/>
+      <c r="N47" s="6" t="inlineStr"/>
+      <c r="O47" s="6" t="inlineStr"/>
+      <c r="P47" s="6" t="inlineStr">
+        <is>
+          <t>Failed to fetch data: Live data fetch timed out after 20s - possible API or network issue</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="6" t="inlineStr">
+        <is>
+          <t>2026-02-10 13:30:00</t>
+        </is>
+      </c>
+      <c r="B48" s="6" t="inlineStr">
+        <is>
+          <t>13:30:00</t>
+        </is>
+      </c>
+      <c r="C48" s="6" t="inlineStr">
+        <is>
+          <t>13:30</t>
+        </is>
+      </c>
+      <c r="D48" s="6" t="inlineStr">
+        <is>
+          <t>83.70</t>
+        </is>
+      </c>
+      <c r="E48" s="6" t="inlineStr"/>
+      <c r="F48" s="6" t="inlineStr">
+        <is>
+          <t>111.75</t>
+        </is>
+      </c>
+      <c r="G48" s="6" t="inlineStr"/>
+      <c r="H48" s="6" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="I48" s="6" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="J48" s="6" t="inlineStr"/>
+      <c r="K48" s="6" t="inlineStr"/>
+      <c r="L48" s="6" t="inlineStr"/>
+      <c r="M48" s="6" t="inlineStr"/>
+      <c r="N48" s="6" t="inlineStr"/>
+      <c r="O48" s="6" t="inlineStr"/>
+      <c r="P48" s="6" t="inlineStr">
+        <is>
+          <t>High Strike Check</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="6" t="inlineStr">
+        <is>
+          <t>2026-02-10 13:30:00</t>
+        </is>
+      </c>
+      <c r="B49" s="6" t="inlineStr">
+        <is>
+          <t>13:30:00</t>
+        </is>
+      </c>
+      <c r="C49" s="6" t="inlineStr">
+        <is>
+          <t>13:30</t>
+        </is>
+      </c>
+      <c r="D49" s="6" t="inlineStr">
+        <is>
+          <t>102.00</t>
+        </is>
+      </c>
+      <c r="E49" s="6" t="inlineStr"/>
+      <c r="F49" s="6" t="inlineStr">
+        <is>
+          <t>79.00</t>
+        </is>
+      </c>
+      <c r="G49" s="6" t="inlineStr"/>
+      <c r="H49" s="6" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="I49" s="6" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="J49" s="6" t="inlineStr"/>
+      <c r="K49" s="6" t="inlineStr"/>
+      <c r="L49" s="6" t="inlineStr"/>
+      <c r="M49" s="6" t="inlineStr"/>
+      <c r="N49" s="6" t="inlineStr"/>
+      <c r="O49" s="6" t="inlineStr"/>
+      <c r="P49" s="6" t="inlineStr">
+        <is>
+          <t>Low Strike Check</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="6" t="inlineStr">
+        <is>
+          <t>2026-02-10 13:35:00</t>
+        </is>
+      </c>
+      <c r="B50" s="6" t="inlineStr">
+        <is>
+          <t>13:35:00</t>
+        </is>
+      </c>
+      <c r="C50" s="6" t="inlineStr">
+        <is>
+          <t>13:35</t>
+        </is>
+      </c>
+      <c r="D50" s="6" t="inlineStr"/>
+      <c r="E50" s="6" t="inlineStr"/>
+      <c r="F50" s="6" t="inlineStr"/>
+      <c r="G50" s="6" t="inlineStr"/>
+      <c r="H50" s="6" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="I50" s="6" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="J50" s="6" t="inlineStr"/>
+      <c r="K50" s="6" t="inlineStr"/>
+      <c r="L50" s="6" t="inlineStr"/>
+      <c r="M50" s="6" t="inlineStr"/>
+      <c r="N50" s="6" t="inlineStr"/>
+      <c r="O50" s="6" t="inlineStr"/>
+      <c r="P50" s="6" t="inlineStr">
+        <is>
+          <t>Failed to fetch data: Live data fetch timed out after 20s - possible API or network issue</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="6" t="inlineStr">
+        <is>
+          <t>2026-02-10 13:40:00</t>
+        </is>
+      </c>
+      <c r="B51" s="6" t="inlineStr">
+        <is>
+          <t>13:40:00</t>
+        </is>
+      </c>
+      <c r="C51" s="6" t="inlineStr">
+        <is>
+          <t>13:40</t>
+        </is>
+      </c>
+      <c r="D51" s="6" t="inlineStr">
+        <is>
+          <t>83.70</t>
+        </is>
+      </c>
+      <c r="E51" s="6" t="inlineStr"/>
+      <c r="F51" s="6" t="inlineStr">
+        <is>
+          <t>111.75</t>
+        </is>
+      </c>
+      <c r="G51" s="6" t="inlineStr"/>
+      <c r="H51" s="6" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="I51" s="6" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="J51" s="6" t="inlineStr"/>
+      <c r="K51" s="6" t="inlineStr"/>
+      <c r="L51" s="6" t="inlineStr"/>
+      <c r="M51" s="6" t="inlineStr"/>
+      <c r="N51" s="6" t="inlineStr"/>
+      <c r="O51" s="6" t="inlineStr"/>
+      <c r="P51" s="6" t="inlineStr">
+        <is>
+          <t>High Strike Check</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="6" t="inlineStr">
+        <is>
+          <t>2026-02-10 13:40:00</t>
+        </is>
+      </c>
+      <c r="B52" s="6" t="inlineStr">
+        <is>
+          <t>13:40:00</t>
+        </is>
+      </c>
+      <c r="C52" s="6" t="inlineStr">
+        <is>
+          <t>13:40</t>
+        </is>
+      </c>
+      <c r="D52" s="6" t="inlineStr">
+        <is>
+          <t>102.00</t>
+        </is>
+      </c>
+      <c r="E52" s="6" t="inlineStr"/>
+      <c r="F52" s="6" t="inlineStr">
+        <is>
+          <t>79.00</t>
+        </is>
+      </c>
+      <c r="G52" s="6" t="inlineStr"/>
+      <c r="H52" s="6" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="I52" s="6" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="J52" s="6" t="inlineStr"/>
+      <c r="K52" s="6" t="inlineStr"/>
+      <c r="L52" s="6" t="inlineStr"/>
+      <c r="M52" s="6" t="inlineStr"/>
+      <c r="N52" s="6" t="inlineStr"/>
+      <c r="O52" s="6" t="inlineStr"/>
+      <c r="P52" s="6" t="inlineStr">
+        <is>
+          <t>Low Strike Check</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="6" t="inlineStr">
+        <is>
+          <t>2026-02-10 13:45:00</t>
+        </is>
+      </c>
+      <c r="B53" s="6" t="inlineStr">
+        <is>
+          <t>13:45:00</t>
+        </is>
+      </c>
+      <c r="C53" s="6" t="inlineStr">
+        <is>
+          <t>13:45</t>
+        </is>
+      </c>
+      <c r="D53" s="6" t="inlineStr"/>
+      <c r="E53" s="6" t="inlineStr"/>
+      <c r="F53" s="6" t="inlineStr"/>
+      <c r="G53" s="6" t="inlineStr"/>
+      <c r="H53" s="6" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="I53" s="6" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="J53" s="6" t="inlineStr"/>
+      <c r="K53" s="6" t="inlineStr"/>
+      <c r="L53" s="6" t="inlineStr"/>
+      <c r="M53" s="6" t="inlineStr"/>
+      <c r="N53" s="6" t="inlineStr"/>
+      <c r="O53" s="6" t="inlineStr"/>
+      <c r="P53" s="6" t="inlineStr">
+        <is>
+          <t>Failed to fetch data: Live data fetch timed out after 20s - possible API or network issue</t>
         </is>
       </c>
     </row>

--- a/Mine/logs/mine_signal_logs.xlsx
+++ b/Mine/logs/mine_signal_logs.xlsx
@@ -33,7 +33,7 @@
       <sz val="11"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="7">
     <fill>
       <patternFill/>
     </fill>
@@ -56,6 +56,18 @@
       <patternFill patternType="solid">
         <fgColor rgb="FFFFFFFF"/>
         <bgColor rgb="FFFFFFFF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFFFFF"/>
+        <bgColor rgb="00FFFFFF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00C6EFCE"/>
+        <bgColor rgb="00C6EFCE"/>
       </patternFill>
     </fill>
   </fills>
@@ -107,7 +119,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -125,6 +137,12 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -492,7 +510,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P53"/>
+  <dimension ref="A1:P89"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -3139,6 +3157,1854 @@
         </is>
       </c>
     </row>
+    <row r="54">
+      <c r="A54" s="6" t="inlineStr">
+        <is>
+          <t>2026-02-10 13:50:00</t>
+        </is>
+      </c>
+      <c r="B54" s="6" t="inlineStr">
+        <is>
+          <t>13:50:00</t>
+        </is>
+      </c>
+      <c r="C54" s="6" t="inlineStr">
+        <is>
+          <t>13:50</t>
+        </is>
+      </c>
+      <c r="D54" s="6" t="inlineStr">
+        <is>
+          <t>83.70</t>
+        </is>
+      </c>
+      <c r="E54" s="6" t="inlineStr"/>
+      <c r="F54" s="6" t="inlineStr">
+        <is>
+          <t>111.75</t>
+        </is>
+      </c>
+      <c r="G54" s="6" t="inlineStr"/>
+      <c r="H54" s="6" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="I54" s="6" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="J54" s="6" t="inlineStr"/>
+      <c r="K54" s="6" t="inlineStr"/>
+      <c r="L54" s="6" t="inlineStr"/>
+      <c r="M54" s="6" t="inlineStr"/>
+      <c r="N54" s="6" t="inlineStr"/>
+      <c r="O54" s="6" t="inlineStr"/>
+      <c r="P54" s="6" t="inlineStr">
+        <is>
+          <t>High Strike Check</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="6" t="inlineStr">
+        <is>
+          <t>2026-02-10 13:50:00</t>
+        </is>
+      </c>
+      <c r="B55" s="6" t="inlineStr">
+        <is>
+          <t>13:50:00</t>
+        </is>
+      </c>
+      <c r="C55" s="6" t="inlineStr">
+        <is>
+          <t>13:50</t>
+        </is>
+      </c>
+      <c r="D55" s="6" t="inlineStr">
+        <is>
+          <t>102.00</t>
+        </is>
+      </c>
+      <c r="E55" s="6" t="inlineStr"/>
+      <c r="F55" s="6" t="inlineStr">
+        <is>
+          <t>79.00</t>
+        </is>
+      </c>
+      <c r="G55" s="6" t="inlineStr"/>
+      <c r="H55" s="6" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="I55" s="6" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="J55" s="6" t="inlineStr"/>
+      <c r="K55" s="6" t="inlineStr"/>
+      <c r="L55" s="6" t="inlineStr"/>
+      <c r="M55" s="6" t="inlineStr"/>
+      <c r="N55" s="6" t="inlineStr"/>
+      <c r="O55" s="6" t="inlineStr"/>
+      <c r="P55" s="6" t="inlineStr">
+        <is>
+          <t>Low Strike Check</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="6" t="inlineStr">
+        <is>
+          <t>2026-02-10 13:55:00</t>
+        </is>
+      </c>
+      <c r="B56" s="6" t="inlineStr">
+        <is>
+          <t>13:55:00</t>
+        </is>
+      </c>
+      <c r="C56" s="6" t="inlineStr">
+        <is>
+          <t>13:55</t>
+        </is>
+      </c>
+      <c r="D56" s="6" t="inlineStr">
+        <is>
+          <t>83.70</t>
+        </is>
+      </c>
+      <c r="E56" s="6" t="inlineStr"/>
+      <c r="F56" s="6" t="inlineStr">
+        <is>
+          <t>111.75</t>
+        </is>
+      </c>
+      <c r="G56" s="6" t="inlineStr"/>
+      <c r="H56" s="6" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="I56" s="6" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="J56" s="6" t="inlineStr"/>
+      <c r="K56" s="6" t="inlineStr"/>
+      <c r="L56" s="6" t="inlineStr"/>
+      <c r="M56" s="6" t="inlineStr"/>
+      <c r="N56" s="6" t="inlineStr"/>
+      <c r="O56" s="6" t="inlineStr"/>
+      <c r="P56" s="6" t="inlineStr">
+        <is>
+          <t>High Strike Check</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="6" t="inlineStr">
+        <is>
+          <t>2026-02-10 13:55:00</t>
+        </is>
+      </c>
+      <c r="B57" s="6" t="inlineStr">
+        <is>
+          <t>13:55:00</t>
+        </is>
+      </c>
+      <c r="C57" s="6" t="inlineStr">
+        <is>
+          <t>13:55</t>
+        </is>
+      </c>
+      <c r="D57" s="6" t="inlineStr">
+        <is>
+          <t>102.00</t>
+        </is>
+      </c>
+      <c r="E57" s="6" t="inlineStr"/>
+      <c r="F57" s="6" t="inlineStr">
+        <is>
+          <t>79.00</t>
+        </is>
+      </c>
+      <c r="G57" s="6" t="inlineStr"/>
+      <c r="H57" s="6" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="I57" s="6" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="J57" s="6" t="inlineStr"/>
+      <c r="K57" s="6" t="inlineStr"/>
+      <c r="L57" s="6" t="inlineStr"/>
+      <c r="M57" s="6" t="inlineStr"/>
+      <c r="N57" s="6" t="inlineStr"/>
+      <c r="O57" s="6" t="inlineStr"/>
+      <c r="P57" s="6" t="inlineStr">
+        <is>
+          <t>Low Strike Check</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="6" t="inlineStr">
+        <is>
+          <t>2026-02-10 14:00:00</t>
+        </is>
+      </c>
+      <c r="B58" s="6" t="inlineStr">
+        <is>
+          <t>14:00:00</t>
+        </is>
+      </c>
+      <c r="C58" s="6" t="inlineStr">
+        <is>
+          <t>14:00</t>
+        </is>
+      </c>
+      <c r="D58" s="6" t="inlineStr">
+        <is>
+          <t>83.70</t>
+        </is>
+      </c>
+      <c r="E58" s="6" t="inlineStr"/>
+      <c r="F58" s="6" t="inlineStr">
+        <is>
+          <t>111.75</t>
+        </is>
+      </c>
+      <c r="G58" s="6" t="inlineStr"/>
+      <c r="H58" s="6" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="I58" s="6" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="J58" s="6" t="inlineStr"/>
+      <c r="K58" s="6" t="inlineStr"/>
+      <c r="L58" s="6" t="inlineStr"/>
+      <c r="M58" s="6" t="inlineStr"/>
+      <c r="N58" s="6" t="inlineStr"/>
+      <c r="O58" s="6" t="inlineStr"/>
+      <c r="P58" s="6" t="inlineStr">
+        <is>
+          <t>High Strike Check</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="6" t="inlineStr">
+        <is>
+          <t>2026-02-10 14:00:00</t>
+        </is>
+      </c>
+      <c r="B59" s="6" t="inlineStr">
+        <is>
+          <t>14:00:00</t>
+        </is>
+      </c>
+      <c r="C59" s="6" t="inlineStr">
+        <is>
+          <t>14:00</t>
+        </is>
+      </c>
+      <c r="D59" s="6" t="inlineStr">
+        <is>
+          <t>102.00</t>
+        </is>
+      </c>
+      <c r="E59" s="6" t="inlineStr"/>
+      <c r="F59" s="6" t="inlineStr">
+        <is>
+          <t>79.00</t>
+        </is>
+      </c>
+      <c r="G59" s="6" t="inlineStr"/>
+      <c r="H59" s="6" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="I59" s="6" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="J59" s="6" t="inlineStr"/>
+      <c r="K59" s="6" t="inlineStr"/>
+      <c r="L59" s="6" t="inlineStr"/>
+      <c r="M59" s="6" t="inlineStr"/>
+      <c r="N59" s="6" t="inlineStr"/>
+      <c r="O59" s="6" t="inlineStr"/>
+      <c r="P59" s="6" t="inlineStr">
+        <is>
+          <t>Low Strike Check</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="6" t="inlineStr">
+        <is>
+          <t>2026-02-10 14:05:00</t>
+        </is>
+      </c>
+      <c r="B60" s="6" t="inlineStr">
+        <is>
+          <t>14:05:00</t>
+        </is>
+      </c>
+      <c r="C60" s="6" t="inlineStr">
+        <is>
+          <t>14:05</t>
+        </is>
+      </c>
+      <c r="D60" s="6" t="inlineStr">
+        <is>
+          <t>83.70</t>
+        </is>
+      </c>
+      <c r="E60" s="6" t="inlineStr"/>
+      <c r="F60" s="6" t="inlineStr">
+        <is>
+          <t>111.75</t>
+        </is>
+      </c>
+      <c r="G60" s="6" t="inlineStr"/>
+      <c r="H60" s="6" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="I60" s="6" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="J60" s="6" t="inlineStr"/>
+      <c r="K60" s="6" t="inlineStr"/>
+      <c r="L60" s="6" t="inlineStr"/>
+      <c r="M60" s="6" t="inlineStr"/>
+      <c r="N60" s="6" t="inlineStr"/>
+      <c r="O60" s="6" t="inlineStr"/>
+      <c r="P60" s="6" t="inlineStr">
+        <is>
+          <t>High Strike Check</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="6" t="inlineStr">
+        <is>
+          <t>2026-02-10 14:05:00</t>
+        </is>
+      </c>
+      <c r="B61" s="6" t="inlineStr">
+        <is>
+          <t>14:05:00</t>
+        </is>
+      </c>
+      <c r="C61" s="6" t="inlineStr">
+        <is>
+          <t>14:05</t>
+        </is>
+      </c>
+      <c r="D61" s="6" t="inlineStr">
+        <is>
+          <t>102.00</t>
+        </is>
+      </c>
+      <c r="E61" s="6" t="inlineStr"/>
+      <c r="F61" s="6" t="inlineStr">
+        <is>
+          <t>79.00</t>
+        </is>
+      </c>
+      <c r="G61" s="6" t="inlineStr"/>
+      <c r="H61" s="6" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="I61" s="6" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="J61" s="6" t="inlineStr"/>
+      <c r="K61" s="6" t="inlineStr"/>
+      <c r="L61" s="6" t="inlineStr"/>
+      <c r="M61" s="6" t="inlineStr"/>
+      <c r="N61" s="6" t="inlineStr"/>
+      <c r="O61" s="6" t="inlineStr"/>
+      <c r="P61" s="6" t="inlineStr">
+        <is>
+          <t>Low Strike Check</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="6" t="inlineStr">
+        <is>
+          <t>2026-02-10 14:10:00</t>
+        </is>
+      </c>
+      <c r="B62" s="6" t="inlineStr">
+        <is>
+          <t>14:10:00</t>
+        </is>
+      </c>
+      <c r="C62" s="6" t="inlineStr">
+        <is>
+          <t>14:10</t>
+        </is>
+      </c>
+      <c r="D62" s="6" t="inlineStr">
+        <is>
+          <t>83.70</t>
+        </is>
+      </c>
+      <c r="E62" s="6" t="inlineStr"/>
+      <c r="F62" s="6" t="inlineStr">
+        <is>
+          <t>111.75</t>
+        </is>
+      </c>
+      <c r="G62" s="6" t="inlineStr"/>
+      <c r="H62" s="6" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="I62" s="6" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="J62" s="6" t="inlineStr"/>
+      <c r="K62" s="6" t="inlineStr"/>
+      <c r="L62" s="6" t="inlineStr"/>
+      <c r="M62" s="6" t="inlineStr"/>
+      <c r="N62" s="6" t="inlineStr"/>
+      <c r="O62" s="6" t="inlineStr"/>
+      <c r="P62" s="6" t="inlineStr">
+        <is>
+          <t>High Strike Check</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="6" t="inlineStr">
+        <is>
+          <t>2026-02-10 14:10:00</t>
+        </is>
+      </c>
+      <c r="B63" s="6" t="inlineStr">
+        <is>
+          <t>14:10:00</t>
+        </is>
+      </c>
+      <c r="C63" s="6" t="inlineStr">
+        <is>
+          <t>14:10</t>
+        </is>
+      </c>
+      <c r="D63" s="6" t="inlineStr">
+        <is>
+          <t>102.00</t>
+        </is>
+      </c>
+      <c r="E63" s="6" t="inlineStr"/>
+      <c r="F63" s="6" t="inlineStr">
+        <is>
+          <t>79.00</t>
+        </is>
+      </c>
+      <c r="G63" s="6" t="inlineStr"/>
+      <c r="H63" s="6" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="I63" s="6" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="J63" s="6" t="inlineStr"/>
+      <c r="K63" s="6" t="inlineStr"/>
+      <c r="L63" s="6" t="inlineStr"/>
+      <c r="M63" s="6" t="inlineStr"/>
+      <c r="N63" s="6" t="inlineStr"/>
+      <c r="O63" s="6" t="inlineStr"/>
+      <c r="P63" s="6" t="inlineStr">
+        <is>
+          <t>Low Strike Check</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="6" t="inlineStr">
+        <is>
+          <t>2026-02-10 14:15:00</t>
+        </is>
+      </c>
+      <c r="B64" s="6" t="inlineStr">
+        <is>
+          <t>14:15:00</t>
+        </is>
+      </c>
+      <c r="C64" s="6" t="inlineStr">
+        <is>
+          <t>14:15</t>
+        </is>
+      </c>
+      <c r="D64" s="6" t="inlineStr">
+        <is>
+          <t>83.70</t>
+        </is>
+      </c>
+      <c r="E64" s="6" t="inlineStr"/>
+      <c r="F64" s="6" t="inlineStr">
+        <is>
+          <t>111.75</t>
+        </is>
+      </c>
+      <c r="G64" s="6" t="inlineStr"/>
+      <c r="H64" s="6" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="I64" s="6" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="J64" s="6" t="inlineStr"/>
+      <c r="K64" s="6" t="inlineStr"/>
+      <c r="L64" s="6" t="inlineStr"/>
+      <c r="M64" s="6" t="inlineStr"/>
+      <c r="N64" s="6" t="inlineStr"/>
+      <c r="O64" s="6" t="inlineStr"/>
+      <c r="P64" s="6" t="inlineStr">
+        <is>
+          <t>High Strike Check</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="6" t="inlineStr">
+        <is>
+          <t>2026-02-10 14:15:00</t>
+        </is>
+      </c>
+      <c r="B65" s="6" t="inlineStr">
+        <is>
+          <t>14:15:00</t>
+        </is>
+      </c>
+      <c r="C65" s="6" t="inlineStr">
+        <is>
+          <t>14:15</t>
+        </is>
+      </c>
+      <c r="D65" s="6" t="inlineStr">
+        <is>
+          <t>102.00</t>
+        </is>
+      </c>
+      <c r="E65" s="6" t="inlineStr"/>
+      <c r="F65" s="6" t="inlineStr">
+        <is>
+          <t>79.00</t>
+        </is>
+      </c>
+      <c r="G65" s="6" t="inlineStr"/>
+      <c r="H65" s="6" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="I65" s="6" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="J65" s="6" t="inlineStr"/>
+      <c r="K65" s="6" t="inlineStr"/>
+      <c r="L65" s="6" t="inlineStr"/>
+      <c r="M65" s="6" t="inlineStr"/>
+      <c r="N65" s="6" t="inlineStr"/>
+      <c r="O65" s="6" t="inlineStr"/>
+      <c r="P65" s="6" t="inlineStr">
+        <is>
+          <t>Low Strike Check</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="6" t="inlineStr">
+        <is>
+          <t>2026-02-10 14:20:00</t>
+        </is>
+      </c>
+      <c r="B66" s="6" t="inlineStr">
+        <is>
+          <t>14:20:00</t>
+        </is>
+      </c>
+      <c r="C66" s="6" t="inlineStr">
+        <is>
+          <t>14:20</t>
+        </is>
+      </c>
+      <c r="D66" s="6" t="inlineStr">
+        <is>
+          <t>102.00</t>
+        </is>
+      </c>
+      <c r="E66" s="6" t="inlineStr"/>
+      <c r="F66" s="6" t="inlineStr">
+        <is>
+          <t>111.75</t>
+        </is>
+      </c>
+      <c r="G66" s="6" t="inlineStr"/>
+      <c r="H66" s="8" t="inlineStr">
+        <is>
+          <t>✓ YES</t>
+        </is>
+      </c>
+      <c r="I66" s="6" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="J66" s="6" t="inlineStr">
+        <is>
+          <t>86.40</t>
+        </is>
+      </c>
+      <c r="K66" s="6" t="inlineStr"/>
+      <c r="L66" s="6" t="inlineStr">
+        <is>
+          <t>59.00</t>
+        </is>
+      </c>
+      <c r="M66" s="6" t="inlineStr"/>
+      <c r="N66" s="6" t="inlineStr">
+        <is>
+          <t>141.20</t>
+        </is>
+      </c>
+      <c r="O66" s="6" t="inlineStr"/>
+      <c r="P66" s="6" t="inlineStr">
+        <is>
+          <t>High Strike Check</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="6" t="inlineStr">
+        <is>
+          <t>2026-02-10 14:20:00</t>
+        </is>
+      </c>
+      <c r="B67" s="6" t="inlineStr">
+        <is>
+          <t>14:20:00</t>
+        </is>
+      </c>
+      <c r="C67" s="6" t="inlineStr">
+        <is>
+          <t>14:20</t>
+        </is>
+      </c>
+      <c r="D67" s="6" t="inlineStr">
+        <is>
+          <t>102.00</t>
+        </is>
+      </c>
+      <c r="E67" s="6" t="inlineStr"/>
+      <c r="F67" s="6" t="inlineStr">
+        <is>
+          <t>79.00</t>
+        </is>
+      </c>
+      <c r="G67" s="6" t="inlineStr"/>
+      <c r="H67" s="8" t="inlineStr">
+        <is>
+          <t>✓ YES</t>
+        </is>
+      </c>
+      <c r="I67" s="6" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="J67" s="6" t="inlineStr">
+        <is>
+          <t>86.40</t>
+        </is>
+      </c>
+      <c r="K67" s="6" t="inlineStr"/>
+      <c r="L67" s="6" t="inlineStr">
+        <is>
+          <t>59.00</t>
+        </is>
+      </c>
+      <c r="M67" s="6" t="inlineStr"/>
+      <c r="N67" s="6" t="inlineStr">
+        <is>
+          <t>141.20</t>
+        </is>
+      </c>
+      <c r="O67" s="6" t="inlineStr"/>
+      <c r="P67" s="6" t="inlineStr">
+        <is>
+          <t>Low Strike Check</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="6" t="inlineStr">
+        <is>
+          <t>2026-02-10 14:25:00</t>
+        </is>
+      </c>
+      <c r="B68" s="6" t="inlineStr">
+        <is>
+          <t>14:25:00</t>
+        </is>
+      </c>
+      <c r="C68" s="6" t="inlineStr">
+        <is>
+          <t>14:25</t>
+        </is>
+      </c>
+      <c r="D68" s="6" t="inlineStr">
+        <is>
+          <t>83.70</t>
+        </is>
+      </c>
+      <c r="E68" s="6" t="inlineStr"/>
+      <c r="F68" s="6" t="inlineStr">
+        <is>
+          <t>111.75</t>
+        </is>
+      </c>
+      <c r="G68" s="6" t="inlineStr"/>
+      <c r="H68" s="6" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="I68" s="6" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="J68" s="6" t="inlineStr"/>
+      <c r="K68" s="6" t="inlineStr"/>
+      <c r="L68" s="6" t="inlineStr"/>
+      <c r="M68" s="6" t="inlineStr"/>
+      <c r="N68" s="6" t="inlineStr"/>
+      <c r="O68" s="6" t="inlineStr"/>
+      <c r="P68" s="6" t="inlineStr">
+        <is>
+          <t>High Strike Check</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="6" t="inlineStr">
+        <is>
+          <t>2026-02-10 14:25:00</t>
+        </is>
+      </c>
+      <c r="B69" s="6" t="inlineStr">
+        <is>
+          <t>14:25:00</t>
+        </is>
+      </c>
+      <c r="C69" s="6" t="inlineStr">
+        <is>
+          <t>14:25</t>
+        </is>
+      </c>
+      <c r="D69" s="6" t="inlineStr">
+        <is>
+          <t>102.00</t>
+        </is>
+      </c>
+      <c r="E69" s="6" t="inlineStr"/>
+      <c r="F69" s="6" t="inlineStr">
+        <is>
+          <t>79.00</t>
+        </is>
+      </c>
+      <c r="G69" s="6" t="inlineStr"/>
+      <c r="H69" s="6" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="I69" s="6" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="J69" s="6" t="inlineStr"/>
+      <c r="K69" s="6" t="inlineStr"/>
+      <c r="L69" s="6" t="inlineStr"/>
+      <c r="M69" s="6" t="inlineStr"/>
+      <c r="N69" s="6" t="inlineStr"/>
+      <c r="O69" s="6" t="inlineStr"/>
+      <c r="P69" s="6" t="inlineStr">
+        <is>
+          <t>Low Strike Check</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="6" t="inlineStr">
+        <is>
+          <t>2026-02-10 14:30:00</t>
+        </is>
+      </c>
+      <c r="B70" s="6" t="inlineStr">
+        <is>
+          <t>14:30:00</t>
+        </is>
+      </c>
+      <c r="C70" s="6" t="inlineStr">
+        <is>
+          <t>14:30</t>
+        </is>
+      </c>
+      <c r="D70" s="6" t="inlineStr">
+        <is>
+          <t>83.70</t>
+        </is>
+      </c>
+      <c r="E70" s="6" t="inlineStr"/>
+      <c r="F70" s="6" t="inlineStr">
+        <is>
+          <t>111.75</t>
+        </is>
+      </c>
+      <c r="G70" s="6" t="inlineStr"/>
+      <c r="H70" s="6" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="I70" s="6" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="J70" s="6" t="inlineStr"/>
+      <c r="K70" s="6" t="inlineStr"/>
+      <c r="L70" s="6" t="inlineStr"/>
+      <c r="M70" s="6" t="inlineStr"/>
+      <c r="N70" s="6" t="inlineStr"/>
+      <c r="O70" s="6" t="inlineStr"/>
+      <c r="P70" s="6" t="inlineStr">
+        <is>
+          <t>High Strike Check</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="6" t="inlineStr">
+        <is>
+          <t>2026-02-10 14:30:00</t>
+        </is>
+      </c>
+      <c r="B71" s="6" t="inlineStr">
+        <is>
+          <t>14:30:00</t>
+        </is>
+      </c>
+      <c r="C71" s="6" t="inlineStr">
+        <is>
+          <t>14:30</t>
+        </is>
+      </c>
+      <c r="D71" s="6" t="inlineStr">
+        <is>
+          <t>102.00</t>
+        </is>
+      </c>
+      <c r="E71" s="6" t="inlineStr"/>
+      <c r="F71" s="6" t="inlineStr">
+        <is>
+          <t>79.00</t>
+        </is>
+      </c>
+      <c r="G71" s="6" t="inlineStr"/>
+      <c r="H71" s="6" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="I71" s="6" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="J71" s="6" t="inlineStr"/>
+      <c r="K71" s="6" t="inlineStr"/>
+      <c r="L71" s="6" t="inlineStr"/>
+      <c r="M71" s="6" t="inlineStr"/>
+      <c r="N71" s="6" t="inlineStr"/>
+      <c r="O71" s="6" t="inlineStr"/>
+      <c r="P71" s="6" t="inlineStr">
+        <is>
+          <t>Low Strike Check</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="6" t="inlineStr">
+        <is>
+          <t>2026-02-10 14:35:00</t>
+        </is>
+      </c>
+      <c r="B72" s="6" t="inlineStr">
+        <is>
+          <t>14:35:00</t>
+        </is>
+      </c>
+      <c r="C72" s="6" t="inlineStr">
+        <is>
+          <t>14:35</t>
+        </is>
+      </c>
+      <c r="D72" s="6" t="inlineStr">
+        <is>
+          <t>83.70</t>
+        </is>
+      </c>
+      <c r="E72" s="6" t="inlineStr"/>
+      <c r="F72" s="6" t="inlineStr">
+        <is>
+          <t>111.75</t>
+        </is>
+      </c>
+      <c r="G72" s="6" t="inlineStr"/>
+      <c r="H72" s="6" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="I72" s="6" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="J72" s="6" t="inlineStr"/>
+      <c r="K72" s="6" t="inlineStr"/>
+      <c r="L72" s="6" t="inlineStr"/>
+      <c r="M72" s="6" t="inlineStr"/>
+      <c r="N72" s="6" t="inlineStr"/>
+      <c r="O72" s="6" t="inlineStr"/>
+      <c r="P72" s="6" t="inlineStr">
+        <is>
+          <t>High Strike Check</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="6" t="inlineStr">
+        <is>
+          <t>2026-02-10 14:35:00</t>
+        </is>
+      </c>
+      <c r="B73" s="6" t="inlineStr">
+        <is>
+          <t>14:35:00</t>
+        </is>
+      </c>
+      <c r="C73" s="6" t="inlineStr">
+        <is>
+          <t>14:35</t>
+        </is>
+      </c>
+      <c r="D73" s="6" t="inlineStr">
+        <is>
+          <t>102.00</t>
+        </is>
+      </c>
+      <c r="E73" s="6" t="inlineStr"/>
+      <c r="F73" s="6" t="inlineStr">
+        <is>
+          <t>79.00</t>
+        </is>
+      </c>
+      <c r="G73" s="6" t="inlineStr"/>
+      <c r="H73" s="6" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="I73" s="6" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="J73" s="6" t="inlineStr"/>
+      <c r="K73" s="6" t="inlineStr"/>
+      <c r="L73" s="6" t="inlineStr"/>
+      <c r="M73" s="6" t="inlineStr"/>
+      <c r="N73" s="6" t="inlineStr"/>
+      <c r="O73" s="6" t="inlineStr"/>
+      <c r="P73" s="6" t="inlineStr">
+        <is>
+          <t>Low Strike Check</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="6" t="inlineStr">
+        <is>
+          <t>2026-02-10 14:40:00</t>
+        </is>
+      </c>
+      <c r="B74" s="6" t="inlineStr">
+        <is>
+          <t>14:40:00</t>
+        </is>
+      </c>
+      <c r="C74" s="6" t="inlineStr">
+        <is>
+          <t>14:40</t>
+        </is>
+      </c>
+      <c r="D74" s="6" t="inlineStr">
+        <is>
+          <t>83.70</t>
+        </is>
+      </c>
+      <c r="E74" s="6" t="inlineStr"/>
+      <c r="F74" s="6" t="inlineStr">
+        <is>
+          <t>111.75</t>
+        </is>
+      </c>
+      <c r="G74" s="6" t="inlineStr"/>
+      <c r="H74" s="6" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="I74" s="6" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="J74" s="6" t="inlineStr"/>
+      <c r="K74" s="6" t="inlineStr"/>
+      <c r="L74" s="6" t="inlineStr"/>
+      <c r="M74" s="6" t="inlineStr"/>
+      <c r="N74" s="6" t="inlineStr"/>
+      <c r="O74" s="6" t="inlineStr"/>
+      <c r="P74" s="6" t="inlineStr">
+        <is>
+          <t>High Strike Check</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="6" t="inlineStr">
+        <is>
+          <t>2026-02-10 14:40:00</t>
+        </is>
+      </c>
+      <c r="B75" s="6" t="inlineStr">
+        <is>
+          <t>14:40:00</t>
+        </is>
+      </c>
+      <c r="C75" s="6" t="inlineStr">
+        <is>
+          <t>14:40</t>
+        </is>
+      </c>
+      <c r="D75" s="6" t="inlineStr">
+        <is>
+          <t>102.00</t>
+        </is>
+      </c>
+      <c r="E75" s="6" t="inlineStr"/>
+      <c r="F75" s="6" t="inlineStr">
+        <is>
+          <t>79.00</t>
+        </is>
+      </c>
+      <c r="G75" s="6" t="inlineStr"/>
+      <c r="H75" s="6" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="I75" s="6" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="J75" s="6" t="inlineStr"/>
+      <c r="K75" s="6" t="inlineStr"/>
+      <c r="L75" s="6" t="inlineStr"/>
+      <c r="M75" s="6" t="inlineStr"/>
+      <c r="N75" s="6" t="inlineStr"/>
+      <c r="O75" s="6" t="inlineStr"/>
+      <c r="P75" s="6" t="inlineStr">
+        <is>
+          <t>Low Strike Check</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="6" t="inlineStr">
+        <is>
+          <t>2026-02-10 14:45:00</t>
+        </is>
+      </c>
+      <c r="B76" s="6" t="inlineStr">
+        <is>
+          <t>14:45:00</t>
+        </is>
+      </c>
+      <c r="C76" s="6" t="inlineStr">
+        <is>
+          <t>14:45</t>
+        </is>
+      </c>
+      <c r="D76" s="6" t="inlineStr">
+        <is>
+          <t>83.70</t>
+        </is>
+      </c>
+      <c r="E76" s="6" t="inlineStr"/>
+      <c r="F76" s="6" t="inlineStr">
+        <is>
+          <t>111.75</t>
+        </is>
+      </c>
+      <c r="G76" s="6" t="inlineStr"/>
+      <c r="H76" s="6" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="I76" s="6" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="J76" s="6" t="inlineStr"/>
+      <c r="K76" s="6" t="inlineStr"/>
+      <c r="L76" s="6" t="inlineStr"/>
+      <c r="M76" s="6" t="inlineStr"/>
+      <c r="N76" s="6" t="inlineStr"/>
+      <c r="O76" s="6" t="inlineStr"/>
+      <c r="P76" s="6" t="inlineStr">
+        <is>
+          <t>High Strike Check</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="6" t="inlineStr">
+        <is>
+          <t>2026-02-10 14:45:00</t>
+        </is>
+      </c>
+      <c r="B77" s="6" t="inlineStr">
+        <is>
+          <t>14:45:00</t>
+        </is>
+      </c>
+      <c r="C77" s="6" t="inlineStr">
+        <is>
+          <t>14:45</t>
+        </is>
+      </c>
+      <c r="D77" s="6" t="inlineStr">
+        <is>
+          <t>102.00</t>
+        </is>
+      </c>
+      <c r="E77" s="6" t="inlineStr"/>
+      <c r="F77" s="6" t="inlineStr">
+        <is>
+          <t>79.00</t>
+        </is>
+      </c>
+      <c r="G77" s="6" t="inlineStr"/>
+      <c r="H77" s="6" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="I77" s="6" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="J77" s="6" t="inlineStr"/>
+      <c r="K77" s="6" t="inlineStr"/>
+      <c r="L77" s="6" t="inlineStr"/>
+      <c r="M77" s="6" t="inlineStr"/>
+      <c r="N77" s="6" t="inlineStr"/>
+      <c r="O77" s="6" t="inlineStr"/>
+      <c r="P77" s="6" t="inlineStr">
+        <is>
+          <t>Low Strike Check</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="6" t="inlineStr">
+        <is>
+          <t>2026-02-10 14:50:00</t>
+        </is>
+      </c>
+      <c r="B78" s="6" t="inlineStr">
+        <is>
+          <t>14:50:00</t>
+        </is>
+      </c>
+      <c r="C78" s="6" t="inlineStr">
+        <is>
+          <t>14:50</t>
+        </is>
+      </c>
+      <c r="D78" s="6" t="inlineStr">
+        <is>
+          <t>83.70</t>
+        </is>
+      </c>
+      <c r="E78" s="6" t="inlineStr"/>
+      <c r="F78" s="6" t="inlineStr">
+        <is>
+          <t>111.75</t>
+        </is>
+      </c>
+      <c r="G78" s="6" t="inlineStr"/>
+      <c r="H78" s="6" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="I78" s="6" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="J78" s="6" t="inlineStr"/>
+      <c r="K78" s="6" t="inlineStr"/>
+      <c r="L78" s="6" t="inlineStr"/>
+      <c r="M78" s="6" t="inlineStr"/>
+      <c r="N78" s="6" t="inlineStr"/>
+      <c r="O78" s="6" t="inlineStr"/>
+      <c r="P78" s="6" t="inlineStr">
+        <is>
+          <t>High Strike Check</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="6" t="inlineStr">
+        <is>
+          <t>2026-02-10 14:50:00</t>
+        </is>
+      </c>
+      <c r="B79" s="6" t="inlineStr">
+        <is>
+          <t>14:50:00</t>
+        </is>
+      </c>
+      <c r="C79" s="6" t="inlineStr">
+        <is>
+          <t>14:50</t>
+        </is>
+      </c>
+      <c r="D79" s="6" t="inlineStr">
+        <is>
+          <t>102.00</t>
+        </is>
+      </c>
+      <c r="E79" s="6" t="inlineStr"/>
+      <c r="F79" s="6" t="inlineStr">
+        <is>
+          <t>79.00</t>
+        </is>
+      </c>
+      <c r="G79" s="6" t="inlineStr"/>
+      <c r="H79" s="6" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="I79" s="6" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="J79" s="6" t="inlineStr"/>
+      <c r="K79" s="6" t="inlineStr"/>
+      <c r="L79" s="6" t="inlineStr"/>
+      <c r="M79" s="6" t="inlineStr"/>
+      <c r="N79" s="6" t="inlineStr"/>
+      <c r="O79" s="6" t="inlineStr"/>
+      <c r="P79" s="6" t="inlineStr">
+        <is>
+          <t>Low Strike Check</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="6" t="inlineStr">
+        <is>
+          <t>2026-02-10 14:55:00</t>
+        </is>
+      </c>
+      <c r="B80" s="6" t="inlineStr">
+        <is>
+          <t>14:55:00</t>
+        </is>
+      </c>
+      <c r="C80" s="6" t="inlineStr">
+        <is>
+          <t>14:55</t>
+        </is>
+      </c>
+      <c r="D80" s="6" t="inlineStr">
+        <is>
+          <t>102.00</t>
+        </is>
+      </c>
+      <c r="E80" s="6" t="inlineStr"/>
+      <c r="F80" s="6" t="inlineStr">
+        <is>
+          <t>111.75</t>
+        </is>
+      </c>
+      <c r="G80" s="6" t="inlineStr"/>
+      <c r="H80" s="8" t="inlineStr">
+        <is>
+          <t>✓ YES</t>
+        </is>
+      </c>
+      <c r="I80" s="6" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="J80" s="6" t="inlineStr">
+        <is>
+          <t>85.95</t>
+        </is>
+      </c>
+      <c r="K80" s="6" t="inlineStr"/>
+      <c r="L80" s="6" t="inlineStr">
+        <is>
+          <t>59.00</t>
+        </is>
+      </c>
+      <c r="M80" s="6" t="inlineStr"/>
+      <c r="N80" s="6" t="inlineStr">
+        <is>
+          <t>139.85</t>
+        </is>
+      </c>
+      <c r="O80" s="6" t="inlineStr"/>
+      <c r="P80" s="6" t="inlineStr">
+        <is>
+          <t>High Strike Check</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="6" t="inlineStr">
+        <is>
+          <t>2026-02-10 14:55:00</t>
+        </is>
+      </c>
+      <c r="B81" s="6" t="inlineStr">
+        <is>
+          <t>14:55:00</t>
+        </is>
+      </c>
+      <c r="C81" s="6" t="inlineStr">
+        <is>
+          <t>14:55</t>
+        </is>
+      </c>
+      <c r="D81" s="6" t="inlineStr">
+        <is>
+          <t>102.00</t>
+        </is>
+      </c>
+      <c r="E81" s="6" t="inlineStr"/>
+      <c r="F81" s="6" t="inlineStr">
+        <is>
+          <t>79.00</t>
+        </is>
+      </c>
+      <c r="G81" s="6" t="inlineStr"/>
+      <c r="H81" s="8" t="inlineStr">
+        <is>
+          <t>✓ YES</t>
+        </is>
+      </c>
+      <c r="I81" s="6" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="J81" s="6" t="inlineStr">
+        <is>
+          <t>85.95</t>
+        </is>
+      </c>
+      <c r="K81" s="6" t="inlineStr"/>
+      <c r="L81" s="6" t="inlineStr">
+        <is>
+          <t>59.00</t>
+        </is>
+      </c>
+      <c r="M81" s="6" t="inlineStr"/>
+      <c r="N81" s="6" t="inlineStr">
+        <is>
+          <t>139.85</t>
+        </is>
+      </c>
+      <c r="O81" s="6" t="inlineStr"/>
+      <c r="P81" s="6" t="inlineStr">
+        <is>
+          <t>Low Strike Check</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="6" t="inlineStr">
+        <is>
+          <t>2026-02-10 15:00:00</t>
+        </is>
+      </c>
+      <c r="B82" s="6" t="inlineStr">
+        <is>
+          <t>15:00:00</t>
+        </is>
+      </c>
+      <c r="C82" s="6" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="D82" s="6" t="inlineStr">
+        <is>
+          <t>83.70</t>
+        </is>
+      </c>
+      <c r="E82" s="6" t="inlineStr"/>
+      <c r="F82" s="6" t="inlineStr">
+        <is>
+          <t>111.75</t>
+        </is>
+      </c>
+      <c r="G82" s="6" t="inlineStr"/>
+      <c r="H82" s="6" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="I82" s="6" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="J82" s="6" t="inlineStr"/>
+      <c r="K82" s="6" t="inlineStr"/>
+      <c r="L82" s="6" t="inlineStr"/>
+      <c r="M82" s="6" t="inlineStr"/>
+      <c r="N82" s="6" t="inlineStr"/>
+      <c r="O82" s="6" t="inlineStr"/>
+      <c r="P82" s="6" t="inlineStr">
+        <is>
+          <t>High Strike Check</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="6" t="inlineStr">
+        <is>
+          <t>2026-02-10 15:00:00</t>
+        </is>
+      </c>
+      <c r="B83" s="6" t="inlineStr">
+        <is>
+          <t>15:00:00</t>
+        </is>
+      </c>
+      <c r="C83" s="6" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="D83" s="6" t="inlineStr">
+        <is>
+          <t>102.00</t>
+        </is>
+      </c>
+      <c r="E83" s="6" t="inlineStr"/>
+      <c r="F83" s="6" t="inlineStr">
+        <is>
+          <t>79.00</t>
+        </is>
+      </c>
+      <c r="G83" s="6" t="inlineStr"/>
+      <c r="H83" s="6" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="I83" s="6" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="J83" s="6" t="inlineStr"/>
+      <c r="K83" s="6" t="inlineStr"/>
+      <c r="L83" s="6" t="inlineStr"/>
+      <c r="M83" s="6" t="inlineStr"/>
+      <c r="N83" s="6" t="inlineStr"/>
+      <c r="O83" s="6" t="inlineStr"/>
+      <c r="P83" s="6" t="inlineStr">
+        <is>
+          <t>Low Strike Check</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="6" t="inlineStr">
+        <is>
+          <t>2026-02-10 15:05:00</t>
+        </is>
+      </c>
+      <c r="B84" s="6" t="inlineStr">
+        <is>
+          <t>15:05:00</t>
+        </is>
+      </c>
+      <c r="C84" s="6" t="inlineStr">
+        <is>
+          <t>15:05</t>
+        </is>
+      </c>
+      <c r="D84" s="6" t="inlineStr">
+        <is>
+          <t>83.70</t>
+        </is>
+      </c>
+      <c r="E84" s="6" t="inlineStr"/>
+      <c r="F84" s="6" t="inlineStr">
+        <is>
+          <t>111.75</t>
+        </is>
+      </c>
+      <c r="G84" s="6" t="inlineStr"/>
+      <c r="H84" s="6" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="I84" s="6" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="J84" s="6" t="inlineStr"/>
+      <c r="K84" s="6" t="inlineStr"/>
+      <c r="L84" s="6" t="inlineStr"/>
+      <c r="M84" s="6" t="inlineStr"/>
+      <c r="N84" s="6" t="inlineStr"/>
+      <c r="O84" s="6" t="inlineStr"/>
+      <c r="P84" s="6" t="inlineStr">
+        <is>
+          <t>High Strike Check</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="6" t="inlineStr">
+        <is>
+          <t>2026-02-10 15:05:00</t>
+        </is>
+      </c>
+      <c r="B85" s="6" t="inlineStr">
+        <is>
+          <t>15:05:00</t>
+        </is>
+      </c>
+      <c r="C85" s="6" t="inlineStr">
+        <is>
+          <t>15:05</t>
+        </is>
+      </c>
+      <c r="D85" s="6" t="inlineStr">
+        <is>
+          <t>102.00</t>
+        </is>
+      </c>
+      <c r="E85" s="6" t="inlineStr"/>
+      <c r="F85" s="6" t="inlineStr">
+        <is>
+          <t>79.00</t>
+        </is>
+      </c>
+      <c r="G85" s="6" t="inlineStr"/>
+      <c r="H85" s="6" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="I85" s="6" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="J85" s="6" t="inlineStr"/>
+      <c r="K85" s="6" t="inlineStr"/>
+      <c r="L85" s="6" t="inlineStr"/>
+      <c r="M85" s="6" t="inlineStr"/>
+      <c r="N85" s="6" t="inlineStr"/>
+      <c r="O85" s="6" t="inlineStr"/>
+      <c r="P85" s="6" t="inlineStr">
+        <is>
+          <t>Low Strike Check</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="6" t="inlineStr">
+        <is>
+          <t>2026-02-10 15:10:00</t>
+        </is>
+      </c>
+      <c r="B86" s="6" t="inlineStr">
+        <is>
+          <t>15:10:00</t>
+        </is>
+      </c>
+      <c r="C86" s="6" t="inlineStr">
+        <is>
+          <t>15:10</t>
+        </is>
+      </c>
+      <c r="D86" s="6" t="inlineStr">
+        <is>
+          <t>83.70</t>
+        </is>
+      </c>
+      <c r="E86" s="6" t="inlineStr"/>
+      <c r="F86" s="6" t="inlineStr">
+        <is>
+          <t>111.75</t>
+        </is>
+      </c>
+      <c r="G86" s="6" t="inlineStr"/>
+      <c r="H86" s="6" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="I86" s="6" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="J86" s="6" t="inlineStr"/>
+      <c r="K86" s="6" t="inlineStr"/>
+      <c r="L86" s="6" t="inlineStr"/>
+      <c r="M86" s="6" t="inlineStr"/>
+      <c r="N86" s="6" t="inlineStr"/>
+      <c r="O86" s="6" t="inlineStr"/>
+      <c r="P86" s="6" t="inlineStr">
+        <is>
+          <t>High Strike Check</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="6" t="inlineStr">
+        <is>
+          <t>2026-02-10 15:10:00</t>
+        </is>
+      </c>
+      <c r="B87" s="6" t="inlineStr">
+        <is>
+          <t>15:10:00</t>
+        </is>
+      </c>
+      <c r="C87" s="6" t="inlineStr">
+        <is>
+          <t>15:10</t>
+        </is>
+      </c>
+      <c r="D87" s="6" t="inlineStr">
+        <is>
+          <t>102.00</t>
+        </is>
+      </c>
+      <c r="E87" s="6" t="inlineStr"/>
+      <c r="F87" s="6" t="inlineStr">
+        <is>
+          <t>79.00</t>
+        </is>
+      </c>
+      <c r="G87" s="6" t="inlineStr"/>
+      <c r="H87" s="6" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="I87" s="6" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="J87" s="6" t="inlineStr"/>
+      <c r="K87" s="6" t="inlineStr"/>
+      <c r="L87" s="6" t="inlineStr"/>
+      <c r="M87" s="6" t="inlineStr"/>
+      <c r="N87" s="6" t="inlineStr"/>
+      <c r="O87" s="6" t="inlineStr"/>
+      <c r="P87" s="6" t="inlineStr">
+        <is>
+          <t>Low Strike Check</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="6" t="inlineStr">
+        <is>
+          <t>2026-02-10 15:15:00</t>
+        </is>
+      </c>
+      <c r="B88" s="6" t="inlineStr">
+        <is>
+          <t>15:15:00</t>
+        </is>
+      </c>
+      <c r="C88" s="6" t="inlineStr">
+        <is>
+          <t>15:15</t>
+        </is>
+      </c>
+      <c r="D88" s="6" t="inlineStr">
+        <is>
+          <t>83.70</t>
+        </is>
+      </c>
+      <c r="E88" s="6" t="inlineStr"/>
+      <c r="F88" s="6" t="inlineStr">
+        <is>
+          <t>111.75</t>
+        </is>
+      </c>
+      <c r="G88" s="6" t="inlineStr"/>
+      <c r="H88" s="6" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="I88" s="6" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="J88" s="6" t="inlineStr"/>
+      <c r="K88" s="6" t="inlineStr"/>
+      <c r="L88" s="6" t="inlineStr"/>
+      <c r="M88" s="6" t="inlineStr"/>
+      <c r="N88" s="6" t="inlineStr"/>
+      <c r="O88" s="6" t="inlineStr"/>
+      <c r="P88" s="6" t="inlineStr">
+        <is>
+          <t>High Strike Check</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="6" t="inlineStr">
+        <is>
+          <t>2026-02-10 15:15:00</t>
+        </is>
+      </c>
+      <c r="B89" s="6" t="inlineStr">
+        <is>
+          <t>15:15:00</t>
+        </is>
+      </c>
+      <c r="C89" s="6" t="inlineStr">
+        <is>
+          <t>15:15</t>
+        </is>
+      </c>
+      <c r="D89" s="6" t="inlineStr">
+        <is>
+          <t>102.00</t>
+        </is>
+      </c>
+      <c r="E89" s="6" t="inlineStr"/>
+      <c r="F89" s="6" t="inlineStr">
+        <is>
+          <t>79.00</t>
+        </is>
+      </c>
+      <c r="G89" s="6" t="inlineStr"/>
+      <c r="H89" s="6" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="I89" s="6" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="J89" s="6" t="inlineStr"/>
+      <c r="K89" s="6" t="inlineStr"/>
+      <c r="L89" s="6" t="inlineStr"/>
+      <c r="M89" s="6" t="inlineStr"/>
+      <c r="N89" s="6" t="inlineStr"/>
+      <c r="O89" s="6" t="inlineStr"/>
+      <c r="P89" s="6" t="inlineStr">
+        <is>
+          <t>Low Strike Check</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -3150,7 +5016,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L5"/>
+  <dimension ref="A1:L9"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -3425,6 +5291,206 @@
         </is>
       </c>
     </row>
+    <row r="6">
+      <c r="A6" s="6" t="inlineStr">
+        <is>
+          <t>2026-02-10 14:20:07</t>
+        </is>
+      </c>
+      <c r="B6" s="6" t="inlineStr">
+        <is>
+          <t>BUY CE</t>
+        </is>
+      </c>
+      <c r="C6" s="6" t="inlineStr">
+        <is>
+          <t>CE</t>
+        </is>
+      </c>
+      <c r="D6" s="6" t="n">
+        <v>25850</v>
+      </c>
+      <c r="E6" s="6" t="inlineStr">
+        <is>
+          <t>86.40</t>
+        </is>
+      </c>
+      <c r="F6" s="6" t="inlineStr">
+        <is>
+          <t>86.40</t>
+        </is>
+      </c>
+      <c r="G6" s="6" t="inlineStr"/>
+      <c r="H6" s="6" t="inlineStr"/>
+      <c r="I6" s="6" t="inlineStr"/>
+      <c r="J6" s="7" t="inlineStr">
+        <is>
+          <t>BUY CE</t>
+        </is>
+      </c>
+      <c r="K6" s="6" t="inlineStr">
+        <is>
+          <t>2021144636487557120</t>
+        </is>
+      </c>
+      <c r="L6" s="6" t="inlineStr">
+        <is>
+          <t>Mode: LIVE | Details: Order placed successfully via KiteService | Order_type: MARKET</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="6" t="inlineStr">
+        <is>
+          <t>2026-02-10 14:20:08</t>
+        </is>
+      </c>
+      <c r="B7" s="6" t="inlineStr">
+        <is>
+          <t>SL_ORDER</t>
+        </is>
+      </c>
+      <c r="C7" s="6" t="inlineStr">
+        <is>
+          <t>CE</t>
+        </is>
+      </c>
+      <c r="D7" s="6" t="n">
+        <v>25850</v>
+      </c>
+      <c r="E7" s="6" t="inlineStr">
+        <is>
+          <t>59.00</t>
+        </is>
+      </c>
+      <c r="F7" s="6" t="inlineStr"/>
+      <c r="G7" s="6" t="inlineStr">
+        <is>
+          <t>141.20</t>
+        </is>
+      </c>
+      <c r="H7" s="6" t="inlineStr">
+        <is>
+          <t>59.00</t>
+        </is>
+      </c>
+      <c r="I7" s="6" t="inlineStr"/>
+      <c r="J7" s="7" t="inlineStr">
+        <is>
+          <t>PLACED</t>
+        </is>
+      </c>
+      <c r="K7" s="6" t="inlineStr">
+        <is>
+          <t>2021144641143234560</t>
+        </is>
+      </c>
+      <c r="L7" s="6" t="inlineStr">
+        <is>
+          <t>SL Order Placed | Trigger: 59.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="6" t="inlineStr">
+        <is>
+          <t>2026-02-10 14:55:10</t>
+        </is>
+      </c>
+      <c r="B8" s="6" t="inlineStr">
+        <is>
+          <t>BUY CE</t>
+        </is>
+      </c>
+      <c r="C8" s="6" t="inlineStr">
+        <is>
+          <t>CE</t>
+        </is>
+      </c>
+      <c r="D8" s="6" t="n">
+        <v>25850</v>
+      </c>
+      <c r="E8" s="6" t="inlineStr">
+        <is>
+          <t>85.95</t>
+        </is>
+      </c>
+      <c r="F8" s="6" t="inlineStr">
+        <is>
+          <t>85.95</t>
+        </is>
+      </c>
+      <c r="G8" s="6" t="inlineStr"/>
+      <c r="H8" s="6" t="inlineStr"/>
+      <c r="I8" s="6" t="inlineStr"/>
+      <c r="J8" s="7" t="inlineStr">
+        <is>
+          <t>BUY CE</t>
+        </is>
+      </c>
+      <c r="K8" s="6" t="inlineStr">
+        <is>
+          <t>2021153458165833728</t>
+        </is>
+      </c>
+      <c r="L8" s="6" t="inlineStr">
+        <is>
+          <t>Mode: LIVE | Details: Order placed successfully via KiteService | Order_type: MARKET</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="6" t="inlineStr">
+        <is>
+          <t>2026-02-10 14:55:11</t>
+        </is>
+      </c>
+      <c r="B9" s="6" t="inlineStr">
+        <is>
+          <t>SL_ORDER</t>
+        </is>
+      </c>
+      <c r="C9" s="6" t="inlineStr">
+        <is>
+          <t>CE</t>
+        </is>
+      </c>
+      <c r="D9" s="6" t="n">
+        <v>25850</v>
+      </c>
+      <c r="E9" s="6" t="inlineStr">
+        <is>
+          <t>59.00</t>
+        </is>
+      </c>
+      <c r="F9" s="6" t="inlineStr"/>
+      <c r="G9" s="6" t="inlineStr">
+        <is>
+          <t>139.85</t>
+        </is>
+      </c>
+      <c r="H9" s="6" t="inlineStr">
+        <is>
+          <t>59.00</t>
+        </is>
+      </c>
+      <c r="I9" s="6" t="inlineStr"/>
+      <c r="J9" s="7" t="inlineStr">
+        <is>
+          <t>PLACED</t>
+        </is>
+      </c>
+      <c r="K9" s="6" t="inlineStr">
+        <is>
+          <t>2021153462783762432</t>
+        </is>
+      </c>
+      <c r="L9" s="6" t="inlineStr">
+        <is>
+          <t>SL Order Placed | Trigger: 59.00</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Mine/logs/mine_signal_logs.xlsx
+++ b/Mine/logs/mine_signal_logs.xlsx
@@ -480,7 +480,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P63"/>
+  <dimension ref="A1:P67"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -3638,6 +3638,206 @@
       <c r="N63" s="4" t="inlineStr"/>
       <c r="O63" s="4" t="inlineStr"/>
       <c r="P63" s="4" t="inlineStr">
+        <is>
+          <t>Low Strike Check</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="4" t="inlineStr">
+        <is>
+          <t>2026-02-11 14:45:00</t>
+        </is>
+      </c>
+      <c r="B64" s="4" t="inlineStr">
+        <is>
+          <t>14:45:00</t>
+        </is>
+      </c>
+      <c r="C64" s="4" t="inlineStr">
+        <is>
+          <t>14:45</t>
+        </is>
+      </c>
+      <c r="D64" s="4" t="inlineStr">
+        <is>
+          <t>146.45</t>
+        </is>
+      </c>
+      <c r="E64" s="4" t="inlineStr"/>
+      <c r="F64" s="4" t="inlineStr">
+        <is>
+          <t>139.00</t>
+        </is>
+      </c>
+      <c r="G64" s="4" t="inlineStr"/>
+      <c r="H64" s="4" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="I64" s="4" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="J64" s="4" t="inlineStr"/>
+      <c r="K64" s="4" t="inlineStr"/>
+      <c r="L64" s="4" t="inlineStr"/>
+      <c r="M64" s="4" t="inlineStr"/>
+      <c r="N64" s="4" t="inlineStr"/>
+      <c r="O64" s="4" t="inlineStr"/>
+      <c r="P64" s="4" t="inlineStr">
+        <is>
+          <t>High Strike Check</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="4" t="inlineStr">
+        <is>
+          <t>2026-02-11 14:45:00</t>
+        </is>
+      </c>
+      <c r="B65" s="4" t="inlineStr">
+        <is>
+          <t>14:45:00</t>
+        </is>
+      </c>
+      <c r="C65" s="4" t="inlineStr">
+        <is>
+          <t>14:45</t>
+        </is>
+      </c>
+      <c r="D65" s="4" t="inlineStr">
+        <is>
+          <t>177.00</t>
+        </is>
+      </c>
+      <c r="E65" s="4" t="inlineStr"/>
+      <c r="F65" s="4" t="inlineStr">
+        <is>
+          <t>118.00</t>
+        </is>
+      </c>
+      <c r="G65" s="4" t="inlineStr"/>
+      <c r="H65" s="4" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="I65" s="4" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="J65" s="4" t="inlineStr"/>
+      <c r="K65" s="4" t="inlineStr"/>
+      <c r="L65" s="4" t="inlineStr"/>
+      <c r="M65" s="4" t="inlineStr"/>
+      <c r="N65" s="4" t="inlineStr"/>
+      <c r="O65" s="4" t="inlineStr"/>
+      <c r="P65" s="4" t="inlineStr">
+        <is>
+          <t>Low Strike Check</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="4" t="inlineStr">
+        <is>
+          <t>2026-02-11 14:50:00</t>
+        </is>
+      </c>
+      <c r="B66" s="4" t="inlineStr">
+        <is>
+          <t>14:50:00</t>
+        </is>
+      </c>
+      <c r="C66" s="4" t="inlineStr">
+        <is>
+          <t>14:50</t>
+        </is>
+      </c>
+      <c r="D66" s="4" t="inlineStr">
+        <is>
+          <t>146.45</t>
+        </is>
+      </c>
+      <c r="E66" s="4" t="inlineStr"/>
+      <c r="F66" s="4" t="inlineStr">
+        <is>
+          <t>139.00</t>
+        </is>
+      </c>
+      <c r="G66" s="4" t="inlineStr"/>
+      <c r="H66" s="4" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="I66" s="4" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="J66" s="4" t="inlineStr"/>
+      <c r="K66" s="4" t="inlineStr"/>
+      <c r="L66" s="4" t="inlineStr"/>
+      <c r="M66" s="4" t="inlineStr"/>
+      <c r="N66" s="4" t="inlineStr"/>
+      <c r="O66" s="4" t="inlineStr"/>
+      <c r="P66" s="4" t="inlineStr">
+        <is>
+          <t>High Strike Check</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="4" t="inlineStr">
+        <is>
+          <t>2026-02-11 14:50:00</t>
+        </is>
+      </c>
+      <c r="B67" s="4" t="inlineStr">
+        <is>
+          <t>14:50:00</t>
+        </is>
+      </c>
+      <c r="C67" s="4" t="inlineStr">
+        <is>
+          <t>14:50</t>
+        </is>
+      </c>
+      <c r="D67" s="4" t="inlineStr">
+        <is>
+          <t>177.00</t>
+        </is>
+      </c>
+      <c r="E67" s="4" t="inlineStr"/>
+      <c r="F67" s="4" t="inlineStr">
+        <is>
+          <t>118.00</t>
+        </is>
+      </c>
+      <c r="G67" s="4" t="inlineStr"/>
+      <c r="H67" s="4" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="I67" s="4" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="J67" s="4" t="inlineStr"/>
+      <c r="K67" s="4" t="inlineStr"/>
+      <c r="L67" s="4" t="inlineStr"/>
+      <c r="M67" s="4" t="inlineStr"/>
+      <c r="N67" s="4" t="inlineStr"/>
+      <c r="O67" s="4" t="inlineStr"/>
+      <c r="P67" s="4" t="inlineStr">
         <is>
           <t>Low Strike Check</t>
         </is>

--- a/Mine/logs/mine_signal_logs.xlsx
+++ b/Mine/logs/mine_signal_logs.xlsx
@@ -480,7 +480,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P67"/>
+  <dimension ref="A1:P69"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -3838,6 +3838,106 @@
       <c r="N67" s="4" t="inlineStr"/>
       <c r="O67" s="4" t="inlineStr"/>
       <c r="P67" s="4" t="inlineStr">
+        <is>
+          <t>Low Strike Check</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="4" t="inlineStr">
+        <is>
+          <t>2026-02-11 15:00:00</t>
+        </is>
+      </c>
+      <c r="B68" s="4" t="inlineStr">
+        <is>
+          <t>15:00:00</t>
+        </is>
+      </c>
+      <c r="C68" s="4" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="D68" s="4" t="inlineStr">
+        <is>
+          <t>146.45</t>
+        </is>
+      </c>
+      <c r="E68" s="4" t="inlineStr"/>
+      <c r="F68" s="4" t="inlineStr">
+        <is>
+          <t>139.00</t>
+        </is>
+      </c>
+      <c r="G68" s="4" t="inlineStr"/>
+      <c r="H68" s="4" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="I68" s="4" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="J68" s="4" t="inlineStr"/>
+      <c r="K68" s="4" t="inlineStr"/>
+      <c r="L68" s="4" t="inlineStr"/>
+      <c r="M68" s="4" t="inlineStr"/>
+      <c r="N68" s="4" t="inlineStr"/>
+      <c r="O68" s="4" t="inlineStr"/>
+      <c r="P68" s="4" t="inlineStr">
+        <is>
+          <t>High Strike Check</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="4" t="inlineStr">
+        <is>
+          <t>2026-02-11 15:00:00</t>
+        </is>
+      </c>
+      <c r="B69" s="4" t="inlineStr">
+        <is>
+          <t>15:00:00</t>
+        </is>
+      </c>
+      <c r="C69" s="4" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="D69" s="4" t="inlineStr">
+        <is>
+          <t>177.00</t>
+        </is>
+      </c>
+      <c r="E69" s="4" t="inlineStr"/>
+      <c r="F69" s="4" t="inlineStr">
+        <is>
+          <t>118.00</t>
+        </is>
+      </c>
+      <c r="G69" s="4" t="inlineStr"/>
+      <c r="H69" s="4" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="I69" s="4" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="J69" s="4" t="inlineStr"/>
+      <c r="K69" s="4" t="inlineStr"/>
+      <c r="L69" s="4" t="inlineStr"/>
+      <c r="M69" s="4" t="inlineStr"/>
+      <c r="N69" s="4" t="inlineStr"/>
+      <c r="O69" s="4" t="inlineStr"/>
+      <c r="P69" s="4" t="inlineStr">
         <is>
           <t>Low Strike Check</t>
         </is>

--- a/Mine/logs/mine_signal_logs.xlsx
+++ b/Mine/logs/mine_signal_logs.xlsx
@@ -480,7 +480,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P69"/>
+  <dimension ref="A1:P71"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -3938,6 +3938,106 @@
       <c r="N69" s="4" t="inlineStr"/>
       <c r="O69" s="4" t="inlineStr"/>
       <c r="P69" s="4" t="inlineStr">
+        <is>
+          <t>Low Strike Check</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="4" t="inlineStr">
+        <is>
+          <t>2026-02-11 15:10:00</t>
+        </is>
+      </c>
+      <c r="B70" s="4" t="inlineStr">
+        <is>
+          <t>15:10:00</t>
+        </is>
+      </c>
+      <c r="C70" s="4" t="inlineStr">
+        <is>
+          <t>15:10</t>
+        </is>
+      </c>
+      <c r="D70" s="4" t="inlineStr">
+        <is>
+          <t>146.45</t>
+        </is>
+      </c>
+      <c r="E70" s="4" t="inlineStr"/>
+      <c r="F70" s="4" t="inlineStr">
+        <is>
+          <t>139.00</t>
+        </is>
+      </c>
+      <c r="G70" s="4" t="inlineStr"/>
+      <c r="H70" s="4" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="I70" s="4" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="J70" s="4" t="inlineStr"/>
+      <c r="K70" s="4" t="inlineStr"/>
+      <c r="L70" s="4" t="inlineStr"/>
+      <c r="M70" s="4" t="inlineStr"/>
+      <c r="N70" s="4" t="inlineStr"/>
+      <c r="O70" s="4" t="inlineStr"/>
+      <c r="P70" s="4" t="inlineStr">
+        <is>
+          <t>High Strike Check</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="4" t="inlineStr">
+        <is>
+          <t>2026-02-11 15:10:00</t>
+        </is>
+      </c>
+      <c r="B71" s="4" t="inlineStr">
+        <is>
+          <t>15:10:00</t>
+        </is>
+      </c>
+      <c r="C71" s="4" t="inlineStr">
+        <is>
+          <t>15:10</t>
+        </is>
+      </c>
+      <c r="D71" s="4" t="inlineStr">
+        <is>
+          <t>177.00</t>
+        </is>
+      </c>
+      <c r="E71" s="4" t="inlineStr"/>
+      <c r="F71" s="4" t="inlineStr">
+        <is>
+          <t>118.00</t>
+        </is>
+      </c>
+      <c r="G71" s="4" t="inlineStr"/>
+      <c r="H71" s="4" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="I71" s="4" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="J71" s="4" t="inlineStr"/>
+      <c r="K71" s="4" t="inlineStr"/>
+      <c r="L71" s="4" t="inlineStr"/>
+      <c r="M71" s="4" t="inlineStr"/>
+      <c r="N71" s="4" t="inlineStr"/>
+      <c r="O71" s="4" t="inlineStr"/>
+      <c r="P71" s="4" t="inlineStr">
         <is>
           <t>Low Strike Check</t>
         </is>

--- a/Mine/logs/mine_signal_logs.xlsx
+++ b/Mine/logs/mine_signal_logs.xlsx
@@ -480,7 +480,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P29"/>
+  <dimension ref="A1:P31"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -1938,6 +1938,106 @@
       <c r="N29" s="4" t="inlineStr"/>
       <c r="O29" s="4" t="inlineStr"/>
       <c r="P29" s="4" t="inlineStr">
+        <is>
+          <t>Low Strike Check</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="4" t="inlineStr">
+        <is>
+          <t>2026-02-12 10:20:00</t>
+        </is>
+      </c>
+      <c r="B30" s="4" t="inlineStr">
+        <is>
+          <t>10:20:00</t>
+        </is>
+      </c>
+      <c r="C30" s="4" t="inlineStr">
+        <is>
+          <t>10:20</t>
+        </is>
+      </c>
+      <c r="D30" s="4" t="inlineStr">
+        <is>
+          <t>156.60</t>
+        </is>
+      </c>
+      <c r="E30" s="4" t="inlineStr"/>
+      <c r="F30" s="4" t="inlineStr">
+        <is>
+          <t>124.55</t>
+        </is>
+      </c>
+      <c r="G30" s="4" t="inlineStr"/>
+      <c r="H30" s="4" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="I30" s="4" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="J30" s="4" t="inlineStr"/>
+      <c r="K30" s="4" t="inlineStr"/>
+      <c r="L30" s="4" t="inlineStr"/>
+      <c r="M30" s="4" t="inlineStr"/>
+      <c r="N30" s="4" t="inlineStr"/>
+      <c r="O30" s="4" t="inlineStr"/>
+      <c r="P30" s="4" t="inlineStr">
+        <is>
+          <t>High Strike Check</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="4" t="inlineStr">
+        <is>
+          <t>2026-02-12 10:20:00</t>
+        </is>
+      </c>
+      <c r="B31" s="4" t="inlineStr">
+        <is>
+          <t>10:20:00</t>
+        </is>
+      </c>
+      <c r="C31" s="4" t="inlineStr">
+        <is>
+          <t>10:20</t>
+        </is>
+      </c>
+      <c r="D31" s="4" t="inlineStr">
+        <is>
+          <t>169.80</t>
+        </is>
+      </c>
+      <c r="E31" s="4" t="inlineStr"/>
+      <c r="F31" s="4" t="inlineStr">
+        <is>
+          <t>101.15</t>
+        </is>
+      </c>
+      <c r="G31" s="4" t="inlineStr"/>
+      <c r="H31" s="4" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="I31" s="4" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="J31" s="4" t="inlineStr"/>
+      <c r="K31" s="4" t="inlineStr"/>
+      <c r="L31" s="4" t="inlineStr"/>
+      <c r="M31" s="4" t="inlineStr"/>
+      <c r="N31" s="4" t="inlineStr"/>
+      <c r="O31" s="4" t="inlineStr"/>
+      <c r="P31" s="4" t="inlineStr">
         <is>
           <t>Low Strike Check</t>
         </is>

--- a/Mine/logs/mine_signal_logs.xlsx
+++ b/Mine/logs/mine_signal_logs.xlsx
@@ -480,7 +480,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P31"/>
+  <dimension ref="A1:P43"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -2038,6 +2038,606 @@
       <c r="N31" s="4" t="inlineStr"/>
       <c r="O31" s="4" t="inlineStr"/>
       <c r="P31" s="4" t="inlineStr">
+        <is>
+          <t>Low Strike Check</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="4" t="inlineStr">
+        <is>
+          <t>2026-02-12 11:00:00</t>
+        </is>
+      </c>
+      <c r="B32" s="4" t="inlineStr">
+        <is>
+          <t>11:00:00</t>
+        </is>
+      </c>
+      <c r="C32" s="4" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
+      <c r="D32" s="4" t="inlineStr">
+        <is>
+          <t>156.60</t>
+        </is>
+      </c>
+      <c r="E32" s="4" t="inlineStr"/>
+      <c r="F32" s="4" t="inlineStr">
+        <is>
+          <t>124.55</t>
+        </is>
+      </c>
+      <c r="G32" s="4" t="inlineStr"/>
+      <c r="H32" s="4" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="I32" s="4" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="J32" s="4" t="inlineStr"/>
+      <c r="K32" s="4" t="inlineStr"/>
+      <c r="L32" s="4" t="inlineStr"/>
+      <c r="M32" s="4" t="inlineStr"/>
+      <c r="N32" s="4" t="inlineStr"/>
+      <c r="O32" s="4" t="inlineStr"/>
+      <c r="P32" s="4" t="inlineStr">
+        <is>
+          <t>High Strike Check</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="4" t="inlineStr">
+        <is>
+          <t>2026-02-12 11:00:00</t>
+        </is>
+      </c>
+      <c r="B33" s="4" t="inlineStr">
+        <is>
+          <t>11:00:00</t>
+        </is>
+      </c>
+      <c r="C33" s="4" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
+      <c r="D33" s="4" t="inlineStr">
+        <is>
+          <t>169.80</t>
+        </is>
+      </c>
+      <c r="E33" s="4" t="inlineStr"/>
+      <c r="F33" s="4" t="inlineStr">
+        <is>
+          <t>101.15</t>
+        </is>
+      </c>
+      <c r="G33" s="4" t="inlineStr"/>
+      <c r="H33" s="4" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="I33" s="4" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="J33" s="4" t="inlineStr"/>
+      <c r="K33" s="4" t="inlineStr"/>
+      <c r="L33" s="4" t="inlineStr"/>
+      <c r="M33" s="4" t="inlineStr"/>
+      <c r="N33" s="4" t="inlineStr"/>
+      <c r="O33" s="4" t="inlineStr"/>
+      <c r="P33" s="4" t="inlineStr">
+        <is>
+          <t>Low Strike Check</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="4" t="inlineStr">
+        <is>
+          <t>2026-02-12 11:05:00</t>
+        </is>
+      </c>
+      <c r="B34" s="4" t="inlineStr">
+        <is>
+          <t>11:05:00</t>
+        </is>
+      </c>
+      <c r="C34" s="4" t="inlineStr">
+        <is>
+          <t>11:05</t>
+        </is>
+      </c>
+      <c r="D34" s="4" t="inlineStr">
+        <is>
+          <t>156.60</t>
+        </is>
+      </c>
+      <c r="E34" s="4" t="inlineStr"/>
+      <c r="F34" s="4" t="inlineStr">
+        <is>
+          <t>124.55</t>
+        </is>
+      </c>
+      <c r="G34" s="4" t="inlineStr"/>
+      <c r="H34" s="4" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="I34" s="4" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="J34" s="4" t="inlineStr"/>
+      <c r="K34" s="4" t="inlineStr"/>
+      <c r="L34" s="4" t="inlineStr"/>
+      <c r="M34" s="4" t="inlineStr"/>
+      <c r="N34" s="4" t="inlineStr"/>
+      <c r="O34" s="4" t="inlineStr"/>
+      <c r="P34" s="4" t="inlineStr">
+        <is>
+          <t>High Strike Check</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="4" t="inlineStr">
+        <is>
+          <t>2026-02-12 11:05:00</t>
+        </is>
+      </c>
+      <c r="B35" s="4" t="inlineStr">
+        <is>
+          <t>11:05:00</t>
+        </is>
+      </c>
+      <c r="C35" s="4" t="inlineStr">
+        <is>
+          <t>11:05</t>
+        </is>
+      </c>
+      <c r="D35" s="4" t="inlineStr">
+        <is>
+          <t>169.80</t>
+        </is>
+      </c>
+      <c r="E35" s="4" t="inlineStr"/>
+      <c r="F35" s="4" t="inlineStr">
+        <is>
+          <t>101.15</t>
+        </is>
+      </c>
+      <c r="G35" s="4" t="inlineStr"/>
+      <c r="H35" s="4" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="I35" s="4" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="J35" s="4" t="inlineStr"/>
+      <c r="K35" s="4" t="inlineStr"/>
+      <c r="L35" s="4" t="inlineStr"/>
+      <c r="M35" s="4" t="inlineStr"/>
+      <c r="N35" s="4" t="inlineStr"/>
+      <c r="O35" s="4" t="inlineStr"/>
+      <c r="P35" s="4" t="inlineStr">
+        <is>
+          <t>Low Strike Check</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="4" t="inlineStr">
+        <is>
+          <t>2026-02-12 11:10:00</t>
+        </is>
+      </c>
+      <c r="B36" s="4" t="inlineStr">
+        <is>
+          <t>11:10:00</t>
+        </is>
+      </c>
+      <c r="C36" s="4" t="inlineStr">
+        <is>
+          <t>11:10</t>
+        </is>
+      </c>
+      <c r="D36" s="4" t="inlineStr">
+        <is>
+          <t>156.60</t>
+        </is>
+      </c>
+      <c r="E36" s="4" t="inlineStr"/>
+      <c r="F36" s="4" t="inlineStr">
+        <is>
+          <t>124.55</t>
+        </is>
+      </c>
+      <c r="G36" s="4" t="inlineStr"/>
+      <c r="H36" s="4" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="I36" s="4" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="J36" s="4" t="inlineStr"/>
+      <c r="K36" s="4" t="inlineStr"/>
+      <c r="L36" s="4" t="inlineStr"/>
+      <c r="M36" s="4" t="inlineStr"/>
+      <c r="N36" s="4" t="inlineStr"/>
+      <c r="O36" s="4" t="inlineStr"/>
+      <c r="P36" s="4" t="inlineStr">
+        <is>
+          <t>High Strike Check</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="4" t="inlineStr">
+        <is>
+          <t>2026-02-12 11:10:00</t>
+        </is>
+      </c>
+      <c r="B37" s="4" t="inlineStr">
+        <is>
+          <t>11:10:00</t>
+        </is>
+      </c>
+      <c r="C37" s="4" t="inlineStr">
+        <is>
+          <t>11:10</t>
+        </is>
+      </c>
+      <c r="D37" s="4" t="inlineStr">
+        <is>
+          <t>169.80</t>
+        </is>
+      </c>
+      <c r="E37" s="4" t="inlineStr"/>
+      <c r="F37" s="4" t="inlineStr">
+        <is>
+          <t>101.15</t>
+        </is>
+      </c>
+      <c r="G37" s="4" t="inlineStr"/>
+      <c r="H37" s="4" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="I37" s="4" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="J37" s="4" t="inlineStr"/>
+      <c r="K37" s="4" t="inlineStr"/>
+      <c r="L37" s="4" t="inlineStr"/>
+      <c r="M37" s="4" t="inlineStr"/>
+      <c r="N37" s="4" t="inlineStr"/>
+      <c r="O37" s="4" t="inlineStr"/>
+      <c r="P37" s="4" t="inlineStr">
+        <is>
+          <t>Low Strike Check</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="4" t="inlineStr">
+        <is>
+          <t>2026-02-12 11:15:00</t>
+        </is>
+      </c>
+      <c r="B38" s="4" t="inlineStr">
+        <is>
+          <t>11:15:00</t>
+        </is>
+      </c>
+      <c r="C38" s="4" t="inlineStr">
+        <is>
+          <t>11:15</t>
+        </is>
+      </c>
+      <c r="D38" s="4" t="inlineStr">
+        <is>
+          <t>156.60</t>
+        </is>
+      </c>
+      <c r="E38" s="4" t="inlineStr"/>
+      <c r="F38" s="4" t="inlineStr">
+        <is>
+          <t>124.55</t>
+        </is>
+      </c>
+      <c r="G38" s="4" t="inlineStr"/>
+      <c r="H38" s="4" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="I38" s="4" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="J38" s="4" t="inlineStr"/>
+      <c r="K38" s="4" t="inlineStr"/>
+      <c r="L38" s="4" t="inlineStr"/>
+      <c r="M38" s="4" t="inlineStr"/>
+      <c r="N38" s="4" t="inlineStr"/>
+      <c r="O38" s="4" t="inlineStr"/>
+      <c r="P38" s="4" t="inlineStr">
+        <is>
+          <t>High Strike Check</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="4" t="inlineStr">
+        <is>
+          <t>2026-02-12 11:15:00</t>
+        </is>
+      </c>
+      <c r="B39" s="4" t="inlineStr">
+        <is>
+          <t>11:15:00</t>
+        </is>
+      </c>
+      <c r="C39" s="4" t="inlineStr">
+        <is>
+          <t>11:15</t>
+        </is>
+      </c>
+      <c r="D39" s="4" t="inlineStr">
+        <is>
+          <t>169.80</t>
+        </is>
+      </c>
+      <c r="E39" s="4" t="inlineStr"/>
+      <c r="F39" s="4" t="inlineStr">
+        <is>
+          <t>101.15</t>
+        </is>
+      </c>
+      <c r="G39" s="4" t="inlineStr"/>
+      <c r="H39" s="4" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="I39" s="4" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="J39" s="4" t="inlineStr"/>
+      <c r="K39" s="4" t="inlineStr"/>
+      <c r="L39" s="4" t="inlineStr"/>
+      <c r="M39" s="4" t="inlineStr"/>
+      <c r="N39" s="4" t="inlineStr"/>
+      <c r="O39" s="4" t="inlineStr"/>
+      <c r="P39" s="4" t="inlineStr">
+        <is>
+          <t>Low Strike Check</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="4" t="inlineStr">
+        <is>
+          <t>2026-02-12 11:20:00</t>
+        </is>
+      </c>
+      <c r="B40" s="4" t="inlineStr">
+        <is>
+          <t>11:20:00</t>
+        </is>
+      </c>
+      <c r="C40" s="4" t="inlineStr">
+        <is>
+          <t>11:20</t>
+        </is>
+      </c>
+      <c r="D40" s="4" t="inlineStr">
+        <is>
+          <t>156.60</t>
+        </is>
+      </c>
+      <c r="E40" s="4" t="inlineStr"/>
+      <c r="F40" s="4" t="inlineStr">
+        <is>
+          <t>124.55</t>
+        </is>
+      </c>
+      <c r="G40" s="4" t="inlineStr"/>
+      <c r="H40" s="4" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="I40" s="4" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="J40" s="4" t="inlineStr"/>
+      <c r="K40" s="4" t="inlineStr"/>
+      <c r="L40" s="4" t="inlineStr"/>
+      <c r="M40" s="4" t="inlineStr"/>
+      <c r="N40" s="4" t="inlineStr"/>
+      <c r="O40" s="4" t="inlineStr"/>
+      <c r="P40" s="4" t="inlineStr">
+        <is>
+          <t>High Strike Check</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="4" t="inlineStr">
+        <is>
+          <t>2026-02-12 11:20:00</t>
+        </is>
+      </c>
+      <c r="B41" s="4" t="inlineStr">
+        <is>
+          <t>11:20:00</t>
+        </is>
+      </c>
+      <c r="C41" s="4" t="inlineStr">
+        <is>
+          <t>11:20</t>
+        </is>
+      </c>
+      <c r="D41" s="4" t="inlineStr">
+        <is>
+          <t>169.80</t>
+        </is>
+      </c>
+      <c r="E41" s="4" t="inlineStr"/>
+      <c r="F41" s="4" t="inlineStr">
+        <is>
+          <t>101.15</t>
+        </is>
+      </c>
+      <c r="G41" s="4" t="inlineStr"/>
+      <c r="H41" s="4" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="I41" s="4" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="J41" s="4" t="inlineStr"/>
+      <c r="K41" s="4" t="inlineStr"/>
+      <c r="L41" s="4" t="inlineStr"/>
+      <c r="M41" s="4" t="inlineStr"/>
+      <c r="N41" s="4" t="inlineStr"/>
+      <c r="O41" s="4" t="inlineStr"/>
+      <c r="P41" s="4" t="inlineStr">
+        <is>
+          <t>Low Strike Check</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="4" t="inlineStr">
+        <is>
+          <t>2026-02-12 11:25:00</t>
+        </is>
+      </c>
+      <c r="B42" s="4" t="inlineStr">
+        <is>
+          <t>11:25:00</t>
+        </is>
+      </c>
+      <c r="C42" s="4" t="inlineStr">
+        <is>
+          <t>11:25</t>
+        </is>
+      </c>
+      <c r="D42" s="4" t="inlineStr">
+        <is>
+          <t>156.60</t>
+        </is>
+      </c>
+      <c r="E42" s="4" t="inlineStr"/>
+      <c r="F42" s="4" t="inlineStr">
+        <is>
+          <t>124.55</t>
+        </is>
+      </c>
+      <c r="G42" s="4" t="inlineStr"/>
+      <c r="H42" s="4" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="I42" s="4" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="J42" s="4" t="inlineStr"/>
+      <c r="K42" s="4" t="inlineStr"/>
+      <c r="L42" s="4" t="inlineStr"/>
+      <c r="M42" s="4" t="inlineStr"/>
+      <c r="N42" s="4" t="inlineStr"/>
+      <c r="O42" s="4" t="inlineStr"/>
+      <c r="P42" s="4" t="inlineStr">
+        <is>
+          <t>High Strike Check</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="4" t="inlineStr">
+        <is>
+          <t>2026-02-12 11:25:00</t>
+        </is>
+      </c>
+      <c r="B43" s="4" t="inlineStr">
+        <is>
+          <t>11:25:00</t>
+        </is>
+      </c>
+      <c r="C43" s="4" t="inlineStr">
+        <is>
+          <t>11:25</t>
+        </is>
+      </c>
+      <c r="D43" s="4" t="inlineStr">
+        <is>
+          <t>169.80</t>
+        </is>
+      </c>
+      <c r="E43" s="4" t="inlineStr"/>
+      <c r="F43" s="4" t="inlineStr">
+        <is>
+          <t>101.15</t>
+        </is>
+      </c>
+      <c r="G43" s="4" t="inlineStr"/>
+      <c r="H43" s="4" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="I43" s="4" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="J43" s="4" t="inlineStr"/>
+      <c r="K43" s="4" t="inlineStr"/>
+      <c r="L43" s="4" t="inlineStr"/>
+      <c r="M43" s="4" t="inlineStr"/>
+      <c r="N43" s="4" t="inlineStr"/>
+      <c r="O43" s="4" t="inlineStr"/>
+      <c r="P43" s="4" t="inlineStr">
         <is>
           <t>Low Strike Check</t>
         </is>

--- a/Mine/logs/mine_signal_logs.xlsx
+++ b/Mine/logs/mine_signal_logs.xlsx
@@ -33,7 +33,7 @@
       <sz val="11"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="6">
     <fill>
       <patternFill/>
     </fill>
@@ -50,6 +50,18 @@
       <patternFill patternType="solid">
         <fgColor rgb="FF70AD47"/>
         <bgColor rgb="FF70AD47"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFFFFF"/>
+        <bgColor rgb="00FFFFFF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00C6EFCE"/>
+        <bgColor rgb="00C6EFCE"/>
       </patternFill>
     </fill>
   </fills>
@@ -101,7 +113,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -113,6 +125,12 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -480,7 +498,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P43"/>
+  <dimension ref="A1:P87"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -2643,6 +2661,2214 @@
         </is>
       </c>
     </row>
+    <row r="44">
+      <c r="A44" s="4" t="inlineStr">
+        <is>
+          <t>2026-02-12 12:00:00</t>
+        </is>
+      </c>
+      <c r="B44" s="4" t="inlineStr">
+        <is>
+          <t>12:00:00</t>
+        </is>
+      </c>
+      <c r="C44" s="4" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
+      <c r="D44" s="4" t="inlineStr">
+        <is>
+          <t>156.60</t>
+        </is>
+      </c>
+      <c r="E44" s="4" t="inlineStr"/>
+      <c r="F44" s="4" t="inlineStr">
+        <is>
+          <t>124.55</t>
+        </is>
+      </c>
+      <c r="G44" s="4" t="inlineStr"/>
+      <c r="H44" s="4" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="I44" s="4" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="J44" s="4" t="inlineStr"/>
+      <c r="K44" s="4" t="inlineStr"/>
+      <c r="L44" s="4" t="inlineStr"/>
+      <c r="M44" s="4" t="inlineStr"/>
+      <c r="N44" s="4" t="inlineStr"/>
+      <c r="O44" s="4" t="inlineStr"/>
+      <c r="P44" s="4" t="inlineStr">
+        <is>
+          <t>High Strike Check</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="4" t="inlineStr">
+        <is>
+          <t>2026-02-12 12:00:00</t>
+        </is>
+      </c>
+      <c r="B45" s="4" t="inlineStr">
+        <is>
+          <t>12:00:00</t>
+        </is>
+      </c>
+      <c r="C45" s="4" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
+      <c r="D45" s="4" t="inlineStr">
+        <is>
+          <t>169.80</t>
+        </is>
+      </c>
+      <c r="E45" s="4" t="inlineStr"/>
+      <c r="F45" s="4" t="inlineStr">
+        <is>
+          <t>101.15</t>
+        </is>
+      </c>
+      <c r="G45" s="4" t="inlineStr"/>
+      <c r="H45" s="4" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="I45" s="4" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="J45" s="4" t="inlineStr"/>
+      <c r="K45" s="4" t="inlineStr"/>
+      <c r="L45" s="4" t="inlineStr"/>
+      <c r="M45" s="4" t="inlineStr"/>
+      <c r="N45" s="4" t="inlineStr"/>
+      <c r="O45" s="4" t="inlineStr"/>
+      <c r="P45" s="4" t="inlineStr">
+        <is>
+          <t>Low Strike Check</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="4" t="inlineStr">
+        <is>
+          <t>2026-02-12 12:25:00</t>
+        </is>
+      </c>
+      <c r="B46" s="4" t="inlineStr">
+        <is>
+          <t>12:25:00</t>
+        </is>
+      </c>
+      <c r="C46" s="4" t="inlineStr">
+        <is>
+          <t>12:25</t>
+        </is>
+      </c>
+      <c r="D46" s="4" t="inlineStr">
+        <is>
+          <t>156.60</t>
+        </is>
+      </c>
+      <c r="E46" s="4" t="inlineStr"/>
+      <c r="F46" s="4" t="inlineStr">
+        <is>
+          <t>124.55</t>
+        </is>
+      </c>
+      <c r="G46" s="4" t="inlineStr"/>
+      <c r="H46" s="4" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="I46" s="4" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="J46" s="4" t="inlineStr"/>
+      <c r="K46" s="4" t="inlineStr"/>
+      <c r="L46" s="4" t="inlineStr"/>
+      <c r="M46" s="4" t="inlineStr"/>
+      <c r="N46" s="4" t="inlineStr"/>
+      <c r="O46" s="4" t="inlineStr"/>
+      <c r="P46" s="4" t="inlineStr">
+        <is>
+          <t>High Strike Check</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="4" t="inlineStr">
+        <is>
+          <t>2026-02-12 12:25:00</t>
+        </is>
+      </c>
+      <c r="B47" s="4" t="inlineStr">
+        <is>
+          <t>12:25:00</t>
+        </is>
+      </c>
+      <c r="C47" s="4" t="inlineStr">
+        <is>
+          <t>12:25</t>
+        </is>
+      </c>
+      <c r="D47" s="4" t="inlineStr">
+        <is>
+          <t>169.80</t>
+        </is>
+      </c>
+      <c r="E47" s="4" t="inlineStr"/>
+      <c r="F47" s="4" t="inlineStr">
+        <is>
+          <t>101.15</t>
+        </is>
+      </c>
+      <c r="G47" s="4" t="inlineStr"/>
+      <c r="H47" s="4" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="I47" s="4" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="J47" s="4" t="inlineStr"/>
+      <c r="K47" s="4" t="inlineStr"/>
+      <c r="L47" s="4" t="inlineStr"/>
+      <c r="M47" s="4" t="inlineStr"/>
+      <c r="N47" s="4" t="inlineStr"/>
+      <c r="O47" s="4" t="inlineStr"/>
+      <c r="P47" s="4" t="inlineStr">
+        <is>
+          <t>Low Strike Check</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="4" t="inlineStr">
+        <is>
+          <t>2026-02-12 13:40:00</t>
+        </is>
+      </c>
+      <c r="B48" s="4" t="inlineStr">
+        <is>
+          <t>13:40:00</t>
+        </is>
+      </c>
+      <c r="C48" s="4" t="inlineStr">
+        <is>
+          <t>13:40</t>
+        </is>
+      </c>
+      <c r="D48" s="4" t="inlineStr">
+        <is>
+          <t>156.60</t>
+        </is>
+      </c>
+      <c r="E48" s="4" t="inlineStr"/>
+      <c r="F48" s="4" t="inlineStr">
+        <is>
+          <t>124.55</t>
+        </is>
+      </c>
+      <c r="G48" s="4" t="inlineStr"/>
+      <c r="H48" s="4" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="I48" s="4" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="J48" s="4" t="inlineStr"/>
+      <c r="K48" s="4" t="inlineStr"/>
+      <c r="L48" s="4" t="inlineStr"/>
+      <c r="M48" s="4" t="inlineStr"/>
+      <c r="N48" s="4" t="inlineStr"/>
+      <c r="O48" s="4" t="inlineStr"/>
+      <c r="P48" s="4" t="inlineStr">
+        <is>
+          <t>High Strike Check</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="4" t="inlineStr">
+        <is>
+          <t>2026-02-12 13:40:00</t>
+        </is>
+      </c>
+      <c r="B49" s="4" t="inlineStr">
+        <is>
+          <t>13:40:00</t>
+        </is>
+      </c>
+      <c r="C49" s="4" t="inlineStr">
+        <is>
+          <t>13:40</t>
+        </is>
+      </c>
+      <c r="D49" s="4" t="inlineStr">
+        <is>
+          <t>169.80</t>
+        </is>
+      </c>
+      <c r="E49" s="4" t="inlineStr"/>
+      <c r="F49" s="4" t="inlineStr">
+        <is>
+          <t>101.15</t>
+        </is>
+      </c>
+      <c r="G49" s="4" t="inlineStr"/>
+      <c r="H49" s="4" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="I49" s="4" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="J49" s="4" t="inlineStr"/>
+      <c r="K49" s="4" t="inlineStr"/>
+      <c r="L49" s="4" t="inlineStr"/>
+      <c r="M49" s="4" t="inlineStr"/>
+      <c r="N49" s="4" t="inlineStr"/>
+      <c r="O49" s="4" t="inlineStr"/>
+      <c r="P49" s="4" t="inlineStr">
+        <is>
+          <t>Low Strike Check</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="4" t="inlineStr">
+        <is>
+          <t>2026-02-12 13:45:00</t>
+        </is>
+      </c>
+      <c r="B50" s="4" t="inlineStr">
+        <is>
+          <t>13:45:00</t>
+        </is>
+      </c>
+      <c r="C50" s="4" t="inlineStr">
+        <is>
+          <t>13:45</t>
+        </is>
+      </c>
+      <c r="D50" s="4" t="inlineStr">
+        <is>
+          <t>156.60</t>
+        </is>
+      </c>
+      <c r="E50" s="4" t="inlineStr"/>
+      <c r="F50" s="4" t="inlineStr">
+        <is>
+          <t>124.55</t>
+        </is>
+      </c>
+      <c r="G50" s="4" t="inlineStr"/>
+      <c r="H50" s="4" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="I50" s="4" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="J50" s="4" t="inlineStr"/>
+      <c r="K50" s="4" t="inlineStr"/>
+      <c r="L50" s="4" t="inlineStr"/>
+      <c r="M50" s="4" t="inlineStr"/>
+      <c r="N50" s="4" t="inlineStr"/>
+      <c r="O50" s="4" t="inlineStr"/>
+      <c r="P50" s="4" t="inlineStr">
+        <is>
+          <t>High Strike Check</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="4" t="inlineStr">
+        <is>
+          <t>2026-02-12 13:45:00</t>
+        </is>
+      </c>
+      <c r="B51" s="4" t="inlineStr">
+        <is>
+          <t>13:45:00</t>
+        </is>
+      </c>
+      <c r="C51" s="4" t="inlineStr">
+        <is>
+          <t>13:45</t>
+        </is>
+      </c>
+      <c r="D51" s="4" t="inlineStr">
+        <is>
+          <t>169.80</t>
+        </is>
+      </c>
+      <c r="E51" s="4" t="inlineStr"/>
+      <c r="F51" s="4" t="inlineStr">
+        <is>
+          <t>101.15</t>
+        </is>
+      </c>
+      <c r="G51" s="4" t="inlineStr"/>
+      <c r="H51" s="4" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="I51" s="4" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="J51" s="4" t="inlineStr"/>
+      <c r="K51" s="4" t="inlineStr"/>
+      <c r="L51" s="4" t="inlineStr"/>
+      <c r="M51" s="4" t="inlineStr"/>
+      <c r="N51" s="4" t="inlineStr"/>
+      <c r="O51" s="4" t="inlineStr"/>
+      <c r="P51" s="4" t="inlineStr">
+        <is>
+          <t>Low Strike Check</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="4" t="inlineStr">
+        <is>
+          <t>2026-02-12 13:50:00</t>
+        </is>
+      </c>
+      <c r="B52" s="4" t="inlineStr">
+        <is>
+          <t>13:50:00</t>
+        </is>
+      </c>
+      <c r="C52" s="4" t="inlineStr">
+        <is>
+          <t>13:50</t>
+        </is>
+      </c>
+      <c r="D52" s="4" t="inlineStr">
+        <is>
+          <t>156.60</t>
+        </is>
+      </c>
+      <c r="E52" s="4" t="inlineStr"/>
+      <c r="F52" s="4" t="inlineStr">
+        <is>
+          <t>124.55</t>
+        </is>
+      </c>
+      <c r="G52" s="4" t="inlineStr"/>
+      <c r="H52" s="4" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="I52" s="4" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="J52" s="4" t="inlineStr"/>
+      <c r="K52" s="4" t="inlineStr"/>
+      <c r="L52" s="4" t="inlineStr"/>
+      <c r="M52" s="4" t="inlineStr"/>
+      <c r="N52" s="4" t="inlineStr"/>
+      <c r="O52" s="4" t="inlineStr"/>
+      <c r="P52" s="4" t="inlineStr">
+        <is>
+          <t>High Strike Check</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="4" t="inlineStr">
+        <is>
+          <t>2026-02-12 13:50:00</t>
+        </is>
+      </c>
+      <c r="B53" s="4" t="inlineStr">
+        <is>
+          <t>13:50:00</t>
+        </is>
+      </c>
+      <c r="C53" s="4" t="inlineStr">
+        <is>
+          <t>13:50</t>
+        </is>
+      </c>
+      <c r="D53" s="4" t="inlineStr">
+        <is>
+          <t>169.80</t>
+        </is>
+      </c>
+      <c r="E53" s="4" t="inlineStr"/>
+      <c r="F53" s="4" t="inlineStr">
+        <is>
+          <t>101.15</t>
+        </is>
+      </c>
+      <c r="G53" s="4" t="inlineStr"/>
+      <c r="H53" s="4" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="I53" s="4" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="J53" s="4" t="inlineStr"/>
+      <c r="K53" s="4" t="inlineStr"/>
+      <c r="L53" s="4" t="inlineStr"/>
+      <c r="M53" s="4" t="inlineStr"/>
+      <c r="N53" s="4" t="inlineStr"/>
+      <c r="O53" s="4" t="inlineStr"/>
+      <c r="P53" s="4" t="inlineStr">
+        <is>
+          <t>Low Strike Check</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="4" t="inlineStr">
+        <is>
+          <t>2026-02-12 13:55:00</t>
+        </is>
+      </c>
+      <c r="B54" s="4" t="inlineStr">
+        <is>
+          <t>13:55:00</t>
+        </is>
+      </c>
+      <c r="C54" s="4" t="inlineStr">
+        <is>
+          <t>13:55</t>
+        </is>
+      </c>
+      <c r="D54" s="4" t="inlineStr">
+        <is>
+          <t>156.60</t>
+        </is>
+      </c>
+      <c r="E54" s="4" t="inlineStr"/>
+      <c r="F54" s="4" t="inlineStr">
+        <is>
+          <t>124.55</t>
+        </is>
+      </c>
+      <c r="G54" s="4" t="inlineStr"/>
+      <c r="H54" s="4" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="I54" s="4" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="J54" s="4" t="inlineStr"/>
+      <c r="K54" s="4" t="inlineStr"/>
+      <c r="L54" s="4" t="inlineStr"/>
+      <c r="M54" s="4" t="inlineStr"/>
+      <c r="N54" s="4" t="inlineStr"/>
+      <c r="O54" s="4" t="inlineStr"/>
+      <c r="P54" s="4" t="inlineStr">
+        <is>
+          <t>High Strike Check</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="4" t="inlineStr">
+        <is>
+          <t>2026-02-12 13:55:00</t>
+        </is>
+      </c>
+      <c r="B55" s="4" t="inlineStr">
+        <is>
+          <t>13:55:00</t>
+        </is>
+      </c>
+      <c r="C55" s="4" t="inlineStr">
+        <is>
+          <t>13:55</t>
+        </is>
+      </c>
+      <c r="D55" s="4" t="inlineStr">
+        <is>
+          <t>169.80</t>
+        </is>
+      </c>
+      <c r="E55" s="4" t="inlineStr"/>
+      <c r="F55" s="4" t="inlineStr">
+        <is>
+          <t>101.15</t>
+        </is>
+      </c>
+      <c r="G55" s="4" t="inlineStr"/>
+      <c r="H55" s="4" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="I55" s="4" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="J55" s="4" t="inlineStr"/>
+      <c r="K55" s="4" t="inlineStr"/>
+      <c r="L55" s="4" t="inlineStr"/>
+      <c r="M55" s="4" t="inlineStr"/>
+      <c r="N55" s="4" t="inlineStr"/>
+      <c r="O55" s="4" t="inlineStr"/>
+      <c r="P55" s="4" t="inlineStr">
+        <is>
+          <t>Low Strike Check</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="4" t="inlineStr">
+        <is>
+          <t>2026-02-12 14:00:00</t>
+        </is>
+      </c>
+      <c r="B56" s="4" t="inlineStr">
+        <is>
+          <t>14:00:00</t>
+        </is>
+      </c>
+      <c r="C56" s="4" t="inlineStr">
+        <is>
+          <t>14:00</t>
+        </is>
+      </c>
+      <c r="D56" s="4" t="inlineStr">
+        <is>
+          <t>156.60</t>
+        </is>
+      </c>
+      <c r="E56" s="4" t="inlineStr"/>
+      <c r="F56" s="4" t="inlineStr">
+        <is>
+          <t>124.55</t>
+        </is>
+      </c>
+      <c r="G56" s="4" t="inlineStr"/>
+      <c r="H56" s="4" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="I56" s="4" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="J56" s="4" t="inlineStr"/>
+      <c r="K56" s="4" t="inlineStr"/>
+      <c r="L56" s="4" t="inlineStr"/>
+      <c r="M56" s="4" t="inlineStr"/>
+      <c r="N56" s="4" t="inlineStr"/>
+      <c r="O56" s="4" t="inlineStr"/>
+      <c r="P56" s="4" t="inlineStr">
+        <is>
+          <t>High Strike Check</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="4" t="inlineStr">
+        <is>
+          <t>2026-02-12 14:00:00</t>
+        </is>
+      </c>
+      <c r="B57" s="4" t="inlineStr">
+        <is>
+          <t>14:00:00</t>
+        </is>
+      </c>
+      <c r="C57" s="4" t="inlineStr">
+        <is>
+          <t>14:00</t>
+        </is>
+      </c>
+      <c r="D57" s="4" t="inlineStr">
+        <is>
+          <t>169.80</t>
+        </is>
+      </c>
+      <c r="E57" s="4" t="inlineStr"/>
+      <c r="F57" s="4" t="inlineStr">
+        <is>
+          <t>101.15</t>
+        </is>
+      </c>
+      <c r="G57" s="4" t="inlineStr"/>
+      <c r="H57" s="4" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="I57" s="4" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="J57" s="4" t="inlineStr"/>
+      <c r="K57" s="4" t="inlineStr"/>
+      <c r="L57" s="4" t="inlineStr"/>
+      <c r="M57" s="4" t="inlineStr"/>
+      <c r="N57" s="4" t="inlineStr"/>
+      <c r="O57" s="4" t="inlineStr"/>
+      <c r="P57" s="4" t="inlineStr">
+        <is>
+          <t>Low Strike Check</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="4" t="inlineStr">
+        <is>
+          <t>2026-02-12 14:05:00</t>
+        </is>
+      </c>
+      <c r="B58" s="4" t="inlineStr">
+        <is>
+          <t>14:05:00</t>
+        </is>
+      </c>
+      <c r="C58" s="4" t="inlineStr">
+        <is>
+          <t>14:05</t>
+        </is>
+      </c>
+      <c r="D58" s="4" t="inlineStr">
+        <is>
+          <t>156.60</t>
+        </is>
+      </c>
+      <c r="E58" s="4" t="inlineStr"/>
+      <c r="F58" s="4" t="inlineStr">
+        <is>
+          <t>124.55</t>
+        </is>
+      </c>
+      <c r="G58" s="4" t="inlineStr"/>
+      <c r="H58" s="4" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="I58" s="4" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="J58" s="4" t="inlineStr"/>
+      <c r="K58" s="4" t="inlineStr"/>
+      <c r="L58" s="4" t="inlineStr"/>
+      <c r="M58" s="4" t="inlineStr"/>
+      <c r="N58" s="4" t="inlineStr"/>
+      <c r="O58" s="4" t="inlineStr"/>
+      <c r="P58" s="4" t="inlineStr">
+        <is>
+          <t>High Strike Check</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="4" t="inlineStr">
+        <is>
+          <t>2026-02-12 14:05:00</t>
+        </is>
+      </c>
+      <c r="B59" s="4" t="inlineStr">
+        <is>
+          <t>14:05:00</t>
+        </is>
+      </c>
+      <c r="C59" s="4" t="inlineStr">
+        <is>
+          <t>14:05</t>
+        </is>
+      </c>
+      <c r="D59" s="4" t="inlineStr">
+        <is>
+          <t>169.80</t>
+        </is>
+      </c>
+      <c r="E59" s="4" t="inlineStr"/>
+      <c r="F59" s="4" t="inlineStr">
+        <is>
+          <t>101.15</t>
+        </is>
+      </c>
+      <c r="G59" s="4" t="inlineStr"/>
+      <c r="H59" s="4" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="I59" s="4" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="J59" s="4" t="inlineStr"/>
+      <c r="K59" s="4" t="inlineStr"/>
+      <c r="L59" s="4" t="inlineStr"/>
+      <c r="M59" s="4" t="inlineStr"/>
+      <c r="N59" s="4" t="inlineStr"/>
+      <c r="O59" s="4" t="inlineStr"/>
+      <c r="P59" s="4" t="inlineStr">
+        <is>
+          <t>Low Strike Check</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="4" t="inlineStr">
+        <is>
+          <t>2026-02-12 14:10:00</t>
+        </is>
+      </c>
+      <c r="B60" s="4" t="inlineStr">
+        <is>
+          <t>14:10:00</t>
+        </is>
+      </c>
+      <c r="C60" s="4" t="inlineStr">
+        <is>
+          <t>14:10</t>
+        </is>
+      </c>
+      <c r="D60" s="4" t="inlineStr">
+        <is>
+          <t>156.60</t>
+        </is>
+      </c>
+      <c r="E60" s="4" t="inlineStr"/>
+      <c r="F60" s="4" t="inlineStr">
+        <is>
+          <t>124.55</t>
+        </is>
+      </c>
+      <c r="G60" s="4" t="inlineStr"/>
+      <c r="H60" s="4" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="I60" s="4" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="J60" s="4" t="inlineStr"/>
+      <c r="K60" s="4" t="inlineStr"/>
+      <c r="L60" s="4" t="inlineStr"/>
+      <c r="M60" s="4" t="inlineStr"/>
+      <c r="N60" s="4" t="inlineStr"/>
+      <c r="O60" s="4" t="inlineStr"/>
+      <c r="P60" s="4" t="inlineStr">
+        <is>
+          <t>High Strike Check</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="4" t="inlineStr">
+        <is>
+          <t>2026-02-12 14:10:00</t>
+        </is>
+      </c>
+      <c r="B61" s="4" t="inlineStr">
+        <is>
+          <t>14:10:00</t>
+        </is>
+      </c>
+      <c r="C61" s="4" t="inlineStr">
+        <is>
+          <t>14:10</t>
+        </is>
+      </c>
+      <c r="D61" s="4" t="inlineStr">
+        <is>
+          <t>169.80</t>
+        </is>
+      </c>
+      <c r="E61" s="4" t="inlineStr"/>
+      <c r="F61" s="4" t="inlineStr">
+        <is>
+          <t>101.15</t>
+        </is>
+      </c>
+      <c r="G61" s="4" t="inlineStr"/>
+      <c r="H61" s="4" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="I61" s="4" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="J61" s="4" t="inlineStr"/>
+      <c r="K61" s="4" t="inlineStr"/>
+      <c r="L61" s="4" t="inlineStr"/>
+      <c r="M61" s="4" t="inlineStr"/>
+      <c r="N61" s="4" t="inlineStr"/>
+      <c r="O61" s="4" t="inlineStr"/>
+      <c r="P61" s="4" t="inlineStr">
+        <is>
+          <t>Low Strike Check</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="4" t="inlineStr">
+        <is>
+          <t>2026-02-12 14:15:00</t>
+        </is>
+      </c>
+      <c r="B62" s="4" t="inlineStr">
+        <is>
+          <t>14:15:00</t>
+        </is>
+      </c>
+      <c r="C62" s="4" t="inlineStr">
+        <is>
+          <t>14:15</t>
+        </is>
+      </c>
+      <c r="D62" s="4" t="inlineStr">
+        <is>
+          <t>156.60</t>
+        </is>
+      </c>
+      <c r="E62" s="4" t="inlineStr"/>
+      <c r="F62" s="4" t="inlineStr">
+        <is>
+          <t>124.55</t>
+        </is>
+      </c>
+      <c r="G62" s="4" t="inlineStr"/>
+      <c r="H62" s="4" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="I62" s="4" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="J62" s="4" t="inlineStr"/>
+      <c r="K62" s="4" t="inlineStr"/>
+      <c r="L62" s="4" t="inlineStr"/>
+      <c r="M62" s="4" t="inlineStr"/>
+      <c r="N62" s="4" t="inlineStr"/>
+      <c r="O62" s="4" t="inlineStr"/>
+      <c r="P62" s="4" t="inlineStr">
+        <is>
+          <t>High Strike Check</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="4" t="inlineStr">
+        <is>
+          <t>2026-02-12 14:15:00</t>
+        </is>
+      </c>
+      <c r="B63" s="4" t="inlineStr">
+        <is>
+          <t>14:15:00</t>
+        </is>
+      </c>
+      <c r="C63" s="4" t="inlineStr">
+        <is>
+          <t>14:15</t>
+        </is>
+      </c>
+      <c r="D63" s="4" t="inlineStr">
+        <is>
+          <t>169.80</t>
+        </is>
+      </c>
+      <c r="E63" s="4" t="inlineStr"/>
+      <c r="F63" s="4" t="inlineStr">
+        <is>
+          <t>101.15</t>
+        </is>
+      </c>
+      <c r="G63" s="4" t="inlineStr"/>
+      <c r="H63" s="4" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="I63" s="4" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="J63" s="4" t="inlineStr"/>
+      <c r="K63" s="4" t="inlineStr"/>
+      <c r="L63" s="4" t="inlineStr"/>
+      <c r="M63" s="4" t="inlineStr"/>
+      <c r="N63" s="4" t="inlineStr"/>
+      <c r="O63" s="4" t="inlineStr"/>
+      <c r="P63" s="4" t="inlineStr">
+        <is>
+          <t>Low Strike Check</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="4" t="inlineStr">
+        <is>
+          <t>2026-02-12 14:20:00</t>
+        </is>
+      </c>
+      <c r="B64" s="4" t="inlineStr">
+        <is>
+          <t>14:20:00</t>
+        </is>
+      </c>
+      <c r="C64" s="4" t="inlineStr">
+        <is>
+          <t>14:20</t>
+        </is>
+      </c>
+      <c r="D64" s="4" t="inlineStr">
+        <is>
+          <t>156.60</t>
+        </is>
+      </c>
+      <c r="E64" s="4" t="inlineStr"/>
+      <c r="F64" s="4" t="inlineStr">
+        <is>
+          <t>124.55</t>
+        </is>
+      </c>
+      <c r="G64" s="4" t="inlineStr"/>
+      <c r="H64" s="4" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="I64" s="4" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="J64" s="4" t="inlineStr"/>
+      <c r="K64" s="4" t="inlineStr"/>
+      <c r="L64" s="4" t="inlineStr"/>
+      <c r="M64" s="4" t="inlineStr"/>
+      <c r="N64" s="4" t="inlineStr"/>
+      <c r="O64" s="4" t="inlineStr"/>
+      <c r="P64" s="4" t="inlineStr">
+        <is>
+          <t>High Strike Check</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="4" t="inlineStr">
+        <is>
+          <t>2026-02-12 14:20:00</t>
+        </is>
+      </c>
+      <c r="B65" s="4" t="inlineStr">
+        <is>
+          <t>14:20:00</t>
+        </is>
+      </c>
+      <c r="C65" s="4" t="inlineStr">
+        <is>
+          <t>14:20</t>
+        </is>
+      </c>
+      <c r="D65" s="4" t="inlineStr">
+        <is>
+          <t>169.80</t>
+        </is>
+      </c>
+      <c r="E65" s="4" t="inlineStr"/>
+      <c r="F65" s="4" t="inlineStr">
+        <is>
+          <t>101.15</t>
+        </is>
+      </c>
+      <c r="G65" s="4" t="inlineStr"/>
+      <c r="H65" s="4" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="I65" s="4" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="J65" s="4" t="inlineStr"/>
+      <c r="K65" s="4" t="inlineStr"/>
+      <c r="L65" s="4" t="inlineStr"/>
+      <c r="M65" s="4" t="inlineStr"/>
+      <c r="N65" s="4" t="inlineStr"/>
+      <c r="O65" s="4" t="inlineStr"/>
+      <c r="P65" s="4" t="inlineStr">
+        <is>
+          <t>Low Strike Check</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="4" t="inlineStr">
+        <is>
+          <t>2026-02-12 14:25:00</t>
+        </is>
+      </c>
+      <c r="B66" s="4" t="inlineStr">
+        <is>
+          <t>14:25:00</t>
+        </is>
+      </c>
+      <c r="C66" s="4" t="inlineStr">
+        <is>
+          <t>14:25</t>
+        </is>
+      </c>
+      <c r="D66" s="4" t="inlineStr">
+        <is>
+          <t>156.60</t>
+        </is>
+      </c>
+      <c r="E66" s="4" t="inlineStr"/>
+      <c r="F66" s="4" t="inlineStr">
+        <is>
+          <t>124.55</t>
+        </is>
+      </c>
+      <c r="G66" s="4" t="inlineStr"/>
+      <c r="H66" s="4" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="I66" s="4" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="J66" s="4" t="inlineStr"/>
+      <c r="K66" s="4" t="inlineStr"/>
+      <c r="L66" s="4" t="inlineStr"/>
+      <c r="M66" s="4" t="inlineStr"/>
+      <c r="N66" s="4" t="inlineStr"/>
+      <c r="O66" s="4" t="inlineStr"/>
+      <c r="P66" s="4" t="inlineStr">
+        <is>
+          <t>High Strike Check</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="4" t="inlineStr">
+        <is>
+          <t>2026-02-12 14:25:00</t>
+        </is>
+      </c>
+      <c r="B67" s="4" t="inlineStr">
+        <is>
+          <t>14:25:00</t>
+        </is>
+      </c>
+      <c r="C67" s="4" t="inlineStr">
+        <is>
+          <t>14:25</t>
+        </is>
+      </c>
+      <c r="D67" s="4" t="inlineStr">
+        <is>
+          <t>169.80</t>
+        </is>
+      </c>
+      <c r="E67" s="4" t="inlineStr"/>
+      <c r="F67" s="4" t="inlineStr">
+        <is>
+          <t>101.15</t>
+        </is>
+      </c>
+      <c r="G67" s="4" t="inlineStr"/>
+      <c r="H67" s="4" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="I67" s="4" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="J67" s="4" t="inlineStr"/>
+      <c r="K67" s="4" t="inlineStr"/>
+      <c r="L67" s="4" t="inlineStr"/>
+      <c r="M67" s="4" t="inlineStr"/>
+      <c r="N67" s="4" t="inlineStr"/>
+      <c r="O67" s="4" t="inlineStr"/>
+      <c r="P67" s="4" t="inlineStr">
+        <is>
+          <t>Low Strike Check</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="4" t="inlineStr">
+        <is>
+          <t>2026-02-12 14:30:00</t>
+        </is>
+      </c>
+      <c r="B68" s="4" t="inlineStr">
+        <is>
+          <t>14:30:00</t>
+        </is>
+      </c>
+      <c r="C68" s="4" t="inlineStr">
+        <is>
+          <t>14:30</t>
+        </is>
+      </c>
+      <c r="D68" s="4" t="inlineStr">
+        <is>
+          <t>156.60</t>
+        </is>
+      </c>
+      <c r="E68" s="4" t="inlineStr"/>
+      <c r="F68" s="4" t="inlineStr">
+        <is>
+          <t>124.55</t>
+        </is>
+      </c>
+      <c r="G68" s="4" t="inlineStr"/>
+      <c r="H68" s="4" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="I68" s="4" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="J68" s="4" t="inlineStr"/>
+      <c r="K68" s="4" t="inlineStr"/>
+      <c r="L68" s="4" t="inlineStr"/>
+      <c r="M68" s="4" t="inlineStr"/>
+      <c r="N68" s="4" t="inlineStr"/>
+      <c r="O68" s="4" t="inlineStr"/>
+      <c r="P68" s="4" t="inlineStr">
+        <is>
+          <t>High Strike Check</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="4" t="inlineStr">
+        <is>
+          <t>2026-02-12 14:30:00</t>
+        </is>
+      </c>
+      <c r="B69" s="4" t="inlineStr">
+        <is>
+          <t>14:30:00</t>
+        </is>
+      </c>
+      <c r="C69" s="4" t="inlineStr">
+        <is>
+          <t>14:30</t>
+        </is>
+      </c>
+      <c r="D69" s="4" t="inlineStr">
+        <is>
+          <t>169.80</t>
+        </is>
+      </c>
+      <c r="E69" s="4" t="inlineStr"/>
+      <c r="F69" s="4" t="inlineStr">
+        <is>
+          <t>101.15</t>
+        </is>
+      </c>
+      <c r="G69" s="4" t="inlineStr"/>
+      <c r="H69" s="4" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="I69" s="4" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="J69" s="4" t="inlineStr"/>
+      <c r="K69" s="4" t="inlineStr"/>
+      <c r="L69" s="4" t="inlineStr"/>
+      <c r="M69" s="4" t="inlineStr"/>
+      <c r="N69" s="4" t="inlineStr"/>
+      <c r="O69" s="4" t="inlineStr"/>
+      <c r="P69" s="4" t="inlineStr">
+        <is>
+          <t>Low Strike Check</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="4" t="inlineStr">
+        <is>
+          <t>2026-02-12 14:35:00</t>
+        </is>
+      </c>
+      <c r="B70" s="4" t="inlineStr">
+        <is>
+          <t>14:35:00</t>
+        </is>
+      </c>
+      <c r="C70" s="4" t="inlineStr">
+        <is>
+          <t>14:35</t>
+        </is>
+      </c>
+      <c r="D70" s="4" t="inlineStr">
+        <is>
+          <t>156.60</t>
+        </is>
+      </c>
+      <c r="E70" s="4" t="inlineStr"/>
+      <c r="F70" s="4" t="inlineStr">
+        <is>
+          <t>124.55</t>
+        </is>
+      </c>
+      <c r="G70" s="4" t="inlineStr"/>
+      <c r="H70" s="4" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="I70" s="4" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="J70" s="4" t="inlineStr"/>
+      <c r="K70" s="4" t="inlineStr"/>
+      <c r="L70" s="4" t="inlineStr"/>
+      <c r="M70" s="4" t="inlineStr"/>
+      <c r="N70" s="4" t="inlineStr"/>
+      <c r="O70" s="4" t="inlineStr"/>
+      <c r="P70" s="4" t="inlineStr">
+        <is>
+          <t>High Strike Check</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="4" t="inlineStr">
+        <is>
+          <t>2026-02-12 14:35:00</t>
+        </is>
+      </c>
+      <c r="B71" s="4" t="inlineStr">
+        <is>
+          <t>14:35:00</t>
+        </is>
+      </c>
+      <c r="C71" s="4" t="inlineStr">
+        <is>
+          <t>14:35</t>
+        </is>
+      </c>
+      <c r="D71" s="4" t="inlineStr">
+        <is>
+          <t>169.80</t>
+        </is>
+      </c>
+      <c r="E71" s="4" t="inlineStr"/>
+      <c r="F71" s="4" t="inlineStr">
+        <is>
+          <t>101.15</t>
+        </is>
+      </c>
+      <c r="G71" s="4" t="inlineStr"/>
+      <c r="H71" s="4" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="I71" s="4" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="J71" s="4" t="inlineStr"/>
+      <c r="K71" s="4" t="inlineStr"/>
+      <c r="L71" s="4" t="inlineStr"/>
+      <c r="M71" s="4" t="inlineStr"/>
+      <c r="N71" s="4" t="inlineStr"/>
+      <c r="O71" s="4" t="inlineStr"/>
+      <c r="P71" s="4" t="inlineStr">
+        <is>
+          <t>Low Strike Check</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="4" t="inlineStr">
+        <is>
+          <t>2026-02-12 14:40:00</t>
+        </is>
+      </c>
+      <c r="B72" s="4" t="inlineStr">
+        <is>
+          <t>14:40:00</t>
+        </is>
+      </c>
+      <c r="C72" s="4" t="inlineStr">
+        <is>
+          <t>14:40</t>
+        </is>
+      </c>
+      <c r="D72" s="4" t="inlineStr">
+        <is>
+          <t>156.60</t>
+        </is>
+      </c>
+      <c r="E72" s="4" t="inlineStr"/>
+      <c r="F72" s="4" t="inlineStr">
+        <is>
+          <t>124.55</t>
+        </is>
+      </c>
+      <c r="G72" s="4" t="inlineStr"/>
+      <c r="H72" s="4" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="I72" s="4" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="J72" s="4" t="inlineStr"/>
+      <c r="K72" s="4" t="inlineStr"/>
+      <c r="L72" s="4" t="inlineStr"/>
+      <c r="M72" s="4" t="inlineStr"/>
+      <c r="N72" s="4" t="inlineStr"/>
+      <c r="O72" s="4" t="inlineStr"/>
+      <c r="P72" s="4" t="inlineStr">
+        <is>
+          <t>High Strike Check</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="4" t="inlineStr">
+        <is>
+          <t>2026-02-12 14:40:00</t>
+        </is>
+      </c>
+      <c r="B73" s="4" t="inlineStr">
+        <is>
+          <t>14:40:00</t>
+        </is>
+      </c>
+      <c r="C73" s="4" t="inlineStr">
+        <is>
+          <t>14:40</t>
+        </is>
+      </c>
+      <c r="D73" s="4" t="inlineStr">
+        <is>
+          <t>169.80</t>
+        </is>
+      </c>
+      <c r="E73" s="4" t="inlineStr"/>
+      <c r="F73" s="4" t="inlineStr">
+        <is>
+          <t>101.15</t>
+        </is>
+      </c>
+      <c r="G73" s="4" t="inlineStr"/>
+      <c r="H73" s="4" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="I73" s="4" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="J73" s="4" t="inlineStr"/>
+      <c r="K73" s="4" t="inlineStr"/>
+      <c r="L73" s="4" t="inlineStr"/>
+      <c r="M73" s="4" t="inlineStr"/>
+      <c r="N73" s="4" t="inlineStr"/>
+      <c r="O73" s="4" t="inlineStr"/>
+      <c r="P73" s="4" t="inlineStr">
+        <is>
+          <t>Low Strike Check</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="4" t="inlineStr">
+        <is>
+          <t>2026-02-12 14:45:00</t>
+        </is>
+      </c>
+      <c r="B74" s="4" t="inlineStr">
+        <is>
+          <t>14:45:00</t>
+        </is>
+      </c>
+      <c r="C74" s="4" t="inlineStr">
+        <is>
+          <t>14:45</t>
+        </is>
+      </c>
+      <c r="D74" s="4" t="inlineStr">
+        <is>
+          <t>156.60</t>
+        </is>
+      </c>
+      <c r="E74" s="4" t="inlineStr"/>
+      <c r="F74" s="4" t="inlineStr">
+        <is>
+          <t>124.55</t>
+        </is>
+      </c>
+      <c r="G74" s="4" t="inlineStr"/>
+      <c r="H74" s="4" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="I74" s="4" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="J74" s="4" t="inlineStr"/>
+      <c r="K74" s="4" t="inlineStr"/>
+      <c r="L74" s="4" t="inlineStr"/>
+      <c r="M74" s="4" t="inlineStr"/>
+      <c r="N74" s="4" t="inlineStr"/>
+      <c r="O74" s="4" t="inlineStr"/>
+      <c r="P74" s="4" t="inlineStr">
+        <is>
+          <t>High Strike Check</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="4" t="inlineStr">
+        <is>
+          <t>2026-02-12 14:45:00</t>
+        </is>
+      </c>
+      <c r="B75" s="4" t="inlineStr">
+        <is>
+          <t>14:45:00</t>
+        </is>
+      </c>
+      <c r="C75" s="4" t="inlineStr">
+        <is>
+          <t>14:45</t>
+        </is>
+      </c>
+      <c r="D75" s="4" t="inlineStr">
+        <is>
+          <t>169.80</t>
+        </is>
+      </c>
+      <c r="E75" s="4" t="inlineStr"/>
+      <c r="F75" s="4" t="inlineStr">
+        <is>
+          <t>101.15</t>
+        </is>
+      </c>
+      <c r="G75" s="4" t="inlineStr"/>
+      <c r="H75" s="4" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="I75" s="4" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="J75" s="4" t="inlineStr"/>
+      <c r="K75" s="4" t="inlineStr"/>
+      <c r="L75" s="4" t="inlineStr"/>
+      <c r="M75" s="4" t="inlineStr"/>
+      <c r="N75" s="4" t="inlineStr"/>
+      <c r="O75" s="4" t="inlineStr"/>
+      <c r="P75" s="4" t="inlineStr">
+        <is>
+          <t>Low Strike Check</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="4" t="inlineStr">
+        <is>
+          <t>2026-02-12 14:50:00</t>
+        </is>
+      </c>
+      <c r="B76" s="4" t="inlineStr">
+        <is>
+          <t>14:50:00</t>
+        </is>
+      </c>
+      <c r="C76" s="4" t="inlineStr">
+        <is>
+          <t>14:50</t>
+        </is>
+      </c>
+      <c r="D76" s="4" t="inlineStr">
+        <is>
+          <t>156.60</t>
+        </is>
+      </c>
+      <c r="E76" s="4" t="inlineStr"/>
+      <c r="F76" s="4" t="inlineStr">
+        <is>
+          <t>124.55</t>
+        </is>
+      </c>
+      <c r="G76" s="4" t="inlineStr"/>
+      <c r="H76" s="4" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="I76" s="6" t="inlineStr">
+        <is>
+          <t>✓ YES</t>
+        </is>
+      </c>
+      <c r="J76" s="4" t="inlineStr"/>
+      <c r="K76" s="4" t="inlineStr">
+        <is>
+          <t>173.55</t>
+        </is>
+      </c>
+      <c r="L76" s="4" t="inlineStr"/>
+      <c r="M76" s="4" t="inlineStr">
+        <is>
+          <t>146.60</t>
+        </is>
+      </c>
+      <c r="N76" s="4" t="inlineStr"/>
+      <c r="O76" s="4" t="inlineStr">
+        <is>
+          <t>227.45</t>
+        </is>
+      </c>
+      <c r="P76" s="4" t="inlineStr">
+        <is>
+          <t>High Strike Check</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="4" t="inlineStr">
+        <is>
+          <t>2026-02-12 14:50:00</t>
+        </is>
+      </c>
+      <c r="B77" s="4" t="inlineStr">
+        <is>
+          <t>14:50:00</t>
+        </is>
+      </c>
+      <c r="C77" s="4" t="inlineStr">
+        <is>
+          <t>14:50</t>
+        </is>
+      </c>
+      <c r="D77" s="4" t="inlineStr">
+        <is>
+          <t>169.80</t>
+        </is>
+      </c>
+      <c r="E77" s="4" t="inlineStr"/>
+      <c r="F77" s="4" t="inlineStr">
+        <is>
+          <t>101.15</t>
+        </is>
+      </c>
+      <c r="G77" s="4" t="inlineStr"/>
+      <c r="H77" s="4" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="I77" s="6" t="inlineStr">
+        <is>
+          <t>✓ YES</t>
+        </is>
+      </c>
+      <c r="J77" s="4" t="inlineStr"/>
+      <c r="K77" s="4" t="inlineStr">
+        <is>
+          <t>173.55</t>
+        </is>
+      </c>
+      <c r="L77" s="4" t="inlineStr"/>
+      <c r="M77" s="4" t="inlineStr">
+        <is>
+          <t>146.60</t>
+        </is>
+      </c>
+      <c r="N77" s="4" t="inlineStr"/>
+      <c r="O77" s="4" t="inlineStr">
+        <is>
+          <t>227.45</t>
+        </is>
+      </c>
+      <c r="P77" s="4" t="inlineStr">
+        <is>
+          <t>Low Strike Check</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="4" t="inlineStr">
+        <is>
+          <t>2026-02-12 14:55:00</t>
+        </is>
+      </c>
+      <c r="B78" s="4" t="inlineStr">
+        <is>
+          <t>14:55:00</t>
+        </is>
+      </c>
+      <c r="C78" s="4" t="inlineStr">
+        <is>
+          <t>14:55</t>
+        </is>
+      </c>
+      <c r="D78" s="4" t="inlineStr"/>
+      <c r="E78" s="4" t="inlineStr"/>
+      <c r="F78" s="4" t="inlineStr"/>
+      <c r="G78" s="4" t="inlineStr"/>
+      <c r="H78" s="4" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="I78" s="4" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="J78" s="4" t="inlineStr"/>
+      <c r="K78" s="4" t="inlineStr"/>
+      <c r="L78" s="4" t="inlineStr"/>
+      <c r="M78" s="4" t="inlineStr"/>
+      <c r="N78" s="4" t="inlineStr"/>
+      <c r="O78" s="4" t="inlineStr"/>
+      <c r="P78" s="4" t="inlineStr">
+        <is>
+          <t>Data fetch failed: Live data fetch timed out after 45s - candle fetching took too long, retrying next cycle</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="4" t="inlineStr">
+        <is>
+          <t>2026-02-12 14:55:00</t>
+        </is>
+      </c>
+      <c r="B79" s="4" t="inlineStr">
+        <is>
+          <t>14:55:00</t>
+        </is>
+      </c>
+      <c r="C79" s="4" t="inlineStr">
+        <is>
+          <t>14:55</t>
+        </is>
+      </c>
+      <c r="D79" s="4" t="inlineStr"/>
+      <c r="E79" s="4" t="inlineStr"/>
+      <c r="F79" s="4" t="inlineStr"/>
+      <c r="G79" s="4" t="inlineStr"/>
+      <c r="H79" s="4" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="I79" s="4" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="J79" s="4" t="inlineStr"/>
+      <c r="K79" s="4" t="inlineStr"/>
+      <c r="L79" s="4" t="inlineStr"/>
+      <c r="M79" s="4" t="inlineStr"/>
+      <c r="N79" s="4" t="inlineStr"/>
+      <c r="O79" s="4" t="inlineStr"/>
+      <c r="P79" s="4" t="inlineStr">
+        <is>
+          <t>Failed to fetch data: Live data fetch timed out after 45s - candle fetching took too long, retrying next cycle</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="4" t="inlineStr">
+        <is>
+          <t>2026-02-12 15:00:00</t>
+        </is>
+      </c>
+      <c r="B80" s="4" t="inlineStr">
+        <is>
+          <t>15:00:00</t>
+        </is>
+      </c>
+      <c r="C80" s="4" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="D80" s="4" t="inlineStr">
+        <is>
+          <t>156.60</t>
+        </is>
+      </c>
+      <c r="E80" s="4" t="inlineStr"/>
+      <c r="F80" s="4" t="inlineStr">
+        <is>
+          <t>124.55</t>
+        </is>
+      </c>
+      <c r="G80" s="4" t="inlineStr"/>
+      <c r="H80" s="4" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="I80" s="4" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="J80" s="4" t="inlineStr"/>
+      <c r="K80" s="4" t="inlineStr"/>
+      <c r="L80" s="4" t="inlineStr"/>
+      <c r="M80" s="4" t="inlineStr"/>
+      <c r="N80" s="4" t="inlineStr"/>
+      <c r="O80" s="4" t="inlineStr"/>
+      <c r="P80" s="4" t="inlineStr">
+        <is>
+          <t>High Strike Check</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="4" t="inlineStr">
+        <is>
+          <t>2026-02-12 15:00:00</t>
+        </is>
+      </c>
+      <c r="B81" s="4" t="inlineStr">
+        <is>
+          <t>15:00:00</t>
+        </is>
+      </c>
+      <c r="C81" s="4" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="D81" s="4" t="inlineStr">
+        <is>
+          <t>169.80</t>
+        </is>
+      </c>
+      <c r="E81" s="4" t="inlineStr"/>
+      <c r="F81" s="4" t="inlineStr">
+        <is>
+          <t>101.15</t>
+        </is>
+      </c>
+      <c r="G81" s="4" t="inlineStr"/>
+      <c r="H81" s="4" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="I81" s="4" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="J81" s="4" t="inlineStr"/>
+      <c r="K81" s="4" t="inlineStr"/>
+      <c r="L81" s="4" t="inlineStr"/>
+      <c r="M81" s="4" t="inlineStr"/>
+      <c r="N81" s="4" t="inlineStr"/>
+      <c r="O81" s="4" t="inlineStr"/>
+      <c r="P81" s="4" t="inlineStr">
+        <is>
+          <t>Low Strike Check</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="4" t="inlineStr">
+        <is>
+          <t>2026-02-12 15:05:00</t>
+        </is>
+      </c>
+      <c r="B82" s="4" t="inlineStr">
+        <is>
+          <t>15:05:00</t>
+        </is>
+      </c>
+      <c r="C82" s="4" t="inlineStr">
+        <is>
+          <t>15:05</t>
+        </is>
+      </c>
+      <c r="D82" s="4" t="inlineStr">
+        <is>
+          <t>156.60</t>
+        </is>
+      </c>
+      <c r="E82" s="4" t="inlineStr"/>
+      <c r="F82" s="4" t="inlineStr">
+        <is>
+          <t>124.55</t>
+        </is>
+      </c>
+      <c r="G82" s="4" t="inlineStr"/>
+      <c r="H82" s="4" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="I82" s="4" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="J82" s="4" t="inlineStr"/>
+      <c r="K82" s="4" t="inlineStr"/>
+      <c r="L82" s="4" t="inlineStr"/>
+      <c r="M82" s="4" t="inlineStr"/>
+      <c r="N82" s="4" t="inlineStr"/>
+      <c r="O82" s="4" t="inlineStr"/>
+      <c r="P82" s="4" t="inlineStr">
+        <is>
+          <t>High Strike Check</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="4" t="inlineStr">
+        <is>
+          <t>2026-02-12 15:05:00</t>
+        </is>
+      </c>
+      <c r="B83" s="4" t="inlineStr">
+        <is>
+          <t>15:05:00</t>
+        </is>
+      </c>
+      <c r="C83" s="4" t="inlineStr">
+        <is>
+          <t>15:05</t>
+        </is>
+      </c>
+      <c r="D83" s="4" t="inlineStr">
+        <is>
+          <t>169.80</t>
+        </is>
+      </c>
+      <c r="E83" s="4" t="inlineStr"/>
+      <c r="F83" s="4" t="inlineStr">
+        <is>
+          <t>101.15</t>
+        </is>
+      </c>
+      <c r="G83" s="4" t="inlineStr"/>
+      <c r="H83" s="4" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="I83" s="4" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="J83" s="4" t="inlineStr"/>
+      <c r="K83" s="4" t="inlineStr"/>
+      <c r="L83" s="4" t="inlineStr"/>
+      <c r="M83" s="4" t="inlineStr"/>
+      <c r="N83" s="4" t="inlineStr"/>
+      <c r="O83" s="4" t="inlineStr"/>
+      <c r="P83" s="4" t="inlineStr">
+        <is>
+          <t>Low Strike Check</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="4" t="inlineStr">
+        <is>
+          <t>2026-02-12 15:10:00</t>
+        </is>
+      </c>
+      <c r="B84" s="4" t="inlineStr">
+        <is>
+          <t>15:10:00</t>
+        </is>
+      </c>
+      <c r="C84" s="4" t="inlineStr">
+        <is>
+          <t>15:10</t>
+        </is>
+      </c>
+      <c r="D84" s="4" t="inlineStr">
+        <is>
+          <t>156.60</t>
+        </is>
+      </c>
+      <c r="E84" s="4" t="inlineStr"/>
+      <c r="F84" s="4" t="inlineStr">
+        <is>
+          <t>124.55</t>
+        </is>
+      </c>
+      <c r="G84" s="4" t="inlineStr"/>
+      <c r="H84" s="4" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="I84" s="4" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="J84" s="4" t="inlineStr"/>
+      <c r="K84" s="4" t="inlineStr"/>
+      <c r="L84" s="4" t="inlineStr"/>
+      <c r="M84" s="4" t="inlineStr"/>
+      <c r="N84" s="4" t="inlineStr"/>
+      <c r="O84" s="4" t="inlineStr"/>
+      <c r="P84" s="4" t="inlineStr">
+        <is>
+          <t>High Strike Check</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="4" t="inlineStr">
+        <is>
+          <t>2026-02-12 15:10:00</t>
+        </is>
+      </c>
+      <c r="B85" s="4" t="inlineStr">
+        <is>
+          <t>15:10:00</t>
+        </is>
+      </c>
+      <c r="C85" s="4" t="inlineStr">
+        <is>
+          <t>15:10</t>
+        </is>
+      </c>
+      <c r="D85" s="4" t="inlineStr">
+        <is>
+          <t>169.80</t>
+        </is>
+      </c>
+      <c r="E85" s="4" t="inlineStr"/>
+      <c r="F85" s="4" t="inlineStr">
+        <is>
+          <t>101.15</t>
+        </is>
+      </c>
+      <c r="G85" s="4" t="inlineStr"/>
+      <c r="H85" s="4" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="I85" s="4" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="J85" s="4" t="inlineStr"/>
+      <c r="K85" s="4" t="inlineStr"/>
+      <c r="L85" s="4" t="inlineStr"/>
+      <c r="M85" s="4" t="inlineStr"/>
+      <c r="N85" s="4" t="inlineStr"/>
+      <c r="O85" s="4" t="inlineStr"/>
+      <c r="P85" s="4" t="inlineStr">
+        <is>
+          <t>Low Strike Check</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="4" t="inlineStr">
+        <is>
+          <t>2026-02-12 15:15:00</t>
+        </is>
+      </c>
+      <c r="B86" s="4" t="inlineStr">
+        <is>
+          <t>15:15:00</t>
+        </is>
+      </c>
+      <c r="C86" s="4" t="inlineStr">
+        <is>
+          <t>15:15</t>
+        </is>
+      </c>
+      <c r="D86" s="4" t="inlineStr">
+        <is>
+          <t>156.60</t>
+        </is>
+      </c>
+      <c r="E86" s="4" t="inlineStr"/>
+      <c r="F86" s="4" t="inlineStr">
+        <is>
+          <t>124.55</t>
+        </is>
+      </c>
+      <c r="G86" s="4" t="inlineStr"/>
+      <c r="H86" s="4" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="I86" s="4" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="J86" s="4" t="inlineStr"/>
+      <c r="K86" s="4" t="inlineStr"/>
+      <c r="L86" s="4" t="inlineStr"/>
+      <c r="M86" s="4" t="inlineStr"/>
+      <c r="N86" s="4" t="inlineStr"/>
+      <c r="O86" s="4" t="inlineStr"/>
+      <c r="P86" s="4" t="inlineStr">
+        <is>
+          <t>High Strike Check</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="4" t="inlineStr">
+        <is>
+          <t>2026-02-12 15:15:00</t>
+        </is>
+      </c>
+      <c r="B87" s="4" t="inlineStr">
+        <is>
+          <t>15:15:00</t>
+        </is>
+      </c>
+      <c r="C87" s="4" t="inlineStr">
+        <is>
+          <t>15:15</t>
+        </is>
+      </c>
+      <c r="D87" s="4" t="inlineStr">
+        <is>
+          <t>169.80</t>
+        </is>
+      </c>
+      <c r="E87" s="4" t="inlineStr"/>
+      <c r="F87" s="4" t="inlineStr">
+        <is>
+          <t>101.15</t>
+        </is>
+      </c>
+      <c r="G87" s="4" t="inlineStr"/>
+      <c r="H87" s="4" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="I87" s="4" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="J87" s="4" t="inlineStr"/>
+      <c r="K87" s="4" t="inlineStr"/>
+      <c r="L87" s="4" t="inlineStr"/>
+      <c r="M87" s="4" t="inlineStr"/>
+      <c r="N87" s="4" t="inlineStr"/>
+      <c r="O87" s="4" t="inlineStr"/>
+      <c r="P87" s="4" t="inlineStr">
+        <is>
+          <t>Low Strike Check</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -2654,7 +4880,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L1"/>
+  <dimension ref="A1:L3"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -2729,6 +4955,106 @@
         </is>
       </c>
     </row>
+    <row r="2">
+      <c r="A2" s="4" t="inlineStr">
+        <is>
+          <t>2026-02-12 14:50:05</t>
+        </is>
+      </c>
+      <c r="B2" s="4" t="inlineStr">
+        <is>
+          <t>BUY PE</t>
+        </is>
+      </c>
+      <c r="C2" s="4" t="inlineStr">
+        <is>
+          <t>PE</t>
+        </is>
+      </c>
+      <c r="D2" s="4" t="n">
+        <v>25900</v>
+      </c>
+      <c r="E2" s="4" t="inlineStr">
+        <is>
+          <t>173.55</t>
+        </is>
+      </c>
+      <c r="F2" s="4" t="inlineStr">
+        <is>
+          <t>173.55</t>
+        </is>
+      </c>
+      <c r="G2" s="4" t="inlineStr"/>
+      <c r="H2" s="4" t="inlineStr"/>
+      <c r="I2" s="4" t="inlineStr"/>
+      <c r="J2" s="5" t="inlineStr">
+        <is>
+          <t>BUY PE</t>
+        </is>
+      </c>
+      <c r="K2" s="4" t="inlineStr">
+        <is>
+          <t>2021876953262776320</t>
+        </is>
+      </c>
+      <c r="L2" s="4" t="inlineStr">
+        <is>
+          <t>Mode: LIVE | Details: Order placed successfully via KiteService | Order_type: MARKET</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="4" t="inlineStr">
+        <is>
+          <t>2026-02-12 14:50:05</t>
+        </is>
+      </c>
+      <c r="B3" s="4" t="inlineStr">
+        <is>
+          <t>SL_ORDER</t>
+        </is>
+      </c>
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t>PE</t>
+        </is>
+      </c>
+      <c r="D3" s="4" t="n">
+        <v>25900</v>
+      </c>
+      <c r="E3" s="4" t="inlineStr">
+        <is>
+          <t>146.60</t>
+        </is>
+      </c>
+      <c r="F3" s="4" t="inlineStr"/>
+      <c r="G3" s="4" t="inlineStr">
+        <is>
+          <t>227.45</t>
+        </is>
+      </c>
+      <c r="H3" s="4" t="inlineStr">
+        <is>
+          <t>146.60</t>
+        </is>
+      </c>
+      <c r="I3" s="4" t="inlineStr"/>
+      <c r="J3" s="5" t="inlineStr">
+        <is>
+          <t>PLACED</t>
+        </is>
+      </c>
+      <c r="K3" s="4" t="inlineStr">
+        <is>
+          <t>2021876953866756096</t>
+        </is>
+      </c>
+      <c r="L3" s="4" t="inlineStr">
+        <is>
+          <t>SL Order Placed | Trigger: 146.60</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Mine/logs/mine_signal_logs.xlsx
+++ b/Mine/logs/mine_signal_logs.xlsx
@@ -579,7 +579,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P84"/>
+  <dimension ref="A1:P90"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -4763,6 +4763,306 @@
       <c r="N84" s="10" t="inlineStr"/>
       <c r="O84" s="10" t="inlineStr"/>
       <c r="P84" s="10" t="inlineStr">
+        <is>
+          <t>Low Strike Check</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="10" t="inlineStr">
+        <is>
+          <t>2026-02-17 12:50:00</t>
+        </is>
+      </c>
+      <c r="B85" s="10" t="inlineStr">
+        <is>
+          <t>12:50:00</t>
+        </is>
+      </c>
+      <c r="C85" s="10" t="inlineStr">
+        <is>
+          <t>12:50</t>
+        </is>
+      </c>
+      <c r="D85" s="10" t="inlineStr">
+        <is>
+          <t>85.00</t>
+        </is>
+      </c>
+      <c r="E85" s="10" t="inlineStr"/>
+      <c r="F85" s="10" t="inlineStr">
+        <is>
+          <t>128.55</t>
+        </is>
+      </c>
+      <c r="G85" s="10" t="inlineStr"/>
+      <c r="H85" s="10" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="I85" s="10" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="J85" s="10" t="inlineStr"/>
+      <c r="K85" s="10" t="inlineStr"/>
+      <c r="L85" s="10" t="inlineStr"/>
+      <c r="M85" s="10" t="inlineStr"/>
+      <c r="N85" s="10" t="inlineStr"/>
+      <c r="O85" s="10" t="inlineStr"/>
+      <c r="P85" s="10" t="inlineStr">
+        <is>
+          <t>High Strike Check</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="10" t="inlineStr">
+        <is>
+          <t>2026-02-17 12:50:00</t>
+        </is>
+      </c>
+      <c r="B86" s="10" t="inlineStr">
+        <is>
+          <t>12:50:00</t>
+        </is>
+      </c>
+      <c r="C86" s="10" t="inlineStr">
+        <is>
+          <t>12:50</t>
+        </is>
+      </c>
+      <c r="D86" s="10" t="inlineStr">
+        <is>
+          <t>118.00</t>
+        </is>
+      </c>
+      <c r="E86" s="10" t="inlineStr"/>
+      <c r="F86" s="10" t="inlineStr">
+        <is>
+          <t>65.00</t>
+        </is>
+      </c>
+      <c r="G86" s="10" t="inlineStr"/>
+      <c r="H86" s="10" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="I86" s="10" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="J86" s="10" t="inlineStr"/>
+      <c r="K86" s="10" t="inlineStr"/>
+      <c r="L86" s="10" t="inlineStr"/>
+      <c r="M86" s="10" t="inlineStr"/>
+      <c r="N86" s="10" t="inlineStr"/>
+      <c r="O86" s="10" t="inlineStr"/>
+      <c r="P86" s="10" t="inlineStr">
+        <is>
+          <t>Low Strike Check</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="10" t="inlineStr">
+        <is>
+          <t>2026-02-17 14:00:00</t>
+        </is>
+      </c>
+      <c r="B87" s="10" t="inlineStr">
+        <is>
+          <t>14:00:00</t>
+        </is>
+      </c>
+      <c r="C87" s="10" t="inlineStr">
+        <is>
+          <t>14:00</t>
+        </is>
+      </c>
+      <c r="D87" s="10" t="inlineStr">
+        <is>
+          <t>85.00</t>
+        </is>
+      </c>
+      <c r="E87" s="10" t="inlineStr"/>
+      <c r="F87" s="10" t="inlineStr">
+        <is>
+          <t>128.55</t>
+        </is>
+      </c>
+      <c r="G87" s="10" t="inlineStr"/>
+      <c r="H87" s="10" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="I87" s="10" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="J87" s="10" t="inlineStr"/>
+      <c r="K87" s="10" t="inlineStr"/>
+      <c r="L87" s="10" t="inlineStr"/>
+      <c r="M87" s="10" t="inlineStr"/>
+      <c r="N87" s="10" t="inlineStr"/>
+      <c r="O87" s="10" t="inlineStr"/>
+      <c r="P87" s="10" t="inlineStr">
+        <is>
+          <t>High Strike Check</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="10" t="inlineStr">
+        <is>
+          <t>2026-02-17 14:00:00</t>
+        </is>
+      </c>
+      <c r="B88" s="10" t="inlineStr">
+        <is>
+          <t>14:00:00</t>
+        </is>
+      </c>
+      <c r="C88" s="10" t="inlineStr">
+        <is>
+          <t>14:00</t>
+        </is>
+      </c>
+      <c r="D88" s="10" t="inlineStr">
+        <is>
+          <t>118.00</t>
+        </is>
+      </c>
+      <c r="E88" s="10" t="inlineStr"/>
+      <c r="F88" s="10" t="inlineStr">
+        <is>
+          <t>65.00</t>
+        </is>
+      </c>
+      <c r="G88" s="10" t="inlineStr"/>
+      <c r="H88" s="10" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="I88" s="10" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="J88" s="10" t="inlineStr"/>
+      <c r="K88" s="10" t="inlineStr"/>
+      <c r="L88" s="10" t="inlineStr"/>
+      <c r="M88" s="10" t="inlineStr"/>
+      <c r="N88" s="10" t="inlineStr"/>
+      <c r="O88" s="10" t="inlineStr"/>
+      <c r="P88" s="10" t="inlineStr">
+        <is>
+          <t>Low Strike Check</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="10" t="inlineStr">
+        <is>
+          <t>2026-02-17 14:05:00</t>
+        </is>
+      </c>
+      <c r="B89" s="10" t="inlineStr">
+        <is>
+          <t>14:05:00</t>
+        </is>
+      </c>
+      <c r="C89" s="10" t="inlineStr">
+        <is>
+          <t>14:05</t>
+        </is>
+      </c>
+      <c r="D89" s="10" t="inlineStr">
+        <is>
+          <t>85.00</t>
+        </is>
+      </c>
+      <c r="E89" s="10" t="inlineStr"/>
+      <c r="F89" s="10" t="inlineStr">
+        <is>
+          <t>128.55</t>
+        </is>
+      </c>
+      <c r="G89" s="10" t="inlineStr"/>
+      <c r="H89" s="10" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="I89" s="10" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="J89" s="10" t="inlineStr"/>
+      <c r="K89" s="10" t="inlineStr"/>
+      <c r="L89" s="10" t="inlineStr"/>
+      <c r="M89" s="10" t="inlineStr"/>
+      <c r="N89" s="10" t="inlineStr"/>
+      <c r="O89" s="10" t="inlineStr"/>
+      <c r="P89" s="10" t="inlineStr">
+        <is>
+          <t>High Strike Check</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="10" t="inlineStr">
+        <is>
+          <t>2026-02-17 14:05:00</t>
+        </is>
+      </c>
+      <c r="B90" s="10" t="inlineStr">
+        <is>
+          <t>14:05:00</t>
+        </is>
+      </c>
+      <c r="C90" s="10" t="inlineStr">
+        <is>
+          <t>14:05</t>
+        </is>
+      </c>
+      <c r="D90" s="10" t="inlineStr">
+        <is>
+          <t>118.00</t>
+        </is>
+      </c>
+      <c r="E90" s="10" t="inlineStr"/>
+      <c r="F90" s="10" t="inlineStr">
+        <is>
+          <t>65.00</t>
+        </is>
+      </c>
+      <c r="G90" s="10" t="inlineStr"/>
+      <c r="H90" s="10" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="I90" s="10" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="J90" s="10" t="inlineStr"/>
+      <c r="K90" s="10" t="inlineStr"/>
+      <c r="L90" s="10" t="inlineStr"/>
+      <c r="M90" s="10" t="inlineStr"/>
+      <c r="N90" s="10" t="inlineStr"/>
+      <c r="O90" s="10" t="inlineStr"/>
+      <c r="P90" s="10" t="inlineStr">
         <is>
           <t>Low Strike Check</t>
         </is>

--- a/Mine/logs/mine_signal_logs.xlsx
+++ b/Mine/logs/mine_signal_logs.xlsx
@@ -17,7 +17,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="3">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -32,8 +32,12 @@
       <color rgb="FFFFFFFF"/>
       <sz val="11"/>
     </font>
+    <font>
+      <color rgb="00000000"/>
+      <sz val="10"/>
+    </font>
   </fonts>
-  <fills count="12">
+  <fills count="13">
     <fill>
       <patternFill/>
     </fill>
@@ -98,6 +102,12 @@
       <patternFill patternType="solid">
         <fgColor rgb="00C6EFCE"/>
         <bgColor rgb="00C6EFCE"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00E7E6E6"/>
+        <bgColor rgb="00E7E6E6"/>
       </patternFill>
     </fill>
   </fills>
@@ -224,7 +234,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -275,6 +285,10 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="11" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="12" borderId="8" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="12" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -642,7 +656,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P128"/>
+  <dimension ref="A1:P137"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -6951,6 +6965,388 @@
         </is>
       </c>
     </row>
+    <row r="129">
+      <c r="A129" s="15" t="inlineStr">
+        <is>
+          <t>2026-02-21 11:30:00</t>
+        </is>
+      </c>
+      <c r="B129" s="15" t="inlineStr">
+        <is>
+          <t>11:30:00</t>
+        </is>
+      </c>
+      <c r="C129" s="15" t="inlineStr">
+        <is>
+          <t>11:30</t>
+        </is>
+      </c>
+      <c r="D129" s="15" t="inlineStr"/>
+      <c r="E129" s="15" t="inlineStr"/>
+      <c r="F129" s="15" t="inlineStr"/>
+      <c r="G129" s="15" t="inlineStr"/>
+      <c r="H129" s="15" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="I129" s="15" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="J129" s="15" t="inlineStr"/>
+      <c r="K129" s="15" t="inlineStr"/>
+      <c r="L129" s="15" t="inlineStr"/>
+      <c r="M129" s="15" t="inlineStr"/>
+      <c r="N129" s="15" t="inlineStr"/>
+      <c r="O129" s="15" t="inlineStr"/>
+      <c r="P129" s="15" t="inlineStr">
+        <is>
+          <t>Data fetch failed: Failed to fetch quote data after all retries</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" s="15" t="inlineStr">
+        <is>
+          <t>2026-02-21 11:30:00</t>
+        </is>
+      </c>
+      <c r="B130" s="15" t="inlineStr">
+        <is>
+          <t>11:30:00</t>
+        </is>
+      </c>
+      <c r="C130" s="15" t="inlineStr">
+        <is>
+          <t>11:30</t>
+        </is>
+      </c>
+      <c r="D130" s="15" t="inlineStr"/>
+      <c r="E130" s="15" t="inlineStr"/>
+      <c r="F130" s="15" t="inlineStr"/>
+      <c r="G130" s="15" t="inlineStr"/>
+      <c r="H130" s="15" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="I130" s="15" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="J130" s="15" t="inlineStr"/>
+      <c r="K130" s="15" t="inlineStr"/>
+      <c r="L130" s="15" t="inlineStr"/>
+      <c r="M130" s="15" t="inlineStr"/>
+      <c r="N130" s="15" t="inlineStr"/>
+      <c r="O130" s="15" t="inlineStr"/>
+      <c r="P130" s="15" t="inlineStr">
+        <is>
+          <t>Failed to fetch data: Failed to fetch quote data after all retries</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" s="15" t="inlineStr">
+        <is>
+          <t>2026-02-21 11:45:00</t>
+        </is>
+      </c>
+      <c r="B131" s="15" t="inlineStr">
+        <is>
+          <t>11:45:00</t>
+        </is>
+      </c>
+      <c r="C131" s="15" t="inlineStr">
+        <is>
+          <t>11:45</t>
+        </is>
+      </c>
+      <c r="D131" s="15" t="inlineStr"/>
+      <c r="E131" s="15" t="inlineStr"/>
+      <c r="F131" s="15" t="inlineStr"/>
+      <c r="G131" s="15" t="inlineStr"/>
+      <c r="H131" s="15" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="I131" s="15" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="J131" s="15" t="inlineStr"/>
+      <c r="K131" s="15" t="inlineStr"/>
+      <c r="L131" s="15" t="inlineStr"/>
+      <c r="M131" s="15" t="inlineStr"/>
+      <c r="N131" s="15" t="inlineStr"/>
+      <c r="O131" s="15" t="inlineStr"/>
+      <c r="P131" s="15" t="inlineStr">
+        <is>
+          <t>Data fetch failed: Failed to fetch quote data after all retries</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" s="15" t="inlineStr">
+        <is>
+          <t>2026-02-21 11:45:00</t>
+        </is>
+      </c>
+      <c r="B132" s="15" t="inlineStr">
+        <is>
+          <t>11:45:00</t>
+        </is>
+      </c>
+      <c r="C132" s="15" t="inlineStr">
+        <is>
+          <t>11:45</t>
+        </is>
+      </c>
+      <c r="D132" s="15" t="inlineStr"/>
+      <c r="E132" s="15" t="inlineStr"/>
+      <c r="F132" s="15" t="inlineStr"/>
+      <c r="G132" s="15" t="inlineStr"/>
+      <c r="H132" s="15" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="I132" s="15" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="J132" s="15" t="inlineStr"/>
+      <c r="K132" s="15" t="inlineStr"/>
+      <c r="L132" s="15" t="inlineStr"/>
+      <c r="M132" s="15" t="inlineStr"/>
+      <c r="N132" s="15" t="inlineStr"/>
+      <c r="O132" s="15" t="inlineStr"/>
+      <c r="P132" s="15" t="inlineStr">
+        <is>
+          <t>Failed to fetch data: Failed to fetch quote data after all retries</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" s="15" t="inlineStr">
+        <is>
+          <t>2026-02-21 13:00:00</t>
+        </is>
+      </c>
+      <c r="B133" s="15" t="inlineStr">
+        <is>
+          <t>13:00:00</t>
+        </is>
+      </c>
+      <c r="C133" s="15" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="D133" s="15" t="inlineStr"/>
+      <c r="E133" s="15" t="inlineStr"/>
+      <c r="F133" s="15" t="inlineStr"/>
+      <c r="G133" s="15" t="inlineStr"/>
+      <c r="H133" s="15" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="I133" s="15" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="J133" s="15" t="inlineStr"/>
+      <c r="K133" s="15" t="inlineStr"/>
+      <c r="L133" s="15" t="inlineStr"/>
+      <c r="M133" s="15" t="inlineStr"/>
+      <c r="N133" s="15" t="inlineStr"/>
+      <c r="O133" s="15" t="inlineStr"/>
+      <c r="P133" s="15" t="inlineStr">
+        <is>
+          <t>Data fetch failed: Failed to fetch quote data after all retries</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" s="15" t="inlineStr">
+        <is>
+          <t>2026-02-21 13:00:00</t>
+        </is>
+      </c>
+      <c r="B134" s="15" t="inlineStr">
+        <is>
+          <t>13:00:00</t>
+        </is>
+      </c>
+      <c r="C134" s="15" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="D134" s="15" t="inlineStr"/>
+      <c r="E134" s="15" t="inlineStr"/>
+      <c r="F134" s="15" t="inlineStr"/>
+      <c r="G134" s="15" t="inlineStr"/>
+      <c r="H134" s="15" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="I134" s="15" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="J134" s="15" t="inlineStr"/>
+      <c r="K134" s="15" t="inlineStr"/>
+      <c r="L134" s="15" t="inlineStr"/>
+      <c r="M134" s="15" t="inlineStr"/>
+      <c r="N134" s="15" t="inlineStr"/>
+      <c r="O134" s="15" t="inlineStr"/>
+      <c r="P134" s="15" t="inlineStr">
+        <is>
+          <t>Failed to fetch data: Failed to fetch quote data after all retries</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" s="18" t="inlineStr">
+        <is>
+          <t>2026-02-21 15:33:58</t>
+        </is>
+      </c>
+      <c r="B135" s="18" t="inlineStr">
+        <is>
+          <t>15:33:58</t>
+        </is>
+      </c>
+      <c r="C135" s="18" t="inlineStr">
+        <is>
+          <t>15:33</t>
+        </is>
+      </c>
+      <c r="D135" s="19" t="n">
+        <v>25450</v>
+      </c>
+      <c r="E135" s="19" t="inlineStr"/>
+      <c r="F135" s="19" t="inlineStr"/>
+      <c r="G135" s="19" t="inlineStr"/>
+      <c r="H135" s="18" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="I135" s="19" t="inlineStr"/>
+      <c r="J135" s="19" t="n">
+        <v>207.1</v>
+      </c>
+      <c r="K135" s="19" t="inlineStr"/>
+      <c r="L135" s="19" t="n">
+        <v>180.8</v>
+      </c>
+      <c r="M135" s="19" t="inlineStr"/>
+      <c r="N135" s="19" t="n">
+        <v>259.7</v>
+      </c>
+      <c r="O135" s="19" t="inlineStr"/>
+      <c r="P135" s="18" t="inlineStr">
+        <is>
+          <t>CE MARKET_CLOSE | Strike: 25450 | Price: 207.10 | Entry: 207.10 | SL: 180.80 | Target: 259.70 | PnL: +0.00 (+0.00%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" s="15" t="inlineStr">
+        <is>
+          <t>2026-02-21 14:50:00</t>
+        </is>
+      </c>
+      <c r="B136" s="15" t="inlineStr">
+        <is>
+          <t>14:50:00</t>
+        </is>
+      </c>
+      <c r="C136" s="15" t="inlineStr">
+        <is>
+          <t>14:50</t>
+        </is>
+      </c>
+      <c r="D136" s="15" t="inlineStr"/>
+      <c r="E136" s="15" t="inlineStr"/>
+      <c r="F136" s="15" t="inlineStr"/>
+      <c r="G136" s="15" t="inlineStr"/>
+      <c r="H136" s="15" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="I136" s="15" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="J136" s="15" t="inlineStr"/>
+      <c r="K136" s="15" t="inlineStr"/>
+      <c r="L136" s="15" t="inlineStr"/>
+      <c r="M136" s="15" t="inlineStr"/>
+      <c r="N136" s="15" t="inlineStr"/>
+      <c r="O136" s="15" t="inlineStr"/>
+      <c r="P136" s="15" t="inlineStr">
+        <is>
+          <t>Data fetch failed: Failed to fetch quote data after all retries</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" s="15" t="inlineStr">
+        <is>
+          <t>2026-02-21 14:50:00</t>
+        </is>
+      </c>
+      <c r="B137" s="15" t="inlineStr">
+        <is>
+          <t>14:50:00</t>
+        </is>
+      </c>
+      <c r="C137" s="15" t="inlineStr">
+        <is>
+          <t>14:50</t>
+        </is>
+      </c>
+      <c r="D137" s="15" t="inlineStr"/>
+      <c r="E137" s="15" t="inlineStr"/>
+      <c r="F137" s="15" t="inlineStr"/>
+      <c r="G137" s="15" t="inlineStr"/>
+      <c r="H137" s="15" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="I137" s="15" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="J137" s="15" t="inlineStr"/>
+      <c r="K137" s="15" t="inlineStr"/>
+      <c r="L137" s="15" t="inlineStr"/>
+      <c r="M137" s="15" t="inlineStr"/>
+      <c r="N137" s="15" t="inlineStr"/>
+      <c r="O137" s="15" t="inlineStr"/>
+      <c r="P137" s="15" t="inlineStr">
+        <is>
+          <t>Failed to fetch data: Failed to fetch quote data after all retries</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -6962,7 +7358,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L21"/>
+  <dimension ref="A1:L23"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -8037,6 +8433,106 @@
         </is>
       </c>
     </row>
+    <row r="22">
+      <c r="A22" s="15" t="inlineStr">
+        <is>
+          <t>2026-02-21 15:34:01</t>
+        </is>
+      </c>
+      <c r="B22" s="15" t="inlineStr">
+        <is>
+          <t>SELL CE</t>
+        </is>
+      </c>
+      <c r="C22" s="15" t="inlineStr">
+        <is>
+          <t>CE</t>
+        </is>
+      </c>
+      <c r="D22" s="15" t="n">
+        <v>25450</v>
+      </c>
+      <c r="E22" s="15" t="inlineStr">
+        <is>
+          <t>207.10</t>
+        </is>
+      </c>
+      <c r="F22" s="15" t="inlineStr">
+        <is>
+          <t>207.10</t>
+        </is>
+      </c>
+      <c r="G22" s="15" t="inlineStr"/>
+      <c r="H22" s="15" t="inlineStr"/>
+      <c r="I22" s="15" t="inlineStr"/>
+      <c r="J22" s="16" t="inlineStr">
+        <is>
+          <t>FAILED</t>
+        </is>
+      </c>
+      <c r="K22" s="15" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="L22" s="15" t="inlineStr">
+        <is>
+          <t>Mode: LIVE | Error: Incorrect `api_key` or `access_token`. | Details: Exit Reason: Market Close (3:20 PM) | Order_type: MARKET</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="15" t="inlineStr">
+        <is>
+          <t>2026-02-21 15:34:01</t>
+        </is>
+      </c>
+      <c r="B23" s="15" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="C23" s="15" t="inlineStr">
+        <is>
+          <t>CE</t>
+        </is>
+      </c>
+      <c r="D23" s="15" t="n">
+        <v>25450</v>
+      </c>
+      <c r="E23" s="15" t="inlineStr">
+        <is>
+          <t>207.10</t>
+        </is>
+      </c>
+      <c r="F23" s="15" t="inlineStr">
+        <is>
+          <t>207.10</t>
+        </is>
+      </c>
+      <c r="G23" s="15" t="inlineStr">
+        <is>
+          <t>259.70</t>
+        </is>
+      </c>
+      <c r="H23" s="15" t="inlineStr">
+        <is>
+          <t>180.80</t>
+        </is>
+      </c>
+      <c r="I23" s="15" t="inlineStr"/>
+      <c r="J23" s="16" t="inlineStr">
+        <is>
+          <t>MARKET_CLOSE</t>
+        </is>
+      </c>
+      <c r="K23" s="15" t="inlineStr"/>
+      <c r="L23" s="15" t="inlineStr">
+        <is>
+          <t>Market Close Square-Off (3:20 PM) | Entry Time: 2026-02-20T13:15:08.706661 | Entry Order ID: 2024752161975885824 | Entry Price: 207.10 | Stop Loss: 180.8 | Exit Price: 207.10 | P&amp;L: +0.00</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Mine/logs/mine_signal_logs.xlsx
+++ b/Mine/logs/mine_signal_logs.xlsx
@@ -469,7 +469,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P6"/>
+  <dimension ref="A1:P14"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -814,6 +814,390 @@
         </is>
       </c>
     </row>
+    <row r="7">
+      <c r="A7" s="3" t="inlineStr">
+        <is>
+          <t>2026-02-25 09:20:00</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>09:20:00</t>
+        </is>
+      </c>
+      <c r="C7" s="3" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="D7" s="3" t="inlineStr">
+        <is>
+          <t>185.45</t>
+        </is>
+      </c>
+      <c r="E7" s="3" t="inlineStr"/>
+      <c r="F7" s="3" t="inlineStr">
+        <is>
+          <t>200.00</t>
+        </is>
+      </c>
+      <c r="G7" s="3" t="inlineStr"/>
+      <c r="H7" s="3" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="I7" s="3" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="J7" s="3" t="inlineStr"/>
+      <c r="K7" s="3" t="inlineStr"/>
+      <c r="L7" s="3" t="inlineStr"/>
+      <c r="M7" s="3" t="inlineStr"/>
+      <c r="N7" s="3" t="inlineStr"/>
+      <c r="O7" s="3" t="inlineStr"/>
+      <c r="P7" s="3" t="inlineStr">
+        <is>
+          <t>High Strike Check</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="3" t="inlineStr">
+        <is>
+          <t>2026-02-25 09:20:00</t>
+        </is>
+      </c>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>09:20:00</t>
+        </is>
+      </c>
+      <c r="C8" s="3" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="D8" s="3" t="inlineStr">
+        <is>
+          <t>215.50</t>
+        </is>
+      </c>
+      <c r="E8" s="3" t="inlineStr"/>
+      <c r="F8" s="3" t="inlineStr">
+        <is>
+          <t>159.00</t>
+        </is>
+      </c>
+      <c r="G8" s="3" t="inlineStr"/>
+      <c r="H8" s="3" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="I8" s="3" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="J8" s="3" t="inlineStr"/>
+      <c r="K8" s="3" t="inlineStr"/>
+      <c r="L8" s="3" t="inlineStr"/>
+      <c r="M8" s="3" t="inlineStr"/>
+      <c r="N8" s="3" t="inlineStr"/>
+      <c r="O8" s="3" t="inlineStr"/>
+      <c r="P8" s="3" t="inlineStr">
+        <is>
+          <t>Low Strike Check</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="3" t="inlineStr">
+        <is>
+          <t>2026-02-25 09:25:00</t>
+        </is>
+      </c>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>09:25:00</t>
+        </is>
+      </c>
+      <c r="C9" s="3" t="inlineStr">
+        <is>
+          <t>09:25</t>
+        </is>
+      </c>
+      <c r="D9" s="3" t="inlineStr">
+        <is>
+          <t>185.45</t>
+        </is>
+      </c>
+      <c r="E9" s="3" t="inlineStr"/>
+      <c r="F9" s="3" t="inlineStr">
+        <is>
+          <t>200.00</t>
+        </is>
+      </c>
+      <c r="G9" s="3" t="inlineStr"/>
+      <c r="H9" s="3" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="I9" s="3" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="J9" s="3" t="inlineStr"/>
+      <c r="K9" s="3" t="inlineStr"/>
+      <c r="L9" s="3" t="inlineStr"/>
+      <c r="M9" s="3" t="inlineStr"/>
+      <c r="N9" s="3" t="inlineStr"/>
+      <c r="O9" s="3" t="inlineStr"/>
+      <c r="P9" s="3" t="inlineStr">
+        <is>
+          <t>High Strike Check</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="3" t="inlineStr">
+        <is>
+          <t>2026-02-25 09:25:00</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>09:25:00</t>
+        </is>
+      </c>
+      <c r="C10" s="3" t="inlineStr">
+        <is>
+          <t>09:25</t>
+        </is>
+      </c>
+      <c r="D10" s="3" t="inlineStr">
+        <is>
+          <t>215.50</t>
+        </is>
+      </c>
+      <c r="E10" s="3" t="inlineStr"/>
+      <c r="F10" s="3" t="inlineStr">
+        <is>
+          <t>159.00</t>
+        </is>
+      </c>
+      <c r="G10" s="3" t="inlineStr"/>
+      <c r="H10" s="3" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="I10" s="3" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="J10" s="3" t="inlineStr"/>
+      <c r="K10" s="3" t="inlineStr"/>
+      <c r="L10" s="3" t="inlineStr"/>
+      <c r="M10" s="3" t="inlineStr"/>
+      <c r="N10" s="3" t="inlineStr"/>
+      <c r="O10" s="3" t="inlineStr"/>
+      <c r="P10" s="3" t="inlineStr">
+        <is>
+          <t>Low Strike Check</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="3" t="inlineStr">
+        <is>
+          <t>2026-02-25 09:30:00</t>
+        </is>
+      </c>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>09:30:00</t>
+        </is>
+      </c>
+      <c r="C11" s="3" t="inlineStr">
+        <is>
+          <t>09:30</t>
+        </is>
+      </c>
+      <c r="D11" s="3" t="inlineStr"/>
+      <c r="E11" s="3" t="inlineStr"/>
+      <c r="F11" s="3" t="inlineStr"/>
+      <c r="G11" s="3" t="inlineStr"/>
+      <c r="H11" s="3" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="I11" s="3" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="J11" s="3" t="inlineStr"/>
+      <c r="K11" s="3" t="inlineStr"/>
+      <c r="L11" s="3" t="inlineStr"/>
+      <c r="M11" s="3" t="inlineStr"/>
+      <c r="N11" s="3" t="inlineStr"/>
+      <c r="O11" s="3" t="inlineStr"/>
+      <c r="P11" s="3" t="inlineStr">
+        <is>
+          <t>Data fetch failed: Live data fetch timed out after 45s - candle fetching took too long, retrying next cycle</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="3" t="inlineStr">
+        <is>
+          <t>2026-02-25 09:30:00</t>
+        </is>
+      </c>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>09:30:00</t>
+        </is>
+      </c>
+      <c r="C12" s="3" t="inlineStr">
+        <is>
+          <t>09:30</t>
+        </is>
+      </c>
+      <c r="D12" s="3" t="inlineStr"/>
+      <c r="E12" s="3" t="inlineStr"/>
+      <c r="F12" s="3" t="inlineStr"/>
+      <c r="G12" s="3" t="inlineStr"/>
+      <c r="H12" s="3" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="I12" s="3" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="J12" s="3" t="inlineStr"/>
+      <c r="K12" s="3" t="inlineStr"/>
+      <c r="L12" s="3" t="inlineStr"/>
+      <c r="M12" s="3" t="inlineStr"/>
+      <c r="N12" s="3" t="inlineStr"/>
+      <c r="O12" s="3" t="inlineStr"/>
+      <c r="P12" s="3" t="inlineStr">
+        <is>
+          <t>Failed to fetch data: Live data fetch timed out after 45s - candle fetching took too long, retrying next cycle</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="3" t="inlineStr">
+        <is>
+          <t>2026-02-25 09:35:00</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>09:35:00</t>
+        </is>
+      </c>
+      <c r="C13" s="3" t="inlineStr">
+        <is>
+          <t>09:35</t>
+        </is>
+      </c>
+      <c r="D13" s="3" t="inlineStr">
+        <is>
+          <t>185.45</t>
+        </is>
+      </c>
+      <c r="E13" s="3" t="inlineStr"/>
+      <c r="F13" s="3" t="inlineStr">
+        <is>
+          <t>200.00</t>
+        </is>
+      </c>
+      <c r="G13" s="3" t="inlineStr"/>
+      <c r="H13" s="3" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="I13" s="3" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="J13" s="3" t="inlineStr"/>
+      <c r="K13" s="3" t="inlineStr"/>
+      <c r="L13" s="3" t="inlineStr"/>
+      <c r="M13" s="3" t="inlineStr"/>
+      <c r="N13" s="3" t="inlineStr"/>
+      <c r="O13" s="3" t="inlineStr"/>
+      <c r="P13" s="3" t="inlineStr">
+        <is>
+          <t>High Strike Check</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="3" t="inlineStr">
+        <is>
+          <t>2026-02-25 09:35:00</t>
+        </is>
+      </c>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>09:35:00</t>
+        </is>
+      </c>
+      <c r="C14" s="3" t="inlineStr">
+        <is>
+          <t>09:35</t>
+        </is>
+      </c>
+      <c r="D14" s="3" t="inlineStr">
+        <is>
+          <t>215.50</t>
+        </is>
+      </c>
+      <c r="E14" s="3" t="inlineStr"/>
+      <c r="F14" s="3" t="inlineStr">
+        <is>
+          <t>159.00</t>
+        </is>
+      </c>
+      <c r="G14" s="3" t="inlineStr"/>
+      <c r="H14" s="3" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="I14" s="3" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="J14" s="3" t="inlineStr"/>
+      <c r="K14" s="3" t="inlineStr"/>
+      <c r="L14" s="3" t="inlineStr"/>
+      <c r="M14" s="3" t="inlineStr"/>
+      <c r="N14" s="3" t="inlineStr"/>
+      <c r="O14" s="3" t="inlineStr"/>
+      <c r="P14" s="3" t="inlineStr">
+        <is>
+          <t>Low Strike Check</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Mine/logs/mine_signal_logs.xlsx
+++ b/Mine/logs/mine_signal_logs.xlsx
@@ -469,7 +469,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P14"/>
+  <dimension ref="A1:P136"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -1198,6 +1198,6042 @@
         </is>
       </c>
     </row>
+    <row r="15">
+      <c r="A15" s="3" t="inlineStr">
+        <is>
+          <t>2026-02-25 09:40:00</t>
+        </is>
+      </c>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>09:40:00</t>
+        </is>
+      </c>
+      <c r="C15" s="3" t="inlineStr">
+        <is>
+          <t>09:40</t>
+        </is>
+      </c>
+      <c r="D15" s="3" t="inlineStr">
+        <is>
+          <t>185.45</t>
+        </is>
+      </c>
+      <c r="E15" s="3" t="inlineStr"/>
+      <c r="F15" s="3" t="inlineStr">
+        <is>
+          <t>200.00</t>
+        </is>
+      </c>
+      <c r="G15" s="3" t="inlineStr"/>
+      <c r="H15" s="3" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="I15" s="3" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="J15" s="3" t="inlineStr"/>
+      <c r="K15" s="3" t="inlineStr"/>
+      <c r="L15" s="3" t="inlineStr"/>
+      <c r="M15" s="3" t="inlineStr"/>
+      <c r="N15" s="3" t="inlineStr"/>
+      <c r="O15" s="3" t="inlineStr"/>
+      <c r="P15" s="3" t="inlineStr">
+        <is>
+          <t>High Strike Check</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="3" t="inlineStr">
+        <is>
+          <t>2026-02-25 09:40:00</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>09:40:00</t>
+        </is>
+      </c>
+      <c r="C16" s="3" t="inlineStr">
+        <is>
+          <t>09:40</t>
+        </is>
+      </c>
+      <c r="D16" s="3" t="inlineStr">
+        <is>
+          <t>215.50</t>
+        </is>
+      </c>
+      <c r="E16" s="3" t="inlineStr"/>
+      <c r="F16" s="3" t="inlineStr">
+        <is>
+          <t>159.00</t>
+        </is>
+      </c>
+      <c r="G16" s="3" t="inlineStr"/>
+      <c r="H16" s="3" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="I16" s="3" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="J16" s="3" t="inlineStr"/>
+      <c r="K16" s="3" t="inlineStr"/>
+      <c r="L16" s="3" t="inlineStr"/>
+      <c r="M16" s="3" t="inlineStr"/>
+      <c r="N16" s="3" t="inlineStr"/>
+      <c r="O16" s="3" t="inlineStr"/>
+      <c r="P16" s="3" t="inlineStr">
+        <is>
+          <t>Low Strike Check</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="3" t="inlineStr">
+        <is>
+          <t>2026-02-25 09:45:00</t>
+        </is>
+      </c>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>09:45:00</t>
+        </is>
+      </c>
+      <c r="C17" s="3" t="inlineStr">
+        <is>
+          <t>09:45</t>
+        </is>
+      </c>
+      <c r="D17" s="3" t="inlineStr">
+        <is>
+          <t>185.45</t>
+        </is>
+      </c>
+      <c r="E17" s="3" t="inlineStr"/>
+      <c r="F17" s="3" t="inlineStr">
+        <is>
+          <t>200.00</t>
+        </is>
+      </c>
+      <c r="G17" s="3" t="inlineStr"/>
+      <c r="H17" s="3" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="I17" s="3" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="J17" s="3" t="inlineStr"/>
+      <c r="K17" s="3" t="inlineStr"/>
+      <c r="L17" s="3" t="inlineStr"/>
+      <c r="M17" s="3" t="inlineStr"/>
+      <c r="N17" s="3" t="inlineStr"/>
+      <c r="O17" s="3" t="inlineStr"/>
+      <c r="P17" s="3" t="inlineStr">
+        <is>
+          <t>High Strike Check</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="3" t="inlineStr">
+        <is>
+          <t>2026-02-25 09:45:00</t>
+        </is>
+      </c>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>09:45:00</t>
+        </is>
+      </c>
+      <c r="C18" s="3" t="inlineStr">
+        <is>
+          <t>09:45</t>
+        </is>
+      </c>
+      <c r="D18" s="3" t="inlineStr">
+        <is>
+          <t>215.50</t>
+        </is>
+      </c>
+      <c r="E18" s="3" t="inlineStr"/>
+      <c r="F18" s="3" t="inlineStr">
+        <is>
+          <t>159.00</t>
+        </is>
+      </c>
+      <c r="G18" s="3" t="inlineStr"/>
+      <c r="H18" s="3" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="I18" s="3" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="J18" s="3" t="inlineStr"/>
+      <c r="K18" s="3" t="inlineStr"/>
+      <c r="L18" s="3" t="inlineStr"/>
+      <c r="M18" s="3" t="inlineStr"/>
+      <c r="N18" s="3" t="inlineStr"/>
+      <c r="O18" s="3" t="inlineStr"/>
+      <c r="P18" s="3" t="inlineStr">
+        <is>
+          <t>Low Strike Check</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="3" t="inlineStr">
+        <is>
+          <t>2026-02-25 09:50:00</t>
+        </is>
+      </c>
+      <c r="B19" s="3" t="inlineStr">
+        <is>
+          <t>09:50:00</t>
+        </is>
+      </c>
+      <c r="C19" s="3" t="inlineStr">
+        <is>
+          <t>09:50</t>
+        </is>
+      </c>
+      <c r="D19" s="3" t="inlineStr">
+        <is>
+          <t>185.45</t>
+        </is>
+      </c>
+      <c r="E19" s="3" t="inlineStr"/>
+      <c r="F19" s="3" t="inlineStr">
+        <is>
+          <t>200.00</t>
+        </is>
+      </c>
+      <c r="G19" s="3" t="inlineStr"/>
+      <c r="H19" s="3" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="I19" s="3" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="J19" s="3" t="inlineStr"/>
+      <c r="K19" s="3" t="inlineStr"/>
+      <c r="L19" s="3" t="inlineStr"/>
+      <c r="M19" s="3" t="inlineStr"/>
+      <c r="N19" s="3" t="inlineStr"/>
+      <c r="O19" s="3" t="inlineStr"/>
+      <c r="P19" s="3" t="inlineStr">
+        <is>
+          <t>High Strike Check</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="3" t="inlineStr">
+        <is>
+          <t>2026-02-25 09:50:00</t>
+        </is>
+      </c>
+      <c r="B20" s="3" t="inlineStr">
+        <is>
+          <t>09:50:00</t>
+        </is>
+      </c>
+      <c r="C20" s="3" t="inlineStr">
+        <is>
+          <t>09:50</t>
+        </is>
+      </c>
+      <c r="D20" s="3" t="inlineStr">
+        <is>
+          <t>215.50</t>
+        </is>
+      </c>
+      <c r="E20" s="3" t="inlineStr"/>
+      <c r="F20" s="3" t="inlineStr">
+        <is>
+          <t>159.00</t>
+        </is>
+      </c>
+      <c r="G20" s="3" t="inlineStr"/>
+      <c r="H20" s="3" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="I20" s="3" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="J20" s="3" t="inlineStr"/>
+      <c r="K20" s="3" t="inlineStr"/>
+      <c r="L20" s="3" t="inlineStr"/>
+      <c r="M20" s="3" t="inlineStr"/>
+      <c r="N20" s="3" t="inlineStr"/>
+      <c r="O20" s="3" t="inlineStr"/>
+      <c r="P20" s="3" t="inlineStr">
+        <is>
+          <t>Low Strike Check</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="3" t="inlineStr">
+        <is>
+          <t>2026-02-25 09:55:00</t>
+        </is>
+      </c>
+      <c r="B21" s="3" t="inlineStr">
+        <is>
+          <t>09:55:00</t>
+        </is>
+      </c>
+      <c r="C21" s="3" t="inlineStr">
+        <is>
+          <t>09:55</t>
+        </is>
+      </c>
+      <c r="D21" s="3" t="inlineStr">
+        <is>
+          <t>185.45</t>
+        </is>
+      </c>
+      <c r="E21" s="3" t="inlineStr"/>
+      <c r="F21" s="3" t="inlineStr">
+        <is>
+          <t>200.00</t>
+        </is>
+      </c>
+      <c r="G21" s="3" t="inlineStr"/>
+      <c r="H21" s="3" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="I21" s="3" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="J21" s="3" t="inlineStr"/>
+      <c r="K21" s="3" t="inlineStr"/>
+      <c r="L21" s="3" t="inlineStr"/>
+      <c r="M21" s="3" t="inlineStr"/>
+      <c r="N21" s="3" t="inlineStr"/>
+      <c r="O21" s="3" t="inlineStr"/>
+      <c r="P21" s="3" t="inlineStr">
+        <is>
+          <t>High Strike Check</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="3" t="inlineStr">
+        <is>
+          <t>2026-02-25 09:55:00</t>
+        </is>
+      </c>
+      <c r="B22" s="3" t="inlineStr">
+        <is>
+          <t>09:55:00</t>
+        </is>
+      </c>
+      <c r="C22" s="3" t="inlineStr">
+        <is>
+          <t>09:55</t>
+        </is>
+      </c>
+      <c r="D22" s="3" t="inlineStr">
+        <is>
+          <t>215.50</t>
+        </is>
+      </c>
+      <c r="E22" s="3" t="inlineStr"/>
+      <c r="F22" s="3" t="inlineStr">
+        <is>
+          <t>159.00</t>
+        </is>
+      </c>
+      <c r="G22" s="3" t="inlineStr"/>
+      <c r="H22" s="3" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="I22" s="3" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="J22" s="3" t="inlineStr"/>
+      <c r="K22" s="3" t="inlineStr"/>
+      <c r="L22" s="3" t="inlineStr"/>
+      <c r="M22" s="3" t="inlineStr"/>
+      <c r="N22" s="3" t="inlineStr"/>
+      <c r="O22" s="3" t="inlineStr"/>
+      <c r="P22" s="3" t="inlineStr">
+        <is>
+          <t>Low Strike Check</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="3" t="inlineStr">
+        <is>
+          <t>2026-02-25 10:00:00</t>
+        </is>
+      </c>
+      <c r="B23" s="3" t="inlineStr">
+        <is>
+          <t>10:00:00</t>
+        </is>
+      </c>
+      <c r="C23" s="3" t="inlineStr">
+        <is>
+          <t>10:00</t>
+        </is>
+      </c>
+      <c r="D23" s="3" t="inlineStr">
+        <is>
+          <t>185.45</t>
+        </is>
+      </c>
+      <c r="E23" s="3" t="inlineStr"/>
+      <c r="F23" s="3" t="inlineStr">
+        <is>
+          <t>200.00</t>
+        </is>
+      </c>
+      <c r="G23" s="3" t="inlineStr"/>
+      <c r="H23" s="3" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="I23" s="3" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="J23" s="3" t="inlineStr"/>
+      <c r="K23" s="3" t="inlineStr"/>
+      <c r="L23" s="3" t="inlineStr"/>
+      <c r="M23" s="3" t="inlineStr"/>
+      <c r="N23" s="3" t="inlineStr"/>
+      <c r="O23" s="3" t="inlineStr"/>
+      <c r="P23" s="3" t="inlineStr">
+        <is>
+          <t>High Strike Check</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="3" t="inlineStr">
+        <is>
+          <t>2026-02-25 10:00:00</t>
+        </is>
+      </c>
+      <c r="B24" s="3" t="inlineStr">
+        <is>
+          <t>10:00:00</t>
+        </is>
+      </c>
+      <c r="C24" s="3" t="inlineStr">
+        <is>
+          <t>10:00</t>
+        </is>
+      </c>
+      <c r="D24" s="3" t="inlineStr">
+        <is>
+          <t>215.50</t>
+        </is>
+      </c>
+      <c r="E24" s="3" t="inlineStr"/>
+      <c r="F24" s="3" t="inlineStr">
+        <is>
+          <t>159.00</t>
+        </is>
+      </c>
+      <c r="G24" s="3" t="inlineStr"/>
+      <c r="H24" s="3" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="I24" s="3" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="J24" s="3" t="inlineStr"/>
+      <c r="K24" s="3" t="inlineStr"/>
+      <c r="L24" s="3" t="inlineStr"/>
+      <c r="M24" s="3" t="inlineStr"/>
+      <c r="N24" s="3" t="inlineStr"/>
+      <c r="O24" s="3" t="inlineStr"/>
+      <c r="P24" s="3" t="inlineStr">
+        <is>
+          <t>Low Strike Check</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="3" t="inlineStr">
+        <is>
+          <t>2026-02-25 10:05:00</t>
+        </is>
+      </c>
+      <c r="B25" s="3" t="inlineStr">
+        <is>
+          <t>10:05:00</t>
+        </is>
+      </c>
+      <c r="C25" s="3" t="inlineStr">
+        <is>
+          <t>10:05</t>
+        </is>
+      </c>
+      <c r="D25" s="3" t="inlineStr">
+        <is>
+          <t>185.45</t>
+        </is>
+      </c>
+      <c r="E25" s="3" t="inlineStr"/>
+      <c r="F25" s="3" t="inlineStr">
+        <is>
+          <t>200.00</t>
+        </is>
+      </c>
+      <c r="G25" s="3" t="inlineStr"/>
+      <c r="H25" s="3" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="I25" s="3" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="J25" s="3" t="inlineStr"/>
+      <c r="K25" s="3" t="inlineStr"/>
+      <c r="L25" s="3" t="inlineStr"/>
+      <c r="M25" s="3" t="inlineStr"/>
+      <c r="N25" s="3" t="inlineStr"/>
+      <c r="O25" s="3" t="inlineStr"/>
+      <c r="P25" s="3" t="inlineStr">
+        <is>
+          <t>High Strike Check</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="3" t="inlineStr">
+        <is>
+          <t>2026-02-25 10:05:00</t>
+        </is>
+      </c>
+      <c r="B26" s="3" t="inlineStr">
+        <is>
+          <t>10:05:00</t>
+        </is>
+      </c>
+      <c r="C26" s="3" t="inlineStr">
+        <is>
+          <t>10:05</t>
+        </is>
+      </c>
+      <c r="D26" s="3" t="inlineStr">
+        <is>
+          <t>215.50</t>
+        </is>
+      </c>
+      <c r="E26" s="3" t="inlineStr"/>
+      <c r="F26" s="3" t="inlineStr">
+        <is>
+          <t>159.00</t>
+        </is>
+      </c>
+      <c r="G26" s="3" t="inlineStr"/>
+      <c r="H26" s="3" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="I26" s="3" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="J26" s="3" t="inlineStr"/>
+      <c r="K26" s="3" t="inlineStr"/>
+      <c r="L26" s="3" t="inlineStr"/>
+      <c r="M26" s="3" t="inlineStr"/>
+      <c r="N26" s="3" t="inlineStr"/>
+      <c r="O26" s="3" t="inlineStr"/>
+      <c r="P26" s="3" t="inlineStr">
+        <is>
+          <t>Low Strike Check</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="3" t="inlineStr">
+        <is>
+          <t>2026-02-25 10:10:00</t>
+        </is>
+      </c>
+      <c r="B27" s="3" t="inlineStr">
+        <is>
+          <t>10:10:00</t>
+        </is>
+      </c>
+      <c r="C27" s="3" t="inlineStr">
+        <is>
+          <t>10:10</t>
+        </is>
+      </c>
+      <c r="D27" s="3" t="inlineStr">
+        <is>
+          <t>185.45</t>
+        </is>
+      </c>
+      <c r="E27" s="3" t="inlineStr"/>
+      <c r="F27" s="3" t="inlineStr">
+        <is>
+          <t>200.00</t>
+        </is>
+      </c>
+      <c r="G27" s="3" t="inlineStr"/>
+      <c r="H27" s="3" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="I27" s="3" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="J27" s="3" t="inlineStr"/>
+      <c r="K27" s="3" t="inlineStr"/>
+      <c r="L27" s="3" t="inlineStr"/>
+      <c r="M27" s="3" t="inlineStr"/>
+      <c r="N27" s="3" t="inlineStr"/>
+      <c r="O27" s="3" t="inlineStr"/>
+      <c r="P27" s="3" t="inlineStr">
+        <is>
+          <t>High Strike Check</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="3" t="inlineStr">
+        <is>
+          <t>2026-02-25 10:10:00</t>
+        </is>
+      </c>
+      <c r="B28" s="3" t="inlineStr">
+        <is>
+          <t>10:10:00</t>
+        </is>
+      </c>
+      <c r="C28" s="3" t="inlineStr">
+        <is>
+          <t>10:10</t>
+        </is>
+      </c>
+      <c r="D28" s="3" t="inlineStr">
+        <is>
+          <t>215.50</t>
+        </is>
+      </c>
+      <c r="E28" s="3" t="inlineStr"/>
+      <c r="F28" s="3" t="inlineStr">
+        <is>
+          <t>159.00</t>
+        </is>
+      </c>
+      <c r="G28" s="3" t="inlineStr"/>
+      <c r="H28" s="3" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="I28" s="3" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="J28" s="3" t="inlineStr"/>
+      <c r="K28" s="3" t="inlineStr"/>
+      <c r="L28" s="3" t="inlineStr"/>
+      <c r="M28" s="3" t="inlineStr"/>
+      <c r="N28" s="3" t="inlineStr"/>
+      <c r="O28" s="3" t="inlineStr"/>
+      <c r="P28" s="3" t="inlineStr">
+        <is>
+          <t>Low Strike Check</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="3" t="inlineStr">
+        <is>
+          <t>2026-02-25 10:15:00</t>
+        </is>
+      </c>
+      <c r="B29" s="3" t="inlineStr">
+        <is>
+          <t>10:15:00</t>
+        </is>
+      </c>
+      <c r="C29" s="3" t="inlineStr">
+        <is>
+          <t>10:15</t>
+        </is>
+      </c>
+      <c r="D29" s="3" t="inlineStr">
+        <is>
+          <t>185.45</t>
+        </is>
+      </c>
+      <c r="E29" s="3" t="inlineStr"/>
+      <c r="F29" s="3" t="inlineStr">
+        <is>
+          <t>200.00</t>
+        </is>
+      </c>
+      <c r="G29" s="3" t="inlineStr"/>
+      <c r="H29" s="3" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="I29" s="3" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="J29" s="3" t="inlineStr"/>
+      <c r="K29" s="3" t="inlineStr"/>
+      <c r="L29" s="3" t="inlineStr"/>
+      <c r="M29" s="3" t="inlineStr"/>
+      <c r="N29" s="3" t="inlineStr"/>
+      <c r="O29" s="3" t="inlineStr"/>
+      <c r="P29" s="3" t="inlineStr">
+        <is>
+          <t>High Strike Check</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="3" t="inlineStr">
+        <is>
+          <t>2026-02-25 10:15:00</t>
+        </is>
+      </c>
+      <c r="B30" s="3" t="inlineStr">
+        <is>
+          <t>10:15:00</t>
+        </is>
+      </c>
+      <c r="C30" s="3" t="inlineStr">
+        <is>
+          <t>10:15</t>
+        </is>
+      </c>
+      <c r="D30" s="3" t="inlineStr">
+        <is>
+          <t>215.50</t>
+        </is>
+      </c>
+      <c r="E30" s="3" t="inlineStr"/>
+      <c r="F30" s="3" t="inlineStr">
+        <is>
+          <t>159.00</t>
+        </is>
+      </c>
+      <c r="G30" s="3" t="inlineStr"/>
+      <c r="H30" s="3" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="I30" s="3" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="J30" s="3" t="inlineStr"/>
+      <c r="K30" s="3" t="inlineStr"/>
+      <c r="L30" s="3" t="inlineStr"/>
+      <c r="M30" s="3" t="inlineStr"/>
+      <c r="N30" s="3" t="inlineStr"/>
+      <c r="O30" s="3" t="inlineStr"/>
+      <c r="P30" s="3" t="inlineStr">
+        <is>
+          <t>Low Strike Check</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="3" t="inlineStr">
+        <is>
+          <t>2026-02-25 10:20:00</t>
+        </is>
+      </c>
+      <c r="B31" s="3" t="inlineStr">
+        <is>
+          <t>10:20:00</t>
+        </is>
+      </c>
+      <c r="C31" s="3" t="inlineStr">
+        <is>
+          <t>10:20</t>
+        </is>
+      </c>
+      <c r="D31" s="3" t="inlineStr">
+        <is>
+          <t>185.45</t>
+        </is>
+      </c>
+      <c r="E31" s="3" t="inlineStr"/>
+      <c r="F31" s="3" t="inlineStr">
+        <is>
+          <t>200.00</t>
+        </is>
+      </c>
+      <c r="G31" s="3" t="inlineStr"/>
+      <c r="H31" s="3" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="I31" s="3" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="J31" s="3" t="inlineStr"/>
+      <c r="K31" s="3" t="inlineStr"/>
+      <c r="L31" s="3" t="inlineStr"/>
+      <c r="M31" s="3" t="inlineStr"/>
+      <c r="N31" s="3" t="inlineStr"/>
+      <c r="O31" s="3" t="inlineStr"/>
+      <c r="P31" s="3" t="inlineStr">
+        <is>
+          <t>High Strike Check</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="3" t="inlineStr">
+        <is>
+          <t>2026-02-25 10:20:00</t>
+        </is>
+      </c>
+      <c r="B32" s="3" t="inlineStr">
+        <is>
+          <t>10:20:00</t>
+        </is>
+      </c>
+      <c r="C32" s="3" t="inlineStr">
+        <is>
+          <t>10:20</t>
+        </is>
+      </c>
+      <c r="D32" s="3" t="inlineStr">
+        <is>
+          <t>215.50</t>
+        </is>
+      </c>
+      <c r="E32" s="3" t="inlineStr"/>
+      <c r="F32" s="3" t="inlineStr">
+        <is>
+          <t>159.00</t>
+        </is>
+      </c>
+      <c r="G32" s="3" t="inlineStr"/>
+      <c r="H32" s="3" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="I32" s="3" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="J32" s="3" t="inlineStr"/>
+      <c r="K32" s="3" t="inlineStr"/>
+      <c r="L32" s="3" t="inlineStr"/>
+      <c r="M32" s="3" t="inlineStr"/>
+      <c r="N32" s="3" t="inlineStr"/>
+      <c r="O32" s="3" t="inlineStr"/>
+      <c r="P32" s="3" t="inlineStr">
+        <is>
+          <t>Low Strike Check</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="3" t="inlineStr">
+        <is>
+          <t>2026-02-25 10:25:00</t>
+        </is>
+      </c>
+      <c r="B33" s="3" t="inlineStr">
+        <is>
+          <t>10:25:00</t>
+        </is>
+      </c>
+      <c r="C33" s="3" t="inlineStr">
+        <is>
+          <t>10:25</t>
+        </is>
+      </c>
+      <c r="D33" s="3" t="inlineStr">
+        <is>
+          <t>185.45</t>
+        </is>
+      </c>
+      <c r="E33" s="3" t="inlineStr"/>
+      <c r="F33" s="3" t="inlineStr">
+        <is>
+          <t>200.00</t>
+        </is>
+      </c>
+      <c r="G33" s="3" t="inlineStr"/>
+      <c r="H33" s="3" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="I33" s="3" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="J33" s="3" t="inlineStr"/>
+      <c r="K33" s="3" t="inlineStr"/>
+      <c r="L33" s="3" t="inlineStr"/>
+      <c r="M33" s="3" t="inlineStr"/>
+      <c r="N33" s="3" t="inlineStr"/>
+      <c r="O33" s="3" t="inlineStr"/>
+      <c r="P33" s="3" t="inlineStr">
+        <is>
+          <t>High Strike Check</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="3" t="inlineStr">
+        <is>
+          <t>2026-02-25 10:25:00</t>
+        </is>
+      </c>
+      <c r="B34" s="3" t="inlineStr">
+        <is>
+          <t>10:25:00</t>
+        </is>
+      </c>
+      <c r="C34" s="3" t="inlineStr">
+        <is>
+          <t>10:25</t>
+        </is>
+      </c>
+      <c r="D34" s="3" t="inlineStr">
+        <is>
+          <t>215.50</t>
+        </is>
+      </c>
+      <c r="E34" s="3" t="inlineStr"/>
+      <c r="F34" s="3" t="inlineStr">
+        <is>
+          <t>159.00</t>
+        </is>
+      </c>
+      <c r="G34" s="3" t="inlineStr"/>
+      <c r="H34" s="3" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="I34" s="3" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="J34" s="3" t="inlineStr"/>
+      <c r="K34" s="3" t="inlineStr"/>
+      <c r="L34" s="3" t="inlineStr"/>
+      <c r="M34" s="3" t="inlineStr"/>
+      <c r="N34" s="3" t="inlineStr"/>
+      <c r="O34" s="3" t="inlineStr"/>
+      <c r="P34" s="3" t="inlineStr">
+        <is>
+          <t>Low Strike Check</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="3" t="inlineStr">
+        <is>
+          <t>2026-02-25 10:30:00</t>
+        </is>
+      </c>
+      <c r="B35" s="3" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="C35" s="3" t="inlineStr">
+        <is>
+          <t>10:30</t>
+        </is>
+      </c>
+      <c r="D35" s="3" t="inlineStr"/>
+      <c r="E35" s="3" t="inlineStr"/>
+      <c r="F35" s="3" t="inlineStr"/>
+      <c r="G35" s="3" t="inlineStr"/>
+      <c r="H35" s="3" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="I35" s="3" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="J35" s="3" t="inlineStr"/>
+      <c r="K35" s="3" t="inlineStr"/>
+      <c r="L35" s="3" t="inlineStr"/>
+      <c r="M35" s="3" t="inlineStr"/>
+      <c r="N35" s="3" t="inlineStr"/>
+      <c r="O35" s="3" t="inlineStr"/>
+      <c r="P35" s="3" t="inlineStr">
+        <is>
+          <t>Data fetch failed: Live data fetch timed out after 45s - candle fetching took too long, retrying next cycle</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="3" t="inlineStr">
+        <is>
+          <t>2026-02-25 10:30:00</t>
+        </is>
+      </c>
+      <c r="B36" s="3" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="C36" s="3" t="inlineStr">
+        <is>
+          <t>10:30</t>
+        </is>
+      </c>
+      <c r="D36" s="3" t="inlineStr"/>
+      <c r="E36" s="3" t="inlineStr"/>
+      <c r="F36" s="3" t="inlineStr"/>
+      <c r="G36" s="3" t="inlineStr"/>
+      <c r="H36" s="3" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="I36" s="3" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="J36" s="3" t="inlineStr"/>
+      <c r="K36" s="3" t="inlineStr"/>
+      <c r="L36" s="3" t="inlineStr"/>
+      <c r="M36" s="3" t="inlineStr"/>
+      <c r="N36" s="3" t="inlineStr"/>
+      <c r="O36" s="3" t="inlineStr"/>
+      <c r="P36" s="3" t="inlineStr">
+        <is>
+          <t>Failed to fetch data: Live data fetch timed out after 45s - candle fetching took too long, retrying next cycle</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="3" t="inlineStr">
+        <is>
+          <t>2026-02-25 10:35:00</t>
+        </is>
+      </c>
+      <c r="B37" s="3" t="inlineStr">
+        <is>
+          <t>10:35:00</t>
+        </is>
+      </c>
+      <c r="C37" s="3" t="inlineStr">
+        <is>
+          <t>10:35</t>
+        </is>
+      </c>
+      <c r="D37" s="3" t="inlineStr">
+        <is>
+          <t>185.45</t>
+        </is>
+      </c>
+      <c r="E37" s="3" t="inlineStr"/>
+      <c r="F37" s="3" t="inlineStr">
+        <is>
+          <t>200.00</t>
+        </is>
+      </c>
+      <c r="G37" s="3" t="inlineStr"/>
+      <c r="H37" s="3" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="I37" s="3" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="J37" s="3" t="inlineStr"/>
+      <c r="K37" s="3" t="inlineStr"/>
+      <c r="L37" s="3" t="inlineStr"/>
+      <c r="M37" s="3" t="inlineStr"/>
+      <c r="N37" s="3" t="inlineStr"/>
+      <c r="O37" s="3" t="inlineStr"/>
+      <c r="P37" s="3" t="inlineStr">
+        <is>
+          <t>High Strike Check</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="3" t="inlineStr">
+        <is>
+          <t>2026-02-25 10:35:00</t>
+        </is>
+      </c>
+      <c r="B38" s="3" t="inlineStr">
+        <is>
+          <t>10:35:00</t>
+        </is>
+      </c>
+      <c r="C38" s="3" t="inlineStr">
+        <is>
+          <t>10:35</t>
+        </is>
+      </c>
+      <c r="D38" s="3" t="inlineStr">
+        <is>
+          <t>215.50</t>
+        </is>
+      </c>
+      <c r="E38" s="3" t="inlineStr"/>
+      <c r="F38" s="3" t="inlineStr">
+        <is>
+          <t>159.00</t>
+        </is>
+      </c>
+      <c r="G38" s="3" t="inlineStr"/>
+      <c r="H38" s="3" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="I38" s="3" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="J38" s="3" t="inlineStr"/>
+      <c r="K38" s="3" t="inlineStr"/>
+      <c r="L38" s="3" t="inlineStr"/>
+      <c r="M38" s="3" t="inlineStr"/>
+      <c r="N38" s="3" t="inlineStr"/>
+      <c r="O38" s="3" t="inlineStr"/>
+      <c r="P38" s="3" t="inlineStr">
+        <is>
+          <t>Low Strike Check</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="3" t="inlineStr">
+        <is>
+          <t>2026-02-25 10:40:00</t>
+        </is>
+      </c>
+      <c r="B39" s="3" t="inlineStr">
+        <is>
+          <t>10:40:00</t>
+        </is>
+      </c>
+      <c r="C39" s="3" t="inlineStr">
+        <is>
+          <t>10:40</t>
+        </is>
+      </c>
+      <c r="D39" s="3" t="inlineStr">
+        <is>
+          <t>185.45</t>
+        </is>
+      </c>
+      <c r="E39" s="3" t="inlineStr"/>
+      <c r="F39" s="3" t="inlineStr">
+        <is>
+          <t>200.00</t>
+        </is>
+      </c>
+      <c r="G39" s="3" t="inlineStr"/>
+      <c r="H39" s="3" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="I39" s="3" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="J39" s="3" t="inlineStr"/>
+      <c r="K39" s="3" t="inlineStr"/>
+      <c r="L39" s="3" t="inlineStr"/>
+      <c r="M39" s="3" t="inlineStr"/>
+      <c r="N39" s="3" t="inlineStr"/>
+      <c r="O39" s="3" t="inlineStr"/>
+      <c r="P39" s="3" t="inlineStr">
+        <is>
+          <t>High Strike Check</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="3" t="inlineStr">
+        <is>
+          <t>2026-02-25 10:40:00</t>
+        </is>
+      </c>
+      <c r="B40" s="3" t="inlineStr">
+        <is>
+          <t>10:40:00</t>
+        </is>
+      </c>
+      <c r="C40" s="3" t="inlineStr">
+        <is>
+          <t>10:40</t>
+        </is>
+      </c>
+      <c r="D40" s="3" t="inlineStr">
+        <is>
+          <t>215.50</t>
+        </is>
+      </c>
+      <c r="E40" s="3" t="inlineStr"/>
+      <c r="F40" s="3" t="inlineStr">
+        <is>
+          <t>159.00</t>
+        </is>
+      </c>
+      <c r="G40" s="3" t="inlineStr"/>
+      <c r="H40" s="3" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="I40" s="3" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="J40" s="3" t="inlineStr"/>
+      <c r="K40" s="3" t="inlineStr"/>
+      <c r="L40" s="3" t="inlineStr"/>
+      <c r="M40" s="3" t="inlineStr"/>
+      <c r="N40" s="3" t="inlineStr"/>
+      <c r="O40" s="3" t="inlineStr"/>
+      <c r="P40" s="3" t="inlineStr">
+        <is>
+          <t>Low Strike Check</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="3" t="inlineStr">
+        <is>
+          <t>2026-02-25 10:45:00</t>
+        </is>
+      </c>
+      <c r="B41" s="3" t="inlineStr">
+        <is>
+          <t>10:45:00</t>
+        </is>
+      </c>
+      <c r="C41" s="3" t="inlineStr">
+        <is>
+          <t>10:45</t>
+        </is>
+      </c>
+      <c r="D41" s="3" t="inlineStr">
+        <is>
+          <t>185.45</t>
+        </is>
+      </c>
+      <c r="E41" s="3" t="inlineStr"/>
+      <c r="F41" s="3" t="inlineStr">
+        <is>
+          <t>200.00</t>
+        </is>
+      </c>
+      <c r="G41" s="3" t="inlineStr"/>
+      <c r="H41" s="3" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="I41" s="3" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="J41" s="3" t="inlineStr"/>
+      <c r="K41" s="3" t="inlineStr"/>
+      <c r="L41" s="3" t="inlineStr"/>
+      <c r="M41" s="3" t="inlineStr"/>
+      <c r="N41" s="3" t="inlineStr"/>
+      <c r="O41" s="3" t="inlineStr"/>
+      <c r="P41" s="3" t="inlineStr">
+        <is>
+          <t>High Strike Check</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="3" t="inlineStr">
+        <is>
+          <t>2026-02-25 10:45:00</t>
+        </is>
+      </c>
+      <c r="B42" s="3" t="inlineStr">
+        <is>
+          <t>10:45:00</t>
+        </is>
+      </c>
+      <c r="C42" s="3" t="inlineStr">
+        <is>
+          <t>10:45</t>
+        </is>
+      </c>
+      <c r="D42" s="3" t="inlineStr">
+        <is>
+          <t>215.50</t>
+        </is>
+      </c>
+      <c r="E42" s="3" t="inlineStr"/>
+      <c r="F42" s="3" t="inlineStr">
+        <is>
+          <t>159.00</t>
+        </is>
+      </c>
+      <c r="G42" s="3" t="inlineStr"/>
+      <c r="H42" s="3" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="I42" s="3" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="J42" s="3" t="inlineStr"/>
+      <c r="K42" s="3" t="inlineStr"/>
+      <c r="L42" s="3" t="inlineStr"/>
+      <c r="M42" s="3" t="inlineStr"/>
+      <c r="N42" s="3" t="inlineStr"/>
+      <c r="O42" s="3" t="inlineStr"/>
+      <c r="P42" s="3" t="inlineStr">
+        <is>
+          <t>Low Strike Check</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="3" t="inlineStr">
+        <is>
+          <t>2026-02-25 11:20:00</t>
+        </is>
+      </c>
+      <c r="B43" s="3" t="inlineStr">
+        <is>
+          <t>11:20:00</t>
+        </is>
+      </c>
+      <c r="C43" s="3" t="inlineStr">
+        <is>
+          <t>11:20</t>
+        </is>
+      </c>
+      <c r="D43" s="3" t="inlineStr">
+        <is>
+          <t>185.45</t>
+        </is>
+      </c>
+      <c r="E43" s="3" t="inlineStr"/>
+      <c r="F43" s="3" t="inlineStr">
+        <is>
+          <t>200.00</t>
+        </is>
+      </c>
+      <c r="G43" s="3" t="inlineStr"/>
+      <c r="H43" s="3" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="I43" s="3" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="J43" s="3" t="inlineStr"/>
+      <c r="K43" s="3" t="inlineStr"/>
+      <c r="L43" s="3" t="inlineStr"/>
+      <c r="M43" s="3" t="inlineStr"/>
+      <c r="N43" s="3" t="inlineStr"/>
+      <c r="O43" s="3" t="inlineStr"/>
+      <c r="P43" s="3" t="inlineStr">
+        <is>
+          <t>High Strike Check</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="3" t="inlineStr">
+        <is>
+          <t>2026-02-25 11:20:00</t>
+        </is>
+      </c>
+      <c r="B44" s="3" t="inlineStr">
+        <is>
+          <t>11:20:00</t>
+        </is>
+      </c>
+      <c r="C44" s="3" t="inlineStr">
+        <is>
+          <t>11:20</t>
+        </is>
+      </c>
+      <c r="D44" s="3" t="inlineStr">
+        <is>
+          <t>215.50</t>
+        </is>
+      </c>
+      <c r="E44" s="3" t="inlineStr"/>
+      <c r="F44" s="3" t="inlineStr">
+        <is>
+          <t>159.00</t>
+        </is>
+      </c>
+      <c r="G44" s="3" t="inlineStr"/>
+      <c r="H44" s="3" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="I44" s="3" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="J44" s="3" t="inlineStr"/>
+      <c r="K44" s="3" t="inlineStr"/>
+      <c r="L44" s="3" t="inlineStr"/>
+      <c r="M44" s="3" t="inlineStr"/>
+      <c r="N44" s="3" t="inlineStr"/>
+      <c r="O44" s="3" t="inlineStr"/>
+      <c r="P44" s="3" t="inlineStr">
+        <is>
+          <t>Low Strike Check</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="3" t="inlineStr">
+        <is>
+          <t>2026-02-25 11:25:00</t>
+        </is>
+      </c>
+      <c r="B45" s="3" t="inlineStr">
+        <is>
+          <t>11:25:00</t>
+        </is>
+      </c>
+      <c r="C45" s="3" t="inlineStr">
+        <is>
+          <t>11:25</t>
+        </is>
+      </c>
+      <c r="D45" s="3" t="inlineStr">
+        <is>
+          <t>185.45</t>
+        </is>
+      </c>
+      <c r="E45" s="3" t="inlineStr"/>
+      <c r="F45" s="3" t="inlineStr">
+        <is>
+          <t>200.00</t>
+        </is>
+      </c>
+      <c r="G45" s="3" t="inlineStr"/>
+      <c r="H45" s="3" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="I45" s="3" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="J45" s="3" t="inlineStr"/>
+      <c r="K45" s="3" t="inlineStr"/>
+      <c r="L45" s="3" t="inlineStr"/>
+      <c r="M45" s="3" t="inlineStr"/>
+      <c r="N45" s="3" t="inlineStr"/>
+      <c r="O45" s="3" t="inlineStr"/>
+      <c r="P45" s="3" t="inlineStr">
+        <is>
+          <t>High Strike Check</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="3" t="inlineStr">
+        <is>
+          <t>2026-02-25 11:25:00</t>
+        </is>
+      </c>
+      <c r="B46" s="3" t="inlineStr">
+        <is>
+          <t>11:25:00</t>
+        </is>
+      </c>
+      <c r="C46" s="3" t="inlineStr">
+        <is>
+          <t>11:25</t>
+        </is>
+      </c>
+      <c r="D46" s="3" t="inlineStr">
+        <is>
+          <t>215.50</t>
+        </is>
+      </c>
+      <c r="E46" s="3" t="inlineStr"/>
+      <c r="F46" s="3" t="inlineStr">
+        <is>
+          <t>159.00</t>
+        </is>
+      </c>
+      <c r="G46" s="3" t="inlineStr"/>
+      <c r="H46" s="3" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="I46" s="3" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="J46" s="3" t="inlineStr"/>
+      <c r="K46" s="3" t="inlineStr"/>
+      <c r="L46" s="3" t="inlineStr"/>
+      <c r="M46" s="3" t="inlineStr"/>
+      <c r="N46" s="3" t="inlineStr"/>
+      <c r="O46" s="3" t="inlineStr"/>
+      <c r="P46" s="3" t="inlineStr">
+        <is>
+          <t>Low Strike Check</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="3" t="inlineStr">
+        <is>
+          <t>2026-02-25 11:30:00</t>
+        </is>
+      </c>
+      <c r="B47" s="3" t="inlineStr">
+        <is>
+          <t>11:30:00</t>
+        </is>
+      </c>
+      <c r="C47" s="3" t="inlineStr">
+        <is>
+          <t>11:30</t>
+        </is>
+      </c>
+      <c r="D47" s="3" t="inlineStr">
+        <is>
+          <t>185.45</t>
+        </is>
+      </c>
+      <c r="E47" s="3" t="inlineStr"/>
+      <c r="F47" s="3" t="inlineStr">
+        <is>
+          <t>200.00</t>
+        </is>
+      </c>
+      <c r="G47" s="3" t="inlineStr"/>
+      <c r="H47" s="3" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="I47" s="3" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="J47" s="3" t="inlineStr"/>
+      <c r="K47" s="3" t="inlineStr"/>
+      <c r="L47" s="3" t="inlineStr"/>
+      <c r="M47" s="3" t="inlineStr"/>
+      <c r="N47" s="3" t="inlineStr"/>
+      <c r="O47" s="3" t="inlineStr"/>
+      <c r="P47" s="3" t="inlineStr">
+        <is>
+          <t>High Strike Check</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="3" t="inlineStr">
+        <is>
+          <t>2026-02-25 11:30:00</t>
+        </is>
+      </c>
+      <c r="B48" s="3" t="inlineStr">
+        <is>
+          <t>11:30:00</t>
+        </is>
+      </c>
+      <c r="C48" s="3" t="inlineStr">
+        <is>
+          <t>11:30</t>
+        </is>
+      </c>
+      <c r="D48" s="3" t="inlineStr">
+        <is>
+          <t>215.50</t>
+        </is>
+      </c>
+      <c r="E48" s="3" t="inlineStr"/>
+      <c r="F48" s="3" t="inlineStr">
+        <is>
+          <t>159.00</t>
+        </is>
+      </c>
+      <c r="G48" s="3" t="inlineStr"/>
+      <c r="H48" s="3" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="I48" s="3" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="J48" s="3" t="inlineStr"/>
+      <c r="K48" s="3" t="inlineStr"/>
+      <c r="L48" s="3" t="inlineStr"/>
+      <c r="M48" s="3" t="inlineStr"/>
+      <c r="N48" s="3" t="inlineStr"/>
+      <c r="O48" s="3" t="inlineStr"/>
+      <c r="P48" s="3" t="inlineStr">
+        <is>
+          <t>Low Strike Check</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="3" t="inlineStr">
+        <is>
+          <t>2026-02-25 11:35:00</t>
+        </is>
+      </c>
+      <c r="B49" s="3" t="inlineStr">
+        <is>
+          <t>11:35:00</t>
+        </is>
+      </c>
+      <c r="C49" s="3" t="inlineStr">
+        <is>
+          <t>11:35</t>
+        </is>
+      </c>
+      <c r="D49" s="3" t="inlineStr">
+        <is>
+          <t>185.45</t>
+        </is>
+      </c>
+      <c r="E49" s="3" t="inlineStr"/>
+      <c r="F49" s="3" t="inlineStr">
+        <is>
+          <t>200.00</t>
+        </is>
+      </c>
+      <c r="G49" s="3" t="inlineStr"/>
+      <c r="H49" s="3" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="I49" s="3" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="J49" s="3" t="inlineStr"/>
+      <c r="K49" s="3" t="inlineStr"/>
+      <c r="L49" s="3" t="inlineStr"/>
+      <c r="M49" s="3" t="inlineStr"/>
+      <c r="N49" s="3" t="inlineStr"/>
+      <c r="O49" s="3" t="inlineStr"/>
+      <c r="P49" s="3" t="inlineStr">
+        <is>
+          <t>High Strike Check</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="3" t="inlineStr">
+        <is>
+          <t>2026-02-25 11:35:00</t>
+        </is>
+      </c>
+      <c r="B50" s="3" t="inlineStr">
+        <is>
+          <t>11:35:00</t>
+        </is>
+      </c>
+      <c r="C50" s="3" t="inlineStr">
+        <is>
+          <t>11:35</t>
+        </is>
+      </c>
+      <c r="D50" s="3" t="inlineStr">
+        <is>
+          <t>215.50</t>
+        </is>
+      </c>
+      <c r="E50" s="3" t="inlineStr"/>
+      <c r="F50" s="3" t="inlineStr">
+        <is>
+          <t>159.00</t>
+        </is>
+      </c>
+      <c r="G50" s="3" t="inlineStr"/>
+      <c r="H50" s="3" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="I50" s="3" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="J50" s="3" t="inlineStr"/>
+      <c r="K50" s="3" t="inlineStr"/>
+      <c r="L50" s="3" t="inlineStr"/>
+      <c r="M50" s="3" t="inlineStr"/>
+      <c r="N50" s="3" t="inlineStr"/>
+      <c r="O50" s="3" t="inlineStr"/>
+      <c r="P50" s="3" t="inlineStr">
+        <is>
+          <t>Low Strike Check</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="3" t="inlineStr">
+        <is>
+          <t>2026-02-25 11:40:00</t>
+        </is>
+      </c>
+      <c r="B51" s="3" t="inlineStr">
+        <is>
+          <t>11:40:00</t>
+        </is>
+      </c>
+      <c r="C51" s="3" t="inlineStr">
+        <is>
+          <t>11:40</t>
+        </is>
+      </c>
+      <c r="D51" s="3" t="inlineStr"/>
+      <c r="E51" s="3" t="inlineStr"/>
+      <c r="F51" s="3" t="inlineStr"/>
+      <c r="G51" s="3" t="inlineStr"/>
+      <c r="H51" s="3" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="I51" s="3" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="J51" s="3" t="inlineStr"/>
+      <c r="K51" s="3" t="inlineStr"/>
+      <c r="L51" s="3" t="inlineStr"/>
+      <c r="M51" s="3" t="inlineStr"/>
+      <c r="N51" s="3" t="inlineStr"/>
+      <c r="O51" s="3" t="inlineStr"/>
+      <c r="P51" s="3" t="inlineStr">
+        <is>
+          <t>Data fetch failed: Live data fetch timed out after 45s - candle fetching took too long, retrying next cycle</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="3" t="inlineStr">
+        <is>
+          <t>2026-02-25 11:40:00</t>
+        </is>
+      </c>
+      <c r="B52" s="3" t="inlineStr">
+        <is>
+          <t>11:40:00</t>
+        </is>
+      </c>
+      <c r="C52" s="3" t="inlineStr">
+        <is>
+          <t>11:40</t>
+        </is>
+      </c>
+      <c r="D52" s="3" t="inlineStr"/>
+      <c r="E52" s="3" t="inlineStr"/>
+      <c r="F52" s="3" t="inlineStr"/>
+      <c r="G52" s="3" t="inlineStr"/>
+      <c r="H52" s="3" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="I52" s="3" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="J52" s="3" t="inlineStr"/>
+      <c r="K52" s="3" t="inlineStr"/>
+      <c r="L52" s="3" t="inlineStr"/>
+      <c r="M52" s="3" t="inlineStr"/>
+      <c r="N52" s="3" t="inlineStr"/>
+      <c r="O52" s="3" t="inlineStr"/>
+      <c r="P52" s="3" t="inlineStr">
+        <is>
+          <t>Failed to fetch data: Live data fetch timed out after 45s - candle fetching took too long, retrying next cycle</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="3" t="inlineStr">
+        <is>
+          <t>2026-02-25 11:45:00</t>
+        </is>
+      </c>
+      <c r="B53" s="3" t="inlineStr">
+        <is>
+          <t>11:45:00</t>
+        </is>
+      </c>
+      <c r="C53" s="3" t="inlineStr">
+        <is>
+          <t>11:45</t>
+        </is>
+      </c>
+      <c r="D53" s="3" t="inlineStr">
+        <is>
+          <t>185.45</t>
+        </is>
+      </c>
+      <c r="E53" s="3" t="inlineStr"/>
+      <c r="F53" s="3" t="inlineStr">
+        <is>
+          <t>200.00</t>
+        </is>
+      </c>
+      <c r="G53" s="3" t="inlineStr"/>
+      <c r="H53" s="3" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="I53" s="3" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="J53" s="3" t="inlineStr"/>
+      <c r="K53" s="3" t="inlineStr"/>
+      <c r="L53" s="3" t="inlineStr"/>
+      <c r="M53" s="3" t="inlineStr"/>
+      <c r="N53" s="3" t="inlineStr"/>
+      <c r="O53" s="3" t="inlineStr"/>
+      <c r="P53" s="3" t="inlineStr">
+        <is>
+          <t>High Strike Check</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="3" t="inlineStr">
+        <is>
+          <t>2026-02-25 11:45:00</t>
+        </is>
+      </c>
+      <c r="B54" s="3" t="inlineStr">
+        <is>
+          <t>11:45:00</t>
+        </is>
+      </c>
+      <c r="C54" s="3" t="inlineStr">
+        <is>
+          <t>11:45</t>
+        </is>
+      </c>
+      <c r="D54" s="3" t="inlineStr">
+        <is>
+          <t>215.50</t>
+        </is>
+      </c>
+      <c r="E54" s="3" t="inlineStr"/>
+      <c r="F54" s="3" t="inlineStr">
+        <is>
+          <t>159.00</t>
+        </is>
+      </c>
+      <c r="G54" s="3" t="inlineStr"/>
+      <c r="H54" s="3" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="I54" s="3" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="J54" s="3" t="inlineStr"/>
+      <c r="K54" s="3" t="inlineStr"/>
+      <c r="L54" s="3" t="inlineStr"/>
+      <c r="M54" s="3" t="inlineStr"/>
+      <c r="N54" s="3" t="inlineStr"/>
+      <c r="O54" s="3" t="inlineStr"/>
+      <c r="P54" s="3" t="inlineStr">
+        <is>
+          <t>Low Strike Check</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="3" t="inlineStr">
+        <is>
+          <t>2026-02-25 11:50:00</t>
+        </is>
+      </c>
+      <c r="B55" s="3" t="inlineStr">
+        <is>
+          <t>11:50:00</t>
+        </is>
+      </c>
+      <c r="C55" s="3" t="inlineStr">
+        <is>
+          <t>11:50</t>
+        </is>
+      </c>
+      <c r="D55" s="3" t="inlineStr">
+        <is>
+          <t>185.45</t>
+        </is>
+      </c>
+      <c r="E55" s="3" t="inlineStr"/>
+      <c r="F55" s="3" t="inlineStr">
+        <is>
+          <t>200.00</t>
+        </is>
+      </c>
+      <c r="G55" s="3" t="inlineStr"/>
+      <c r="H55" s="3" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="I55" s="3" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="J55" s="3" t="inlineStr"/>
+      <c r="K55" s="3" t="inlineStr"/>
+      <c r="L55" s="3" t="inlineStr"/>
+      <c r="M55" s="3" t="inlineStr"/>
+      <c r="N55" s="3" t="inlineStr"/>
+      <c r="O55" s="3" t="inlineStr"/>
+      <c r="P55" s="3" t="inlineStr">
+        <is>
+          <t>High Strike Check</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="3" t="inlineStr">
+        <is>
+          <t>2026-02-25 11:50:00</t>
+        </is>
+      </c>
+      <c r="B56" s="3" t="inlineStr">
+        <is>
+          <t>11:50:00</t>
+        </is>
+      </c>
+      <c r="C56" s="3" t="inlineStr">
+        <is>
+          <t>11:50</t>
+        </is>
+      </c>
+      <c r="D56" s="3" t="inlineStr">
+        <is>
+          <t>215.50</t>
+        </is>
+      </c>
+      <c r="E56" s="3" t="inlineStr"/>
+      <c r="F56" s="3" t="inlineStr">
+        <is>
+          <t>159.00</t>
+        </is>
+      </c>
+      <c r="G56" s="3" t="inlineStr"/>
+      <c r="H56" s="3" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="I56" s="3" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="J56" s="3" t="inlineStr"/>
+      <c r="K56" s="3" t="inlineStr"/>
+      <c r="L56" s="3" t="inlineStr"/>
+      <c r="M56" s="3" t="inlineStr"/>
+      <c r="N56" s="3" t="inlineStr"/>
+      <c r="O56" s="3" t="inlineStr"/>
+      <c r="P56" s="3" t="inlineStr">
+        <is>
+          <t>Low Strike Check</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="3" t="inlineStr">
+        <is>
+          <t>2026-02-25 11:55:00</t>
+        </is>
+      </c>
+      <c r="B57" s="3" t="inlineStr">
+        <is>
+          <t>11:55:00</t>
+        </is>
+      </c>
+      <c r="C57" s="3" t="inlineStr">
+        <is>
+          <t>11:55</t>
+        </is>
+      </c>
+      <c r="D57" s="3" t="inlineStr">
+        <is>
+          <t>185.45</t>
+        </is>
+      </c>
+      <c r="E57" s="3" t="inlineStr"/>
+      <c r="F57" s="3" t="inlineStr">
+        <is>
+          <t>200.00</t>
+        </is>
+      </c>
+      <c r="G57" s="3" t="inlineStr"/>
+      <c r="H57" s="3" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="I57" s="3" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="J57" s="3" t="inlineStr"/>
+      <c r="K57" s="3" t="inlineStr"/>
+      <c r="L57" s="3" t="inlineStr"/>
+      <c r="M57" s="3" t="inlineStr"/>
+      <c r="N57" s="3" t="inlineStr"/>
+      <c r="O57" s="3" t="inlineStr"/>
+      <c r="P57" s="3" t="inlineStr">
+        <is>
+          <t>High Strike Check</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="3" t="inlineStr">
+        <is>
+          <t>2026-02-25 11:55:00</t>
+        </is>
+      </c>
+      <c r="B58" s="3" t="inlineStr">
+        <is>
+          <t>11:55:00</t>
+        </is>
+      </c>
+      <c r="C58" s="3" t="inlineStr">
+        <is>
+          <t>11:55</t>
+        </is>
+      </c>
+      <c r="D58" s="3" t="inlineStr">
+        <is>
+          <t>215.50</t>
+        </is>
+      </c>
+      <c r="E58" s="3" t="inlineStr"/>
+      <c r="F58" s="3" t="inlineStr">
+        <is>
+          <t>159.00</t>
+        </is>
+      </c>
+      <c r="G58" s="3" t="inlineStr"/>
+      <c r="H58" s="3" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="I58" s="3" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="J58" s="3" t="inlineStr"/>
+      <c r="K58" s="3" t="inlineStr"/>
+      <c r="L58" s="3" t="inlineStr"/>
+      <c r="M58" s="3" t="inlineStr"/>
+      <c r="N58" s="3" t="inlineStr"/>
+      <c r="O58" s="3" t="inlineStr"/>
+      <c r="P58" s="3" t="inlineStr">
+        <is>
+          <t>Low Strike Check</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="3" t="inlineStr">
+        <is>
+          <t>2026-02-25 12:00:00</t>
+        </is>
+      </c>
+      <c r="B59" s="3" t="inlineStr">
+        <is>
+          <t>12:00:00</t>
+        </is>
+      </c>
+      <c r="C59" s="3" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
+      <c r="D59" s="3" t="inlineStr">
+        <is>
+          <t>185.45</t>
+        </is>
+      </c>
+      <c r="E59" s="3" t="inlineStr"/>
+      <c r="F59" s="3" t="inlineStr">
+        <is>
+          <t>200.00</t>
+        </is>
+      </c>
+      <c r="G59" s="3" t="inlineStr"/>
+      <c r="H59" s="3" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="I59" s="3" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="J59" s="3" t="inlineStr"/>
+      <c r="K59" s="3" t="inlineStr"/>
+      <c r="L59" s="3" t="inlineStr"/>
+      <c r="M59" s="3" t="inlineStr"/>
+      <c r="N59" s="3" t="inlineStr"/>
+      <c r="O59" s="3" t="inlineStr"/>
+      <c r="P59" s="3" t="inlineStr">
+        <is>
+          <t>High Strike Check</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="3" t="inlineStr">
+        <is>
+          <t>2026-02-25 12:00:00</t>
+        </is>
+      </c>
+      <c r="B60" s="3" t="inlineStr">
+        <is>
+          <t>12:00:00</t>
+        </is>
+      </c>
+      <c r="C60" s="3" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
+      <c r="D60" s="3" t="inlineStr">
+        <is>
+          <t>215.50</t>
+        </is>
+      </c>
+      <c r="E60" s="3" t="inlineStr"/>
+      <c r="F60" s="3" t="inlineStr">
+        <is>
+          <t>159.00</t>
+        </is>
+      </c>
+      <c r="G60" s="3" t="inlineStr"/>
+      <c r="H60" s="3" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="I60" s="3" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="J60" s="3" t="inlineStr"/>
+      <c r="K60" s="3" t="inlineStr"/>
+      <c r="L60" s="3" t="inlineStr"/>
+      <c r="M60" s="3" t="inlineStr"/>
+      <c r="N60" s="3" t="inlineStr"/>
+      <c r="O60" s="3" t="inlineStr"/>
+      <c r="P60" s="3" t="inlineStr">
+        <is>
+          <t>Low Strike Check</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="3" t="inlineStr">
+        <is>
+          <t>2026-02-25 12:05:00</t>
+        </is>
+      </c>
+      <c r="B61" s="3" t="inlineStr">
+        <is>
+          <t>12:05:00</t>
+        </is>
+      </c>
+      <c r="C61" s="3" t="inlineStr">
+        <is>
+          <t>12:05</t>
+        </is>
+      </c>
+      <c r="D61" s="3" t="inlineStr">
+        <is>
+          <t>185.45</t>
+        </is>
+      </c>
+      <c r="E61" s="3" t="inlineStr"/>
+      <c r="F61" s="3" t="inlineStr">
+        <is>
+          <t>200.00</t>
+        </is>
+      </c>
+      <c r="G61" s="3" t="inlineStr"/>
+      <c r="H61" s="3" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="I61" s="3" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="J61" s="3" t="inlineStr"/>
+      <c r="K61" s="3" t="inlineStr"/>
+      <c r="L61" s="3" t="inlineStr"/>
+      <c r="M61" s="3" t="inlineStr"/>
+      <c r="N61" s="3" t="inlineStr"/>
+      <c r="O61" s="3" t="inlineStr"/>
+      <c r="P61" s="3" t="inlineStr">
+        <is>
+          <t>High Strike Check</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="3" t="inlineStr">
+        <is>
+          <t>2026-02-25 12:05:00</t>
+        </is>
+      </c>
+      <c r="B62" s="3" t="inlineStr">
+        <is>
+          <t>12:05:00</t>
+        </is>
+      </c>
+      <c r="C62" s="3" t="inlineStr">
+        <is>
+          <t>12:05</t>
+        </is>
+      </c>
+      <c r="D62" s="3" t="inlineStr">
+        <is>
+          <t>215.50</t>
+        </is>
+      </c>
+      <c r="E62" s="3" t="inlineStr"/>
+      <c r="F62" s="3" t="inlineStr">
+        <is>
+          <t>159.00</t>
+        </is>
+      </c>
+      <c r="G62" s="3" t="inlineStr"/>
+      <c r="H62" s="3" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="I62" s="3" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="J62" s="3" t="inlineStr"/>
+      <c r="K62" s="3" t="inlineStr"/>
+      <c r="L62" s="3" t="inlineStr"/>
+      <c r="M62" s="3" t="inlineStr"/>
+      <c r="N62" s="3" t="inlineStr"/>
+      <c r="O62" s="3" t="inlineStr"/>
+      <c r="P62" s="3" t="inlineStr">
+        <is>
+          <t>Low Strike Check</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="3" t="inlineStr">
+        <is>
+          <t>2026-02-25 12:10:00</t>
+        </is>
+      </c>
+      <c r="B63" s="3" t="inlineStr">
+        <is>
+          <t>12:10:00</t>
+        </is>
+      </c>
+      <c r="C63" s="3" t="inlineStr">
+        <is>
+          <t>12:10</t>
+        </is>
+      </c>
+      <c r="D63" s="3" t="inlineStr">
+        <is>
+          <t>185.45</t>
+        </is>
+      </c>
+      <c r="E63" s="3" t="inlineStr"/>
+      <c r="F63" s="3" t="inlineStr">
+        <is>
+          <t>200.00</t>
+        </is>
+      </c>
+      <c r="G63" s="3" t="inlineStr"/>
+      <c r="H63" s="3" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="I63" s="3" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="J63" s="3" t="inlineStr"/>
+      <c r="K63" s="3" t="inlineStr"/>
+      <c r="L63" s="3" t="inlineStr"/>
+      <c r="M63" s="3" t="inlineStr"/>
+      <c r="N63" s="3" t="inlineStr"/>
+      <c r="O63" s="3" t="inlineStr"/>
+      <c r="P63" s="3" t="inlineStr">
+        <is>
+          <t>High Strike Check</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="3" t="inlineStr">
+        <is>
+          <t>2026-02-25 12:10:00</t>
+        </is>
+      </c>
+      <c r="B64" s="3" t="inlineStr">
+        <is>
+          <t>12:10:00</t>
+        </is>
+      </c>
+      <c r="C64" s="3" t="inlineStr">
+        <is>
+          <t>12:10</t>
+        </is>
+      </c>
+      <c r="D64" s="3" t="inlineStr">
+        <is>
+          <t>215.50</t>
+        </is>
+      </c>
+      <c r="E64" s="3" t="inlineStr"/>
+      <c r="F64" s="3" t="inlineStr">
+        <is>
+          <t>159.00</t>
+        </is>
+      </c>
+      <c r="G64" s="3" t="inlineStr"/>
+      <c r="H64" s="3" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="I64" s="3" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="J64" s="3" t="inlineStr"/>
+      <c r="K64" s="3" t="inlineStr"/>
+      <c r="L64" s="3" t="inlineStr"/>
+      <c r="M64" s="3" t="inlineStr"/>
+      <c r="N64" s="3" t="inlineStr"/>
+      <c r="O64" s="3" t="inlineStr"/>
+      <c r="P64" s="3" t="inlineStr">
+        <is>
+          <t>Low Strike Check</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="3" t="inlineStr">
+        <is>
+          <t>2026-02-25 12:15:00</t>
+        </is>
+      </c>
+      <c r="B65" s="3" t="inlineStr">
+        <is>
+          <t>12:15:00</t>
+        </is>
+      </c>
+      <c r="C65" s="3" t="inlineStr">
+        <is>
+          <t>12:15</t>
+        </is>
+      </c>
+      <c r="D65" s="3" t="inlineStr">
+        <is>
+          <t>185.45</t>
+        </is>
+      </c>
+      <c r="E65" s="3" t="inlineStr"/>
+      <c r="F65" s="3" t="inlineStr">
+        <is>
+          <t>200.00</t>
+        </is>
+      </c>
+      <c r="G65" s="3" t="inlineStr"/>
+      <c r="H65" s="3" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="I65" s="3" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="J65" s="3" t="inlineStr"/>
+      <c r="K65" s="3" t="inlineStr"/>
+      <c r="L65" s="3" t="inlineStr"/>
+      <c r="M65" s="3" t="inlineStr"/>
+      <c r="N65" s="3" t="inlineStr"/>
+      <c r="O65" s="3" t="inlineStr"/>
+      <c r="P65" s="3" t="inlineStr">
+        <is>
+          <t>High Strike Check</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="3" t="inlineStr">
+        <is>
+          <t>2026-02-25 12:15:00</t>
+        </is>
+      </c>
+      <c r="B66" s="3" t="inlineStr">
+        <is>
+          <t>12:15:00</t>
+        </is>
+      </c>
+      <c r="C66" s="3" t="inlineStr">
+        <is>
+          <t>12:15</t>
+        </is>
+      </c>
+      <c r="D66" s="3" t="inlineStr">
+        <is>
+          <t>215.50</t>
+        </is>
+      </c>
+      <c r="E66" s="3" t="inlineStr"/>
+      <c r="F66" s="3" t="inlineStr">
+        <is>
+          <t>159.00</t>
+        </is>
+      </c>
+      <c r="G66" s="3" t="inlineStr"/>
+      <c r="H66" s="3" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="I66" s="3" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="J66" s="3" t="inlineStr"/>
+      <c r="K66" s="3" t="inlineStr"/>
+      <c r="L66" s="3" t="inlineStr"/>
+      <c r="M66" s="3" t="inlineStr"/>
+      <c r="N66" s="3" t="inlineStr"/>
+      <c r="O66" s="3" t="inlineStr"/>
+      <c r="P66" s="3" t="inlineStr">
+        <is>
+          <t>Low Strike Check</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="3" t="inlineStr">
+        <is>
+          <t>2026-02-25 12:20:00</t>
+        </is>
+      </c>
+      <c r="B67" s="3" t="inlineStr">
+        <is>
+          <t>12:20:00</t>
+        </is>
+      </c>
+      <c r="C67" s="3" t="inlineStr">
+        <is>
+          <t>12:20</t>
+        </is>
+      </c>
+      <c r="D67" s="3" t="inlineStr"/>
+      <c r="E67" s="3" t="inlineStr"/>
+      <c r="F67" s="3" t="inlineStr"/>
+      <c r="G67" s="3" t="inlineStr"/>
+      <c r="H67" s="3" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="I67" s="3" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="J67" s="3" t="inlineStr"/>
+      <c r="K67" s="3" t="inlineStr"/>
+      <c r="L67" s="3" t="inlineStr"/>
+      <c r="M67" s="3" t="inlineStr"/>
+      <c r="N67" s="3" t="inlineStr"/>
+      <c r="O67" s="3" t="inlineStr"/>
+      <c r="P67" s="3" t="inlineStr">
+        <is>
+          <t>Data fetch failed: Live data fetch timed out after 45s - candle fetching took too long, retrying next cycle</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="3" t="inlineStr">
+        <is>
+          <t>2026-02-25 12:20:00</t>
+        </is>
+      </c>
+      <c r="B68" s="3" t="inlineStr">
+        <is>
+          <t>12:20:00</t>
+        </is>
+      </c>
+      <c r="C68" s="3" t="inlineStr">
+        <is>
+          <t>12:20</t>
+        </is>
+      </c>
+      <c r="D68" s="3" t="inlineStr"/>
+      <c r="E68" s="3" t="inlineStr"/>
+      <c r="F68" s="3" t="inlineStr"/>
+      <c r="G68" s="3" t="inlineStr"/>
+      <c r="H68" s="3" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="I68" s="3" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="J68" s="3" t="inlineStr"/>
+      <c r="K68" s="3" t="inlineStr"/>
+      <c r="L68" s="3" t="inlineStr"/>
+      <c r="M68" s="3" t="inlineStr"/>
+      <c r="N68" s="3" t="inlineStr"/>
+      <c r="O68" s="3" t="inlineStr"/>
+      <c r="P68" s="3" t="inlineStr">
+        <is>
+          <t>Failed to fetch data: Live data fetch timed out after 45s - candle fetching took too long, retrying next cycle</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="3" t="inlineStr">
+        <is>
+          <t>2026-02-25 12:25:00</t>
+        </is>
+      </c>
+      <c r="B69" s="3" t="inlineStr">
+        <is>
+          <t>12:25:00</t>
+        </is>
+      </c>
+      <c r="C69" s="3" t="inlineStr">
+        <is>
+          <t>12:25</t>
+        </is>
+      </c>
+      <c r="D69" s="3" t="inlineStr">
+        <is>
+          <t>185.45</t>
+        </is>
+      </c>
+      <c r="E69" s="3" t="inlineStr"/>
+      <c r="F69" s="3" t="inlineStr">
+        <is>
+          <t>200.00</t>
+        </is>
+      </c>
+      <c r="G69" s="3" t="inlineStr"/>
+      <c r="H69" s="3" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="I69" s="3" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="J69" s="3" t="inlineStr"/>
+      <c r="K69" s="3" t="inlineStr"/>
+      <c r="L69" s="3" t="inlineStr"/>
+      <c r="M69" s="3" t="inlineStr"/>
+      <c r="N69" s="3" t="inlineStr"/>
+      <c r="O69" s="3" t="inlineStr"/>
+      <c r="P69" s="3" t="inlineStr">
+        <is>
+          <t>High Strike Check</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="3" t="inlineStr">
+        <is>
+          <t>2026-02-25 12:25:00</t>
+        </is>
+      </c>
+      <c r="B70" s="3" t="inlineStr">
+        <is>
+          <t>12:25:00</t>
+        </is>
+      </c>
+      <c r="C70" s="3" t="inlineStr">
+        <is>
+          <t>12:25</t>
+        </is>
+      </c>
+      <c r="D70" s="3" t="inlineStr">
+        <is>
+          <t>215.50</t>
+        </is>
+      </c>
+      <c r="E70" s="3" t="inlineStr"/>
+      <c r="F70" s="3" t="inlineStr">
+        <is>
+          <t>159.00</t>
+        </is>
+      </c>
+      <c r="G70" s="3" t="inlineStr"/>
+      <c r="H70" s="3" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="I70" s="3" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="J70" s="3" t="inlineStr"/>
+      <c r="K70" s="3" t="inlineStr"/>
+      <c r="L70" s="3" t="inlineStr"/>
+      <c r="M70" s="3" t="inlineStr"/>
+      <c r="N70" s="3" t="inlineStr"/>
+      <c r="O70" s="3" t="inlineStr"/>
+      <c r="P70" s="3" t="inlineStr">
+        <is>
+          <t>Low Strike Check</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="3" t="inlineStr">
+        <is>
+          <t>2026-02-25 12:30:00</t>
+        </is>
+      </c>
+      <c r="B71" s="3" t="inlineStr">
+        <is>
+          <t>12:30:00</t>
+        </is>
+      </c>
+      <c r="C71" s="3" t="inlineStr">
+        <is>
+          <t>12:30</t>
+        </is>
+      </c>
+      <c r="D71" s="3" t="inlineStr">
+        <is>
+          <t>185.45</t>
+        </is>
+      </c>
+      <c r="E71" s="3" t="inlineStr"/>
+      <c r="F71" s="3" t="inlineStr">
+        <is>
+          <t>200.00</t>
+        </is>
+      </c>
+      <c r="G71" s="3" t="inlineStr"/>
+      <c r="H71" s="3" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="I71" s="3" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="J71" s="3" t="inlineStr"/>
+      <c r="K71" s="3" t="inlineStr"/>
+      <c r="L71" s="3" t="inlineStr"/>
+      <c r="M71" s="3" t="inlineStr"/>
+      <c r="N71" s="3" t="inlineStr"/>
+      <c r="O71" s="3" t="inlineStr"/>
+      <c r="P71" s="3" t="inlineStr">
+        <is>
+          <t>High Strike Check</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="3" t="inlineStr">
+        <is>
+          <t>2026-02-25 12:30:00</t>
+        </is>
+      </c>
+      <c r="B72" s="3" t="inlineStr">
+        <is>
+          <t>12:30:00</t>
+        </is>
+      </c>
+      <c r="C72" s="3" t="inlineStr">
+        <is>
+          <t>12:30</t>
+        </is>
+      </c>
+      <c r="D72" s="3" t="inlineStr">
+        <is>
+          <t>215.50</t>
+        </is>
+      </c>
+      <c r="E72" s="3" t="inlineStr"/>
+      <c r="F72" s="3" t="inlineStr">
+        <is>
+          <t>159.00</t>
+        </is>
+      </c>
+      <c r="G72" s="3" t="inlineStr"/>
+      <c r="H72" s="3" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="I72" s="3" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="J72" s="3" t="inlineStr"/>
+      <c r="K72" s="3" t="inlineStr"/>
+      <c r="L72" s="3" t="inlineStr"/>
+      <c r="M72" s="3" t="inlineStr"/>
+      <c r="N72" s="3" t="inlineStr"/>
+      <c r="O72" s="3" t="inlineStr"/>
+      <c r="P72" s="3" t="inlineStr">
+        <is>
+          <t>Low Strike Check</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="3" t="inlineStr">
+        <is>
+          <t>2026-02-25 12:35:00</t>
+        </is>
+      </c>
+      <c r="B73" s="3" t="inlineStr">
+        <is>
+          <t>12:35:00</t>
+        </is>
+      </c>
+      <c r="C73" s="3" t="inlineStr">
+        <is>
+          <t>12:35</t>
+        </is>
+      </c>
+      <c r="D73" s="3" t="inlineStr">
+        <is>
+          <t>185.45</t>
+        </is>
+      </c>
+      <c r="E73" s="3" t="inlineStr"/>
+      <c r="F73" s="3" t="inlineStr">
+        <is>
+          <t>200.00</t>
+        </is>
+      </c>
+      <c r="G73" s="3" t="inlineStr"/>
+      <c r="H73" s="3" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="I73" s="3" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="J73" s="3" t="inlineStr"/>
+      <c r="K73" s="3" t="inlineStr"/>
+      <c r="L73" s="3" t="inlineStr"/>
+      <c r="M73" s="3" t="inlineStr"/>
+      <c r="N73" s="3" t="inlineStr"/>
+      <c r="O73" s="3" t="inlineStr"/>
+      <c r="P73" s="3" t="inlineStr">
+        <is>
+          <t>High Strike Check</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="3" t="inlineStr">
+        <is>
+          <t>2026-02-25 12:35:00</t>
+        </is>
+      </c>
+      <c r="B74" s="3" t="inlineStr">
+        <is>
+          <t>12:35:00</t>
+        </is>
+      </c>
+      <c r="C74" s="3" t="inlineStr">
+        <is>
+          <t>12:35</t>
+        </is>
+      </c>
+      <c r="D74" s="3" t="inlineStr">
+        <is>
+          <t>215.50</t>
+        </is>
+      </c>
+      <c r="E74" s="3" t="inlineStr"/>
+      <c r="F74" s="3" t="inlineStr">
+        <is>
+          <t>159.00</t>
+        </is>
+      </c>
+      <c r="G74" s="3" t="inlineStr"/>
+      <c r="H74" s="3" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="I74" s="3" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="J74" s="3" t="inlineStr"/>
+      <c r="K74" s="3" t="inlineStr"/>
+      <c r="L74" s="3" t="inlineStr"/>
+      <c r="M74" s="3" t="inlineStr"/>
+      <c r="N74" s="3" t="inlineStr"/>
+      <c r="O74" s="3" t="inlineStr"/>
+      <c r="P74" s="3" t="inlineStr">
+        <is>
+          <t>Low Strike Check</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="3" t="inlineStr">
+        <is>
+          <t>2026-02-25 12:40:00</t>
+        </is>
+      </c>
+      <c r="B75" s="3" t="inlineStr">
+        <is>
+          <t>12:40:00</t>
+        </is>
+      </c>
+      <c r="C75" s="3" t="inlineStr">
+        <is>
+          <t>12:40</t>
+        </is>
+      </c>
+      <c r="D75" s="3" t="inlineStr">
+        <is>
+          <t>185.45</t>
+        </is>
+      </c>
+      <c r="E75" s="3" t="inlineStr"/>
+      <c r="F75" s="3" t="inlineStr">
+        <is>
+          <t>200.00</t>
+        </is>
+      </c>
+      <c r="G75" s="3" t="inlineStr"/>
+      <c r="H75" s="3" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="I75" s="3" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="J75" s="3" t="inlineStr"/>
+      <c r="K75" s="3" t="inlineStr"/>
+      <c r="L75" s="3" t="inlineStr"/>
+      <c r="M75" s="3" t="inlineStr"/>
+      <c r="N75" s="3" t="inlineStr"/>
+      <c r="O75" s="3" t="inlineStr"/>
+      <c r="P75" s="3" t="inlineStr">
+        <is>
+          <t>High Strike Check</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="3" t="inlineStr">
+        <is>
+          <t>2026-02-25 12:40:00</t>
+        </is>
+      </c>
+      <c r="B76" s="3" t="inlineStr">
+        <is>
+          <t>12:40:00</t>
+        </is>
+      </c>
+      <c r="C76" s="3" t="inlineStr">
+        <is>
+          <t>12:40</t>
+        </is>
+      </c>
+      <c r="D76" s="3" t="inlineStr">
+        <is>
+          <t>215.50</t>
+        </is>
+      </c>
+      <c r="E76" s="3" t="inlineStr"/>
+      <c r="F76" s="3" t="inlineStr">
+        <is>
+          <t>159.00</t>
+        </is>
+      </c>
+      <c r="G76" s="3" t="inlineStr"/>
+      <c r="H76" s="3" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="I76" s="3" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="J76" s="3" t="inlineStr"/>
+      <c r="K76" s="3" t="inlineStr"/>
+      <c r="L76" s="3" t="inlineStr"/>
+      <c r="M76" s="3" t="inlineStr"/>
+      <c r="N76" s="3" t="inlineStr"/>
+      <c r="O76" s="3" t="inlineStr"/>
+      <c r="P76" s="3" t="inlineStr">
+        <is>
+          <t>Low Strike Check</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="3" t="inlineStr">
+        <is>
+          <t>2026-02-25 12:45:00</t>
+        </is>
+      </c>
+      <c r="B77" s="3" t="inlineStr">
+        <is>
+          <t>12:45:00</t>
+        </is>
+      </c>
+      <c r="C77" s="3" t="inlineStr">
+        <is>
+          <t>12:45</t>
+        </is>
+      </c>
+      <c r="D77" s="3" t="inlineStr">
+        <is>
+          <t>185.45</t>
+        </is>
+      </c>
+      <c r="E77" s="3" t="inlineStr"/>
+      <c r="F77" s="3" t="inlineStr">
+        <is>
+          <t>200.00</t>
+        </is>
+      </c>
+      <c r="G77" s="3" t="inlineStr"/>
+      <c r="H77" s="3" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="I77" s="3" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="J77" s="3" t="inlineStr"/>
+      <c r="K77" s="3" t="inlineStr"/>
+      <c r="L77" s="3" t="inlineStr"/>
+      <c r="M77" s="3" t="inlineStr"/>
+      <c r="N77" s="3" t="inlineStr"/>
+      <c r="O77" s="3" t="inlineStr"/>
+      <c r="P77" s="3" t="inlineStr">
+        <is>
+          <t>High Strike Check</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="3" t="inlineStr">
+        <is>
+          <t>2026-02-25 12:45:00</t>
+        </is>
+      </c>
+      <c r="B78" s="3" t="inlineStr">
+        <is>
+          <t>12:45:00</t>
+        </is>
+      </c>
+      <c r="C78" s="3" t="inlineStr">
+        <is>
+          <t>12:45</t>
+        </is>
+      </c>
+      <c r="D78" s="3" t="inlineStr">
+        <is>
+          <t>215.50</t>
+        </is>
+      </c>
+      <c r="E78" s="3" t="inlineStr"/>
+      <c r="F78" s="3" t="inlineStr">
+        <is>
+          <t>159.00</t>
+        </is>
+      </c>
+      <c r="G78" s="3" t="inlineStr"/>
+      <c r="H78" s="3" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="I78" s="3" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="J78" s="3" t="inlineStr"/>
+      <c r="K78" s="3" t="inlineStr"/>
+      <c r="L78" s="3" t="inlineStr"/>
+      <c r="M78" s="3" t="inlineStr"/>
+      <c r="N78" s="3" t="inlineStr"/>
+      <c r="O78" s="3" t="inlineStr"/>
+      <c r="P78" s="3" t="inlineStr">
+        <is>
+          <t>Low Strike Check</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="3" t="inlineStr">
+        <is>
+          <t>2026-02-25 12:50:00</t>
+        </is>
+      </c>
+      <c r="B79" s="3" t="inlineStr">
+        <is>
+          <t>12:50:00</t>
+        </is>
+      </c>
+      <c r="C79" s="3" t="inlineStr">
+        <is>
+          <t>12:50</t>
+        </is>
+      </c>
+      <c r="D79" s="3" t="inlineStr">
+        <is>
+          <t>185.45</t>
+        </is>
+      </c>
+      <c r="E79" s="3" t="inlineStr"/>
+      <c r="F79" s="3" t="inlineStr">
+        <is>
+          <t>200.00</t>
+        </is>
+      </c>
+      <c r="G79" s="3" t="inlineStr"/>
+      <c r="H79" s="3" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="I79" s="3" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="J79" s="3" t="inlineStr"/>
+      <c r="K79" s="3" t="inlineStr"/>
+      <c r="L79" s="3" t="inlineStr"/>
+      <c r="M79" s="3" t="inlineStr"/>
+      <c r="N79" s="3" t="inlineStr"/>
+      <c r="O79" s="3" t="inlineStr"/>
+      <c r="P79" s="3" t="inlineStr">
+        <is>
+          <t>High Strike Check</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="3" t="inlineStr">
+        <is>
+          <t>2026-02-25 12:50:00</t>
+        </is>
+      </c>
+      <c r="B80" s="3" t="inlineStr">
+        <is>
+          <t>12:50:00</t>
+        </is>
+      </c>
+      <c r="C80" s="3" t="inlineStr">
+        <is>
+          <t>12:50</t>
+        </is>
+      </c>
+      <c r="D80" s="3" t="inlineStr">
+        <is>
+          <t>215.50</t>
+        </is>
+      </c>
+      <c r="E80" s="3" t="inlineStr"/>
+      <c r="F80" s="3" t="inlineStr">
+        <is>
+          <t>159.00</t>
+        </is>
+      </c>
+      <c r="G80" s="3" t="inlineStr"/>
+      <c r="H80" s="3" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="I80" s="3" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="J80" s="3" t="inlineStr"/>
+      <c r="K80" s="3" t="inlineStr"/>
+      <c r="L80" s="3" t="inlineStr"/>
+      <c r="M80" s="3" t="inlineStr"/>
+      <c r="N80" s="3" t="inlineStr"/>
+      <c r="O80" s="3" t="inlineStr"/>
+      <c r="P80" s="3" t="inlineStr">
+        <is>
+          <t>Low Strike Check</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="3" t="inlineStr">
+        <is>
+          <t>2026-02-25 12:55:00</t>
+        </is>
+      </c>
+      <c r="B81" s="3" t="inlineStr">
+        <is>
+          <t>12:55:00</t>
+        </is>
+      </c>
+      <c r="C81" s="3" t="inlineStr">
+        <is>
+          <t>12:55</t>
+        </is>
+      </c>
+      <c r="D81" s="3" t="inlineStr">
+        <is>
+          <t>185.45</t>
+        </is>
+      </c>
+      <c r="E81" s="3" t="inlineStr"/>
+      <c r="F81" s="3" t="inlineStr">
+        <is>
+          <t>200.00</t>
+        </is>
+      </c>
+      <c r="G81" s="3" t="inlineStr"/>
+      <c r="H81" s="3" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="I81" s="3" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="J81" s="3" t="inlineStr"/>
+      <c r="K81" s="3" t="inlineStr"/>
+      <c r="L81" s="3" t="inlineStr"/>
+      <c r="M81" s="3" t="inlineStr"/>
+      <c r="N81" s="3" t="inlineStr"/>
+      <c r="O81" s="3" t="inlineStr"/>
+      <c r="P81" s="3" t="inlineStr">
+        <is>
+          <t>High Strike Check</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="3" t="inlineStr">
+        <is>
+          <t>2026-02-25 12:55:00</t>
+        </is>
+      </c>
+      <c r="B82" s="3" t="inlineStr">
+        <is>
+          <t>12:55:00</t>
+        </is>
+      </c>
+      <c r="C82" s="3" t="inlineStr">
+        <is>
+          <t>12:55</t>
+        </is>
+      </c>
+      <c r="D82" s="3" t="inlineStr">
+        <is>
+          <t>215.50</t>
+        </is>
+      </c>
+      <c r="E82" s="3" t="inlineStr"/>
+      <c r="F82" s="3" t="inlineStr">
+        <is>
+          <t>159.00</t>
+        </is>
+      </c>
+      <c r="G82" s="3" t="inlineStr"/>
+      <c r="H82" s="3" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="I82" s="3" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="J82" s="3" t="inlineStr"/>
+      <c r="K82" s="3" t="inlineStr"/>
+      <c r="L82" s="3" t="inlineStr"/>
+      <c r="M82" s="3" t="inlineStr"/>
+      <c r="N82" s="3" t="inlineStr"/>
+      <c r="O82" s="3" t="inlineStr"/>
+      <c r="P82" s="3" t="inlineStr">
+        <is>
+          <t>Low Strike Check</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="3" t="inlineStr">
+        <is>
+          <t>2026-02-25 13:00:00</t>
+        </is>
+      </c>
+      <c r="B83" s="3" t="inlineStr">
+        <is>
+          <t>13:00:00</t>
+        </is>
+      </c>
+      <c r="C83" s="3" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="D83" s="3" t="inlineStr">
+        <is>
+          <t>185.45</t>
+        </is>
+      </c>
+      <c r="E83" s="3" t="inlineStr"/>
+      <c r="F83" s="3" t="inlineStr">
+        <is>
+          <t>200.00</t>
+        </is>
+      </c>
+      <c r="G83" s="3" t="inlineStr"/>
+      <c r="H83" s="3" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="I83" s="3" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="J83" s="3" t="inlineStr"/>
+      <c r="K83" s="3" t="inlineStr"/>
+      <c r="L83" s="3" t="inlineStr"/>
+      <c r="M83" s="3" t="inlineStr"/>
+      <c r="N83" s="3" t="inlineStr"/>
+      <c r="O83" s="3" t="inlineStr"/>
+      <c r="P83" s="3" t="inlineStr">
+        <is>
+          <t>High Strike Check</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="3" t="inlineStr">
+        <is>
+          <t>2026-02-25 13:00:00</t>
+        </is>
+      </c>
+      <c r="B84" s="3" t="inlineStr">
+        <is>
+          <t>13:00:00</t>
+        </is>
+      </c>
+      <c r="C84" s="3" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="D84" s="3" t="inlineStr">
+        <is>
+          <t>215.50</t>
+        </is>
+      </c>
+      <c r="E84" s="3" t="inlineStr"/>
+      <c r="F84" s="3" t="inlineStr">
+        <is>
+          <t>159.00</t>
+        </is>
+      </c>
+      <c r="G84" s="3" t="inlineStr"/>
+      <c r="H84" s="3" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="I84" s="3" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="J84" s="3" t="inlineStr"/>
+      <c r="K84" s="3" t="inlineStr"/>
+      <c r="L84" s="3" t="inlineStr"/>
+      <c r="M84" s="3" t="inlineStr"/>
+      <c r="N84" s="3" t="inlineStr"/>
+      <c r="O84" s="3" t="inlineStr"/>
+      <c r="P84" s="3" t="inlineStr">
+        <is>
+          <t>Low Strike Check</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="3" t="inlineStr">
+        <is>
+          <t>2026-02-25 13:05:00</t>
+        </is>
+      </c>
+      <c r="B85" s="3" t="inlineStr">
+        <is>
+          <t>13:05:00</t>
+        </is>
+      </c>
+      <c r="C85" s="3" t="inlineStr">
+        <is>
+          <t>13:05</t>
+        </is>
+      </c>
+      <c r="D85" s="3" t="inlineStr">
+        <is>
+          <t>185.45</t>
+        </is>
+      </c>
+      <c r="E85" s="3" t="inlineStr"/>
+      <c r="F85" s="3" t="inlineStr">
+        <is>
+          <t>200.00</t>
+        </is>
+      </c>
+      <c r="G85" s="3" t="inlineStr"/>
+      <c r="H85" s="3" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="I85" s="3" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="J85" s="3" t="inlineStr"/>
+      <c r="K85" s="3" t="inlineStr"/>
+      <c r="L85" s="3" t="inlineStr"/>
+      <c r="M85" s="3" t="inlineStr"/>
+      <c r="N85" s="3" t="inlineStr"/>
+      <c r="O85" s="3" t="inlineStr"/>
+      <c r="P85" s="3" t="inlineStr">
+        <is>
+          <t>High Strike Check</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="3" t="inlineStr">
+        <is>
+          <t>2026-02-25 13:05:00</t>
+        </is>
+      </c>
+      <c r="B86" s="3" t="inlineStr">
+        <is>
+          <t>13:05:00</t>
+        </is>
+      </c>
+      <c r="C86" s="3" t="inlineStr">
+        <is>
+          <t>13:05</t>
+        </is>
+      </c>
+      <c r="D86" s="3" t="inlineStr">
+        <is>
+          <t>215.50</t>
+        </is>
+      </c>
+      <c r="E86" s="3" t="inlineStr"/>
+      <c r="F86" s="3" t="inlineStr">
+        <is>
+          <t>159.00</t>
+        </is>
+      </c>
+      <c r="G86" s="3" t="inlineStr"/>
+      <c r="H86" s="3" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="I86" s="3" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="J86" s="3" t="inlineStr"/>
+      <c r="K86" s="3" t="inlineStr"/>
+      <c r="L86" s="3" t="inlineStr"/>
+      <c r="M86" s="3" t="inlineStr"/>
+      <c r="N86" s="3" t="inlineStr"/>
+      <c r="O86" s="3" t="inlineStr"/>
+      <c r="P86" s="3" t="inlineStr">
+        <is>
+          <t>Low Strike Check</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="3" t="inlineStr">
+        <is>
+          <t>2026-02-25 13:10:00</t>
+        </is>
+      </c>
+      <c r="B87" s="3" t="inlineStr">
+        <is>
+          <t>13:10:00</t>
+        </is>
+      </c>
+      <c r="C87" s="3" t="inlineStr">
+        <is>
+          <t>13:10</t>
+        </is>
+      </c>
+      <c r="D87" s="3" t="inlineStr">
+        <is>
+          <t>185.45</t>
+        </is>
+      </c>
+      <c r="E87" s="3" t="inlineStr"/>
+      <c r="F87" s="3" t="inlineStr">
+        <is>
+          <t>200.00</t>
+        </is>
+      </c>
+      <c r="G87" s="3" t="inlineStr"/>
+      <c r="H87" s="3" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="I87" s="3" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="J87" s="3" t="inlineStr"/>
+      <c r="K87" s="3" t="inlineStr"/>
+      <c r="L87" s="3" t="inlineStr"/>
+      <c r="M87" s="3" t="inlineStr"/>
+      <c r="N87" s="3" t="inlineStr"/>
+      <c r="O87" s="3" t="inlineStr"/>
+      <c r="P87" s="3" t="inlineStr">
+        <is>
+          <t>High Strike Check</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="3" t="inlineStr">
+        <is>
+          <t>2026-02-25 13:10:00</t>
+        </is>
+      </c>
+      <c r="B88" s="3" t="inlineStr">
+        <is>
+          <t>13:10:00</t>
+        </is>
+      </c>
+      <c r="C88" s="3" t="inlineStr">
+        <is>
+          <t>13:10</t>
+        </is>
+      </c>
+      <c r="D88" s="3" t="inlineStr">
+        <is>
+          <t>215.50</t>
+        </is>
+      </c>
+      <c r="E88" s="3" t="inlineStr"/>
+      <c r="F88" s="3" t="inlineStr">
+        <is>
+          <t>159.00</t>
+        </is>
+      </c>
+      <c r="G88" s="3" t="inlineStr"/>
+      <c r="H88" s="3" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="I88" s="3" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="J88" s="3" t="inlineStr"/>
+      <c r="K88" s="3" t="inlineStr"/>
+      <c r="L88" s="3" t="inlineStr"/>
+      <c r="M88" s="3" t="inlineStr"/>
+      <c r="N88" s="3" t="inlineStr"/>
+      <c r="O88" s="3" t="inlineStr"/>
+      <c r="P88" s="3" t="inlineStr">
+        <is>
+          <t>Low Strike Check</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="3" t="inlineStr">
+        <is>
+          <t>2026-02-25 13:15:00</t>
+        </is>
+      </c>
+      <c r="B89" s="3" t="inlineStr">
+        <is>
+          <t>13:15:00</t>
+        </is>
+      </c>
+      <c r="C89" s="3" t="inlineStr">
+        <is>
+          <t>13:15</t>
+        </is>
+      </c>
+      <c r="D89" s="3" t="inlineStr">
+        <is>
+          <t>185.45</t>
+        </is>
+      </c>
+      <c r="E89" s="3" t="inlineStr"/>
+      <c r="F89" s="3" t="inlineStr">
+        <is>
+          <t>200.00</t>
+        </is>
+      </c>
+      <c r="G89" s="3" t="inlineStr"/>
+      <c r="H89" s="3" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="I89" s="3" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="J89" s="3" t="inlineStr"/>
+      <c r="K89" s="3" t="inlineStr"/>
+      <c r="L89" s="3" t="inlineStr"/>
+      <c r="M89" s="3" t="inlineStr"/>
+      <c r="N89" s="3" t="inlineStr"/>
+      <c r="O89" s="3" t="inlineStr"/>
+      <c r="P89" s="3" t="inlineStr">
+        <is>
+          <t>High Strike Check</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="3" t="inlineStr">
+        <is>
+          <t>2026-02-25 13:15:00</t>
+        </is>
+      </c>
+      <c r="B90" s="3" t="inlineStr">
+        <is>
+          <t>13:15:00</t>
+        </is>
+      </c>
+      <c r="C90" s="3" t="inlineStr">
+        <is>
+          <t>13:15</t>
+        </is>
+      </c>
+      <c r="D90" s="3" t="inlineStr">
+        <is>
+          <t>215.50</t>
+        </is>
+      </c>
+      <c r="E90" s="3" t="inlineStr"/>
+      <c r="F90" s="3" t="inlineStr">
+        <is>
+          <t>159.00</t>
+        </is>
+      </c>
+      <c r="G90" s="3" t="inlineStr"/>
+      <c r="H90" s="3" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="I90" s="3" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="J90" s="3" t="inlineStr"/>
+      <c r="K90" s="3" t="inlineStr"/>
+      <c r="L90" s="3" t="inlineStr"/>
+      <c r="M90" s="3" t="inlineStr"/>
+      <c r="N90" s="3" t="inlineStr"/>
+      <c r="O90" s="3" t="inlineStr"/>
+      <c r="P90" s="3" t="inlineStr">
+        <is>
+          <t>Low Strike Check</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="3" t="inlineStr">
+        <is>
+          <t>2026-02-25 13:20:00</t>
+        </is>
+      </c>
+      <c r="B91" s="3" t="inlineStr">
+        <is>
+          <t>13:20:00</t>
+        </is>
+      </c>
+      <c r="C91" s="3" t="inlineStr">
+        <is>
+          <t>13:20</t>
+        </is>
+      </c>
+      <c r="D91" s="3" t="inlineStr">
+        <is>
+          <t>185.45</t>
+        </is>
+      </c>
+      <c r="E91" s="3" t="inlineStr"/>
+      <c r="F91" s="3" t="inlineStr">
+        <is>
+          <t>200.00</t>
+        </is>
+      </c>
+      <c r="G91" s="3" t="inlineStr"/>
+      <c r="H91" s="3" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="I91" s="3" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="J91" s="3" t="inlineStr"/>
+      <c r="K91" s="3" t="inlineStr"/>
+      <c r="L91" s="3" t="inlineStr"/>
+      <c r="M91" s="3" t="inlineStr"/>
+      <c r="N91" s="3" t="inlineStr"/>
+      <c r="O91" s="3" t="inlineStr"/>
+      <c r="P91" s="3" t="inlineStr">
+        <is>
+          <t>High Strike Check</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="3" t="inlineStr">
+        <is>
+          <t>2026-02-25 13:20:00</t>
+        </is>
+      </c>
+      <c r="B92" s="3" t="inlineStr">
+        <is>
+          <t>13:20:00</t>
+        </is>
+      </c>
+      <c r="C92" s="3" t="inlineStr">
+        <is>
+          <t>13:20</t>
+        </is>
+      </c>
+      <c r="D92" s="3" t="inlineStr">
+        <is>
+          <t>215.50</t>
+        </is>
+      </c>
+      <c r="E92" s="3" t="inlineStr"/>
+      <c r="F92" s="3" t="inlineStr">
+        <is>
+          <t>159.00</t>
+        </is>
+      </c>
+      <c r="G92" s="3" t="inlineStr"/>
+      <c r="H92" s="3" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="I92" s="3" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="J92" s="3" t="inlineStr"/>
+      <c r="K92" s="3" t="inlineStr"/>
+      <c r="L92" s="3" t="inlineStr"/>
+      <c r="M92" s="3" t="inlineStr"/>
+      <c r="N92" s="3" t="inlineStr"/>
+      <c r="O92" s="3" t="inlineStr"/>
+      <c r="P92" s="3" t="inlineStr">
+        <is>
+          <t>Low Strike Check</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="3" t="inlineStr">
+        <is>
+          <t>2026-02-25 13:25:00</t>
+        </is>
+      </c>
+      <c r="B93" s="3" t="inlineStr">
+        <is>
+          <t>13:25:00</t>
+        </is>
+      </c>
+      <c r="C93" s="3" t="inlineStr">
+        <is>
+          <t>13:25</t>
+        </is>
+      </c>
+      <c r="D93" s="3" t="inlineStr">
+        <is>
+          <t>185.45</t>
+        </is>
+      </c>
+      <c r="E93" s="3" t="inlineStr"/>
+      <c r="F93" s="3" t="inlineStr">
+        <is>
+          <t>200.00</t>
+        </is>
+      </c>
+      <c r="G93" s="3" t="inlineStr"/>
+      <c r="H93" s="3" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="I93" s="3" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="J93" s="3" t="inlineStr"/>
+      <c r="K93" s="3" t="inlineStr"/>
+      <c r="L93" s="3" t="inlineStr"/>
+      <c r="M93" s="3" t="inlineStr"/>
+      <c r="N93" s="3" t="inlineStr"/>
+      <c r="O93" s="3" t="inlineStr"/>
+      <c r="P93" s="3" t="inlineStr">
+        <is>
+          <t>High Strike Check</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="3" t="inlineStr">
+        <is>
+          <t>2026-02-25 13:25:00</t>
+        </is>
+      </c>
+      <c r="B94" s="3" t="inlineStr">
+        <is>
+          <t>13:25:00</t>
+        </is>
+      </c>
+      <c r="C94" s="3" t="inlineStr">
+        <is>
+          <t>13:25</t>
+        </is>
+      </c>
+      <c r="D94" s="3" t="inlineStr">
+        <is>
+          <t>215.50</t>
+        </is>
+      </c>
+      <c r="E94" s="3" t="inlineStr"/>
+      <c r="F94" s="3" t="inlineStr">
+        <is>
+          <t>159.00</t>
+        </is>
+      </c>
+      <c r="G94" s="3" t="inlineStr"/>
+      <c r="H94" s="3" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="I94" s="3" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="J94" s="3" t="inlineStr"/>
+      <c r="K94" s="3" t="inlineStr"/>
+      <c r="L94" s="3" t="inlineStr"/>
+      <c r="M94" s="3" t="inlineStr"/>
+      <c r="N94" s="3" t="inlineStr"/>
+      <c r="O94" s="3" t="inlineStr"/>
+      <c r="P94" s="3" t="inlineStr">
+        <is>
+          <t>Low Strike Check</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="3" t="inlineStr">
+        <is>
+          <t>2026-02-25 13:30:00</t>
+        </is>
+      </c>
+      <c r="B95" s="3" t="inlineStr">
+        <is>
+          <t>13:30:00</t>
+        </is>
+      </c>
+      <c r="C95" s="3" t="inlineStr">
+        <is>
+          <t>13:30</t>
+        </is>
+      </c>
+      <c r="D95" s="3" t="inlineStr">
+        <is>
+          <t>185.45</t>
+        </is>
+      </c>
+      <c r="E95" s="3" t="inlineStr"/>
+      <c r="F95" s="3" t="inlineStr">
+        <is>
+          <t>200.00</t>
+        </is>
+      </c>
+      <c r="G95" s="3" t="inlineStr"/>
+      <c r="H95" s="3" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="I95" s="3" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="J95" s="3" t="inlineStr"/>
+      <c r="K95" s="3" t="inlineStr"/>
+      <c r="L95" s="3" t="inlineStr"/>
+      <c r="M95" s="3" t="inlineStr"/>
+      <c r="N95" s="3" t="inlineStr"/>
+      <c r="O95" s="3" t="inlineStr"/>
+      <c r="P95" s="3" t="inlineStr">
+        <is>
+          <t>High Strike Check</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="3" t="inlineStr">
+        <is>
+          <t>2026-02-25 13:30:00</t>
+        </is>
+      </c>
+      <c r="B96" s="3" t="inlineStr">
+        <is>
+          <t>13:30:00</t>
+        </is>
+      </c>
+      <c r="C96" s="3" t="inlineStr">
+        <is>
+          <t>13:30</t>
+        </is>
+      </c>
+      <c r="D96" s="3" t="inlineStr">
+        <is>
+          <t>215.50</t>
+        </is>
+      </c>
+      <c r="E96" s="3" t="inlineStr"/>
+      <c r="F96" s="3" t="inlineStr">
+        <is>
+          <t>159.00</t>
+        </is>
+      </c>
+      <c r="G96" s="3" t="inlineStr"/>
+      <c r="H96" s="3" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="I96" s="3" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="J96" s="3" t="inlineStr"/>
+      <c r="K96" s="3" t="inlineStr"/>
+      <c r="L96" s="3" t="inlineStr"/>
+      <c r="M96" s="3" t="inlineStr"/>
+      <c r="N96" s="3" t="inlineStr"/>
+      <c r="O96" s="3" t="inlineStr"/>
+      <c r="P96" s="3" t="inlineStr">
+        <is>
+          <t>Low Strike Check</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="3" t="inlineStr">
+        <is>
+          <t>2026-02-25 13:35:00</t>
+        </is>
+      </c>
+      <c r="B97" s="3" t="inlineStr">
+        <is>
+          <t>13:35:00</t>
+        </is>
+      </c>
+      <c r="C97" s="3" t="inlineStr">
+        <is>
+          <t>13:35</t>
+        </is>
+      </c>
+      <c r="D97" s="3" t="inlineStr">
+        <is>
+          <t>185.45</t>
+        </is>
+      </c>
+      <c r="E97" s="3" t="inlineStr"/>
+      <c r="F97" s="3" t="inlineStr">
+        <is>
+          <t>200.00</t>
+        </is>
+      </c>
+      <c r="G97" s="3" t="inlineStr"/>
+      <c r="H97" s="3" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="I97" s="3" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="J97" s="3" t="inlineStr"/>
+      <c r="K97" s="3" t="inlineStr"/>
+      <c r="L97" s="3" t="inlineStr"/>
+      <c r="M97" s="3" t="inlineStr"/>
+      <c r="N97" s="3" t="inlineStr"/>
+      <c r="O97" s="3" t="inlineStr"/>
+      <c r="P97" s="3" t="inlineStr">
+        <is>
+          <t>High Strike Check</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="3" t="inlineStr">
+        <is>
+          <t>2026-02-25 13:35:00</t>
+        </is>
+      </c>
+      <c r="B98" s="3" t="inlineStr">
+        <is>
+          <t>13:35:00</t>
+        </is>
+      </c>
+      <c r="C98" s="3" t="inlineStr">
+        <is>
+          <t>13:35</t>
+        </is>
+      </c>
+      <c r="D98" s="3" t="inlineStr">
+        <is>
+          <t>215.50</t>
+        </is>
+      </c>
+      <c r="E98" s="3" t="inlineStr"/>
+      <c r="F98" s="3" t="inlineStr">
+        <is>
+          <t>159.00</t>
+        </is>
+      </c>
+      <c r="G98" s="3" t="inlineStr"/>
+      <c r="H98" s="3" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="I98" s="3" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="J98" s="3" t="inlineStr"/>
+      <c r="K98" s="3" t="inlineStr"/>
+      <c r="L98" s="3" t="inlineStr"/>
+      <c r="M98" s="3" t="inlineStr"/>
+      <c r="N98" s="3" t="inlineStr"/>
+      <c r="O98" s="3" t="inlineStr"/>
+      <c r="P98" s="3" t="inlineStr">
+        <is>
+          <t>Low Strike Check</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="3" t="inlineStr">
+        <is>
+          <t>2026-02-25 13:40:00</t>
+        </is>
+      </c>
+      <c r="B99" s="3" t="inlineStr">
+        <is>
+          <t>13:40:00</t>
+        </is>
+      </c>
+      <c r="C99" s="3" t="inlineStr">
+        <is>
+          <t>13:40</t>
+        </is>
+      </c>
+      <c r="D99" s="3" t="inlineStr">
+        <is>
+          <t>185.45</t>
+        </is>
+      </c>
+      <c r="E99" s="3" t="inlineStr"/>
+      <c r="F99" s="3" t="inlineStr">
+        <is>
+          <t>200.00</t>
+        </is>
+      </c>
+      <c r="G99" s="3" t="inlineStr"/>
+      <c r="H99" s="3" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="I99" s="3" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="J99" s="3" t="inlineStr"/>
+      <c r="K99" s="3" t="inlineStr"/>
+      <c r="L99" s="3" t="inlineStr"/>
+      <c r="M99" s="3" t="inlineStr"/>
+      <c r="N99" s="3" t="inlineStr"/>
+      <c r="O99" s="3" t="inlineStr"/>
+      <c r="P99" s="3" t="inlineStr">
+        <is>
+          <t>High Strike Check</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="3" t="inlineStr">
+        <is>
+          <t>2026-02-25 13:40:00</t>
+        </is>
+      </c>
+      <c r="B100" s="3" t="inlineStr">
+        <is>
+          <t>13:40:00</t>
+        </is>
+      </c>
+      <c r="C100" s="3" t="inlineStr">
+        <is>
+          <t>13:40</t>
+        </is>
+      </c>
+      <c r="D100" s="3" t="inlineStr">
+        <is>
+          <t>215.50</t>
+        </is>
+      </c>
+      <c r="E100" s="3" t="inlineStr"/>
+      <c r="F100" s="3" t="inlineStr">
+        <is>
+          <t>159.00</t>
+        </is>
+      </c>
+      <c r="G100" s="3" t="inlineStr"/>
+      <c r="H100" s="3" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="I100" s="3" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="J100" s="3" t="inlineStr"/>
+      <c r="K100" s="3" t="inlineStr"/>
+      <c r="L100" s="3" t="inlineStr"/>
+      <c r="M100" s="3" t="inlineStr"/>
+      <c r="N100" s="3" t="inlineStr"/>
+      <c r="O100" s="3" t="inlineStr"/>
+      <c r="P100" s="3" t="inlineStr">
+        <is>
+          <t>Low Strike Check</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="3" t="inlineStr">
+        <is>
+          <t>2026-02-25 13:45:00</t>
+        </is>
+      </c>
+      <c r="B101" s="3" t="inlineStr">
+        <is>
+          <t>13:45:00</t>
+        </is>
+      </c>
+      <c r="C101" s="3" t="inlineStr">
+        <is>
+          <t>13:45</t>
+        </is>
+      </c>
+      <c r="D101" s="3" t="inlineStr">
+        <is>
+          <t>185.45</t>
+        </is>
+      </c>
+      <c r="E101" s="3" t="inlineStr"/>
+      <c r="F101" s="3" t="inlineStr">
+        <is>
+          <t>200.00</t>
+        </is>
+      </c>
+      <c r="G101" s="3" t="inlineStr"/>
+      <c r="H101" s="3" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="I101" s="3" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="J101" s="3" t="inlineStr"/>
+      <c r="K101" s="3" t="inlineStr"/>
+      <c r="L101" s="3" t="inlineStr"/>
+      <c r="M101" s="3" t="inlineStr"/>
+      <c r="N101" s="3" t="inlineStr"/>
+      <c r="O101" s="3" t="inlineStr"/>
+      <c r="P101" s="3" t="inlineStr">
+        <is>
+          <t>High Strike Check</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="3" t="inlineStr">
+        <is>
+          <t>2026-02-25 13:45:00</t>
+        </is>
+      </c>
+      <c r="B102" s="3" t="inlineStr">
+        <is>
+          <t>13:45:00</t>
+        </is>
+      </c>
+      <c r="C102" s="3" t="inlineStr">
+        <is>
+          <t>13:45</t>
+        </is>
+      </c>
+      <c r="D102" s="3" t="inlineStr">
+        <is>
+          <t>215.50</t>
+        </is>
+      </c>
+      <c r="E102" s="3" t="inlineStr"/>
+      <c r="F102" s="3" t="inlineStr">
+        <is>
+          <t>159.00</t>
+        </is>
+      </c>
+      <c r="G102" s="3" t="inlineStr"/>
+      <c r="H102" s="3" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="I102" s="3" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="J102" s="3" t="inlineStr"/>
+      <c r="K102" s="3" t="inlineStr"/>
+      <c r="L102" s="3" t="inlineStr"/>
+      <c r="M102" s="3" t="inlineStr"/>
+      <c r="N102" s="3" t="inlineStr"/>
+      <c r="O102" s="3" t="inlineStr"/>
+      <c r="P102" s="3" t="inlineStr">
+        <is>
+          <t>Low Strike Check</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="3" t="inlineStr">
+        <is>
+          <t>2026-02-25 13:50:00</t>
+        </is>
+      </c>
+      <c r="B103" s="3" t="inlineStr">
+        <is>
+          <t>13:50:00</t>
+        </is>
+      </c>
+      <c r="C103" s="3" t="inlineStr">
+        <is>
+          <t>13:50</t>
+        </is>
+      </c>
+      <c r="D103" s="3" t="inlineStr">
+        <is>
+          <t>185.45</t>
+        </is>
+      </c>
+      <c r="E103" s="3" t="inlineStr"/>
+      <c r="F103" s="3" t="inlineStr">
+        <is>
+          <t>200.00</t>
+        </is>
+      </c>
+      <c r="G103" s="3" t="inlineStr"/>
+      <c r="H103" s="3" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="I103" s="3" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="J103" s="3" t="inlineStr"/>
+      <c r="K103" s="3" t="inlineStr"/>
+      <c r="L103" s="3" t="inlineStr"/>
+      <c r="M103" s="3" t="inlineStr"/>
+      <c r="N103" s="3" t="inlineStr"/>
+      <c r="O103" s="3" t="inlineStr"/>
+      <c r="P103" s="3" t="inlineStr">
+        <is>
+          <t>High Strike Check</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="3" t="inlineStr">
+        <is>
+          <t>2026-02-25 13:50:00</t>
+        </is>
+      </c>
+      <c r="B104" s="3" t="inlineStr">
+        <is>
+          <t>13:50:00</t>
+        </is>
+      </c>
+      <c r="C104" s="3" t="inlineStr">
+        <is>
+          <t>13:50</t>
+        </is>
+      </c>
+      <c r="D104" s="3" t="inlineStr">
+        <is>
+          <t>215.50</t>
+        </is>
+      </c>
+      <c r="E104" s="3" t="inlineStr"/>
+      <c r="F104" s="3" t="inlineStr">
+        <is>
+          <t>159.00</t>
+        </is>
+      </c>
+      <c r="G104" s="3" t="inlineStr"/>
+      <c r="H104" s="3" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="I104" s="3" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="J104" s="3" t="inlineStr"/>
+      <c r="K104" s="3" t="inlineStr"/>
+      <c r="L104" s="3" t="inlineStr"/>
+      <c r="M104" s="3" t="inlineStr"/>
+      <c r="N104" s="3" t="inlineStr"/>
+      <c r="O104" s="3" t="inlineStr"/>
+      <c r="P104" s="3" t="inlineStr">
+        <is>
+          <t>Low Strike Check</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="3" t="inlineStr">
+        <is>
+          <t>2026-02-25 13:55:00</t>
+        </is>
+      </c>
+      <c r="B105" s="3" t="inlineStr">
+        <is>
+          <t>13:55:00</t>
+        </is>
+      </c>
+      <c r="C105" s="3" t="inlineStr">
+        <is>
+          <t>13:55</t>
+        </is>
+      </c>
+      <c r="D105" s="3" t="inlineStr">
+        <is>
+          <t>185.45</t>
+        </is>
+      </c>
+      <c r="E105" s="3" t="inlineStr"/>
+      <c r="F105" s="3" t="inlineStr">
+        <is>
+          <t>200.00</t>
+        </is>
+      </c>
+      <c r="G105" s="3" t="inlineStr"/>
+      <c r="H105" s="3" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="I105" s="3" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="J105" s="3" t="inlineStr"/>
+      <c r="K105" s="3" t="inlineStr"/>
+      <c r="L105" s="3" t="inlineStr"/>
+      <c r="M105" s="3" t="inlineStr"/>
+      <c r="N105" s="3" t="inlineStr"/>
+      <c r="O105" s="3" t="inlineStr"/>
+      <c r="P105" s="3" t="inlineStr">
+        <is>
+          <t>High Strike Check</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" s="3" t="inlineStr">
+        <is>
+          <t>2026-02-25 13:55:00</t>
+        </is>
+      </c>
+      <c r="B106" s="3" t="inlineStr">
+        <is>
+          <t>13:55:00</t>
+        </is>
+      </c>
+      <c r="C106" s="3" t="inlineStr">
+        <is>
+          <t>13:55</t>
+        </is>
+      </c>
+      <c r="D106" s="3" t="inlineStr">
+        <is>
+          <t>215.50</t>
+        </is>
+      </c>
+      <c r="E106" s="3" t="inlineStr"/>
+      <c r="F106" s="3" t="inlineStr">
+        <is>
+          <t>159.00</t>
+        </is>
+      </c>
+      <c r="G106" s="3" t="inlineStr"/>
+      <c r="H106" s="3" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="I106" s="3" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="J106" s="3" t="inlineStr"/>
+      <c r="K106" s="3" t="inlineStr"/>
+      <c r="L106" s="3" t="inlineStr"/>
+      <c r="M106" s="3" t="inlineStr"/>
+      <c r="N106" s="3" t="inlineStr"/>
+      <c r="O106" s="3" t="inlineStr"/>
+      <c r="P106" s="3" t="inlineStr">
+        <is>
+          <t>Low Strike Check</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" s="3" t="inlineStr">
+        <is>
+          <t>2026-02-25 14:00:00</t>
+        </is>
+      </c>
+      <c r="B107" s="3" t="inlineStr">
+        <is>
+          <t>14:00:00</t>
+        </is>
+      </c>
+      <c r="C107" s="3" t="inlineStr">
+        <is>
+          <t>14:00</t>
+        </is>
+      </c>
+      <c r="D107" s="3" t="inlineStr">
+        <is>
+          <t>185.45</t>
+        </is>
+      </c>
+      <c r="E107" s="3" t="inlineStr"/>
+      <c r="F107" s="3" t="inlineStr">
+        <is>
+          <t>200.00</t>
+        </is>
+      </c>
+      <c r="G107" s="3" t="inlineStr"/>
+      <c r="H107" s="3" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="I107" s="3" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="J107" s="3" t="inlineStr"/>
+      <c r="K107" s="3" t="inlineStr"/>
+      <c r="L107" s="3" t="inlineStr"/>
+      <c r="M107" s="3" t="inlineStr"/>
+      <c r="N107" s="3" t="inlineStr"/>
+      <c r="O107" s="3" t="inlineStr"/>
+      <c r="P107" s="3" t="inlineStr">
+        <is>
+          <t>High Strike Check</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" s="3" t="inlineStr">
+        <is>
+          <t>2026-02-25 14:00:00</t>
+        </is>
+      </c>
+      <c r="B108" s="3" t="inlineStr">
+        <is>
+          <t>14:00:00</t>
+        </is>
+      </c>
+      <c r="C108" s="3" t="inlineStr">
+        <is>
+          <t>14:00</t>
+        </is>
+      </c>
+      <c r="D108" s="3" t="inlineStr">
+        <is>
+          <t>215.50</t>
+        </is>
+      </c>
+      <c r="E108" s="3" t="inlineStr"/>
+      <c r="F108" s="3" t="inlineStr">
+        <is>
+          <t>159.00</t>
+        </is>
+      </c>
+      <c r="G108" s="3" t="inlineStr"/>
+      <c r="H108" s="3" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="I108" s="3" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="J108" s="3" t="inlineStr"/>
+      <c r="K108" s="3" t="inlineStr"/>
+      <c r="L108" s="3" t="inlineStr"/>
+      <c r="M108" s="3" t="inlineStr"/>
+      <c r="N108" s="3" t="inlineStr"/>
+      <c r="O108" s="3" t="inlineStr"/>
+      <c r="P108" s="3" t="inlineStr">
+        <is>
+          <t>Low Strike Check</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" s="3" t="inlineStr">
+        <is>
+          <t>2026-02-25 14:05:00</t>
+        </is>
+      </c>
+      <c r="B109" s="3" t="inlineStr">
+        <is>
+          <t>14:05:00</t>
+        </is>
+      </c>
+      <c r="C109" s="3" t="inlineStr">
+        <is>
+          <t>14:05</t>
+        </is>
+      </c>
+      <c r="D109" s="3" t="inlineStr">
+        <is>
+          <t>185.45</t>
+        </is>
+      </c>
+      <c r="E109" s="3" t="inlineStr"/>
+      <c r="F109" s="3" t="inlineStr">
+        <is>
+          <t>200.00</t>
+        </is>
+      </c>
+      <c r="G109" s="3" t="inlineStr"/>
+      <c r="H109" s="3" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="I109" s="3" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="J109" s="3" t="inlineStr"/>
+      <c r="K109" s="3" t="inlineStr"/>
+      <c r="L109" s="3" t="inlineStr"/>
+      <c r="M109" s="3" t="inlineStr"/>
+      <c r="N109" s="3" t="inlineStr"/>
+      <c r="O109" s="3" t="inlineStr"/>
+      <c r="P109" s="3" t="inlineStr">
+        <is>
+          <t>High Strike Check</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" s="3" t="inlineStr">
+        <is>
+          <t>2026-02-25 14:05:00</t>
+        </is>
+      </c>
+      <c r="B110" s="3" t="inlineStr">
+        <is>
+          <t>14:05:00</t>
+        </is>
+      </c>
+      <c r="C110" s="3" t="inlineStr">
+        <is>
+          <t>14:05</t>
+        </is>
+      </c>
+      <c r="D110" s="3" t="inlineStr">
+        <is>
+          <t>215.50</t>
+        </is>
+      </c>
+      <c r="E110" s="3" t="inlineStr"/>
+      <c r="F110" s="3" t="inlineStr">
+        <is>
+          <t>159.00</t>
+        </is>
+      </c>
+      <c r="G110" s="3" t="inlineStr"/>
+      <c r="H110" s="3" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="I110" s="3" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="J110" s="3" t="inlineStr"/>
+      <c r="K110" s="3" t="inlineStr"/>
+      <c r="L110" s="3" t="inlineStr"/>
+      <c r="M110" s="3" t="inlineStr"/>
+      <c r="N110" s="3" t="inlineStr"/>
+      <c r="O110" s="3" t="inlineStr"/>
+      <c r="P110" s="3" t="inlineStr">
+        <is>
+          <t>Low Strike Check</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" s="3" t="inlineStr">
+        <is>
+          <t>2026-02-25 14:10:00</t>
+        </is>
+      </c>
+      <c r="B111" s="3" t="inlineStr">
+        <is>
+          <t>14:10:00</t>
+        </is>
+      </c>
+      <c r="C111" s="3" t="inlineStr">
+        <is>
+          <t>14:10</t>
+        </is>
+      </c>
+      <c r="D111" s="3" t="inlineStr">
+        <is>
+          <t>185.45</t>
+        </is>
+      </c>
+      <c r="E111" s="3" t="inlineStr"/>
+      <c r="F111" s="3" t="inlineStr">
+        <is>
+          <t>200.00</t>
+        </is>
+      </c>
+      <c r="G111" s="3" t="inlineStr"/>
+      <c r="H111" s="3" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="I111" s="3" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="J111" s="3" t="inlineStr"/>
+      <c r="K111" s="3" t="inlineStr"/>
+      <c r="L111" s="3" t="inlineStr"/>
+      <c r="M111" s="3" t="inlineStr"/>
+      <c r="N111" s="3" t="inlineStr"/>
+      <c r="O111" s="3" t="inlineStr"/>
+      <c r="P111" s="3" t="inlineStr">
+        <is>
+          <t>High Strike Check</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" s="3" t="inlineStr">
+        <is>
+          <t>2026-02-25 14:10:00</t>
+        </is>
+      </c>
+      <c r="B112" s="3" t="inlineStr">
+        <is>
+          <t>14:10:00</t>
+        </is>
+      </c>
+      <c r="C112" s="3" t="inlineStr">
+        <is>
+          <t>14:10</t>
+        </is>
+      </c>
+      <c r="D112" s="3" t="inlineStr">
+        <is>
+          <t>215.50</t>
+        </is>
+      </c>
+      <c r="E112" s="3" t="inlineStr"/>
+      <c r="F112" s="3" t="inlineStr">
+        <is>
+          <t>159.00</t>
+        </is>
+      </c>
+      <c r="G112" s="3" t="inlineStr"/>
+      <c r="H112" s="3" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="I112" s="3" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="J112" s="3" t="inlineStr"/>
+      <c r="K112" s="3" t="inlineStr"/>
+      <c r="L112" s="3" t="inlineStr"/>
+      <c r="M112" s="3" t="inlineStr"/>
+      <c r="N112" s="3" t="inlineStr"/>
+      <c r="O112" s="3" t="inlineStr"/>
+      <c r="P112" s="3" t="inlineStr">
+        <is>
+          <t>Low Strike Check</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" s="3" t="inlineStr">
+        <is>
+          <t>2026-02-25 14:15:00</t>
+        </is>
+      </c>
+      <c r="B113" s="3" t="inlineStr">
+        <is>
+          <t>14:15:00</t>
+        </is>
+      </c>
+      <c r="C113" s="3" t="inlineStr">
+        <is>
+          <t>14:15</t>
+        </is>
+      </c>
+      <c r="D113" s="3" t="inlineStr">
+        <is>
+          <t>185.45</t>
+        </is>
+      </c>
+      <c r="E113" s="3" t="inlineStr"/>
+      <c r="F113" s="3" t="inlineStr">
+        <is>
+          <t>200.00</t>
+        </is>
+      </c>
+      <c r="G113" s="3" t="inlineStr"/>
+      <c r="H113" s="3" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="I113" s="3" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="J113" s="3" t="inlineStr"/>
+      <c r="K113" s="3" t="inlineStr"/>
+      <c r="L113" s="3" t="inlineStr"/>
+      <c r="M113" s="3" t="inlineStr"/>
+      <c r="N113" s="3" t="inlineStr"/>
+      <c r="O113" s="3" t="inlineStr"/>
+      <c r="P113" s="3" t="inlineStr">
+        <is>
+          <t>High Strike Check</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" s="3" t="inlineStr">
+        <is>
+          <t>2026-02-25 14:15:00</t>
+        </is>
+      </c>
+      <c r="B114" s="3" t="inlineStr">
+        <is>
+          <t>14:15:00</t>
+        </is>
+      </c>
+      <c r="C114" s="3" t="inlineStr">
+        <is>
+          <t>14:15</t>
+        </is>
+      </c>
+      <c r="D114" s="3" t="inlineStr">
+        <is>
+          <t>215.50</t>
+        </is>
+      </c>
+      <c r="E114" s="3" t="inlineStr"/>
+      <c r="F114" s="3" t="inlineStr">
+        <is>
+          <t>159.00</t>
+        </is>
+      </c>
+      <c r="G114" s="3" t="inlineStr"/>
+      <c r="H114" s="3" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="I114" s="3" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="J114" s="3" t="inlineStr"/>
+      <c r="K114" s="3" t="inlineStr"/>
+      <c r="L114" s="3" t="inlineStr"/>
+      <c r="M114" s="3" t="inlineStr"/>
+      <c r="N114" s="3" t="inlineStr"/>
+      <c r="O114" s="3" t="inlineStr"/>
+      <c r="P114" s="3" t="inlineStr">
+        <is>
+          <t>Low Strike Check</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" s="3" t="inlineStr">
+        <is>
+          <t>2026-02-25 14:20:00</t>
+        </is>
+      </c>
+      <c r="B115" s="3" t="inlineStr">
+        <is>
+          <t>14:20:00</t>
+        </is>
+      </c>
+      <c r="C115" s="3" t="inlineStr">
+        <is>
+          <t>14:20</t>
+        </is>
+      </c>
+      <c r="D115" s="3" t="inlineStr">
+        <is>
+          <t>185.45</t>
+        </is>
+      </c>
+      <c r="E115" s="3" t="inlineStr"/>
+      <c r="F115" s="3" t="inlineStr">
+        <is>
+          <t>200.00</t>
+        </is>
+      </c>
+      <c r="G115" s="3" t="inlineStr"/>
+      <c r="H115" s="3" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="I115" s="3" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="J115" s="3" t="inlineStr"/>
+      <c r="K115" s="3" t="inlineStr"/>
+      <c r="L115" s="3" t="inlineStr"/>
+      <c r="M115" s="3" t="inlineStr"/>
+      <c r="N115" s="3" t="inlineStr"/>
+      <c r="O115" s="3" t="inlineStr"/>
+      <c r="P115" s="3" t="inlineStr">
+        <is>
+          <t>High Strike Check</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" s="3" t="inlineStr">
+        <is>
+          <t>2026-02-25 14:20:00</t>
+        </is>
+      </c>
+      <c r="B116" s="3" t="inlineStr">
+        <is>
+          <t>14:20:00</t>
+        </is>
+      </c>
+      <c r="C116" s="3" t="inlineStr">
+        <is>
+          <t>14:20</t>
+        </is>
+      </c>
+      <c r="D116" s="3" t="inlineStr">
+        <is>
+          <t>215.50</t>
+        </is>
+      </c>
+      <c r="E116" s="3" t="inlineStr"/>
+      <c r="F116" s="3" t="inlineStr">
+        <is>
+          <t>159.00</t>
+        </is>
+      </c>
+      <c r="G116" s="3" t="inlineStr"/>
+      <c r="H116" s="3" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="I116" s="3" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="J116" s="3" t="inlineStr"/>
+      <c r="K116" s="3" t="inlineStr"/>
+      <c r="L116" s="3" t="inlineStr"/>
+      <c r="M116" s="3" t="inlineStr"/>
+      <c r="N116" s="3" t="inlineStr"/>
+      <c r="O116" s="3" t="inlineStr"/>
+      <c r="P116" s="3" t="inlineStr">
+        <is>
+          <t>Low Strike Check</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="3" t="inlineStr">
+        <is>
+          <t>2026-02-25 14:25:00</t>
+        </is>
+      </c>
+      <c r="B117" s="3" t="inlineStr">
+        <is>
+          <t>14:25:00</t>
+        </is>
+      </c>
+      <c r="C117" s="3" t="inlineStr">
+        <is>
+          <t>14:25</t>
+        </is>
+      </c>
+      <c r="D117" s="3" t="inlineStr">
+        <is>
+          <t>185.45</t>
+        </is>
+      </c>
+      <c r="E117" s="3" t="inlineStr"/>
+      <c r="F117" s="3" t="inlineStr">
+        <is>
+          <t>200.00</t>
+        </is>
+      </c>
+      <c r="G117" s="3" t="inlineStr"/>
+      <c r="H117" s="3" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="I117" s="3" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="J117" s="3" t="inlineStr"/>
+      <c r="K117" s="3" t="inlineStr"/>
+      <c r="L117" s="3" t="inlineStr"/>
+      <c r="M117" s="3" t="inlineStr"/>
+      <c r="N117" s="3" t="inlineStr"/>
+      <c r="O117" s="3" t="inlineStr"/>
+      <c r="P117" s="3" t="inlineStr">
+        <is>
+          <t>High Strike Check</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="3" t="inlineStr">
+        <is>
+          <t>2026-02-25 14:25:00</t>
+        </is>
+      </c>
+      <c r="B118" s="3" t="inlineStr">
+        <is>
+          <t>14:25:00</t>
+        </is>
+      </c>
+      <c r="C118" s="3" t="inlineStr">
+        <is>
+          <t>14:25</t>
+        </is>
+      </c>
+      <c r="D118" s="3" t="inlineStr">
+        <is>
+          <t>215.50</t>
+        </is>
+      </c>
+      <c r="E118" s="3" t="inlineStr"/>
+      <c r="F118" s="3" t="inlineStr">
+        <is>
+          <t>159.00</t>
+        </is>
+      </c>
+      <c r="G118" s="3" t="inlineStr"/>
+      <c r="H118" s="3" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="I118" s="3" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="J118" s="3" t="inlineStr"/>
+      <c r="K118" s="3" t="inlineStr"/>
+      <c r="L118" s="3" t="inlineStr"/>
+      <c r="M118" s="3" t="inlineStr"/>
+      <c r="N118" s="3" t="inlineStr"/>
+      <c r="O118" s="3" t="inlineStr"/>
+      <c r="P118" s="3" t="inlineStr">
+        <is>
+          <t>Low Strike Check</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="3" t="inlineStr">
+        <is>
+          <t>2026-02-25 14:30:00</t>
+        </is>
+      </c>
+      <c r="B119" s="3" t="inlineStr">
+        <is>
+          <t>14:30:00</t>
+        </is>
+      </c>
+      <c r="C119" s="3" t="inlineStr">
+        <is>
+          <t>14:30</t>
+        </is>
+      </c>
+      <c r="D119" s="3" t="inlineStr">
+        <is>
+          <t>185.45</t>
+        </is>
+      </c>
+      <c r="E119" s="3" t="inlineStr"/>
+      <c r="F119" s="3" t="inlineStr">
+        <is>
+          <t>200.00</t>
+        </is>
+      </c>
+      <c r="G119" s="3" t="inlineStr"/>
+      <c r="H119" s="3" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="I119" s="3" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="J119" s="3" t="inlineStr"/>
+      <c r="K119" s="3" t="inlineStr"/>
+      <c r="L119" s="3" t="inlineStr"/>
+      <c r="M119" s="3" t="inlineStr"/>
+      <c r="N119" s="3" t="inlineStr"/>
+      <c r="O119" s="3" t="inlineStr"/>
+      <c r="P119" s="3" t="inlineStr">
+        <is>
+          <t>High Strike Check</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="3" t="inlineStr">
+        <is>
+          <t>2026-02-25 14:30:00</t>
+        </is>
+      </c>
+      <c r="B120" s="3" t="inlineStr">
+        <is>
+          <t>14:30:00</t>
+        </is>
+      </c>
+      <c r="C120" s="3" t="inlineStr">
+        <is>
+          <t>14:30</t>
+        </is>
+      </c>
+      <c r="D120" s="3" t="inlineStr">
+        <is>
+          <t>215.50</t>
+        </is>
+      </c>
+      <c r="E120" s="3" t="inlineStr"/>
+      <c r="F120" s="3" t="inlineStr">
+        <is>
+          <t>159.00</t>
+        </is>
+      </c>
+      <c r="G120" s="3" t="inlineStr"/>
+      <c r="H120" s="3" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="I120" s="3" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="J120" s="3" t="inlineStr"/>
+      <c r="K120" s="3" t="inlineStr"/>
+      <c r="L120" s="3" t="inlineStr"/>
+      <c r="M120" s="3" t="inlineStr"/>
+      <c r="N120" s="3" t="inlineStr"/>
+      <c r="O120" s="3" t="inlineStr"/>
+      <c r="P120" s="3" t="inlineStr">
+        <is>
+          <t>Low Strike Check</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="3" t="inlineStr">
+        <is>
+          <t>2026-02-25 14:35:00</t>
+        </is>
+      </c>
+      <c r="B121" s="3" t="inlineStr">
+        <is>
+          <t>14:35:00</t>
+        </is>
+      </c>
+      <c r="C121" s="3" t="inlineStr">
+        <is>
+          <t>14:35</t>
+        </is>
+      </c>
+      <c r="D121" s="3" t="inlineStr">
+        <is>
+          <t>185.45</t>
+        </is>
+      </c>
+      <c r="E121" s="3" t="inlineStr"/>
+      <c r="F121" s="3" t="inlineStr">
+        <is>
+          <t>200.00</t>
+        </is>
+      </c>
+      <c r="G121" s="3" t="inlineStr"/>
+      <c r="H121" s="3" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="I121" s="3" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="J121" s="3" t="inlineStr"/>
+      <c r="K121" s="3" t="inlineStr"/>
+      <c r="L121" s="3" t="inlineStr"/>
+      <c r="M121" s="3" t="inlineStr"/>
+      <c r="N121" s="3" t="inlineStr"/>
+      <c r="O121" s="3" t="inlineStr"/>
+      <c r="P121" s="3" t="inlineStr">
+        <is>
+          <t>High Strike Check</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="3" t="inlineStr">
+        <is>
+          <t>2026-02-25 14:35:00</t>
+        </is>
+      </c>
+      <c r="B122" s="3" t="inlineStr">
+        <is>
+          <t>14:35:00</t>
+        </is>
+      </c>
+      <c r="C122" s="3" t="inlineStr">
+        <is>
+          <t>14:35</t>
+        </is>
+      </c>
+      <c r="D122" s="3" t="inlineStr">
+        <is>
+          <t>215.50</t>
+        </is>
+      </c>
+      <c r="E122" s="3" t="inlineStr"/>
+      <c r="F122" s="3" t="inlineStr">
+        <is>
+          <t>159.00</t>
+        </is>
+      </c>
+      <c r="G122" s="3" t="inlineStr"/>
+      <c r="H122" s="3" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="I122" s="3" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="J122" s="3" t="inlineStr"/>
+      <c r="K122" s="3" t="inlineStr"/>
+      <c r="L122" s="3" t="inlineStr"/>
+      <c r="M122" s="3" t="inlineStr"/>
+      <c r="N122" s="3" t="inlineStr"/>
+      <c r="O122" s="3" t="inlineStr"/>
+      <c r="P122" s="3" t="inlineStr">
+        <is>
+          <t>Low Strike Check</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="3" t="inlineStr">
+        <is>
+          <t>2026-02-25 14:40:00</t>
+        </is>
+      </c>
+      <c r="B123" s="3" t="inlineStr">
+        <is>
+          <t>14:40:00</t>
+        </is>
+      </c>
+      <c r="C123" s="3" t="inlineStr">
+        <is>
+          <t>14:40</t>
+        </is>
+      </c>
+      <c r="D123" s="3" t="inlineStr">
+        <is>
+          <t>185.45</t>
+        </is>
+      </c>
+      <c r="E123" s="3" t="inlineStr"/>
+      <c r="F123" s="3" t="inlineStr">
+        <is>
+          <t>200.00</t>
+        </is>
+      </c>
+      <c r="G123" s="3" t="inlineStr"/>
+      <c r="H123" s="3" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="I123" s="3" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="J123" s="3" t="inlineStr"/>
+      <c r="K123" s="3" t="inlineStr"/>
+      <c r="L123" s="3" t="inlineStr"/>
+      <c r="M123" s="3" t="inlineStr"/>
+      <c r="N123" s="3" t="inlineStr"/>
+      <c r="O123" s="3" t="inlineStr"/>
+      <c r="P123" s="3" t="inlineStr">
+        <is>
+          <t>High Strike Check</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="3" t="inlineStr">
+        <is>
+          <t>2026-02-25 14:40:00</t>
+        </is>
+      </c>
+      <c r="B124" s="3" t="inlineStr">
+        <is>
+          <t>14:40:00</t>
+        </is>
+      </c>
+      <c r="C124" s="3" t="inlineStr">
+        <is>
+          <t>14:40</t>
+        </is>
+      </c>
+      <c r="D124" s="3" t="inlineStr">
+        <is>
+          <t>215.50</t>
+        </is>
+      </c>
+      <c r="E124" s="3" t="inlineStr"/>
+      <c r="F124" s="3" t="inlineStr">
+        <is>
+          <t>159.00</t>
+        </is>
+      </c>
+      <c r="G124" s="3" t="inlineStr"/>
+      <c r="H124" s="3" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="I124" s="3" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="J124" s="3" t="inlineStr"/>
+      <c r="K124" s="3" t="inlineStr"/>
+      <c r="L124" s="3" t="inlineStr"/>
+      <c r="M124" s="3" t="inlineStr"/>
+      <c r="N124" s="3" t="inlineStr"/>
+      <c r="O124" s="3" t="inlineStr"/>
+      <c r="P124" s="3" t="inlineStr">
+        <is>
+          <t>Low Strike Check</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="3" t="inlineStr">
+        <is>
+          <t>2026-02-25 14:45:00</t>
+        </is>
+      </c>
+      <c r="B125" s="3" t="inlineStr">
+        <is>
+          <t>14:45:00</t>
+        </is>
+      </c>
+      <c r="C125" s="3" t="inlineStr">
+        <is>
+          <t>14:45</t>
+        </is>
+      </c>
+      <c r="D125" s="3" t="inlineStr">
+        <is>
+          <t>185.45</t>
+        </is>
+      </c>
+      <c r="E125" s="3" t="inlineStr"/>
+      <c r="F125" s="3" t="inlineStr">
+        <is>
+          <t>200.00</t>
+        </is>
+      </c>
+      <c r="G125" s="3" t="inlineStr"/>
+      <c r="H125" s="3" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="I125" s="3" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="J125" s="3" t="inlineStr"/>
+      <c r="K125" s="3" t="inlineStr"/>
+      <c r="L125" s="3" t="inlineStr"/>
+      <c r="M125" s="3" t="inlineStr"/>
+      <c r="N125" s="3" t="inlineStr"/>
+      <c r="O125" s="3" t="inlineStr"/>
+      <c r="P125" s="3" t="inlineStr">
+        <is>
+          <t>High Strike Check</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="3" t="inlineStr">
+        <is>
+          <t>2026-02-25 14:45:00</t>
+        </is>
+      </c>
+      <c r="B126" s="3" t="inlineStr">
+        <is>
+          <t>14:45:00</t>
+        </is>
+      </c>
+      <c r="C126" s="3" t="inlineStr">
+        <is>
+          <t>14:45</t>
+        </is>
+      </c>
+      <c r="D126" s="3" t="inlineStr">
+        <is>
+          <t>215.50</t>
+        </is>
+      </c>
+      <c r="E126" s="3" t="inlineStr"/>
+      <c r="F126" s="3" t="inlineStr">
+        <is>
+          <t>159.00</t>
+        </is>
+      </c>
+      <c r="G126" s="3" t="inlineStr"/>
+      <c r="H126" s="3" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="I126" s="3" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="J126" s="3" t="inlineStr"/>
+      <c r="K126" s="3" t="inlineStr"/>
+      <c r="L126" s="3" t="inlineStr"/>
+      <c r="M126" s="3" t="inlineStr"/>
+      <c r="N126" s="3" t="inlineStr"/>
+      <c r="O126" s="3" t="inlineStr"/>
+      <c r="P126" s="3" t="inlineStr">
+        <is>
+          <t>Low Strike Check</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="3" t="inlineStr">
+        <is>
+          <t>2026-02-25 14:50:00</t>
+        </is>
+      </c>
+      <c r="B127" s="3" t="inlineStr">
+        <is>
+          <t>14:50:00</t>
+        </is>
+      </c>
+      <c r="C127" s="3" t="inlineStr">
+        <is>
+          <t>14:50</t>
+        </is>
+      </c>
+      <c r="D127" s="3" t="inlineStr">
+        <is>
+          <t>185.45</t>
+        </is>
+      </c>
+      <c r="E127" s="3" t="inlineStr"/>
+      <c r="F127" s="3" t="inlineStr">
+        <is>
+          <t>200.00</t>
+        </is>
+      </c>
+      <c r="G127" s="3" t="inlineStr"/>
+      <c r="H127" s="3" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="I127" s="3" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="J127" s="3" t="inlineStr"/>
+      <c r="K127" s="3" t="inlineStr"/>
+      <c r="L127" s="3" t="inlineStr"/>
+      <c r="M127" s="3" t="inlineStr"/>
+      <c r="N127" s="3" t="inlineStr"/>
+      <c r="O127" s="3" t="inlineStr"/>
+      <c r="P127" s="3" t="inlineStr">
+        <is>
+          <t>High Strike Check</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="3" t="inlineStr">
+        <is>
+          <t>2026-02-25 14:50:00</t>
+        </is>
+      </c>
+      <c r="B128" s="3" t="inlineStr">
+        <is>
+          <t>14:50:00</t>
+        </is>
+      </c>
+      <c r="C128" s="3" t="inlineStr">
+        <is>
+          <t>14:50</t>
+        </is>
+      </c>
+      <c r="D128" s="3" t="inlineStr">
+        <is>
+          <t>215.50</t>
+        </is>
+      </c>
+      <c r="E128" s="3" t="inlineStr"/>
+      <c r="F128" s="3" t="inlineStr">
+        <is>
+          <t>159.00</t>
+        </is>
+      </c>
+      <c r="G128" s="3" t="inlineStr"/>
+      <c r="H128" s="3" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="I128" s="3" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="J128" s="3" t="inlineStr"/>
+      <c r="K128" s="3" t="inlineStr"/>
+      <c r="L128" s="3" t="inlineStr"/>
+      <c r="M128" s="3" t="inlineStr"/>
+      <c r="N128" s="3" t="inlineStr"/>
+      <c r="O128" s="3" t="inlineStr"/>
+      <c r="P128" s="3" t="inlineStr">
+        <is>
+          <t>Low Strike Check</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="3" t="inlineStr">
+        <is>
+          <t>2026-02-25 14:55:00</t>
+        </is>
+      </c>
+      <c r="B129" s="3" t="inlineStr">
+        <is>
+          <t>14:55:00</t>
+        </is>
+      </c>
+      <c r="C129" s="3" t="inlineStr">
+        <is>
+          <t>14:55</t>
+        </is>
+      </c>
+      <c r="D129" s="3" t="inlineStr">
+        <is>
+          <t>185.45</t>
+        </is>
+      </c>
+      <c r="E129" s="3" t="inlineStr"/>
+      <c r="F129" s="3" t="inlineStr">
+        <is>
+          <t>200.00</t>
+        </is>
+      </c>
+      <c r="G129" s="3" t="inlineStr"/>
+      <c r="H129" s="3" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="I129" s="3" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="J129" s="3" t="inlineStr"/>
+      <c r="K129" s="3" t="inlineStr"/>
+      <c r="L129" s="3" t="inlineStr"/>
+      <c r="M129" s="3" t="inlineStr"/>
+      <c r="N129" s="3" t="inlineStr"/>
+      <c r="O129" s="3" t="inlineStr"/>
+      <c r="P129" s="3" t="inlineStr">
+        <is>
+          <t>High Strike Check</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" s="3" t="inlineStr">
+        <is>
+          <t>2026-02-25 14:55:00</t>
+        </is>
+      </c>
+      <c r="B130" s="3" t="inlineStr">
+        <is>
+          <t>14:55:00</t>
+        </is>
+      </c>
+      <c r="C130" s="3" t="inlineStr">
+        <is>
+          <t>14:55</t>
+        </is>
+      </c>
+      <c r="D130" s="3" t="inlineStr">
+        <is>
+          <t>215.50</t>
+        </is>
+      </c>
+      <c r="E130" s="3" t="inlineStr"/>
+      <c r="F130" s="3" t="inlineStr">
+        <is>
+          <t>159.00</t>
+        </is>
+      </c>
+      <c r="G130" s="3" t="inlineStr"/>
+      <c r="H130" s="3" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="I130" s="3" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="J130" s="3" t="inlineStr"/>
+      <c r="K130" s="3" t="inlineStr"/>
+      <c r="L130" s="3" t="inlineStr"/>
+      <c r="M130" s="3" t="inlineStr"/>
+      <c r="N130" s="3" t="inlineStr"/>
+      <c r="O130" s="3" t="inlineStr"/>
+      <c r="P130" s="3" t="inlineStr">
+        <is>
+          <t>Low Strike Check</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" s="3" t="inlineStr">
+        <is>
+          <t>2026-02-25 15:00:00</t>
+        </is>
+      </c>
+      <c r="B131" s="3" t="inlineStr">
+        <is>
+          <t>15:00:00</t>
+        </is>
+      </c>
+      <c r="C131" s="3" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="D131" s="3" t="inlineStr">
+        <is>
+          <t>185.45</t>
+        </is>
+      </c>
+      <c r="E131" s="3" t="inlineStr"/>
+      <c r="F131" s="3" t="inlineStr">
+        <is>
+          <t>200.00</t>
+        </is>
+      </c>
+      <c r="G131" s="3" t="inlineStr"/>
+      <c r="H131" s="3" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="I131" s="3" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="J131" s="3" t="inlineStr"/>
+      <c r="K131" s="3" t="inlineStr"/>
+      <c r="L131" s="3" t="inlineStr"/>
+      <c r="M131" s="3" t="inlineStr"/>
+      <c r="N131" s="3" t="inlineStr"/>
+      <c r="O131" s="3" t="inlineStr"/>
+      <c r="P131" s="3" t="inlineStr">
+        <is>
+          <t>High Strike Check</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" s="3" t="inlineStr">
+        <is>
+          <t>2026-02-25 15:00:00</t>
+        </is>
+      </c>
+      <c r="B132" s="3" t="inlineStr">
+        <is>
+          <t>15:00:00</t>
+        </is>
+      </c>
+      <c r="C132" s="3" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="D132" s="3" t="inlineStr">
+        <is>
+          <t>215.50</t>
+        </is>
+      </c>
+      <c r="E132" s="3" t="inlineStr"/>
+      <c r="F132" s="3" t="inlineStr">
+        <is>
+          <t>159.00</t>
+        </is>
+      </c>
+      <c r="G132" s="3" t="inlineStr"/>
+      <c r="H132" s="3" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="I132" s="3" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="J132" s="3" t="inlineStr"/>
+      <c r="K132" s="3" t="inlineStr"/>
+      <c r="L132" s="3" t="inlineStr"/>
+      <c r="M132" s="3" t="inlineStr"/>
+      <c r="N132" s="3" t="inlineStr"/>
+      <c r="O132" s="3" t="inlineStr"/>
+      <c r="P132" s="3" t="inlineStr">
+        <is>
+          <t>Low Strike Check</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" s="3" t="inlineStr">
+        <is>
+          <t>2026-02-25 15:05:00</t>
+        </is>
+      </c>
+      <c r="B133" s="3" t="inlineStr">
+        <is>
+          <t>15:05:00</t>
+        </is>
+      </c>
+      <c r="C133" s="3" t="inlineStr">
+        <is>
+          <t>15:05</t>
+        </is>
+      </c>
+      <c r="D133" s="3" t="inlineStr">
+        <is>
+          <t>185.45</t>
+        </is>
+      </c>
+      <c r="E133" s="3" t="inlineStr"/>
+      <c r="F133" s="3" t="inlineStr">
+        <is>
+          <t>200.00</t>
+        </is>
+      </c>
+      <c r="G133" s="3" t="inlineStr"/>
+      <c r="H133" s="3" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="I133" s="3" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="J133" s="3" t="inlineStr"/>
+      <c r="K133" s="3" t="inlineStr"/>
+      <c r="L133" s="3" t="inlineStr"/>
+      <c r="M133" s="3" t="inlineStr"/>
+      <c r="N133" s="3" t="inlineStr"/>
+      <c r="O133" s="3" t="inlineStr"/>
+      <c r="P133" s="3" t="inlineStr">
+        <is>
+          <t>High Strike Check</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" s="3" t="inlineStr">
+        <is>
+          <t>2026-02-25 15:05:00</t>
+        </is>
+      </c>
+      <c r="B134" s="3" t="inlineStr">
+        <is>
+          <t>15:05:00</t>
+        </is>
+      </c>
+      <c r="C134" s="3" t="inlineStr">
+        <is>
+          <t>15:05</t>
+        </is>
+      </c>
+      <c r="D134" s="3" t="inlineStr">
+        <is>
+          <t>215.50</t>
+        </is>
+      </c>
+      <c r="E134" s="3" t="inlineStr"/>
+      <c r="F134" s="3" t="inlineStr">
+        <is>
+          <t>159.00</t>
+        </is>
+      </c>
+      <c r="G134" s="3" t="inlineStr"/>
+      <c r="H134" s="3" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="I134" s="3" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="J134" s="3" t="inlineStr"/>
+      <c r="K134" s="3" t="inlineStr"/>
+      <c r="L134" s="3" t="inlineStr"/>
+      <c r="M134" s="3" t="inlineStr"/>
+      <c r="N134" s="3" t="inlineStr"/>
+      <c r="O134" s="3" t="inlineStr"/>
+      <c r="P134" s="3" t="inlineStr">
+        <is>
+          <t>Low Strike Check</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" s="3" t="inlineStr">
+        <is>
+          <t>2026-02-25 15:10:00</t>
+        </is>
+      </c>
+      <c r="B135" s="3" t="inlineStr">
+        <is>
+          <t>15:10:00</t>
+        </is>
+      </c>
+      <c r="C135" s="3" t="inlineStr">
+        <is>
+          <t>15:10</t>
+        </is>
+      </c>
+      <c r="D135" s="3" t="inlineStr"/>
+      <c r="E135" s="3" t="inlineStr"/>
+      <c r="F135" s="3" t="inlineStr"/>
+      <c r="G135" s="3" t="inlineStr"/>
+      <c r="H135" s="3" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="I135" s="3" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="J135" s="3" t="inlineStr"/>
+      <c r="K135" s="3" t="inlineStr"/>
+      <c r="L135" s="3" t="inlineStr"/>
+      <c r="M135" s="3" t="inlineStr"/>
+      <c r="N135" s="3" t="inlineStr"/>
+      <c r="O135" s="3" t="inlineStr"/>
+      <c r="P135" s="3" t="inlineStr">
+        <is>
+          <t>Data fetch failed: Live data fetch timed out after 45s - candle fetching took too long, retrying next cycle</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" s="3" t="inlineStr">
+        <is>
+          <t>2026-02-25 15:10:00</t>
+        </is>
+      </c>
+      <c r="B136" s="3" t="inlineStr">
+        <is>
+          <t>15:10:00</t>
+        </is>
+      </c>
+      <c r="C136" s="3" t="inlineStr">
+        <is>
+          <t>15:10</t>
+        </is>
+      </c>
+      <c r="D136" s="3" t="inlineStr"/>
+      <c r="E136" s="3" t="inlineStr"/>
+      <c r="F136" s="3" t="inlineStr"/>
+      <c r="G136" s="3" t="inlineStr"/>
+      <c r="H136" s="3" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="I136" s="3" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="J136" s="3" t="inlineStr"/>
+      <c r="K136" s="3" t="inlineStr"/>
+      <c r="L136" s="3" t="inlineStr"/>
+      <c r="M136" s="3" t="inlineStr"/>
+      <c r="N136" s="3" t="inlineStr"/>
+      <c r="O136" s="3" t="inlineStr"/>
+      <c r="P136" s="3" t="inlineStr">
+        <is>
+          <t>Failed to fetch data: Live data fetch timed out after 45s - candle fetching took too long, retrying next cycle</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Mine/logs/mine_signal_logs.xlsx
+++ b/Mine/logs/mine_signal_logs.xlsx
@@ -518,7 +518,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P193"/>
+  <dimension ref="A1:P201"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -9888,6 +9888,342 @@
       <c r="N193" s="4" t="inlineStr"/>
       <c r="O193" s="4" t="inlineStr"/>
       <c r="P193" s="4" t="inlineStr">
+        <is>
+          <t>Failed to fetch data: Failed to fetch quote data after all retries</t>
+        </is>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" s="4" t="inlineStr">
+        <is>
+          <t>2026-03-03 11:25:00</t>
+        </is>
+      </c>
+      <c r="B194" s="4" t="inlineStr">
+        <is>
+          <t>11:25:00</t>
+        </is>
+      </c>
+      <c r="C194" s="4" t="inlineStr">
+        <is>
+          <t>11:25</t>
+        </is>
+      </c>
+      <c r="D194" s="4" t="inlineStr"/>
+      <c r="E194" s="4" t="inlineStr"/>
+      <c r="F194" s="4" t="inlineStr"/>
+      <c r="G194" s="4" t="inlineStr"/>
+      <c r="H194" s="4" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="I194" s="4" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="J194" s="4" t="inlineStr"/>
+      <c r="K194" s="4" t="inlineStr"/>
+      <c r="L194" s="4" t="inlineStr"/>
+      <c r="M194" s="4" t="inlineStr"/>
+      <c r="N194" s="4" t="inlineStr"/>
+      <c r="O194" s="4" t="inlineStr"/>
+      <c r="P194" s="4" t="inlineStr">
+        <is>
+          <t>Data fetch failed: Failed to fetch quote data after all retries</t>
+        </is>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" s="4" t="inlineStr">
+        <is>
+          <t>2026-03-03 11:25:00</t>
+        </is>
+      </c>
+      <c r="B195" s="4" t="inlineStr">
+        <is>
+          <t>11:25:00</t>
+        </is>
+      </c>
+      <c r="C195" s="4" t="inlineStr">
+        <is>
+          <t>11:25</t>
+        </is>
+      </c>
+      <c r="D195" s="4" t="inlineStr"/>
+      <c r="E195" s="4" t="inlineStr"/>
+      <c r="F195" s="4" t="inlineStr"/>
+      <c r="G195" s="4" t="inlineStr"/>
+      <c r="H195" s="4" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="I195" s="4" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="J195" s="4" t="inlineStr"/>
+      <c r="K195" s="4" t="inlineStr"/>
+      <c r="L195" s="4" t="inlineStr"/>
+      <c r="M195" s="4" t="inlineStr"/>
+      <c r="N195" s="4" t="inlineStr"/>
+      <c r="O195" s="4" t="inlineStr"/>
+      <c r="P195" s="4" t="inlineStr">
+        <is>
+          <t>Failed to fetch data: Failed to fetch quote data after all retries</t>
+        </is>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" s="4" t="inlineStr">
+        <is>
+          <t>2026-03-03 11:30:00</t>
+        </is>
+      </c>
+      <c r="B196" s="4" t="inlineStr">
+        <is>
+          <t>11:30:00</t>
+        </is>
+      </c>
+      <c r="C196" s="4" t="inlineStr">
+        <is>
+          <t>11:30</t>
+        </is>
+      </c>
+      <c r="D196" s="4" t="inlineStr"/>
+      <c r="E196" s="4" t="inlineStr"/>
+      <c r="F196" s="4" t="inlineStr"/>
+      <c r="G196" s="4" t="inlineStr"/>
+      <c r="H196" s="4" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="I196" s="4" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="J196" s="4" t="inlineStr"/>
+      <c r="K196" s="4" t="inlineStr"/>
+      <c r="L196" s="4" t="inlineStr"/>
+      <c r="M196" s="4" t="inlineStr"/>
+      <c r="N196" s="4" t="inlineStr"/>
+      <c r="O196" s="4" t="inlineStr"/>
+      <c r="P196" s="4" t="inlineStr">
+        <is>
+          <t>Data fetch failed: Failed to fetch quote data after all retries</t>
+        </is>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" s="4" t="inlineStr">
+        <is>
+          <t>2026-03-03 11:30:00</t>
+        </is>
+      </c>
+      <c r="B197" s="4" t="inlineStr">
+        <is>
+          <t>11:30:00</t>
+        </is>
+      </c>
+      <c r="C197" s="4" t="inlineStr">
+        <is>
+          <t>11:30</t>
+        </is>
+      </c>
+      <c r="D197" s="4" t="inlineStr"/>
+      <c r="E197" s="4" t="inlineStr"/>
+      <c r="F197" s="4" t="inlineStr"/>
+      <c r="G197" s="4" t="inlineStr"/>
+      <c r="H197" s="4" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="I197" s="4" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="J197" s="4" t="inlineStr"/>
+      <c r="K197" s="4" t="inlineStr"/>
+      <c r="L197" s="4" t="inlineStr"/>
+      <c r="M197" s="4" t="inlineStr"/>
+      <c r="N197" s="4" t="inlineStr"/>
+      <c r="O197" s="4" t="inlineStr"/>
+      <c r="P197" s="4" t="inlineStr">
+        <is>
+          <t>Failed to fetch data: Failed to fetch quote data after all retries</t>
+        </is>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" s="4" t="inlineStr">
+        <is>
+          <t>2026-03-03 11:35:00</t>
+        </is>
+      </c>
+      <c r="B198" s="4" t="inlineStr">
+        <is>
+          <t>11:35:00</t>
+        </is>
+      </c>
+      <c r="C198" s="4" t="inlineStr">
+        <is>
+          <t>11:35</t>
+        </is>
+      </c>
+      <c r="D198" s="4" t="inlineStr"/>
+      <c r="E198" s="4" t="inlineStr"/>
+      <c r="F198" s="4" t="inlineStr"/>
+      <c r="G198" s="4" t="inlineStr"/>
+      <c r="H198" s="4" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="I198" s="4" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="J198" s="4" t="inlineStr"/>
+      <c r="K198" s="4" t="inlineStr"/>
+      <c r="L198" s="4" t="inlineStr"/>
+      <c r="M198" s="4" t="inlineStr"/>
+      <c r="N198" s="4" t="inlineStr"/>
+      <c r="O198" s="4" t="inlineStr"/>
+      <c r="P198" s="4" t="inlineStr">
+        <is>
+          <t>Data fetch failed: Failed to fetch quote data after all retries</t>
+        </is>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" s="4" t="inlineStr">
+        <is>
+          <t>2026-03-03 11:35:00</t>
+        </is>
+      </c>
+      <c r="B199" s="4" t="inlineStr">
+        <is>
+          <t>11:35:00</t>
+        </is>
+      </c>
+      <c r="C199" s="4" t="inlineStr">
+        <is>
+          <t>11:35</t>
+        </is>
+      </c>
+      <c r="D199" s="4" t="inlineStr"/>
+      <c r="E199" s="4" t="inlineStr"/>
+      <c r="F199" s="4" t="inlineStr"/>
+      <c r="G199" s="4" t="inlineStr"/>
+      <c r="H199" s="4" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="I199" s="4" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="J199" s="4" t="inlineStr"/>
+      <c r="K199" s="4" t="inlineStr"/>
+      <c r="L199" s="4" t="inlineStr"/>
+      <c r="M199" s="4" t="inlineStr"/>
+      <c r="N199" s="4" t="inlineStr"/>
+      <c r="O199" s="4" t="inlineStr"/>
+      <c r="P199" s="4" t="inlineStr">
+        <is>
+          <t>Failed to fetch data: Failed to fetch quote data after all retries</t>
+        </is>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" s="4" t="inlineStr">
+        <is>
+          <t>2026-03-03 11:40:00</t>
+        </is>
+      </c>
+      <c r="B200" s="4" t="inlineStr">
+        <is>
+          <t>11:40:00</t>
+        </is>
+      </c>
+      <c r="C200" s="4" t="inlineStr">
+        <is>
+          <t>11:40</t>
+        </is>
+      </c>
+      <c r="D200" s="4" t="inlineStr"/>
+      <c r="E200" s="4" t="inlineStr"/>
+      <c r="F200" s="4" t="inlineStr"/>
+      <c r="G200" s="4" t="inlineStr"/>
+      <c r="H200" s="4" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="I200" s="4" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="J200" s="4" t="inlineStr"/>
+      <c r="K200" s="4" t="inlineStr"/>
+      <c r="L200" s="4" t="inlineStr"/>
+      <c r="M200" s="4" t="inlineStr"/>
+      <c r="N200" s="4" t="inlineStr"/>
+      <c r="O200" s="4" t="inlineStr"/>
+      <c r="P200" s="4" t="inlineStr">
+        <is>
+          <t>Data fetch failed: Failed to fetch quote data after all retries</t>
+        </is>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" s="4" t="inlineStr">
+        <is>
+          <t>2026-03-03 11:40:00</t>
+        </is>
+      </c>
+      <c r="B201" s="4" t="inlineStr">
+        <is>
+          <t>11:40:00</t>
+        </is>
+      </c>
+      <c r="C201" s="4" t="inlineStr">
+        <is>
+          <t>11:40</t>
+        </is>
+      </c>
+      <c r="D201" s="4" t="inlineStr"/>
+      <c r="E201" s="4" t="inlineStr"/>
+      <c r="F201" s="4" t="inlineStr"/>
+      <c r="G201" s="4" t="inlineStr"/>
+      <c r="H201" s="4" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="I201" s="4" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="J201" s="4" t="inlineStr"/>
+      <c r="K201" s="4" t="inlineStr"/>
+      <c r="L201" s="4" t="inlineStr"/>
+      <c r="M201" s="4" t="inlineStr"/>
+      <c r="N201" s="4" t="inlineStr"/>
+      <c r="O201" s="4" t="inlineStr"/>
+      <c r="P201" s="4" t="inlineStr">
         <is>
           <t>Failed to fetch data: Failed to fetch quote data after all retries</t>
         </is>

--- a/Mine/logs/mine_signal_logs.xlsx
+++ b/Mine/logs/mine_signal_logs.xlsx
@@ -518,7 +518,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P201"/>
+  <dimension ref="A1:P203"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -10224,6 +10224,90 @@
       <c r="N201" s="4" t="inlineStr"/>
       <c r="O201" s="4" t="inlineStr"/>
       <c r="P201" s="4" t="inlineStr">
+        <is>
+          <t>Failed to fetch data: Failed to fetch quote data after all retries</t>
+        </is>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" s="4" t="inlineStr">
+        <is>
+          <t>2026-03-03 11:45:00</t>
+        </is>
+      </c>
+      <c r="B202" s="4" t="inlineStr">
+        <is>
+          <t>11:45:00</t>
+        </is>
+      </c>
+      <c r="C202" s="4" t="inlineStr">
+        <is>
+          <t>11:45</t>
+        </is>
+      </c>
+      <c r="D202" s="4" t="inlineStr"/>
+      <c r="E202" s="4" t="inlineStr"/>
+      <c r="F202" s="4" t="inlineStr"/>
+      <c r="G202" s="4" t="inlineStr"/>
+      <c r="H202" s="4" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="I202" s="4" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="J202" s="4" t="inlineStr"/>
+      <c r="K202" s="4" t="inlineStr"/>
+      <c r="L202" s="4" t="inlineStr"/>
+      <c r="M202" s="4" t="inlineStr"/>
+      <c r="N202" s="4" t="inlineStr"/>
+      <c r="O202" s="4" t="inlineStr"/>
+      <c r="P202" s="4" t="inlineStr">
+        <is>
+          <t>Data fetch failed: Failed to fetch quote data after all retries</t>
+        </is>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" s="4" t="inlineStr">
+        <is>
+          <t>2026-03-03 11:45:00</t>
+        </is>
+      </c>
+      <c r="B203" s="4" t="inlineStr">
+        <is>
+          <t>11:45:00</t>
+        </is>
+      </c>
+      <c r="C203" s="4" t="inlineStr">
+        <is>
+          <t>11:45</t>
+        </is>
+      </c>
+      <c r="D203" s="4" t="inlineStr"/>
+      <c r="E203" s="4" t="inlineStr"/>
+      <c r="F203" s="4" t="inlineStr"/>
+      <c r="G203" s="4" t="inlineStr"/>
+      <c r="H203" s="4" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="I203" s="4" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="J203" s="4" t="inlineStr"/>
+      <c r="K203" s="4" t="inlineStr"/>
+      <c r="L203" s="4" t="inlineStr"/>
+      <c r="M203" s="4" t="inlineStr"/>
+      <c r="N203" s="4" t="inlineStr"/>
+      <c r="O203" s="4" t="inlineStr"/>
+      <c r="P203" s="4" t="inlineStr">
         <is>
           <t>Failed to fetch data: Failed to fetch quote data after all retries</t>
         </is>

--- a/Mine/logs/mine_signal_logs.xlsx
+++ b/Mine/logs/mine_signal_logs.xlsx
@@ -518,7 +518,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P203"/>
+  <dimension ref="A1:P269"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -10308,6 +10308,2778 @@
       <c r="N203" s="4" t="inlineStr"/>
       <c r="O203" s="4" t="inlineStr"/>
       <c r="P203" s="4" t="inlineStr">
+        <is>
+          <t>Failed to fetch data: Failed to fetch quote data after all retries</t>
+        </is>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" s="4" t="inlineStr">
+        <is>
+          <t>2026-03-03 11:50:00</t>
+        </is>
+      </c>
+      <c r="B204" s="4" t="inlineStr">
+        <is>
+          <t>11:50:00</t>
+        </is>
+      </c>
+      <c r="C204" s="4" t="inlineStr">
+        <is>
+          <t>11:50</t>
+        </is>
+      </c>
+      <c r="D204" s="4" t="inlineStr"/>
+      <c r="E204" s="4" t="inlineStr"/>
+      <c r="F204" s="4" t="inlineStr"/>
+      <c r="G204" s="4" t="inlineStr"/>
+      <c r="H204" s="4" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="I204" s="4" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="J204" s="4" t="inlineStr"/>
+      <c r="K204" s="4" t="inlineStr"/>
+      <c r="L204" s="4" t="inlineStr"/>
+      <c r="M204" s="4" t="inlineStr"/>
+      <c r="N204" s="4" t="inlineStr"/>
+      <c r="O204" s="4" t="inlineStr"/>
+      <c r="P204" s="4" t="inlineStr">
+        <is>
+          <t>Data fetch failed: Failed to fetch quote data after all retries</t>
+        </is>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" s="4" t="inlineStr">
+        <is>
+          <t>2026-03-03 11:50:00</t>
+        </is>
+      </c>
+      <c r="B205" s="4" t="inlineStr">
+        <is>
+          <t>11:50:00</t>
+        </is>
+      </c>
+      <c r="C205" s="4" t="inlineStr">
+        <is>
+          <t>11:50</t>
+        </is>
+      </c>
+      <c r="D205" s="4" t="inlineStr"/>
+      <c r="E205" s="4" t="inlineStr"/>
+      <c r="F205" s="4" t="inlineStr"/>
+      <c r="G205" s="4" t="inlineStr"/>
+      <c r="H205" s="4" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="I205" s="4" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="J205" s="4" t="inlineStr"/>
+      <c r="K205" s="4" t="inlineStr"/>
+      <c r="L205" s="4" t="inlineStr"/>
+      <c r="M205" s="4" t="inlineStr"/>
+      <c r="N205" s="4" t="inlineStr"/>
+      <c r="O205" s="4" t="inlineStr"/>
+      <c r="P205" s="4" t="inlineStr">
+        <is>
+          <t>Failed to fetch data: Failed to fetch quote data after all retries</t>
+        </is>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" s="4" t="inlineStr">
+        <is>
+          <t>2026-03-03 11:55:00</t>
+        </is>
+      </c>
+      <c r="B206" s="4" t="inlineStr">
+        <is>
+          <t>11:55:00</t>
+        </is>
+      </c>
+      <c r="C206" s="4" t="inlineStr">
+        <is>
+          <t>11:55</t>
+        </is>
+      </c>
+      <c r="D206" s="4" t="inlineStr"/>
+      <c r="E206" s="4" t="inlineStr"/>
+      <c r="F206" s="4" t="inlineStr"/>
+      <c r="G206" s="4" t="inlineStr"/>
+      <c r="H206" s="4" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="I206" s="4" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="J206" s="4" t="inlineStr"/>
+      <c r="K206" s="4" t="inlineStr"/>
+      <c r="L206" s="4" t="inlineStr"/>
+      <c r="M206" s="4" t="inlineStr"/>
+      <c r="N206" s="4" t="inlineStr"/>
+      <c r="O206" s="4" t="inlineStr"/>
+      <c r="P206" s="4" t="inlineStr">
+        <is>
+          <t>Data fetch failed: Failed to fetch quote data after all retries</t>
+        </is>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" s="4" t="inlineStr">
+        <is>
+          <t>2026-03-03 11:55:00</t>
+        </is>
+      </c>
+      <c r="B207" s="4" t="inlineStr">
+        <is>
+          <t>11:55:00</t>
+        </is>
+      </c>
+      <c r="C207" s="4" t="inlineStr">
+        <is>
+          <t>11:55</t>
+        </is>
+      </c>
+      <c r="D207" s="4" t="inlineStr"/>
+      <c r="E207" s="4" t="inlineStr"/>
+      <c r="F207" s="4" t="inlineStr"/>
+      <c r="G207" s="4" t="inlineStr"/>
+      <c r="H207" s="4" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="I207" s="4" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="J207" s="4" t="inlineStr"/>
+      <c r="K207" s="4" t="inlineStr"/>
+      <c r="L207" s="4" t="inlineStr"/>
+      <c r="M207" s="4" t="inlineStr"/>
+      <c r="N207" s="4" t="inlineStr"/>
+      <c r="O207" s="4" t="inlineStr"/>
+      <c r="P207" s="4" t="inlineStr">
+        <is>
+          <t>Failed to fetch data: Failed to fetch quote data after all retries</t>
+        </is>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" s="4" t="inlineStr">
+        <is>
+          <t>2026-03-03 12:00:00</t>
+        </is>
+      </c>
+      <c r="B208" s="4" t="inlineStr">
+        <is>
+          <t>12:00:00</t>
+        </is>
+      </c>
+      <c r="C208" s="4" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
+      <c r="D208" s="4" t="inlineStr"/>
+      <c r="E208" s="4" t="inlineStr"/>
+      <c r="F208" s="4" t="inlineStr"/>
+      <c r="G208" s="4" t="inlineStr"/>
+      <c r="H208" s="4" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="I208" s="4" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="J208" s="4" t="inlineStr"/>
+      <c r="K208" s="4" t="inlineStr"/>
+      <c r="L208" s="4" t="inlineStr"/>
+      <c r="M208" s="4" t="inlineStr"/>
+      <c r="N208" s="4" t="inlineStr"/>
+      <c r="O208" s="4" t="inlineStr"/>
+      <c r="P208" s="4" t="inlineStr">
+        <is>
+          <t>Data fetch failed: Failed to fetch quote data after all retries</t>
+        </is>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" s="4" t="inlineStr">
+        <is>
+          <t>2026-03-03 12:00:00</t>
+        </is>
+      </c>
+      <c r="B209" s="4" t="inlineStr">
+        <is>
+          <t>12:00:00</t>
+        </is>
+      </c>
+      <c r="C209" s="4" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
+      <c r="D209" s="4" t="inlineStr"/>
+      <c r="E209" s="4" t="inlineStr"/>
+      <c r="F209" s="4" t="inlineStr"/>
+      <c r="G209" s="4" t="inlineStr"/>
+      <c r="H209" s="4" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="I209" s="4" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="J209" s="4" t="inlineStr"/>
+      <c r="K209" s="4" t="inlineStr"/>
+      <c r="L209" s="4" t="inlineStr"/>
+      <c r="M209" s="4" t="inlineStr"/>
+      <c r="N209" s="4" t="inlineStr"/>
+      <c r="O209" s="4" t="inlineStr"/>
+      <c r="P209" s="4" t="inlineStr">
+        <is>
+          <t>Failed to fetch data: Failed to fetch quote data after all retries</t>
+        </is>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" s="4" t="inlineStr">
+        <is>
+          <t>2026-03-03 12:05:00</t>
+        </is>
+      </c>
+      <c r="B210" s="4" t="inlineStr">
+        <is>
+          <t>12:05:00</t>
+        </is>
+      </c>
+      <c r="C210" s="4" t="inlineStr">
+        <is>
+          <t>12:05</t>
+        </is>
+      </c>
+      <c r="D210" s="4" t="inlineStr"/>
+      <c r="E210" s="4" t="inlineStr"/>
+      <c r="F210" s="4" t="inlineStr"/>
+      <c r="G210" s="4" t="inlineStr"/>
+      <c r="H210" s="4" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="I210" s="4" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="J210" s="4" t="inlineStr"/>
+      <c r="K210" s="4" t="inlineStr"/>
+      <c r="L210" s="4" t="inlineStr"/>
+      <c r="M210" s="4" t="inlineStr"/>
+      <c r="N210" s="4" t="inlineStr"/>
+      <c r="O210" s="4" t="inlineStr"/>
+      <c r="P210" s="4" t="inlineStr">
+        <is>
+          <t>Data fetch failed: Failed to fetch quote data after all retries</t>
+        </is>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" s="4" t="inlineStr">
+        <is>
+          <t>2026-03-03 12:05:00</t>
+        </is>
+      </c>
+      <c r="B211" s="4" t="inlineStr">
+        <is>
+          <t>12:05:00</t>
+        </is>
+      </c>
+      <c r="C211" s="4" t="inlineStr">
+        <is>
+          <t>12:05</t>
+        </is>
+      </c>
+      <c r="D211" s="4" t="inlineStr"/>
+      <c r="E211" s="4" t="inlineStr"/>
+      <c r="F211" s="4" t="inlineStr"/>
+      <c r="G211" s="4" t="inlineStr"/>
+      <c r="H211" s="4" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="I211" s="4" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="J211" s="4" t="inlineStr"/>
+      <c r="K211" s="4" t="inlineStr"/>
+      <c r="L211" s="4" t="inlineStr"/>
+      <c r="M211" s="4" t="inlineStr"/>
+      <c r="N211" s="4" t="inlineStr"/>
+      <c r="O211" s="4" t="inlineStr"/>
+      <c r="P211" s="4" t="inlineStr">
+        <is>
+          <t>Failed to fetch data: Failed to fetch quote data after all retries</t>
+        </is>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" s="4" t="inlineStr">
+        <is>
+          <t>2026-03-03 12:10:00</t>
+        </is>
+      </c>
+      <c r="B212" s="4" t="inlineStr">
+        <is>
+          <t>12:10:00</t>
+        </is>
+      </c>
+      <c r="C212" s="4" t="inlineStr">
+        <is>
+          <t>12:10</t>
+        </is>
+      </c>
+      <c r="D212" s="4" t="inlineStr"/>
+      <c r="E212" s="4" t="inlineStr"/>
+      <c r="F212" s="4" t="inlineStr"/>
+      <c r="G212" s="4" t="inlineStr"/>
+      <c r="H212" s="4" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="I212" s="4" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="J212" s="4" t="inlineStr"/>
+      <c r="K212" s="4" t="inlineStr"/>
+      <c r="L212" s="4" t="inlineStr"/>
+      <c r="M212" s="4" t="inlineStr"/>
+      <c r="N212" s="4" t="inlineStr"/>
+      <c r="O212" s="4" t="inlineStr"/>
+      <c r="P212" s="4" t="inlineStr">
+        <is>
+          <t>Data fetch failed: Failed to fetch quote data after all retries</t>
+        </is>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" s="4" t="inlineStr">
+        <is>
+          <t>2026-03-03 12:10:00</t>
+        </is>
+      </c>
+      <c r="B213" s="4" t="inlineStr">
+        <is>
+          <t>12:10:00</t>
+        </is>
+      </c>
+      <c r="C213" s="4" t="inlineStr">
+        <is>
+          <t>12:10</t>
+        </is>
+      </c>
+      <c r="D213" s="4" t="inlineStr"/>
+      <c r="E213" s="4" t="inlineStr"/>
+      <c r="F213" s="4" t="inlineStr"/>
+      <c r="G213" s="4" t="inlineStr"/>
+      <c r="H213" s="4" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="I213" s="4" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="J213" s="4" t="inlineStr"/>
+      <c r="K213" s="4" t="inlineStr"/>
+      <c r="L213" s="4" t="inlineStr"/>
+      <c r="M213" s="4" t="inlineStr"/>
+      <c r="N213" s="4" t="inlineStr"/>
+      <c r="O213" s="4" t="inlineStr"/>
+      <c r="P213" s="4" t="inlineStr">
+        <is>
+          <t>Failed to fetch data: Failed to fetch quote data after all retries</t>
+        </is>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" s="4" t="inlineStr">
+        <is>
+          <t>2026-03-03 12:15:00</t>
+        </is>
+      </c>
+      <c r="B214" s="4" t="inlineStr">
+        <is>
+          <t>12:15:00</t>
+        </is>
+      </c>
+      <c r="C214" s="4" t="inlineStr">
+        <is>
+          <t>12:15</t>
+        </is>
+      </c>
+      <c r="D214" s="4" t="inlineStr"/>
+      <c r="E214" s="4" t="inlineStr"/>
+      <c r="F214" s="4" t="inlineStr"/>
+      <c r="G214" s="4" t="inlineStr"/>
+      <c r="H214" s="4" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="I214" s="4" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="J214" s="4" t="inlineStr"/>
+      <c r="K214" s="4" t="inlineStr"/>
+      <c r="L214" s="4" t="inlineStr"/>
+      <c r="M214" s="4" t="inlineStr"/>
+      <c r="N214" s="4" t="inlineStr"/>
+      <c r="O214" s="4" t="inlineStr"/>
+      <c r="P214" s="4" t="inlineStr">
+        <is>
+          <t>Data fetch failed: Failed to fetch quote data after all retries</t>
+        </is>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" s="4" t="inlineStr">
+        <is>
+          <t>2026-03-03 12:15:00</t>
+        </is>
+      </c>
+      <c r="B215" s="4" t="inlineStr">
+        <is>
+          <t>12:15:00</t>
+        </is>
+      </c>
+      <c r="C215" s="4" t="inlineStr">
+        <is>
+          <t>12:15</t>
+        </is>
+      </c>
+      <c r="D215" s="4" t="inlineStr"/>
+      <c r="E215" s="4" t="inlineStr"/>
+      <c r="F215" s="4" t="inlineStr"/>
+      <c r="G215" s="4" t="inlineStr"/>
+      <c r="H215" s="4" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="I215" s="4" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="J215" s="4" t="inlineStr"/>
+      <c r="K215" s="4" t="inlineStr"/>
+      <c r="L215" s="4" t="inlineStr"/>
+      <c r="M215" s="4" t="inlineStr"/>
+      <c r="N215" s="4" t="inlineStr"/>
+      <c r="O215" s="4" t="inlineStr"/>
+      <c r="P215" s="4" t="inlineStr">
+        <is>
+          <t>Failed to fetch data: Failed to fetch quote data after all retries</t>
+        </is>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" s="4" t="inlineStr">
+        <is>
+          <t>2026-03-03 12:20:00</t>
+        </is>
+      </c>
+      <c r="B216" s="4" t="inlineStr">
+        <is>
+          <t>12:20:00</t>
+        </is>
+      </c>
+      <c r="C216" s="4" t="inlineStr">
+        <is>
+          <t>12:20</t>
+        </is>
+      </c>
+      <c r="D216" s="4" t="inlineStr"/>
+      <c r="E216" s="4" t="inlineStr"/>
+      <c r="F216" s="4" t="inlineStr"/>
+      <c r="G216" s="4" t="inlineStr"/>
+      <c r="H216" s="4" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="I216" s="4" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="J216" s="4" t="inlineStr"/>
+      <c r="K216" s="4" t="inlineStr"/>
+      <c r="L216" s="4" t="inlineStr"/>
+      <c r="M216" s="4" t="inlineStr"/>
+      <c r="N216" s="4" t="inlineStr"/>
+      <c r="O216" s="4" t="inlineStr"/>
+      <c r="P216" s="4" t="inlineStr">
+        <is>
+          <t>Data fetch failed: Failed to fetch quote data after all retries</t>
+        </is>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" s="4" t="inlineStr">
+        <is>
+          <t>2026-03-03 12:20:00</t>
+        </is>
+      </c>
+      <c r="B217" s="4" t="inlineStr">
+        <is>
+          <t>12:20:00</t>
+        </is>
+      </c>
+      <c r="C217" s="4" t="inlineStr">
+        <is>
+          <t>12:20</t>
+        </is>
+      </c>
+      <c r="D217" s="4" t="inlineStr"/>
+      <c r="E217" s="4" t="inlineStr"/>
+      <c r="F217" s="4" t="inlineStr"/>
+      <c r="G217" s="4" t="inlineStr"/>
+      <c r="H217" s="4" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="I217" s="4" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="J217" s="4" t="inlineStr"/>
+      <c r="K217" s="4" t="inlineStr"/>
+      <c r="L217" s="4" t="inlineStr"/>
+      <c r="M217" s="4" t="inlineStr"/>
+      <c r="N217" s="4" t="inlineStr"/>
+      <c r="O217" s="4" t="inlineStr"/>
+      <c r="P217" s="4" t="inlineStr">
+        <is>
+          <t>Failed to fetch data: Failed to fetch quote data after all retries</t>
+        </is>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" s="4" t="inlineStr">
+        <is>
+          <t>2026-03-03 12:25:00</t>
+        </is>
+      </c>
+      <c r="B218" s="4" t="inlineStr">
+        <is>
+          <t>12:25:00</t>
+        </is>
+      </c>
+      <c r="C218" s="4" t="inlineStr">
+        <is>
+          <t>12:25</t>
+        </is>
+      </c>
+      <c r="D218" s="4" t="inlineStr"/>
+      <c r="E218" s="4" t="inlineStr"/>
+      <c r="F218" s="4" t="inlineStr"/>
+      <c r="G218" s="4" t="inlineStr"/>
+      <c r="H218" s="4" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="I218" s="4" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="J218" s="4" t="inlineStr"/>
+      <c r="K218" s="4" t="inlineStr"/>
+      <c r="L218" s="4" t="inlineStr"/>
+      <c r="M218" s="4" t="inlineStr"/>
+      <c r="N218" s="4" t="inlineStr"/>
+      <c r="O218" s="4" t="inlineStr"/>
+      <c r="P218" s="4" t="inlineStr">
+        <is>
+          <t>Data fetch failed: Failed to fetch quote data after all retries</t>
+        </is>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" s="4" t="inlineStr">
+        <is>
+          <t>2026-03-03 12:25:00</t>
+        </is>
+      </c>
+      <c r="B219" s="4" t="inlineStr">
+        <is>
+          <t>12:25:00</t>
+        </is>
+      </c>
+      <c r="C219" s="4" t="inlineStr">
+        <is>
+          <t>12:25</t>
+        </is>
+      </c>
+      <c r="D219" s="4" t="inlineStr"/>
+      <c r="E219" s="4" t="inlineStr"/>
+      <c r="F219" s="4" t="inlineStr"/>
+      <c r="G219" s="4" t="inlineStr"/>
+      <c r="H219" s="4" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="I219" s="4" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="J219" s="4" t="inlineStr"/>
+      <c r="K219" s="4" t="inlineStr"/>
+      <c r="L219" s="4" t="inlineStr"/>
+      <c r="M219" s="4" t="inlineStr"/>
+      <c r="N219" s="4" t="inlineStr"/>
+      <c r="O219" s="4" t="inlineStr"/>
+      <c r="P219" s="4" t="inlineStr">
+        <is>
+          <t>Failed to fetch data: Failed to fetch quote data after all retries</t>
+        </is>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" s="4" t="inlineStr">
+        <is>
+          <t>2026-03-03 12:30:00</t>
+        </is>
+      </c>
+      <c r="B220" s="4" t="inlineStr">
+        <is>
+          <t>12:30:00</t>
+        </is>
+      </c>
+      <c r="C220" s="4" t="inlineStr">
+        <is>
+          <t>12:30</t>
+        </is>
+      </c>
+      <c r="D220" s="4" t="inlineStr"/>
+      <c r="E220" s="4" t="inlineStr"/>
+      <c r="F220" s="4" t="inlineStr"/>
+      <c r="G220" s="4" t="inlineStr"/>
+      <c r="H220" s="4" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="I220" s="4" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="J220" s="4" t="inlineStr"/>
+      <c r="K220" s="4" t="inlineStr"/>
+      <c r="L220" s="4" t="inlineStr"/>
+      <c r="M220" s="4" t="inlineStr"/>
+      <c r="N220" s="4" t="inlineStr"/>
+      <c r="O220" s="4" t="inlineStr"/>
+      <c r="P220" s="4" t="inlineStr">
+        <is>
+          <t>Data fetch failed: Failed to fetch quote data after all retries</t>
+        </is>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" s="4" t="inlineStr">
+        <is>
+          <t>2026-03-03 12:30:00</t>
+        </is>
+      </c>
+      <c r="B221" s="4" t="inlineStr">
+        <is>
+          <t>12:30:00</t>
+        </is>
+      </c>
+      <c r="C221" s="4" t="inlineStr">
+        <is>
+          <t>12:30</t>
+        </is>
+      </c>
+      <c r="D221" s="4" t="inlineStr"/>
+      <c r="E221" s="4" t="inlineStr"/>
+      <c r="F221" s="4" t="inlineStr"/>
+      <c r="G221" s="4" t="inlineStr"/>
+      <c r="H221" s="4" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="I221" s="4" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="J221" s="4" t="inlineStr"/>
+      <c r="K221" s="4" t="inlineStr"/>
+      <c r="L221" s="4" t="inlineStr"/>
+      <c r="M221" s="4" t="inlineStr"/>
+      <c r="N221" s="4" t="inlineStr"/>
+      <c r="O221" s="4" t="inlineStr"/>
+      <c r="P221" s="4" t="inlineStr">
+        <is>
+          <t>Failed to fetch data: Failed to fetch quote data after all retries</t>
+        </is>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" s="4" t="inlineStr">
+        <is>
+          <t>2026-03-03 12:35:00</t>
+        </is>
+      </c>
+      <c r="B222" s="4" t="inlineStr">
+        <is>
+          <t>12:35:00</t>
+        </is>
+      </c>
+      <c r="C222" s="4" t="inlineStr">
+        <is>
+          <t>12:35</t>
+        </is>
+      </c>
+      <c r="D222" s="4" t="inlineStr"/>
+      <c r="E222" s="4" t="inlineStr"/>
+      <c r="F222" s="4" t="inlineStr"/>
+      <c r="G222" s="4" t="inlineStr"/>
+      <c r="H222" s="4" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="I222" s="4" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="J222" s="4" t="inlineStr"/>
+      <c r="K222" s="4" t="inlineStr"/>
+      <c r="L222" s="4" t="inlineStr"/>
+      <c r="M222" s="4" t="inlineStr"/>
+      <c r="N222" s="4" t="inlineStr"/>
+      <c r="O222" s="4" t="inlineStr"/>
+      <c r="P222" s="4" t="inlineStr">
+        <is>
+          <t>Data fetch failed: Failed to fetch quote data after all retries</t>
+        </is>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" s="4" t="inlineStr">
+        <is>
+          <t>2026-03-03 12:35:00</t>
+        </is>
+      </c>
+      <c r="B223" s="4" t="inlineStr">
+        <is>
+          <t>12:35:00</t>
+        </is>
+      </c>
+      <c r="C223" s="4" t="inlineStr">
+        <is>
+          <t>12:35</t>
+        </is>
+      </c>
+      <c r="D223" s="4" t="inlineStr"/>
+      <c r="E223" s="4" t="inlineStr"/>
+      <c r="F223" s="4" t="inlineStr"/>
+      <c r="G223" s="4" t="inlineStr"/>
+      <c r="H223" s="4" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="I223" s="4" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="J223" s="4" t="inlineStr"/>
+      <c r="K223" s="4" t="inlineStr"/>
+      <c r="L223" s="4" t="inlineStr"/>
+      <c r="M223" s="4" t="inlineStr"/>
+      <c r="N223" s="4" t="inlineStr"/>
+      <c r="O223" s="4" t="inlineStr"/>
+      <c r="P223" s="4" t="inlineStr">
+        <is>
+          <t>Failed to fetch data: Failed to fetch quote data after all retries</t>
+        </is>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" s="4" t="inlineStr">
+        <is>
+          <t>2026-03-03 12:40:00</t>
+        </is>
+      </c>
+      <c r="B224" s="4" t="inlineStr">
+        <is>
+          <t>12:40:00</t>
+        </is>
+      </c>
+      <c r="C224" s="4" t="inlineStr">
+        <is>
+          <t>12:40</t>
+        </is>
+      </c>
+      <c r="D224" s="4" t="inlineStr"/>
+      <c r="E224" s="4" t="inlineStr"/>
+      <c r="F224" s="4" t="inlineStr"/>
+      <c r="G224" s="4" t="inlineStr"/>
+      <c r="H224" s="4" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="I224" s="4" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="J224" s="4" t="inlineStr"/>
+      <c r="K224" s="4" t="inlineStr"/>
+      <c r="L224" s="4" t="inlineStr"/>
+      <c r="M224" s="4" t="inlineStr"/>
+      <c r="N224" s="4" t="inlineStr"/>
+      <c r="O224" s="4" t="inlineStr"/>
+      <c r="P224" s="4" t="inlineStr">
+        <is>
+          <t>Data fetch failed: Failed to fetch quote data after all retries</t>
+        </is>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" s="4" t="inlineStr">
+        <is>
+          <t>2026-03-03 12:40:00</t>
+        </is>
+      </c>
+      <c r="B225" s="4" t="inlineStr">
+        <is>
+          <t>12:40:00</t>
+        </is>
+      </c>
+      <c r="C225" s="4" t="inlineStr">
+        <is>
+          <t>12:40</t>
+        </is>
+      </c>
+      <c r="D225" s="4" t="inlineStr"/>
+      <c r="E225" s="4" t="inlineStr"/>
+      <c r="F225" s="4" t="inlineStr"/>
+      <c r="G225" s="4" t="inlineStr"/>
+      <c r="H225" s="4" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="I225" s="4" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="J225" s="4" t="inlineStr"/>
+      <c r="K225" s="4" t="inlineStr"/>
+      <c r="L225" s="4" t="inlineStr"/>
+      <c r="M225" s="4" t="inlineStr"/>
+      <c r="N225" s="4" t="inlineStr"/>
+      <c r="O225" s="4" t="inlineStr"/>
+      <c r="P225" s="4" t="inlineStr">
+        <is>
+          <t>Failed to fetch data: Failed to fetch quote data after all retries</t>
+        </is>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226" s="4" t="inlineStr">
+        <is>
+          <t>2026-03-03 12:45:00</t>
+        </is>
+      </c>
+      <c r="B226" s="4" t="inlineStr">
+        <is>
+          <t>12:45:00</t>
+        </is>
+      </c>
+      <c r="C226" s="4" t="inlineStr">
+        <is>
+          <t>12:45</t>
+        </is>
+      </c>
+      <c r="D226" s="4" t="inlineStr"/>
+      <c r="E226" s="4" t="inlineStr"/>
+      <c r="F226" s="4" t="inlineStr"/>
+      <c r="G226" s="4" t="inlineStr"/>
+      <c r="H226" s="4" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="I226" s="4" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="J226" s="4" t="inlineStr"/>
+      <c r="K226" s="4" t="inlineStr"/>
+      <c r="L226" s="4" t="inlineStr"/>
+      <c r="M226" s="4" t="inlineStr"/>
+      <c r="N226" s="4" t="inlineStr"/>
+      <c r="O226" s="4" t="inlineStr"/>
+      <c r="P226" s="4" t="inlineStr">
+        <is>
+          <t>Data fetch failed: Failed to fetch quote data after all retries</t>
+        </is>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227" s="4" t="inlineStr">
+        <is>
+          <t>2026-03-03 12:45:00</t>
+        </is>
+      </c>
+      <c r="B227" s="4" t="inlineStr">
+        <is>
+          <t>12:45:00</t>
+        </is>
+      </c>
+      <c r="C227" s="4" t="inlineStr">
+        <is>
+          <t>12:45</t>
+        </is>
+      </c>
+      <c r="D227" s="4" t="inlineStr"/>
+      <c r="E227" s="4" t="inlineStr"/>
+      <c r="F227" s="4" t="inlineStr"/>
+      <c r="G227" s="4" t="inlineStr"/>
+      <c r="H227" s="4" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="I227" s="4" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="J227" s="4" t="inlineStr"/>
+      <c r="K227" s="4" t="inlineStr"/>
+      <c r="L227" s="4" t="inlineStr"/>
+      <c r="M227" s="4" t="inlineStr"/>
+      <c r="N227" s="4" t="inlineStr"/>
+      <c r="O227" s="4" t="inlineStr"/>
+      <c r="P227" s="4" t="inlineStr">
+        <is>
+          <t>Failed to fetch data: Failed to fetch quote data after all retries</t>
+        </is>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228" s="4" t="inlineStr">
+        <is>
+          <t>2026-03-03 12:50:00</t>
+        </is>
+      </c>
+      <c r="B228" s="4" t="inlineStr">
+        <is>
+          <t>12:50:00</t>
+        </is>
+      </c>
+      <c r="C228" s="4" t="inlineStr">
+        <is>
+          <t>12:50</t>
+        </is>
+      </c>
+      <c r="D228" s="4" t="inlineStr"/>
+      <c r="E228" s="4" t="inlineStr"/>
+      <c r="F228" s="4" t="inlineStr"/>
+      <c r="G228" s="4" t="inlineStr"/>
+      <c r="H228" s="4" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="I228" s="4" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="J228" s="4" t="inlineStr"/>
+      <c r="K228" s="4" t="inlineStr"/>
+      <c r="L228" s="4" t="inlineStr"/>
+      <c r="M228" s="4" t="inlineStr"/>
+      <c r="N228" s="4" t="inlineStr"/>
+      <c r="O228" s="4" t="inlineStr"/>
+      <c r="P228" s="4" t="inlineStr">
+        <is>
+          <t>Data fetch failed: Failed to fetch quote data after all retries</t>
+        </is>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229" s="4" t="inlineStr">
+        <is>
+          <t>2026-03-03 12:50:00</t>
+        </is>
+      </c>
+      <c r="B229" s="4" t="inlineStr">
+        <is>
+          <t>12:50:00</t>
+        </is>
+      </c>
+      <c r="C229" s="4" t="inlineStr">
+        <is>
+          <t>12:50</t>
+        </is>
+      </c>
+      <c r="D229" s="4" t="inlineStr"/>
+      <c r="E229" s="4" t="inlineStr"/>
+      <c r="F229" s="4" t="inlineStr"/>
+      <c r="G229" s="4" t="inlineStr"/>
+      <c r="H229" s="4" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="I229" s="4" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="J229" s="4" t="inlineStr"/>
+      <c r="K229" s="4" t="inlineStr"/>
+      <c r="L229" s="4" t="inlineStr"/>
+      <c r="M229" s="4" t="inlineStr"/>
+      <c r="N229" s="4" t="inlineStr"/>
+      <c r="O229" s="4" t="inlineStr"/>
+      <c r="P229" s="4" t="inlineStr">
+        <is>
+          <t>Failed to fetch data: Failed to fetch quote data after all retries</t>
+        </is>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230" s="4" t="inlineStr">
+        <is>
+          <t>2026-03-03 12:55:00</t>
+        </is>
+      </c>
+      <c r="B230" s="4" t="inlineStr">
+        <is>
+          <t>12:55:00</t>
+        </is>
+      </c>
+      <c r="C230" s="4" t="inlineStr">
+        <is>
+          <t>12:55</t>
+        </is>
+      </c>
+      <c r="D230" s="4" t="inlineStr"/>
+      <c r="E230" s="4" t="inlineStr"/>
+      <c r="F230" s="4" t="inlineStr"/>
+      <c r="G230" s="4" t="inlineStr"/>
+      <c r="H230" s="4" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="I230" s="4" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="J230" s="4" t="inlineStr"/>
+      <c r="K230" s="4" t="inlineStr"/>
+      <c r="L230" s="4" t="inlineStr"/>
+      <c r="M230" s="4" t="inlineStr"/>
+      <c r="N230" s="4" t="inlineStr"/>
+      <c r="O230" s="4" t="inlineStr"/>
+      <c r="P230" s="4" t="inlineStr">
+        <is>
+          <t>Data fetch failed: Failed to fetch quote data after all retries</t>
+        </is>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231" s="4" t="inlineStr">
+        <is>
+          <t>2026-03-03 12:55:00</t>
+        </is>
+      </c>
+      <c r="B231" s="4" t="inlineStr">
+        <is>
+          <t>12:55:00</t>
+        </is>
+      </c>
+      <c r="C231" s="4" t="inlineStr">
+        <is>
+          <t>12:55</t>
+        </is>
+      </c>
+      <c r="D231" s="4" t="inlineStr"/>
+      <c r="E231" s="4" t="inlineStr"/>
+      <c r="F231" s="4" t="inlineStr"/>
+      <c r="G231" s="4" t="inlineStr"/>
+      <c r="H231" s="4" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="I231" s="4" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="J231" s="4" t="inlineStr"/>
+      <c r="K231" s="4" t="inlineStr"/>
+      <c r="L231" s="4" t="inlineStr"/>
+      <c r="M231" s="4" t="inlineStr"/>
+      <c r="N231" s="4" t="inlineStr"/>
+      <c r="O231" s="4" t="inlineStr"/>
+      <c r="P231" s="4" t="inlineStr">
+        <is>
+          <t>Failed to fetch data: Failed to fetch quote data after all retries</t>
+        </is>
+      </c>
+    </row>
+    <row r="232">
+      <c r="A232" s="4" t="inlineStr">
+        <is>
+          <t>2026-03-03 13:00:00</t>
+        </is>
+      </c>
+      <c r="B232" s="4" t="inlineStr">
+        <is>
+          <t>13:00:00</t>
+        </is>
+      </c>
+      <c r="C232" s="4" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="D232" s="4" t="inlineStr"/>
+      <c r="E232" s="4" t="inlineStr"/>
+      <c r="F232" s="4" t="inlineStr"/>
+      <c r="G232" s="4" t="inlineStr"/>
+      <c r="H232" s="4" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="I232" s="4" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="J232" s="4" t="inlineStr"/>
+      <c r="K232" s="4" t="inlineStr"/>
+      <c r="L232" s="4" t="inlineStr"/>
+      <c r="M232" s="4" t="inlineStr"/>
+      <c r="N232" s="4" t="inlineStr"/>
+      <c r="O232" s="4" t="inlineStr"/>
+      <c r="P232" s="4" t="inlineStr">
+        <is>
+          <t>Data fetch failed: Failed to fetch quote data after all retries</t>
+        </is>
+      </c>
+    </row>
+    <row r="233">
+      <c r="A233" s="4" t="inlineStr">
+        <is>
+          <t>2026-03-03 13:00:00</t>
+        </is>
+      </c>
+      <c r="B233" s="4" t="inlineStr">
+        <is>
+          <t>13:00:00</t>
+        </is>
+      </c>
+      <c r="C233" s="4" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="D233" s="4" t="inlineStr"/>
+      <c r="E233" s="4" t="inlineStr"/>
+      <c r="F233" s="4" t="inlineStr"/>
+      <c r="G233" s="4" t="inlineStr"/>
+      <c r="H233" s="4" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="I233" s="4" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="J233" s="4" t="inlineStr"/>
+      <c r="K233" s="4" t="inlineStr"/>
+      <c r="L233" s="4" t="inlineStr"/>
+      <c r="M233" s="4" t="inlineStr"/>
+      <c r="N233" s="4" t="inlineStr"/>
+      <c r="O233" s="4" t="inlineStr"/>
+      <c r="P233" s="4" t="inlineStr">
+        <is>
+          <t>Failed to fetch data: Failed to fetch quote data after all retries</t>
+        </is>
+      </c>
+    </row>
+    <row r="234">
+      <c r="A234" s="4" t="inlineStr">
+        <is>
+          <t>2026-03-03 13:35:00</t>
+        </is>
+      </c>
+      <c r="B234" s="4" t="inlineStr">
+        <is>
+          <t>13:35:00</t>
+        </is>
+      </c>
+      <c r="C234" s="4" t="inlineStr">
+        <is>
+          <t>13:35</t>
+        </is>
+      </c>
+      <c r="D234" s="4" t="inlineStr"/>
+      <c r="E234" s="4" t="inlineStr"/>
+      <c r="F234" s="4" t="inlineStr"/>
+      <c r="G234" s="4" t="inlineStr"/>
+      <c r="H234" s="4" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="I234" s="4" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="J234" s="4" t="inlineStr"/>
+      <c r="K234" s="4" t="inlineStr"/>
+      <c r="L234" s="4" t="inlineStr"/>
+      <c r="M234" s="4" t="inlineStr"/>
+      <c r="N234" s="4" t="inlineStr"/>
+      <c r="O234" s="4" t="inlineStr"/>
+      <c r="P234" s="4" t="inlineStr">
+        <is>
+          <t>Data fetch failed: Failed to fetch quote data after all retries</t>
+        </is>
+      </c>
+    </row>
+    <row r="235">
+      <c r="A235" s="4" t="inlineStr">
+        <is>
+          <t>2026-03-03 13:35:00</t>
+        </is>
+      </c>
+      <c r="B235" s="4" t="inlineStr">
+        <is>
+          <t>13:35:00</t>
+        </is>
+      </c>
+      <c r="C235" s="4" t="inlineStr">
+        <is>
+          <t>13:35</t>
+        </is>
+      </c>
+      <c r="D235" s="4" t="inlineStr"/>
+      <c r="E235" s="4" t="inlineStr"/>
+      <c r="F235" s="4" t="inlineStr"/>
+      <c r="G235" s="4" t="inlineStr"/>
+      <c r="H235" s="4" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="I235" s="4" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="J235" s="4" t="inlineStr"/>
+      <c r="K235" s="4" t="inlineStr"/>
+      <c r="L235" s="4" t="inlineStr"/>
+      <c r="M235" s="4" t="inlineStr"/>
+      <c r="N235" s="4" t="inlineStr"/>
+      <c r="O235" s="4" t="inlineStr"/>
+      <c r="P235" s="4" t="inlineStr">
+        <is>
+          <t>Failed to fetch data: Failed to fetch quote data after all retries</t>
+        </is>
+      </c>
+    </row>
+    <row r="236">
+      <c r="A236" s="4" t="inlineStr">
+        <is>
+          <t>2026-03-03 13:40:00</t>
+        </is>
+      </c>
+      <c r="B236" s="4" t="inlineStr">
+        <is>
+          <t>13:40:00</t>
+        </is>
+      </c>
+      <c r="C236" s="4" t="inlineStr">
+        <is>
+          <t>13:40</t>
+        </is>
+      </c>
+      <c r="D236" s="4" t="inlineStr"/>
+      <c r="E236" s="4" t="inlineStr"/>
+      <c r="F236" s="4" t="inlineStr"/>
+      <c r="G236" s="4" t="inlineStr"/>
+      <c r="H236" s="4" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="I236" s="4" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="J236" s="4" t="inlineStr"/>
+      <c r="K236" s="4" t="inlineStr"/>
+      <c r="L236" s="4" t="inlineStr"/>
+      <c r="M236" s="4" t="inlineStr"/>
+      <c r="N236" s="4" t="inlineStr"/>
+      <c r="O236" s="4" t="inlineStr"/>
+      <c r="P236" s="4" t="inlineStr">
+        <is>
+          <t>Data fetch failed: Failed to fetch quote data after all retries</t>
+        </is>
+      </c>
+    </row>
+    <row r="237">
+      <c r="A237" s="4" t="inlineStr">
+        <is>
+          <t>2026-03-03 13:40:00</t>
+        </is>
+      </c>
+      <c r="B237" s="4" t="inlineStr">
+        <is>
+          <t>13:40:00</t>
+        </is>
+      </c>
+      <c r="C237" s="4" t="inlineStr">
+        <is>
+          <t>13:40</t>
+        </is>
+      </c>
+      <c r="D237" s="4" t="inlineStr"/>
+      <c r="E237" s="4" t="inlineStr"/>
+      <c r="F237" s="4" t="inlineStr"/>
+      <c r="G237" s="4" t="inlineStr"/>
+      <c r="H237" s="4" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="I237" s="4" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="J237" s="4" t="inlineStr"/>
+      <c r="K237" s="4" t="inlineStr"/>
+      <c r="L237" s="4" t="inlineStr"/>
+      <c r="M237" s="4" t="inlineStr"/>
+      <c r="N237" s="4" t="inlineStr"/>
+      <c r="O237" s="4" t="inlineStr"/>
+      <c r="P237" s="4" t="inlineStr">
+        <is>
+          <t>Failed to fetch data: Failed to fetch quote data after all retries</t>
+        </is>
+      </c>
+    </row>
+    <row r="238">
+      <c r="A238" s="4" t="inlineStr">
+        <is>
+          <t>2026-03-03 13:45:00</t>
+        </is>
+      </c>
+      <c r="B238" s="4" t="inlineStr">
+        <is>
+          <t>13:45:00</t>
+        </is>
+      </c>
+      <c r="C238" s="4" t="inlineStr">
+        <is>
+          <t>13:45</t>
+        </is>
+      </c>
+      <c r="D238" s="4" t="inlineStr"/>
+      <c r="E238" s="4" t="inlineStr"/>
+      <c r="F238" s="4" t="inlineStr"/>
+      <c r="G238" s="4" t="inlineStr"/>
+      <c r="H238" s="4" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="I238" s="4" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="J238" s="4" t="inlineStr"/>
+      <c r="K238" s="4" t="inlineStr"/>
+      <c r="L238" s="4" t="inlineStr"/>
+      <c r="M238" s="4" t="inlineStr"/>
+      <c r="N238" s="4" t="inlineStr"/>
+      <c r="O238" s="4" t="inlineStr"/>
+      <c r="P238" s="4" t="inlineStr">
+        <is>
+          <t>Data fetch failed: Failed to fetch quote data after all retries</t>
+        </is>
+      </c>
+    </row>
+    <row r="239">
+      <c r="A239" s="4" t="inlineStr">
+        <is>
+          <t>2026-03-03 13:45:00</t>
+        </is>
+      </c>
+      <c r="B239" s="4" t="inlineStr">
+        <is>
+          <t>13:45:00</t>
+        </is>
+      </c>
+      <c r="C239" s="4" t="inlineStr">
+        <is>
+          <t>13:45</t>
+        </is>
+      </c>
+      <c r="D239" s="4" t="inlineStr"/>
+      <c r="E239" s="4" t="inlineStr"/>
+      <c r="F239" s="4" t="inlineStr"/>
+      <c r="G239" s="4" t="inlineStr"/>
+      <c r="H239" s="4" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="I239" s="4" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="J239" s="4" t="inlineStr"/>
+      <c r="K239" s="4" t="inlineStr"/>
+      <c r="L239" s="4" t="inlineStr"/>
+      <c r="M239" s="4" t="inlineStr"/>
+      <c r="N239" s="4" t="inlineStr"/>
+      <c r="O239" s="4" t="inlineStr"/>
+      <c r="P239" s="4" t="inlineStr">
+        <is>
+          <t>Failed to fetch data: Failed to fetch quote data after all retries</t>
+        </is>
+      </c>
+    </row>
+    <row r="240">
+      <c r="A240" s="4" t="inlineStr">
+        <is>
+          <t>2026-03-03 13:50:00</t>
+        </is>
+      </c>
+      <c r="B240" s="4" t="inlineStr">
+        <is>
+          <t>13:50:00</t>
+        </is>
+      </c>
+      <c r="C240" s="4" t="inlineStr">
+        <is>
+          <t>13:50</t>
+        </is>
+      </c>
+      <c r="D240" s="4" t="inlineStr"/>
+      <c r="E240" s="4" t="inlineStr"/>
+      <c r="F240" s="4" t="inlineStr"/>
+      <c r="G240" s="4" t="inlineStr"/>
+      <c r="H240" s="4" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="I240" s="4" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="J240" s="4" t="inlineStr"/>
+      <c r="K240" s="4" t="inlineStr"/>
+      <c r="L240" s="4" t="inlineStr"/>
+      <c r="M240" s="4" t="inlineStr"/>
+      <c r="N240" s="4" t="inlineStr"/>
+      <c r="O240" s="4" t="inlineStr"/>
+      <c r="P240" s="4" t="inlineStr">
+        <is>
+          <t>Data fetch failed: Failed to fetch quote data after all retries</t>
+        </is>
+      </c>
+    </row>
+    <row r="241">
+      <c r="A241" s="4" t="inlineStr">
+        <is>
+          <t>2026-03-03 13:50:00</t>
+        </is>
+      </c>
+      <c r="B241" s="4" t="inlineStr">
+        <is>
+          <t>13:50:00</t>
+        </is>
+      </c>
+      <c r="C241" s="4" t="inlineStr">
+        <is>
+          <t>13:50</t>
+        </is>
+      </c>
+      <c r="D241" s="4" t="inlineStr"/>
+      <c r="E241" s="4" t="inlineStr"/>
+      <c r="F241" s="4" t="inlineStr"/>
+      <c r="G241" s="4" t="inlineStr"/>
+      <c r="H241" s="4" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="I241" s="4" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="J241" s="4" t="inlineStr"/>
+      <c r="K241" s="4" t="inlineStr"/>
+      <c r="L241" s="4" t="inlineStr"/>
+      <c r="M241" s="4" t="inlineStr"/>
+      <c r="N241" s="4" t="inlineStr"/>
+      <c r="O241" s="4" t="inlineStr"/>
+      <c r="P241" s="4" t="inlineStr">
+        <is>
+          <t>Failed to fetch data: Failed to fetch quote data after all retries</t>
+        </is>
+      </c>
+    </row>
+    <row r="242">
+      <c r="A242" s="4" t="inlineStr">
+        <is>
+          <t>2026-03-03 13:55:00</t>
+        </is>
+      </c>
+      <c r="B242" s="4" t="inlineStr">
+        <is>
+          <t>13:55:00</t>
+        </is>
+      </c>
+      <c r="C242" s="4" t="inlineStr">
+        <is>
+          <t>13:55</t>
+        </is>
+      </c>
+      <c r="D242" s="4" t="inlineStr"/>
+      <c r="E242" s="4" t="inlineStr"/>
+      <c r="F242" s="4" t="inlineStr"/>
+      <c r="G242" s="4" t="inlineStr"/>
+      <c r="H242" s="4" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="I242" s="4" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="J242" s="4" t="inlineStr"/>
+      <c r="K242" s="4" t="inlineStr"/>
+      <c r="L242" s="4" t="inlineStr"/>
+      <c r="M242" s="4" t="inlineStr"/>
+      <c r="N242" s="4" t="inlineStr"/>
+      <c r="O242" s="4" t="inlineStr"/>
+      <c r="P242" s="4" t="inlineStr">
+        <is>
+          <t>Data fetch failed: Failed to fetch quote data after all retries</t>
+        </is>
+      </c>
+    </row>
+    <row r="243">
+      <c r="A243" s="4" t="inlineStr">
+        <is>
+          <t>2026-03-03 13:55:00</t>
+        </is>
+      </c>
+      <c r="B243" s="4" t="inlineStr">
+        <is>
+          <t>13:55:00</t>
+        </is>
+      </c>
+      <c r="C243" s="4" t="inlineStr">
+        <is>
+          <t>13:55</t>
+        </is>
+      </c>
+      <c r="D243" s="4" t="inlineStr"/>
+      <c r="E243" s="4" t="inlineStr"/>
+      <c r="F243" s="4" t="inlineStr"/>
+      <c r="G243" s="4" t="inlineStr"/>
+      <c r="H243" s="4" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="I243" s="4" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="J243" s="4" t="inlineStr"/>
+      <c r="K243" s="4" t="inlineStr"/>
+      <c r="L243" s="4" t="inlineStr"/>
+      <c r="M243" s="4" t="inlineStr"/>
+      <c r="N243" s="4" t="inlineStr"/>
+      <c r="O243" s="4" t="inlineStr"/>
+      <c r="P243" s="4" t="inlineStr">
+        <is>
+          <t>Failed to fetch data: Failed to fetch quote data after all retries</t>
+        </is>
+      </c>
+    </row>
+    <row r="244">
+      <c r="A244" s="4" t="inlineStr">
+        <is>
+          <t>2026-03-03 14:00:00</t>
+        </is>
+      </c>
+      <c r="B244" s="4" t="inlineStr">
+        <is>
+          <t>14:00:00</t>
+        </is>
+      </c>
+      <c r="C244" s="4" t="inlineStr">
+        <is>
+          <t>14:00</t>
+        </is>
+      </c>
+      <c r="D244" s="4" t="inlineStr"/>
+      <c r="E244" s="4" t="inlineStr"/>
+      <c r="F244" s="4" t="inlineStr"/>
+      <c r="G244" s="4" t="inlineStr"/>
+      <c r="H244" s="4" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="I244" s="4" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="J244" s="4" t="inlineStr"/>
+      <c r="K244" s="4" t="inlineStr"/>
+      <c r="L244" s="4" t="inlineStr"/>
+      <c r="M244" s="4" t="inlineStr"/>
+      <c r="N244" s="4" t="inlineStr"/>
+      <c r="O244" s="4" t="inlineStr"/>
+      <c r="P244" s="4" t="inlineStr">
+        <is>
+          <t>Data fetch failed: Failed to fetch quote data after all retries</t>
+        </is>
+      </c>
+    </row>
+    <row r="245">
+      <c r="A245" s="4" t="inlineStr">
+        <is>
+          <t>2026-03-03 14:00:00</t>
+        </is>
+      </c>
+      <c r="B245" s="4" t="inlineStr">
+        <is>
+          <t>14:00:00</t>
+        </is>
+      </c>
+      <c r="C245" s="4" t="inlineStr">
+        <is>
+          <t>14:00</t>
+        </is>
+      </c>
+      <c r="D245" s="4" t="inlineStr"/>
+      <c r="E245" s="4" t="inlineStr"/>
+      <c r="F245" s="4" t="inlineStr"/>
+      <c r="G245" s="4" t="inlineStr"/>
+      <c r="H245" s="4" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="I245" s="4" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="J245" s="4" t="inlineStr"/>
+      <c r="K245" s="4" t="inlineStr"/>
+      <c r="L245" s="4" t="inlineStr"/>
+      <c r="M245" s="4" t="inlineStr"/>
+      <c r="N245" s="4" t="inlineStr"/>
+      <c r="O245" s="4" t="inlineStr"/>
+      <c r="P245" s="4" t="inlineStr">
+        <is>
+          <t>Failed to fetch data: Failed to fetch quote data after all retries</t>
+        </is>
+      </c>
+    </row>
+    <row r="246">
+      <c r="A246" s="4" t="inlineStr">
+        <is>
+          <t>2026-03-03 14:05:00</t>
+        </is>
+      </c>
+      <c r="B246" s="4" t="inlineStr">
+        <is>
+          <t>14:05:00</t>
+        </is>
+      </c>
+      <c r="C246" s="4" t="inlineStr">
+        <is>
+          <t>14:05</t>
+        </is>
+      </c>
+      <c r="D246" s="4" t="inlineStr"/>
+      <c r="E246" s="4" t="inlineStr"/>
+      <c r="F246" s="4" t="inlineStr"/>
+      <c r="G246" s="4" t="inlineStr"/>
+      <c r="H246" s="4" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="I246" s="4" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="J246" s="4" t="inlineStr"/>
+      <c r="K246" s="4" t="inlineStr"/>
+      <c r="L246" s="4" t="inlineStr"/>
+      <c r="M246" s="4" t="inlineStr"/>
+      <c r="N246" s="4" t="inlineStr"/>
+      <c r="O246" s="4" t="inlineStr"/>
+      <c r="P246" s="4" t="inlineStr">
+        <is>
+          <t>Data fetch failed: Failed to fetch quote data after all retries</t>
+        </is>
+      </c>
+    </row>
+    <row r="247">
+      <c r="A247" s="4" t="inlineStr">
+        <is>
+          <t>2026-03-03 14:05:00</t>
+        </is>
+      </c>
+      <c r="B247" s="4" t="inlineStr">
+        <is>
+          <t>14:05:00</t>
+        </is>
+      </c>
+      <c r="C247" s="4" t="inlineStr">
+        <is>
+          <t>14:05</t>
+        </is>
+      </c>
+      <c r="D247" s="4" t="inlineStr"/>
+      <c r="E247" s="4" t="inlineStr"/>
+      <c r="F247" s="4" t="inlineStr"/>
+      <c r="G247" s="4" t="inlineStr"/>
+      <c r="H247" s="4" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="I247" s="4" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="J247" s="4" t="inlineStr"/>
+      <c r="K247" s="4" t="inlineStr"/>
+      <c r="L247" s="4" t="inlineStr"/>
+      <c r="M247" s="4" t="inlineStr"/>
+      <c r="N247" s="4" t="inlineStr"/>
+      <c r="O247" s="4" t="inlineStr"/>
+      <c r="P247" s="4" t="inlineStr">
+        <is>
+          <t>Failed to fetch data: Failed to fetch quote data after all retries</t>
+        </is>
+      </c>
+    </row>
+    <row r="248">
+      <c r="A248" s="4" t="inlineStr">
+        <is>
+          <t>2026-03-03 14:10:00</t>
+        </is>
+      </c>
+      <c r="B248" s="4" t="inlineStr">
+        <is>
+          <t>14:10:00</t>
+        </is>
+      </c>
+      <c r="C248" s="4" t="inlineStr">
+        <is>
+          <t>14:10</t>
+        </is>
+      </c>
+      <c r="D248" s="4" t="inlineStr"/>
+      <c r="E248" s="4" t="inlineStr"/>
+      <c r="F248" s="4" t="inlineStr"/>
+      <c r="G248" s="4" t="inlineStr"/>
+      <c r="H248" s="4" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="I248" s="4" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="J248" s="4" t="inlineStr"/>
+      <c r="K248" s="4" t="inlineStr"/>
+      <c r="L248" s="4" t="inlineStr"/>
+      <c r="M248" s="4" t="inlineStr"/>
+      <c r="N248" s="4" t="inlineStr"/>
+      <c r="O248" s="4" t="inlineStr"/>
+      <c r="P248" s="4" t="inlineStr">
+        <is>
+          <t>Data fetch failed: Failed to fetch quote data after all retries</t>
+        </is>
+      </c>
+    </row>
+    <row r="249">
+      <c r="A249" s="4" t="inlineStr">
+        <is>
+          <t>2026-03-03 14:10:00</t>
+        </is>
+      </c>
+      <c r="B249" s="4" t="inlineStr">
+        <is>
+          <t>14:10:00</t>
+        </is>
+      </c>
+      <c r="C249" s="4" t="inlineStr">
+        <is>
+          <t>14:10</t>
+        </is>
+      </c>
+      <c r="D249" s="4" t="inlineStr"/>
+      <c r="E249" s="4" t="inlineStr"/>
+      <c r="F249" s="4" t="inlineStr"/>
+      <c r="G249" s="4" t="inlineStr"/>
+      <c r="H249" s="4" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="I249" s="4" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="J249" s="4" t="inlineStr"/>
+      <c r="K249" s="4" t="inlineStr"/>
+      <c r="L249" s="4" t="inlineStr"/>
+      <c r="M249" s="4" t="inlineStr"/>
+      <c r="N249" s="4" t="inlineStr"/>
+      <c r="O249" s="4" t="inlineStr"/>
+      <c r="P249" s="4" t="inlineStr">
+        <is>
+          <t>Failed to fetch data: Failed to fetch quote data after all retries</t>
+        </is>
+      </c>
+    </row>
+    <row r="250">
+      <c r="A250" s="4" t="inlineStr">
+        <is>
+          <t>2026-03-03 14:15:00</t>
+        </is>
+      </c>
+      <c r="B250" s="4" t="inlineStr">
+        <is>
+          <t>14:15:00</t>
+        </is>
+      </c>
+      <c r="C250" s="4" t="inlineStr">
+        <is>
+          <t>14:15</t>
+        </is>
+      </c>
+      <c r="D250" s="4" t="inlineStr"/>
+      <c r="E250" s="4" t="inlineStr"/>
+      <c r="F250" s="4" t="inlineStr"/>
+      <c r="G250" s="4" t="inlineStr"/>
+      <c r="H250" s="4" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="I250" s="4" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="J250" s="4" t="inlineStr"/>
+      <c r="K250" s="4" t="inlineStr"/>
+      <c r="L250" s="4" t="inlineStr"/>
+      <c r="M250" s="4" t="inlineStr"/>
+      <c r="N250" s="4" t="inlineStr"/>
+      <c r="O250" s="4" t="inlineStr"/>
+      <c r="P250" s="4" t="inlineStr">
+        <is>
+          <t>Data fetch failed: Failed to fetch quote data after all retries</t>
+        </is>
+      </c>
+    </row>
+    <row r="251">
+      <c r="A251" s="4" t="inlineStr">
+        <is>
+          <t>2026-03-03 14:15:00</t>
+        </is>
+      </c>
+      <c r="B251" s="4" t="inlineStr">
+        <is>
+          <t>14:15:00</t>
+        </is>
+      </c>
+      <c r="C251" s="4" t="inlineStr">
+        <is>
+          <t>14:15</t>
+        </is>
+      </c>
+      <c r="D251" s="4" t="inlineStr"/>
+      <c r="E251" s="4" t="inlineStr"/>
+      <c r="F251" s="4" t="inlineStr"/>
+      <c r="G251" s="4" t="inlineStr"/>
+      <c r="H251" s="4" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="I251" s="4" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="J251" s="4" t="inlineStr"/>
+      <c r="K251" s="4" t="inlineStr"/>
+      <c r="L251" s="4" t="inlineStr"/>
+      <c r="M251" s="4" t="inlineStr"/>
+      <c r="N251" s="4" t="inlineStr"/>
+      <c r="O251" s="4" t="inlineStr"/>
+      <c r="P251" s="4" t="inlineStr">
+        <is>
+          <t>Failed to fetch data: Failed to fetch quote data after all retries</t>
+        </is>
+      </c>
+    </row>
+    <row r="252">
+      <c r="A252" s="4" t="inlineStr">
+        <is>
+          <t>2026-03-03 14:20:00</t>
+        </is>
+      </c>
+      <c r="B252" s="4" t="inlineStr">
+        <is>
+          <t>14:20:00</t>
+        </is>
+      </c>
+      <c r="C252" s="4" t="inlineStr">
+        <is>
+          <t>14:20</t>
+        </is>
+      </c>
+      <c r="D252" s="4" t="inlineStr"/>
+      <c r="E252" s="4" t="inlineStr"/>
+      <c r="F252" s="4" t="inlineStr"/>
+      <c r="G252" s="4" t="inlineStr"/>
+      <c r="H252" s="4" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="I252" s="4" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="J252" s="4" t="inlineStr"/>
+      <c r="K252" s="4" t="inlineStr"/>
+      <c r="L252" s="4" t="inlineStr"/>
+      <c r="M252" s="4" t="inlineStr"/>
+      <c r="N252" s="4" t="inlineStr"/>
+      <c r="O252" s="4" t="inlineStr"/>
+      <c r="P252" s="4" t="inlineStr">
+        <is>
+          <t>Data fetch failed: Failed to fetch quote data after all retries</t>
+        </is>
+      </c>
+    </row>
+    <row r="253">
+      <c r="A253" s="4" t="inlineStr">
+        <is>
+          <t>2026-03-03 14:20:00</t>
+        </is>
+      </c>
+      <c r="B253" s="4" t="inlineStr">
+        <is>
+          <t>14:20:00</t>
+        </is>
+      </c>
+      <c r="C253" s="4" t="inlineStr">
+        <is>
+          <t>14:20</t>
+        </is>
+      </c>
+      <c r="D253" s="4" t="inlineStr"/>
+      <c r="E253" s="4" t="inlineStr"/>
+      <c r="F253" s="4" t="inlineStr"/>
+      <c r="G253" s="4" t="inlineStr"/>
+      <c r="H253" s="4" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="I253" s="4" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="J253" s="4" t="inlineStr"/>
+      <c r="K253" s="4" t="inlineStr"/>
+      <c r="L253" s="4" t="inlineStr"/>
+      <c r="M253" s="4" t="inlineStr"/>
+      <c r="N253" s="4" t="inlineStr"/>
+      <c r="O253" s="4" t="inlineStr"/>
+      <c r="P253" s="4" t="inlineStr">
+        <is>
+          <t>Failed to fetch data: Failed to fetch quote data after all retries</t>
+        </is>
+      </c>
+    </row>
+    <row r="254">
+      <c r="A254" s="4" t="inlineStr">
+        <is>
+          <t>2026-03-03 14:25:00</t>
+        </is>
+      </c>
+      <c r="B254" s="4" t="inlineStr">
+        <is>
+          <t>14:25:00</t>
+        </is>
+      </c>
+      <c r="C254" s="4" t="inlineStr">
+        <is>
+          <t>14:25</t>
+        </is>
+      </c>
+      <c r="D254" s="4" t="inlineStr"/>
+      <c r="E254" s="4" t="inlineStr"/>
+      <c r="F254" s="4" t="inlineStr"/>
+      <c r="G254" s="4" t="inlineStr"/>
+      <c r="H254" s="4" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="I254" s="4" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="J254" s="4" t="inlineStr"/>
+      <c r="K254" s="4" t="inlineStr"/>
+      <c r="L254" s="4" t="inlineStr"/>
+      <c r="M254" s="4" t="inlineStr"/>
+      <c r="N254" s="4" t="inlineStr"/>
+      <c r="O254" s="4" t="inlineStr"/>
+      <c r="P254" s="4" t="inlineStr">
+        <is>
+          <t>Data fetch failed: Failed to fetch quote data after all retries</t>
+        </is>
+      </c>
+    </row>
+    <row r="255">
+      <c r="A255" s="4" t="inlineStr">
+        <is>
+          <t>2026-03-03 14:25:00</t>
+        </is>
+      </c>
+      <c r="B255" s="4" t="inlineStr">
+        <is>
+          <t>14:25:00</t>
+        </is>
+      </c>
+      <c r="C255" s="4" t="inlineStr">
+        <is>
+          <t>14:25</t>
+        </is>
+      </c>
+      <c r="D255" s="4" t="inlineStr"/>
+      <c r="E255" s="4" t="inlineStr"/>
+      <c r="F255" s="4" t="inlineStr"/>
+      <c r="G255" s="4" t="inlineStr"/>
+      <c r="H255" s="4" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="I255" s="4" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="J255" s="4" t="inlineStr"/>
+      <c r="K255" s="4" t="inlineStr"/>
+      <c r="L255" s="4" t="inlineStr"/>
+      <c r="M255" s="4" t="inlineStr"/>
+      <c r="N255" s="4" t="inlineStr"/>
+      <c r="O255" s="4" t="inlineStr"/>
+      <c r="P255" s="4" t="inlineStr">
+        <is>
+          <t>Failed to fetch data: Failed to fetch quote data after all retries</t>
+        </is>
+      </c>
+    </row>
+    <row r="256">
+      <c r="A256" s="4" t="inlineStr">
+        <is>
+          <t>2026-03-03 14:30:00</t>
+        </is>
+      </c>
+      <c r="B256" s="4" t="inlineStr">
+        <is>
+          <t>14:30:00</t>
+        </is>
+      </c>
+      <c r="C256" s="4" t="inlineStr">
+        <is>
+          <t>14:30</t>
+        </is>
+      </c>
+      <c r="D256" s="4" t="inlineStr"/>
+      <c r="E256" s="4" t="inlineStr"/>
+      <c r="F256" s="4" t="inlineStr"/>
+      <c r="G256" s="4" t="inlineStr"/>
+      <c r="H256" s="4" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="I256" s="4" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="J256" s="4" t="inlineStr"/>
+      <c r="K256" s="4" t="inlineStr"/>
+      <c r="L256" s="4" t="inlineStr"/>
+      <c r="M256" s="4" t="inlineStr"/>
+      <c r="N256" s="4" t="inlineStr"/>
+      <c r="O256" s="4" t="inlineStr"/>
+      <c r="P256" s="4" t="inlineStr">
+        <is>
+          <t>Data fetch failed: Failed to fetch quote data after all retries</t>
+        </is>
+      </c>
+    </row>
+    <row r="257">
+      <c r="A257" s="4" t="inlineStr">
+        <is>
+          <t>2026-03-03 14:30:00</t>
+        </is>
+      </c>
+      <c r="B257" s="4" t="inlineStr">
+        <is>
+          <t>14:30:00</t>
+        </is>
+      </c>
+      <c r="C257" s="4" t="inlineStr">
+        <is>
+          <t>14:30</t>
+        </is>
+      </c>
+      <c r="D257" s="4" t="inlineStr"/>
+      <c r="E257" s="4" t="inlineStr"/>
+      <c r="F257" s="4" t="inlineStr"/>
+      <c r="G257" s="4" t="inlineStr"/>
+      <c r="H257" s="4" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="I257" s="4" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="J257" s="4" t="inlineStr"/>
+      <c r="K257" s="4" t="inlineStr"/>
+      <c r="L257" s="4" t="inlineStr"/>
+      <c r="M257" s="4" t="inlineStr"/>
+      <c r="N257" s="4" t="inlineStr"/>
+      <c r="O257" s="4" t="inlineStr"/>
+      <c r="P257" s="4" t="inlineStr">
+        <is>
+          <t>Failed to fetch data: Failed to fetch quote data after all retries</t>
+        </is>
+      </c>
+    </row>
+    <row r="258">
+      <c r="A258" s="4" t="inlineStr">
+        <is>
+          <t>2026-03-03 14:35:00</t>
+        </is>
+      </c>
+      <c r="B258" s="4" t="inlineStr">
+        <is>
+          <t>14:35:00</t>
+        </is>
+      </c>
+      <c r="C258" s="4" t="inlineStr">
+        <is>
+          <t>14:35</t>
+        </is>
+      </c>
+      <c r="D258" s="4" t="inlineStr"/>
+      <c r="E258" s="4" t="inlineStr"/>
+      <c r="F258" s="4" t="inlineStr"/>
+      <c r="G258" s="4" t="inlineStr"/>
+      <c r="H258" s="4" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="I258" s="4" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="J258" s="4" t="inlineStr"/>
+      <c r="K258" s="4" t="inlineStr"/>
+      <c r="L258" s="4" t="inlineStr"/>
+      <c r="M258" s="4" t="inlineStr"/>
+      <c r="N258" s="4" t="inlineStr"/>
+      <c r="O258" s="4" t="inlineStr"/>
+      <c r="P258" s="4" t="inlineStr">
+        <is>
+          <t>Data fetch failed: Failed to fetch quote data after all retries</t>
+        </is>
+      </c>
+    </row>
+    <row r="259">
+      <c r="A259" s="4" t="inlineStr">
+        <is>
+          <t>2026-03-03 14:35:00</t>
+        </is>
+      </c>
+      <c r="B259" s="4" t="inlineStr">
+        <is>
+          <t>14:35:00</t>
+        </is>
+      </c>
+      <c r="C259" s="4" t="inlineStr">
+        <is>
+          <t>14:35</t>
+        </is>
+      </c>
+      <c r="D259" s="4" t="inlineStr"/>
+      <c r="E259" s="4" t="inlineStr"/>
+      <c r="F259" s="4" t="inlineStr"/>
+      <c r="G259" s="4" t="inlineStr"/>
+      <c r="H259" s="4" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="I259" s="4" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="J259" s="4" t="inlineStr"/>
+      <c r="K259" s="4" t="inlineStr"/>
+      <c r="L259" s="4" t="inlineStr"/>
+      <c r="M259" s="4" t="inlineStr"/>
+      <c r="N259" s="4" t="inlineStr"/>
+      <c r="O259" s="4" t="inlineStr"/>
+      <c r="P259" s="4" t="inlineStr">
+        <is>
+          <t>Failed to fetch data: Failed to fetch quote data after all retries</t>
+        </is>
+      </c>
+    </row>
+    <row r="260">
+      <c r="A260" s="4" t="inlineStr">
+        <is>
+          <t>2026-03-03 14:40:00</t>
+        </is>
+      </c>
+      <c r="B260" s="4" t="inlineStr">
+        <is>
+          <t>14:40:00</t>
+        </is>
+      </c>
+      <c r="C260" s="4" t="inlineStr">
+        <is>
+          <t>14:40</t>
+        </is>
+      </c>
+      <c r="D260" s="4" t="inlineStr"/>
+      <c r="E260" s="4" t="inlineStr"/>
+      <c r="F260" s="4" t="inlineStr"/>
+      <c r="G260" s="4" t="inlineStr"/>
+      <c r="H260" s="4" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="I260" s="4" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="J260" s="4" t="inlineStr"/>
+      <c r="K260" s="4" t="inlineStr"/>
+      <c r="L260" s="4" t="inlineStr"/>
+      <c r="M260" s="4" t="inlineStr"/>
+      <c r="N260" s="4" t="inlineStr"/>
+      <c r="O260" s="4" t="inlineStr"/>
+      <c r="P260" s="4" t="inlineStr">
+        <is>
+          <t>Data fetch failed: Failed to fetch quote data after all retries</t>
+        </is>
+      </c>
+    </row>
+    <row r="261">
+      <c r="A261" s="4" t="inlineStr">
+        <is>
+          <t>2026-03-03 14:40:00</t>
+        </is>
+      </c>
+      <c r="B261" s="4" t="inlineStr">
+        <is>
+          <t>14:40:00</t>
+        </is>
+      </c>
+      <c r="C261" s="4" t="inlineStr">
+        <is>
+          <t>14:40</t>
+        </is>
+      </c>
+      <c r="D261" s="4" t="inlineStr"/>
+      <c r="E261" s="4" t="inlineStr"/>
+      <c r="F261" s="4" t="inlineStr"/>
+      <c r="G261" s="4" t="inlineStr"/>
+      <c r="H261" s="4" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="I261" s="4" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="J261" s="4" t="inlineStr"/>
+      <c r="K261" s="4" t="inlineStr"/>
+      <c r="L261" s="4" t="inlineStr"/>
+      <c r="M261" s="4" t="inlineStr"/>
+      <c r="N261" s="4" t="inlineStr"/>
+      <c r="O261" s="4" t="inlineStr"/>
+      <c r="P261" s="4" t="inlineStr">
+        <is>
+          <t>Failed to fetch data: Failed to fetch quote data after all retries</t>
+        </is>
+      </c>
+    </row>
+    <row r="262">
+      <c r="A262" s="4" t="inlineStr">
+        <is>
+          <t>2026-03-03 14:45:00</t>
+        </is>
+      </c>
+      <c r="B262" s="4" t="inlineStr">
+        <is>
+          <t>14:45:00</t>
+        </is>
+      </c>
+      <c r="C262" s="4" t="inlineStr">
+        <is>
+          <t>14:45</t>
+        </is>
+      </c>
+      <c r="D262" s="4" t="inlineStr"/>
+      <c r="E262" s="4" t="inlineStr"/>
+      <c r="F262" s="4" t="inlineStr"/>
+      <c r="G262" s="4" t="inlineStr"/>
+      <c r="H262" s="4" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="I262" s="4" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="J262" s="4" t="inlineStr"/>
+      <c r="K262" s="4" t="inlineStr"/>
+      <c r="L262" s="4" t="inlineStr"/>
+      <c r="M262" s="4" t="inlineStr"/>
+      <c r="N262" s="4" t="inlineStr"/>
+      <c r="O262" s="4" t="inlineStr"/>
+      <c r="P262" s="4" t="inlineStr">
+        <is>
+          <t>Data fetch failed: Failed to fetch quote data after all retries</t>
+        </is>
+      </c>
+    </row>
+    <row r="263">
+      <c r="A263" s="4" t="inlineStr">
+        <is>
+          <t>2026-03-03 14:45:00</t>
+        </is>
+      </c>
+      <c r="B263" s="4" t="inlineStr">
+        <is>
+          <t>14:45:00</t>
+        </is>
+      </c>
+      <c r="C263" s="4" t="inlineStr">
+        <is>
+          <t>14:45</t>
+        </is>
+      </c>
+      <c r="D263" s="4" t="inlineStr"/>
+      <c r="E263" s="4" t="inlineStr"/>
+      <c r="F263" s="4" t="inlineStr"/>
+      <c r="G263" s="4" t="inlineStr"/>
+      <c r="H263" s="4" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="I263" s="4" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="J263" s="4" t="inlineStr"/>
+      <c r="K263" s="4" t="inlineStr"/>
+      <c r="L263" s="4" t="inlineStr"/>
+      <c r="M263" s="4" t="inlineStr"/>
+      <c r="N263" s="4" t="inlineStr"/>
+      <c r="O263" s="4" t="inlineStr"/>
+      <c r="P263" s="4" t="inlineStr">
+        <is>
+          <t>Failed to fetch data: Failed to fetch quote data after all retries</t>
+        </is>
+      </c>
+    </row>
+    <row r="264">
+      <c r="A264" s="4" t="inlineStr">
+        <is>
+          <t>2026-03-03 14:50:00</t>
+        </is>
+      </c>
+      <c r="B264" s="4" t="inlineStr">
+        <is>
+          <t>14:50:00</t>
+        </is>
+      </c>
+      <c r="C264" s="4" t="inlineStr">
+        <is>
+          <t>14:50</t>
+        </is>
+      </c>
+      <c r="D264" s="4" t="inlineStr"/>
+      <c r="E264" s="4" t="inlineStr"/>
+      <c r="F264" s="4" t="inlineStr"/>
+      <c r="G264" s="4" t="inlineStr"/>
+      <c r="H264" s="4" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="I264" s="4" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="J264" s="4" t="inlineStr"/>
+      <c r="K264" s="4" t="inlineStr"/>
+      <c r="L264" s="4" t="inlineStr"/>
+      <c r="M264" s="4" t="inlineStr"/>
+      <c r="N264" s="4" t="inlineStr"/>
+      <c r="O264" s="4" t="inlineStr"/>
+      <c r="P264" s="4" t="inlineStr">
+        <is>
+          <t>Data fetch failed: Failed to fetch quote data after all retries</t>
+        </is>
+      </c>
+    </row>
+    <row r="265">
+      <c r="A265" s="4" t="inlineStr">
+        <is>
+          <t>2026-03-03 14:50:00</t>
+        </is>
+      </c>
+      <c r="B265" s="4" t="inlineStr">
+        <is>
+          <t>14:50:00</t>
+        </is>
+      </c>
+      <c r="C265" s="4" t="inlineStr">
+        <is>
+          <t>14:50</t>
+        </is>
+      </c>
+      <c r="D265" s="4" t="inlineStr"/>
+      <c r="E265" s="4" t="inlineStr"/>
+      <c r="F265" s="4" t="inlineStr"/>
+      <c r="G265" s="4" t="inlineStr"/>
+      <c r="H265" s="4" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="I265" s="4" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="J265" s="4" t="inlineStr"/>
+      <c r="K265" s="4" t="inlineStr"/>
+      <c r="L265" s="4" t="inlineStr"/>
+      <c r="M265" s="4" t="inlineStr"/>
+      <c r="N265" s="4" t="inlineStr"/>
+      <c r="O265" s="4" t="inlineStr"/>
+      <c r="P265" s="4" t="inlineStr">
+        <is>
+          <t>Failed to fetch data: Failed to fetch quote data after all retries</t>
+        </is>
+      </c>
+    </row>
+    <row r="266">
+      <c r="A266" s="4" t="inlineStr">
+        <is>
+          <t>2026-03-03 14:55:00</t>
+        </is>
+      </c>
+      <c r="B266" s="4" t="inlineStr">
+        <is>
+          <t>14:55:00</t>
+        </is>
+      </c>
+      <c r="C266" s="4" t="inlineStr">
+        <is>
+          <t>14:55</t>
+        </is>
+      </c>
+      <c r="D266" s="4" t="inlineStr"/>
+      <c r="E266" s="4" t="inlineStr"/>
+      <c r="F266" s="4" t="inlineStr"/>
+      <c r="G266" s="4" t="inlineStr"/>
+      <c r="H266" s="4" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="I266" s="4" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="J266" s="4" t="inlineStr"/>
+      <c r="K266" s="4" t="inlineStr"/>
+      <c r="L266" s="4" t="inlineStr"/>
+      <c r="M266" s="4" t="inlineStr"/>
+      <c r="N266" s="4" t="inlineStr"/>
+      <c r="O266" s="4" t="inlineStr"/>
+      <c r="P266" s="4" t="inlineStr">
+        <is>
+          <t>Data fetch failed: Failed to fetch quote data after all retries</t>
+        </is>
+      </c>
+    </row>
+    <row r="267">
+      <c r="A267" s="4" t="inlineStr">
+        <is>
+          <t>2026-03-03 14:55:00</t>
+        </is>
+      </c>
+      <c r="B267" s="4" t="inlineStr">
+        <is>
+          <t>14:55:00</t>
+        </is>
+      </c>
+      <c r="C267" s="4" t="inlineStr">
+        <is>
+          <t>14:55</t>
+        </is>
+      </c>
+      <c r="D267" s="4" t="inlineStr"/>
+      <c r="E267" s="4" t="inlineStr"/>
+      <c r="F267" s="4" t="inlineStr"/>
+      <c r="G267" s="4" t="inlineStr"/>
+      <c r="H267" s="4" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="I267" s="4" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="J267" s="4" t="inlineStr"/>
+      <c r="K267" s="4" t="inlineStr"/>
+      <c r="L267" s="4" t="inlineStr"/>
+      <c r="M267" s="4" t="inlineStr"/>
+      <c r="N267" s="4" t="inlineStr"/>
+      <c r="O267" s="4" t="inlineStr"/>
+      <c r="P267" s="4" t="inlineStr">
+        <is>
+          <t>Failed to fetch data: Failed to fetch quote data after all retries</t>
+        </is>
+      </c>
+    </row>
+    <row r="268">
+      <c r="A268" s="4" t="inlineStr">
+        <is>
+          <t>2026-03-03 15:00:00</t>
+        </is>
+      </c>
+      <c r="B268" s="4" t="inlineStr">
+        <is>
+          <t>15:00:00</t>
+        </is>
+      </c>
+      <c r="C268" s="4" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="D268" s="4" t="inlineStr"/>
+      <c r="E268" s="4" t="inlineStr"/>
+      <c r="F268" s="4" t="inlineStr"/>
+      <c r="G268" s="4" t="inlineStr"/>
+      <c r="H268" s="4" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="I268" s="4" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="J268" s="4" t="inlineStr"/>
+      <c r="K268" s="4" t="inlineStr"/>
+      <c r="L268" s="4" t="inlineStr"/>
+      <c r="M268" s="4" t="inlineStr"/>
+      <c r="N268" s="4" t="inlineStr"/>
+      <c r="O268" s="4" t="inlineStr"/>
+      <c r="P268" s="4" t="inlineStr">
+        <is>
+          <t>Data fetch failed: Failed to fetch quote data after all retries</t>
+        </is>
+      </c>
+    </row>
+    <row r="269">
+      <c r="A269" s="4" t="inlineStr">
+        <is>
+          <t>2026-03-03 15:00:00</t>
+        </is>
+      </c>
+      <c r="B269" s="4" t="inlineStr">
+        <is>
+          <t>15:00:00</t>
+        </is>
+      </c>
+      <c r="C269" s="4" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="D269" s="4" t="inlineStr"/>
+      <c r="E269" s="4" t="inlineStr"/>
+      <c r="F269" s="4" t="inlineStr"/>
+      <c r="G269" s="4" t="inlineStr"/>
+      <c r="H269" s="4" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="I269" s="4" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="J269" s="4" t="inlineStr"/>
+      <c r="K269" s="4" t="inlineStr"/>
+      <c r="L269" s="4" t="inlineStr"/>
+      <c r="M269" s="4" t="inlineStr"/>
+      <c r="N269" s="4" t="inlineStr"/>
+      <c r="O269" s="4" t="inlineStr"/>
+      <c r="P269" s="4" t="inlineStr">
         <is>
           <t>Failed to fetch data: Failed to fetch quote data after all retries</t>
         </is>

--- a/Mine/logs/mine_signal_logs.xlsx
+++ b/Mine/logs/mine_signal_logs.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="880" yWindow="780" windowWidth="33320" windowHeight="21460" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="880" yWindow="780" windowWidth="33320" windowHeight="21460" tabRatio="600" firstSheet="0" activeTab="1" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet name="Signal Checks" sheetId="1" state="visible" r:id="rId1"/>
@@ -27,12 +27,14 @@
     </font>
     <font>
       <name val="Calibri"/>
+      <family val="2"/>
       <b val="1"/>
       <color rgb="FFFFFFFF"/>
       <sz val="11"/>
     </font>
     <font>
       <name val="Calibri"/>
+      <family val="2"/>
       <b val="1"/>
       <color rgb="FFFFFFFF"/>
       <sz val="11"/>
@@ -527,7 +529,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P26"/>
+  <dimension ref="A1:P144"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -625,28 +627,28 @@
     <row r="2">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>2026-03-05 11:00:00</t>
+          <t>2026-03-09 15:05:00</t>
         </is>
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
-          <t>11:00:00</t>
+          <t>15:05:00</t>
         </is>
       </c>
       <c r="C2" s="3" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>15:05</t>
         </is>
       </c>
       <c r="D2" s="3" t="inlineStr">
         <is>
-          <t>320.55</t>
+          <t>358.65</t>
         </is>
       </c>
       <c r="E2" s="3" t="n"/>
       <c r="F2" s="3" t="inlineStr">
         <is>
-          <t>277.00</t>
+          <t>245.00</t>
         </is>
       </c>
       <c r="G2" s="3" t="n"/>
@@ -675,28 +677,28 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>2026-03-05 11:05:00</t>
+          <t>2026-03-09 15:10:00</t>
         </is>
       </c>
       <c r="B3" s="3" t="inlineStr">
         <is>
-          <t>11:05:00</t>
+          <t>15:10:00</t>
         </is>
       </c>
       <c r="C3" s="3" t="inlineStr">
         <is>
-          <t>11:05</t>
+          <t>15:10</t>
         </is>
       </c>
       <c r="D3" s="3" t="inlineStr">
         <is>
-          <t>275.20</t>
+          <t>226.05</t>
         </is>
       </c>
       <c r="E3" s="3" t="n"/>
       <c r="F3" s="3" t="inlineStr">
         <is>
-          <t>359.15</t>
+          <t>347.15</t>
         </is>
       </c>
       <c r="G3" s="3" t="n"/>
@@ -725,28 +727,28 @@
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>2026-03-05 11:05:00</t>
+          <t>2026-03-09 15:10:00</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>11:05:00</t>
+          <t>15:10:00</t>
         </is>
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
-          <t>11:05</t>
+          <t>15:10</t>
         </is>
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>320.55</t>
+          <t>358.65</t>
         </is>
       </c>
       <c r="E4" s="3" t="n"/>
       <c r="F4" s="3" t="inlineStr">
         <is>
-          <t>277.00</t>
+          <t>245.00</t>
         </is>
       </c>
       <c r="G4" s="3" t="n"/>
@@ -775,28 +777,28 @@
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>2026-03-05 11:10:00</t>
+          <t>2026-03-09 15:15:00</t>
         </is>
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>11:10:00</t>
+          <t>15:15:00</t>
         </is>
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t>11:10</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
-          <t>275.20</t>
+          <t>226.05</t>
         </is>
       </c>
       <c r="E5" s="3" t="n"/>
       <c r="F5" s="3" t="inlineStr">
         <is>
-          <t>359.15</t>
+          <t>347.15</t>
         </is>
       </c>
       <c r="G5" s="3" t="n"/>
@@ -825,28 +827,28 @@
     <row r="6">
       <c r="A6" s="3" t="inlineStr">
         <is>
-          <t>2026-03-05 11:10:00</t>
+          <t>2026-03-09 15:15:00</t>
         </is>
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>11:10:00</t>
+          <t>15:15:00</t>
         </is>
       </c>
       <c r="C6" s="3" t="inlineStr">
         <is>
-          <t>11:10</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="D6" s="3" t="inlineStr">
         <is>
-          <t>320.55</t>
+          <t>358.65</t>
         </is>
       </c>
       <c r="E6" s="3" t="n"/>
       <c r="F6" s="3" t="inlineStr">
         <is>
-          <t>277.00</t>
+          <t>245.00</t>
         </is>
       </c>
       <c r="G6" s="3" t="n"/>
@@ -875,34 +877,26 @@
     <row r="7">
       <c r="A7" s="5" t="inlineStr">
         <is>
-          <t>2026-03-06 09:25:00</t>
+          <t>2026-03-10 09:15:00</t>
         </is>
       </c>
       <c r="B7" s="5" t="inlineStr">
         <is>
-          <t>09:25:00</t>
+          <t>09:15:00</t>
         </is>
       </c>
       <c r="C7" s="5" t="inlineStr">
         <is>
-          <t>09:25</t>
-        </is>
-      </c>
-      <c r="D7" s="5" t="inlineStr">
-        <is>
-          <t>249.00</t>
-        </is>
-      </c>
+          <t>09:15</t>
+        </is>
+      </c>
+      <c r="D7" s="5" t="inlineStr"/>
       <c r="E7" s="5" t="inlineStr"/>
-      <c r="F7" s="5" t="inlineStr">
-        <is>
-          <t>274.95</t>
-        </is>
-      </c>
+      <c r="F7" s="5" t="inlineStr"/>
       <c r="G7" s="5" t="inlineStr"/>
-      <c r="H7" s="7" t="inlineStr">
-        <is>
-          <t>✓ YES</t>
+      <c r="H7" s="5" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
         </is>
       </c>
       <c r="I7" s="5" t="inlineStr">
@@ -910,61 +904,41 @@
           <t>✗ NO</t>
         </is>
       </c>
-      <c r="J7" s="5" t="inlineStr">
-        <is>
-          <t>234.40</t>
-        </is>
-      </c>
+      <c r="J7" s="5" t="inlineStr"/>
       <c r="K7" s="5" t="inlineStr"/>
-      <c r="L7" s="5" t="inlineStr">
-        <is>
-          <t>205.00</t>
-        </is>
-      </c>
+      <c r="L7" s="5" t="inlineStr"/>
       <c r="M7" s="5" t="inlineStr"/>
-      <c r="N7" s="5" t="inlineStr">
-        <is>
-          <t>293.20</t>
-        </is>
-      </c>
+      <c r="N7" s="5" t="inlineStr"/>
       <c r="O7" s="5" t="inlineStr"/>
       <c r="P7" s="5" t="inlineStr">
         <is>
-          <t>High Strike Check</t>
+          <t>Data fetch failed: Error fetching quote: Insufficient permission for that call.</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="5" t="inlineStr">
         <is>
-          <t>2026-03-06 09:25:00</t>
+          <t>2026-03-10 09:15:00</t>
         </is>
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
-          <t>09:25:00</t>
+          <t>09:15:00</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
         <is>
-          <t>09:25</t>
-        </is>
-      </c>
-      <c r="D8" s="5" t="inlineStr">
-        <is>
-          <t>249.00</t>
-        </is>
-      </c>
+          <t>09:15</t>
+        </is>
+      </c>
+      <c r="D8" s="5" t="inlineStr"/>
       <c r="E8" s="5" t="inlineStr"/>
-      <c r="F8" s="5" t="inlineStr">
-        <is>
-          <t>225.00</t>
-        </is>
-      </c>
+      <c r="F8" s="5" t="inlineStr"/>
       <c r="G8" s="5" t="inlineStr"/>
-      <c r="H8" s="7" t="inlineStr">
-        <is>
-          <t>✓ YES</t>
+      <c r="H8" s="5" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
         </is>
       </c>
       <c r="I8" s="5" t="inlineStr">
@@ -972,57 +946,37 @@
           <t>✗ NO</t>
         </is>
       </c>
-      <c r="J8" s="5" t="inlineStr">
-        <is>
-          <t>234.40</t>
-        </is>
-      </c>
+      <c r="J8" s="5" t="inlineStr"/>
       <c r="K8" s="5" t="inlineStr"/>
-      <c r="L8" s="5" t="inlineStr">
-        <is>
-          <t>205.00</t>
-        </is>
-      </c>
+      <c r="L8" s="5" t="inlineStr"/>
       <c r="M8" s="5" t="inlineStr"/>
-      <c r="N8" s="5" t="inlineStr">
-        <is>
-          <t>293.20</t>
-        </is>
-      </c>
+      <c r="N8" s="5" t="inlineStr"/>
       <c r="O8" s="5" t="inlineStr"/>
       <c r="P8" s="5" t="inlineStr">
         <is>
-          <t>Low Strike Check</t>
+          <t>Failed to fetch data: Error fetching quote: Insufficient permission for that call.</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="5" t="inlineStr">
         <is>
-          <t>2026-03-06 09:30:00</t>
+          <t>2026-03-10 09:20:00</t>
         </is>
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>09:30:00</t>
+          <t>09:20:00</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
         <is>
-          <t>09:30</t>
-        </is>
-      </c>
-      <c r="D9" s="5" t="inlineStr">
-        <is>
-          <t>198.00</t>
-        </is>
-      </c>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="D9" s="5" t="inlineStr"/>
       <c r="E9" s="5" t="inlineStr"/>
-      <c r="F9" s="5" t="inlineStr">
-        <is>
-          <t>274.95</t>
-        </is>
-      </c>
+      <c r="F9" s="5" t="inlineStr"/>
       <c r="G9" s="5" t="inlineStr"/>
       <c r="H9" s="5" t="inlineStr">
         <is>
@@ -1042,37 +996,29 @@
       <c r="O9" s="5" t="inlineStr"/>
       <c r="P9" s="5" t="inlineStr">
         <is>
-          <t>High Strike Check</t>
+          <t>Data fetch failed: Error fetching quote: Insufficient permission for that call.</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="5" t="inlineStr">
         <is>
-          <t>2026-03-06 09:30:00</t>
+          <t>2026-03-10 09:20:00</t>
         </is>
       </c>
       <c r="B10" s="5" t="inlineStr">
         <is>
-          <t>09:30:00</t>
+          <t>09:20:00</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
         <is>
-          <t>09:30</t>
-        </is>
-      </c>
-      <c r="D10" s="5" t="inlineStr">
-        <is>
-          <t>249.00</t>
-        </is>
-      </c>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="D10" s="5" t="inlineStr"/>
       <c r="E10" s="5" t="inlineStr"/>
-      <c r="F10" s="5" t="inlineStr">
-        <is>
-          <t>225.00</t>
-        </is>
-      </c>
+      <c r="F10" s="5" t="inlineStr"/>
       <c r="G10" s="5" t="inlineStr"/>
       <c r="H10" s="5" t="inlineStr">
         <is>
@@ -1092,37 +1038,29 @@
       <c r="O10" s="5" t="inlineStr"/>
       <c r="P10" s="5" t="inlineStr">
         <is>
-          <t>Low Strike Check</t>
+          <t>Failed to fetch data: Error fetching quote: Insufficient permission for that call.</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="5" t="inlineStr">
         <is>
-          <t>2026-03-06 09:35:00</t>
+          <t>2026-03-10 09:25:00</t>
         </is>
       </c>
       <c r="B11" s="5" t="inlineStr">
         <is>
-          <t>09:35:00</t>
+          <t>09:25:00</t>
         </is>
       </c>
       <c r="C11" s="5" t="inlineStr">
         <is>
-          <t>09:35</t>
-        </is>
-      </c>
-      <c r="D11" s="5" t="inlineStr">
-        <is>
-          <t>198.00</t>
-        </is>
-      </c>
+          <t>09:25</t>
+        </is>
+      </c>
+      <c r="D11" s="5" t="inlineStr"/>
       <c r="E11" s="5" t="inlineStr"/>
-      <c r="F11" s="5" t="inlineStr">
-        <is>
-          <t>274.95</t>
-        </is>
-      </c>
+      <c r="F11" s="5" t="inlineStr"/>
       <c r="G11" s="5" t="inlineStr"/>
       <c r="H11" s="5" t="inlineStr">
         <is>
@@ -1142,37 +1080,29 @@
       <c r="O11" s="5" t="inlineStr"/>
       <c r="P11" s="5" t="inlineStr">
         <is>
-          <t>High Strike Check</t>
+          <t>Data fetch failed: Error fetching quote: Insufficient permission for that call.</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="5" t="inlineStr">
         <is>
-          <t>2026-03-06 09:35:00</t>
+          <t>2026-03-10 09:25:00</t>
         </is>
       </c>
       <c r="B12" s="5" t="inlineStr">
         <is>
-          <t>09:35:00</t>
+          <t>09:25:00</t>
         </is>
       </c>
       <c r="C12" s="5" t="inlineStr">
         <is>
-          <t>09:35</t>
-        </is>
-      </c>
-      <c r="D12" s="5" t="inlineStr">
-        <is>
-          <t>249.00</t>
-        </is>
-      </c>
+          <t>09:25</t>
+        </is>
+      </c>
+      <c r="D12" s="5" t="inlineStr"/>
       <c r="E12" s="5" t="inlineStr"/>
-      <c r="F12" s="5" t="inlineStr">
-        <is>
-          <t>225.00</t>
-        </is>
-      </c>
+      <c r="F12" s="5" t="inlineStr"/>
       <c r="G12" s="5" t="inlineStr"/>
       <c r="H12" s="5" t="inlineStr">
         <is>
@@ -1192,37 +1122,29 @@
       <c r="O12" s="5" t="inlineStr"/>
       <c r="P12" s="5" t="inlineStr">
         <is>
-          <t>Low Strike Check</t>
+          <t>Failed to fetch data: Error fetching quote: Insufficient permission for that call.</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="5" t="inlineStr">
         <is>
-          <t>2026-03-06 09:40:00</t>
+          <t>2026-03-10 09:30:00</t>
         </is>
       </c>
       <c r="B13" s="5" t="inlineStr">
         <is>
-          <t>09:40:00</t>
+          <t>09:30:00</t>
         </is>
       </c>
       <c r="C13" s="5" t="inlineStr">
         <is>
-          <t>09:40</t>
-        </is>
-      </c>
-      <c r="D13" s="5" t="inlineStr">
-        <is>
-          <t>198.00</t>
-        </is>
-      </c>
+          <t>09:30</t>
+        </is>
+      </c>
+      <c r="D13" s="5" t="inlineStr"/>
       <c r="E13" s="5" t="inlineStr"/>
-      <c r="F13" s="5" t="inlineStr">
-        <is>
-          <t>274.95</t>
-        </is>
-      </c>
+      <c r="F13" s="5" t="inlineStr"/>
       <c r="G13" s="5" t="inlineStr"/>
       <c r="H13" s="5" t="inlineStr">
         <is>
@@ -1242,37 +1164,29 @@
       <c r="O13" s="5" t="inlineStr"/>
       <c r="P13" s="5" t="inlineStr">
         <is>
-          <t>High Strike Check</t>
+          <t>Data fetch failed: Error fetching quote: Insufficient permission for that call.</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="5" t="inlineStr">
         <is>
-          <t>2026-03-06 09:40:00</t>
+          <t>2026-03-10 09:30:00</t>
         </is>
       </c>
       <c r="B14" s="5" t="inlineStr">
         <is>
-          <t>09:40:00</t>
+          <t>09:30:00</t>
         </is>
       </c>
       <c r="C14" s="5" t="inlineStr">
         <is>
-          <t>09:40</t>
-        </is>
-      </c>
-      <c r="D14" s="5" t="inlineStr">
-        <is>
-          <t>249.00</t>
-        </is>
-      </c>
+          <t>09:30</t>
+        </is>
+      </c>
+      <c r="D14" s="5" t="inlineStr"/>
       <c r="E14" s="5" t="inlineStr"/>
-      <c r="F14" s="5" t="inlineStr">
-        <is>
-          <t>225.00</t>
-        </is>
-      </c>
+      <c r="F14" s="5" t="inlineStr"/>
       <c r="G14" s="5" t="inlineStr"/>
       <c r="H14" s="5" t="inlineStr">
         <is>
@@ -1292,37 +1206,29 @@
       <c r="O14" s="5" t="inlineStr"/>
       <c r="P14" s="5" t="inlineStr">
         <is>
-          <t>Low Strike Check</t>
+          <t>Failed to fetch data: Error fetching quote: Insufficient permission for that call.</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="5" t="inlineStr">
         <is>
-          <t>2026-03-06 09:45:00</t>
+          <t>2026-03-10 09:35:00</t>
         </is>
       </c>
       <c r="B15" s="5" t="inlineStr">
         <is>
-          <t>09:45:00</t>
+          <t>09:35:00</t>
         </is>
       </c>
       <c r="C15" s="5" t="inlineStr">
         <is>
-          <t>09:45</t>
-        </is>
-      </c>
-      <c r="D15" s="5" t="inlineStr">
-        <is>
-          <t>198.00</t>
-        </is>
-      </c>
+          <t>09:35</t>
+        </is>
+      </c>
+      <c r="D15" s="5" t="inlineStr"/>
       <c r="E15" s="5" t="inlineStr"/>
-      <c r="F15" s="5" t="inlineStr">
-        <is>
-          <t>274.95</t>
-        </is>
-      </c>
+      <c r="F15" s="5" t="inlineStr"/>
       <c r="G15" s="5" t="inlineStr"/>
       <c r="H15" s="5" t="inlineStr">
         <is>
@@ -1342,37 +1248,29 @@
       <c r="O15" s="5" t="inlineStr"/>
       <c r="P15" s="5" t="inlineStr">
         <is>
-          <t>High Strike Check</t>
+          <t>Data fetch failed: Error fetching quote: Insufficient permission for that call.</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="5" t="inlineStr">
         <is>
-          <t>2026-03-06 09:45:00</t>
+          <t>2026-03-10 09:35:00</t>
         </is>
       </c>
       <c r="B16" s="5" t="inlineStr">
         <is>
-          <t>09:45:00</t>
+          <t>09:35:00</t>
         </is>
       </c>
       <c r="C16" s="5" t="inlineStr">
         <is>
-          <t>09:45</t>
-        </is>
-      </c>
-      <c r="D16" s="5" t="inlineStr">
-        <is>
-          <t>249.00</t>
-        </is>
-      </c>
+          <t>09:35</t>
+        </is>
+      </c>
+      <c r="D16" s="5" t="inlineStr"/>
       <c r="E16" s="5" t="inlineStr"/>
-      <c r="F16" s="5" t="inlineStr">
-        <is>
-          <t>225.00</t>
-        </is>
-      </c>
+      <c r="F16" s="5" t="inlineStr"/>
       <c r="G16" s="5" t="inlineStr"/>
       <c r="H16" s="5" t="inlineStr">
         <is>
@@ -1392,37 +1290,29 @@
       <c r="O16" s="5" t="inlineStr"/>
       <c r="P16" s="5" t="inlineStr">
         <is>
-          <t>Low Strike Check</t>
+          <t>Failed to fetch data: Error fetching quote: Insufficient permission for that call.</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="5" t="inlineStr">
         <is>
-          <t>2026-03-06 09:50:00</t>
+          <t>2026-03-10 09:40:00</t>
         </is>
       </c>
       <c r="B17" s="5" t="inlineStr">
         <is>
-          <t>09:50:00</t>
+          <t>09:40:00</t>
         </is>
       </c>
       <c r="C17" s="5" t="inlineStr">
         <is>
-          <t>09:50</t>
-        </is>
-      </c>
-      <c r="D17" s="5" t="inlineStr">
-        <is>
-          <t>198.00</t>
-        </is>
-      </c>
+          <t>09:40</t>
+        </is>
+      </c>
+      <c r="D17" s="5" t="inlineStr"/>
       <c r="E17" s="5" t="inlineStr"/>
-      <c r="F17" s="5" t="inlineStr">
-        <is>
-          <t>274.95</t>
-        </is>
-      </c>
+      <c r="F17" s="5" t="inlineStr"/>
       <c r="G17" s="5" t="inlineStr"/>
       <c r="H17" s="5" t="inlineStr">
         <is>
@@ -1442,37 +1332,29 @@
       <c r="O17" s="5" t="inlineStr"/>
       <c r="P17" s="5" t="inlineStr">
         <is>
-          <t>High Strike Check</t>
+          <t>Data fetch failed: Error fetching quote: Insufficient permission for that call.</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="5" t="inlineStr">
         <is>
-          <t>2026-03-06 09:50:00</t>
+          <t>2026-03-10 09:40:00</t>
         </is>
       </c>
       <c r="B18" s="5" t="inlineStr">
         <is>
-          <t>09:50:00</t>
+          <t>09:40:00</t>
         </is>
       </c>
       <c r="C18" s="5" t="inlineStr">
         <is>
-          <t>09:50</t>
-        </is>
-      </c>
-      <c r="D18" s="5" t="inlineStr">
-        <is>
-          <t>249.00</t>
-        </is>
-      </c>
+          <t>09:40</t>
+        </is>
+      </c>
+      <c r="D18" s="5" t="inlineStr"/>
       <c r="E18" s="5" t="inlineStr"/>
-      <c r="F18" s="5" t="inlineStr">
-        <is>
-          <t>225.00</t>
-        </is>
-      </c>
+      <c r="F18" s="5" t="inlineStr"/>
       <c r="G18" s="5" t="inlineStr"/>
       <c r="H18" s="5" t="inlineStr">
         <is>
@@ -1492,37 +1374,29 @@
       <c r="O18" s="5" t="inlineStr"/>
       <c r="P18" s="5" t="inlineStr">
         <is>
-          <t>Low Strike Check</t>
+          <t>Failed to fetch data: Error fetching quote: Insufficient permission for that call.</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="5" t="inlineStr">
         <is>
-          <t>2026-03-06 09:55:00</t>
+          <t>2026-03-10 09:45:00</t>
         </is>
       </c>
       <c r="B19" s="5" t="inlineStr">
         <is>
-          <t>09:55:00</t>
+          <t>09:45:00</t>
         </is>
       </c>
       <c r="C19" s="5" t="inlineStr">
         <is>
-          <t>09:55</t>
-        </is>
-      </c>
-      <c r="D19" s="5" t="inlineStr">
-        <is>
-          <t>198.00</t>
-        </is>
-      </c>
+          <t>09:45</t>
+        </is>
+      </c>
+      <c r="D19" s="5" t="inlineStr"/>
       <c r="E19" s="5" t="inlineStr"/>
-      <c r="F19" s="5" t="inlineStr">
-        <is>
-          <t>274.95</t>
-        </is>
-      </c>
+      <c r="F19" s="5" t="inlineStr"/>
       <c r="G19" s="5" t="inlineStr"/>
       <c r="H19" s="5" t="inlineStr">
         <is>
@@ -1542,37 +1416,29 @@
       <c r="O19" s="5" t="inlineStr"/>
       <c r="P19" s="5" t="inlineStr">
         <is>
-          <t>High Strike Check</t>
+          <t>Data fetch failed: Error fetching quote: Insufficient permission for that call.</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="5" t="inlineStr">
         <is>
-          <t>2026-03-06 09:55:00</t>
+          <t>2026-03-10 09:45:00</t>
         </is>
       </c>
       <c r="B20" s="5" t="inlineStr">
         <is>
-          <t>09:55:00</t>
+          <t>09:45:00</t>
         </is>
       </c>
       <c r="C20" s="5" t="inlineStr">
         <is>
-          <t>09:55</t>
-        </is>
-      </c>
-      <c r="D20" s="5" t="inlineStr">
-        <is>
-          <t>249.00</t>
-        </is>
-      </c>
+          <t>09:45</t>
+        </is>
+      </c>
+      <c r="D20" s="5" t="inlineStr"/>
       <c r="E20" s="5" t="inlineStr"/>
-      <c r="F20" s="5" t="inlineStr">
-        <is>
-          <t>225.00</t>
-        </is>
-      </c>
+      <c r="F20" s="5" t="inlineStr"/>
       <c r="G20" s="5" t="inlineStr"/>
       <c r="H20" s="5" t="inlineStr">
         <is>
@@ -1592,37 +1458,29 @@
       <c r="O20" s="5" t="inlineStr"/>
       <c r="P20" s="5" t="inlineStr">
         <is>
-          <t>Low Strike Check</t>
+          <t>Failed to fetch data: Error fetching quote: Insufficient permission for that call.</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="5" t="inlineStr">
         <is>
-          <t>2026-03-06 10:00:00</t>
+          <t>2026-03-10 09:50:00</t>
         </is>
       </c>
       <c r="B21" s="5" t="inlineStr">
         <is>
-          <t>10:00:00</t>
+          <t>09:50:00</t>
         </is>
       </c>
       <c r="C21" s="5" t="inlineStr">
         <is>
-          <t>10:00</t>
-        </is>
-      </c>
-      <c r="D21" s="5" t="inlineStr">
-        <is>
-          <t>198.00</t>
-        </is>
-      </c>
+          <t>09:50</t>
+        </is>
+      </c>
+      <c r="D21" s="5" t="inlineStr"/>
       <c r="E21" s="5" t="inlineStr"/>
-      <c r="F21" s="5" t="inlineStr">
-        <is>
-          <t>274.95</t>
-        </is>
-      </c>
+      <c r="F21" s="5" t="inlineStr"/>
       <c r="G21" s="5" t="inlineStr"/>
       <c r="H21" s="5" t="inlineStr">
         <is>
@@ -1642,37 +1500,29 @@
       <c r="O21" s="5" t="inlineStr"/>
       <c r="P21" s="5" t="inlineStr">
         <is>
-          <t>High Strike Check</t>
+          <t>Data fetch failed: Error fetching quote: Insufficient permission for that call.</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="5" t="inlineStr">
         <is>
-          <t>2026-03-06 10:00:00</t>
+          <t>2026-03-10 09:50:00</t>
         </is>
       </c>
       <c r="B22" s="5" t="inlineStr">
         <is>
-          <t>10:00:00</t>
+          <t>09:50:00</t>
         </is>
       </c>
       <c r="C22" s="5" t="inlineStr">
         <is>
-          <t>10:00</t>
-        </is>
-      </c>
-      <c r="D22" s="5" t="inlineStr">
-        <is>
-          <t>249.00</t>
-        </is>
-      </c>
+          <t>09:50</t>
+        </is>
+      </c>
+      <c r="D22" s="5" t="inlineStr"/>
       <c r="E22" s="5" t="inlineStr"/>
-      <c r="F22" s="5" t="inlineStr">
-        <is>
-          <t>225.00</t>
-        </is>
-      </c>
+      <c r="F22" s="5" t="inlineStr"/>
       <c r="G22" s="5" t="inlineStr"/>
       <c r="H22" s="5" t="inlineStr">
         <is>
@@ -1692,41 +1542,33 @@
       <c r="O22" s="5" t="inlineStr"/>
       <c r="P22" s="5" t="inlineStr">
         <is>
-          <t>Low Strike Check</t>
+          <t>Failed to fetch data: Error fetching quote: Insufficient permission for that call.</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="5" t="inlineStr">
         <is>
-          <t>2026-03-06 10:05:00</t>
+          <t>2026-03-10 09:55:00</t>
         </is>
       </c>
       <c r="B23" s="5" t="inlineStr">
         <is>
-          <t>10:05:00</t>
+          <t>09:55:00</t>
         </is>
       </c>
       <c r="C23" s="5" t="inlineStr">
         <is>
-          <t>10:05</t>
-        </is>
-      </c>
-      <c r="D23" s="5" t="inlineStr">
-        <is>
-          <t>249.00</t>
-        </is>
-      </c>
+          <t>09:55</t>
+        </is>
+      </c>
+      <c r="D23" s="5" t="inlineStr"/>
       <c r="E23" s="5" t="inlineStr"/>
-      <c r="F23" s="5" t="inlineStr">
-        <is>
-          <t>274.95</t>
-        </is>
-      </c>
+      <c r="F23" s="5" t="inlineStr"/>
       <c r="G23" s="5" t="inlineStr"/>
-      <c r="H23" s="7" t="inlineStr">
-        <is>
-          <t>✓ YES</t>
+      <c r="H23" s="5" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
         </is>
       </c>
       <c r="I23" s="5" t="inlineStr">
@@ -1734,61 +1576,41 @@
           <t>✗ NO</t>
         </is>
       </c>
-      <c r="J23" s="5" t="inlineStr">
-        <is>
-          <t>238.70</t>
-        </is>
-      </c>
+      <c r="J23" s="5" t="inlineStr"/>
       <c r="K23" s="5" t="inlineStr"/>
-      <c r="L23" s="5" t="inlineStr">
-        <is>
-          <t>215.00</t>
-        </is>
-      </c>
+      <c r="L23" s="5" t="inlineStr"/>
       <c r="M23" s="5" t="inlineStr"/>
-      <c r="N23" s="5" t="inlineStr">
-        <is>
-          <t>286.10</t>
-        </is>
-      </c>
+      <c r="N23" s="5" t="inlineStr"/>
       <c r="O23" s="5" t="inlineStr"/>
       <c r="P23" s="5" t="inlineStr">
         <is>
-          <t>High Strike Check</t>
+          <t>Data fetch failed: Error fetching quote: Insufficient permission for that call.</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="5" t="inlineStr">
         <is>
-          <t>2026-03-06 10:05:00</t>
+          <t>2026-03-10 09:55:00</t>
         </is>
       </c>
       <c r="B24" s="5" t="inlineStr">
         <is>
-          <t>10:05:00</t>
+          <t>09:55:00</t>
         </is>
       </c>
       <c r="C24" s="5" t="inlineStr">
         <is>
-          <t>10:05</t>
-        </is>
-      </c>
-      <c r="D24" s="5" t="inlineStr">
-        <is>
-          <t>249.00</t>
-        </is>
-      </c>
+          <t>09:55</t>
+        </is>
+      </c>
+      <c r="D24" s="5" t="inlineStr"/>
       <c r="E24" s="5" t="inlineStr"/>
-      <c r="F24" s="5" t="inlineStr">
-        <is>
-          <t>225.00</t>
-        </is>
-      </c>
+      <c r="F24" s="5" t="inlineStr"/>
       <c r="G24" s="5" t="inlineStr"/>
-      <c r="H24" s="7" t="inlineStr">
-        <is>
-          <t>✓ YES</t>
+      <c r="H24" s="5" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
         </is>
       </c>
       <c r="I24" s="5" t="inlineStr">
@@ -1796,57 +1618,37 @@
           <t>✗ NO</t>
         </is>
       </c>
-      <c r="J24" s="5" t="inlineStr">
-        <is>
-          <t>238.70</t>
-        </is>
-      </c>
+      <c r="J24" s="5" t="inlineStr"/>
       <c r="K24" s="5" t="inlineStr"/>
-      <c r="L24" s="5" t="inlineStr">
-        <is>
-          <t>215.00</t>
-        </is>
-      </c>
+      <c r="L24" s="5" t="inlineStr"/>
       <c r="M24" s="5" t="inlineStr"/>
-      <c r="N24" s="5" t="inlineStr">
-        <is>
-          <t>286.10</t>
-        </is>
-      </c>
+      <c r="N24" s="5" t="inlineStr"/>
       <c r="O24" s="5" t="inlineStr"/>
       <c r="P24" s="5" t="inlineStr">
         <is>
-          <t>Low Strike Check</t>
+          <t>Failed to fetch data: Error fetching quote: Insufficient permission for that call.</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="5" t="inlineStr">
         <is>
-          <t>2026-03-06 10:10:00</t>
+          <t>2026-03-10 10:00:00</t>
         </is>
       </c>
       <c r="B25" s="5" t="inlineStr">
         <is>
-          <t>10:10:00</t>
+          <t>10:00:00</t>
         </is>
       </c>
       <c r="C25" s="5" t="inlineStr">
         <is>
-          <t>10:10</t>
-        </is>
-      </c>
-      <c r="D25" s="5" t="inlineStr">
-        <is>
-          <t>198.00</t>
-        </is>
-      </c>
+          <t>10:00</t>
+        </is>
+      </c>
+      <c r="D25" s="5" t="inlineStr"/>
       <c r="E25" s="5" t="inlineStr"/>
-      <c r="F25" s="5" t="inlineStr">
-        <is>
-          <t>274.95</t>
-        </is>
-      </c>
+      <c r="F25" s="5" t="inlineStr"/>
       <c r="G25" s="5" t="inlineStr"/>
       <c r="H25" s="5" t="inlineStr">
         <is>
@@ -1866,37 +1668,29 @@
       <c r="O25" s="5" t="inlineStr"/>
       <c r="P25" s="5" t="inlineStr">
         <is>
-          <t>High Strike Check</t>
+          <t>Data fetch failed: Error fetching quote: Insufficient permission for that call.</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="5" t="inlineStr">
         <is>
-          <t>2026-03-06 10:10:00</t>
+          <t>2026-03-10 10:00:00</t>
         </is>
       </c>
       <c r="B26" s="5" t="inlineStr">
         <is>
-          <t>10:10:00</t>
+          <t>10:00:00</t>
         </is>
       </c>
       <c r="C26" s="5" t="inlineStr">
         <is>
-          <t>10:10</t>
-        </is>
-      </c>
-      <c r="D26" s="5" t="inlineStr">
-        <is>
-          <t>249.00</t>
-        </is>
-      </c>
+          <t>10:00</t>
+        </is>
+      </c>
+      <c r="D26" s="5" t="inlineStr"/>
       <c r="E26" s="5" t="inlineStr"/>
-      <c r="F26" s="5" t="inlineStr">
-        <is>
-          <t>225.00</t>
-        </is>
-      </c>
+      <c r="F26" s="5" t="inlineStr"/>
       <c r="G26" s="5" t="inlineStr"/>
       <c r="H26" s="5" t="inlineStr">
         <is>
@@ -1916,7 +1710,5075 @@
       <c r="O26" s="5" t="inlineStr"/>
       <c r="P26" s="5" t="inlineStr">
         <is>
+          <t>Failed to fetch data: Error fetching quote: Insufficient permission for that call.</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="5" t="inlineStr">
+        <is>
+          <t>2026-03-10 10:05:00</t>
+        </is>
+      </c>
+      <c r="B27" s="5" t="inlineStr">
+        <is>
+          <t>10:05:00</t>
+        </is>
+      </c>
+      <c r="C27" s="5" t="inlineStr">
+        <is>
+          <t>10:05</t>
+        </is>
+      </c>
+      <c r="D27" s="5" t="inlineStr"/>
+      <c r="E27" s="5" t="inlineStr"/>
+      <c r="F27" s="5" t="inlineStr"/>
+      <c r="G27" s="5" t="inlineStr"/>
+      <c r="H27" s="5" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="I27" s="5" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="J27" s="5" t="inlineStr"/>
+      <c r="K27" s="5" t="inlineStr"/>
+      <c r="L27" s="5" t="inlineStr"/>
+      <c r="M27" s="5" t="inlineStr"/>
+      <c r="N27" s="5" t="inlineStr"/>
+      <c r="O27" s="5" t="inlineStr"/>
+      <c r="P27" s="5" t="inlineStr">
+        <is>
+          <t>Data fetch failed: Error fetching quote: Insufficient permission for that call.</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="5" t="inlineStr">
+        <is>
+          <t>2026-03-10 10:05:00</t>
+        </is>
+      </c>
+      <c r="B28" s="5" t="inlineStr">
+        <is>
+          <t>10:05:00</t>
+        </is>
+      </c>
+      <c r="C28" s="5" t="inlineStr">
+        <is>
+          <t>10:05</t>
+        </is>
+      </c>
+      <c r="D28" s="5" t="inlineStr"/>
+      <c r="E28" s="5" t="inlineStr"/>
+      <c r="F28" s="5" t="inlineStr"/>
+      <c r="G28" s="5" t="inlineStr"/>
+      <c r="H28" s="5" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="I28" s="5" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="J28" s="5" t="inlineStr"/>
+      <c r="K28" s="5" t="inlineStr"/>
+      <c r="L28" s="5" t="inlineStr"/>
+      <c r="M28" s="5" t="inlineStr"/>
+      <c r="N28" s="5" t="inlineStr"/>
+      <c r="O28" s="5" t="inlineStr"/>
+      <c r="P28" s="5" t="inlineStr">
+        <is>
+          <t>Failed to fetch data: Error fetching quote: Insufficient permission for that call.</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="5" t="inlineStr">
+        <is>
+          <t>2026-03-10 10:10:00</t>
+        </is>
+      </c>
+      <c r="B29" s="5" t="inlineStr">
+        <is>
+          <t>10:10:00</t>
+        </is>
+      </c>
+      <c r="C29" s="5" t="inlineStr">
+        <is>
+          <t>10:10</t>
+        </is>
+      </c>
+      <c r="D29" s="5" t="inlineStr"/>
+      <c r="E29" s="5" t="inlineStr"/>
+      <c r="F29" s="5" t="inlineStr"/>
+      <c r="G29" s="5" t="inlineStr"/>
+      <c r="H29" s="5" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="I29" s="5" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="J29" s="5" t="inlineStr"/>
+      <c r="K29" s="5" t="inlineStr"/>
+      <c r="L29" s="5" t="inlineStr"/>
+      <c r="M29" s="5" t="inlineStr"/>
+      <c r="N29" s="5" t="inlineStr"/>
+      <c r="O29" s="5" t="inlineStr"/>
+      <c r="P29" s="5" t="inlineStr">
+        <is>
+          <t>Data fetch failed: Error fetching quote: Insufficient permission for that call.</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="5" t="inlineStr">
+        <is>
+          <t>2026-03-10 10:10:00</t>
+        </is>
+      </c>
+      <c r="B30" s="5" t="inlineStr">
+        <is>
+          <t>10:10:00</t>
+        </is>
+      </c>
+      <c r="C30" s="5" t="inlineStr">
+        <is>
+          <t>10:10</t>
+        </is>
+      </c>
+      <c r="D30" s="5" t="inlineStr"/>
+      <c r="E30" s="5" t="inlineStr"/>
+      <c r="F30" s="5" t="inlineStr"/>
+      <c r="G30" s="5" t="inlineStr"/>
+      <c r="H30" s="5" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="I30" s="5" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="J30" s="5" t="inlineStr"/>
+      <c r="K30" s="5" t="inlineStr"/>
+      <c r="L30" s="5" t="inlineStr"/>
+      <c r="M30" s="5" t="inlineStr"/>
+      <c r="N30" s="5" t="inlineStr"/>
+      <c r="O30" s="5" t="inlineStr"/>
+      <c r="P30" s="5" t="inlineStr">
+        <is>
+          <t>Failed to fetch data: Error fetching quote: Insufficient permission for that call.</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="5" t="inlineStr">
+        <is>
+          <t>2026-03-10 10:20:00</t>
+        </is>
+      </c>
+      <c r="B31" s="5" t="inlineStr">
+        <is>
+          <t>10:20:00</t>
+        </is>
+      </c>
+      <c r="C31" s="5" t="inlineStr">
+        <is>
+          <t>10:20</t>
+        </is>
+      </c>
+      <c r="D31" s="5" t="inlineStr">
+        <is>
+          <t>202.60</t>
+        </is>
+      </c>
+      <c r="E31" s="5" t="inlineStr"/>
+      <c r="F31" s="5" t="inlineStr">
+        <is>
+          <t>189.90</t>
+        </is>
+      </c>
+      <c r="G31" s="5" t="inlineStr"/>
+      <c r="H31" s="7" t="inlineStr">
+        <is>
+          <t>✓ YES</t>
+        </is>
+      </c>
+      <c r="I31" s="5" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="J31" s="5" t="inlineStr">
+        <is>
+          <t>119.65</t>
+        </is>
+      </c>
+      <c r="K31" s="5" t="inlineStr"/>
+      <c r="L31" s="5" t="inlineStr">
+        <is>
+          <t>89.70</t>
+        </is>
+      </c>
+      <c r="M31" s="5" t="inlineStr"/>
+      <c r="N31" s="5" t="inlineStr">
+        <is>
+          <t>179.55</t>
+        </is>
+      </c>
+      <c r="O31" s="5" t="inlineStr"/>
+      <c r="P31" s="5" t="inlineStr">
+        <is>
+          <t>High Strike Check</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="5" t="inlineStr">
+        <is>
+          <t>2026-03-10 10:20:00</t>
+        </is>
+      </c>
+      <c r="B32" s="5" t="inlineStr">
+        <is>
+          <t>10:20:00</t>
+        </is>
+      </c>
+      <c r="C32" s="5" t="inlineStr">
+        <is>
+          <t>10:20</t>
+        </is>
+      </c>
+      <c r="D32" s="5" t="inlineStr">
+        <is>
+          <t>202.60</t>
+        </is>
+      </c>
+      <c r="E32" s="5" t="inlineStr"/>
+      <c r="F32" s="5" t="inlineStr">
+        <is>
+          <t>99.70</t>
+        </is>
+      </c>
+      <c r="G32" s="5" t="inlineStr"/>
+      <c r="H32" s="7" t="inlineStr">
+        <is>
+          <t>✓ YES</t>
+        </is>
+      </c>
+      <c r="I32" s="5" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="J32" s="5" t="inlineStr">
+        <is>
+          <t>119.65</t>
+        </is>
+      </c>
+      <c r="K32" s="5" t="inlineStr"/>
+      <c r="L32" s="5" t="inlineStr">
+        <is>
+          <t>89.70</t>
+        </is>
+      </c>
+      <c r="M32" s="5" t="inlineStr"/>
+      <c r="N32" s="5" t="inlineStr">
+        <is>
+          <t>179.55</t>
+        </is>
+      </c>
+      <c r="O32" s="5" t="inlineStr"/>
+      <c r="P32" s="5" t="inlineStr">
+        <is>
           <t>Low Strike Check</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="5" t="inlineStr">
+        <is>
+          <t>2026-03-10 10:25:00</t>
+        </is>
+      </c>
+      <c r="B33" s="5" t="inlineStr">
+        <is>
+          <t>10:25:00</t>
+        </is>
+      </c>
+      <c r="C33" s="5" t="inlineStr">
+        <is>
+          <t>10:25</t>
+        </is>
+      </c>
+      <c r="D33" s="5" t="inlineStr">
+        <is>
+          <t>99.35</t>
+        </is>
+      </c>
+      <c r="E33" s="5" t="inlineStr"/>
+      <c r="F33" s="5" t="inlineStr">
+        <is>
+          <t>189.90</t>
+        </is>
+      </c>
+      <c r="G33" s="5" t="inlineStr"/>
+      <c r="H33" s="5" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="I33" s="5" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="J33" s="5" t="inlineStr"/>
+      <c r="K33" s="5" t="inlineStr"/>
+      <c r="L33" s="5" t="inlineStr"/>
+      <c r="M33" s="5" t="inlineStr"/>
+      <c r="N33" s="5" t="inlineStr"/>
+      <c r="O33" s="5" t="inlineStr"/>
+      <c r="P33" s="5" t="inlineStr">
+        <is>
+          <t>High Strike Check</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="5" t="inlineStr">
+        <is>
+          <t>2026-03-10 10:25:00</t>
+        </is>
+      </c>
+      <c r="B34" s="5" t="inlineStr">
+        <is>
+          <t>10:25:00</t>
+        </is>
+      </c>
+      <c r="C34" s="5" t="inlineStr">
+        <is>
+          <t>10:25</t>
+        </is>
+      </c>
+      <c r="D34" s="5" t="inlineStr">
+        <is>
+          <t>202.60</t>
+        </is>
+      </c>
+      <c r="E34" s="5" t="inlineStr"/>
+      <c r="F34" s="5" t="inlineStr">
+        <is>
+          <t>99.70</t>
+        </is>
+      </c>
+      <c r="G34" s="5" t="inlineStr"/>
+      <c r="H34" s="5" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="I34" s="5" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="J34" s="5" t="inlineStr"/>
+      <c r="K34" s="5" t="inlineStr"/>
+      <c r="L34" s="5" t="inlineStr"/>
+      <c r="M34" s="5" t="inlineStr"/>
+      <c r="N34" s="5" t="inlineStr"/>
+      <c r="O34" s="5" t="inlineStr"/>
+      <c r="P34" s="5" t="inlineStr">
+        <is>
+          <t>Low Strike Check</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="5" t="inlineStr">
+        <is>
+          <t>2026-03-10 10:30:00</t>
+        </is>
+      </c>
+      <c r="B35" s="5" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="C35" s="5" t="inlineStr">
+        <is>
+          <t>10:30</t>
+        </is>
+      </c>
+      <c r="D35" s="5" t="inlineStr">
+        <is>
+          <t>99.35</t>
+        </is>
+      </c>
+      <c r="E35" s="5" t="inlineStr"/>
+      <c r="F35" s="5" t="inlineStr">
+        <is>
+          <t>189.90</t>
+        </is>
+      </c>
+      <c r="G35" s="5" t="inlineStr"/>
+      <c r="H35" s="5" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="I35" s="5" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="J35" s="5" t="inlineStr"/>
+      <c r="K35" s="5" t="inlineStr"/>
+      <c r="L35" s="5" t="inlineStr"/>
+      <c r="M35" s="5" t="inlineStr"/>
+      <c r="N35" s="5" t="inlineStr"/>
+      <c r="O35" s="5" t="inlineStr"/>
+      <c r="P35" s="5" t="inlineStr">
+        <is>
+          <t>High Strike Check</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="5" t="inlineStr">
+        <is>
+          <t>2026-03-10 10:30:00</t>
+        </is>
+      </c>
+      <c r="B36" s="5" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="C36" s="5" t="inlineStr">
+        <is>
+          <t>10:30</t>
+        </is>
+      </c>
+      <c r="D36" s="5" t="inlineStr">
+        <is>
+          <t>202.60</t>
+        </is>
+      </c>
+      <c r="E36" s="5" t="inlineStr"/>
+      <c r="F36" s="5" t="inlineStr">
+        <is>
+          <t>99.70</t>
+        </is>
+      </c>
+      <c r="G36" s="5" t="inlineStr"/>
+      <c r="H36" s="5" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="I36" s="5" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="J36" s="5" t="inlineStr"/>
+      <c r="K36" s="5" t="inlineStr"/>
+      <c r="L36" s="5" t="inlineStr"/>
+      <c r="M36" s="5" t="inlineStr"/>
+      <c r="N36" s="5" t="inlineStr"/>
+      <c r="O36" s="5" t="inlineStr"/>
+      <c r="P36" s="5" t="inlineStr">
+        <is>
+          <t>Low Strike Check</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="5" t="inlineStr">
+        <is>
+          <t>2026-03-10 10:35:00</t>
+        </is>
+      </c>
+      <c r="B37" s="5" t="inlineStr">
+        <is>
+          <t>10:35:00</t>
+        </is>
+      </c>
+      <c r="C37" s="5" t="inlineStr">
+        <is>
+          <t>10:35</t>
+        </is>
+      </c>
+      <c r="D37" s="5" t="inlineStr">
+        <is>
+          <t>202.60</t>
+        </is>
+      </c>
+      <c r="E37" s="5" t="inlineStr"/>
+      <c r="F37" s="5" t="inlineStr">
+        <is>
+          <t>189.90</t>
+        </is>
+      </c>
+      <c r="G37" s="5" t="inlineStr"/>
+      <c r="H37" s="7" t="inlineStr">
+        <is>
+          <t>✓ YES</t>
+        </is>
+      </c>
+      <c r="I37" s="5" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="J37" s="5" t="inlineStr">
+        <is>
+          <t>113.75</t>
+        </is>
+      </c>
+      <c r="K37" s="5" t="inlineStr"/>
+      <c r="L37" s="5" t="inlineStr">
+        <is>
+          <t>89.70</t>
+        </is>
+      </c>
+      <c r="M37" s="5" t="inlineStr"/>
+      <c r="N37" s="5" t="inlineStr">
+        <is>
+          <t>161.85</t>
+        </is>
+      </c>
+      <c r="O37" s="5" t="inlineStr"/>
+      <c r="P37" s="5" t="inlineStr">
+        <is>
+          <t>High Strike Check</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="5" t="inlineStr">
+        <is>
+          <t>2026-03-10 10:35:00</t>
+        </is>
+      </c>
+      <c r="B38" s="5" t="inlineStr">
+        <is>
+          <t>10:35:00</t>
+        </is>
+      </c>
+      <c r="C38" s="5" t="inlineStr">
+        <is>
+          <t>10:35</t>
+        </is>
+      </c>
+      <c r="D38" s="5" t="inlineStr">
+        <is>
+          <t>202.60</t>
+        </is>
+      </c>
+      <c r="E38" s="5" t="inlineStr"/>
+      <c r="F38" s="5" t="inlineStr">
+        <is>
+          <t>99.70</t>
+        </is>
+      </c>
+      <c r="G38" s="5" t="inlineStr"/>
+      <c r="H38" s="7" t="inlineStr">
+        <is>
+          <t>✓ YES</t>
+        </is>
+      </c>
+      <c r="I38" s="5" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="J38" s="5" t="inlineStr">
+        <is>
+          <t>113.75</t>
+        </is>
+      </c>
+      <c r="K38" s="5" t="inlineStr"/>
+      <c r="L38" s="5" t="inlineStr">
+        <is>
+          <t>89.70</t>
+        </is>
+      </c>
+      <c r="M38" s="5" t="inlineStr"/>
+      <c r="N38" s="5" t="inlineStr">
+        <is>
+          <t>161.85</t>
+        </is>
+      </c>
+      <c r="O38" s="5" t="inlineStr"/>
+      <c r="P38" s="5" t="inlineStr">
+        <is>
+          <t>Low Strike Check</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="5" t="inlineStr">
+        <is>
+          <t>2026-03-10 10:45:00</t>
+        </is>
+      </c>
+      <c r="B39" s="5" t="inlineStr">
+        <is>
+          <t>10:45:00</t>
+        </is>
+      </c>
+      <c r="C39" s="5" t="inlineStr">
+        <is>
+          <t>10:45</t>
+        </is>
+      </c>
+      <c r="D39" s="5" t="inlineStr"/>
+      <c r="E39" s="5" t="inlineStr"/>
+      <c r="F39" s="5" t="inlineStr"/>
+      <c r="G39" s="5" t="inlineStr"/>
+      <c r="H39" s="5" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="I39" s="5" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="J39" s="5" t="inlineStr"/>
+      <c r="K39" s="5" t="inlineStr"/>
+      <c r="L39" s="5" t="inlineStr"/>
+      <c r="M39" s="5" t="inlineStr"/>
+      <c r="N39" s="5" t="inlineStr"/>
+      <c r="O39" s="5" t="inlineStr"/>
+      <c r="P39" s="5" t="inlineStr">
+        <is>
+          <t>Data fetch failed: Error fetching quote: Insufficient permission for that call.. Please ensure you are logged in to the correct Zerodha account with a valid API subscription.</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="5" t="inlineStr">
+        <is>
+          <t>2026-03-10 10:45:00</t>
+        </is>
+      </c>
+      <c r="B40" s="5" t="inlineStr">
+        <is>
+          <t>10:45:00</t>
+        </is>
+      </c>
+      <c r="C40" s="5" t="inlineStr">
+        <is>
+          <t>10:45</t>
+        </is>
+      </c>
+      <c r="D40" s="5" t="inlineStr"/>
+      <c r="E40" s="5" t="inlineStr"/>
+      <c r="F40" s="5" t="inlineStr"/>
+      <c r="G40" s="5" t="inlineStr"/>
+      <c r="H40" s="5" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="I40" s="5" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="J40" s="5" t="inlineStr"/>
+      <c r="K40" s="5" t="inlineStr"/>
+      <c r="L40" s="5" t="inlineStr"/>
+      <c r="M40" s="5" t="inlineStr"/>
+      <c r="N40" s="5" t="inlineStr"/>
+      <c r="O40" s="5" t="inlineStr"/>
+      <c r="P40" s="5" t="inlineStr">
+        <is>
+          <t>Failed to fetch data: Error fetching quote: Insufficient permission for that call.. Please ensure you are logged in to the correct Zerodha account with a valid API subscription.</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="5" t="inlineStr">
+        <is>
+          <t>2026-03-10 10:50:00</t>
+        </is>
+      </c>
+      <c r="B41" s="5" t="inlineStr">
+        <is>
+          <t>10:50:00</t>
+        </is>
+      </c>
+      <c r="C41" s="5" t="inlineStr">
+        <is>
+          <t>10:50</t>
+        </is>
+      </c>
+      <c r="D41" s="5" t="inlineStr"/>
+      <c r="E41" s="5" t="inlineStr"/>
+      <c r="F41" s="5" t="inlineStr"/>
+      <c r="G41" s="5" t="inlineStr"/>
+      <c r="H41" s="5" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="I41" s="5" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="J41" s="5" t="inlineStr"/>
+      <c r="K41" s="5" t="inlineStr"/>
+      <c r="L41" s="5" t="inlineStr"/>
+      <c r="M41" s="5" t="inlineStr"/>
+      <c r="N41" s="5" t="inlineStr"/>
+      <c r="O41" s="5" t="inlineStr"/>
+      <c r="P41" s="5" t="inlineStr">
+        <is>
+          <t>Data fetch failed: Failed to fetch quote data after all retries</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="5" t="inlineStr">
+        <is>
+          <t>2026-03-10 10:50:00</t>
+        </is>
+      </c>
+      <c r="B42" s="5" t="inlineStr">
+        <is>
+          <t>10:50:00</t>
+        </is>
+      </c>
+      <c r="C42" s="5" t="inlineStr">
+        <is>
+          <t>10:50</t>
+        </is>
+      </c>
+      <c r="D42" s="5" t="inlineStr"/>
+      <c r="E42" s="5" t="inlineStr"/>
+      <c r="F42" s="5" t="inlineStr"/>
+      <c r="G42" s="5" t="inlineStr"/>
+      <c r="H42" s="5" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="I42" s="5" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="J42" s="5" t="inlineStr"/>
+      <c r="K42" s="5" t="inlineStr"/>
+      <c r="L42" s="5" t="inlineStr"/>
+      <c r="M42" s="5" t="inlineStr"/>
+      <c r="N42" s="5" t="inlineStr"/>
+      <c r="O42" s="5" t="inlineStr"/>
+      <c r="P42" s="5" t="inlineStr">
+        <is>
+          <t>Failed to fetch data: Failed to fetch quote data after all retries</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="5" t="inlineStr">
+        <is>
+          <t>2026-03-10 10:55:00</t>
+        </is>
+      </c>
+      <c r="B43" s="5" t="inlineStr">
+        <is>
+          <t>10:55:00</t>
+        </is>
+      </c>
+      <c r="C43" s="5" t="inlineStr">
+        <is>
+          <t>10:55</t>
+        </is>
+      </c>
+      <c r="D43" s="5" t="inlineStr"/>
+      <c r="E43" s="5" t="inlineStr"/>
+      <c r="F43" s="5" t="inlineStr"/>
+      <c r="G43" s="5" t="inlineStr"/>
+      <c r="H43" s="5" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="I43" s="5" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="J43" s="5" t="inlineStr"/>
+      <c r="K43" s="5" t="inlineStr"/>
+      <c r="L43" s="5" t="inlineStr"/>
+      <c r="M43" s="5" t="inlineStr"/>
+      <c r="N43" s="5" t="inlineStr"/>
+      <c r="O43" s="5" t="inlineStr"/>
+      <c r="P43" s="5" t="inlineStr">
+        <is>
+          <t>Data fetch failed: Failed to fetch quote data after all retries</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="5" t="inlineStr">
+        <is>
+          <t>2026-03-10 10:55:00</t>
+        </is>
+      </c>
+      <c r="B44" s="5" t="inlineStr">
+        <is>
+          <t>10:55:00</t>
+        </is>
+      </c>
+      <c r="C44" s="5" t="inlineStr">
+        <is>
+          <t>10:55</t>
+        </is>
+      </c>
+      <c r="D44" s="5" t="inlineStr"/>
+      <c r="E44" s="5" t="inlineStr"/>
+      <c r="F44" s="5" t="inlineStr"/>
+      <c r="G44" s="5" t="inlineStr"/>
+      <c r="H44" s="5" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="I44" s="5" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="J44" s="5" t="inlineStr"/>
+      <c r="K44" s="5" t="inlineStr"/>
+      <c r="L44" s="5" t="inlineStr"/>
+      <c r="M44" s="5" t="inlineStr"/>
+      <c r="N44" s="5" t="inlineStr"/>
+      <c r="O44" s="5" t="inlineStr"/>
+      <c r="P44" s="5" t="inlineStr">
+        <is>
+          <t>Failed to fetch data: Failed to fetch quote data after all retries</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="5" t="inlineStr">
+        <is>
+          <t>2026-03-10 11:00:00</t>
+        </is>
+      </c>
+      <c r="B45" s="5" t="inlineStr">
+        <is>
+          <t>11:00:00</t>
+        </is>
+      </c>
+      <c r="C45" s="5" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
+      <c r="D45" s="5" t="inlineStr"/>
+      <c r="E45" s="5" t="inlineStr"/>
+      <c r="F45" s="5" t="inlineStr"/>
+      <c r="G45" s="5" t="inlineStr"/>
+      <c r="H45" s="5" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="I45" s="5" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="J45" s="5" t="inlineStr"/>
+      <c r="K45" s="5" t="inlineStr"/>
+      <c r="L45" s="5" t="inlineStr"/>
+      <c r="M45" s="5" t="inlineStr"/>
+      <c r="N45" s="5" t="inlineStr"/>
+      <c r="O45" s="5" t="inlineStr"/>
+      <c r="P45" s="5" t="inlineStr">
+        <is>
+          <t>Data fetch failed: Failed to fetch quote data after all retries</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="5" t="inlineStr">
+        <is>
+          <t>2026-03-10 11:00:00</t>
+        </is>
+      </c>
+      <c r="B46" s="5" t="inlineStr">
+        <is>
+          <t>11:00:00</t>
+        </is>
+      </c>
+      <c r="C46" s="5" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
+      <c r="D46" s="5" t="inlineStr"/>
+      <c r="E46" s="5" t="inlineStr"/>
+      <c r="F46" s="5" t="inlineStr"/>
+      <c r="G46" s="5" t="inlineStr"/>
+      <c r="H46" s="5" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="I46" s="5" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="J46" s="5" t="inlineStr"/>
+      <c r="K46" s="5" t="inlineStr"/>
+      <c r="L46" s="5" t="inlineStr"/>
+      <c r="M46" s="5" t="inlineStr"/>
+      <c r="N46" s="5" t="inlineStr"/>
+      <c r="O46" s="5" t="inlineStr"/>
+      <c r="P46" s="5" t="inlineStr">
+        <is>
+          <t>Failed to fetch data: Failed to fetch quote data after all retries</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="5" t="inlineStr">
+        <is>
+          <t>2026-03-10 11:05:00</t>
+        </is>
+      </c>
+      <c r="B47" s="5" t="inlineStr">
+        <is>
+          <t>11:05:00</t>
+        </is>
+      </c>
+      <c r="C47" s="5" t="inlineStr">
+        <is>
+          <t>11:05</t>
+        </is>
+      </c>
+      <c r="D47" s="5" t="inlineStr"/>
+      <c r="E47" s="5" t="inlineStr"/>
+      <c r="F47" s="5" t="inlineStr"/>
+      <c r="G47" s="5" t="inlineStr"/>
+      <c r="H47" s="5" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="I47" s="5" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="J47" s="5" t="inlineStr"/>
+      <c r="K47" s="5" t="inlineStr"/>
+      <c r="L47" s="5" t="inlineStr"/>
+      <c r="M47" s="5" t="inlineStr"/>
+      <c r="N47" s="5" t="inlineStr"/>
+      <c r="O47" s="5" t="inlineStr"/>
+      <c r="P47" s="5" t="inlineStr">
+        <is>
+          <t>Data fetch failed: Failed to fetch quote data after all retries</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="5" t="inlineStr">
+        <is>
+          <t>2026-03-10 11:05:00</t>
+        </is>
+      </c>
+      <c r="B48" s="5" t="inlineStr">
+        <is>
+          <t>11:05:00</t>
+        </is>
+      </c>
+      <c r="C48" s="5" t="inlineStr">
+        <is>
+          <t>11:05</t>
+        </is>
+      </c>
+      <c r="D48" s="5" t="inlineStr"/>
+      <c r="E48" s="5" t="inlineStr"/>
+      <c r="F48" s="5" t="inlineStr"/>
+      <c r="G48" s="5" t="inlineStr"/>
+      <c r="H48" s="5" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="I48" s="5" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="J48" s="5" t="inlineStr"/>
+      <c r="K48" s="5" t="inlineStr"/>
+      <c r="L48" s="5" t="inlineStr"/>
+      <c r="M48" s="5" t="inlineStr"/>
+      <c r="N48" s="5" t="inlineStr"/>
+      <c r="O48" s="5" t="inlineStr"/>
+      <c r="P48" s="5" t="inlineStr">
+        <is>
+          <t>Failed to fetch data: Failed to fetch quote data after all retries</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="5" t="inlineStr">
+        <is>
+          <t>2026-03-10 11:10:00</t>
+        </is>
+      </c>
+      <c r="B49" s="5" t="inlineStr">
+        <is>
+          <t>11:10:00</t>
+        </is>
+      </c>
+      <c r="C49" s="5" t="inlineStr">
+        <is>
+          <t>11:10</t>
+        </is>
+      </c>
+      <c r="D49" s="5" t="inlineStr"/>
+      <c r="E49" s="5" t="inlineStr"/>
+      <c r="F49" s="5" t="inlineStr"/>
+      <c r="G49" s="5" t="inlineStr"/>
+      <c r="H49" s="5" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="I49" s="5" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="J49" s="5" t="inlineStr"/>
+      <c r="K49" s="5" t="inlineStr"/>
+      <c r="L49" s="5" t="inlineStr"/>
+      <c r="M49" s="5" t="inlineStr"/>
+      <c r="N49" s="5" t="inlineStr"/>
+      <c r="O49" s="5" t="inlineStr"/>
+      <c r="P49" s="5" t="inlineStr">
+        <is>
+          <t>Data fetch failed: Failed to fetch quote data after all retries</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="5" t="inlineStr">
+        <is>
+          <t>2026-03-10 11:10:00</t>
+        </is>
+      </c>
+      <c r="B50" s="5" t="inlineStr">
+        <is>
+          <t>11:10:00</t>
+        </is>
+      </c>
+      <c r="C50" s="5" t="inlineStr">
+        <is>
+          <t>11:10</t>
+        </is>
+      </c>
+      <c r="D50" s="5" t="inlineStr"/>
+      <c r="E50" s="5" t="inlineStr"/>
+      <c r="F50" s="5" t="inlineStr"/>
+      <c r="G50" s="5" t="inlineStr"/>
+      <c r="H50" s="5" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="I50" s="5" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="J50" s="5" t="inlineStr"/>
+      <c r="K50" s="5" t="inlineStr"/>
+      <c r="L50" s="5" t="inlineStr"/>
+      <c r="M50" s="5" t="inlineStr"/>
+      <c r="N50" s="5" t="inlineStr"/>
+      <c r="O50" s="5" t="inlineStr"/>
+      <c r="P50" s="5" t="inlineStr">
+        <is>
+          <t>Failed to fetch data: Failed to fetch quote data after all retries</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="5" t="inlineStr">
+        <is>
+          <t>2026-03-10 11:15:00</t>
+        </is>
+      </c>
+      <c r="B51" s="5" t="inlineStr">
+        <is>
+          <t>11:15:00</t>
+        </is>
+      </c>
+      <c r="C51" s="5" t="inlineStr">
+        <is>
+          <t>11:15</t>
+        </is>
+      </c>
+      <c r="D51" s="5" t="inlineStr"/>
+      <c r="E51" s="5" t="inlineStr"/>
+      <c r="F51" s="5" t="inlineStr"/>
+      <c r="G51" s="5" t="inlineStr"/>
+      <c r="H51" s="5" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="I51" s="5" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="J51" s="5" t="inlineStr"/>
+      <c r="K51" s="5" t="inlineStr"/>
+      <c r="L51" s="5" t="inlineStr"/>
+      <c r="M51" s="5" t="inlineStr"/>
+      <c r="N51" s="5" t="inlineStr"/>
+      <c r="O51" s="5" t="inlineStr"/>
+      <c r="P51" s="5" t="inlineStr">
+        <is>
+          <t>Data fetch failed: Failed to fetch quote data after all retries</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="5" t="inlineStr">
+        <is>
+          <t>2026-03-10 11:15:00</t>
+        </is>
+      </c>
+      <c r="B52" s="5" t="inlineStr">
+        <is>
+          <t>11:15:00</t>
+        </is>
+      </c>
+      <c r="C52" s="5" t="inlineStr">
+        <is>
+          <t>11:15</t>
+        </is>
+      </c>
+      <c r="D52" s="5" t="inlineStr"/>
+      <c r="E52" s="5" t="inlineStr"/>
+      <c r="F52" s="5" t="inlineStr"/>
+      <c r="G52" s="5" t="inlineStr"/>
+      <c r="H52" s="5" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="I52" s="5" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="J52" s="5" t="inlineStr"/>
+      <c r="K52" s="5" t="inlineStr"/>
+      <c r="L52" s="5" t="inlineStr"/>
+      <c r="M52" s="5" t="inlineStr"/>
+      <c r="N52" s="5" t="inlineStr"/>
+      <c r="O52" s="5" t="inlineStr"/>
+      <c r="P52" s="5" t="inlineStr">
+        <is>
+          <t>Failed to fetch data: Failed to fetch quote data after all retries</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="5" t="inlineStr">
+        <is>
+          <t>2026-03-10 11:20:00</t>
+        </is>
+      </c>
+      <c r="B53" s="5" t="inlineStr">
+        <is>
+          <t>11:20:00</t>
+        </is>
+      </c>
+      <c r="C53" s="5" t="inlineStr">
+        <is>
+          <t>11:20</t>
+        </is>
+      </c>
+      <c r="D53" s="5" t="inlineStr"/>
+      <c r="E53" s="5" t="inlineStr"/>
+      <c r="F53" s="5" t="inlineStr"/>
+      <c r="G53" s="5" t="inlineStr"/>
+      <c r="H53" s="5" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="I53" s="5" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="J53" s="5" t="inlineStr"/>
+      <c r="K53" s="5" t="inlineStr"/>
+      <c r="L53" s="5" t="inlineStr"/>
+      <c r="M53" s="5" t="inlineStr"/>
+      <c r="N53" s="5" t="inlineStr"/>
+      <c r="O53" s="5" t="inlineStr"/>
+      <c r="P53" s="5" t="inlineStr">
+        <is>
+          <t>Data fetch failed: Failed to fetch quote data after all retries</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="5" t="inlineStr">
+        <is>
+          <t>2026-03-10 11:20:00</t>
+        </is>
+      </c>
+      <c r="B54" s="5" t="inlineStr">
+        <is>
+          <t>11:20:00</t>
+        </is>
+      </c>
+      <c r="C54" s="5" t="inlineStr">
+        <is>
+          <t>11:20</t>
+        </is>
+      </c>
+      <c r="D54" s="5" t="inlineStr"/>
+      <c r="E54" s="5" t="inlineStr"/>
+      <c r="F54" s="5" t="inlineStr"/>
+      <c r="G54" s="5" t="inlineStr"/>
+      <c r="H54" s="5" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="I54" s="5" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="J54" s="5" t="inlineStr"/>
+      <c r="K54" s="5" t="inlineStr"/>
+      <c r="L54" s="5" t="inlineStr"/>
+      <c r="M54" s="5" t="inlineStr"/>
+      <c r="N54" s="5" t="inlineStr"/>
+      <c r="O54" s="5" t="inlineStr"/>
+      <c r="P54" s="5" t="inlineStr">
+        <is>
+          <t>Failed to fetch data: Failed to fetch quote data after all retries</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="5" t="inlineStr">
+        <is>
+          <t>2026-03-10 11:25:00</t>
+        </is>
+      </c>
+      <c r="B55" s="5" t="inlineStr">
+        <is>
+          <t>11:25:00</t>
+        </is>
+      </c>
+      <c r="C55" s="5" t="inlineStr">
+        <is>
+          <t>11:25</t>
+        </is>
+      </c>
+      <c r="D55" s="5" t="inlineStr"/>
+      <c r="E55" s="5" t="inlineStr"/>
+      <c r="F55" s="5" t="inlineStr"/>
+      <c r="G55" s="5" t="inlineStr"/>
+      <c r="H55" s="5" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="I55" s="5" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="J55" s="5" t="inlineStr"/>
+      <c r="K55" s="5" t="inlineStr"/>
+      <c r="L55" s="5" t="inlineStr"/>
+      <c r="M55" s="5" t="inlineStr"/>
+      <c r="N55" s="5" t="inlineStr"/>
+      <c r="O55" s="5" t="inlineStr"/>
+      <c r="P55" s="5" t="inlineStr">
+        <is>
+          <t>Data fetch failed: Failed to fetch quote data after all retries</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="5" t="inlineStr">
+        <is>
+          <t>2026-03-10 11:25:00</t>
+        </is>
+      </c>
+      <c r="B56" s="5" t="inlineStr">
+        <is>
+          <t>11:25:00</t>
+        </is>
+      </c>
+      <c r="C56" s="5" t="inlineStr">
+        <is>
+          <t>11:25</t>
+        </is>
+      </c>
+      <c r="D56" s="5" t="inlineStr"/>
+      <c r="E56" s="5" t="inlineStr"/>
+      <c r="F56" s="5" t="inlineStr"/>
+      <c r="G56" s="5" t="inlineStr"/>
+      <c r="H56" s="5" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="I56" s="5" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="J56" s="5" t="inlineStr"/>
+      <c r="K56" s="5" t="inlineStr"/>
+      <c r="L56" s="5" t="inlineStr"/>
+      <c r="M56" s="5" t="inlineStr"/>
+      <c r="N56" s="5" t="inlineStr"/>
+      <c r="O56" s="5" t="inlineStr"/>
+      <c r="P56" s="5" t="inlineStr">
+        <is>
+          <t>Failed to fetch data: Failed to fetch quote data after all retries</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="5" t="inlineStr">
+        <is>
+          <t>2026-03-10 11:30:00</t>
+        </is>
+      </c>
+      <c r="B57" s="5" t="inlineStr">
+        <is>
+          <t>11:30:00</t>
+        </is>
+      </c>
+      <c r="C57" s="5" t="inlineStr">
+        <is>
+          <t>11:30</t>
+        </is>
+      </c>
+      <c r="D57" s="5" t="inlineStr"/>
+      <c r="E57" s="5" t="inlineStr"/>
+      <c r="F57" s="5" t="inlineStr"/>
+      <c r="G57" s="5" t="inlineStr"/>
+      <c r="H57" s="5" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="I57" s="5" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="J57" s="5" t="inlineStr"/>
+      <c r="K57" s="5" t="inlineStr"/>
+      <c r="L57" s="5" t="inlineStr"/>
+      <c r="M57" s="5" t="inlineStr"/>
+      <c r="N57" s="5" t="inlineStr"/>
+      <c r="O57" s="5" t="inlineStr"/>
+      <c r="P57" s="5" t="inlineStr">
+        <is>
+          <t>Data fetch failed: Failed to fetch quote data after all retries</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="5" t="inlineStr">
+        <is>
+          <t>2026-03-10 11:30:00</t>
+        </is>
+      </c>
+      <c r="B58" s="5" t="inlineStr">
+        <is>
+          <t>11:30:00</t>
+        </is>
+      </c>
+      <c r="C58" s="5" t="inlineStr">
+        <is>
+          <t>11:30</t>
+        </is>
+      </c>
+      <c r="D58" s="5" t="inlineStr"/>
+      <c r="E58" s="5" t="inlineStr"/>
+      <c r="F58" s="5" t="inlineStr"/>
+      <c r="G58" s="5" t="inlineStr"/>
+      <c r="H58" s="5" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="I58" s="5" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="J58" s="5" t="inlineStr"/>
+      <c r="K58" s="5" t="inlineStr"/>
+      <c r="L58" s="5" t="inlineStr"/>
+      <c r="M58" s="5" t="inlineStr"/>
+      <c r="N58" s="5" t="inlineStr"/>
+      <c r="O58" s="5" t="inlineStr"/>
+      <c r="P58" s="5" t="inlineStr">
+        <is>
+          <t>Failed to fetch data: Failed to fetch quote data after all retries</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="5" t="inlineStr">
+        <is>
+          <t>2026-03-10 11:35:00</t>
+        </is>
+      </c>
+      <c r="B59" s="5" t="inlineStr">
+        <is>
+          <t>11:35:00</t>
+        </is>
+      </c>
+      <c r="C59" s="5" t="inlineStr">
+        <is>
+          <t>11:35</t>
+        </is>
+      </c>
+      <c r="D59" s="5" t="inlineStr"/>
+      <c r="E59" s="5" t="inlineStr"/>
+      <c r="F59" s="5" t="inlineStr"/>
+      <c r="G59" s="5" t="inlineStr"/>
+      <c r="H59" s="5" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="I59" s="5" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="J59" s="5" t="inlineStr"/>
+      <c r="K59" s="5" t="inlineStr"/>
+      <c r="L59" s="5" t="inlineStr"/>
+      <c r="M59" s="5" t="inlineStr"/>
+      <c r="N59" s="5" t="inlineStr"/>
+      <c r="O59" s="5" t="inlineStr"/>
+      <c r="P59" s="5" t="inlineStr">
+        <is>
+          <t>Data fetch failed: Failed to fetch quote data after all retries</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="5" t="inlineStr">
+        <is>
+          <t>2026-03-10 11:35:00</t>
+        </is>
+      </c>
+      <c r="B60" s="5" t="inlineStr">
+        <is>
+          <t>11:35:00</t>
+        </is>
+      </c>
+      <c r="C60" s="5" t="inlineStr">
+        <is>
+          <t>11:35</t>
+        </is>
+      </c>
+      <c r="D60" s="5" t="inlineStr"/>
+      <c r="E60" s="5" t="inlineStr"/>
+      <c r="F60" s="5" t="inlineStr"/>
+      <c r="G60" s="5" t="inlineStr"/>
+      <c r="H60" s="5" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="I60" s="5" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="J60" s="5" t="inlineStr"/>
+      <c r="K60" s="5" t="inlineStr"/>
+      <c r="L60" s="5" t="inlineStr"/>
+      <c r="M60" s="5" t="inlineStr"/>
+      <c r="N60" s="5" t="inlineStr"/>
+      <c r="O60" s="5" t="inlineStr"/>
+      <c r="P60" s="5" t="inlineStr">
+        <is>
+          <t>Failed to fetch data: Failed to fetch quote data after all retries</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="5" t="inlineStr">
+        <is>
+          <t>2026-03-10 11:40:00</t>
+        </is>
+      </c>
+      <c r="B61" s="5" t="inlineStr">
+        <is>
+          <t>11:40:00</t>
+        </is>
+      </c>
+      <c r="C61" s="5" t="inlineStr">
+        <is>
+          <t>11:40</t>
+        </is>
+      </c>
+      <c r="D61" s="5" t="inlineStr"/>
+      <c r="E61" s="5" t="inlineStr"/>
+      <c r="F61" s="5" t="inlineStr"/>
+      <c r="G61" s="5" t="inlineStr"/>
+      <c r="H61" s="5" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="I61" s="5" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="J61" s="5" t="inlineStr"/>
+      <c r="K61" s="5" t="inlineStr"/>
+      <c r="L61" s="5" t="inlineStr"/>
+      <c r="M61" s="5" t="inlineStr"/>
+      <c r="N61" s="5" t="inlineStr"/>
+      <c r="O61" s="5" t="inlineStr"/>
+      <c r="P61" s="5" t="inlineStr">
+        <is>
+          <t>Data fetch failed: Failed to fetch quote data after all retries</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="5" t="inlineStr">
+        <is>
+          <t>2026-03-10 11:40:00</t>
+        </is>
+      </c>
+      <c r="B62" s="5" t="inlineStr">
+        <is>
+          <t>11:40:00</t>
+        </is>
+      </c>
+      <c r="C62" s="5" t="inlineStr">
+        <is>
+          <t>11:40</t>
+        </is>
+      </c>
+      <c r="D62" s="5" t="inlineStr"/>
+      <c r="E62" s="5" t="inlineStr"/>
+      <c r="F62" s="5" t="inlineStr"/>
+      <c r="G62" s="5" t="inlineStr"/>
+      <c r="H62" s="5" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="I62" s="5" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="J62" s="5" t="inlineStr"/>
+      <c r="K62" s="5" t="inlineStr"/>
+      <c r="L62" s="5" t="inlineStr"/>
+      <c r="M62" s="5" t="inlineStr"/>
+      <c r="N62" s="5" t="inlineStr"/>
+      <c r="O62" s="5" t="inlineStr"/>
+      <c r="P62" s="5" t="inlineStr">
+        <is>
+          <t>Failed to fetch data: Failed to fetch quote data after all retries</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="5" t="inlineStr">
+        <is>
+          <t>2026-03-10 11:45:00</t>
+        </is>
+      </c>
+      <c r="B63" s="5" t="inlineStr">
+        <is>
+          <t>11:45:00</t>
+        </is>
+      </c>
+      <c r="C63" s="5" t="inlineStr">
+        <is>
+          <t>11:45</t>
+        </is>
+      </c>
+      <c r="D63" s="5" t="inlineStr"/>
+      <c r="E63" s="5" t="inlineStr"/>
+      <c r="F63" s="5" t="inlineStr"/>
+      <c r="G63" s="5" t="inlineStr"/>
+      <c r="H63" s="5" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="I63" s="5" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="J63" s="5" t="inlineStr"/>
+      <c r="K63" s="5" t="inlineStr"/>
+      <c r="L63" s="5" t="inlineStr"/>
+      <c r="M63" s="5" t="inlineStr"/>
+      <c r="N63" s="5" t="inlineStr"/>
+      <c r="O63" s="5" t="inlineStr"/>
+      <c r="P63" s="5" t="inlineStr">
+        <is>
+          <t>Data fetch failed: Failed to fetch quote data after all retries</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="5" t="inlineStr">
+        <is>
+          <t>2026-03-10 11:45:00</t>
+        </is>
+      </c>
+      <c r="B64" s="5" t="inlineStr">
+        <is>
+          <t>11:45:00</t>
+        </is>
+      </c>
+      <c r="C64" s="5" t="inlineStr">
+        <is>
+          <t>11:45</t>
+        </is>
+      </c>
+      <c r="D64" s="5" t="inlineStr"/>
+      <c r="E64" s="5" t="inlineStr"/>
+      <c r="F64" s="5" t="inlineStr"/>
+      <c r="G64" s="5" t="inlineStr"/>
+      <c r="H64" s="5" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="I64" s="5" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="J64" s="5" t="inlineStr"/>
+      <c r="K64" s="5" t="inlineStr"/>
+      <c r="L64" s="5" t="inlineStr"/>
+      <c r="M64" s="5" t="inlineStr"/>
+      <c r="N64" s="5" t="inlineStr"/>
+      <c r="O64" s="5" t="inlineStr"/>
+      <c r="P64" s="5" t="inlineStr">
+        <is>
+          <t>Failed to fetch data: Failed to fetch quote data after all retries</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="5" t="inlineStr">
+        <is>
+          <t>2026-03-10 11:50:00</t>
+        </is>
+      </c>
+      <c r="B65" s="5" t="inlineStr">
+        <is>
+          <t>11:50:00</t>
+        </is>
+      </c>
+      <c r="C65" s="5" t="inlineStr">
+        <is>
+          <t>11:50</t>
+        </is>
+      </c>
+      <c r="D65" s="5" t="inlineStr"/>
+      <c r="E65" s="5" t="inlineStr"/>
+      <c r="F65" s="5" t="inlineStr"/>
+      <c r="G65" s="5" t="inlineStr"/>
+      <c r="H65" s="5" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="I65" s="5" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="J65" s="5" t="inlineStr"/>
+      <c r="K65" s="5" t="inlineStr"/>
+      <c r="L65" s="5" t="inlineStr"/>
+      <c r="M65" s="5" t="inlineStr"/>
+      <c r="N65" s="5" t="inlineStr"/>
+      <c r="O65" s="5" t="inlineStr"/>
+      <c r="P65" s="5" t="inlineStr">
+        <is>
+          <t>Data fetch failed: Failed to fetch quote data after all retries</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="5" t="inlineStr">
+        <is>
+          <t>2026-03-10 11:50:00</t>
+        </is>
+      </c>
+      <c r="B66" s="5" t="inlineStr">
+        <is>
+          <t>11:50:00</t>
+        </is>
+      </c>
+      <c r="C66" s="5" t="inlineStr">
+        <is>
+          <t>11:50</t>
+        </is>
+      </c>
+      <c r="D66" s="5" t="inlineStr"/>
+      <c r="E66" s="5" t="inlineStr"/>
+      <c r="F66" s="5" t="inlineStr"/>
+      <c r="G66" s="5" t="inlineStr"/>
+      <c r="H66" s="5" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="I66" s="5" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="J66" s="5" t="inlineStr"/>
+      <c r="K66" s="5" t="inlineStr"/>
+      <c r="L66" s="5" t="inlineStr"/>
+      <c r="M66" s="5" t="inlineStr"/>
+      <c r="N66" s="5" t="inlineStr"/>
+      <c r="O66" s="5" t="inlineStr"/>
+      <c r="P66" s="5" t="inlineStr">
+        <is>
+          <t>Failed to fetch data: Failed to fetch quote data after all retries</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="5" t="inlineStr">
+        <is>
+          <t>2026-03-10 11:55:00</t>
+        </is>
+      </c>
+      <c r="B67" s="5" t="inlineStr">
+        <is>
+          <t>11:55:00</t>
+        </is>
+      </c>
+      <c r="C67" s="5" t="inlineStr">
+        <is>
+          <t>11:55</t>
+        </is>
+      </c>
+      <c r="D67" s="5" t="inlineStr"/>
+      <c r="E67" s="5" t="inlineStr"/>
+      <c r="F67" s="5" t="inlineStr"/>
+      <c r="G67" s="5" t="inlineStr"/>
+      <c r="H67" s="5" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="I67" s="5" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="J67" s="5" t="inlineStr"/>
+      <c r="K67" s="5" t="inlineStr"/>
+      <c r="L67" s="5" t="inlineStr"/>
+      <c r="M67" s="5" t="inlineStr"/>
+      <c r="N67" s="5" t="inlineStr"/>
+      <c r="O67" s="5" t="inlineStr"/>
+      <c r="P67" s="5" t="inlineStr">
+        <is>
+          <t>Data fetch failed: Failed to fetch quote data after all retries</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="5" t="inlineStr">
+        <is>
+          <t>2026-03-10 11:55:00</t>
+        </is>
+      </c>
+      <c r="B68" s="5" t="inlineStr">
+        <is>
+          <t>11:55:00</t>
+        </is>
+      </c>
+      <c r="C68" s="5" t="inlineStr">
+        <is>
+          <t>11:55</t>
+        </is>
+      </c>
+      <c r="D68" s="5" t="inlineStr"/>
+      <c r="E68" s="5" t="inlineStr"/>
+      <c r="F68" s="5" t="inlineStr"/>
+      <c r="G68" s="5" t="inlineStr"/>
+      <c r="H68" s="5" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="I68" s="5" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="J68" s="5" t="inlineStr"/>
+      <c r="K68" s="5" t="inlineStr"/>
+      <c r="L68" s="5" t="inlineStr"/>
+      <c r="M68" s="5" t="inlineStr"/>
+      <c r="N68" s="5" t="inlineStr"/>
+      <c r="O68" s="5" t="inlineStr"/>
+      <c r="P68" s="5" t="inlineStr">
+        <is>
+          <t>Failed to fetch data: Failed to fetch quote data after all retries</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="5" t="inlineStr">
+        <is>
+          <t>2026-03-10 12:00:00</t>
+        </is>
+      </c>
+      <c r="B69" s="5" t="inlineStr">
+        <is>
+          <t>12:00:00</t>
+        </is>
+      </c>
+      <c r="C69" s="5" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
+      <c r="D69" s="5" t="inlineStr"/>
+      <c r="E69" s="5" t="inlineStr"/>
+      <c r="F69" s="5" t="inlineStr"/>
+      <c r="G69" s="5" t="inlineStr"/>
+      <c r="H69" s="5" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="I69" s="5" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="J69" s="5" t="inlineStr"/>
+      <c r="K69" s="5" t="inlineStr"/>
+      <c r="L69" s="5" t="inlineStr"/>
+      <c r="M69" s="5" t="inlineStr"/>
+      <c r="N69" s="5" t="inlineStr"/>
+      <c r="O69" s="5" t="inlineStr"/>
+      <c r="P69" s="5" t="inlineStr">
+        <is>
+          <t>Data fetch failed: Failed to fetch quote data after all retries</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="5" t="inlineStr">
+        <is>
+          <t>2026-03-10 12:00:00</t>
+        </is>
+      </c>
+      <c r="B70" s="5" t="inlineStr">
+        <is>
+          <t>12:00:00</t>
+        </is>
+      </c>
+      <c r="C70" s="5" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
+      <c r="D70" s="5" t="inlineStr"/>
+      <c r="E70" s="5" t="inlineStr"/>
+      <c r="F70" s="5" t="inlineStr"/>
+      <c r="G70" s="5" t="inlineStr"/>
+      <c r="H70" s="5" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="I70" s="5" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="J70" s="5" t="inlineStr"/>
+      <c r="K70" s="5" t="inlineStr"/>
+      <c r="L70" s="5" t="inlineStr"/>
+      <c r="M70" s="5" t="inlineStr"/>
+      <c r="N70" s="5" t="inlineStr"/>
+      <c r="O70" s="5" t="inlineStr"/>
+      <c r="P70" s="5" t="inlineStr">
+        <is>
+          <t>Failed to fetch data: Failed to fetch quote data after all retries</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="5" t="inlineStr">
+        <is>
+          <t>2026-03-10 12:05:00</t>
+        </is>
+      </c>
+      <c r="B71" s="5" t="inlineStr">
+        <is>
+          <t>12:05:00</t>
+        </is>
+      </c>
+      <c r="C71" s="5" t="inlineStr">
+        <is>
+          <t>12:05</t>
+        </is>
+      </c>
+      <c r="D71" s="5" t="inlineStr"/>
+      <c r="E71" s="5" t="inlineStr"/>
+      <c r="F71" s="5" t="inlineStr"/>
+      <c r="G71" s="5" t="inlineStr"/>
+      <c r="H71" s="5" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="I71" s="5" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="J71" s="5" t="inlineStr"/>
+      <c r="K71" s="5" t="inlineStr"/>
+      <c r="L71" s="5" t="inlineStr"/>
+      <c r="M71" s="5" t="inlineStr"/>
+      <c r="N71" s="5" t="inlineStr"/>
+      <c r="O71" s="5" t="inlineStr"/>
+      <c r="P71" s="5" t="inlineStr">
+        <is>
+          <t>Data fetch failed: Failed to fetch quote data after all retries</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="5" t="inlineStr">
+        <is>
+          <t>2026-03-10 12:05:00</t>
+        </is>
+      </c>
+      <c r="B72" s="5" t="inlineStr">
+        <is>
+          <t>12:05:00</t>
+        </is>
+      </c>
+      <c r="C72" s="5" t="inlineStr">
+        <is>
+          <t>12:05</t>
+        </is>
+      </c>
+      <c r="D72" s="5" t="inlineStr"/>
+      <c r="E72" s="5" t="inlineStr"/>
+      <c r="F72" s="5" t="inlineStr"/>
+      <c r="G72" s="5" t="inlineStr"/>
+      <c r="H72" s="5" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="I72" s="5" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="J72" s="5" t="inlineStr"/>
+      <c r="K72" s="5" t="inlineStr"/>
+      <c r="L72" s="5" t="inlineStr"/>
+      <c r="M72" s="5" t="inlineStr"/>
+      <c r="N72" s="5" t="inlineStr"/>
+      <c r="O72" s="5" t="inlineStr"/>
+      <c r="P72" s="5" t="inlineStr">
+        <is>
+          <t>Failed to fetch data: Failed to fetch quote data after all retries</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="5" t="inlineStr">
+        <is>
+          <t>2026-03-10 12:10:00</t>
+        </is>
+      </c>
+      <c r="B73" s="5" t="inlineStr">
+        <is>
+          <t>12:10:00</t>
+        </is>
+      </c>
+      <c r="C73" s="5" t="inlineStr">
+        <is>
+          <t>12:10</t>
+        </is>
+      </c>
+      <c r="D73" s="5" t="inlineStr"/>
+      <c r="E73" s="5" t="inlineStr"/>
+      <c r="F73" s="5" t="inlineStr"/>
+      <c r="G73" s="5" t="inlineStr"/>
+      <c r="H73" s="5" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="I73" s="5" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="J73" s="5" t="inlineStr"/>
+      <c r="K73" s="5" t="inlineStr"/>
+      <c r="L73" s="5" t="inlineStr"/>
+      <c r="M73" s="5" t="inlineStr"/>
+      <c r="N73" s="5" t="inlineStr"/>
+      <c r="O73" s="5" t="inlineStr"/>
+      <c r="P73" s="5" t="inlineStr">
+        <is>
+          <t>Data fetch failed: Failed to fetch quote data after all retries</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="5" t="inlineStr">
+        <is>
+          <t>2026-03-10 12:10:00</t>
+        </is>
+      </c>
+      <c r="B74" s="5" t="inlineStr">
+        <is>
+          <t>12:10:00</t>
+        </is>
+      </c>
+      <c r="C74" s="5" t="inlineStr">
+        <is>
+          <t>12:10</t>
+        </is>
+      </c>
+      <c r="D74" s="5" t="inlineStr"/>
+      <c r="E74" s="5" t="inlineStr"/>
+      <c r="F74" s="5" t="inlineStr"/>
+      <c r="G74" s="5" t="inlineStr"/>
+      <c r="H74" s="5" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="I74" s="5" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="J74" s="5" t="inlineStr"/>
+      <c r="K74" s="5" t="inlineStr"/>
+      <c r="L74" s="5" t="inlineStr"/>
+      <c r="M74" s="5" t="inlineStr"/>
+      <c r="N74" s="5" t="inlineStr"/>
+      <c r="O74" s="5" t="inlineStr"/>
+      <c r="P74" s="5" t="inlineStr">
+        <is>
+          <t>Failed to fetch data: Failed to fetch quote data after all retries</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="5" t="inlineStr">
+        <is>
+          <t>2026-03-10 12:15:00</t>
+        </is>
+      </c>
+      <c r="B75" s="5" t="inlineStr">
+        <is>
+          <t>12:15:00</t>
+        </is>
+      </c>
+      <c r="C75" s="5" t="inlineStr">
+        <is>
+          <t>12:15</t>
+        </is>
+      </c>
+      <c r="D75" s="5" t="inlineStr"/>
+      <c r="E75" s="5" t="inlineStr"/>
+      <c r="F75" s="5" t="inlineStr"/>
+      <c r="G75" s="5" t="inlineStr"/>
+      <c r="H75" s="5" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="I75" s="5" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="J75" s="5" t="inlineStr"/>
+      <c r="K75" s="5" t="inlineStr"/>
+      <c r="L75" s="5" t="inlineStr"/>
+      <c r="M75" s="5" t="inlineStr"/>
+      <c r="N75" s="5" t="inlineStr"/>
+      <c r="O75" s="5" t="inlineStr"/>
+      <c r="P75" s="5" t="inlineStr">
+        <is>
+          <t>Data fetch failed: Failed to fetch quote data after all retries</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="5" t="inlineStr">
+        <is>
+          <t>2026-03-10 12:15:00</t>
+        </is>
+      </c>
+      <c r="B76" s="5" t="inlineStr">
+        <is>
+          <t>12:15:00</t>
+        </is>
+      </c>
+      <c r="C76" s="5" t="inlineStr">
+        <is>
+          <t>12:15</t>
+        </is>
+      </c>
+      <c r="D76" s="5" t="inlineStr"/>
+      <c r="E76" s="5" t="inlineStr"/>
+      <c r="F76" s="5" t="inlineStr"/>
+      <c r="G76" s="5" t="inlineStr"/>
+      <c r="H76" s="5" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="I76" s="5" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="J76" s="5" t="inlineStr"/>
+      <c r="K76" s="5" t="inlineStr"/>
+      <c r="L76" s="5" t="inlineStr"/>
+      <c r="M76" s="5" t="inlineStr"/>
+      <c r="N76" s="5" t="inlineStr"/>
+      <c r="O76" s="5" t="inlineStr"/>
+      <c r="P76" s="5" t="inlineStr">
+        <is>
+          <t>Failed to fetch data: Failed to fetch quote data after all retries</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="5" t="inlineStr">
+        <is>
+          <t>2026-03-10 12:20:00</t>
+        </is>
+      </c>
+      <c r="B77" s="5" t="inlineStr">
+        <is>
+          <t>12:20:00</t>
+        </is>
+      </c>
+      <c r="C77" s="5" t="inlineStr">
+        <is>
+          <t>12:20</t>
+        </is>
+      </c>
+      <c r="D77" s="5" t="inlineStr"/>
+      <c r="E77" s="5" t="inlineStr"/>
+      <c r="F77" s="5" t="inlineStr"/>
+      <c r="G77" s="5" t="inlineStr"/>
+      <c r="H77" s="5" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="I77" s="5" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="J77" s="5" t="inlineStr"/>
+      <c r="K77" s="5" t="inlineStr"/>
+      <c r="L77" s="5" t="inlineStr"/>
+      <c r="M77" s="5" t="inlineStr"/>
+      <c r="N77" s="5" t="inlineStr"/>
+      <c r="O77" s="5" t="inlineStr"/>
+      <c r="P77" s="5" t="inlineStr">
+        <is>
+          <t>Data fetch failed: Failed to fetch quote data after all retries</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="5" t="inlineStr">
+        <is>
+          <t>2026-03-10 12:20:00</t>
+        </is>
+      </c>
+      <c r="B78" s="5" t="inlineStr">
+        <is>
+          <t>12:20:00</t>
+        </is>
+      </c>
+      <c r="C78" s="5" t="inlineStr">
+        <is>
+          <t>12:20</t>
+        </is>
+      </c>
+      <c r="D78" s="5" t="inlineStr"/>
+      <c r="E78" s="5" t="inlineStr"/>
+      <c r="F78" s="5" t="inlineStr"/>
+      <c r="G78" s="5" t="inlineStr"/>
+      <c r="H78" s="5" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="I78" s="5" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="J78" s="5" t="inlineStr"/>
+      <c r="K78" s="5" t="inlineStr"/>
+      <c r="L78" s="5" t="inlineStr"/>
+      <c r="M78" s="5" t="inlineStr"/>
+      <c r="N78" s="5" t="inlineStr"/>
+      <c r="O78" s="5" t="inlineStr"/>
+      <c r="P78" s="5" t="inlineStr">
+        <is>
+          <t>Failed to fetch data: Failed to fetch quote data after all retries</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="5" t="inlineStr">
+        <is>
+          <t>2026-03-10 12:25:00</t>
+        </is>
+      </c>
+      <c r="B79" s="5" t="inlineStr">
+        <is>
+          <t>12:25:00</t>
+        </is>
+      </c>
+      <c r="C79" s="5" t="inlineStr">
+        <is>
+          <t>12:25</t>
+        </is>
+      </c>
+      <c r="D79" s="5" t="inlineStr"/>
+      <c r="E79" s="5" t="inlineStr"/>
+      <c r="F79" s="5" t="inlineStr"/>
+      <c r="G79" s="5" t="inlineStr"/>
+      <c r="H79" s="5" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="I79" s="5" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="J79" s="5" t="inlineStr"/>
+      <c r="K79" s="5" t="inlineStr"/>
+      <c r="L79" s="5" t="inlineStr"/>
+      <c r="M79" s="5" t="inlineStr"/>
+      <c r="N79" s="5" t="inlineStr"/>
+      <c r="O79" s="5" t="inlineStr"/>
+      <c r="P79" s="5" t="inlineStr">
+        <is>
+          <t>Data fetch failed: Failed to fetch quote data after all retries</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="5" t="inlineStr">
+        <is>
+          <t>2026-03-10 12:25:00</t>
+        </is>
+      </c>
+      <c r="B80" s="5" t="inlineStr">
+        <is>
+          <t>12:25:00</t>
+        </is>
+      </c>
+      <c r="C80" s="5" t="inlineStr">
+        <is>
+          <t>12:25</t>
+        </is>
+      </c>
+      <c r="D80" s="5" t="inlineStr"/>
+      <c r="E80" s="5" t="inlineStr"/>
+      <c r="F80" s="5" t="inlineStr"/>
+      <c r="G80" s="5" t="inlineStr"/>
+      <c r="H80" s="5" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="I80" s="5" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="J80" s="5" t="inlineStr"/>
+      <c r="K80" s="5" t="inlineStr"/>
+      <c r="L80" s="5" t="inlineStr"/>
+      <c r="M80" s="5" t="inlineStr"/>
+      <c r="N80" s="5" t="inlineStr"/>
+      <c r="O80" s="5" t="inlineStr"/>
+      <c r="P80" s="5" t="inlineStr">
+        <is>
+          <t>Failed to fetch data: Failed to fetch quote data after all retries</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="5" t="inlineStr">
+        <is>
+          <t>2026-03-10 12:30:00</t>
+        </is>
+      </c>
+      <c r="B81" s="5" t="inlineStr">
+        <is>
+          <t>12:30:00</t>
+        </is>
+      </c>
+      <c r="C81" s="5" t="inlineStr">
+        <is>
+          <t>12:30</t>
+        </is>
+      </c>
+      <c r="D81" s="5" t="inlineStr"/>
+      <c r="E81" s="5" t="inlineStr"/>
+      <c r="F81" s="5" t="inlineStr"/>
+      <c r="G81" s="5" t="inlineStr"/>
+      <c r="H81" s="5" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="I81" s="5" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="J81" s="5" t="inlineStr"/>
+      <c r="K81" s="5" t="inlineStr"/>
+      <c r="L81" s="5" t="inlineStr"/>
+      <c r="M81" s="5" t="inlineStr"/>
+      <c r="N81" s="5" t="inlineStr"/>
+      <c r="O81" s="5" t="inlineStr"/>
+      <c r="P81" s="5" t="inlineStr">
+        <is>
+          <t>Data fetch failed: Failed to fetch quote data after all retries</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="5" t="inlineStr">
+        <is>
+          <t>2026-03-10 12:30:00</t>
+        </is>
+      </c>
+      <c r="B82" s="5" t="inlineStr">
+        <is>
+          <t>12:30:00</t>
+        </is>
+      </c>
+      <c r="C82" s="5" t="inlineStr">
+        <is>
+          <t>12:30</t>
+        </is>
+      </c>
+      <c r="D82" s="5" t="inlineStr"/>
+      <c r="E82" s="5" t="inlineStr"/>
+      <c r="F82" s="5" t="inlineStr"/>
+      <c r="G82" s="5" t="inlineStr"/>
+      <c r="H82" s="5" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="I82" s="5" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="J82" s="5" t="inlineStr"/>
+      <c r="K82" s="5" t="inlineStr"/>
+      <c r="L82" s="5" t="inlineStr"/>
+      <c r="M82" s="5" t="inlineStr"/>
+      <c r="N82" s="5" t="inlineStr"/>
+      <c r="O82" s="5" t="inlineStr"/>
+      <c r="P82" s="5" t="inlineStr">
+        <is>
+          <t>Failed to fetch data: Failed to fetch quote data after all retries</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="5" t="inlineStr">
+        <is>
+          <t>2026-03-10 12:35:00</t>
+        </is>
+      </c>
+      <c r="B83" s="5" t="inlineStr">
+        <is>
+          <t>12:35:00</t>
+        </is>
+      </c>
+      <c r="C83" s="5" t="inlineStr">
+        <is>
+          <t>12:35</t>
+        </is>
+      </c>
+      <c r="D83" s="5" t="inlineStr"/>
+      <c r="E83" s="5" t="inlineStr"/>
+      <c r="F83" s="5" t="inlineStr"/>
+      <c r="G83" s="5" t="inlineStr"/>
+      <c r="H83" s="5" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="I83" s="5" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="J83" s="5" t="inlineStr"/>
+      <c r="K83" s="5" t="inlineStr"/>
+      <c r="L83" s="5" t="inlineStr"/>
+      <c r="M83" s="5" t="inlineStr"/>
+      <c r="N83" s="5" t="inlineStr"/>
+      <c r="O83" s="5" t="inlineStr"/>
+      <c r="P83" s="5" t="inlineStr">
+        <is>
+          <t>Data fetch failed: Failed to fetch quote data after all retries</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="5" t="inlineStr">
+        <is>
+          <t>2026-03-10 12:35:00</t>
+        </is>
+      </c>
+      <c r="B84" s="5" t="inlineStr">
+        <is>
+          <t>12:35:00</t>
+        </is>
+      </c>
+      <c r="C84" s="5" t="inlineStr">
+        <is>
+          <t>12:35</t>
+        </is>
+      </c>
+      <c r="D84" s="5" t="inlineStr"/>
+      <c r="E84" s="5" t="inlineStr"/>
+      <c r="F84" s="5" t="inlineStr"/>
+      <c r="G84" s="5" t="inlineStr"/>
+      <c r="H84" s="5" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="I84" s="5" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="J84" s="5" t="inlineStr"/>
+      <c r="K84" s="5" t="inlineStr"/>
+      <c r="L84" s="5" t="inlineStr"/>
+      <c r="M84" s="5" t="inlineStr"/>
+      <c r="N84" s="5" t="inlineStr"/>
+      <c r="O84" s="5" t="inlineStr"/>
+      <c r="P84" s="5" t="inlineStr">
+        <is>
+          <t>Failed to fetch data: Failed to fetch quote data after all retries</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="5" t="inlineStr">
+        <is>
+          <t>2026-03-10 12:40:00</t>
+        </is>
+      </c>
+      <c r="B85" s="5" t="inlineStr">
+        <is>
+          <t>12:40:00</t>
+        </is>
+      </c>
+      <c r="C85" s="5" t="inlineStr">
+        <is>
+          <t>12:40</t>
+        </is>
+      </c>
+      <c r="D85" s="5" t="inlineStr"/>
+      <c r="E85" s="5" t="inlineStr"/>
+      <c r="F85" s="5" t="inlineStr"/>
+      <c r="G85" s="5" t="inlineStr"/>
+      <c r="H85" s="5" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="I85" s="5" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="J85" s="5" t="inlineStr"/>
+      <c r="K85" s="5" t="inlineStr"/>
+      <c r="L85" s="5" t="inlineStr"/>
+      <c r="M85" s="5" t="inlineStr"/>
+      <c r="N85" s="5" t="inlineStr"/>
+      <c r="O85" s="5" t="inlineStr"/>
+      <c r="P85" s="5" t="inlineStr">
+        <is>
+          <t>Data fetch failed: Failed to fetch quote data after all retries</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="5" t="inlineStr">
+        <is>
+          <t>2026-03-10 12:40:00</t>
+        </is>
+      </c>
+      <c r="B86" s="5" t="inlineStr">
+        <is>
+          <t>12:40:00</t>
+        </is>
+      </c>
+      <c r="C86" s="5" t="inlineStr">
+        <is>
+          <t>12:40</t>
+        </is>
+      </c>
+      <c r="D86" s="5" t="inlineStr"/>
+      <c r="E86" s="5" t="inlineStr"/>
+      <c r="F86" s="5" t="inlineStr"/>
+      <c r="G86" s="5" t="inlineStr"/>
+      <c r="H86" s="5" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="I86" s="5" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="J86" s="5" t="inlineStr"/>
+      <c r="K86" s="5" t="inlineStr"/>
+      <c r="L86" s="5" t="inlineStr"/>
+      <c r="M86" s="5" t="inlineStr"/>
+      <c r="N86" s="5" t="inlineStr"/>
+      <c r="O86" s="5" t="inlineStr"/>
+      <c r="P86" s="5" t="inlineStr">
+        <is>
+          <t>Failed to fetch data: Failed to fetch quote data after all retries</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="5" t="inlineStr">
+        <is>
+          <t>2026-03-10 12:45:00</t>
+        </is>
+      </c>
+      <c r="B87" s="5" t="inlineStr">
+        <is>
+          <t>12:45:00</t>
+        </is>
+      </c>
+      <c r="C87" s="5" t="inlineStr">
+        <is>
+          <t>12:45</t>
+        </is>
+      </c>
+      <c r="D87" s="5" t="inlineStr"/>
+      <c r="E87" s="5" t="inlineStr"/>
+      <c r="F87" s="5" t="inlineStr"/>
+      <c r="G87" s="5" t="inlineStr"/>
+      <c r="H87" s="5" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="I87" s="5" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="J87" s="5" t="inlineStr"/>
+      <c r="K87" s="5" t="inlineStr"/>
+      <c r="L87" s="5" t="inlineStr"/>
+      <c r="M87" s="5" t="inlineStr"/>
+      <c r="N87" s="5" t="inlineStr"/>
+      <c r="O87" s="5" t="inlineStr"/>
+      <c r="P87" s="5" t="inlineStr">
+        <is>
+          <t>Data fetch failed: Failed to fetch quote data after all retries</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="5" t="inlineStr">
+        <is>
+          <t>2026-03-10 12:45:00</t>
+        </is>
+      </c>
+      <c r="B88" s="5" t="inlineStr">
+        <is>
+          <t>12:45:00</t>
+        </is>
+      </c>
+      <c r="C88" s="5" t="inlineStr">
+        <is>
+          <t>12:45</t>
+        </is>
+      </c>
+      <c r="D88" s="5" t="inlineStr"/>
+      <c r="E88" s="5" t="inlineStr"/>
+      <c r="F88" s="5" t="inlineStr"/>
+      <c r="G88" s="5" t="inlineStr"/>
+      <c r="H88" s="5" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="I88" s="5" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="J88" s="5" t="inlineStr"/>
+      <c r="K88" s="5" t="inlineStr"/>
+      <c r="L88" s="5" t="inlineStr"/>
+      <c r="M88" s="5" t="inlineStr"/>
+      <c r="N88" s="5" t="inlineStr"/>
+      <c r="O88" s="5" t="inlineStr"/>
+      <c r="P88" s="5" t="inlineStr">
+        <is>
+          <t>Failed to fetch data: Failed to fetch quote data after all retries</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="5" t="inlineStr">
+        <is>
+          <t>2026-03-10 12:50:00</t>
+        </is>
+      </c>
+      <c r="B89" s="5" t="inlineStr">
+        <is>
+          <t>12:50:00</t>
+        </is>
+      </c>
+      <c r="C89" s="5" t="inlineStr">
+        <is>
+          <t>12:50</t>
+        </is>
+      </c>
+      <c r="D89" s="5" t="inlineStr"/>
+      <c r="E89" s="5" t="inlineStr"/>
+      <c r="F89" s="5" t="inlineStr"/>
+      <c r="G89" s="5" t="inlineStr"/>
+      <c r="H89" s="5" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="I89" s="5" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="J89" s="5" t="inlineStr"/>
+      <c r="K89" s="5" t="inlineStr"/>
+      <c r="L89" s="5" t="inlineStr"/>
+      <c r="M89" s="5" t="inlineStr"/>
+      <c r="N89" s="5" t="inlineStr"/>
+      <c r="O89" s="5" t="inlineStr"/>
+      <c r="P89" s="5" t="inlineStr">
+        <is>
+          <t>Data fetch failed: Failed to fetch quote data after all retries</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="5" t="inlineStr">
+        <is>
+          <t>2026-03-10 12:50:00</t>
+        </is>
+      </c>
+      <c r="B90" s="5" t="inlineStr">
+        <is>
+          <t>12:50:00</t>
+        </is>
+      </c>
+      <c r="C90" s="5" t="inlineStr">
+        <is>
+          <t>12:50</t>
+        </is>
+      </c>
+      <c r="D90" s="5" t="inlineStr"/>
+      <c r="E90" s="5" t="inlineStr"/>
+      <c r="F90" s="5" t="inlineStr"/>
+      <c r="G90" s="5" t="inlineStr"/>
+      <c r="H90" s="5" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="I90" s="5" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="J90" s="5" t="inlineStr"/>
+      <c r="K90" s="5" t="inlineStr"/>
+      <c r="L90" s="5" t="inlineStr"/>
+      <c r="M90" s="5" t="inlineStr"/>
+      <c r="N90" s="5" t="inlineStr"/>
+      <c r="O90" s="5" t="inlineStr"/>
+      <c r="P90" s="5" t="inlineStr">
+        <is>
+          <t>Failed to fetch data: Failed to fetch quote data after all retries</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="5" t="inlineStr">
+        <is>
+          <t>2026-03-10 12:55:00</t>
+        </is>
+      </c>
+      <c r="B91" s="5" t="inlineStr">
+        <is>
+          <t>12:55:00</t>
+        </is>
+      </c>
+      <c r="C91" s="5" t="inlineStr">
+        <is>
+          <t>12:55</t>
+        </is>
+      </c>
+      <c r="D91" s="5" t="inlineStr"/>
+      <c r="E91" s="5" t="inlineStr"/>
+      <c r="F91" s="5" t="inlineStr"/>
+      <c r="G91" s="5" t="inlineStr"/>
+      <c r="H91" s="5" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="I91" s="5" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="J91" s="5" t="inlineStr"/>
+      <c r="K91" s="5" t="inlineStr"/>
+      <c r="L91" s="5" t="inlineStr"/>
+      <c r="M91" s="5" t="inlineStr"/>
+      <c r="N91" s="5" t="inlineStr"/>
+      <c r="O91" s="5" t="inlineStr"/>
+      <c r="P91" s="5" t="inlineStr">
+        <is>
+          <t>Data fetch failed: Failed to fetch quote data after all retries</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="5" t="inlineStr">
+        <is>
+          <t>2026-03-10 12:55:00</t>
+        </is>
+      </c>
+      <c r="B92" s="5" t="inlineStr">
+        <is>
+          <t>12:55:00</t>
+        </is>
+      </c>
+      <c r="C92" s="5" t="inlineStr">
+        <is>
+          <t>12:55</t>
+        </is>
+      </c>
+      <c r="D92" s="5" t="inlineStr"/>
+      <c r="E92" s="5" t="inlineStr"/>
+      <c r="F92" s="5" t="inlineStr"/>
+      <c r="G92" s="5" t="inlineStr"/>
+      <c r="H92" s="5" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="I92" s="5" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="J92" s="5" t="inlineStr"/>
+      <c r="K92" s="5" t="inlineStr"/>
+      <c r="L92" s="5" t="inlineStr"/>
+      <c r="M92" s="5" t="inlineStr"/>
+      <c r="N92" s="5" t="inlineStr"/>
+      <c r="O92" s="5" t="inlineStr"/>
+      <c r="P92" s="5" t="inlineStr">
+        <is>
+          <t>Failed to fetch data: Failed to fetch quote data after all retries</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="5" t="inlineStr">
+        <is>
+          <t>2026-03-10 13:00:00</t>
+        </is>
+      </c>
+      <c r="B93" s="5" t="inlineStr">
+        <is>
+          <t>13:00:00</t>
+        </is>
+      </c>
+      <c r="C93" s="5" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="D93" s="5" t="inlineStr"/>
+      <c r="E93" s="5" t="inlineStr"/>
+      <c r="F93" s="5" t="inlineStr"/>
+      <c r="G93" s="5" t="inlineStr"/>
+      <c r="H93" s="5" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="I93" s="5" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="J93" s="5" t="inlineStr"/>
+      <c r="K93" s="5" t="inlineStr"/>
+      <c r="L93" s="5" t="inlineStr"/>
+      <c r="M93" s="5" t="inlineStr"/>
+      <c r="N93" s="5" t="inlineStr"/>
+      <c r="O93" s="5" t="inlineStr"/>
+      <c r="P93" s="5" t="inlineStr">
+        <is>
+          <t>Data fetch failed: Failed to fetch quote data after all retries</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="5" t="inlineStr">
+        <is>
+          <t>2026-03-10 13:00:00</t>
+        </is>
+      </c>
+      <c r="B94" s="5" t="inlineStr">
+        <is>
+          <t>13:00:00</t>
+        </is>
+      </c>
+      <c r="C94" s="5" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="D94" s="5" t="inlineStr"/>
+      <c r="E94" s="5" t="inlineStr"/>
+      <c r="F94" s="5" t="inlineStr"/>
+      <c r="G94" s="5" t="inlineStr"/>
+      <c r="H94" s="5" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="I94" s="5" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="J94" s="5" t="inlineStr"/>
+      <c r="K94" s="5" t="inlineStr"/>
+      <c r="L94" s="5" t="inlineStr"/>
+      <c r="M94" s="5" t="inlineStr"/>
+      <c r="N94" s="5" t="inlineStr"/>
+      <c r="O94" s="5" t="inlineStr"/>
+      <c r="P94" s="5" t="inlineStr">
+        <is>
+          <t>Failed to fetch data: Failed to fetch quote data after all retries</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="5" t="inlineStr">
+        <is>
+          <t>2026-03-10 13:05:00</t>
+        </is>
+      </c>
+      <c r="B95" s="5" t="inlineStr">
+        <is>
+          <t>13:05:00</t>
+        </is>
+      </c>
+      <c r="C95" s="5" t="inlineStr">
+        <is>
+          <t>13:05</t>
+        </is>
+      </c>
+      <c r="D95" s="5" t="inlineStr"/>
+      <c r="E95" s="5" t="inlineStr"/>
+      <c r="F95" s="5" t="inlineStr"/>
+      <c r="G95" s="5" t="inlineStr"/>
+      <c r="H95" s="5" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="I95" s="5" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="J95" s="5" t="inlineStr"/>
+      <c r="K95" s="5" t="inlineStr"/>
+      <c r="L95" s="5" t="inlineStr"/>
+      <c r="M95" s="5" t="inlineStr"/>
+      <c r="N95" s="5" t="inlineStr"/>
+      <c r="O95" s="5" t="inlineStr"/>
+      <c r="P95" s="5" t="inlineStr">
+        <is>
+          <t>Data fetch failed: Failed to fetch quote data after all retries</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="5" t="inlineStr">
+        <is>
+          <t>2026-03-10 13:05:00</t>
+        </is>
+      </c>
+      <c r="B96" s="5" t="inlineStr">
+        <is>
+          <t>13:05:00</t>
+        </is>
+      </c>
+      <c r="C96" s="5" t="inlineStr">
+        <is>
+          <t>13:05</t>
+        </is>
+      </c>
+      <c r="D96" s="5" t="inlineStr"/>
+      <c r="E96" s="5" t="inlineStr"/>
+      <c r="F96" s="5" t="inlineStr"/>
+      <c r="G96" s="5" t="inlineStr"/>
+      <c r="H96" s="5" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="I96" s="5" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="J96" s="5" t="inlineStr"/>
+      <c r="K96" s="5" t="inlineStr"/>
+      <c r="L96" s="5" t="inlineStr"/>
+      <c r="M96" s="5" t="inlineStr"/>
+      <c r="N96" s="5" t="inlineStr"/>
+      <c r="O96" s="5" t="inlineStr"/>
+      <c r="P96" s="5" t="inlineStr">
+        <is>
+          <t>Failed to fetch data: Failed to fetch quote data after all retries</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="5" t="inlineStr">
+        <is>
+          <t>2026-03-10 13:10:00</t>
+        </is>
+      </c>
+      <c r="B97" s="5" t="inlineStr">
+        <is>
+          <t>13:10:00</t>
+        </is>
+      </c>
+      <c r="C97" s="5" t="inlineStr">
+        <is>
+          <t>13:10</t>
+        </is>
+      </c>
+      <c r="D97" s="5" t="inlineStr"/>
+      <c r="E97" s="5" t="inlineStr"/>
+      <c r="F97" s="5" t="inlineStr"/>
+      <c r="G97" s="5" t="inlineStr"/>
+      <c r="H97" s="5" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="I97" s="5" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="J97" s="5" t="inlineStr"/>
+      <c r="K97" s="5" t="inlineStr"/>
+      <c r="L97" s="5" t="inlineStr"/>
+      <c r="M97" s="5" t="inlineStr"/>
+      <c r="N97" s="5" t="inlineStr"/>
+      <c r="O97" s="5" t="inlineStr"/>
+      <c r="P97" s="5" t="inlineStr">
+        <is>
+          <t>Data fetch failed: Failed to fetch quote data after all retries</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="5" t="inlineStr">
+        <is>
+          <t>2026-03-10 13:10:00</t>
+        </is>
+      </c>
+      <c r="B98" s="5" t="inlineStr">
+        <is>
+          <t>13:10:00</t>
+        </is>
+      </c>
+      <c r="C98" s="5" t="inlineStr">
+        <is>
+          <t>13:10</t>
+        </is>
+      </c>
+      <c r="D98" s="5" t="inlineStr"/>
+      <c r="E98" s="5" t="inlineStr"/>
+      <c r="F98" s="5" t="inlineStr"/>
+      <c r="G98" s="5" t="inlineStr"/>
+      <c r="H98" s="5" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="I98" s="5" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="J98" s="5" t="inlineStr"/>
+      <c r="K98" s="5" t="inlineStr"/>
+      <c r="L98" s="5" t="inlineStr"/>
+      <c r="M98" s="5" t="inlineStr"/>
+      <c r="N98" s="5" t="inlineStr"/>
+      <c r="O98" s="5" t="inlineStr"/>
+      <c r="P98" s="5" t="inlineStr">
+        <is>
+          <t>Failed to fetch data: Failed to fetch quote data after all retries</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="5" t="inlineStr">
+        <is>
+          <t>2026-03-10 13:15:00</t>
+        </is>
+      </c>
+      <c r="B99" s="5" t="inlineStr">
+        <is>
+          <t>13:15:00</t>
+        </is>
+      </c>
+      <c r="C99" s="5" t="inlineStr">
+        <is>
+          <t>13:15</t>
+        </is>
+      </c>
+      <c r="D99" s="5" t="inlineStr"/>
+      <c r="E99" s="5" t="inlineStr"/>
+      <c r="F99" s="5" t="inlineStr"/>
+      <c r="G99" s="5" t="inlineStr"/>
+      <c r="H99" s="5" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="I99" s="5" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="J99" s="5" t="inlineStr"/>
+      <c r="K99" s="5" t="inlineStr"/>
+      <c r="L99" s="5" t="inlineStr"/>
+      <c r="M99" s="5" t="inlineStr"/>
+      <c r="N99" s="5" t="inlineStr"/>
+      <c r="O99" s="5" t="inlineStr"/>
+      <c r="P99" s="5" t="inlineStr">
+        <is>
+          <t>Data fetch failed: Failed to fetch quote data after all retries</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="5" t="inlineStr">
+        <is>
+          <t>2026-03-10 13:15:00</t>
+        </is>
+      </c>
+      <c r="B100" s="5" t="inlineStr">
+        <is>
+          <t>13:15:00</t>
+        </is>
+      </c>
+      <c r="C100" s="5" t="inlineStr">
+        <is>
+          <t>13:15</t>
+        </is>
+      </c>
+      <c r="D100" s="5" t="inlineStr"/>
+      <c r="E100" s="5" t="inlineStr"/>
+      <c r="F100" s="5" t="inlineStr"/>
+      <c r="G100" s="5" t="inlineStr"/>
+      <c r="H100" s="5" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="I100" s="5" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="J100" s="5" t="inlineStr"/>
+      <c r="K100" s="5" t="inlineStr"/>
+      <c r="L100" s="5" t="inlineStr"/>
+      <c r="M100" s="5" t="inlineStr"/>
+      <c r="N100" s="5" t="inlineStr"/>
+      <c r="O100" s="5" t="inlineStr"/>
+      <c r="P100" s="5" t="inlineStr">
+        <is>
+          <t>Failed to fetch data: Failed to fetch quote data after all retries</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="5" t="inlineStr">
+        <is>
+          <t>2026-03-10 13:20:00</t>
+        </is>
+      </c>
+      <c r="B101" s="5" t="inlineStr">
+        <is>
+          <t>13:20:00</t>
+        </is>
+      </c>
+      <c r="C101" s="5" t="inlineStr">
+        <is>
+          <t>13:20</t>
+        </is>
+      </c>
+      <c r="D101" s="5" t="inlineStr"/>
+      <c r="E101" s="5" t="inlineStr"/>
+      <c r="F101" s="5" t="inlineStr"/>
+      <c r="G101" s="5" t="inlineStr"/>
+      <c r="H101" s="5" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="I101" s="5" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="J101" s="5" t="inlineStr"/>
+      <c r="K101" s="5" t="inlineStr"/>
+      <c r="L101" s="5" t="inlineStr"/>
+      <c r="M101" s="5" t="inlineStr"/>
+      <c r="N101" s="5" t="inlineStr"/>
+      <c r="O101" s="5" t="inlineStr"/>
+      <c r="P101" s="5" t="inlineStr">
+        <is>
+          <t>Data fetch failed: Failed to fetch quote data after all retries</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="5" t="inlineStr">
+        <is>
+          <t>2026-03-10 13:20:00</t>
+        </is>
+      </c>
+      <c r="B102" s="5" t="inlineStr">
+        <is>
+          <t>13:20:00</t>
+        </is>
+      </c>
+      <c r="C102" s="5" t="inlineStr">
+        <is>
+          <t>13:20</t>
+        </is>
+      </c>
+      <c r="D102" s="5" t="inlineStr"/>
+      <c r="E102" s="5" t="inlineStr"/>
+      <c r="F102" s="5" t="inlineStr"/>
+      <c r="G102" s="5" t="inlineStr"/>
+      <c r="H102" s="5" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="I102" s="5" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="J102" s="5" t="inlineStr"/>
+      <c r="K102" s="5" t="inlineStr"/>
+      <c r="L102" s="5" t="inlineStr"/>
+      <c r="M102" s="5" t="inlineStr"/>
+      <c r="N102" s="5" t="inlineStr"/>
+      <c r="O102" s="5" t="inlineStr"/>
+      <c r="P102" s="5" t="inlineStr">
+        <is>
+          <t>Failed to fetch data: Failed to fetch quote data after all retries</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="5" t="inlineStr">
+        <is>
+          <t>2026-03-10 13:25:00</t>
+        </is>
+      </c>
+      <c r="B103" s="5" t="inlineStr">
+        <is>
+          <t>13:25:00</t>
+        </is>
+      </c>
+      <c r="C103" s="5" t="inlineStr">
+        <is>
+          <t>13:25</t>
+        </is>
+      </c>
+      <c r="D103" s="5" t="inlineStr"/>
+      <c r="E103" s="5" t="inlineStr"/>
+      <c r="F103" s="5" t="inlineStr"/>
+      <c r="G103" s="5" t="inlineStr"/>
+      <c r="H103" s="5" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="I103" s="5" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="J103" s="5" t="inlineStr"/>
+      <c r="K103" s="5" t="inlineStr"/>
+      <c r="L103" s="5" t="inlineStr"/>
+      <c r="M103" s="5" t="inlineStr"/>
+      <c r="N103" s="5" t="inlineStr"/>
+      <c r="O103" s="5" t="inlineStr"/>
+      <c r="P103" s="5" t="inlineStr">
+        <is>
+          <t>Data fetch failed: Failed to fetch quote data after all retries</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="5" t="inlineStr">
+        <is>
+          <t>2026-03-10 13:25:00</t>
+        </is>
+      </c>
+      <c r="B104" s="5" t="inlineStr">
+        <is>
+          <t>13:25:00</t>
+        </is>
+      </c>
+      <c r="C104" s="5" t="inlineStr">
+        <is>
+          <t>13:25</t>
+        </is>
+      </c>
+      <c r="D104" s="5" t="inlineStr"/>
+      <c r="E104" s="5" t="inlineStr"/>
+      <c r="F104" s="5" t="inlineStr"/>
+      <c r="G104" s="5" t="inlineStr"/>
+      <c r="H104" s="5" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="I104" s="5" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="J104" s="5" t="inlineStr"/>
+      <c r="K104" s="5" t="inlineStr"/>
+      <c r="L104" s="5" t="inlineStr"/>
+      <c r="M104" s="5" t="inlineStr"/>
+      <c r="N104" s="5" t="inlineStr"/>
+      <c r="O104" s="5" t="inlineStr"/>
+      <c r="P104" s="5" t="inlineStr">
+        <is>
+          <t>Failed to fetch data: Failed to fetch quote data after all retries</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="5" t="inlineStr">
+        <is>
+          <t>2026-03-10 13:30:00</t>
+        </is>
+      </c>
+      <c r="B105" s="5" t="inlineStr">
+        <is>
+          <t>13:30:00</t>
+        </is>
+      </c>
+      <c r="C105" s="5" t="inlineStr">
+        <is>
+          <t>13:30</t>
+        </is>
+      </c>
+      <c r="D105" s="5" t="inlineStr"/>
+      <c r="E105" s="5" t="inlineStr"/>
+      <c r="F105" s="5" t="inlineStr"/>
+      <c r="G105" s="5" t="inlineStr"/>
+      <c r="H105" s="5" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="I105" s="5" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="J105" s="5" t="inlineStr"/>
+      <c r="K105" s="5" t="inlineStr"/>
+      <c r="L105" s="5" t="inlineStr"/>
+      <c r="M105" s="5" t="inlineStr"/>
+      <c r="N105" s="5" t="inlineStr"/>
+      <c r="O105" s="5" t="inlineStr"/>
+      <c r="P105" s="5" t="inlineStr">
+        <is>
+          <t>Data fetch failed: Failed to fetch quote data after all retries</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" s="5" t="inlineStr">
+        <is>
+          <t>2026-03-10 13:30:00</t>
+        </is>
+      </c>
+      <c r="B106" s="5" t="inlineStr">
+        <is>
+          <t>13:30:00</t>
+        </is>
+      </c>
+      <c r="C106" s="5" t="inlineStr">
+        <is>
+          <t>13:30</t>
+        </is>
+      </c>
+      <c r="D106" s="5" t="inlineStr"/>
+      <c r="E106" s="5" t="inlineStr"/>
+      <c r="F106" s="5" t="inlineStr"/>
+      <c r="G106" s="5" t="inlineStr"/>
+      <c r="H106" s="5" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="I106" s="5" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="J106" s="5" t="inlineStr"/>
+      <c r="K106" s="5" t="inlineStr"/>
+      <c r="L106" s="5" t="inlineStr"/>
+      <c r="M106" s="5" t="inlineStr"/>
+      <c r="N106" s="5" t="inlineStr"/>
+      <c r="O106" s="5" t="inlineStr"/>
+      <c r="P106" s="5" t="inlineStr">
+        <is>
+          <t>Failed to fetch data: Failed to fetch quote data after all retries</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" s="5" t="inlineStr">
+        <is>
+          <t>2026-03-10 13:35:00</t>
+        </is>
+      </c>
+      <c r="B107" s="5" t="inlineStr">
+        <is>
+          <t>13:35:00</t>
+        </is>
+      </c>
+      <c r="C107" s="5" t="inlineStr">
+        <is>
+          <t>13:35</t>
+        </is>
+      </c>
+      <c r="D107" s="5" t="inlineStr"/>
+      <c r="E107" s="5" t="inlineStr"/>
+      <c r="F107" s="5" t="inlineStr"/>
+      <c r="G107" s="5" t="inlineStr"/>
+      <c r="H107" s="5" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="I107" s="5" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="J107" s="5" t="inlineStr"/>
+      <c r="K107" s="5" t="inlineStr"/>
+      <c r="L107" s="5" t="inlineStr"/>
+      <c r="M107" s="5" t="inlineStr"/>
+      <c r="N107" s="5" t="inlineStr"/>
+      <c r="O107" s="5" t="inlineStr"/>
+      <c r="P107" s="5" t="inlineStr">
+        <is>
+          <t>Data fetch failed: Failed to fetch quote data after all retries</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" s="5" t="inlineStr">
+        <is>
+          <t>2026-03-10 13:35:00</t>
+        </is>
+      </c>
+      <c r="B108" s="5" t="inlineStr">
+        <is>
+          <t>13:35:00</t>
+        </is>
+      </c>
+      <c r="C108" s="5" t="inlineStr">
+        <is>
+          <t>13:35</t>
+        </is>
+      </c>
+      <c r="D108" s="5" t="inlineStr"/>
+      <c r="E108" s="5" t="inlineStr"/>
+      <c r="F108" s="5" t="inlineStr"/>
+      <c r="G108" s="5" t="inlineStr"/>
+      <c r="H108" s="5" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="I108" s="5" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="J108" s="5" t="inlineStr"/>
+      <c r="K108" s="5" t="inlineStr"/>
+      <c r="L108" s="5" t="inlineStr"/>
+      <c r="M108" s="5" t="inlineStr"/>
+      <c r="N108" s="5" t="inlineStr"/>
+      <c r="O108" s="5" t="inlineStr"/>
+      <c r="P108" s="5" t="inlineStr">
+        <is>
+          <t>Failed to fetch data: Failed to fetch quote data after all retries</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" s="5" t="inlineStr">
+        <is>
+          <t>2026-03-10 13:40:00</t>
+        </is>
+      </c>
+      <c r="B109" s="5" t="inlineStr">
+        <is>
+          <t>13:40:00</t>
+        </is>
+      </c>
+      <c r="C109" s="5" t="inlineStr">
+        <is>
+          <t>13:40</t>
+        </is>
+      </c>
+      <c r="D109" s="5" t="inlineStr"/>
+      <c r="E109" s="5" t="inlineStr"/>
+      <c r="F109" s="5" t="inlineStr"/>
+      <c r="G109" s="5" t="inlineStr"/>
+      <c r="H109" s="5" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="I109" s="5" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="J109" s="5" t="inlineStr"/>
+      <c r="K109" s="5" t="inlineStr"/>
+      <c r="L109" s="5" t="inlineStr"/>
+      <c r="M109" s="5" t="inlineStr"/>
+      <c r="N109" s="5" t="inlineStr"/>
+      <c r="O109" s="5" t="inlineStr"/>
+      <c r="P109" s="5" t="inlineStr">
+        <is>
+          <t>Data fetch failed: Failed to fetch quote data after all retries</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" s="5" t="inlineStr">
+        <is>
+          <t>2026-03-10 13:40:00</t>
+        </is>
+      </c>
+      <c r="B110" s="5" t="inlineStr">
+        <is>
+          <t>13:40:00</t>
+        </is>
+      </c>
+      <c r="C110" s="5" t="inlineStr">
+        <is>
+          <t>13:40</t>
+        </is>
+      </c>
+      <c r="D110" s="5" t="inlineStr"/>
+      <c r="E110" s="5" t="inlineStr"/>
+      <c r="F110" s="5" t="inlineStr"/>
+      <c r="G110" s="5" t="inlineStr"/>
+      <c r="H110" s="5" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="I110" s="5" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="J110" s="5" t="inlineStr"/>
+      <c r="K110" s="5" t="inlineStr"/>
+      <c r="L110" s="5" t="inlineStr"/>
+      <c r="M110" s="5" t="inlineStr"/>
+      <c r="N110" s="5" t="inlineStr"/>
+      <c r="O110" s="5" t="inlineStr"/>
+      <c r="P110" s="5" t="inlineStr">
+        <is>
+          <t>Failed to fetch data: Failed to fetch quote data after all retries</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" s="5" t="inlineStr">
+        <is>
+          <t>2026-03-10 13:45:00</t>
+        </is>
+      </c>
+      <c r="B111" s="5" t="inlineStr">
+        <is>
+          <t>13:45:00</t>
+        </is>
+      </c>
+      <c r="C111" s="5" t="inlineStr">
+        <is>
+          <t>13:45</t>
+        </is>
+      </c>
+      <c r="D111" s="5" t="inlineStr"/>
+      <c r="E111" s="5" t="inlineStr"/>
+      <c r="F111" s="5" t="inlineStr"/>
+      <c r="G111" s="5" t="inlineStr"/>
+      <c r="H111" s="5" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="I111" s="5" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="J111" s="5" t="inlineStr"/>
+      <c r="K111" s="5" t="inlineStr"/>
+      <c r="L111" s="5" t="inlineStr"/>
+      <c r="M111" s="5" t="inlineStr"/>
+      <c r="N111" s="5" t="inlineStr"/>
+      <c r="O111" s="5" t="inlineStr"/>
+      <c r="P111" s="5" t="inlineStr">
+        <is>
+          <t>Data fetch failed: Failed to fetch quote data after all retries</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" s="5" t="inlineStr">
+        <is>
+          <t>2026-03-10 13:45:00</t>
+        </is>
+      </c>
+      <c r="B112" s="5" t="inlineStr">
+        <is>
+          <t>13:45:00</t>
+        </is>
+      </c>
+      <c r="C112" s="5" t="inlineStr">
+        <is>
+          <t>13:45</t>
+        </is>
+      </c>
+      <c r="D112" s="5" t="inlineStr"/>
+      <c r="E112" s="5" t="inlineStr"/>
+      <c r="F112" s="5" t="inlineStr"/>
+      <c r="G112" s="5" t="inlineStr"/>
+      <c r="H112" s="5" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="I112" s="5" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="J112" s="5" t="inlineStr"/>
+      <c r="K112" s="5" t="inlineStr"/>
+      <c r="L112" s="5" t="inlineStr"/>
+      <c r="M112" s="5" t="inlineStr"/>
+      <c r="N112" s="5" t="inlineStr"/>
+      <c r="O112" s="5" t="inlineStr"/>
+      <c r="P112" s="5" t="inlineStr">
+        <is>
+          <t>Failed to fetch data: Failed to fetch quote data after all retries</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" s="5" t="inlineStr">
+        <is>
+          <t>2026-03-10 13:50:00</t>
+        </is>
+      </c>
+      <c r="B113" s="5" t="inlineStr">
+        <is>
+          <t>13:50:00</t>
+        </is>
+      </c>
+      <c r="C113" s="5" t="inlineStr">
+        <is>
+          <t>13:50</t>
+        </is>
+      </c>
+      <c r="D113" s="5" t="inlineStr"/>
+      <c r="E113" s="5" t="inlineStr"/>
+      <c r="F113" s="5" t="inlineStr"/>
+      <c r="G113" s="5" t="inlineStr"/>
+      <c r="H113" s="5" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="I113" s="5" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="J113" s="5" t="inlineStr"/>
+      <c r="K113" s="5" t="inlineStr"/>
+      <c r="L113" s="5" t="inlineStr"/>
+      <c r="M113" s="5" t="inlineStr"/>
+      <c r="N113" s="5" t="inlineStr"/>
+      <c r="O113" s="5" t="inlineStr"/>
+      <c r="P113" s="5" t="inlineStr">
+        <is>
+          <t>Data fetch failed: Failed to fetch quote data after all retries</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" s="5" t="inlineStr">
+        <is>
+          <t>2026-03-10 13:50:00</t>
+        </is>
+      </c>
+      <c r="B114" s="5" t="inlineStr">
+        <is>
+          <t>13:50:00</t>
+        </is>
+      </c>
+      <c r="C114" s="5" t="inlineStr">
+        <is>
+          <t>13:50</t>
+        </is>
+      </c>
+      <c r="D114" s="5" t="inlineStr"/>
+      <c r="E114" s="5" t="inlineStr"/>
+      <c r="F114" s="5" t="inlineStr"/>
+      <c r="G114" s="5" t="inlineStr"/>
+      <c r="H114" s="5" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="I114" s="5" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="J114" s="5" t="inlineStr"/>
+      <c r="K114" s="5" t="inlineStr"/>
+      <c r="L114" s="5" t="inlineStr"/>
+      <c r="M114" s="5" t="inlineStr"/>
+      <c r="N114" s="5" t="inlineStr"/>
+      <c r="O114" s="5" t="inlineStr"/>
+      <c r="P114" s="5" t="inlineStr">
+        <is>
+          <t>Failed to fetch data: Failed to fetch quote data after all retries</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" s="5" t="inlineStr">
+        <is>
+          <t>2026-03-10 13:55:00</t>
+        </is>
+      </c>
+      <c r="B115" s="5" t="inlineStr">
+        <is>
+          <t>13:55:00</t>
+        </is>
+      </c>
+      <c r="C115" s="5" t="inlineStr">
+        <is>
+          <t>13:55</t>
+        </is>
+      </c>
+      <c r="D115" s="5" t="inlineStr"/>
+      <c r="E115" s="5" t="inlineStr"/>
+      <c r="F115" s="5" t="inlineStr"/>
+      <c r="G115" s="5" t="inlineStr"/>
+      <c r="H115" s="5" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="I115" s="5" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="J115" s="5" t="inlineStr"/>
+      <c r="K115" s="5" t="inlineStr"/>
+      <c r="L115" s="5" t="inlineStr"/>
+      <c r="M115" s="5" t="inlineStr"/>
+      <c r="N115" s="5" t="inlineStr"/>
+      <c r="O115" s="5" t="inlineStr"/>
+      <c r="P115" s="5" t="inlineStr">
+        <is>
+          <t>Data fetch failed: Failed to fetch quote data after all retries</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" s="5" t="inlineStr">
+        <is>
+          <t>2026-03-10 13:55:00</t>
+        </is>
+      </c>
+      <c r="B116" s="5" t="inlineStr">
+        <is>
+          <t>13:55:00</t>
+        </is>
+      </c>
+      <c r="C116" s="5" t="inlineStr">
+        <is>
+          <t>13:55</t>
+        </is>
+      </c>
+      <c r="D116" s="5" t="inlineStr"/>
+      <c r="E116" s="5" t="inlineStr"/>
+      <c r="F116" s="5" t="inlineStr"/>
+      <c r="G116" s="5" t="inlineStr"/>
+      <c r="H116" s="5" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="I116" s="5" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="J116" s="5" t="inlineStr"/>
+      <c r="K116" s="5" t="inlineStr"/>
+      <c r="L116" s="5" t="inlineStr"/>
+      <c r="M116" s="5" t="inlineStr"/>
+      <c r="N116" s="5" t="inlineStr"/>
+      <c r="O116" s="5" t="inlineStr"/>
+      <c r="P116" s="5" t="inlineStr">
+        <is>
+          <t>Failed to fetch data: Failed to fetch quote data after all retries</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="5" t="inlineStr">
+        <is>
+          <t>2026-03-10 14:00:00</t>
+        </is>
+      </c>
+      <c r="B117" s="5" t="inlineStr">
+        <is>
+          <t>14:00:00</t>
+        </is>
+      </c>
+      <c r="C117" s="5" t="inlineStr">
+        <is>
+          <t>14:00</t>
+        </is>
+      </c>
+      <c r="D117" s="5" t="inlineStr"/>
+      <c r="E117" s="5" t="inlineStr"/>
+      <c r="F117" s="5" t="inlineStr"/>
+      <c r="G117" s="5" t="inlineStr"/>
+      <c r="H117" s="5" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="I117" s="5" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="J117" s="5" t="inlineStr"/>
+      <c r="K117" s="5" t="inlineStr"/>
+      <c r="L117" s="5" t="inlineStr"/>
+      <c r="M117" s="5" t="inlineStr"/>
+      <c r="N117" s="5" t="inlineStr"/>
+      <c r="O117" s="5" t="inlineStr"/>
+      <c r="P117" s="5" t="inlineStr">
+        <is>
+          <t>Data fetch failed: Failed to fetch quote data after all retries</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="5" t="inlineStr">
+        <is>
+          <t>2026-03-10 14:00:00</t>
+        </is>
+      </c>
+      <c r="B118" s="5" t="inlineStr">
+        <is>
+          <t>14:00:00</t>
+        </is>
+      </c>
+      <c r="C118" s="5" t="inlineStr">
+        <is>
+          <t>14:00</t>
+        </is>
+      </c>
+      <c r="D118" s="5" t="inlineStr"/>
+      <c r="E118" s="5" t="inlineStr"/>
+      <c r="F118" s="5" t="inlineStr"/>
+      <c r="G118" s="5" t="inlineStr"/>
+      <c r="H118" s="5" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="I118" s="5" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="J118" s="5" t="inlineStr"/>
+      <c r="K118" s="5" t="inlineStr"/>
+      <c r="L118" s="5" t="inlineStr"/>
+      <c r="M118" s="5" t="inlineStr"/>
+      <c r="N118" s="5" t="inlineStr"/>
+      <c r="O118" s="5" t="inlineStr"/>
+      <c r="P118" s="5" t="inlineStr">
+        <is>
+          <t>Failed to fetch data: Failed to fetch quote data after all retries</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="5" t="inlineStr">
+        <is>
+          <t>2026-03-10 14:05:00</t>
+        </is>
+      </c>
+      <c r="B119" s="5" t="inlineStr">
+        <is>
+          <t>14:05:00</t>
+        </is>
+      </c>
+      <c r="C119" s="5" t="inlineStr">
+        <is>
+          <t>14:05</t>
+        </is>
+      </c>
+      <c r="D119" s="5" t="inlineStr"/>
+      <c r="E119" s="5" t="inlineStr"/>
+      <c r="F119" s="5" t="inlineStr"/>
+      <c r="G119" s="5" t="inlineStr"/>
+      <c r="H119" s="5" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="I119" s="5" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="J119" s="5" t="inlineStr"/>
+      <c r="K119" s="5" t="inlineStr"/>
+      <c r="L119" s="5" t="inlineStr"/>
+      <c r="M119" s="5" t="inlineStr"/>
+      <c r="N119" s="5" t="inlineStr"/>
+      <c r="O119" s="5" t="inlineStr"/>
+      <c r="P119" s="5" t="inlineStr">
+        <is>
+          <t>Data fetch failed: Failed to fetch quote data after all retries</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="5" t="inlineStr">
+        <is>
+          <t>2026-03-10 14:05:00</t>
+        </is>
+      </c>
+      <c r="B120" s="5" t="inlineStr">
+        <is>
+          <t>14:05:00</t>
+        </is>
+      </c>
+      <c r="C120" s="5" t="inlineStr">
+        <is>
+          <t>14:05</t>
+        </is>
+      </c>
+      <c r="D120" s="5" t="inlineStr"/>
+      <c r="E120" s="5" t="inlineStr"/>
+      <c r="F120" s="5" t="inlineStr"/>
+      <c r="G120" s="5" t="inlineStr"/>
+      <c r="H120" s="5" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="I120" s="5" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="J120" s="5" t="inlineStr"/>
+      <c r="K120" s="5" t="inlineStr"/>
+      <c r="L120" s="5" t="inlineStr"/>
+      <c r="M120" s="5" t="inlineStr"/>
+      <c r="N120" s="5" t="inlineStr"/>
+      <c r="O120" s="5" t="inlineStr"/>
+      <c r="P120" s="5" t="inlineStr">
+        <is>
+          <t>Failed to fetch data: Failed to fetch quote data after all retries</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="5" t="inlineStr">
+        <is>
+          <t>2026-03-10 14:10:00</t>
+        </is>
+      </c>
+      <c r="B121" s="5" t="inlineStr">
+        <is>
+          <t>14:10:00</t>
+        </is>
+      </c>
+      <c r="C121" s="5" t="inlineStr">
+        <is>
+          <t>14:10</t>
+        </is>
+      </c>
+      <c r="D121" s="5" t="inlineStr"/>
+      <c r="E121" s="5" t="inlineStr"/>
+      <c r="F121" s="5" t="inlineStr"/>
+      <c r="G121" s="5" t="inlineStr"/>
+      <c r="H121" s="5" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="I121" s="5" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="J121" s="5" t="inlineStr"/>
+      <c r="K121" s="5" t="inlineStr"/>
+      <c r="L121" s="5" t="inlineStr"/>
+      <c r="M121" s="5" t="inlineStr"/>
+      <c r="N121" s="5" t="inlineStr"/>
+      <c r="O121" s="5" t="inlineStr"/>
+      <c r="P121" s="5" t="inlineStr">
+        <is>
+          <t>Data fetch failed: Failed to fetch quote data after all retries</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="5" t="inlineStr">
+        <is>
+          <t>2026-03-10 14:10:00</t>
+        </is>
+      </c>
+      <c r="B122" s="5" t="inlineStr">
+        <is>
+          <t>14:10:00</t>
+        </is>
+      </c>
+      <c r="C122" s="5" t="inlineStr">
+        <is>
+          <t>14:10</t>
+        </is>
+      </c>
+      <c r="D122" s="5" t="inlineStr"/>
+      <c r="E122" s="5" t="inlineStr"/>
+      <c r="F122" s="5" t="inlineStr"/>
+      <c r="G122" s="5" t="inlineStr"/>
+      <c r="H122" s="5" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="I122" s="5" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="J122" s="5" t="inlineStr"/>
+      <c r="K122" s="5" t="inlineStr"/>
+      <c r="L122" s="5" t="inlineStr"/>
+      <c r="M122" s="5" t="inlineStr"/>
+      <c r="N122" s="5" t="inlineStr"/>
+      <c r="O122" s="5" t="inlineStr"/>
+      <c r="P122" s="5" t="inlineStr">
+        <is>
+          <t>Failed to fetch data: Failed to fetch quote data after all retries</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="5" t="inlineStr">
+        <is>
+          <t>2026-03-10 14:15:00</t>
+        </is>
+      </c>
+      <c r="B123" s="5" t="inlineStr">
+        <is>
+          <t>14:15:00</t>
+        </is>
+      </c>
+      <c r="C123" s="5" t="inlineStr">
+        <is>
+          <t>14:15</t>
+        </is>
+      </c>
+      <c r="D123" s="5" t="inlineStr"/>
+      <c r="E123" s="5" t="inlineStr"/>
+      <c r="F123" s="5" t="inlineStr"/>
+      <c r="G123" s="5" t="inlineStr"/>
+      <c r="H123" s="5" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="I123" s="5" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="J123" s="5" t="inlineStr"/>
+      <c r="K123" s="5" t="inlineStr"/>
+      <c r="L123" s="5" t="inlineStr"/>
+      <c r="M123" s="5" t="inlineStr"/>
+      <c r="N123" s="5" t="inlineStr"/>
+      <c r="O123" s="5" t="inlineStr"/>
+      <c r="P123" s="5" t="inlineStr">
+        <is>
+          <t>Data fetch failed: Failed to fetch quote data after all retries</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="5" t="inlineStr">
+        <is>
+          <t>2026-03-10 14:15:00</t>
+        </is>
+      </c>
+      <c r="B124" s="5" t="inlineStr">
+        <is>
+          <t>14:15:00</t>
+        </is>
+      </c>
+      <c r="C124" s="5" t="inlineStr">
+        <is>
+          <t>14:15</t>
+        </is>
+      </c>
+      <c r="D124" s="5" t="inlineStr"/>
+      <c r="E124" s="5" t="inlineStr"/>
+      <c r="F124" s="5" t="inlineStr"/>
+      <c r="G124" s="5" t="inlineStr"/>
+      <c r="H124" s="5" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="I124" s="5" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="J124" s="5" t="inlineStr"/>
+      <c r="K124" s="5" t="inlineStr"/>
+      <c r="L124" s="5" t="inlineStr"/>
+      <c r="M124" s="5" t="inlineStr"/>
+      <c r="N124" s="5" t="inlineStr"/>
+      <c r="O124" s="5" t="inlineStr"/>
+      <c r="P124" s="5" t="inlineStr">
+        <is>
+          <t>Failed to fetch data: Failed to fetch quote data after all retries</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="5" t="inlineStr">
+        <is>
+          <t>2026-03-10 14:20:00</t>
+        </is>
+      </c>
+      <c r="B125" s="5" t="inlineStr">
+        <is>
+          <t>14:20:00</t>
+        </is>
+      </c>
+      <c r="C125" s="5" t="inlineStr">
+        <is>
+          <t>14:20</t>
+        </is>
+      </c>
+      <c r="D125" s="5" t="inlineStr"/>
+      <c r="E125" s="5" t="inlineStr"/>
+      <c r="F125" s="5" t="inlineStr"/>
+      <c r="G125" s="5" t="inlineStr"/>
+      <c r="H125" s="5" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="I125" s="5" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="J125" s="5" t="inlineStr"/>
+      <c r="K125" s="5" t="inlineStr"/>
+      <c r="L125" s="5" t="inlineStr"/>
+      <c r="M125" s="5" t="inlineStr"/>
+      <c r="N125" s="5" t="inlineStr"/>
+      <c r="O125" s="5" t="inlineStr"/>
+      <c r="P125" s="5" t="inlineStr">
+        <is>
+          <t>Data fetch failed: Failed to fetch quote data after all retries</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="5" t="inlineStr">
+        <is>
+          <t>2026-03-10 14:20:00</t>
+        </is>
+      </c>
+      <c r="B126" s="5" t="inlineStr">
+        <is>
+          <t>14:20:00</t>
+        </is>
+      </c>
+      <c r="C126" s="5" t="inlineStr">
+        <is>
+          <t>14:20</t>
+        </is>
+      </c>
+      <c r="D126" s="5" t="inlineStr"/>
+      <c r="E126" s="5" t="inlineStr"/>
+      <c r="F126" s="5" t="inlineStr"/>
+      <c r="G126" s="5" t="inlineStr"/>
+      <c r="H126" s="5" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="I126" s="5" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="J126" s="5" t="inlineStr"/>
+      <c r="K126" s="5" t="inlineStr"/>
+      <c r="L126" s="5" t="inlineStr"/>
+      <c r="M126" s="5" t="inlineStr"/>
+      <c r="N126" s="5" t="inlineStr"/>
+      <c r="O126" s="5" t="inlineStr"/>
+      <c r="P126" s="5" t="inlineStr">
+        <is>
+          <t>Failed to fetch data: Failed to fetch quote data after all retries</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="5" t="inlineStr">
+        <is>
+          <t>2026-03-10 14:25:00</t>
+        </is>
+      </c>
+      <c r="B127" s="5" t="inlineStr">
+        <is>
+          <t>14:25:00</t>
+        </is>
+      </c>
+      <c r="C127" s="5" t="inlineStr">
+        <is>
+          <t>14:25</t>
+        </is>
+      </c>
+      <c r="D127" s="5" t="inlineStr"/>
+      <c r="E127" s="5" t="inlineStr"/>
+      <c r="F127" s="5" t="inlineStr"/>
+      <c r="G127" s="5" t="inlineStr"/>
+      <c r="H127" s="5" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="I127" s="5" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="J127" s="5" t="inlineStr"/>
+      <c r="K127" s="5" t="inlineStr"/>
+      <c r="L127" s="5" t="inlineStr"/>
+      <c r="M127" s="5" t="inlineStr"/>
+      <c r="N127" s="5" t="inlineStr"/>
+      <c r="O127" s="5" t="inlineStr"/>
+      <c r="P127" s="5" t="inlineStr">
+        <is>
+          <t>Data fetch failed: Failed to fetch quote data after all retries</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="5" t="inlineStr">
+        <is>
+          <t>2026-03-10 14:25:00</t>
+        </is>
+      </c>
+      <c r="B128" s="5" t="inlineStr">
+        <is>
+          <t>14:25:00</t>
+        </is>
+      </c>
+      <c r="C128" s="5" t="inlineStr">
+        <is>
+          <t>14:25</t>
+        </is>
+      </c>
+      <c r="D128" s="5" t="inlineStr"/>
+      <c r="E128" s="5" t="inlineStr"/>
+      <c r="F128" s="5" t="inlineStr"/>
+      <c r="G128" s="5" t="inlineStr"/>
+      <c r="H128" s="5" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="I128" s="5" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="J128" s="5" t="inlineStr"/>
+      <c r="K128" s="5" t="inlineStr"/>
+      <c r="L128" s="5" t="inlineStr"/>
+      <c r="M128" s="5" t="inlineStr"/>
+      <c r="N128" s="5" t="inlineStr"/>
+      <c r="O128" s="5" t="inlineStr"/>
+      <c r="P128" s="5" t="inlineStr">
+        <is>
+          <t>Failed to fetch data: Failed to fetch quote data after all retries</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="5" t="inlineStr">
+        <is>
+          <t>2026-03-10 14:30:00</t>
+        </is>
+      </c>
+      <c r="B129" s="5" t="inlineStr">
+        <is>
+          <t>14:30:00</t>
+        </is>
+      </c>
+      <c r="C129" s="5" t="inlineStr">
+        <is>
+          <t>14:30</t>
+        </is>
+      </c>
+      <c r="D129" s="5" t="inlineStr"/>
+      <c r="E129" s="5" t="inlineStr"/>
+      <c r="F129" s="5" t="inlineStr"/>
+      <c r="G129" s="5" t="inlineStr"/>
+      <c r="H129" s="5" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="I129" s="5" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="J129" s="5" t="inlineStr"/>
+      <c r="K129" s="5" t="inlineStr"/>
+      <c r="L129" s="5" t="inlineStr"/>
+      <c r="M129" s="5" t="inlineStr"/>
+      <c r="N129" s="5" t="inlineStr"/>
+      <c r="O129" s="5" t="inlineStr"/>
+      <c r="P129" s="5" t="inlineStr">
+        <is>
+          <t>Data fetch failed: Failed to fetch quote data after all retries</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" s="5" t="inlineStr">
+        <is>
+          <t>2026-03-10 14:30:00</t>
+        </is>
+      </c>
+      <c r="B130" s="5" t="inlineStr">
+        <is>
+          <t>14:30:00</t>
+        </is>
+      </c>
+      <c r="C130" s="5" t="inlineStr">
+        <is>
+          <t>14:30</t>
+        </is>
+      </c>
+      <c r="D130" s="5" t="inlineStr"/>
+      <c r="E130" s="5" t="inlineStr"/>
+      <c r="F130" s="5" t="inlineStr"/>
+      <c r="G130" s="5" t="inlineStr"/>
+      <c r="H130" s="5" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="I130" s="5" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="J130" s="5" t="inlineStr"/>
+      <c r="K130" s="5" t="inlineStr"/>
+      <c r="L130" s="5" t="inlineStr"/>
+      <c r="M130" s="5" t="inlineStr"/>
+      <c r="N130" s="5" t="inlineStr"/>
+      <c r="O130" s="5" t="inlineStr"/>
+      <c r="P130" s="5" t="inlineStr">
+        <is>
+          <t>Failed to fetch data: Failed to fetch quote data after all retries</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" s="5" t="inlineStr">
+        <is>
+          <t>2026-03-10 14:35:00</t>
+        </is>
+      </c>
+      <c r="B131" s="5" t="inlineStr">
+        <is>
+          <t>14:35:00</t>
+        </is>
+      </c>
+      <c r="C131" s="5" t="inlineStr">
+        <is>
+          <t>14:35</t>
+        </is>
+      </c>
+      <c r="D131" s="5" t="inlineStr"/>
+      <c r="E131" s="5" t="inlineStr"/>
+      <c r="F131" s="5" t="inlineStr"/>
+      <c r="G131" s="5" t="inlineStr"/>
+      <c r="H131" s="5" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="I131" s="5" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="J131" s="5" t="inlineStr"/>
+      <c r="K131" s="5" t="inlineStr"/>
+      <c r="L131" s="5" t="inlineStr"/>
+      <c r="M131" s="5" t="inlineStr"/>
+      <c r="N131" s="5" t="inlineStr"/>
+      <c r="O131" s="5" t="inlineStr"/>
+      <c r="P131" s="5" t="inlineStr">
+        <is>
+          <t>Data fetch failed: Failed to fetch quote data after all retries</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" s="5" t="inlineStr">
+        <is>
+          <t>2026-03-10 14:35:00</t>
+        </is>
+      </c>
+      <c r="B132" s="5" t="inlineStr">
+        <is>
+          <t>14:35:00</t>
+        </is>
+      </c>
+      <c r="C132" s="5" t="inlineStr">
+        <is>
+          <t>14:35</t>
+        </is>
+      </c>
+      <c r="D132" s="5" t="inlineStr"/>
+      <c r="E132" s="5" t="inlineStr"/>
+      <c r="F132" s="5" t="inlineStr"/>
+      <c r="G132" s="5" t="inlineStr"/>
+      <c r="H132" s="5" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="I132" s="5" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="J132" s="5" t="inlineStr"/>
+      <c r="K132" s="5" t="inlineStr"/>
+      <c r="L132" s="5" t="inlineStr"/>
+      <c r="M132" s="5" t="inlineStr"/>
+      <c r="N132" s="5" t="inlineStr"/>
+      <c r="O132" s="5" t="inlineStr"/>
+      <c r="P132" s="5" t="inlineStr">
+        <is>
+          <t>Failed to fetch data: Failed to fetch quote data after all retries</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" s="5" t="inlineStr">
+        <is>
+          <t>2026-03-10 14:40:00</t>
+        </is>
+      </c>
+      <c r="B133" s="5" t="inlineStr">
+        <is>
+          <t>14:40:00</t>
+        </is>
+      </c>
+      <c r="C133" s="5" t="inlineStr">
+        <is>
+          <t>14:40</t>
+        </is>
+      </c>
+      <c r="D133" s="5" t="inlineStr"/>
+      <c r="E133" s="5" t="inlineStr"/>
+      <c r="F133" s="5" t="inlineStr"/>
+      <c r="G133" s="5" t="inlineStr"/>
+      <c r="H133" s="5" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="I133" s="5" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="J133" s="5" t="inlineStr"/>
+      <c r="K133" s="5" t="inlineStr"/>
+      <c r="L133" s="5" t="inlineStr"/>
+      <c r="M133" s="5" t="inlineStr"/>
+      <c r="N133" s="5" t="inlineStr"/>
+      <c r="O133" s="5" t="inlineStr"/>
+      <c r="P133" s="5" t="inlineStr">
+        <is>
+          <t>Data fetch failed: Failed to fetch quote data after all retries</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" s="5" t="inlineStr">
+        <is>
+          <t>2026-03-10 14:40:00</t>
+        </is>
+      </c>
+      <c r="B134" s="5" t="inlineStr">
+        <is>
+          <t>14:40:00</t>
+        </is>
+      </c>
+      <c r="C134" s="5" t="inlineStr">
+        <is>
+          <t>14:40</t>
+        </is>
+      </c>
+      <c r="D134" s="5" t="inlineStr"/>
+      <c r="E134" s="5" t="inlineStr"/>
+      <c r="F134" s="5" t="inlineStr"/>
+      <c r="G134" s="5" t="inlineStr"/>
+      <c r="H134" s="5" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="I134" s="5" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="J134" s="5" t="inlineStr"/>
+      <c r="K134" s="5" t="inlineStr"/>
+      <c r="L134" s="5" t="inlineStr"/>
+      <c r="M134" s="5" t="inlineStr"/>
+      <c r="N134" s="5" t="inlineStr"/>
+      <c r="O134" s="5" t="inlineStr"/>
+      <c r="P134" s="5" t="inlineStr">
+        <is>
+          <t>Failed to fetch data: Failed to fetch quote data after all retries</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" s="5" t="inlineStr">
+        <is>
+          <t>2026-03-10 14:45:00</t>
+        </is>
+      </c>
+      <c r="B135" s="5" t="inlineStr">
+        <is>
+          <t>14:45:00</t>
+        </is>
+      </c>
+      <c r="C135" s="5" t="inlineStr">
+        <is>
+          <t>14:45</t>
+        </is>
+      </c>
+      <c r="D135" s="5" t="inlineStr"/>
+      <c r="E135" s="5" t="inlineStr"/>
+      <c r="F135" s="5" t="inlineStr"/>
+      <c r="G135" s="5" t="inlineStr"/>
+      <c r="H135" s="5" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="I135" s="5" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="J135" s="5" t="inlineStr"/>
+      <c r="K135" s="5" t="inlineStr"/>
+      <c r="L135" s="5" t="inlineStr"/>
+      <c r="M135" s="5" t="inlineStr"/>
+      <c r="N135" s="5" t="inlineStr"/>
+      <c r="O135" s="5" t="inlineStr"/>
+      <c r="P135" s="5" t="inlineStr">
+        <is>
+          <t>Data fetch failed: Failed to fetch quote data after all retries</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" s="5" t="inlineStr">
+        <is>
+          <t>2026-03-10 14:45:00</t>
+        </is>
+      </c>
+      <c r="B136" s="5" t="inlineStr">
+        <is>
+          <t>14:45:00</t>
+        </is>
+      </c>
+      <c r="C136" s="5" t="inlineStr">
+        <is>
+          <t>14:45</t>
+        </is>
+      </c>
+      <c r="D136" s="5" t="inlineStr"/>
+      <c r="E136" s="5" t="inlineStr"/>
+      <c r="F136" s="5" t="inlineStr"/>
+      <c r="G136" s="5" t="inlineStr"/>
+      <c r="H136" s="5" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="I136" s="5" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="J136" s="5" t="inlineStr"/>
+      <c r="K136" s="5" t="inlineStr"/>
+      <c r="L136" s="5" t="inlineStr"/>
+      <c r="M136" s="5" t="inlineStr"/>
+      <c r="N136" s="5" t="inlineStr"/>
+      <c r="O136" s="5" t="inlineStr"/>
+      <c r="P136" s="5" t="inlineStr">
+        <is>
+          <t>Failed to fetch data: Failed to fetch quote data after all retries</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" s="5" t="inlineStr">
+        <is>
+          <t>2026-03-10 14:50:00</t>
+        </is>
+      </c>
+      <c r="B137" s="5" t="inlineStr">
+        <is>
+          <t>14:50:00</t>
+        </is>
+      </c>
+      <c r="C137" s="5" t="inlineStr">
+        <is>
+          <t>14:50</t>
+        </is>
+      </c>
+      <c r="D137" s="5" t="inlineStr"/>
+      <c r="E137" s="5" t="inlineStr"/>
+      <c r="F137" s="5" t="inlineStr"/>
+      <c r="G137" s="5" t="inlineStr"/>
+      <c r="H137" s="5" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="I137" s="5" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="J137" s="5" t="inlineStr"/>
+      <c r="K137" s="5" t="inlineStr"/>
+      <c r="L137" s="5" t="inlineStr"/>
+      <c r="M137" s="5" t="inlineStr"/>
+      <c r="N137" s="5" t="inlineStr"/>
+      <c r="O137" s="5" t="inlineStr"/>
+      <c r="P137" s="5" t="inlineStr">
+        <is>
+          <t>Data fetch failed: Failed to fetch quote data after all retries</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" s="5" t="inlineStr">
+        <is>
+          <t>2026-03-10 14:50:00</t>
+        </is>
+      </c>
+      <c r="B138" s="5" t="inlineStr">
+        <is>
+          <t>14:50:00</t>
+        </is>
+      </c>
+      <c r="C138" s="5" t="inlineStr">
+        <is>
+          <t>14:50</t>
+        </is>
+      </c>
+      <c r="D138" s="5" t="inlineStr"/>
+      <c r="E138" s="5" t="inlineStr"/>
+      <c r="F138" s="5" t="inlineStr"/>
+      <c r="G138" s="5" t="inlineStr"/>
+      <c r="H138" s="5" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="I138" s="5" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="J138" s="5" t="inlineStr"/>
+      <c r="K138" s="5" t="inlineStr"/>
+      <c r="L138" s="5" t="inlineStr"/>
+      <c r="M138" s="5" t="inlineStr"/>
+      <c r="N138" s="5" t="inlineStr"/>
+      <c r="O138" s="5" t="inlineStr"/>
+      <c r="P138" s="5" t="inlineStr">
+        <is>
+          <t>Failed to fetch data: Failed to fetch quote data after all retries</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" s="5" t="inlineStr">
+        <is>
+          <t>2026-03-10 14:55:00</t>
+        </is>
+      </c>
+      <c r="B139" s="5" t="inlineStr">
+        <is>
+          <t>14:55:00</t>
+        </is>
+      </c>
+      <c r="C139" s="5" t="inlineStr">
+        <is>
+          <t>14:55</t>
+        </is>
+      </c>
+      <c r="D139" s="5" t="inlineStr"/>
+      <c r="E139" s="5" t="inlineStr"/>
+      <c r="F139" s="5" t="inlineStr"/>
+      <c r="G139" s="5" t="inlineStr"/>
+      <c r="H139" s="5" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="I139" s="5" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="J139" s="5" t="inlineStr"/>
+      <c r="K139" s="5" t="inlineStr"/>
+      <c r="L139" s="5" t="inlineStr"/>
+      <c r="M139" s="5" t="inlineStr"/>
+      <c r="N139" s="5" t="inlineStr"/>
+      <c r="O139" s="5" t="inlineStr"/>
+      <c r="P139" s="5" t="inlineStr">
+        <is>
+          <t>Data fetch failed: Failed to fetch quote data after all retries</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" s="5" t="inlineStr">
+        <is>
+          <t>2026-03-10 14:55:00</t>
+        </is>
+      </c>
+      <c r="B140" s="5" t="inlineStr">
+        <is>
+          <t>14:55:00</t>
+        </is>
+      </c>
+      <c r="C140" s="5" t="inlineStr">
+        <is>
+          <t>14:55</t>
+        </is>
+      </c>
+      <c r="D140" s="5" t="inlineStr"/>
+      <c r="E140" s="5" t="inlineStr"/>
+      <c r="F140" s="5" t="inlineStr"/>
+      <c r="G140" s="5" t="inlineStr"/>
+      <c r="H140" s="5" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="I140" s="5" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="J140" s="5" t="inlineStr"/>
+      <c r="K140" s="5" t="inlineStr"/>
+      <c r="L140" s="5" t="inlineStr"/>
+      <c r="M140" s="5" t="inlineStr"/>
+      <c r="N140" s="5" t="inlineStr"/>
+      <c r="O140" s="5" t="inlineStr"/>
+      <c r="P140" s="5" t="inlineStr">
+        <is>
+          <t>Failed to fetch data: Failed to fetch quote data after all retries</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" s="5" t="inlineStr">
+        <is>
+          <t>2026-03-10 15:00:00</t>
+        </is>
+      </c>
+      <c r="B141" s="5" t="inlineStr">
+        <is>
+          <t>15:00:00</t>
+        </is>
+      </c>
+      <c r="C141" s="5" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="D141" s="5" t="inlineStr"/>
+      <c r="E141" s="5" t="inlineStr"/>
+      <c r="F141" s="5" t="inlineStr"/>
+      <c r="G141" s="5" t="inlineStr"/>
+      <c r="H141" s="5" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="I141" s="5" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="J141" s="5" t="inlineStr"/>
+      <c r="K141" s="5" t="inlineStr"/>
+      <c r="L141" s="5" t="inlineStr"/>
+      <c r="M141" s="5" t="inlineStr"/>
+      <c r="N141" s="5" t="inlineStr"/>
+      <c r="O141" s="5" t="inlineStr"/>
+      <c r="P141" s="5" t="inlineStr">
+        <is>
+          <t>Data fetch failed: Failed to fetch quote data after all retries</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" s="5" t="inlineStr">
+        <is>
+          <t>2026-03-10 15:00:00</t>
+        </is>
+      </c>
+      <c r="B142" s="5" t="inlineStr">
+        <is>
+          <t>15:00:00</t>
+        </is>
+      </c>
+      <c r="C142" s="5" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="D142" s="5" t="inlineStr"/>
+      <c r="E142" s="5" t="inlineStr"/>
+      <c r="F142" s="5" t="inlineStr"/>
+      <c r="G142" s="5" t="inlineStr"/>
+      <c r="H142" s="5" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="I142" s="5" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="J142" s="5" t="inlineStr"/>
+      <c r="K142" s="5" t="inlineStr"/>
+      <c r="L142" s="5" t="inlineStr"/>
+      <c r="M142" s="5" t="inlineStr"/>
+      <c r="N142" s="5" t="inlineStr"/>
+      <c r="O142" s="5" t="inlineStr"/>
+      <c r="P142" s="5" t="inlineStr">
+        <is>
+          <t>Failed to fetch data: Failed to fetch quote data after all retries</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" s="5" t="inlineStr">
+        <is>
+          <t>2026-03-10 15:05:00</t>
+        </is>
+      </c>
+      <c r="B143" s="5" t="inlineStr">
+        <is>
+          <t>15:05:00</t>
+        </is>
+      </c>
+      <c r="C143" s="5" t="inlineStr">
+        <is>
+          <t>15:05</t>
+        </is>
+      </c>
+      <c r="D143" s="5" t="inlineStr"/>
+      <c r="E143" s="5" t="inlineStr"/>
+      <c r="F143" s="5" t="inlineStr"/>
+      <c r="G143" s="5" t="inlineStr"/>
+      <c r="H143" s="5" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="I143" s="5" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="J143" s="5" t="inlineStr"/>
+      <c r="K143" s="5" t="inlineStr"/>
+      <c r="L143" s="5" t="inlineStr"/>
+      <c r="M143" s="5" t="inlineStr"/>
+      <c r="N143" s="5" t="inlineStr"/>
+      <c r="O143" s="5" t="inlineStr"/>
+      <c r="P143" s="5" t="inlineStr">
+        <is>
+          <t>Data fetch failed: Failed to fetch quote data after all retries</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" s="5" t="inlineStr">
+        <is>
+          <t>2026-03-10 15:05:00</t>
+        </is>
+      </c>
+      <c r="B144" s="5" t="inlineStr">
+        <is>
+          <t>15:05:00</t>
+        </is>
+      </c>
+      <c r="C144" s="5" t="inlineStr">
+        <is>
+          <t>15:05</t>
+        </is>
+      </c>
+      <c r="D144" s="5" t="inlineStr"/>
+      <c r="E144" s="5" t="inlineStr"/>
+      <c r="F144" s="5" t="inlineStr"/>
+      <c r="G144" s="5" t="inlineStr"/>
+      <c r="H144" s="5" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="I144" s="5" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="J144" s="5" t="inlineStr"/>
+      <c r="K144" s="5" t="inlineStr"/>
+      <c r="L144" s="5" t="inlineStr"/>
+      <c r="M144" s="5" t="inlineStr"/>
+      <c r="N144" s="5" t="inlineStr"/>
+      <c r="O144" s="5" t="inlineStr"/>
+      <c r="P144" s="5" t="inlineStr">
+        <is>
+          <t>Failed to fetch data: Failed to fetch quote data after all retries</t>
         </is>
       </c>
     </row>
@@ -1931,7 +6793,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L19"/>
+  <dimension ref="A1:L18"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -2009,267 +6871,279 @@
     <row r="2">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>2026-03-05 10:10:20</t>
+          <t>2026-03-09 13:25:21</t>
         </is>
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
-          <t>BUY</t>
+          <t>BUY PE</t>
         </is>
       </c>
       <c r="C2" s="3" t="inlineStr">
         <is>
-          <t>CE</t>
+          <t>PE</t>
         </is>
       </c>
       <c r="D2" s="3" t="n">
-        <v>24550</v>
+        <v>23950</v>
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
-          <t>0.00</t>
-        </is>
-      </c>
-      <c r="F2" s="3" t="n"/>
+          <t>243.45</t>
+        </is>
+      </c>
+      <c r="F2" s="3" t="inlineStr">
+        <is>
+          <t>243.45</t>
+        </is>
+      </c>
       <c r="G2" s="3" t="n"/>
       <c r="H2" s="3" t="n"/>
       <c r="I2" s="3" t="n"/>
       <c r="J2" s="4" t="inlineStr">
         <is>
-          <t>FAILED</t>
-        </is>
-      </c>
-      <c r="K2" s="3" t="n"/>
+          <t>BUY PE</t>
+        </is>
+      </c>
+      <c r="K2" s="3" t="inlineStr">
+        <is>
+          <t>2030915325511786496</t>
+        </is>
+      </c>
       <c r="L2" s="3" t="inlineStr">
         <is>
-          <t>[KOTAK] Order Failed: Missing or expired credentials.</t>
+          <t>Mode: LIVE | Details: Order placed successfully via KiteService | Order_type: MARKET</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>2026-03-05 10:10:20</t>
+          <t>2026-03-09 13:25:21</t>
         </is>
       </c>
       <c r="B3" s="3" t="inlineStr">
         <is>
-          <t>BUY CE</t>
+          <t>BUY</t>
         </is>
       </c>
       <c r="C3" s="3" t="inlineStr">
         <is>
-          <t>CE</t>
+          <t>PE</t>
         </is>
       </c>
       <c r="D3" s="3" t="n">
-        <v>24550</v>
+        <v>23950</v>
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>286.25</t>
-        </is>
-      </c>
-      <c r="F3" s="3" t="inlineStr">
-        <is>
-          <t>286.25</t>
-        </is>
-      </c>
+          <t>0.00</t>
+        </is>
+      </c>
+      <c r="F3" s="3" t="n"/>
       <c r="G3" s="3" t="n"/>
       <c r="H3" s="3" t="n"/>
       <c r="I3" s="3" t="n"/>
       <c r="J3" s="4" t="inlineStr">
         <is>
-          <t>BUY CE</t>
+          <t>SUCCESS</t>
         </is>
       </c>
       <c r="K3" s="3" t="inlineStr">
         <is>
-          <t>2029416699211997184</t>
+          <t>260309000392436</t>
         </is>
       </c>
       <c r="L3" s="3" t="inlineStr">
         <is>
-          <t>Mode: LIVE | Details: Order placed successfully via KiteService | Order_type: MARKET</t>
+          <t>[KOTAK] BUY order placed successfully | Order ID: 260309000392436</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>2026-03-05 10:10:20</t>
+          <t>2026-03-09 13:25:22</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>SL_ORDER</t>
+          <t>BUY</t>
         </is>
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
-          <t>CE</t>
+          <t>PE</t>
         </is>
       </c>
       <c r="D4" s="3" t="n">
-        <v>24550</v>
+        <v>23950</v>
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>257.00</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="F4" s="3" t="n"/>
       <c r="G4" s="3" t="n"/>
-      <c r="H4" s="3" t="inlineStr">
-        <is>
-          <t>257.00</t>
-        </is>
-      </c>
+      <c r="H4" s="3" t="n"/>
       <c r="I4" s="3" t="n"/>
       <c r="J4" s="4" t="inlineStr">
         <is>
-          <t>FAILED</t>
-        </is>
-      </c>
-      <c r="K4" s="3" t="n"/>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="K4" s="3" t="inlineStr">
+        <is>
+          <t>26030900302006</t>
+        </is>
+      </c>
       <c r="L4" s="3" t="inlineStr">
         <is>
-          <t>[KOTAK] SL Order Failed: Not authenticated. Please login to Kotak Neo first.</t>
+          <t>[FYERS] BUY order placed successfully | Order ID: 26030900302006</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>2026-03-05 10:10:21</t>
+          <t>2026-03-09 13:25:22</t>
         </is>
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>BUY</t>
+          <t>SL_ORDER</t>
         </is>
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t>CE</t>
+          <t>PE</t>
         </is>
       </c>
       <c r="D5" s="3" t="n">
-        <v>24550</v>
+        <v>23950</v>
       </c>
       <c r="E5" s="3" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>216.05</t>
         </is>
       </c>
       <c r="F5" s="3" t="n"/>
       <c r="G5" s="3" t="n"/>
-      <c r="H5" s="3" t="n"/>
+      <c r="H5" s="3" t="inlineStr">
+        <is>
+          <t>216.05</t>
+        </is>
+      </c>
       <c r="I5" s="3" t="n"/>
       <c r="J5" s="4" t="inlineStr">
         <is>
-          <t>SUCCESS</t>
-        </is>
-      </c>
-      <c r="K5" s="3" t="inlineStr">
-        <is>
-          <t>26030500127217</t>
-        </is>
-      </c>
+          <t>FAILED</t>
+        </is>
+      </c>
+      <c r="K5" s="3" t="n"/>
       <c r="L5" s="3" t="inlineStr">
         <is>
-          <t>[FYERS] BUY order placed successfully | Order ID: 26030500127217</t>
+          <t>[FYERS] SL Order Failed: limitPrice should be lesser than stopPrice for side SELL</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="inlineStr">
         <is>
-          <t>2026-03-05 10:10:21</t>
+          <t>2026-03-09 13:25:22</t>
         </is>
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>SL_ORDER</t>
+          <t>BUY</t>
         </is>
       </c>
       <c r="C6" s="3" t="inlineStr">
         <is>
-          <t>CE</t>
+          <t>PE</t>
         </is>
       </c>
       <c r="D6" s="3" t="n">
-        <v>24550</v>
+        <v>23950</v>
       </c>
       <c r="E6" s="3" t="inlineStr">
         <is>
-          <t>257.00</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="F6" s="3" t="n"/>
       <c r="G6" s="3" t="n"/>
-      <c r="H6" s="3" t="inlineStr">
-        <is>
-          <t>257.00</t>
-        </is>
-      </c>
+      <c r="H6" s="3" t="n"/>
       <c r="I6" s="3" t="n"/>
       <c r="J6" s="4" t="inlineStr">
         <is>
-          <t>FAILED</t>
-        </is>
-      </c>
-      <c r="K6" s="3" t="n"/>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="K6" s="3" t="inlineStr">
+        <is>
+          <t>260309191231769</t>
+        </is>
+      </c>
       <c r="L6" s="3" t="inlineStr">
         <is>
-          <t>[FYERS] SL Order Failed: limitPrice should be lesser than stopPrice for side SELL</t>
+          <t>[ZERODHA_5] BUY order placed successfully | Order ID: 260309191231769</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>2026-03-05 10:10:34</t>
+          <t>2026-03-09 13:25:22</t>
         </is>
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>BUY</t>
+          <t>SL_ORDER</t>
         </is>
       </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
-          <t>CE</t>
+          <t>PE</t>
         </is>
       </c>
       <c r="D7" s="3" t="n">
-        <v>24550</v>
+        <v>23950</v>
       </c>
       <c r="E7" s="3" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>216.05</t>
         </is>
       </c>
       <c r="F7" s="3" t="n"/>
       <c r="G7" s="3" t="n"/>
-      <c r="H7" s="3" t="n"/>
+      <c r="H7" s="3" t="inlineStr">
+        <is>
+          <t>216.05</t>
+        </is>
+      </c>
       <c r="I7" s="3" t="n"/>
       <c r="J7" s="4" t="inlineStr">
         <is>
-          <t>FAILED</t>
-        </is>
-      </c>
-      <c r="K7" s="3" t="n"/>
+          <t>PLACED</t>
+        </is>
+      </c>
+      <c r="K7" s="3" t="inlineStr">
+        <is>
+          <t>260309191231810</t>
+        </is>
+      </c>
       <c r="L7" s="3" t="inlineStr">
         <is>
-          <t>[DHAN] BUY Order Failed: Invalid SecurityId</t>
+          <t>[ZERODHA_5] SL Order Placed | Trigger: 216.05 | Order ID: 260309191231810</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="inlineStr">
         <is>
-          <t>2026-03-05 10:10:38</t>
+          <t>2026-03-09 13:25:23</t>
         </is>
       </c>
       <c r="B8" s="3" t="inlineStr">
@@ -2279,186 +7153,190 @@
       </c>
       <c r="C8" s="3" t="inlineStr">
         <is>
-          <t>CE</t>
+          <t>PE</t>
         </is>
       </c>
       <c r="D8" s="3" t="n">
-        <v>24550</v>
+        <v>23950</v>
       </c>
       <c r="E8" s="3" t="inlineStr">
         <is>
-          <t>257.00</t>
+          <t>216.05</t>
         </is>
       </c>
       <c r="F8" s="3" t="n"/>
       <c r="G8" s="3" t="n"/>
       <c r="H8" s="3" t="inlineStr">
         <is>
-          <t>257.00</t>
+          <t>216.05</t>
         </is>
       </c>
       <c r="I8" s="3" t="n"/>
       <c r="J8" s="4" t="inlineStr">
         <is>
-          <t>FAILED</t>
-        </is>
-      </c>
-      <c r="K8" s="3" t="n"/>
+          <t>PLACED</t>
+        </is>
+      </c>
+      <c r="K8" s="3" t="inlineStr">
+        <is>
+          <t>260309000392455</t>
+        </is>
+      </c>
       <c r="L8" s="3" t="inlineStr">
         <is>
-          <t>[DHAN] SL Order Failed: Invalid SecurityId</t>
+          <t>[KOTAK] SL Order Placed | Trigger: 216.05 | Order ID: 260309000392455</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="inlineStr">
         <is>
-          <t>2026-03-05 10:10:39</t>
+          <t>2026-03-09 13:25:42</t>
         </is>
       </c>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>SL_ORDER</t>
+          <t>BUY</t>
         </is>
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
-          <t>CE</t>
+          <t>PE</t>
         </is>
       </c>
       <c r="D9" s="3" t="n">
-        <v>24550</v>
+        <v>23950</v>
       </c>
       <c r="E9" s="3" t="inlineStr">
         <is>
-          <t>257.00</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="F9" s="3" t="n"/>
-      <c r="G9" s="3" t="inlineStr">
-        <is>
-          <t>344.75</t>
-        </is>
-      </c>
-      <c r="H9" s="3" t="inlineStr">
-        <is>
-          <t>257.00</t>
-        </is>
-      </c>
+      <c r="G9" s="3" t="n"/>
+      <c r="H9" s="3" t="n"/>
       <c r="I9" s="3" t="n"/>
       <c r="J9" s="4" t="inlineStr">
         <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="K9" s="3" t="inlineStr">
+        <is>
+          <t>222260309562010</t>
+        </is>
+      </c>
+      <c r="L9" s="3" t="inlineStr">
+        <is>
+          <t>[DHAN] BUY order placed successfully | Order ID: 222260309562010</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="3" t="inlineStr">
+        <is>
+          <t>2026-03-09 13:25:43</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>SL_ORDER</t>
+        </is>
+      </c>
+      <c r="C10" s="3" t="inlineStr">
+        <is>
+          <t>PE</t>
+        </is>
+      </c>
+      <c r="D10" s="3" t="n">
+        <v>23950</v>
+      </c>
+      <c r="E10" s="3" t="inlineStr">
+        <is>
+          <t>216.05</t>
+        </is>
+      </c>
+      <c r="F10" s="3" t="n"/>
+      <c r="G10" s="3" t="n"/>
+      <c r="H10" s="3" t="inlineStr">
+        <is>
+          <t>216.05</t>
+        </is>
+      </c>
+      <c r="I10" s="3" t="n"/>
+      <c r="J10" s="4" t="inlineStr">
+        <is>
+          <t>FAILED</t>
+        </is>
+      </c>
+      <c r="K10" s="3" t="n"/>
+      <c r="L10" s="3" t="inlineStr">
+        <is>
+          <t>[DHAN] SL Order Failed: Trigger Price should be greater than Price</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="3" t="inlineStr">
+        <is>
+          <t>2026-03-09 13:25:43</t>
+        </is>
+      </c>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>SL_ORDER</t>
+        </is>
+      </c>
+      <c r="C11" s="3" t="inlineStr">
+        <is>
+          <t>PE</t>
+        </is>
+      </c>
+      <c r="D11" s="3" t="n">
+        <v>23950</v>
+      </c>
+      <c r="E11" s="3" t="inlineStr">
+        <is>
+          <t>216.05</t>
+        </is>
+      </c>
+      <c r="F11" s="3" t="n"/>
+      <c r="G11" s="3" t="inlineStr">
+        <is>
+          <t>298.25</t>
+        </is>
+      </c>
+      <c r="H11" s="3" t="inlineStr">
+        <is>
+          <t>216.05</t>
+        </is>
+      </c>
+      <c r="I11" s="3" t="n"/>
+      <c r="J11" s="4" t="inlineStr">
+        <is>
           <t>PLACED</t>
         </is>
       </c>
-      <c r="K9" s="3" t="inlineStr">
-        <is>
-          <t>2029416700298321920</t>
-        </is>
-      </c>
-      <c r="L9" s="3" t="inlineStr">
-        <is>
-          <t>SL Order Placed | Trigger: 257.00</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="5" t="inlineStr">
-        <is>
-          <t>2026-03-06 09:25:23</t>
-        </is>
-      </c>
-      <c r="B10" s="5" t="inlineStr">
-        <is>
-          <t>BUY</t>
-        </is>
-      </c>
-      <c r="C10" s="5" t="inlineStr">
-        <is>
-          <t>CE</t>
-        </is>
-      </c>
-      <c r="D10" s="5" t="n">
-        <v>24600</v>
-      </c>
-      <c r="E10" s="5" t="inlineStr">
-        <is>
-          <t>0.00</t>
-        </is>
-      </c>
-      <c r="F10" s="5" t="inlineStr"/>
-      <c r="G10" s="5" t="inlineStr"/>
-      <c r="H10" s="5" t="inlineStr"/>
-      <c r="I10" s="5" t="inlineStr"/>
-      <c r="J10" s="6" t="inlineStr">
-        <is>
-          <t>FAILED</t>
-        </is>
-      </c>
-      <c r="K10" s="5" t="inlineStr"/>
-      <c r="L10" s="5" t="inlineStr">
-        <is>
-          <t>[KOTAK] Order Failed: Missing or expired credentials.</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="5" t="inlineStr">
-        <is>
-          <t>2026-03-06 09:25:23</t>
-        </is>
-      </c>
-      <c r="B11" s="5" t="inlineStr">
-        <is>
-          <t>BUY CE</t>
-        </is>
-      </c>
-      <c r="C11" s="5" t="inlineStr">
-        <is>
-          <t>CE</t>
-        </is>
-      </c>
-      <c r="D11" s="5" t="n">
-        <v>24600</v>
-      </c>
-      <c r="E11" s="5" t="inlineStr">
-        <is>
-          <t>234.40</t>
-        </is>
-      </c>
-      <c r="F11" s="5" t="inlineStr">
-        <is>
-          <t>234.40</t>
-        </is>
-      </c>
-      <c r="G11" s="5" t="inlineStr"/>
-      <c r="H11" s="5" t="inlineStr"/>
-      <c r="I11" s="5" t="inlineStr"/>
-      <c r="J11" s="6" t="inlineStr">
-        <is>
-          <t>BUY CE</t>
-        </is>
-      </c>
-      <c r="K11" s="5" t="inlineStr">
-        <is>
-          <t>2029767775626911744</t>
-        </is>
-      </c>
-      <c r="L11" s="5" t="inlineStr">
-        <is>
-          <t>Mode: LIVE | Details: Order placed successfully via KiteService | Order_type: MARKET</t>
+      <c r="K11" s="3" t="inlineStr">
+        <is>
+          <t>2030915328955310080</t>
+        </is>
+      </c>
+      <c r="L11" s="3" t="inlineStr">
+        <is>
+          <t>SL Order Placed | Trigger: 216.05</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="5" t="inlineStr">
         <is>
-          <t>2026-03-06 09:25:23</t>
+          <t>2026-03-10 10:20:21</t>
         </is>
       </c>
       <c r="B12" s="5" t="inlineStr">
         <is>
-          <t>BUY</t>
+          <t>BUY CE</t>
         </is>
       </c>
       <c r="C12" s="5" t="inlineStr">
@@ -2467,33 +7345,41 @@
         </is>
       </c>
       <c r="D12" s="5" t="n">
-        <v>24600</v>
+        <v>24150</v>
       </c>
       <c r="E12" s="5" t="inlineStr">
         <is>
-          <t>0.00</t>
-        </is>
-      </c>
-      <c r="F12" s="5" t="inlineStr"/>
+          <t>119.65</t>
+        </is>
+      </c>
+      <c r="F12" s="5" t="inlineStr">
+        <is>
+          <t>119.65</t>
+        </is>
+      </c>
       <c r="G12" s="5" t="inlineStr"/>
       <c r="H12" s="5" t="inlineStr"/>
       <c r="I12" s="5" t="inlineStr"/>
       <c r="J12" s="6" t="inlineStr">
         <is>
-          <t>FAILED</t>
-        </is>
-      </c>
-      <c r="K12" s="5" t="inlineStr"/>
+          <t>BUY CE</t>
+        </is>
+      </c>
+      <c r="K12" s="5" t="inlineStr">
+        <is>
+          <t>2031231157894832128</t>
+        </is>
+      </c>
       <c r="L12" s="5" t="inlineStr">
         <is>
-          <t>[ZERODHA_5] BUY Order Failed: Could not determine price for NIFTY2631024600CE</t>
+          <t>Mode: LIVE | Details: Order placed successfully via KiteService | Order_type: MARKET</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="5" t="inlineStr">
         <is>
-          <t>2026-03-06 09:25:23</t>
+          <t>2026-03-10 10:20:22</t>
         </is>
       </c>
       <c r="B13" s="5" t="inlineStr">
@@ -2507,42 +7393,46 @@
         </is>
       </c>
       <c r="D13" s="5" t="n">
-        <v>24600</v>
+        <v>24150</v>
       </c>
       <c r="E13" s="5" t="inlineStr">
         <is>
-          <t>205.00</t>
+          <t>89.70</t>
         </is>
       </c>
       <c r="F13" s="5" t="inlineStr"/>
       <c r="G13" s="5" t="inlineStr"/>
       <c r="H13" s="5" t="inlineStr">
         <is>
-          <t>205.00</t>
+          <t>89.70</t>
         </is>
       </c>
       <c r="I13" s="5" t="inlineStr"/>
       <c r="J13" s="6" t="inlineStr">
         <is>
-          <t>FAILED</t>
-        </is>
-      </c>
-      <c r="K13" s="5" t="inlineStr"/>
+          <t>PLACED</t>
+        </is>
+      </c>
+      <c r="K13" s="5" t="inlineStr">
+        <is>
+          <t>2031231161917169664</t>
+        </is>
+      </c>
       <c r="L13" s="5" t="inlineStr">
         <is>
-          <t>[KOTAK] SL Order Failed: Not authenticated. Please login to Kotak Neo first.</t>
+          <t>[ZERODHA_5] SL Order Placed | Trigger: 89.70 | Order ID: 2031231161917169664</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="5" t="inlineStr">
         <is>
-          <t>2026-03-06 09:25:24</t>
+          <t>2026-03-10 10:20:22</t>
         </is>
       </c>
       <c r="B14" s="5" t="inlineStr">
         <is>
-          <t>SL_ORDER</t>
+          <t>BUY</t>
         </is>
       </c>
       <c r="C14" s="5" t="inlineStr">
@@ -2551,37 +7441,37 @@
         </is>
       </c>
       <c r="D14" s="5" t="n">
-        <v>24600</v>
+        <v>24150</v>
       </c>
       <c r="E14" s="5" t="inlineStr">
         <is>
-          <t>205.00</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="F14" s="5" t="inlineStr"/>
       <c r="G14" s="5" t="inlineStr"/>
-      <c r="H14" s="5" t="inlineStr">
-        <is>
-          <t>205.00</t>
-        </is>
-      </c>
+      <c r="H14" s="5" t="inlineStr"/>
       <c r="I14" s="5" t="inlineStr"/>
       <c r="J14" s="6" t="inlineStr">
         <is>
-          <t>FAILED</t>
-        </is>
-      </c>
-      <c r="K14" s="5" t="inlineStr"/>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="K14" s="5" t="inlineStr">
+        <is>
+          <t>2031231161560653824</t>
+        </is>
+      </c>
       <c r="L14" s="5" t="inlineStr">
         <is>
-          <t>[ZERODHA_5] SL Order Failed: Incorrect `api_key` or `access_token`.</t>
+          <t>[ZERODHA_5] BUY order placed successfully | Order ID: 2031231161560653824</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="5" t="inlineStr">
         <is>
-          <t>2026-03-06 09:25:24</t>
+          <t>2026-03-10 10:20:22</t>
         </is>
       </c>
       <c r="B15" s="5" t="inlineStr">
@@ -2595,7 +7485,7 @@
         </is>
       </c>
       <c r="D15" s="5" t="n">
-        <v>24600</v>
+        <v>24150</v>
       </c>
       <c r="E15" s="5" t="inlineStr">
         <is>
@@ -2614,14 +7504,14 @@
       <c r="K15" s="5" t="inlineStr"/>
       <c r="L15" s="5" t="inlineStr">
         <is>
-          <t>[FYERS] BUY Order Failed: Could not authenticate the user</t>
+          <t>[KOTAK] BUY Order Failed: please provide valid product</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="5" t="inlineStr">
         <is>
-          <t>2026-03-06 09:25:24</t>
+          <t>2026-03-10 10:20:23</t>
         </is>
       </c>
       <c r="B16" s="5" t="inlineStr">
@@ -2635,37 +7525,41 @@
         </is>
       </c>
       <c r="D16" s="5" t="n">
-        <v>24600</v>
+        <v>24150</v>
       </c>
       <c r="E16" s="5" t="inlineStr">
         <is>
-          <t>205.00</t>
+          <t>89.70</t>
         </is>
       </c>
       <c r="F16" s="5" t="inlineStr"/>
       <c r="G16" s="5" t="inlineStr"/>
       <c r="H16" s="5" t="inlineStr">
         <is>
-          <t>205.00</t>
+          <t>89.70</t>
         </is>
       </c>
       <c r="I16" s="5" t="inlineStr"/>
       <c r="J16" s="6" t="inlineStr">
         <is>
-          <t>FAILED</t>
-        </is>
-      </c>
-      <c r="K16" s="5" t="inlineStr"/>
+          <t>PLACED</t>
+        </is>
+      </c>
+      <c r="K16" s="5" t="inlineStr">
+        <is>
+          <t>260310000213103</t>
+        </is>
+      </c>
       <c r="L16" s="5" t="inlineStr">
         <is>
-          <t>[FYERS] SL Order Failed: Could not authenticate the user</t>
+          <t>[KOTAK] SL Order Placed | Trigger: 89.70 | Order ID: 260310000213103</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="5" t="inlineStr">
         <is>
-          <t>2026-03-06 09:25:41</t>
+          <t>2026-03-10 10:20:56</t>
         </is>
       </c>
       <c r="B17" s="5" t="inlineStr">
@@ -2679,7 +7573,7 @@
         </is>
       </c>
       <c r="D17" s="5" t="n">
-        <v>24600</v>
+        <v>24150</v>
       </c>
       <c r="E17" s="5" t="inlineStr">
         <is>
@@ -2698,14 +7592,14 @@
       <c r="K17" s="5" t="inlineStr"/>
       <c r="L17" s="5" t="inlineStr">
         <is>
-          <t>[DHAN] BUY Order Failed: Invalid Token</t>
+          <t>[DHAN] Order Failed: Could not resolve security ID.</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="5" t="inlineStr">
         <is>
-          <t>2026-03-06 09:25:42</t>
+          <t>2026-03-10 10:20:59</t>
         </is>
       </c>
       <c r="B18" s="5" t="inlineStr">
@@ -2719,82 +7613,38 @@
         </is>
       </c>
       <c r="D18" s="5" t="n">
-        <v>24600</v>
+        <v>24150</v>
       </c>
       <c r="E18" s="5" t="inlineStr">
         <is>
-          <t>205.00</t>
+          <t>89.70</t>
         </is>
       </c>
       <c r="F18" s="5" t="inlineStr"/>
-      <c r="G18" s="5" t="inlineStr"/>
+      <c r="G18" s="5" t="inlineStr">
+        <is>
+          <t>179.55</t>
+        </is>
+      </c>
       <c r="H18" s="5" t="inlineStr">
         <is>
-          <t>205.00</t>
+          <t>89.70</t>
         </is>
       </c>
       <c r="I18" s="5" t="inlineStr"/>
       <c r="J18" s="6" t="inlineStr">
         <is>
-          <t>FAILED</t>
-        </is>
-      </c>
-      <c r="K18" s="5" t="inlineStr"/>
+          <t>PLACED</t>
+        </is>
+      </c>
+      <c r="K18" s="5" t="inlineStr">
+        <is>
+          <t>2031231161271246848</t>
+        </is>
+      </c>
       <c r="L18" s="5" t="inlineStr">
         <is>
-          <t>[DHAN] SL Order Failed: Invalid Token</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="5" t="inlineStr">
-        <is>
-          <t>2026-03-06 09:25:42</t>
-        </is>
-      </c>
-      <c r="B19" s="5" t="inlineStr">
-        <is>
-          <t>SL_ORDER</t>
-        </is>
-      </c>
-      <c r="C19" s="5" t="inlineStr">
-        <is>
-          <t>CE</t>
-        </is>
-      </c>
-      <c r="D19" s="5" t="n">
-        <v>24600</v>
-      </c>
-      <c r="E19" s="5" t="inlineStr">
-        <is>
-          <t>205.00</t>
-        </is>
-      </c>
-      <c r="F19" s="5" t="inlineStr"/>
-      <c r="G19" s="5" t="inlineStr">
-        <is>
-          <t>293.20</t>
-        </is>
-      </c>
-      <c r="H19" s="5" t="inlineStr">
-        <is>
-          <t>205.00</t>
-        </is>
-      </c>
-      <c r="I19" s="5" t="inlineStr"/>
-      <c r="J19" s="6" t="inlineStr">
-        <is>
-          <t>PLACED</t>
-        </is>
-      </c>
-      <c r="K19" s="5" t="inlineStr">
-        <is>
-          <t>2029767776541270016</t>
-        </is>
-      </c>
-      <c r="L19" s="5" t="inlineStr">
-        <is>
-          <t>SL Order Placed | Trigger: 205.00</t>
+          <t>SL Order Placed | Trigger: 89.70</t>
         </is>
       </c>
     </row>

--- a/Mine/logs/mine_signal_logs.xlsx
+++ b/Mine/logs/mine_signal_logs.xlsx
@@ -40,7 +40,7 @@
       <sz val="11"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="7">
     <fill>
       <patternFill/>
     </fill>
@@ -57,6 +57,24 @@
       <patternFill patternType="solid">
         <fgColor rgb="FF70AD47"/>
         <bgColor rgb="FF70AD47"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00B4C7E7"/>
+        <bgColor rgb="00B4C7E7"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFFFFF"/>
+        <bgColor rgb="00FFFFFF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00C6EFCE"/>
+        <bgColor rgb="00C6EFCE"/>
       </patternFill>
     </fill>
   </fills>
@@ -123,7 +141,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -135,6 +153,15 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -502,7 +529,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P25"/>
+  <dimension ref="A1:P171"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -1797,6 +1824,7318 @@
         </is>
       </c>
     </row>
+    <row r="26">
+      <c r="A26" s="4" t="inlineStr">
+        <is>
+          <t>2026-03-24 09:15:00</t>
+        </is>
+      </c>
+      <c r="B26" s="4" t="inlineStr">
+        <is>
+          <t>09:15:00</t>
+        </is>
+      </c>
+      <c r="C26" s="4" t="inlineStr">
+        <is>
+          <t>09:15</t>
+        </is>
+      </c>
+      <c r="D26" s="4" t="inlineStr">
+        <is>
+          <t>111.60</t>
+        </is>
+      </c>
+      <c r="E26" s="4" t="inlineStr"/>
+      <c r="F26" s="4" t="inlineStr">
+        <is>
+          <t>200.05</t>
+        </is>
+      </c>
+      <c r="G26" s="4" t="inlineStr"/>
+      <c r="H26" s="4" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="I26" s="4" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="J26" s="4" t="inlineStr"/>
+      <c r="K26" s="4" t="inlineStr"/>
+      <c r="L26" s="4" t="inlineStr"/>
+      <c r="M26" s="4" t="inlineStr"/>
+      <c r="N26" s="4" t="inlineStr"/>
+      <c r="O26" s="4" t="inlineStr"/>
+      <c r="P26" s="4" t="inlineStr">
+        <is>
+          <t>High Strike Check | No signal | No signal</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="4" t="inlineStr">
+        <is>
+          <t>2026-03-24 09:15:00</t>
+        </is>
+      </c>
+      <c r="B27" s="4" t="inlineStr">
+        <is>
+          <t>09:15:00</t>
+        </is>
+      </c>
+      <c r="C27" s="4" t="inlineStr">
+        <is>
+          <t>09:15</t>
+        </is>
+      </c>
+      <c r="D27" s="4" t="inlineStr">
+        <is>
+          <t>171.85</t>
+        </is>
+      </c>
+      <c r="E27" s="4" t="inlineStr"/>
+      <c r="F27" s="4" t="inlineStr">
+        <is>
+          <t>182.30</t>
+        </is>
+      </c>
+      <c r="G27" s="4" t="inlineStr"/>
+      <c r="H27" s="4" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="I27" s="4" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="J27" s="4" t="inlineStr"/>
+      <c r="K27" s="4" t="inlineStr"/>
+      <c r="L27" s="4" t="inlineStr"/>
+      <c r="M27" s="4" t="inlineStr"/>
+      <c r="N27" s="4" t="inlineStr"/>
+      <c r="O27" s="4" t="inlineStr"/>
+      <c r="P27" s="4" t="inlineStr">
+        <is>
+          <t>Low Strike Check | No signal | No signal</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="4" t="inlineStr">
+        <is>
+          <t>2026-03-24 09:20:00</t>
+        </is>
+      </c>
+      <c r="B28" s="4" t="inlineStr">
+        <is>
+          <t>09:20:00</t>
+        </is>
+      </c>
+      <c r="C28" s="4" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="D28" s="4" t="inlineStr">
+        <is>
+          <t>118.95</t>
+        </is>
+      </c>
+      <c r="E28" s="4" t="inlineStr"/>
+      <c r="F28" s="4" t="inlineStr">
+        <is>
+          <t>200.05</t>
+        </is>
+      </c>
+      <c r="G28" s="4" t="inlineStr"/>
+      <c r="H28" s="4" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="I28" s="4" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="J28" s="4" t="inlineStr"/>
+      <c r="K28" s="4" t="inlineStr"/>
+      <c r="L28" s="4" t="inlineStr"/>
+      <c r="M28" s="4" t="inlineStr"/>
+      <c r="N28" s="4" t="inlineStr"/>
+      <c r="O28" s="4" t="inlineStr"/>
+      <c r="P28" s="4" t="inlineStr">
+        <is>
+          <t>High Strike Check | No signal | No signal</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="4" t="inlineStr">
+        <is>
+          <t>2026-03-24 09:20:00</t>
+        </is>
+      </c>
+      <c r="B29" s="4" t="inlineStr">
+        <is>
+          <t>09:20:00</t>
+        </is>
+      </c>
+      <c r="C29" s="4" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="D29" s="4" t="inlineStr">
+        <is>
+          <t>209.00</t>
+        </is>
+      </c>
+      <c r="E29" s="4" t="inlineStr"/>
+      <c r="F29" s="4" t="inlineStr">
+        <is>
+          <t>168.55</t>
+        </is>
+      </c>
+      <c r="G29" s="4" t="inlineStr"/>
+      <c r="H29" s="4" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="I29" s="4" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="J29" s="4" t="inlineStr"/>
+      <c r="K29" s="4" t="inlineStr"/>
+      <c r="L29" s="4" t="inlineStr"/>
+      <c r="M29" s="4" t="inlineStr"/>
+      <c r="N29" s="4" t="inlineStr"/>
+      <c r="O29" s="4" t="inlineStr"/>
+      <c r="P29" s="4" t="inlineStr">
+        <is>
+          <t>Low Strike Check | No signal | No signal</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="4" t="inlineStr">
+        <is>
+          <t>2026-03-24 09:25:00</t>
+        </is>
+      </c>
+      <c r="B30" s="4" t="inlineStr">
+        <is>
+          <t>09:25:00</t>
+        </is>
+      </c>
+      <c r="C30" s="4" t="inlineStr">
+        <is>
+          <t>09:25</t>
+        </is>
+      </c>
+      <c r="D30" s="4" t="inlineStr">
+        <is>
+          <t>118.95</t>
+        </is>
+      </c>
+      <c r="E30" s="4" t="inlineStr"/>
+      <c r="F30" s="4" t="inlineStr">
+        <is>
+          <t>200.05</t>
+        </is>
+      </c>
+      <c r="G30" s="4" t="inlineStr"/>
+      <c r="H30" s="4" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="I30" s="4" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="J30" s="4" t="inlineStr"/>
+      <c r="K30" s="4" t="inlineStr"/>
+      <c r="L30" s="4" t="inlineStr"/>
+      <c r="M30" s="4" t="inlineStr"/>
+      <c r="N30" s="4" t="inlineStr"/>
+      <c r="O30" s="4" t="inlineStr"/>
+      <c r="P30" s="4" t="inlineStr">
+        <is>
+          <t>High Strike Check | No signal | No signal</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="4" t="inlineStr">
+        <is>
+          <t>2026-03-24 09:25:00</t>
+        </is>
+      </c>
+      <c r="B31" s="4" t="inlineStr">
+        <is>
+          <t>09:25:00</t>
+        </is>
+      </c>
+      <c r="C31" s="4" t="inlineStr">
+        <is>
+          <t>09:25</t>
+        </is>
+      </c>
+      <c r="D31" s="4" t="inlineStr">
+        <is>
+          <t>209.00</t>
+        </is>
+      </c>
+      <c r="E31" s="4" t="inlineStr"/>
+      <c r="F31" s="4" t="inlineStr">
+        <is>
+          <t>168.55</t>
+        </is>
+      </c>
+      <c r="G31" s="4" t="inlineStr"/>
+      <c r="H31" s="4" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="I31" s="4" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="J31" s="4" t="inlineStr"/>
+      <c r="K31" s="4" t="inlineStr"/>
+      <c r="L31" s="4" t="inlineStr"/>
+      <c r="M31" s="4" t="inlineStr"/>
+      <c r="N31" s="4" t="inlineStr"/>
+      <c r="O31" s="4" t="inlineStr"/>
+      <c r="P31" s="4" t="inlineStr">
+        <is>
+          <t>Low Strike Check | No signal | No signal</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="4" t="inlineStr">
+        <is>
+          <t>2026-03-24 09:30:00</t>
+        </is>
+      </c>
+      <c r="B32" s="4" t="inlineStr">
+        <is>
+          <t>09:30:00</t>
+        </is>
+      </c>
+      <c r="C32" s="4" t="inlineStr">
+        <is>
+          <t>09:30</t>
+        </is>
+      </c>
+      <c r="D32" s="4" t="inlineStr">
+        <is>
+          <t>118.95</t>
+        </is>
+      </c>
+      <c r="E32" s="4" t="inlineStr"/>
+      <c r="F32" s="4" t="inlineStr">
+        <is>
+          <t>200.05</t>
+        </is>
+      </c>
+      <c r="G32" s="4" t="inlineStr"/>
+      <c r="H32" s="4" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="I32" s="4" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="J32" s="4" t="inlineStr"/>
+      <c r="K32" s="4" t="inlineStr"/>
+      <c r="L32" s="4" t="inlineStr"/>
+      <c r="M32" s="4" t="inlineStr"/>
+      <c r="N32" s="4" t="inlineStr"/>
+      <c r="O32" s="4" t="inlineStr"/>
+      <c r="P32" s="4" t="inlineStr">
+        <is>
+          <t>High Strike Check | No signal | No signal</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="4" t="inlineStr">
+        <is>
+          <t>2026-03-24 09:30:00</t>
+        </is>
+      </c>
+      <c r="B33" s="4" t="inlineStr">
+        <is>
+          <t>09:30:00</t>
+        </is>
+      </c>
+      <c r="C33" s="4" t="inlineStr">
+        <is>
+          <t>09:30</t>
+        </is>
+      </c>
+      <c r="D33" s="4" t="inlineStr">
+        <is>
+          <t>209.00</t>
+        </is>
+      </c>
+      <c r="E33" s="4" t="inlineStr"/>
+      <c r="F33" s="4" t="inlineStr">
+        <is>
+          <t>168.55</t>
+        </is>
+      </c>
+      <c r="G33" s="4" t="inlineStr"/>
+      <c r="H33" s="4" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="I33" s="4" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="J33" s="4" t="inlineStr"/>
+      <c r="K33" s="4" t="inlineStr"/>
+      <c r="L33" s="4" t="inlineStr"/>
+      <c r="M33" s="4" t="inlineStr"/>
+      <c r="N33" s="4" t="inlineStr"/>
+      <c r="O33" s="4" t="inlineStr"/>
+      <c r="P33" s="4" t="inlineStr">
+        <is>
+          <t>Low Strike Check | No signal | No signal</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="4" t="inlineStr">
+        <is>
+          <t>2026-03-24 09:35:00</t>
+        </is>
+      </c>
+      <c r="B34" s="4" t="inlineStr">
+        <is>
+          <t>09:35:00</t>
+        </is>
+      </c>
+      <c r="C34" s="4" t="inlineStr">
+        <is>
+          <t>09:35</t>
+        </is>
+      </c>
+      <c r="D34" s="4" t="inlineStr">
+        <is>
+          <t>118.95</t>
+        </is>
+      </c>
+      <c r="E34" s="4" t="inlineStr"/>
+      <c r="F34" s="4" t="inlineStr">
+        <is>
+          <t>200.05</t>
+        </is>
+      </c>
+      <c r="G34" s="4" t="inlineStr"/>
+      <c r="H34" s="4" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="I34" s="4" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="J34" s="4" t="inlineStr"/>
+      <c r="K34" s="4" t="inlineStr"/>
+      <c r="L34" s="4" t="inlineStr"/>
+      <c r="M34" s="4" t="inlineStr"/>
+      <c r="N34" s="4" t="inlineStr"/>
+      <c r="O34" s="4" t="inlineStr"/>
+      <c r="P34" s="4" t="inlineStr">
+        <is>
+          <t>High Strike Check | No signal | No signal</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="4" t="inlineStr">
+        <is>
+          <t>2026-03-24 09:35:00</t>
+        </is>
+      </c>
+      <c r="B35" s="4" t="inlineStr">
+        <is>
+          <t>09:35:00</t>
+        </is>
+      </c>
+      <c r="C35" s="4" t="inlineStr">
+        <is>
+          <t>09:35</t>
+        </is>
+      </c>
+      <c r="D35" s="4" t="inlineStr">
+        <is>
+          <t>209.00</t>
+        </is>
+      </c>
+      <c r="E35" s="4" t="inlineStr"/>
+      <c r="F35" s="4" t="inlineStr">
+        <is>
+          <t>168.55</t>
+        </is>
+      </c>
+      <c r="G35" s="4" t="inlineStr"/>
+      <c r="H35" s="4" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="I35" s="4" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="J35" s="4" t="inlineStr"/>
+      <c r="K35" s="4" t="inlineStr"/>
+      <c r="L35" s="4" t="inlineStr"/>
+      <c r="M35" s="4" t="inlineStr"/>
+      <c r="N35" s="4" t="inlineStr"/>
+      <c r="O35" s="4" t="inlineStr"/>
+      <c r="P35" s="4" t="inlineStr">
+        <is>
+          <t>Low Strike Check | No signal | No signal</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="4" t="inlineStr">
+        <is>
+          <t>2026-03-24 09:40:00</t>
+        </is>
+      </c>
+      <c r="B36" s="4" t="inlineStr">
+        <is>
+          <t>09:40:00</t>
+        </is>
+      </c>
+      <c r="C36" s="4" t="inlineStr">
+        <is>
+          <t>09:40</t>
+        </is>
+      </c>
+      <c r="D36" s="4" t="inlineStr">
+        <is>
+          <t>118.95</t>
+        </is>
+      </c>
+      <c r="E36" s="4" t="inlineStr"/>
+      <c r="F36" s="4" t="inlineStr">
+        <is>
+          <t>200.05</t>
+        </is>
+      </c>
+      <c r="G36" s="4" t="inlineStr"/>
+      <c r="H36" s="4" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="I36" s="4" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="J36" s="4" t="inlineStr"/>
+      <c r="K36" s="4" t="inlineStr"/>
+      <c r="L36" s="4" t="inlineStr"/>
+      <c r="M36" s="4" t="inlineStr"/>
+      <c r="N36" s="4" t="inlineStr"/>
+      <c r="O36" s="4" t="inlineStr"/>
+      <c r="P36" s="4" t="inlineStr">
+        <is>
+          <t>High Strike Check | No signal | No signal</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="4" t="inlineStr">
+        <is>
+          <t>2026-03-24 09:40:00</t>
+        </is>
+      </c>
+      <c r="B37" s="4" t="inlineStr">
+        <is>
+          <t>09:40:00</t>
+        </is>
+      </c>
+      <c r="C37" s="4" t="inlineStr">
+        <is>
+          <t>09:40</t>
+        </is>
+      </c>
+      <c r="D37" s="4" t="inlineStr">
+        <is>
+          <t>209.00</t>
+        </is>
+      </c>
+      <c r="E37" s="4" t="inlineStr"/>
+      <c r="F37" s="4" t="inlineStr">
+        <is>
+          <t>168.55</t>
+        </is>
+      </c>
+      <c r="G37" s="4" t="inlineStr"/>
+      <c r="H37" s="4" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="I37" s="4" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="J37" s="4" t="inlineStr"/>
+      <c r="K37" s="4" t="inlineStr"/>
+      <c r="L37" s="4" t="inlineStr"/>
+      <c r="M37" s="4" t="inlineStr"/>
+      <c r="N37" s="4" t="inlineStr"/>
+      <c r="O37" s="4" t="inlineStr"/>
+      <c r="P37" s="4" t="inlineStr">
+        <is>
+          <t>Low Strike Check | No signal | No signal</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="4" t="inlineStr">
+        <is>
+          <t>2026-03-24 09:45:00</t>
+        </is>
+      </c>
+      <c r="B38" s="4" t="inlineStr">
+        <is>
+          <t>09:45:00</t>
+        </is>
+      </c>
+      <c r="C38" s="4" t="inlineStr">
+        <is>
+          <t>09:45</t>
+        </is>
+      </c>
+      <c r="D38" s="4" t="inlineStr">
+        <is>
+          <t>118.95</t>
+        </is>
+      </c>
+      <c r="E38" s="4" t="inlineStr"/>
+      <c r="F38" s="4" t="inlineStr">
+        <is>
+          <t>200.05</t>
+        </is>
+      </c>
+      <c r="G38" s="4" t="inlineStr"/>
+      <c r="H38" s="4" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="I38" s="4" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="J38" s="4" t="inlineStr"/>
+      <c r="K38" s="4" t="inlineStr"/>
+      <c r="L38" s="4" t="inlineStr"/>
+      <c r="M38" s="4" t="inlineStr"/>
+      <c r="N38" s="4" t="inlineStr"/>
+      <c r="O38" s="4" t="inlineStr"/>
+      <c r="P38" s="4" t="inlineStr">
+        <is>
+          <t>High Strike Check | No signal | No signal</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="4" t="inlineStr">
+        <is>
+          <t>2026-03-24 09:45:00</t>
+        </is>
+      </c>
+      <c r="B39" s="4" t="inlineStr">
+        <is>
+          <t>09:45:00</t>
+        </is>
+      </c>
+      <c r="C39" s="4" t="inlineStr">
+        <is>
+          <t>09:45</t>
+        </is>
+      </c>
+      <c r="D39" s="4" t="inlineStr">
+        <is>
+          <t>209.00</t>
+        </is>
+      </c>
+      <c r="E39" s="4" t="inlineStr"/>
+      <c r="F39" s="4" t="inlineStr">
+        <is>
+          <t>168.55</t>
+        </is>
+      </c>
+      <c r="G39" s="4" t="inlineStr"/>
+      <c r="H39" s="4" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="I39" s="4" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="J39" s="4" t="inlineStr"/>
+      <c r="K39" s="4" t="inlineStr"/>
+      <c r="L39" s="4" t="inlineStr"/>
+      <c r="M39" s="4" t="inlineStr"/>
+      <c r="N39" s="4" t="inlineStr"/>
+      <c r="O39" s="4" t="inlineStr"/>
+      <c r="P39" s="4" t="inlineStr">
+        <is>
+          <t>Low Strike Check | No signal | No signal</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="4" t="inlineStr">
+        <is>
+          <t>2026-03-24 09:50:00</t>
+        </is>
+      </c>
+      <c r="B40" s="4" t="inlineStr">
+        <is>
+          <t>09:50:00</t>
+        </is>
+      </c>
+      <c r="C40" s="4" t="inlineStr">
+        <is>
+          <t>09:50</t>
+        </is>
+      </c>
+      <c r="D40" s="4" t="inlineStr">
+        <is>
+          <t>118.95</t>
+        </is>
+      </c>
+      <c r="E40" s="4" t="inlineStr"/>
+      <c r="F40" s="4" t="inlineStr">
+        <is>
+          <t>200.05</t>
+        </is>
+      </c>
+      <c r="G40" s="4" t="inlineStr"/>
+      <c r="H40" s="4" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="I40" s="4" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="J40" s="4" t="inlineStr"/>
+      <c r="K40" s="4" t="inlineStr"/>
+      <c r="L40" s="4" t="inlineStr"/>
+      <c r="M40" s="4" t="inlineStr"/>
+      <c r="N40" s="4" t="inlineStr"/>
+      <c r="O40" s="4" t="inlineStr"/>
+      <c r="P40" s="4" t="inlineStr">
+        <is>
+          <t>High Strike Check | No signal | No signal</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="4" t="inlineStr">
+        <is>
+          <t>2026-03-24 09:50:00</t>
+        </is>
+      </c>
+      <c r="B41" s="4" t="inlineStr">
+        <is>
+          <t>09:50:00</t>
+        </is>
+      </c>
+      <c r="C41" s="4" t="inlineStr">
+        <is>
+          <t>09:50</t>
+        </is>
+      </c>
+      <c r="D41" s="4" t="inlineStr">
+        <is>
+          <t>209.00</t>
+        </is>
+      </c>
+      <c r="E41" s="4" t="inlineStr"/>
+      <c r="F41" s="4" t="inlineStr">
+        <is>
+          <t>168.55</t>
+        </is>
+      </c>
+      <c r="G41" s="4" t="inlineStr"/>
+      <c r="H41" s="4" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="I41" s="4" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="J41" s="4" t="inlineStr"/>
+      <c r="K41" s="4" t="inlineStr"/>
+      <c r="L41" s="4" t="inlineStr"/>
+      <c r="M41" s="4" t="inlineStr"/>
+      <c r="N41" s="4" t="inlineStr"/>
+      <c r="O41" s="4" t="inlineStr"/>
+      <c r="P41" s="4" t="inlineStr">
+        <is>
+          <t>Low Strike Check | No signal | No signal</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="4" t="inlineStr">
+        <is>
+          <t>2026-03-24 09:55:00</t>
+        </is>
+      </c>
+      <c r="B42" s="4" t="inlineStr">
+        <is>
+          <t>09:55:00</t>
+        </is>
+      </c>
+      <c r="C42" s="4" t="inlineStr">
+        <is>
+          <t>09:55</t>
+        </is>
+      </c>
+      <c r="D42" s="4" t="inlineStr">
+        <is>
+          <t>118.95</t>
+        </is>
+      </c>
+      <c r="E42" s="4" t="inlineStr"/>
+      <c r="F42" s="4" t="inlineStr">
+        <is>
+          <t>200.05</t>
+        </is>
+      </c>
+      <c r="G42" s="4" t="inlineStr"/>
+      <c r="H42" s="4" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="I42" s="4" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="J42" s="4" t="inlineStr"/>
+      <c r="K42" s="4" t="inlineStr"/>
+      <c r="L42" s="4" t="inlineStr"/>
+      <c r="M42" s="4" t="inlineStr"/>
+      <c r="N42" s="4" t="inlineStr"/>
+      <c r="O42" s="4" t="inlineStr"/>
+      <c r="P42" s="4" t="inlineStr">
+        <is>
+          <t>High Strike Check | No signal | No signal</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="4" t="inlineStr">
+        <is>
+          <t>2026-03-24 09:55:00</t>
+        </is>
+      </c>
+      <c r="B43" s="4" t="inlineStr">
+        <is>
+          <t>09:55:00</t>
+        </is>
+      </c>
+      <c r="C43" s="4" t="inlineStr">
+        <is>
+          <t>09:55</t>
+        </is>
+      </c>
+      <c r="D43" s="4" t="inlineStr">
+        <is>
+          <t>209.00</t>
+        </is>
+      </c>
+      <c r="E43" s="4" t="inlineStr"/>
+      <c r="F43" s="4" t="inlineStr">
+        <is>
+          <t>168.55</t>
+        </is>
+      </c>
+      <c r="G43" s="4" t="inlineStr"/>
+      <c r="H43" s="4" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="I43" s="4" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="J43" s="4" t="inlineStr"/>
+      <c r="K43" s="4" t="inlineStr"/>
+      <c r="L43" s="4" t="inlineStr"/>
+      <c r="M43" s="4" t="inlineStr"/>
+      <c r="N43" s="4" t="inlineStr"/>
+      <c r="O43" s="4" t="inlineStr"/>
+      <c r="P43" s="4" t="inlineStr">
+        <is>
+          <t>Low Strike Check | No signal | No signal</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="4" t="inlineStr">
+        <is>
+          <t>2026-03-24 10:00:00</t>
+        </is>
+      </c>
+      <c r="B44" s="4" t="inlineStr">
+        <is>
+          <t>10:00:00</t>
+        </is>
+      </c>
+      <c r="C44" s="4" t="inlineStr">
+        <is>
+          <t>10:00</t>
+        </is>
+      </c>
+      <c r="D44" s="4" t="inlineStr">
+        <is>
+          <t>118.95</t>
+        </is>
+      </c>
+      <c r="E44" s="4" t="inlineStr"/>
+      <c r="F44" s="4" t="inlineStr">
+        <is>
+          <t>200.05</t>
+        </is>
+      </c>
+      <c r="G44" s="4" t="inlineStr"/>
+      <c r="H44" s="4" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="I44" s="4" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="J44" s="4" t="inlineStr"/>
+      <c r="K44" s="4" t="inlineStr"/>
+      <c r="L44" s="4" t="inlineStr"/>
+      <c r="M44" s="4" t="inlineStr"/>
+      <c r="N44" s="4" t="inlineStr"/>
+      <c r="O44" s="4" t="inlineStr"/>
+      <c r="P44" s="4" t="inlineStr">
+        <is>
+          <t>High Strike Check | No signal | No signal</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="4" t="inlineStr">
+        <is>
+          <t>2026-03-24 10:00:00</t>
+        </is>
+      </c>
+      <c r="B45" s="4" t="inlineStr">
+        <is>
+          <t>10:00:00</t>
+        </is>
+      </c>
+      <c r="C45" s="4" t="inlineStr">
+        <is>
+          <t>10:00</t>
+        </is>
+      </c>
+      <c r="D45" s="4" t="inlineStr">
+        <is>
+          <t>209.00</t>
+        </is>
+      </c>
+      <c r="E45" s="4" t="inlineStr"/>
+      <c r="F45" s="4" t="inlineStr">
+        <is>
+          <t>168.55</t>
+        </is>
+      </c>
+      <c r="G45" s="4" t="inlineStr"/>
+      <c r="H45" s="4" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="I45" s="4" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="J45" s="4" t="inlineStr"/>
+      <c r="K45" s="4" t="inlineStr"/>
+      <c r="L45" s="4" t="inlineStr"/>
+      <c r="M45" s="4" t="inlineStr"/>
+      <c r="N45" s="4" t="inlineStr"/>
+      <c r="O45" s="4" t="inlineStr"/>
+      <c r="P45" s="4" t="inlineStr">
+        <is>
+          <t>Low Strike Check | No signal | No signal</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="4" t="inlineStr">
+        <is>
+          <t>2026-03-24 10:05:00</t>
+        </is>
+      </c>
+      <c r="B46" s="4" t="inlineStr">
+        <is>
+          <t>10:05:00</t>
+        </is>
+      </c>
+      <c r="C46" s="4" t="inlineStr">
+        <is>
+          <t>10:05</t>
+        </is>
+      </c>
+      <c r="D46" s="4" t="inlineStr">
+        <is>
+          <t>118.95</t>
+        </is>
+      </c>
+      <c r="E46" s="4" t="inlineStr"/>
+      <c r="F46" s="4" t="inlineStr">
+        <is>
+          <t>200.05</t>
+        </is>
+      </c>
+      <c r="G46" s="4" t="inlineStr"/>
+      <c r="H46" s="4" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="I46" s="4" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="J46" s="4" t="inlineStr"/>
+      <c r="K46" s="4" t="inlineStr"/>
+      <c r="L46" s="4" t="inlineStr"/>
+      <c r="M46" s="4" t="inlineStr"/>
+      <c r="N46" s="4" t="inlineStr"/>
+      <c r="O46" s="4" t="inlineStr"/>
+      <c r="P46" s="4" t="inlineStr">
+        <is>
+          <t>High Strike Check | No signal | No signal</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="4" t="inlineStr">
+        <is>
+          <t>2026-03-24 10:05:00</t>
+        </is>
+      </c>
+      <c r="B47" s="4" t="inlineStr">
+        <is>
+          <t>10:05:00</t>
+        </is>
+      </c>
+      <c r="C47" s="4" t="inlineStr">
+        <is>
+          <t>10:05</t>
+        </is>
+      </c>
+      <c r="D47" s="4" t="inlineStr">
+        <is>
+          <t>209.00</t>
+        </is>
+      </c>
+      <c r="E47" s="4" t="inlineStr"/>
+      <c r="F47" s="4" t="inlineStr">
+        <is>
+          <t>168.55</t>
+        </is>
+      </c>
+      <c r="G47" s="4" t="inlineStr"/>
+      <c r="H47" s="4" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="I47" s="4" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="J47" s="4" t="inlineStr"/>
+      <c r="K47" s="4" t="inlineStr"/>
+      <c r="L47" s="4" t="inlineStr"/>
+      <c r="M47" s="4" t="inlineStr"/>
+      <c r="N47" s="4" t="inlineStr"/>
+      <c r="O47" s="4" t="inlineStr"/>
+      <c r="P47" s="4" t="inlineStr">
+        <is>
+          <t>Low Strike Check | No signal | No signal</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="4" t="inlineStr">
+        <is>
+          <t>2026-03-24 10:10:00</t>
+        </is>
+      </c>
+      <c r="B48" s="4" t="inlineStr">
+        <is>
+          <t>10:10:00</t>
+        </is>
+      </c>
+      <c r="C48" s="4" t="inlineStr">
+        <is>
+          <t>10:10</t>
+        </is>
+      </c>
+      <c r="D48" s="4" t="inlineStr">
+        <is>
+          <t>118.95</t>
+        </is>
+      </c>
+      <c r="E48" s="4" t="inlineStr"/>
+      <c r="F48" s="4" t="inlineStr">
+        <is>
+          <t>200.05</t>
+        </is>
+      </c>
+      <c r="G48" s="4" t="inlineStr"/>
+      <c r="H48" s="4" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="I48" s="4" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="J48" s="4" t="inlineStr"/>
+      <c r="K48" s="4" t="inlineStr"/>
+      <c r="L48" s="4" t="inlineStr"/>
+      <c r="M48" s="4" t="inlineStr"/>
+      <c r="N48" s="4" t="inlineStr"/>
+      <c r="O48" s="4" t="inlineStr"/>
+      <c r="P48" s="4" t="inlineStr">
+        <is>
+          <t>High Strike Check | No signal | No signal</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="4" t="inlineStr">
+        <is>
+          <t>2026-03-24 10:10:00</t>
+        </is>
+      </c>
+      <c r="B49" s="4" t="inlineStr">
+        <is>
+          <t>10:10:00</t>
+        </is>
+      </c>
+      <c r="C49" s="4" t="inlineStr">
+        <is>
+          <t>10:10</t>
+        </is>
+      </c>
+      <c r="D49" s="4" t="inlineStr">
+        <is>
+          <t>209.00</t>
+        </is>
+      </c>
+      <c r="E49" s="4" t="inlineStr"/>
+      <c r="F49" s="4" t="inlineStr">
+        <is>
+          <t>168.55</t>
+        </is>
+      </c>
+      <c r="G49" s="4" t="inlineStr"/>
+      <c r="H49" s="4" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="I49" s="4" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="J49" s="4" t="inlineStr"/>
+      <c r="K49" s="4" t="inlineStr"/>
+      <c r="L49" s="4" t="inlineStr"/>
+      <c r="M49" s="4" t="inlineStr"/>
+      <c r="N49" s="4" t="inlineStr"/>
+      <c r="O49" s="4" t="inlineStr"/>
+      <c r="P49" s="4" t="inlineStr">
+        <is>
+          <t>Low Strike Check | No signal | No signal</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="4" t="inlineStr">
+        <is>
+          <t>2026-03-24 10:15:00</t>
+        </is>
+      </c>
+      <c r="B50" s="4" t="inlineStr">
+        <is>
+          <t>10:15:00</t>
+        </is>
+      </c>
+      <c r="C50" s="4" t="inlineStr">
+        <is>
+          <t>10:15</t>
+        </is>
+      </c>
+      <c r="D50" s="4" t="inlineStr">
+        <is>
+          <t>118.95</t>
+        </is>
+      </c>
+      <c r="E50" s="4" t="inlineStr"/>
+      <c r="F50" s="4" t="inlineStr">
+        <is>
+          <t>200.05</t>
+        </is>
+      </c>
+      <c r="G50" s="4" t="inlineStr"/>
+      <c r="H50" s="4" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="I50" s="4" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="J50" s="4" t="inlineStr"/>
+      <c r="K50" s="4" t="inlineStr"/>
+      <c r="L50" s="4" t="inlineStr"/>
+      <c r="M50" s="4" t="inlineStr"/>
+      <c r="N50" s="4" t="inlineStr"/>
+      <c r="O50" s="4" t="inlineStr"/>
+      <c r="P50" s="4" t="inlineStr">
+        <is>
+          <t>High Strike Check | No signal | No signal</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="4" t="inlineStr">
+        <is>
+          <t>2026-03-24 10:15:00</t>
+        </is>
+      </c>
+      <c r="B51" s="4" t="inlineStr">
+        <is>
+          <t>10:15:00</t>
+        </is>
+      </c>
+      <c r="C51" s="4" t="inlineStr">
+        <is>
+          <t>10:15</t>
+        </is>
+      </c>
+      <c r="D51" s="4" t="inlineStr">
+        <is>
+          <t>209.00</t>
+        </is>
+      </c>
+      <c r="E51" s="4" t="inlineStr"/>
+      <c r="F51" s="4" t="inlineStr">
+        <is>
+          <t>168.55</t>
+        </is>
+      </c>
+      <c r="G51" s="4" t="inlineStr"/>
+      <c r="H51" s="4" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="I51" s="4" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="J51" s="4" t="inlineStr"/>
+      <c r="K51" s="4" t="inlineStr"/>
+      <c r="L51" s="4" t="inlineStr"/>
+      <c r="M51" s="4" t="inlineStr"/>
+      <c r="N51" s="4" t="inlineStr"/>
+      <c r="O51" s="4" t="inlineStr"/>
+      <c r="P51" s="4" t="inlineStr">
+        <is>
+          <t>Low Strike Check | No signal | No signal</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="4" t="inlineStr">
+        <is>
+          <t>2026-03-24 10:20:00</t>
+        </is>
+      </c>
+      <c r="B52" s="4" t="inlineStr">
+        <is>
+          <t>10:20:00</t>
+        </is>
+      </c>
+      <c r="C52" s="4" t="inlineStr">
+        <is>
+          <t>10:20</t>
+        </is>
+      </c>
+      <c r="D52" s="4" t="inlineStr">
+        <is>
+          <t>118.95</t>
+        </is>
+      </c>
+      <c r="E52" s="4" t="inlineStr"/>
+      <c r="F52" s="4" t="inlineStr">
+        <is>
+          <t>200.05</t>
+        </is>
+      </c>
+      <c r="G52" s="4" t="inlineStr"/>
+      <c r="H52" s="4" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="I52" s="4" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="J52" s="4" t="inlineStr"/>
+      <c r="K52" s="4" t="inlineStr"/>
+      <c r="L52" s="4" t="inlineStr"/>
+      <c r="M52" s="4" t="inlineStr"/>
+      <c r="N52" s="4" t="inlineStr"/>
+      <c r="O52" s="4" t="inlineStr"/>
+      <c r="P52" s="4" t="inlineStr">
+        <is>
+          <t>High Strike Check | No signal | No signal</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="4" t="inlineStr">
+        <is>
+          <t>2026-03-24 10:20:00</t>
+        </is>
+      </c>
+      <c r="B53" s="4" t="inlineStr">
+        <is>
+          <t>10:20:00</t>
+        </is>
+      </c>
+      <c r="C53" s="4" t="inlineStr">
+        <is>
+          <t>10:20</t>
+        </is>
+      </c>
+      <c r="D53" s="4" t="inlineStr">
+        <is>
+          <t>209.00</t>
+        </is>
+      </c>
+      <c r="E53" s="4" t="inlineStr"/>
+      <c r="F53" s="4" t="inlineStr">
+        <is>
+          <t>168.55</t>
+        </is>
+      </c>
+      <c r="G53" s="4" t="inlineStr"/>
+      <c r="H53" s="4" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="I53" s="4" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="J53" s="4" t="inlineStr"/>
+      <c r="K53" s="4" t="inlineStr"/>
+      <c r="L53" s="4" t="inlineStr"/>
+      <c r="M53" s="4" t="inlineStr"/>
+      <c r="N53" s="4" t="inlineStr"/>
+      <c r="O53" s="4" t="inlineStr"/>
+      <c r="P53" s="4" t="inlineStr">
+        <is>
+          <t>Low Strike Check | No signal | No signal</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="4" t="inlineStr">
+        <is>
+          <t>2026-03-24 10:25:00</t>
+        </is>
+      </c>
+      <c r="B54" s="4" t="inlineStr">
+        <is>
+          <t>10:25:00</t>
+        </is>
+      </c>
+      <c r="C54" s="4" t="inlineStr">
+        <is>
+          <t>10:25</t>
+        </is>
+      </c>
+      <c r="D54" s="4" t="inlineStr">
+        <is>
+          <t>118.95</t>
+        </is>
+      </c>
+      <c r="E54" s="4" t="inlineStr"/>
+      <c r="F54" s="4" t="inlineStr">
+        <is>
+          <t>200.05</t>
+        </is>
+      </c>
+      <c r="G54" s="4" t="inlineStr"/>
+      <c r="H54" s="4" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="I54" s="4" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="J54" s="4" t="inlineStr"/>
+      <c r="K54" s="4" t="inlineStr"/>
+      <c r="L54" s="4" t="inlineStr"/>
+      <c r="M54" s="4" t="inlineStr"/>
+      <c r="N54" s="4" t="inlineStr"/>
+      <c r="O54" s="4" t="inlineStr"/>
+      <c r="P54" s="4" t="inlineStr">
+        <is>
+          <t>High Strike Check | No signal | No signal</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="4" t="inlineStr">
+        <is>
+          <t>2026-03-24 10:25:00</t>
+        </is>
+      </c>
+      <c r="B55" s="4" t="inlineStr">
+        <is>
+          <t>10:25:00</t>
+        </is>
+      </c>
+      <c r="C55" s="4" t="inlineStr">
+        <is>
+          <t>10:25</t>
+        </is>
+      </c>
+      <c r="D55" s="4" t="inlineStr">
+        <is>
+          <t>209.00</t>
+        </is>
+      </c>
+      <c r="E55" s="4" t="inlineStr"/>
+      <c r="F55" s="4" t="inlineStr">
+        <is>
+          <t>168.55</t>
+        </is>
+      </c>
+      <c r="G55" s="4" t="inlineStr"/>
+      <c r="H55" s="4" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="I55" s="4" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="J55" s="4" t="inlineStr"/>
+      <c r="K55" s="4" t="inlineStr"/>
+      <c r="L55" s="4" t="inlineStr"/>
+      <c r="M55" s="4" t="inlineStr"/>
+      <c r="N55" s="4" t="inlineStr"/>
+      <c r="O55" s="4" t="inlineStr"/>
+      <c r="P55" s="4" t="inlineStr">
+        <is>
+          <t>Low Strike Check | No signal | No signal</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="4" t="inlineStr">
+        <is>
+          <t>2026-03-24 10:30:00</t>
+        </is>
+      </c>
+      <c r="B56" s="4" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="C56" s="4" t="inlineStr">
+        <is>
+          <t>10:30</t>
+        </is>
+      </c>
+      <c r="D56" s="4" t="inlineStr">
+        <is>
+          <t>118.95</t>
+        </is>
+      </c>
+      <c r="E56" s="4" t="inlineStr"/>
+      <c r="F56" s="4" t="inlineStr">
+        <is>
+          <t>200.05</t>
+        </is>
+      </c>
+      <c r="G56" s="4" t="inlineStr"/>
+      <c r="H56" s="4" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="I56" s="4" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="J56" s="4" t="inlineStr"/>
+      <c r="K56" s="4" t="inlineStr"/>
+      <c r="L56" s="4" t="inlineStr"/>
+      <c r="M56" s="4" t="inlineStr"/>
+      <c r="N56" s="4" t="inlineStr"/>
+      <c r="O56" s="4" t="inlineStr"/>
+      <c r="P56" s="4" t="inlineStr">
+        <is>
+          <t>High Strike Check | No signal | No signal</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="4" t="inlineStr">
+        <is>
+          <t>2026-03-24 10:30:00</t>
+        </is>
+      </c>
+      <c r="B57" s="4" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="C57" s="4" t="inlineStr">
+        <is>
+          <t>10:30</t>
+        </is>
+      </c>
+      <c r="D57" s="4" t="inlineStr">
+        <is>
+          <t>209.00</t>
+        </is>
+      </c>
+      <c r="E57" s="4" t="inlineStr"/>
+      <c r="F57" s="4" t="inlineStr">
+        <is>
+          <t>168.55</t>
+        </is>
+      </c>
+      <c r="G57" s="4" t="inlineStr"/>
+      <c r="H57" s="4" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="I57" s="4" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="J57" s="4" t="inlineStr"/>
+      <c r="K57" s="4" t="inlineStr"/>
+      <c r="L57" s="4" t="inlineStr"/>
+      <c r="M57" s="4" t="inlineStr"/>
+      <c r="N57" s="4" t="inlineStr"/>
+      <c r="O57" s="4" t="inlineStr"/>
+      <c r="P57" s="4" t="inlineStr">
+        <is>
+          <t>Low Strike Check | No signal | No signal</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="4" t="inlineStr">
+        <is>
+          <t>2026-03-24 10:35:00</t>
+        </is>
+      </c>
+      <c r="B58" s="4" t="inlineStr">
+        <is>
+          <t>10:35:00</t>
+        </is>
+      </c>
+      <c r="C58" s="4" t="inlineStr">
+        <is>
+          <t>10:35</t>
+        </is>
+      </c>
+      <c r="D58" s="4" t="inlineStr">
+        <is>
+          <t>118.95</t>
+        </is>
+      </c>
+      <c r="E58" s="4" t="inlineStr"/>
+      <c r="F58" s="4" t="inlineStr">
+        <is>
+          <t>200.05</t>
+        </is>
+      </c>
+      <c r="G58" s="4" t="inlineStr"/>
+      <c r="H58" s="4" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="I58" s="4" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="J58" s="4" t="inlineStr"/>
+      <c r="K58" s="4" t="inlineStr"/>
+      <c r="L58" s="4" t="inlineStr"/>
+      <c r="M58" s="4" t="inlineStr"/>
+      <c r="N58" s="4" t="inlineStr"/>
+      <c r="O58" s="4" t="inlineStr"/>
+      <c r="P58" s="4" t="inlineStr">
+        <is>
+          <t>High Strike Check | No signal | No signal</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="4" t="inlineStr">
+        <is>
+          <t>2026-03-24 10:35:00</t>
+        </is>
+      </c>
+      <c r="B59" s="4" t="inlineStr">
+        <is>
+          <t>10:35:00</t>
+        </is>
+      </c>
+      <c r="C59" s="4" t="inlineStr">
+        <is>
+          <t>10:35</t>
+        </is>
+      </c>
+      <c r="D59" s="4" t="inlineStr">
+        <is>
+          <t>209.00</t>
+        </is>
+      </c>
+      <c r="E59" s="4" t="inlineStr"/>
+      <c r="F59" s="4" t="inlineStr">
+        <is>
+          <t>168.55</t>
+        </is>
+      </c>
+      <c r="G59" s="4" t="inlineStr"/>
+      <c r="H59" s="4" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="I59" s="4" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="J59" s="4" t="inlineStr"/>
+      <c r="K59" s="4" t="inlineStr"/>
+      <c r="L59" s="4" t="inlineStr"/>
+      <c r="M59" s="4" t="inlineStr"/>
+      <c r="N59" s="4" t="inlineStr"/>
+      <c r="O59" s="4" t="inlineStr"/>
+      <c r="P59" s="4" t="inlineStr">
+        <is>
+          <t>Low Strike Check | No signal | No signal</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="4" t="inlineStr">
+        <is>
+          <t>2026-03-24 10:40:00</t>
+        </is>
+      </c>
+      <c r="B60" s="4" t="inlineStr">
+        <is>
+          <t>10:40:00</t>
+        </is>
+      </c>
+      <c r="C60" s="4" t="inlineStr">
+        <is>
+          <t>10:40</t>
+        </is>
+      </c>
+      <c r="D60" s="4" t="inlineStr">
+        <is>
+          <t>118.95</t>
+        </is>
+      </c>
+      <c r="E60" s="4" t="inlineStr"/>
+      <c r="F60" s="4" t="inlineStr">
+        <is>
+          <t>200.05</t>
+        </is>
+      </c>
+      <c r="G60" s="4" t="inlineStr"/>
+      <c r="H60" s="4" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="I60" s="4" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="J60" s="4" t="inlineStr"/>
+      <c r="K60" s="4" t="inlineStr"/>
+      <c r="L60" s="4" t="inlineStr"/>
+      <c r="M60" s="4" t="inlineStr"/>
+      <c r="N60" s="4" t="inlineStr"/>
+      <c r="O60" s="4" t="inlineStr"/>
+      <c r="P60" s="4" t="inlineStr">
+        <is>
+          <t>High Strike Check | No signal | No signal</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="4" t="inlineStr">
+        <is>
+          <t>2026-03-24 10:40:00</t>
+        </is>
+      </c>
+      <c r="B61" s="4" t="inlineStr">
+        <is>
+          <t>10:40:00</t>
+        </is>
+      </c>
+      <c r="C61" s="4" t="inlineStr">
+        <is>
+          <t>10:40</t>
+        </is>
+      </c>
+      <c r="D61" s="4" t="inlineStr">
+        <is>
+          <t>209.00</t>
+        </is>
+      </c>
+      <c r="E61" s="4" t="inlineStr"/>
+      <c r="F61" s="4" t="inlineStr">
+        <is>
+          <t>168.55</t>
+        </is>
+      </c>
+      <c r="G61" s="4" t="inlineStr"/>
+      <c r="H61" s="4" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="I61" s="4" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="J61" s="4" t="inlineStr"/>
+      <c r="K61" s="4" t="inlineStr"/>
+      <c r="L61" s="4" t="inlineStr"/>
+      <c r="M61" s="4" t="inlineStr"/>
+      <c r="N61" s="4" t="inlineStr"/>
+      <c r="O61" s="4" t="inlineStr"/>
+      <c r="P61" s="4" t="inlineStr">
+        <is>
+          <t>Low Strike Check | No signal | No signal</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="4" t="inlineStr">
+        <is>
+          <t>2026-03-24 10:45:00</t>
+        </is>
+      </c>
+      <c r="B62" s="4" t="inlineStr">
+        <is>
+          <t>10:45:00</t>
+        </is>
+      </c>
+      <c r="C62" s="4" t="inlineStr">
+        <is>
+          <t>10:45</t>
+        </is>
+      </c>
+      <c r="D62" s="4" t="inlineStr">
+        <is>
+          <t>118.95</t>
+        </is>
+      </c>
+      <c r="E62" s="4" t="inlineStr"/>
+      <c r="F62" s="4" t="inlineStr">
+        <is>
+          <t>200.05</t>
+        </is>
+      </c>
+      <c r="G62" s="4" t="inlineStr"/>
+      <c r="H62" s="4" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="I62" s="4" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="J62" s="4" t="inlineStr"/>
+      <c r="K62" s="4" t="inlineStr"/>
+      <c r="L62" s="4" t="inlineStr"/>
+      <c r="M62" s="4" t="inlineStr"/>
+      <c r="N62" s="4" t="inlineStr"/>
+      <c r="O62" s="4" t="inlineStr"/>
+      <c r="P62" s="4" t="inlineStr">
+        <is>
+          <t>High Strike Check | No signal | No signal</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="4" t="inlineStr">
+        <is>
+          <t>2026-03-24 10:45:00</t>
+        </is>
+      </c>
+      <c r="B63" s="4" t="inlineStr">
+        <is>
+          <t>10:45:00</t>
+        </is>
+      </c>
+      <c r="C63" s="4" t="inlineStr">
+        <is>
+          <t>10:45</t>
+        </is>
+      </c>
+      <c r="D63" s="4" t="inlineStr">
+        <is>
+          <t>209.00</t>
+        </is>
+      </c>
+      <c r="E63" s="4" t="inlineStr"/>
+      <c r="F63" s="4" t="inlineStr">
+        <is>
+          <t>168.55</t>
+        </is>
+      </c>
+      <c r="G63" s="4" t="inlineStr"/>
+      <c r="H63" s="4" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="I63" s="4" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="J63" s="4" t="inlineStr"/>
+      <c r="K63" s="4" t="inlineStr"/>
+      <c r="L63" s="4" t="inlineStr"/>
+      <c r="M63" s="4" t="inlineStr"/>
+      <c r="N63" s="4" t="inlineStr"/>
+      <c r="O63" s="4" t="inlineStr"/>
+      <c r="P63" s="4" t="inlineStr">
+        <is>
+          <t>Low Strike Check | No signal | No signal</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="4" t="inlineStr">
+        <is>
+          <t>2026-03-24 10:50:00</t>
+        </is>
+      </c>
+      <c r="B64" s="4" t="inlineStr">
+        <is>
+          <t>10:50:00</t>
+        </is>
+      </c>
+      <c r="C64" s="4" t="inlineStr">
+        <is>
+          <t>10:50</t>
+        </is>
+      </c>
+      <c r="D64" s="4" t="inlineStr">
+        <is>
+          <t>118.95</t>
+        </is>
+      </c>
+      <c r="E64" s="4" t="inlineStr"/>
+      <c r="F64" s="4" t="inlineStr">
+        <is>
+          <t>200.05</t>
+        </is>
+      </c>
+      <c r="G64" s="4" t="inlineStr"/>
+      <c r="H64" s="4" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="I64" s="4" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="J64" s="4" t="inlineStr"/>
+      <c r="K64" s="4" t="inlineStr"/>
+      <c r="L64" s="4" t="inlineStr"/>
+      <c r="M64" s="4" t="inlineStr"/>
+      <c r="N64" s="4" t="inlineStr"/>
+      <c r="O64" s="4" t="inlineStr"/>
+      <c r="P64" s="4" t="inlineStr">
+        <is>
+          <t>High Strike Check | No signal | No signal</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="4" t="inlineStr">
+        <is>
+          <t>2026-03-24 10:50:00</t>
+        </is>
+      </c>
+      <c r="B65" s="4" t="inlineStr">
+        <is>
+          <t>10:50:00</t>
+        </is>
+      </c>
+      <c r="C65" s="4" t="inlineStr">
+        <is>
+          <t>10:50</t>
+        </is>
+      </c>
+      <c r="D65" s="4" t="inlineStr">
+        <is>
+          <t>209.00</t>
+        </is>
+      </c>
+      <c r="E65" s="4" t="inlineStr"/>
+      <c r="F65" s="4" t="inlineStr">
+        <is>
+          <t>168.55</t>
+        </is>
+      </c>
+      <c r="G65" s="4" t="inlineStr"/>
+      <c r="H65" s="4" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="I65" s="4" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="J65" s="4" t="inlineStr"/>
+      <c r="K65" s="4" t="inlineStr"/>
+      <c r="L65" s="4" t="inlineStr"/>
+      <c r="M65" s="4" t="inlineStr"/>
+      <c r="N65" s="4" t="inlineStr"/>
+      <c r="O65" s="4" t="inlineStr"/>
+      <c r="P65" s="4" t="inlineStr">
+        <is>
+          <t>Low Strike Check | No signal | No signal</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="4" t="inlineStr">
+        <is>
+          <t>2026-03-24 10:55:00</t>
+        </is>
+      </c>
+      <c r="B66" s="4" t="inlineStr">
+        <is>
+          <t>10:55:00</t>
+        </is>
+      </c>
+      <c r="C66" s="4" t="inlineStr">
+        <is>
+          <t>10:55</t>
+        </is>
+      </c>
+      <c r="D66" s="4" t="inlineStr">
+        <is>
+          <t>118.95</t>
+        </is>
+      </c>
+      <c r="E66" s="4" t="inlineStr"/>
+      <c r="F66" s="4" t="inlineStr">
+        <is>
+          <t>200.05</t>
+        </is>
+      </c>
+      <c r="G66" s="4" t="inlineStr"/>
+      <c r="H66" s="4" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="I66" s="4" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="J66" s="4" t="inlineStr"/>
+      <c r="K66" s="4" t="inlineStr"/>
+      <c r="L66" s="4" t="inlineStr"/>
+      <c r="M66" s="4" t="inlineStr"/>
+      <c r="N66" s="4" t="inlineStr"/>
+      <c r="O66" s="4" t="inlineStr"/>
+      <c r="P66" s="4" t="inlineStr">
+        <is>
+          <t>High Strike Check | No signal | No signal</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="4" t="inlineStr">
+        <is>
+          <t>2026-03-24 10:55:00</t>
+        </is>
+      </c>
+      <c r="B67" s="4" t="inlineStr">
+        <is>
+          <t>10:55:00</t>
+        </is>
+      </c>
+      <c r="C67" s="4" t="inlineStr">
+        <is>
+          <t>10:55</t>
+        </is>
+      </c>
+      <c r="D67" s="4" t="inlineStr">
+        <is>
+          <t>209.00</t>
+        </is>
+      </c>
+      <c r="E67" s="4" t="inlineStr"/>
+      <c r="F67" s="4" t="inlineStr">
+        <is>
+          <t>168.55</t>
+        </is>
+      </c>
+      <c r="G67" s="4" t="inlineStr"/>
+      <c r="H67" s="4" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="I67" s="4" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="J67" s="4" t="inlineStr"/>
+      <c r="K67" s="4" t="inlineStr"/>
+      <c r="L67" s="4" t="inlineStr"/>
+      <c r="M67" s="4" t="inlineStr"/>
+      <c r="N67" s="4" t="inlineStr"/>
+      <c r="O67" s="4" t="inlineStr"/>
+      <c r="P67" s="4" t="inlineStr">
+        <is>
+          <t>Low Strike Check | No signal | No signal</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="4" t="inlineStr">
+        <is>
+          <t>2026-03-24 11:00:00</t>
+        </is>
+      </c>
+      <c r="B68" s="4" t="inlineStr">
+        <is>
+          <t>11:00:00</t>
+        </is>
+      </c>
+      <c r="C68" s="4" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
+      <c r="D68" s="4" t="inlineStr">
+        <is>
+          <t>118.95</t>
+        </is>
+      </c>
+      <c r="E68" s="4" t="inlineStr"/>
+      <c r="F68" s="4" t="inlineStr">
+        <is>
+          <t>200.05</t>
+        </is>
+      </c>
+      <c r="G68" s="4" t="inlineStr"/>
+      <c r="H68" s="4" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="I68" s="4" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="J68" s="4" t="inlineStr"/>
+      <c r="K68" s="4" t="inlineStr"/>
+      <c r="L68" s="4" t="inlineStr"/>
+      <c r="M68" s="4" t="inlineStr"/>
+      <c r="N68" s="4" t="inlineStr"/>
+      <c r="O68" s="4" t="inlineStr"/>
+      <c r="P68" s="4" t="inlineStr">
+        <is>
+          <t>High Strike Check | No signal | No signal</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="4" t="inlineStr">
+        <is>
+          <t>2026-03-24 11:00:00</t>
+        </is>
+      </c>
+      <c r="B69" s="4" t="inlineStr">
+        <is>
+          <t>11:00:00</t>
+        </is>
+      </c>
+      <c r="C69" s="4" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
+      <c r="D69" s="4" t="inlineStr">
+        <is>
+          <t>209.00</t>
+        </is>
+      </c>
+      <c r="E69" s="4" t="inlineStr"/>
+      <c r="F69" s="4" t="inlineStr">
+        <is>
+          <t>168.55</t>
+        </is>
+      </c>
+      <c r="G69" s="4" t="inlineStr"/>
+      <c r="H69" s="4" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="I69" s="4" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="J69" s="4" t="inlineStr"/>
+      <c r="K69" s="4" t="inlineStr"/>
+      <c r="L69" s="4" t="inlineStr"/>
+      <c r="M69" s="4" t="inlineStr"/>
+      <c r="N69" s="4" t="inlineStr"/>
+      <c r="O69" s="4" t="inlineStr"/>
+      <c r="P69" s="4" t="inlineStr">
+        <is>
+          <t>Low Strike Check | No signal | No signal</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="4" t="inlineStr">
+        <is>
+          <t>2026-03-24 11:05:00</t>
+        </is>
+      </c>
+      <c r="B70" s="4" t="inlineStr">
+        <is>
+          <t>11:05:00</t>
+        </is>
+      </c>
+      <c r="C70" s="4" t="inlineStr">
+        <is>
+          <t>11:05</t>
+        </is>
+      </c>
+      <c r="D70" s="4" t="inlineStr">
+        <is>
+          <t>118.95</t>
+        </is>
+      </c>
+      <c r="E70" s="4" t="inlineStr"/>
+      <c r="F70" s="4" t="inlineStr">
+        <is>
+          <t>200.05</t>
+        </is>
+      </c>
+      <c r="G70" s="4" t="inlineStr"/>
+      <c r="H70" s="4" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="I70" s="4" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="J70" s="4" t="inlineStr"/>
+      <c r="K70" s="4" t="inlineStr"/>
+      <c r="L70" s="4" t="inlineStr"/>
+      <c r="M70" s="4" t="inlineStr"/>
+      <c r="N70" s="4" t="inlineStr"/>
+      <c r="O70" s="4" t="inlineStr"/>
+      <c r="P70" s="4" t="inlineStr">
+        <is>
+          <t>High Strike Check | No signal | No signal</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="4" t="inlineStr">
+        <is>
+          <t>2026-03-24 11:05:00</t>
+        </is>
+      </c>
+      <c r="B71" s="4" t="inlineStr">
+        <is>
+          <t>11:05:00</t>
+        </is>
+      </c>
+      <c r="C71" s="4" t="inlineStr">
+        <is>
+          <t>11:05</t>
+        </is>
+      </c>
+      <c r="D71" s="4" t="inlineStr">
+        <is>
+          <t>209.00</t>
+        </is>
+      </c>
+      <c r="E71" s="4" t="inlineStr"/>
+      <c r="F71" s="4" t="inlineStr">
+        <is>
+          <t>168.55</t>
+        </is>
+      </c>
+      <c r="G71" s="4" t="inlineStr"/>
+      <c r="H71" s="4" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="I71" s="4" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="J71" s="4" t="inlineStr"/>
+      <c r="K71" s="4" t="inlineStr"/>
+      <c r="L71" s="4" t="inlineStr"/>
+      <c r="M71" s="4" t="inlineStr"/>
+      <c r="N71" s="4" t="inlineStr"/>
+      <c r="O71" s="4" t="inlineStr"/>
+      <c r="P71" s="4" t="inlineStr">
+        <is>
+          <t>Low Strike Check | No signal | No signal</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="4" t="inlineStr">
+        <is>
+          <t>2026-03-24 11:10:00</t>
+        </is>
+      </c>
+      <c r="B72" s="4" t="inlineStr">
+        <is>
+          <t>11:10:00</t>
+        </is>
+      </c>
+      <c r="C72" s="4" t="inlineStr">
+        <is>
+          <t>11:10</t>
+        </is>
+      </c>
+      <c r="D72" s="4" t="inlineStr">
+        <is>
+          <t>118.95</t>
+        </is>
+      </c>
+      <c r="E72" s="4" t="inlineStr"/>
+      <c r="F72" s="4" t="inlineStr">
+        <is>
+          <t>200.05</t>
+        </is>
+      </c>
+      <c r="G72" s="4" t="inlineStr"/>
+      <c r="H72" s="4" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="I72" s="4" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="J72" s="4" t="inlineStr"/>
+      <c r="K72" s="4" t="inlineStr"/>
+      <c r="L72" s="4" t="inlineStr"/>
+      <c r="M72" s="4" t="inlineStr"/>
+      <c r="N72" s="4" t="inlineStr"/>
+      <c r="O72" s="4" t="inlineStr"/>
+      <c r="P72" s="4" t="inlineStr">
+        <is>
+          <t>High Strike Check | No signal | No signal</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="4" t="inlineStr">
+        <is>
+          <t>2026-03-24 11:10:00</t>
+        </is>
+      </c>
+      <c r="B73" s="4" t="inlineStr">
+        <is>
+          <t>11:10:00</t>
+        </is>
+      </c>
+      <c r="C73" s="4" t="inlineStr">
+        <is>
+          <t>11:10</t>
+        </is>
+      </c>
+      <c r="D73" s="4" t="inlineStr">
+        <is>
+          <t>209.00</t>
+        </is>
+      </c>
+      <c r="E73" s="4" t="inlineStr"/>
+      <c r="F73" s="4" t="inlineStr">
+        <is>
+          <t>168.55</t>
+        </is>
+      </c>
+      <c r="G73" s="4" t="inlineStr"/>
+      <c r="H73" s="4" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="I73" s="4" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="J73" s="4" t="inlineStr"/>
+      <c r="K73" s="4" t="inlineStr"/>
+      <c r="L73" s="4" t="inlineStr"/>
+      <c r="M73" s="4" t="inlineStr"/>
+      <c r="N73" s="4" t="inlineStr"/>
+      <c r="O73" s="4" t="inlineStr"/>
+      <c r="P73" s="4" t="inlineStr">
+        <is>
+          <t>Low Strike Check | No signal | No signal</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="4" t="inlineStr">
+        <is>
+          <t>2026-03-24 11:15:00</t>
+        </is>
+      </c>
+      <c r="B74" s="4" t="inlineStr">
+        <is>
+          <t>11:15:00</t>
+        </is>
+      </c>
+      <c r="C74" s="4" t="inlineStr">
+        <is>
+          <t>11:15</t>
+        </is>
+      </c>
+      <c r="D74" s="4" t="inlineStr">
+        <is>
+          <t>118.95</t>
+        </is>
+      </c>
+      <c r="E74" s="4" t="inlineStr"/>
+      <c r="F74" s="4" t="inlineStr">
+        <is>
+          <t>200.05</t>
+        </is>
+      </c>
+      <c r="G74" s="4" t="inlineStr"/>
+      <c r="H74" s="4" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="I74" s="4" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="J74" s="4" t="inlineStr"/>
+      <c r="K74" s="4" t="inlineStr"/>
+      <c r="L74" s="4" t="inlineStr"/>
+      <c r="M74" s="4" t="inlineStr"/>
+      <c r="N74" s="4" t="inlineStr"/>
+      <c r="O74" s="4" t="inlineStr"/>
+      <c r="P74" s="4" t="inlineStr">
+        <is>
+          <t>High Strike Check | No signal | No signal</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="4" t="inlineStr">
+        <is>
+          <t>2026-03-24 11:15:00</t>
+        </is>
+      </c>
+      <c r="B75" s="4" t="inlineStr">
+        <is>
+          <t>11:15:00</t>
+        </is>
+      </c>
+      <c r="C75" s="4" t="inlineStr">
+        <is>
+          <t>11:15</t>
+        </is>
+      </c>
+      <c r="D75" s="4" t="inlineStr">
+        <is>
+          <t>209.00</t>
+        </is>
+      </c>
+      <c r="E75" s="4" t="inlineStr"/>
+      <c r="F75" s="4" t="inlineStr">
+        <is>
+          <t>168.55</t>
+        </is>
+      </c>
+      <c r="G75" s="4" t="inlineStr"/>
+      <c r="H75" s="4" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="I75" s="4" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="J75" s="4" t="inlineStr"/>
+      <c r="K75" s="4" t="inlineStr"/>
+      <c r="L75" s="4" t="inlineStr"/>
+      <c r="M75" s="4" t="inlineStr"/>
+      <c r="N75" s="4" t="inlineStr"/>
+      <c r="O75" s="4" t="inlineStr"/>
+      <c r="P75" s="4" t="inlineStr">
+        <is>
+          <t>Low Strike Check | No signal | No signal</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="4" t="inlineStr">
+        <is>
+          <t>2026-03-24 11:20:00</t>
+        </is>
+      </c>
+      <c r="B76" s="4" t="inlineStr">
+        <is>
+          <t>11:20:00</t>
+        </is>
+      </c>
+      <c r="C76" s="4" t="inlineStr">
+        <is>
+          <t>11:20</t>
+        </is>
+      </c>
+      <c r="D76" s="4" t="inlineStr">
+        <is>
+          <t>118.95</t>
+        </is>
+      </c>
+      <c r="E76" s="4" t="inlineStr"/>
+      <c r="F76" s="4" t="inlineStr">
+        <is>
+          <t>200.05</t>
+        </is>
+      </c>
+      <c r="G76" s="4" t="inlineStr"/>
+      <c r="H76" s="4" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="I76" s="4" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="J76" s="4" t="inlineStr"/>
+      <c r="K76" s="4" t="inlineStr"/>
+      <c r="L76" s="4" t="inlineStr"/>
+      <c r="M76" s="4" t="inlineStr"/>
+      <c r="N76" s="4" t="inlineStr"/>
+      <c r="O76" s="4" t="inlineStr"/>
+      <c r="P76" s="4" t="inlineStr">
+        <is>
+          <t>High Strike Check | No signal | No signal</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="4" t="inlineStr">
+        <is>
+          <t>2026-03-24 11:20:00</t>
+        </is>
+      </c>
+      <c r="B77" s="4" t="inlineStr">
+        <is>
+          <t>11:20:00</t>
+        </is>
+      </c>
+      <c r="C77" s="4" t="inlineStr">
+        <is>
+          <t>11:20</t>
+        </is>
+      </c>
+      <c r="D77" s="4" t="inlineStr">
+        <is>
+          <t>209.00</t>
+        </is>
+      </c>
+      <c r="E77" s="4" t="inlineStr"/>
+      <c r="F77" s="4" t="inlineStr">
+        <is>
+          <t>168.55</t>
+        </is>
+      </c>
+      <c r="G77" s="4" t="inlineStr"/>
+      <c r="H77" s="4" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="I77" s="4" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="J77" s="4" t="inlineStr"/>
+      <c r="K77" s="4" t="inlineStr"/>
+      <c r="L77" s="4" t="inlineStr"/>
+      <c r="M77" s="4" t="inlineStr"/>
+      <c r="N77" s="4" t="inlineStr"/>
+      <c r="O77" s="4" t="inlineStr"/>
+      <c r="P77" s="4" t="inlineStr">
+        <is>
+          <t>Low Strike Check | No signal | No signal</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="4" t="inlineStr">
+        <is>
+          <t>2026-03-24 11:25:00</t>
+        </is>
+      </c>
+      <c r="B78" s="4" t="inlineStr">
+        <is>
+          <t>11:25:00</t>
+        </is>
+      </c>
+      <c r="C78" s="4" t="inlineStr">
+        <is>
+          <t>11:25</t>
+        </is>
+      </c>
+      <c r="D78" s="4" t="inlineStr">
+        <is>
+          <t>118.95</t>
+        </is>
+      </c>
+      <c r="E78" s="4" t="inlineStr"/>
+      <c r="F78" s="4" t="inlineStr">
+        <is>
+          <t>200.05</t>
+        </is>
+      </c>
+      <c r="G78" s="4" t="inlineStr"/>
+      <c r="H78" s="4" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="I78" s="4" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="J78" s="4" t="inlineStr"/>
+      <c r="K78" s="4" t="inlineStr"/>
+      <c r="L78" s="4" t="inlineStr"/>
+      <c r="M78" s="4" t="inlineStr"/>
+      <c r="N78" s="4" t="inlineStr"/>
+      <c r="O78" s="4" t="inlineStr"/>
+      <c r="P78" s="4" t="inlineStr">
+        <is>
+          <t>High Strike Check | No signal | No signal</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="4" t="inlineStr">
+        <is>
+          <t>2026-03-24 11:25:00</t>
+        </is>
+      </c>
+      <c r="B79" s="4" t="inlineStr">
+        <is>
+          <t>11:25:00</t>
+        </is>
+      </c>
+      <c r="C79" s="4" t="inlineStr">
+        <is>
+          <t>11:25</t>
+        </is>
+      </c>
+      <c r="D79" s="4" t="inlineStr">
+        <is>
+          <t>209.00</t>
+        </is>
+      </c>
+      <c r="E79" s="4" t="inlineStr"/>
+      <c r="F79" s="4" t="inlineStr">
+        <is>
+          <t>168.55</t>
+        </is>
+      </c>
+      <c r="G79" s="4" t="inlineStr"/>
+      <c r="H79" s="4" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="I79" s="4" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="J79" s="4" t="inlineStr"/>
+      <c r="K79" s="4" t="inlineStr"/>
+      <c r="L79" s="4" t="inlineStr"/>
+      <c r="M79" s="4" t="inlineStr"/>
+      <c r="N79" s="4" t="inlineStr"/>
+      <c r="O79" s="4" t="inlineStr"/>
+      <c r="P79" s="4" t="inlineStr">
+        <is>
+          <t>Low Strike Check | No signal | No signal</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="4" t="inlineStr">
+        <is>
+          <t>2026-03-24 11:30:00</t>
+        </is>
+      </c>
+      <c r="B80" s="4" t="inlineStr">
+        <is>
+          <t>11:30:00</t>
+        </is>
+      </c>
+      <c r="C80" s="4" t="inlineStr">
+        <is>
+          <t>11:30</t>
+        </is>
+      </c>
+      <c r="D80" s="4" t="inlineStr">
+        <is>
+          <t>118.95</t>
+        </is>
+      </c>
+      <c r="E80" s="4" t="inlineStr"/>
+      <c r="F80" s="4" t="inlineStr">
+        <is>
+          <t>200.05</t>
+        </is>
+      </c>
+      <c r="G80" s="4" t="inlineStr"/>
+      <c r="H80" s="4" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="I80" s="4" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="J80" s="4" t="inlineStr"/>
+      <c r="K80" s="4" t="inlineStr"/>
+      <c r="L80" s="4" t="inlineStr"/>
+      <c r="M80" s="4" t="inlineStr"/>
+      <c r="N80" s="4" t="inlineStr"/>
+      <c r="O80" s="4" t="inlineStr"/>
+      <c r="P80" s="4" t="inlineStr">
+        <is>
+          <t>High Strike Check | No signal | No signal</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="4" t="inlineStr">
+        <is>
+          <t>2026-03-24 11:30:00</t>
+        </is>
+      </c>
+      <c r="B81" s="4" t="inlineStr">
+        <is>
+          <t>11:30:00</t>
+        </is>
+      </c>
+      <c r="C81" s="4" t="inlineStr">
+        <is>
+          <t>11:30</t>
+        </is>
+      </c>
+      <c r="D81" s="4" t="inlineStr">
+        <is>
+          <t>209.00</t>
+        </is>
+      </c>
+      <c r="E81" s="4" t="inlineStr"/>
+      <c r="F81" s="4" t="inlineStr">
+        <is>
+          <t>168.55</t>
+        </is>
+      </c>
+      <c r="G81" s="4" t="inlineStr"/>
+      <c r="H81" s="4" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="I81" s="4" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="J81" s="4" t="inlineStr"/>
+      <c r="K81" s="4" t="inlineStr"/>
+      <c r="L81" s="4" t="inlineStr"/>
+      <c r="M81" s="4" t="inlineStr"/>
+      <c r="N81" s="4" t="inlineStr"/>
+      <c r="O81" s="4" t="inlineStr"/>
+      <c r="P81" s="4" t="inlineStr">
+        <is>
+          <t>Low Strike Check | No signal | No signal</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="4" t="inlineStr">
+        <is>
+          <t>2026-03-24 11:35:00</t>
+        </is>
+      </c>
+      <c r="B82" s="4" t="inlineStr">
+        <is>
+          <t>11:35:00</t>
+        </is>
+      </c>
+      <c r="C82" s="4" t="inlineStr">
+        <is>
+          <t>11:35</t>
+        </is>
+      </c>
+      <c r="D82" s="4" t="inlineStr">
+        <is>
+          <t>118.95</t>
+        </is>
+      </c>
+      <c r="E82" s="4" t="inlineStr"/>
+      <c r="F82" s="4" t="inlineStr">
+        <is>
+          <t>200.05</t>
+        </is>
+      </c>
+      <c r="G82" s="4" t="inlineStr"/>
+      <c r="H82" s="4" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="I82" s="4" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="J82" s="4" t="inlineStr"/>
+      <c r="K82" s="4" t="inlineStr"/>
+      <c r="L82" s="4" t="inlineStr"/>
+      <c r="M82" s="4" t="inlineStr"/>
+      <c r="N82" s="4" t="inlineStr"/>
+      <c r="O82" s="4" t="inlineStr"/>
+      <c r="P82" s="4" t="inlineStr">
+        <is>
+          <t>High Strike Check | No signal | No signal</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="4" t="inlineStr">
+        <is>
+          <t>2026-03-24 11:35:00</t>
+        </is>
+      </c>
+      <c r="B83" s="4" t="inlineStr">
+        <is>
+          <t>11:35:00</t>
+        </is>
+      </c>
+      <c r="C83" s="4" t="inlineStr">
+        <is>
+          <t>11:35</t>
+        </is>
+      </c>
+      <c r="D83" s="4" t="inlineStr">
+        <is>
+          <t>209.00</t>
+        </is>
+      </c>
+      <c r="E83" s="4" t="inlineStr"/>
+      <c r="F83" s="4" t="inlineStr">
+        <is>
+          <t>168.55</t>
+        </is>
+      </c>
+      <c r="G83" s="4" t="inlineStr"/>
+      <c r="H83" s="4" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="I83" s="4" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="J83" s="4" t="inlineStr"/>
+      <c r="K83" s="4" t="inlineStr"/>
+      <c r="L83" s="4" t="inlineStr"/>
+      <c r="M83" s="4" t="inlineStr"/>
+      <c r="N83" s="4" t="inlineStr"/>
+      <c r="O83" s="4" t="inlineStr"/>
+      <c r="P83" s="4" t="inlineStr">
+        <is>
+          <t>Low Strike Check | No signal | No signal</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="4" t="inlineStr">
+        <is>
+          <t>2026-03-24 11:40:00</t>
+        </is>
+      </c>
+      <c r="B84" s="4" t="inlineStr">
+        <is>
+          <t>11:40:00</t>
+        </is>
+      </c>
+      <c r="C84" s="4" t="inlineStr">
+        <is>
+          <t>11:40</t>
+        </is>
+      </c>
+      <c r="D84" s="4" t="inlineStr">
+        <is>
+          <t>118.95</t>
+        </is>
+      </c>
+      <c r="E84" s="4" t="inlineStr"/>
+      <c r="F84" s="4" t="inlineStr">
+        <is>
+          <t>200.05</t>
+        </is>
+      </c>
+      <c r="G84" s="4" t="inlineStr"/>
+      <c r="H84" s="4" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="I84" s="4" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="J84" s="4" t="inlineStr"/>
+      <c r="K84" s="4" t="inlineStr"/>
+      <c r="L84" s="4" t="inlineStr"/>
+      <c r="M84" s="4" t="inlineStr"/>
+      <c r="N84" s="4" t="inlineStr"/>
+      <c r="O84" s="4" t="inlineStr"/>
+      <c r="P84" s="4" t="inlineStr">
+        <is>
+          <t>High Strike Check | No signal | No signal</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="4" t="inlineStr">
+        <is>
+          <t>2026-03-24 11:40:00</t>
+        </is>
+      </c>
+      <c r="B85" s="4" t="inlineStr">
+        <is>
+          <t>11:40:00</t>
+        </is>
+      </c>
+      <c r="C85" s="4" t="inlineStr">
+        <is>
+          <t>11:40</t>
+        </is>
+      </c>
+      <c r="D85" s="4" t="inlineStr">
+        <is>
+          <t>209.00</t>
+        </is>
+      </c>
+      <c r="E85" s="4" t="inlineStr"/>
+      <c r="F85" s="4" t="inlineStr">
+        <is>
+          <t>168.55</t>
+        </is>
+      </c>
+      <c r="G85" s="4" t="inlineStr"/>
+      <c r="H85" s="4" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="I85" s="4" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="J85" s="4" t="inlineStr"/>
+      <c r="K85" s="4" t="inlineStr"/>
+      <c r="L85" s="4" t="inlineStr"/>
+      <c r="M85" s="4" t="inlineStr"/>
+      <c r="N85" s="4" t="inlineStr"/>
+      <c r="O85" s="4" t="inlineStr"/>
+      <c r="P85" s="4" t="inlineStr">
+        <is>
+          <t>Low Strike Check | No signal | No signal</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="4" t="inlineStr">
+        <is>
+          <t>2026-03-24 11:45:00</t>
+        </is>
+      </c>
+      <c r="B86" s="4" t="inlineStr">
+        <is>
+          <t>11:45:00</t>
+        </is>
+      </c>
+      <c r="C86" s="4" t="inlineStr">
+        <is>
+          <t>11:45</t>
+        </is>
+      </c>
+      <c r="D86" s="4" t="inlineStr">
+        <is>
+          <t>118.95</t>
+        </is>
+      </c>
+      <c r="E86" s="4" t="inlineStr"/>
+      <c r="F86" s="4" t="inlineStr">
+        <is>
+          <t>200.05</t>
+        </is>
+      </c>
+      <c r="G86" s="4" t="inlineStr"/>
+      <c r="H86" s="4" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="I86" s="4" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="J86" s="4" t="inlineStr"/>
+      <c r="K86" s="4" t="inlineStr"/>
+      <c r="L86" s="4" t="inlineStr"/>
+      <c r="M86" s="4" t="inlineStr"/>
+      <c r="N86" s="4" t="inlineStr"/>
+      <c r="O86" s="4" t="inlineStr"/>
+      <c r="P86" s="4" t="inlineStr">
+        <is>
+          <t>High Strike Check | No signal | No signal</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="4" t="inlineStr">
+        <is>
+          <t>2026-03-24 11:45:00</t>
+        </is>
+      </c>
+      <c r="B87" s="4" t="inlineStr">
+        <is>
+          <t>11:45:00</t>
+        </is>
+      </c>
+      <c r="C87" s="4" t="inlineStr">
+        <is>
+          <t>11:45</t>
+        </is>
+      </c>
+      <c r="D87" s="4" t="inlineStr">
+        <is>
+          <t>209.00</t>
+        </is>
+      </c>
+      <c r="E87" s="4" t="inlineStr"/>
+      <c r="F87" s="4" t="inlineStr">
+        <is>
+          <t>168.55</t>
+        </is>
+      </c>
+      <c r="G87" s="4" t="inlineStr"/>
+      <c r="H87" s="4" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="I87" s="4" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="J87" s="4" t="inlineStr"/>
+      <c r="K87" s="4" t="inlineStr"/>
+      <c r="L87" s="4" t="inlineStr"/>
+      <c r="M87" s="4" t="inlineStr"/>
+      <c r="N87" s="4" t="inlineStr"/>
+      <c r="O87" s="4" t="inlineStr"/>
+      <c r="P87" s="4" t="inlineStr">
+        <is>
+          <t>Low Strike Check | No signal | No signal</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="4" t="inlineStr">
+        <is>
+          <t>2026-03-24 11:50:00</t>
+        </is>
+      </c>
+      <c r="B88" s="4" t="inlineStr">
+        <is>
+          <t>11:50:00</t>
+        </is>
+      </c>
+      <c r="C88" s="4" t="inlineStr">
+        <is>
+          <t>11:50</t>
+        </is>
+      </c>
+      <c r="D88" s="4" t="inlineStr">
+        <is>
+          <t>118.95</t>
+        </is>
+      </c>
+      <c r="E88" s="4" t="inlineStr"/>
+      <c r="F88" s="4" t="inlineStr">
+        <is>
+          <t>200.05</t>
+        </is>
+      </c>
+      <c r="G88" s="4" t="inlineStr"/>
+      <c r="H88" s="4" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="I88" s="4" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="J88" s="4" t="inlineStr"/>
+      <c r="K88" s="4" t="inlineStr"/>
+      <c r="L88" s="4" t="inlineStr"/>
+      <c r="M88" s="4" t="inlineStr"/>
+      <c r="N88" s="4" t="inlineStr"/>
+      <c r="O88" s="4" t="inlineStr"/>
+      <c r="P88" s="4" t="inlineStr">
+        <is>
+          <t>High Strike Check | No signal | No signal</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="4" t="inlineStr">
+        <is>
+          <t>2026-03-24 11:50:00</t>
+        </is>
+      </c>
+      <c r="B89" s="4" t="inlineStr">
+        <is>
+          <t>11:50:00</t>
+        </is>
+      </c>
+      <c r="C89" s="4" t="inlineStr">
+        <is>
+          <t>11:50</t>
+        </is>
+      </c>
+      <c r="D89" s="4" t="inlineStr">
+        <is>
+          <t>209.00</t>
+        </is>
+      </c>
+      <c r="E89" s="4" t="inlineStr"/>
+      <c r="F89" s="4" t="inlineStr">
+        <is>
+          <t>168.55</t>
+        </is>
+      </c>
+      <c r="G89" s="4" t="inlineStr"/>
+      <c r="H89" s="4" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="I89" s="4" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="J89" s="4" t="inlineStr"/>
+      <c r="K89" s="4" t="inlineStr"/>
+      <c r="L89" s="4" t="inlineStr"/>
+      <c r="M89" s="4" t="inlineStr"/>
+      <c r="N89" s="4" t="inlineStr"/>
+      <c r="O89" s="4" t="inlineStr"/>
+      <c r="P89" s="4" t="inlineStr">
+        <is>
+          <t>Low Strike Check | No signal | No signal</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="4" t="inlineStr">
+        <is>
+          <t>2026-03-24 11:55:00</t>
+        </is>
+      </c>
+      <c r="B90" s="4" t="inlineStr">
+        <is>
+          <t>11:55:00</t>
+        </is>
+      </c>
+      <c r="C90" s="4" t="inlineStr">
+        <is>
+          <t>11:55</t>
+        </is>
+      </c>
+      <c r="D90" s="4" t="inlineStr">
+        <is>
+          <t>118.95</t>
+        </is>
+      </c>
+      <c r="E90" s="4" t="inlineStr"/>
+      <c r="F90" s="4" t="inlineStr">
+        <is>
+          <t>200.05</t>
+        </is>
+      </c>
+      <c r="G90" s="4" t="inlineStr"/>
+      <c r="H90" s="4" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="I90" s="4" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="J90" s="4" t="inlineStr"/>
+      <c r="K90" s="4" t="inlineStr"/>
+      <c r="L90" s="4" t="inlineStr"/>
+      <c r="M90" s="4" t="inlineStr"/>
+      <c r="N90" s="4" t="inlineStr"/>
+      <c r="O90" s="4" t="inlineStr"/>
+      <c r="P90" s="4" t="inlineStr">
+        <is>
+          <t>High Strike Check | No signal | No signal</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="4" t="inlineStr">
+        <is>
+          <t>2026-03-24 11:55:00</t>
+        </is>
+      </c>
+      <c r="B91" s="4" t="inlineStr">
+        <is>
+          <t>11:55:00</t>
+        </is>
+      </c>
+      <c r="C91" s="4" t="inlineStr">
+        <is>
+          <t>11:55</t>
+        </is>
+      </c>
+      <c r="D91" s="4" t="inlineStr">
+        <is>
+          <t>209.00</t>
+        </is>
+      </c>
+      <c r="E91" s="4" t="inlineStr"/>
+      <c r="F91" s="4" t="inlineStr">
+        <is>
+          <t>168.55</t>
+        </is>
+      </c>
+      <c r="G91" s="4" t="inlineStr"/>
+      <c r="H91" s="4" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="I91" s="4" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="J91" s="4" t="inlineStr"/>
+      <c r="K91" s="4" t="inlineStr"/>
+      <c r="L91" s="4" t="inlineStr"/>
+      <c r="M91" s="4" t="inlineStr"/>
+      <c r="N91" s="4" t="inlineStr"/>
+      <c r="O91" s="4" t="inlineStr"/>
+      <c r="P91" s="4" t="inlineStr">
+        <is>
+          <t>Low Strike Check | No signal | No signal</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="4" t="inlineStr">
+        <is>
+          <t>2026-03-24 12:00:00</t>
+        </is>
+      </c>
+      <c r="B92" s="4" t="inlineStr">
+        <is>
+          <t>12:00:00</t>
+        </is>
+      </c>
+      <c r="C92" s="4" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
+      <c r="D92" s="4" t="inlineStr">
+        <is>
+          <t>118.95</t>
+        </is>
+      </c>
+      <c r="E92" s="4" t="inlineStr"/>
+      <c r="F92" s="4" t="inlineStr">
+        <is>
+          <t>200.05</t>
+        </is>
+      </c>
+      <c r="G92" s="4" t="inlineStr"/>
+      <c r="H92" s="4" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="I92" s="7" t="inlineStr">
+        <is>
+          <t>✓ YES</t>
+        </is>
+      </c>
+      <c r="J92" s="4" t="inlineStr"/>
+      <c r="K92" s="4" t="inlineStr">
+        <is>
+          <t>129.70</t>
+        </is>
+      </c>
+      <c r="L92" s="4" t="inlineStr"/>
+      <c r="M92" s="4" t="inlineStr">
+        <is>
+          <t>108.95</t>
+        </is>
+      </c>
+      <c r="N92" s="4" t="inlineStr"/>
+      <c r="O92" s="4" t="inlineStr">
+        <is>
+          <t>171.20</t>
+        </is>
+      </c>
+      <c r="P92" s="4" t="inlineStr">
+        <is>
+          <t>High Strike Check | No signal | Low 114.00 &lt; CE High 118.95, Close 129.70 &gt; CE High + 5</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="4" t="inlineStr">
+        <is>
+          <t>2026-03-24 12:00:00</t>
+        </is>
+      </c>
+      <c r="B93" s="4" t="inlineStr">
+        <is>
+          <t>12:00:00</t>
+        </is>
+      </c>
+      <c r="C93" s="4" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
+      <c r="D93" s="4" t="inlineStr">
+        <is>
+          <t>209.00</t>
+        </is>
+      </c>
+      <c r="E93" s="4" t="inlineStr"/>
+      <c r="F93" s="4" t="inlineStr">
+        <is>
+          <t>168.55</t>
+        </is>
+      </c>
+      <c r="G93" s="4" t="inlineStr"/>
+      <c r="H93" s="4" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="I93" s="4" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="J93" s="4" t="inlineStr"/>
+      <c r="K93" s="4" t="inlineStr"/>
+      <c r="L93" s="4" t="inlineStr"/>
+      <c r="M93" s="4" t="inlineStr"/>
+      <c r="N93" s="4" t="inlineStr"/>
+      <c r="O93" s="4" t="inlineStr"/>
+      <c r="P93" s="4" t="inlineStr">
+        <is>
+          <t>Low Strike skipped (High strike matched)</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="4" t="inlineStr">
+        <is>
+          <t>2026-03-24 12:05:00</t>
+        </is>
+      </c>
+      <c r="B94" s="4" t="inlineStr">
+        <is>
+          <t>12:05:00</t>
+        </is>
+      </c>
+      <c r="C94" s="4" t="inlineStr">
+        <is>
+          <t>12:05</t>
+        </is>
+      </c>
+      <c r="D94" s="4" t="inlineStr">
+        <is>
+          <t>118.95</t>
+        </is>
+      </c>
+      <c r="E94" s="4" t="inlineStr"/>
+      <c r="F94" s="4" t="inlineStr">
+        <is>
+          <t>200.05</t>
+        </is>
+      </c>
+      <c r="G94" s="4" t="inlineStr"/>
+      <c r="H94" s="4" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="I94" s="4" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="J94" s="4" t="inlineStr"/>
+      <c r="K94" s="4" t="inlineStr"/>
+      <c r="L94" s="4" t="inlineStr"/>
+      <c r="M94" s="4" t="inlineStr"/>
+      <c r="N94" s="4" t="inlineStr"/>
+      <c r="O94" s="4" t="inlineStr"/>
+      <c r="P94" s="4" t="inlineStr">
+        <is>
+          <t>High Strike Check | No signal | No signal</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="4" t="inlineStr">
+        <is>
+          <t>2026-03-24 12:05:00</t>
+        </is>
+      </c>
+      <c r="B95" s="4" t="inlineStr">
+        <is>
+          <t>12:05:00</t>
+        </is>
+      </c>
+      <c r="C95" s="4" t="inlineStr">
+        <is>
+          <t>12:05</t>
+        </is>
+      </c>
+      <c r="D95" s="4" t="inlineStr">
+        <is>
+          <t>209.00</t>
+        </is>
+      </c>
+      <c r="E95" s="4" t="inlineStr"/>
+      <c r="F95" s="4" t="inlineStr">
+        <is>
+          <t>168.55</t>
+        </is>
+      </c>
+      <c r="G95" s="4" t="inlineStr"/>
+      <c r="H95" s="4" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="I95" s="4" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="J95" s="4" t="inlineStr"/>
+      <c r="K95" s="4" t="inlineStr"/>
+      <c r="L95" s="4" t="inlineStr"/>
+      <c r="M95" s="4" t="inlineStr"/>
+      <c r="N95" s="4" t="inlineStr"/>
+      <c r="O95" s="4" t="inlineStr"/>
+      <c r="P95" s="4" t="inlineStr">
+        <is>
+          <t>Low Strike Check | No signal | No signal</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="4" t="inlineStr">
+        <is>
+          <t>2026-03-24 12:10:00</t>
+        </is>
+      </c>
+      <c r="B96" s="4" t="inlineStr">
+        <is>
+          <t>12:10:00</t>
+        </is>
+      </c>
+      <c r="C96" s="4" t="inlineStr">
+        <is>
+          <t>12:10</t>
+        </is>
+      </c>
+      <c r="D96" s="4" t="inlineStr">
+        <is>
+          <t>118.95</t>
+        </is>
+      </c>
+      <c r="E96" s="4" t="inlineStr"/>
+      <c r="F96" s="4" t="inlineStr">
+        <is>
+          <t>200.05</t>
+        </is>
+      </c>
+      <c r="G96" s="4" t="inlineStr"/>
+      <c r="H96" s="4" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="I96" s="4" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="J96" s="4" t="inlineStr"/>
+      <c r="K96" s="4" t="inlineStr"/>
+      <c r="L96" s="4" t="inlineStr"/>
+      <c r="M96" s="4" t="inlineStr"/>
+      <c r="N96" s="4" t="inlineStr"/>
+      <c r="O96" s="4" t="inlineStr"/>
+      <c r="P96" s="4" t="inlineStr">
+        <is>
+          <t>High Strike Check | No signal | No signal</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="4" t="inlineStr">
+        <is>
+          <t>2026-03-24 12:10:00</t>
+        </is>
+      </c>
+      <c r="B97" s="4" t="inlineStr">
+        <is>
+          <t>12:10:00</t>
+        </is>
+      </c>
+      <c r="C97" s="4" t="inlineStr">
+        <is>
+          <t>12:10</t>
+        </is>
+      </c>
+      <c r="D97" s="4" t="inlineStr">
+        <is>
+          <t>209.00</t>
+        </is>
+      </c>
+      <c r="E97" s="4" t="inlineStr"/>
+      <c r="F97" s="4" t="inlineStr">
+        <is>
+          <t>168.55</t>
+        </is>
+      </c>
+      <c r="G97" s="4" t="inlineStr"/>
+      <c r="H97" s="4" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="I97" s="4" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="J97" s="4" t="inlineStr"/>
+      <c r="K97" s="4" t="inlineStr"/>
+      <c r="L97" s="4" t="inlineStr"/>
+      <c r="M97" s="4" t="inlineStr"/>
+      <c r="N97" s="4" t="inlineStr"/>
+      <c r="O97" s="4" t="inlineStr"/>
+      <c r="P97" s="4" t="inlineStr">
+        <is>
+          <t>Low Strike Check | No signal | No signal</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="4" t="inlineStr">
+        <is>
+          <t>2026-03-24 12:15:00</t>
+        </is>
+      </c>
+      <c r="B98" s="4" t="inlineStr">
+        <is>
+          <t>12:15:00</t>
+        </is>
+      </c>
+      <c r="C98" s="4" t="inlineStr">
+        <is>
+          <t>12:15</t>
+        </is>
+      </c>
+      <c r="D98" s="4" t="inlineStr">
+        <is>
+          <t>118.95</t>
+        </is>
+      </c>
+      <c r="E98" s="4" t="inlineStr"/>
+      <c r="F98" s="4" t="inlineStr">
+        <is>
+          <t>200.05</t>
+        </is>
+      </c>
+      <c r="G98" s="4" t="inlineStr"/>
+      <c r="H98" s="4" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="I98" s="4" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="J98" s="4" t="inlineStr"/>
+      <c r="K98" s="4" t="inlineStr"/>
+      <c r="L98" s="4" t="inlineStr"/>
+      <c r="M98" s="4" t="inlineStr"/>
+      <c r="N98" s="4" t="inlineStr"/>
+      <c r="O98" s="4" t="inlineStr"/>
+      <c r="P98" s="4" t="inlineStr">
+        <is>
+          <t>High Strike Check | No signal | No signal</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="4" t="inlineStr">
+        <is>
+          <t>2026-03-24 12:15:00</t>
+        </is>
+      </c>
+      <c r="B99" s="4" t="inlineStr">
+        <is>
+          <t>12:15:00</t>
+        </is>
+      </c>
+      <c r="C99" s="4" t="inlineStr">
+        <is>
+          <t>12:15</t>
+        </is>
+      </c>
+      <c r="D99" s="4" t="inlineStr">
+        <is>
+          <t>209.00</t>
+        </is>
+      </c>
+      <c r="E99" s="4" t="inlineStr"/>
+      <c r="F99" s="4" t="inlineStr">
+        <is>
+          <t>168.55</t>
+        </is>
+      </c>
+      <c r="G99" s="4" t="inlineStr"/>
+      <c r="H99" s="4" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="I99" s="4" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="J99" s="4" t="inlineStr"/>
+      <c r="K99" s="4" t="inlineStr"/>
+      <c r="L99" s="4" t="inlineStr"/>
+      <c r="M99" s="4" t="inlineStr"/>
+      <c r="N99" s="4" t="inlineStr"/>
+      <c r="O99" s="4" t="inlineStr"/>
+      <c r="P99" s="4" t="inlineStr">
+        <is>
+          <t>Low Strike Check | No signal | No signal</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="4" t="inlineStr">
+        <is>
+          <t>2026-03-24 12:20:00</t>
+        </is>
+      </c>
+      <c r="B100" s="4" t="inlineStr">
+        <is>
+          <t>12:20:00</t>
+        </is>
+      </c>
+      <c r="C100" s="4" t="inlineStr">
+        <is>
+          <t>12:20</t>
+        </is>
+      </c>
+      <c r="D100" s="4" t="inlineStr">
+        <is>
+          <t>118.95</t>
+        </is>
+      </c>
+      <c r="E100" s="4" t="inlineStr"/>
+      <c r="F100" s="4" t="inlineStr">
+        <is>
+          <t>200.05</t>
+        </is>
+      </c>
+      <c r="G100" s="4" t="inlineStr"/>
+      <c r="H100" s="4" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="I100" s="4" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="J100" s="4" t="inlineStr"/>
+      <c r="K100" s="4" t="inlineStr"/>
+      <c r="L100" s="4" t="inlineStr"/>
+      <c r="M100" s="4" t="inlineStr"/>
+      <c r="N100" s="4" t="inlineStr"/>
+      <c r="O100" s="4" t="inlineStr"/>
+      <c r="P100" s="4" t="inlineStr">
+        <is>
+          <t>High Strike Check | No signal | No signal</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="4" t="inlineStr">
+        <is>
+          <t>2026-03-24 12:20:00</t>
+        </is>
+      </c>
+      <c r="B101" s="4" t="inlineStr">
+        <is>
+          <t>12:20:00</t>
+        </is>
+      </c>
+      <c r="C101" s="4" t="inlineStr">
+        <is>
+          <t>12:20</t>
+        </is>
+      </c>
+      <c r="D101" s="4" t="inlineStr">
+        <is>
+          <t>209.00</t>
+        </is>
+      </c>
+      <c r="E101" s="4" t="inlineStr"/>
+      <c r="F101" s="4" t="inlineStr">
+        <is>
+          <t>168.55</t>
+        </is>
+      </c>
+      <c r="G101" s="4" t="inlineStr"/>
+      <c r="H101" s="4" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="I101" s="4" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="J101" s="4" t="inlineStr"/>
+      <c r="K101" s="4" t="inlineStr"/>
+      <c r="L101" s="4" t="inlineStr"/>
+      <c r="M101" s="4" t="inlineStr"/>
+      <c r="N101" s="4" t="inlineStr"/>
+      <c r="O101" s="4" t="inlineStr"/>
+      <c r="P101" s="4" t="inlineStr">
+        <is>
+          <t>Low Strike Check | No signal | No signal</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="4" t="inlineStr">
+        <is>
+          <t>2026-03-24 12:25:00</t>
+        </is>
+      </c>
+      <c r="B102" s="4" t="inlineStr">
+        <is>
+          <t>12:25:00</t>
+        </is>
+      </c>
+      <c r="C102" s="4" t="inlineStr">
+        <is>
+          <t>12:25</t>
+        </is>
+      </c>
+      <c r="D102" s="4" t="inlineStr">
+        <is>
+          <t>118.95</t>
+        </is>
+      </c>
+      <c r="E102" s="4" t="inlineStr"/>
+      <c r="F102" s="4" t="inlineStr">
+        <is>
+          <t>200.05</t>
+        </is>
+      </c>
+      <c r="G102" s="4" t="inlineStr"/>
+      <c r="H102" s="4" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="I102" s="4" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="J102" s="4" t="inlineStr"/>
+      <c r="K102" s="4" t="inlineStr"/>
+      <c r="L102" s="4" t="inlineStr"/>
+      <c r="M102" s="4" t="inlineStr"/>
+      <c r="N102" s="4" t="inlineStr"/>
+      <c r="O102" s="4" t="inlineStr"/>
+      <c r="P102" s="4" t="inlineStr">
+        <is>
+          <t>High Strike Check | No signal | No signal</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="4" t="inlineStr">
+        <is>
+          <t>2026-03-24 12:25:00</t>
+        </is>
+      </c>
+      <c r="B103" s="4" t="inlineStr">
+        <is>
+          <t>12:25:00</t>
+        </is>
+      </c>
+      <c r="C103" s="4" t="inlineStr">
+        <is>
+          <t>12:25</t>
+        </is>
+      </c>
+      <c r="D103" s="4" t="inlineStr">
+        <is>
+          <t>209.00</t>
+        </is>
+      </c>
+      <c r="E103" s="4" t="inlineStr"/>
+      <c r="F103" s="4" t="inlineStr">
+        <is>
+          <t>168.55</t>
+        </is>
+      </c>
+      <c r="G103" s="4" t="inlineStr"/>
+      <c r="H103" s="4" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="I103" s="4" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="J103" s="4" t="inlineStr"/>
+      <c r="K103" s="4" t="inlineStr"/>
+      <c r="L103" s="4" t="inlineStr"/>
+      <c r="M103" s="4" t="inlineStr"/>
+      <c r="N103" s="4" t="inlineStr"/>
+      <c r="O103" s="4" t="inlineStr"/>
+      <c r="P103" s="4" t="inlineStr">
+        <is>
+          <t>Low Strike Check | No signal | No signal</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="4" t="inlineStr">
+        <is>
+          <t>2026-03-24 12:30:00</t>
+        </is>
+      </c>
+      <c r="B104" s="4" t="inlineStr">
+        <is>
+          <t>12:30:00</t>
+        </is>
+      </c>
+      <c r="C104" s="4" t="inlineStr">
+        <is>
+          <t>12:30</t>
+        </is>
+      </c>
+      <c r="D104" s="4" t="inlineStr">
+        <is>
+          <t>118.95</t>
+        </is>
+      </c>
+      <c r="E104" s="4" t="inlineStr"/>
+      <c r="F104" s="4" t="inlineStr">
+        <is>
+          <t>200.05</t>
+        </is>
+      </c>
+      <c r="G104" s="4" t="inlineStr"/>
+      <c r="H104" s="4" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="I104" s="4" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="J104" s="4" t="inlineStr"/>
+      <c r="K104" s="4" t="inlineStr"/>
+      <c r="L104" s="4" t="inlineStr"/>
+      <c r="M104" s="4" t="inlineStr"/>
+      <c r="N104" s="4" t="inlineStr"/>
+      <c r="O104" s="4" t="inlineStr"/>
+      <c r="P104" s="4" t="inlineStr">
+        <is>
+          <t>High Strike Check | No signal | No signal</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="4" t="inlineStr">
+        <is>
+          <t>2026-03-24 12:30:00</t>
+        </is>
+      </c>
+      <c r="B105" s="4" t="inlineStr">
+        <is>
+          <t>12:30:00</t>
+        </is>
+      </c>
+      <c r="C105" s="4" t="inlineStr">
+        <is>
+          <t>12:30</t>
+        </is>
+      </c>
+      <c r="D105" s="4" t="inlineStr">
+        <is>
+          <t>209.00</t>
+        </is>
+      </c>
+      <c r="E105" s="4" t="inlineStr"/>
+      <c r="F105" s="4" t="inlineStr">
+        <is>
+          <t>168.55</t>
+        </is>
+      </c>
+      <c r="G105" s="4" t="inlineStr"/>
+      <c r="H105" s="4" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="I105" s="4" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="J105" s="4" t="inlineStr"/>
+      <c r="K105" s="4" t="inlineStr"/>
+      <c r="L105" s="4" t="inlineStr"/>
+      <c r="M105" s="4" t="inlineStr"/>
+      <c r="N105" s="4" t="inlineStr"/>
+      <c r="O105" s="4" t="inlineStr"/>
+      <c r="P105" s="4" t="inlineStr">
+        <is>
+          <t>Low Strike Check | No signal | No signal</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" s="4" t="inlineStr">
+        <is>
+          <t>2026-03-24 12:35:00</t>
+        </is>
+      </c>
+      <c r="B106" s="4" t="inlineStr">
+        <is>
+          <t>12:35:00</t>
+        </is>
+      </c>
+      <c r="C106" s="4" t="inlineStr">
+        <is>
+          <t>12:35</t>
+        </is>
+      </c>
+      <c r="D106" s="4" t="inlineStr">
+        <is>
+          <t>118.95</t>
+        </is>
+      </c>
+      <c r="E106" s="4" t="inlineStr"/>
+      <c r="F106" s="4" t="inlineStr">
+        <is>
+          <t>200.05</t>
+        </is>
+      </c>
+      <c r="G106" s="4" t="inlineStr"/>
+      <c r="H106" s="4" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="I106" s="4" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="J106" s="4" t="inlineStr"/>
+      <c r="K106" s="4" t="inlineStr"/>
+      <c r="L106" s="4" t="inlineStr"/>
+      <c r="M106" s="4" t="inlineStr"/>
+      <c r="N106" s="4" t="inlineStr"/>
+      <c r="O106" s="4" t="inlineStr"/>
+      <c r="P106" s="4" t="inlineStr">
+        <is>
+          <t>High Strike Check | No signal | No signal</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" s="4" t="inlineStr">
+        <is>
+          <t>2026-03-24 12:35:00</t>
+        </is>
+      </c>
+      <c r="B107" s="4" t="inlineStr">
+        <is>
+          <t>12:35:00</t>
+        </is>
+      </c>
+      <c r="C107" s="4" t="inlineStr">
+        <is>
+          <t>12:35</t>
+        </is>
+      </c>
+      <c r="D107" s="4" t="inlineStr">
+        <is>
+          <t>209.00</t>
+        </is>
+      </c>
+      <c r="E107" s="4" t="inlineStr"/>
+      <c r="F107" s="4" t="inlineStr">
+        <is>
+          <t>168.55</t>
+        </is>
+      </c>
+      <c r="G107" s="4" t="inlineStr"/>
+      <c r="H107" s="4" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="I107" s="4" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="J107" s="4" t="inlineStr"/>
+      <c r="K107" s="4" t="inlineStr"/>
+      <c r="L107" s="4" t="inlineStr"/>
+      <c r="M107" s="4" t="inlineStr"/>
+      <c r="N107" s="4" t="inlineStr"/>
+      <c r="O107" s="4" t="inlineStr"/>
+      <c r="P107" s="4" t="inlineStr">
+        <is>
+          <t>Low Strike Check | No signal | No signal</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" s="4" t="inlineStr">
+        <is>
+          <t>2026-03-24 12:40:00</t>
+        </is>
+      </c>
+      <c r="B108" s="4" t="inlineStr">
+        <is>
+          <t>12:40:00</t>
+        </is>
+      </c>
+      <c r="C108" s="4" t="inlineStr">
+        <is>
+          <t>12:40</t>
+        </is>
+      </c>
+      <c r="D108" s="4" t="inlineStr">
+        <is>
+          <t>118.95</t>
+        </is>
+      </c>
+      <c r="E108" s="4" t="inlineStr"/>
+      <c r="F108" s="4" t="inlineStr">
+        <is>
+          <t>200.05</t>
+        </is>
+      </c>
+      <c r="G108" s="4" t="inlineStr"/>
+      <c r="H108" s="4" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="I108" s="4" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="J108" s="4" t="inlineStr"/>
+      <c r="K108" s="4" t="inlineStr"/>
+      <c r="L108" s="4" t="inlineStr"/>
+      <c r="M108" s="4" t="inlineStr"/>
+      <c r="N108" s="4" t="inlineStr"/>
+      <c r="O108" s="4" t="inlineStr"/>
+      <c r="P108" s="4" t="inlineStr">
+        <is>
+          <t>High Strike Check | No signal | No signal</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" s="4" t="inlineStr">
+        <is>
+          <t>2026-03-24 12:40:00</t>
+        </is>
+      </c>
+      <c r="B109" s="4" t="inlineStr">
+        <is>
+          <t>12:40:00</t>
+        </is>
+      </c>
+      <c r="C109" s="4" t="inlineStr">
+        <is>
+          <t>12:40</t>
+        </is>
+      </c>
+      <c r="D109" s="4" t="inlineStr">
+        <is>
+          <t>209.00</t>
+        </is>
+      </c>
+      <c r="E109" s="4" t="inlineStr"/>
+      <c r="F109" s="4" t="inlineStr">
+        <is>
+          <t>168.55</t>
+        </is>
+      </c>
+      <c r="G109" s="4" t="inlineStr"/>
+      <c r="H109" s="4" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="I109" s="4" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="J109" s="4" t="inlineStr"/>
+      <c r="K109" s="4" t="inlineStr"/>
+      <c r="L109" s="4" t="inlineStr"/>
+      <c r="M109" s="4" t="inlineStr"/>
+      <c r="N109" s="4" t="inlineStr"/>
+      <c r="O109" s="4" t="inlineStr"/>
+      <c r="P109" s="4" t="inlineStr">
+        <is>
+          <t>Low Strike Check | No signal | No signal</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" s="4" t="inlineStr">
+        <is>
+          <t>2026-03-24 13:25:00</t>
+        </is>
+      </c>
+      <c r="B110" s="4" t="inlineStr">
+        <is>
+          <t>13:25:00</t>
+        </is>
+      </c>
+      <c r="C110" s="4" t="inlineStr">
+        <is>
+          <t>13:25</t>
+        </is>
+      </c>
+      <c r="D110" s="4" t="inlineStr">
+        <is>
+          <t>118.95</t>
+        </is>
+      </c>
+      <c r="E110" s="4" t="inlineStr"/>
+      <c r="F110" s="4" t="inlineStr">
+        <is>
+          <t>200.05</t>
+        </is>
+      </c>
+      <c r="G110" s="4" t="inlineStr"/>
+      <c r="H110" s="4" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="I110" s="4" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="J110" s="4" t="inlineStr"/>
+      <c r="K110" s="4" t="inlineStr"/>
+      <c r="L110" s="4" t="inlineStr"/>
+      <c r="M110" s="4" t="inlineStr"/>
+      <c r="N110" s="4" t="inlineStr"/>
+      <c r="O110" s="4" t="inlineStr"/>
+      <c r="P110" s="4" t="inlineStr">
+        <is>
+          <t>High Strike Check | No signal | No signal</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" s="4" t="inlineStr">
+        <is>
+          <t>2026-03-24 13:25:00</t>
+        </is>
+      </c>
+      <c r="B111" s="4" t="inlineStr">
+        <is>
+          <t>13:25:00</t>
+        </is>
+      </c>
+      <c r="C111" s="4" t="inlineStr">
+        <is>
+          <t>13:25</t>
+        </is>
+      </c>
+      <c r="D111" s="4" t="inlineStr">
+        <is>
+          <t>209.00</t>
+        </is>
+      </c>
+      <c r="E111" s="4" t="inlineStr"/>
+      <c r="F111" s="4" t="inlineStr">
+        <is>
+          <t>168.55</t>
+        </is>
+      </c>
+      <c r="G111" s="4" t="inlineStr"/>
+      <c r="H111" s="4" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="I111" s="4" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="J111" s="4" t="inlineStr"/>
+      <c r="K111" s="4" t="inlineStr"/>
+      <c r="L111" s="4" t="inlineStr"/>
+      <c r="M111" s="4" t="inlineStr"/>
+      <c r="N111" s="4" t="inlineStr"/>
+      <c r="O111" s="4" t="inlineStr"/>
+      <c r="P111" s="4" t="inlineStr">
+        <is>
+          <t>Low Strike Check | No signal | No signal</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" s="4" t="inlineStr">
+        <is>
+          <t>2026-03-24 13:30:00</t>
+        </is>
+      </c>
+      <c r="B112" s="4" t="inlineStr">
+        <is>
+          <t>13:30:00</t>
+        </is>
+      </c>
+      <c r="C112" s="4" t="inlineStr">
+        <is>
+          <t>13:30</t>
+        </is>
+      </c>
+      <c r="D112" s="4" t="inlineStr">
+        <is>
+          <t>118.95</t>
+        </is>
+      </c>
+      <c r="E112" s="4" t="inlineStr"/>
+      <c r="F112" s="4" t="inlineStr">
+        <is>
+          <t>200.05</t>
+        </is>
+      </c>
+      <c r="G112" s="4" t="inlineStr"/>
+      <c r="H112" s="4" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="I112" s="4" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="J112" s="4" t="inlineStr"/>
+      <c r="K112" s="4" t="inlineStr"/>
+      <c r="L112" s="4" t="inlineStr"/>
+      <c r="M112" s="4" t="inlineStr"/>
+      <c r="N112" s="4" t="inlineStr"/>
+      <c r="O112" s="4" t="inlineStr"/>
+      <c r="P112" s="4" t="inlineStr">
+        <is>
+          <t>High Strike Check | No signal | No signal</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" s="4" t="inlineStr">
+        <is>
+          <t>2026-03-24 13:30:00</t>
+        </is>
+      </c>
+      <c r="B113" s="4" t="inlineStr">
+        <is>
+          <t>13:30:00</t>
+        </is>
+      </c>
+      <c r="C113" s="4" t="inlineStr">
+        <is>
+          <t>13:30</t>
+        </is>
+      </c>
+      <c r="D113" s="4" t="inlineStr">
+        <is>
+          <t>209.00</t>
+        </is>
+      </c>
+      <c r="E113" s="4" t="inlineStr"/>
+      <c r="F113" s="4" t="inlineStr">
+        <is>
+          <t>168.55</t>
+        </is>
+      </c>
+      <c r="G113" s="4" t="inlineStr"/>
+      <c r="H113" s="4" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="I113" s="4" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="J113" s="4" t="inlineStr"/>
+      <c r="K113" s="4" t="inlineStr"/>
+      <c r="L113" s="4" t="inlineStr"/>
+      <c r="M113" s="4" t="inlineStr"/>
+      <c r="N113" s="4" t="inlineStr"/>
+      <c r="O113" s="4" t="inlineStr"/>
+      <c r="P113" s="4" t="inlineStr">
+        <is>
+          <t>Low Strike Check | No signal | No signal</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" s="4" t="inlineStr">
+        <is>
+          <t>2026-03-24 13:35:00</t>
+        </is>
+      </c>
+      <c r="B114" s="4" t="inlineStr">
+        <is>
+          <t>13:35:00</t>
+        </is>
+      </c>
+      <c r="C114" s="4" t="inlineStr">
+        <is>
+          <t>13:35</t>
+        </is>
+      </c>
+      <c r="D114" s="4" t="inlineStr">
+        <is>
+          <t>118.95</t>
+        </is>
+      </c>
+      <c r="E114" s="4" t="inlineStr"/>
+      <c r="F114" s="4" t="inlineStr">
+        <is>
+          <t>200.05</t>
+        </is>
+      </c>
+      <c r="G114" s="4" t="inlineStr"/>
+      <c r="H114" s="4" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="I114" s="4" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="J114" s="4" t="inlineStr"/>
+      <c r="K114" s="4" t="inlineStr"/>
+      <c r="L114" s="4" t="inlineStr"/>
+      <c r="M114" s="4" t="inlineStr"/>
+      <c r="N114" s="4" t="inlineStr"/>
+      <c r="O114" s="4" t="inlineStr"/>
+      <c r="P114" s="4" t="inlineStr">
+        <is>
+          <t>High Strike Check | No signal | No signal</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" s="4" t="inlineStr">
+        <is>
+          <t>2026-03-24 13:35:00</t>
+        </is>
+      </c>
+      <c r="B115" s="4" t="inlineStr">
+        <is>
+          <t>13:35:00</t>
+        </is>
+      </c>
+      <c r="C115" s="4" t="inlineStr">
+        <is>
+          <t>13:35</t>
+        </is>
+      </c>
+      <c r="D115" s="4" t="inlineStr">
+        <is>
+          <t>209.00</t>
+        </is>
+      </c>
+      <c r="E115" s="4" t="inlineStr"/>
+      <c r="F115" s="4" t="inlineStr">
+        <is>
+          <t>168.55</t>
+        </is>
+      </c>
+      <c r="G115" s="4" t="inlineStr"/>
+      <c r="H115" s="4" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="I115" s="4" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="J115" s="4" t="inlineStr"/>
+      <c r="K115" s="4" t="inlineStr"/>
+      <c r="L115" s="4" t="inlineStr"/>
+      <c r="M115" s="4" t="inlineStr"/>
+      <c r="N115" s="4" t="inlineStr"/>
+      <c r="O115" s="4" t="inlineStr"/>
+      <c r="P115" s="4" t="inlineStr">
+        <is>
+          <t>Low Strike Check | No signal | No signal</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" s="4" t="inlineStr">
+        <is>
+          <t>2026-03-24 13:40:00</t>
+        </is>
+      </c>
+      <c r="B116" s="4" t="inlineStr">
+        <is>
+          <t>13:40:00</t>
+        </is>
+      </c>
+      <c r="C116" s="4" t="inlineStr">
+        <is>
+          <t>13:40</t>
+        </is>
+      </c>
+      <c r="D116" s="4" t="inlineStr">
+        <is>
+          <t>118.95</t>
+        </is>
+      </c>
+      <c r="E116" s="4" t="inlineStr"/>
+      <c r="F116" s="4" t="inlineStr">
+        <is>
+          <t>200.05</t>
+        </is>
+      </c>
+      <c r="G116" s="4" t="inlineStr"/>
+      <c r="H116" s="4" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="I116" s="4" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="J116" s="4" t="inlineStr"/>
+      <c r="K116" s="4" t="inlineStr"/>
+      <c r="L116" s="4" t="inlineStr"/>
+      <c r="M116" s="4" t="inlineStr"/>
+      <c r="N116" s="4" t="inlineStr"/>
+      <c r="O116" s="4" t="inlineStr"/>
+      <c r="P116" s="4" t="inlineStr">
+        <is>
+          <t>High Strike Check | No signal | No signal</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="4" t="inlineStr">
+        <is>
+          <t>2026-03-24 13:40:00</t>
+        </is>
+      </c>
+      <c r="B117" s="4" t="inlineStr">
+        <is>
+          <t>13:40:00</t>
+        </is>
+      </c>
+      <c r="C117" s="4" t="inlineStr">
+        <is>
+          <t>13:40</t>
+        </is>
+      </c>
+      <c r="D117" s="4" t="inlineStr">
+        <is>
+          <t>209.00</t>
+        </is>
+      </c>
+      <c r="E117" s="4" t="inlineStr"/>
+      <c r="F117" s="4" t="inlineStr">
+        <is>
+          <t>168.55</t>
+        </is>
+      </c>
+      <c r="G117" s="4" t="inlineStr"/>
+      <c r="H117" s="4" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="I117" s="4" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="J117" s="4" t="inlineStr"/>
+      <c r="K117" s="4" t="inlineStr"/>
+      <c r="L117" s="4" t="inlineStr"/>
+      <c r="M117" s="4" t="inlineStr"/>
+      <c r="N117" s="4" t="inlineStr"/>
+      <c r="O117" s="4" t="inlineStr"/>
+      <c r="P117" s="4" t="inlineStr">
+        <is>
+          <t>Low Strike Check | No signal | No signal</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="4" t="inlineStr">
+        <is>
+          <t>2026-03-24 13:45:00</t>
+        </is>
+      </c>
+      <c r="B118" s="4" t="inlineStr">
+        <is>
+          <t>13:45:00</t>
+        </is>
+      </c>
+      <c r="C118" s="4" t="inlineStr">
+        <is>
+          <t>13:45</t>
+        </is>
+      </c>
+      <c r="D118" s="4" t="inlineStr">
+        <is>
+          <t>118.95</t>
+        </is>
+      </c>
+      <c r="E118" s="4" t="inlineStr"/>
+      <c r="F118" s="4" t="inlineStr">
+        <is>
+          <t>200.05</t>
+        </is>
+      </c>
+      <c r="G118" s="4" t="inlineStr"/>
+      <c r="H118" s="4" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="I118" s="4" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="J118" s="4" t="inlineStr"/>
+      <c r="K118" s="4" t="inlineStr"/>
+      <c r="L118" s="4" t="inlineStr"/>
+      <c r="M118" s="4" t="inlineStr"/>
+      <c r="N118" s="4" t="inlineStr"/>
+      <c r="O118" s="4" t="inlineStr"/>
+      <c r="P118" s="4" t="inlineStr">
+        <is>
+          <t>High Strike Check | No signal | No signal</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="4" t="inlineStr">
+        <is>
+          <t>2026-03-24 13:45:00</t>
+        </is>
+      </c>
+      <c r="B119" s="4" t="inlineStr">
+        <is>
+          <t>13:45:00</t>
+        </is>
+      </c>
+      <c r="C119" s="4" t="inlineStr">
+        <is>
+          <t>13:45</t>
+        </is>
+      </c>
+      <c r="D119" s="4" t="inlineStr">
+        <is>
+          <t>209.00</t>
+        </is>
+      </c>
+      <c r="E119" s="4" t="inlineStr"/>
+      <c r="F119" s="4" t="inlineStr">
+        <is>
+          <t>168.55</t>
+        </is>
+      </c>
+      <c r="G119" s="4" t="inlineStr"/>
+      <c r="H119" s="4" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="I119" s="4" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="J119" s="4" t="inlineStr"/>
+      <c r="K119" s="4" t="inlineStr"/>
+      <c r="L119" s="4" t="inlineStr"/>
+      <c r="M119" s="4" t="inlineStr"/>
+      <c r="N119" s="4" t="inlineStr"/>
+      <c r="O119" s="4" t="inlineStr"/>
+      <c r="P119" s="4" t="inlineStr">
+        <is>
+          <t>Low Strike Check | No signal | No signal</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="4" t="inlineStr">
+        <is>
+          <t>2026-03-24 13:50:00</t>
+        </is>
+      </c>
+      <c r="B120" s="4" t="inlineStr">
+        <is>
+          <t>13:50:00</t>
+        </is>
+      </c>
+      <c r="C120" s="4" t="inlineStr">
+        <is>
+          <t>13:50</t>
+        </is>
+      </c>
+      <c r="D120" s="4" t="inlineStr">
+        <is>
+          <t>118.95</t>
+        </is>
+      </c>
+      <c r="E120" s="4" t="inlineStr"/>
+      <c r="F120" s="4" t="inlineStr">
+        <is>
+          <t>200.05</t>
+        </is>
+      </c>
+      <c r="G120" s="4" t="inlineStr"/>
+      <c r="H120" s="4" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="I120" s="4" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="J120" s="4" t="inlineStr"/>
+      <c r="K120" s="4" t="inlineStr"/>
+      <c r="L120" s="4" t="inlineStr"/>
+      <c r="M120" s="4" t="inlineStr"/>
+      <c r="N120" s="4" t="inlineStr"/>
+      <c r="O120" s="4" t="inlineStr"/>
+      <c r="P120" s="4" t="inlineStr">
+        <is>
+          <t>High Strike Check | No signal | No signal</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="4" t="inlineStr">
+        <is>
+          <t>2026-03-24 13:50:00</t>
+        </is>
+      </c>
+      <c r="B121" s="4" t="inlineStr">
+        <is>
+          <t>13:50:00</t>
+        </is>
+      </c>
+      <c r="C121" s="4" t="inlineStr">
+        <is>
+          <t>13:50</t>
+        </is>
+      </c>
+      <c r="D121" s="4" t="inlineStr">
+        <is>
+          <t>209.00</t>
+        </is>
+      </c>
+      <c r="E121" s="4" t="inlineStr"/>
+      <c r="F121" s="4" t="inlineStr">
+        <is>
+          <t>168.55</t>
+        </is>
+      </c>
+      <c r="G121" s="4" t="inlineStr"/>
+      <c r="H121" s="4" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="I121" s="4" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="J121" s="4" t="inlineStr"/>
+      <c r="K121" s="4" t="inlineStr"/>
+      <c r="L121" s="4" t="inlineStr"/>
+      <c r="M121" s="4" t="inlineStr"/>
+      <c r="N121" s="4" t="inlineStr"/>
+      <c r="O121" s="4" t="inlineStr"/>
+      <c r="P121" s="4" t="inlineStr">
+        <is>
+          <t>Low Strike Check | No signal | No signal</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="4" t="inlineStr">
+        <is>
+          <t>2026-03-24 13:55:00</t>
+        </is>
+      </c>
+      <c r="B122" s="4" t="inlineStr">
+        <is>
+          <t>13:55:00</t>
+        </is>
+      </c>
+      <c r="C122" s="4" t="inlineStr">
+        <is>
+          <t>13:55</t>
+        </is>
+      </c>
+      <c r="D122" s="4" t="inlineStr">
+        <is>
+          <t>118.95</t>
+        </is>
+      </c>
+      <c r="E122" s="4" t="inlineStr"/>
+      <c r="F122" s="4" t="inlineStr">
+        <is>
+          <t>200.05</t>
+        </is>
+      </c>
+      <c r="G122" s="4" t="inlineStr"/>
+      <c r="H122" s="4" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="I122" s="4" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="J122" s="4" t="inlineStr"/>
+      <c r="K122" s="4" t="inlineStr"/>
+      <c r="L122" s="4" t="inlineStr"/>
+      <c r="M122" s="4" t="inlineStr"/>
+      <c r="N122" s="4" t="inlineStr"/>
+      <c r="O122" s="4" t="inlineStr"/>
+      <c r="P122" s="4" t="inlineStr">
+        <is>
+          <t>High Strike Check | No signal | No signal</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="4" t="inlineStr">
+        <is>
+          <t>2026-03-24 13:55:00</t>
+        </is>
+      </c>
+      <c r="B123" s="4" t="inlineStr">
+        <is>
+          <t>13:55:00</t>
+        </is>
+      </c>
+      <c r="C123" s="4" t="inlineStr">
+        <is>
+          <t>13:55</t>
+        </is>
+      </c>
+      <c r="D123" s="4" t="inlineStr">
+        <is>
+          <t>209.00</t>
+        </is>
+      </c>
+      <c r="E123" s="4" t="inlineStr"/>
+      <c r="F123" s="4" t="inlineStr">
+        <is>
+          <t>168.55</t>
+        </is>
+      </c>
+      <c r="G123" s="4" t="inlineStr"/>
+      <c r="H123" s="4" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="I123" s="4" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="J123" s="4" t="inlineStr"/>
+      <c r="K123" s="4" t="inlineStr"/>
+      <c r="L123" s="4" t="inlineStr"/>
+      <c r="M123" s="4" t="inlineStr"/>
+      <c r="N123" s="4" t="inlineStr"/>
+      <c r="O123" s="4" t="inlineStr"/>
+      <c r="P123" s="4" t="inlineStr">
+        <is>
+          <t>Low Strike Check | No signal | No signal</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="4" t="inlineStr">
+        <is>
+          <t>2026-03-24 14:00:00</t>
+        </is>
+      </c>
+      <c r="B124" s="4" t="inlineStr">
+        <is>
+          <t>14:00:00</t>
+        </is>
+      </c>
+      <c r="C124" s="4" t="inlineStr">
+        <is>
+          <t>14:00</t>
+        </is>
+      </c>
+      <c r="D124" s="4" t="inlineStr">
+        <is>
+          <t>118.95</t>
+        </is>
+      </c>
+      <c r="E124" s="4" t="inlineStr"/>
+      <c r="F124" s="4" t="inlineStr">
+        <is>
+          <t>200.05</t>
+        </is>
+      </c>
+      <c r="G124" s="4" t="inlineStr"/>
+      <c r="H124" s="4" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="I124" s="4" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="J124" s="4" t="inlineStr"/>
+      <c r="K124" s="4" t="inlineStr"/>
+      <c r="L124" s="4" t="inlineStr"/>
+      <c r="M124" s="4" t="inlineStr"/>
+      <c r="N124" s="4" t="inlineStr"/>
+      <c r="O124" s="4" t="inlineStr"/>
+      <c r="P124" s="4" t="inlineStr">
+        <is>
+          <t>High Strike Check | No signal | No signal</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="4" t="inlineStr">
+        <is>
+          <t>2026-03-24 14:00:00</t>
+        </is>
+      </c>
+      <c r="B125" s="4" t="inlineStr">
+        <is>
+          <t>14:00:00</t>
+        </is>
+      </c>
+      <c r="C125" s="4" t="inlineStr">
+        <is>
+          <t>14:00</t>
+        </is>
+      </c>
+      <c r="D125" s="4" t="inlineStr">
+        <is>
+          <t>209.00</t>
+        </is>
+      </c>
+      <c r="E125" s="4" t="inlineStr"/>
+      <c r="F125" s="4" t="inlineStr">
+        <is>
+          <t>168.55</t>
+        </is>
+      </c>
+      <c r="G125" s="4" t="inlineStr"/>
+      <c r="H125" s="4" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="I125" s="4" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="J125" s="4" t="inlineStr"/>
+      <c r="K125" s="4" t="inlineStr"/>
+      <c r="L125" s="4" t="inlineStr"/>
+      <c r="M125" s="4" t="inlineStr"/>
+      <c r="N125" s="4" t="inlineStr"/>
+      <c r="O125" s="4" t="inlineStr"/>
+      <c r="P125" s="4" t="inlineStr">
+        <is>
+          <t>Low Strike Check | No signal | No signal</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="4" t="inlineStr">
+        <is>
+          <t>2026-03-24 14:05:00</t>
+        </is>
+      </c>
+      <c r="B126" s="4" t="inlineStr">
+        <is>
+          <t>14:05:00</t>
+        </is>
+      </c>
+      <c r="C126" s="4" t="inlineStr">
+        <is>
+          <t>14:05</t>
+        </is>
+      </c>
+      <c r="D126" s="4" t="inlineStr">
+        <is>
+          <t>118.95</t>
+        </is>
+      </c>
+      <c r="E126" s="4" t="inlineStr"/>
+      <c r="F126" s="4" t="inlineStr">
+        <is>
+          <t>200.05</t>
+        </is>
+      </c>
+      <c r="G126" s="4" t="inlineStr"/>
+      <c r="H126" s="4" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="I126" s="4" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="J126" s="4" t="inlineStr"/>
+      <c r="K126" s="4" t="inlineStr"/>
+      <c r="L126" s="4" t="inlineStr"/>
+      <c r="M126" s="4" t="inlineStr"/>
+      <c r="N126" s="4" t="inlineStr"/>
+      <c r="O126" s="4" t="inlineStr"/>
+      <c r="P126" s="4" t="inlineStr">
+        <is>
+          <t>High Strike Check | No signal | No signal</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="4" t="inlineStr">
+        <is>
+          <t>2026-03-24 14:05:00</t>
+        </is>
+      </c>
+      <c r="B127" s="4" t="inlineStr">
+        <is>
+          <t>14:05:00</t>
+        </is>
+      </c>
+      <c r="C127" s="4" t="inlineStr">
+        <is>
+          <t>14:05</t>
+        </is>
+      </c>
+      <c r="D127" s="4" t="inlineStr">
+        <is>
+          <t>209.00</t>
+        </is>
+      </c>
+      <c r="E127" s="4" t="inlineStr"/>
+      <c r="F127" s="4" t="inlineStr">
+        <is>
+          <t>168.55</t>
+        </is>
+      </c>
+      <c r="G127" s="4" t="inlineStr"/>
+      <c r="H127" s="4" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="I127" s="4" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="J127" s="4" t="inlineStr"/>
+      <c r="K127" s="4" t="inlineStr"/>
+      <c r="L127" s="4" t="inlineStr"/>
+      <c r="M127" s="4" t="inlineStr"/>
+      <c r="N127" s="4" t="inlineStr"/>
+      <c r="O127" s="4" t="inlineStr"/>
+      <c r="P127" s="4" t="inlineStr">
+        <is>
+          <t>Low Strike Check | No signal | No signal</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="4" t="inlineStr">
+        <is>
+          <t>2026-03-24 14:10:00</t>
+        </is>
+      </c>
+      <c r="B128" s="4" t="inlineStr">
+        <is>
+          <t>14:10:00</t>
+        </is>
+      </c>
+      <c r="C128" s="4" t="inlineStr">
+        <is>
+          <t>14:10</t>
+        </is>
+      </c>
+      <c r="D128" s="4" t="inlineStr">
+        <is>
+          <t>118.95</t>
+        </is>
+      </c>
+      <c r="E128" s="4" t="inlineStr"/>
+      <c r="F128" s="4" t="inlineStr">
+        <is>
+          <t>200.05</t>
+        </is>
+      </c>
+      <c r="G128" s="4" t="inlineStr"/>
+      <c r="H128" s="4" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="I128" s="4" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="J128" s="4" t="inlineStr"/>
+      <c r="K128" s="4" t="inlineStr"/>
+      <c r="L128" s="4" t="inlineStr"/>
+      <c r="M128" s="4" t="inlineStr"/>
+      <c r="N128" s="4" t="inlineStr"/>
+      <c r="O128" s="4" t="inlineStr"/>
+      <c r="P128" s="4" t="inlineStr">
+        <is>
+          <t>High Strike Check | No signal | No signal</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="4" t="inlineStr">
+        <is>
+          <t>2026-03-24 14:10:00</t>
+        </is>
+      </c>
+      <c r="B129" s="4" t="inlineStr">
+        <is>
+          <t>14:10:00</t>
+        </is>
+      </c>
+      <c r="C129" s="4" t="inlineStr">
+        <is>
+          <t>14:10</t>
+        </is>
+      </c>
+      <c r="D129" s="4" t="inlineStr">
+        <is>
+          <t>209.00</t>
+        </is>
+      </c>
+      <c r="E129" s="4" t="inlineStr"/>
+      <c r="F129" s="4" t="inlineStr">
+        <is>
+          <t>168.55</t>
+        </is>
+      </c>
+      <c r="G129" s="4" t="inlineStr"/>
+      <c r="H129" s="4" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="I129" s="4" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="J129" s="4" t="inlineStr"/>
+      <c r="K129" s="4" t="inlineStr"/>
+      <c r="L129" s="4" t="inlineStr"/>
+      <c r="M129" s="4" t="inlineStr"/>
+      <c r="N129" s="4" t="inlineStr"/>
+      <c r="O129" s="4" t="inlineStr"/>
+      <c r="P129" s="4" t="inlineStr">
+        <is>
+          <t>Low Strike Check | No signal | No signal</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" s="4" t="inlineStr">
+        <is>
+          <t>2026-03-24 14:15:00</t>
+        </is>
+      </c>
+      <c r="B130" s="4" t="inlineStr">
+        <is>
+          <t>14:15:00</t>
+        </is>
+      </c>
+      <c r="C130" s="4" t="inlineStr">
+        <is>
+          <t>14:15</t>
+        </is>
+      </c>
+      <c r="D130" s="4" t="inlineStr">
+        <is>
+          <t>118.95</t>
+        </is>
+      </c>
+      <c r="E130" s="4" t="inlineStr"/>
+      <c r="F130" s="4" t="inlineStr">
+        <is>
+          <t>200.05</t>
+        </is>
+      </c>
+      <c r="G130" s="4" t="inlineStr"/>
+      <c r="H130" s="4" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="I130" s="4" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="J130" s="4" t="inlineStr"/>
+      <c r="K130" s="4" t="inlineStr"/>
+      <c r="L130" s="4" t="inlineStr"/>
+      <c r="M130" s="4" t="inlineStr"/>
+      <c r="N130" s="4" t="inlineStr"/>
+      <c r="O130" s="4" t="inlineStr"/>
+      <c r="P130" s="4" t="inlineStr">
+        <is>
+          <t>High Strike Check | No signal | No signal</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" s="4" t="inlineStr">
+        <is>
+          <t>2026-03-24 14:15:00</t>
+        </is>
+      </c>
+      <c r="B131" s="4" t="inlineStr">
+        <is>
+          <t>14:15:00</t>
+        </is>
+      </c>
+      <c r="C131" s="4" t="inlineStr">
+        <is>
+          <t>14:15</t>
+        </is>
+      </c>
+      <c r="D131" s="4" t="inlineStr">
+        <is>
+          <t>209.00</t>
+        </is>
+      </c>
+      <c r="E131" s="4" t="inlineStr"/>
+      <c r="F131" s="4" t="inlineStr">
+        <is>
+          <t>168.55</t>
+        </is>
+      </c>
+      <c r="G131" s="4" t="inlineStr"/>
+      <c r="H131" s="4" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="I131" s="4" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="J131" s="4" t="inlineStr"/>
+      <c r="K131" s="4" t="inlineStr"/>
+      <c r="L131" s="4" t="inlineStr"/>
+      <c r="M131" s="4" t="inlineStr"/>
+      <c r="N131" s="4" t="inlineStr"/>
+      <c r="O131" s="4" t="inlineStr"/>
+      <c r="P131" s="4" t="inlineStr">
+        <is>
+          <t>Low Strike Check | No signal | No signal</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" s="4" t="inlineStr">
+        <is>
+          <t>2026-03-24 14:20:00</t>
+        </is>
+      </c>
+      <c r="B132" s="4" t="inlineStr">
+        <is>
+          <t>14:20:00</t>
+        </is>
+      </c>
+      <c r="C132" s="4" t="inlineStr">
+        <is>
+          <t>14:20</t>
+        </is>
+      </c>
+      <c r="D132" s="4" t="inlineStr">
+        <is>
+          <t>118.95</t>
+        </is>
+      </c>
+      <c r="E132" s="4" t="inlineStr"/>
+      <c r="F132" s="4" t="inlineStr">
+        <is>
+          <t>200.05</t>
+        </is>
+      </c>
+      <c r="G132" s="4" t="inlineStr"/>
+      <c r="H132" s="4" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="I132" s="4" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="J132" s="4" t="inlineStr"/>
+      <c r="K132" s="4" t="inlineStr"/>
+      <c r="L132" s="4" t="inlineStr"/>
+      <c r="M132" s="4" t="inlineStr"/>
+      <c r="N132" s="4" t="inlineStr"/>
+      <c r="O132" s="4" t="inlineStr"/>
+      <c r="P132" s="4" t="inlineStr">
+        <is>
+          <t>High Strike Check | No signal | No signal</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" s="4" t="inlineStr">
+        <is>
+          <t>2026-03-24 14:20:00</t>
+        </is>
+      </c>
+      <c r="B133" s="4" t="inlineStr">
+        <is>
+          <t>14:20:00</t>
+        </is>
+      </c>
+      <c r="C133" s="4" t="inlineStr">
+        <is>
+          <t>14:20</t>
+        </is>
+      </c>
+      <c r="D133" s="4" t="inlineStr">
+        <is>
+          <t>209.00</t>
+        </is>
+      </c>
+      <c r="E133" s="4" t="inlineStr"/>
+      <c r="F133" s="4" t="inlineStr">
+        <is>
+          <t>168.55</t>
+        </is>
+      </c>
+      <c r="G133" s="4" t="inlineStr"/>
+      <c r="H133" s="4" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="I133" s="4" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="J133" s="4" t="inlineStr"/>
+      <c r="K133" s="4" t="inlineStr"/>
+      <c r="L133" s="4" t="inlineStr"/>
+      <c r="M133" s="4" t="inlineStr"/>
+      <c r="N133" s="4" t="inlineStr"/>
+      <c r="O133" s="4" t="inlineStr"/>
+      <c r="P133" s="4" t="inlineStr">
+        <is>
+          <t>Low Strike Check | No signal | No signal</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" s="4" t="inlineStr">
+        <is>
+          <t>2026-03-24 14:25:00</t>
+        </is>
+      </c>
+      <c r="B134" s="4" t="inlineStr">
+        <is>
+          <t>14:25:00</t>
+        </is>
+      </c>
+      <c r="C134" s="4" t="inlineStr">
+        <is>
+          <t>14:25</t>
+        </is>
+      </c>
+      <c r="D134" s="4" t="inlineStr">
+        <is>
+          <t>118.95</t>
+        </is>
+      </c>
+      <c r="E134" s="4" t="inlineStr"/>
+      <c r="F134" s="4" t="inlineStr">
+        <is>
+          <t>200.05</t>
+        </is>
+      </c>
+      <c r="G134" s="4" t="inlineStr"/>
+      <c r="H134" s="4" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="I134" s="4" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="J134" s="4" t="inlineStr"/>
+      <c r="K134" s="4" t="inlineStr"/>
+      <c r="L134" s="4" t="inlineStr"/>
+      <c r="M134" s="4" t="inlineStr"/>
+      <c r="N134" s="4" t="inlineStr"/>
+      <c r="O134" s="4" t="inlineStr"/>
+      <c r="P134" s="4" t="inlineStr">
+        <is>
+          <t>High Strike Check | No signal | No signal</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" s="4" t="inlineStr">
+        <is>
+          <t>2026-03-24 14:25:00</t>
+        </is>
+      </c>
+      <c r="B135" s="4" t="inlineStr">
+        <is>
+          <t>14:25:00</t>
+        </is>
+      </c>
+      <c r="C135" s="4" t="inlineStr">
+        <is>
+          <t>14:25</t>
+        </is>
+      </c>
+      <c r="D135" s="4" t="inlineStr">
+        <is>
+          <t>209.00</t>
+        </is>
+      </c>
+      <c r="E135" s="4" t="inlineStr"/>
+      <c r="F135" s="4" t="inlineStr">
+        <is>
+          <t>168.55</t>
+        </is>
+      </c>
+      <c r="G135" s="4" t="inlineStr"/>
+      <c r="H135" s="4" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="I135" s="4" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="J135" s="4" t="inlineStr"/>
+      <c r="K135" s="4" t="inlineStr"/>
+      <c r="L135" s="4" t="inlineStr"/>
+      <c r="M135" s="4" t="inlineStr"/>
+      <c r="N135" s="4" t="inlineStr"/>
+      <c r="O135" s="4" t="inlineStr"/>
+      <c r="P135" s="4" t="inlineStr">
+        <is>
+          <t>Low Strike Check | No signal | No signal</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" s="4" t="inlineStr">
+        <is>
+          <t>2026-03-24 14:30:00</t>
+        </is>
+      </c>
+      <c r="B136" s="4" t="inlineStr">
+        <is>
+          <t>14:30:00</t>
+        </is>
+      </c>
+      <c r="C136" s="4" t="inlineStr">
+        <is>
+          <t>14:30</t>
+        </is>
+      </c>
+      <c r="D136" s="4" t="inlineStr">
+        <is>
+          <t>118.95</t>
+        </is>
+      </c>
+      <c r="E136" s="4" t="inlineStr"/>
+      <c r="F136" s="4" t="inlineStr">
+        <is>
+          <t>200.05</t>
+        </is>
+      </c>
+      <c r="G136" s="4" t="inlineStr"/>
+      <c r="H136" s="4" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="I136" s="4" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="J136" s="4" t="inlineStr"/>
+      <c r="K136" s="4" t="inlineStr"/>
+      <c r="L136" s="4" t="inlineStr"/>
+      <c r="M136" s="4" t="inlineStr"/>
+      <c r="N136" s="4" t="inlineStr"/>
+      <c r="O136" s="4" t="inlineStr"/>
+      <c r="P136" s="4" t="inlineStr">
+        <is>
+          <t>High Strike Check | No signal | No signal</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" s="4" t="inlineStr">
+        <is>
+          <t>2026-03-24 14:30:00</t>
+        </is>
+      </c>
+      <c r="B137" s="4" t="inlineStr">
+        <is>
+          <t>14:30:00</t>
+        </is>
+      </c>
+      <c r="C137" s="4" t="inlineStr">
+        <is>
+          <t>14:30</t>
+        </is>
+      </c>
+      <c r="D137" s="4" t="inlineStr">
+        <is>
+          <t>209.00</t>
+        </is>
+      </c>
+      <c r="E137" s="4" t="inlineStr"/>
+      <c r="F137" s="4" t="inlineStr">
+        <is>
+          <t>168.55</t>
+        </is>
+      </c>
+      <c r="G137" s="4" t="inlineStr"/>
+      <c r="H137" s="4" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="I137" s="4" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="J137" s="4" t="inlineStr"/>
+      <c r="K137" s="4" t="inlineStr"/>
+      <c r="L137" s="4" t="inlineStr"/>
+      <c r="M137" s="4" t="inlineStr"/>
+      <c r="N137" s="4" t="inlineStr"/>
+      <c r="O137" s="4" t="inlineStr"/>
+      <c r="P137" s="4" t="inlineStr">
+        <is>
+          <t>Low Strike Check | No signal | No signal</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" s="4" t="inlineStr">
+        <is>
+          <t>2026-03-24 14:35:00</t>
+        </is>
+      </c>
+      <c r="B138" s="4" t="inlineStr">
+        <is>
+          <t>14:35:00</t>
+        </is>
+      </c>
+      <c r="C138" s="4" t="inlineStr">
+        <is>
+          <t>14:35</t>
+        </is>
+      </c>
+      <c r="D138" s="4" t="inlineStr">
+        <is>
+          <t>118.95</t>
+        </is>
+      </c>
+      <c r="E138" s="4" t="inlineStr"/>
+      <c r="F138" s="4" t="inlineStr">
+        <is>
+          <t>200.05</t>
+        </is>
+      </c>
+      <c r="G138" s="4" t="inlineStr"/>
+      <c r="H138" s="4" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="I138" s="4" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="J138" s="4" t="inlineStr"/>
+      <c r="K138" s="4" t="inlineStr"/>
+      <c r="L138" s="4" t="inlineStr"/>
+      <c r="M138" s="4" t="inlineStr"/>
+      <c r="N138" s="4" t="inlineStr"/>
+      <c r="O138" s="4" t="inlineStr"/>
+      <c r="P138" s="4" t="inlineStr">
+        <is>
+          <t>High Strike Check | No signal | No signal</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" s="4" t="inlineStr">
+        <is>
+          <t>2026-03-24 14:35:00</t>
+        </is>
+      </c>
+      <c r="B139" s="4" t="inlineStr">
+        <is>
+          <t>14:35:00</t>
+        </is>
+      </c>
+      <c r="C139" s="4" t="inlineStr">
+        <is>
+          <t>14:35</t>
+        </is>
+      </c>
+      <c r="D139" s="4" t="inlineStr">
+        <is>
+          <t>209.00</t>
+        </is>
+      </c>
+      <c r="E139" s="4" t="inlineStr"/>
+      <c r="F139" s="4" t="inlineStr">
+        <is>
+          <t>168.55</t>
+        </is>
+      </c>
+      <c r="G139" s="4" t="inlineStr"/>
+      <c r="H139" s="4" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="I139" s="4" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="J139" s="4" t="inlineStr"/>
+      <c r="K139" s="4" t="inlineStr"/>
+      <c r="L139" s="4" t="inlineStr"/>
+      <c r="M139" s="4" t="inlineStr"/>
+      <c r="N139" s="4" t="inlineStr"/>
+      <c r="O139" s="4" t="inlineStr"/>
+      <c r="P139" s="4" t="inlineStr">
+        <is>
+          <t>Low Strike Check | No signal | No signal</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" s="4" t="inlineStr">
+        <is>
+          <t>2026-03-24 14:40:00</t>
+        </is>
+      </c>
+      <c r="B140" s="4" t="inlineStr">
+        <is>
+          <t>14:40:00</t>
+        </is>
+      </c>
+      <c r="C140" s="4" t="inlineStr">
+        <is>
+          <t>14:40</t>
+        </is>
+      </c>
+      <c r="D140" s="4" t="inlineStr">
+        <is>
+          <t>118.95</t>
+        </is>
+      </c>
+      <c r="E140" s="4" t="inlineStr"/>
+      <c r="F140" s="4" t="inlineStr">
+        <is>
+          <t>200.05</t>
+        </is>
+      </c>
+      <c r="G140" s="4" t="inlineStr"/>
+      <c r="H140" s="4" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="I140" s="4" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="J140" s="4" t="inlineStr"/>
+      <c r="K140" s="4" t="inlineStr"/>
+      <c r="L140" s="4" t="inlineStr"/>
+      <c r="M140" s="4" t="inlineStr"/>
+      <c r="N140" s="4" t="inlineStr"/>
+      <c r="O140" s="4" t="inlineStr"/>
+      <c r="P140" s="4" t="inlineStr">
+        <is>
+          <t>High Strike Check | No signal | No signal</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" s="4" t="inlineStr">
+        <is>
+          <t>2026-03-24 14:40:00</t>
+        </is>
+      </c>
+      <c r="B141" s="4" t="inlineStr">
+        <is>
+          <t>14:40:00</t>
+        </is>
+      </c>
+      <c r="C141" s="4" t="inlineStr">
+        <is>
+          <t>14:40</t>
+        </is>
+      </c>
+      <c r="D141" s="4" t="inlineStr">
+        <is>
+          <t>209.00</t>
+        </is>
+      </c>
+      <c r="E141" s="4" t="inlineStr"/>
+      <c r="F141" s="4" t="inlineStr">
+        <is>
+          <t>168.55</t>
+        </is>
+      </c>
+      <c r="G141" s="4" t="inlineStr"/>
+      <c r="H141" s="4" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="I141" s="4" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="J141" s="4" t="inlineStr"/>
+      <c r="K141" s="4" t="inlineStr"/>
+      <c r="L141" s="4" t="inlineStr"/>
+      <c r="M141" s="4" t="inlineStr"/>
+      <c r="N141" s="4" t="inlineStr"/>
+      <c r="O141" s="4" t="inlineStr"/>
+      <c r="P141" s="4" t="inlineStr">
+        <is>
+          <t>Low Strike Check | No signal | No signal</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" s="4" t="inlineStr">
+        <is>
+          <t>2026-03-24 14:45:00</t>
+        </is>
+      </c>
+      <c r="B142" s="4" t="inlineStr">
+        <is>
+          <t>14:45:00</t>
+        </is>
+      </c>
+      <c r="C142" s="4" t="inlineStr">
+        <is>
+          <t>14:45</t>
+        </is>
+      </c>
+      <c r="D142" s="4" t="inlineStr">
+        <is>
+          <t>118.95</t>
+        </is>
+      </c>
+      <c r="E142" s="4" t="inlineStr"/>
+      <c r="F142" s="4" t="inlineStr">
+        <is>
+          <t>200.05</t>
+        </is>
+      </c>
+      <c r="G142" s="4" t="inlineStr"/>
+      <c r="H142" s="4" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="I142" s="4" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="J142" s="4" t="inlineStr"/>
+      <c r="K142" s="4" t="inlineStr"/>
+      <c r="L142" s="4" t="inlineStr"/>
+      <c r="M142" s="4" t="inlineStr"/>
+      <c r="N142" s="4" t="inlineStr"/>
+      <c r="O142" s="4" t="inlineStr"/>
+      <c r="P142" s="4" t="inlineStr">
+        <is>
+          <t>High Strike Check | No signal | No signal</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" s="4" t="inlineStr">
+        <is>
+          <t>2026-03-24 14:45:00</t>
+        </is>
+      </c>
+      <c r="B143" s="4" t="inlineStr">
+        <is>
+          <t>14:45:00</t>
+        </is>
+      </c>
+      <c r="C143" s="4" t="inlineStr">
+        <is>
+          <t>14:45</t>
+        </is>
+      </c>
+      <c r="D143" s="4" t="inlineStr">
+        <is>
+          <t>209.00</t>
+        </is>
+      </c>
+      <c r="E143" s="4" t="inlineStr"/>
+      <c r="F143" s="4" t="inlineStr">
+        <is>
+          <t>168.55</t>
+        </is>
+      </c>
+      <c r="G143" s="4" t="inlineStr"/>
+      <c r="H143" s="4" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="I143" s="4" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="J143" s="4" t="inlineStr"/>
+      <c r="K143" s="4" t="inlineStr"/>
+      <c r="L143" s="4" t="inlineStr"/>
+      <c r="M143" s="4" t="inlineStr"/>
+      <c r="N143" s="4" t="inlineStr"/>
+      <c r="O143" s="4" t="inlineStr"/>
+      <c r="P143" s="4" t="inlineStr">
+        <is>
+          <t>Low Strike Check | No signal | No signal</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" s="4" t="inlineStr">
+        <is>
+          <t>2026-03-24 14:50:00</t>
+        </is>
+      </c>
+      <c r="B144" s="4" t="inlineStr">
+        <is>
+          <t>14:50:00</t>
+        </is>
+      </c>
+      <c r="C144" s="4" t="inlineStr">
+        <is>
+          <t>14:50</t>
+        </is>
+      </c>
+      <c r="D144" s="4" t="inlineStr">
+        <is>
+          <t>118.95</t>
+        </is>
+      </c>
+      <c r="E144" s="4" t="inlineStr"/>
+      <c r="F144" s="4" t="inlineStr">
+        <is>
+          <t>200.05</t>
+        </is>
+      </c>
+      <c r="G144" s="4" t="inlineStr"/>
+      <c r="H144" s="4" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="I144" s="4" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="J144" s="4" t="inlineStr"/>
+      <c r="K144" s="4" t="inlineStr"/>
+      <c r="L144" s="4" t="inlineStr"/>
+      <c r="M144" s="4" t="inlineStr"/>
+      <c r="N144" s="4" t="inlineStr"/>
+      <c r="O144" s="4" t="inlineStr"/>
+      <c r="P144" s="4" t="inlineStr">
+        <is>
+          <t>High Strike Check | No signal | No signal</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" s="4" t="inlineStr">
+        <is>
+          <t>2026-03-24 14:50:00</t>
+        </is>
+      </c>
+      <c r="B145" s="4" t="inlineStr">
+        <is>
+          <t>14:50:00</t>
+        </is>
+      </c>
+      <c r="C145" s="4" t="inlineStr">
+        <is>
+          <t>14:50</t>
+        </is>
+      </c>
+      <c r="D145" s="4" t="inlineStr">
+        <is>
+          <t>209.00</t>
+        </is>
+      </c>
+      <c r="E145" s="4" t="inlineStr"/>
+      <c r="F145" s="4" t="inlineStr">
+        <is>
+          <t>168.55</t>
+        </is>
+      </c>
+      <c r="G145" s="4" t="inlineStr"/>
+      <c r="H145" s="4" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="I145" s="4" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="J145" s="4" t="inlineStr"/>
+      <c r="K145" s="4" t="inlineStr"/>
+      <c r="L145" s="4" t="inlineStr"/>
+      <c r="M145" s="4" t="inlineStr"/>
+      <c r="N145" s="4" t="inlineStr"/>
+      <c r="O145" s="4" t="inlineStr"/>
+      <c r="P145" s="4" t="inlineStr">
+        <is>
+          <t>Low Strike Check | No signal | No signal</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" s="4" t="inlineStr">
+        <is>
+          <t>2026-03-24 14:55:00</t>
+        </is>
+      </c>
+      <c r="B146" s="4" t="inlineStr">
+        <is>
+          <t>14:55:00</t>
+        </is>
+      </c>
+      <c r="C146" s="4" t="inlineStr">
+        <is>
+          <t>14:55</t>
+        </is>
+      </c>
+      <c r="D146" s="4" t="inlineStr">
+        <is>
+          <t>118.95</t>
+        </is>
+      </c>
+      <c r="E146" s="4" t="inlineStr"/>
+      <c r="F146" s="4" t="inlineStr">
+        <is>
+          <t>200.05</t>
+        </is>
+      </c>
+      <c r="G146" s="4" t="inlineStr"/>
+      <c r="H146" s="4" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="I146" s="4" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="J146" s="4" t="inlineStr"/>
+      <c r="K146" s="4" t="inlineStr"/>
+      <c r="L146" s="4" t="inlineStr"/>
+      <c r="M146" s="4" t="inlineStr"/>
+      <c r="N146" s="4" t="inlineStr"/>
+      <c r="O146" s="4" t="inlineStr"/>
+      <c r="P146" s="4" t="inlineStr">
+        <is>
+          <t>High Strike Check | No signal | No signal</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" s="4" t="inlineStr">
+        <is>
+          <t>2026-03-24 14:55:00</t>
+        </is>
+      </c>
+      <c r="B147" s="4" t="inlineStr">
+        <is>
+          <t>14:55:00</t>
+        </is>
+      </c>
+      <c r="C147" s="4" t="inlineStr">
+        <is>
+          <t>14:55</t>
+        </is>
+      </c>
+      <c r="D147" s="4" t="inlineStr">
+        <is>
+          <t>209.00</t>
+        </is>
+      </c>
+      <c r="E147" s="4" t="inlineStr"/>
+      <c r="F147" s="4" t="inlineStr">
+        <is>
+          <t>168.55</t>
+        </is>
+      </c>
+      <c r="G147" s="4" t="inlineStr"/>
+      <c r="H147" s="4" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="I147" s="4" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="J147" s="4" t="inlineStr"/>
+      <c r="K147" s="4" t="inlineStr"/>
+      <c r="L147" s="4" t="inlineStr"/>
+      <c r="M147" s="4" t="inlineStr"/>
+      <c r="N147" s="4" t="inlineStr"/>
+      <c r="O147" s="4" t="inlineStr"/>
+      <c r="P147" s="4" t="inlineStr">
+        <is>
+          <t>Low Strike Check | No signal | No signal</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" s="4" t="inlineStr">
+        <is>
+          <t>2026-03-24 15:00:00</t>
+        </is>
+      </c>
+      <c r="B148" s="4" t="inlineStr">
+        <is>
+          <t>15:00:00</t>
+        </is>
+      </c>
+      <c r="C148" s="4" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="D148" s="4" t="inlineStr">
+        <is>
+          <t>118.95</t>
+        </is>
+      </c>
+      <c r="E148" s="4" t="inlineStr"/>
+      <c r="F148" s="4" t="inlineStr">
+        <is>
+          <t>200.05</t>
+        </is>
+      </c>
+      <c r="G148" s="4" t="inlineStr"/>
+      <c r="H148" s="4" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="I148" s="4" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="J148" s="4" t="inlineStr"/>
+      <c r="K148" s="4" t="inlineStr"/>
+      <c r="L148" s="4" t="inlineStr"/>
+      <c r="M148" s="4" t="inlineStr"/>
+      <c r="N148" s="4" t="inlineStr"/>
+      <c r="O148" s="4" t="inlineStr"/>
+      <c r="P148" s="4" t="inlineStr">
+        <is>
+          <t>High Strike Check | No signal | No signal</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" s="4" t="inlineStr">
+        <is>
+          <t>2026-03-24 15:00:00</t>
+        </is>
+      </c>
+      <c r="B149" s="4" t="inlineStr">
+        <is>
+          <t>15:00:00</t>
+        </is>
+      </c>
+      <c r="C149" s="4" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="D149" s="4" t="inlineStr">
+        <is>
+          <t>209.00</t>
+        </is>
+      </c>
+      <c r="E149" s="4" t="inlineStr"/>
+      <c r="F149" s="4" t="inlineStr">
+        <is>
+          <t>168.55</t>
+        </is>
+      </c>
+      <c r="G149" s="4" t="inlineStr"/>
+      <c r="H149" s="4" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="I149" s="4" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="J149" s="4" t="inlineStr"/>
+      <c r="K149" s="4" t="inlineStr"/>
+      <c r="L149" s="4" t="inlineStr"/>
+      <c r="M149" s="4" t="inlineStr"/>
+      <c r="N149" s="4" t="inlineStr"/>
+      <c r="O149" s="4" t="inlineStr"/>
+      <c r="P149" s="4" t="inlineStr">
+        <is>
+          <t>Low Strike Check | No signal | No signal</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" s="4" t="inlineStr">
+        <is>
+          <t>2026-03-24 15:05:00</t>
+        </is>
+      </c>
+      <c r="B150" s="4" t="inlineStr">
+        <is>
+          <t>15:05:00</t>
+        </is>
+      </c>
+      <c r="C150" s="4" t="inlineStr">
+        <is>
+          <t>15:05</t>
+        </is>
+      </c>
+      <c r="D150" s="4" t="inlineStr">
+        <is>
+          <t>118.95</t>
+        </is>
+      </c>
+      <c r="E150" s="4" t="inlineStr"/>
+      <c r="F150" s="4" t="inlineStr">
+        <is>
+          <t>200.05</t>
+        </is>
+      </c>
+      <c r="G150" s="4" t="inlineStr"/>
+      <c r="H150" s="4" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="I150" s="4" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="J150" s="4" t="inlineStr"/>
+      <c r="K150" s="4" t="inlineStr"/>
+      <c r="L150" s="4" t="inlineStr"/>
+      <c r="M150" s="4" t="inlineStr"/>
+      <c r="N150" s="4" t="inlineStr"/>
+      <c r="O150" s="4" t="inlineStr"/>
+      <c r="P150" s="4" t="inlineStr">
+        <is>
+          <t>High Strike Check | No signal | No signal</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" s="4" t="inlineStr">
+        <is>
+          <t>2026-03-24 15:05:00</t>
+        </is>
+      </c>
+      <c r="B151" s="4" t="inlineStr">
+        <is>
+          <t>15:05:00</t>
+        </is>
+      </c>
+      <c r="C151" s="4" t="inlineStr">
+        <is>
+          <t>15:05</t>
+        </is>
+      </c>
+      <c r="D151" s="4" t="inlineStr">
+        <is>
+          <t>209.00</t>
+        </is>
+      </c>
+      <c r="E151" s="4" t="inlineStr"/>
+      <c r="F151" s="4" t="inlineStr">
+        <is>
+          <t>168.55</t>
+        </is>
+      </c>
+      <c r="G151" s="4" t="inlineStr"/>
+      <c r="H151" s="4" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="I151" s="4" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="J151" s="4" t="inlineStr"/>
+      <c r="K151" s="4" t="inlineStr"/>
+      <c r="L151" s="4" t="inlineStr"/>
+      <c r="M151" s="4" t="inlineStr"/>
+      <c r="N151" s="4" t="inlineStr"/>
+      <c r="O151" s="4" t="inlineStr"/>
+      <c r="P151" s="4" t="inlineStr">
+        <is>
+          <t>Low Strike Check | No signal | No signal</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" s="4" t="inlineStr">
+        <is>
+          <t>2026-03-24 15:10:00</t>
+        </is>
+      </c>
+      <c r="B152" s="4" t="inlineStr">
+        <is>
+          <t>15:10:00</t>
+        </is>
+      </c>
+      <c r="C152" s="4" t="inlineStr">
+        <is>
+          <t>15:10</t>
+        </is>
+      </c>
+      <c r="D152" s="4" t="inlineStr">
+        <is>
+          <t>118.95</t>
+        </is>
+      </c>
+      <c r="E152" s="4" t="inlineStr"/>
+      <c r="F152" s="4" t="inlineStr">
+        <is>
+          <t>200.05</t>
+        </is>
+      </c>
+      <c r="G152" s="4" t="inlineStr"/>
+      <c r="H152" s="4" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="I152" s="4" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="J152" s="4" t="inlineStr"/>
+      <c r="K152" s="4" t="inlineStr"/>
+      <c r="L152" s="4" t="inlineStr"/>
+      <c r="M152" s="4" t="inlineStr"/>
+      <c r="N152" s="4" t="inlineStr"/>
+      <c r="O152" s="4" t="inlineStr"/>
+      <c r="P152" s="4" t="inlineStr">
+        <is>
+          <t>High Strike Check | No signal | No signal</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" s="4" t="inlineStr">
+        <is>
+          <t>2026-03-24 15:10:00</t>
+        </is>
+      </c>
+      <c r="B153" s="4" t="inlineStr">
+        <is>
+          <t>15:10:00</t>
+        </is>
+      </c>
+      <c r="C153" s="4" t="inlineStr">
+        <is>
+          <t>15:10</t>
+        </is>
+      </c>
+      <c r="D153" s="4" t="inlineStr">
+        <is>
+          <t>209.00</t>
+        </is>
+      </c>
+      <c r="E153" s="4" t="inlineStr"/>
+      <c r="F153" s="4" t="inlineStr">
+        <is>
+          <t>168.55</t>
+        </is>
+      </c>
+      <c r="G153" s="4" t="inlineStr"/>
+      <c r="H153" s="4" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="I153" s="4" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="J153" s="4" t="inlineStr"/>
+      <c r="K153" s="4" t="inlineStr"/>
+      <c r="L153" s="4" t="inlineStr"/>
+      <c r="M153" s="4" t="inlineStr"/>
+      <c r="N153" s="4" t="inlineStr"/>
+      <c r="O153" s="4" t="inlineStr"/>
+      <c r="P153" s="4" t="inlineStr">
+        <is>
+          <t>Low Strike Check | No signal | No signal</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" s="4" t="inlineStr">
+        <is>
+          <t>2026-03-24 15:15:00</t>
+        </is>
+      </c>
+      <c r="B154" s="4" t="inlineStr">
+        <is>
+          <t>15:15:00</t>
+        </is>
+      </c>
+      <c r="C154" s="4" t="inlineStr">
+        <is>
+          <t>15:15</t>
+        </is>
+      </c>
+      <c r="D154" s="4" t="inlineStr">
+        <is>
+          <t>118.95</t>
+        </is>
+      </c>
+      <c r="E154" s="4" t="inlineStr"/>
+      <c r="F154" s="4" t="inlineStr">
+        <is>
+          <t>200.05</t>
+        </is>
+      </c>
+      <c r="G154" s="4" t="inlineStr"/>
+      <c r="H154" s="4" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="I154" s="4" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="J154" s="4" t="inlineStr"/>
+      <c r="K154" s="4" t="inlineStr"/>
+      <c r="L154" s="4" t="inlineStr"/>
+      <c r="M154" s="4" t="inlineStr"/>
+      <c r="N154" s="4" t="inlineStr"/>
+      <c r="O154" s="4" t="inlineStr"/>
+      <c r="P154" s="4" t="inlineStr">
+        <is>
+          <t>High Strike Check | No signal | No signal</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" s="4" t="inlineStr">
+        <is>
+          <t>2026-03-24 15:15:00</t>
+        </is>
+      </c>
+      <c r="B155" s="4" t="inlineStr">
+        <is>
+          <t>15:15:00</t>
+        </is>
+      </c>
+      <c r="C155" s="4" t="inlineStr">
+        <is>
+          <t>15:15</t>
+        </is>
+      </c>
+      <c r="D155" s="4" t="inlineStr">
+        <is>
+          <t>209.00</t>
+        </is>
+      </c>
+      <c r="E155" s="4" t="inlineStr"/>
+      <c r="F155" s="4" t="inlineStr">
+        <is>
+          <t>168.55</t>
+        </is>
+      </c>
+      <c r="G155" s="4" t="inlineStr"/>
+      <c r="H155" s="4" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="I155" s="4" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="J155" s="4" t="inlineStr"/>
+      <c r="K155" s="4" t="inlineStr"/>
+      <c r="L155" s="4" t="inlineStr"/>
+      <c r="M155" s="4" t="inlineStr"/>
+      <c r="N155" s="4" t="inlineStr"/>
+      <c r="O155" s="4" t="inlineStr"/>
+      <c r="P155" s="4" t="inlineStr">
+        <is>
+          <t>Low Strike Check | No signal | No signal</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" s="4" t="inlineStr">
+        <is>
+          <t>2026-03-25 09:15:00</t>
+        </is>
+      </c>
+      <c r="B156" s="4" t="inlineStr">
+        <is>
+          <t>09:15:00</t>
+        </is>
+      </c>
+      <c r="C156" s="4" t="inlineStr">
+        <is>
+          <t>09:15</t>
+        </is>
+      </c>
+      <c r="D156" s="4" t="inlineStr">
+        <is>
+          <t>303.85</t>
+        </is>
+      </c>
+      <c r="E156" s="4" t="inlineStr"/>
+      <c r="F156" s="4" t="inlineStr">
+        <is>
+          <t>333.00</t>
+        </is>
+      </c>
+      <c r="G156" s="4" t="inlineStr"/>
+      <c r="H156" s="4" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="I156" s="4" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="J156" s="4" t="inlineStr"/>
+      <c r="K156" s="4" t="inlineStr"/>
+      <c r="L156" s="4" t="inlineStr"/>
+      <c r="M156" s="4" t="inlineStr"/>
+      <c r="N156" s="4" t="inlineStr"/>
+      <c r="O156" s="4" t="inlineStr"/>
+      <c r="P156" s="4" t="inlineStr">
+        <is>
+          <t>High Strike Check | No signal | No signal</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" s="4" t="inlineStr">
+        <is>
+          <t>2026-03-25 09:15:00</t>
+        </is>
+      </c>
+      <c r="B157" s="4" t="inlineStr">
+        <is>
+          <t>09:15:00</t>
+        </is>
+      </c>
+      <c r="C157" s="4" t="inlineStr">
+        <is>
+          <t>09:15</t>
+        </is>
+      </c>
+      <c r="D157" s="4" t="inlineStr">
+        <is>
+          <t>330.75</t>
+        </is>
+      </c>
+      <c r="E157" s="4" t="inlineStr"/>
+      <c r="F157" s="4" t="inlineStr">
+        <is>
+          <t>331.00</t>
+        </is>
+      </c>
+      <c r="G157" s="4" t="inlineStr"/>
+      <c r="H157" s="4" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="I157" s="4" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="J157" s="4" t="inlineStr"/>
+      <c r="K157" s="4" t="inlineStr"/>
+      <c r="L157" s="4" t="inlineStr"/>
+      <c r="M157" s="4" t="inlineStr"/>
+      <c r="N157" s="4" t="inlineStr"/>
+      <c r="O157" s="4" t="inlineStr"/>
+      <c r="P157" s="4" t="inlineStr">
+        <is>
+          <t>Low Strike Check | No signal | No signal</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" s="4" t="inlineStr">
+        <is>
+          <t>2026-03-25 09:20:00</t>
+        </is>
+      </c>
+      <c r="B158" s="4" t="inlineStr">
+        <is>
+          <t>09:20:00</t>
+        </is>
+      </c>
+      <c r="C158" s="4" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="D158" s="4" t="inlineStr">
+        <is>
+          <t>310.00</t>
+        </is>
+      </c>
+      <c r="E158" s="4" t="inlineStr"/>
+      <c r="F158" s="4" t="inlineStr">
+        <is>
+          <t>364.95</t>
+        </is>
+      </c>
+      <c r="G158" s="4" t="inlineStr"/>
+      <c r="H158" s="4" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="I158" s="4" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="J158" s="4" t="inlineStr"/>
+      <c r="K158" s="4" t="inlineStr"/>
+      <c r="L158" s="4" t="inlineStr"/>
+      <c r="M158" s="4" t="inlineStr"/>
+      <c r="N158" s="4" t="inlineStr"/>
+      <c r="O158" s="4" t="inlineStr"/>
+      <c r="P158" s="4" t="inlineStr">
+        <is>
+          <t>High Strike Check | No signal | No signal</t>
+        </is>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" s="4" t="inlineStr">
+        <is>
+          <t>2026-03-25 09:20:00</t>
+        </is>
+      </c>
+      <c r="B159" s="4" t="inlineStr">
+        <is>
+          <t>09:20:00</t>
+        </is>
+      </c>
+      <c r="C159" s="4" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="D159" s="4" t="inlineStr">
+        <is>
+          <t>368.75</t>
+        </is>
+      </c>
+      <c r="E159" s="4" t="inlineStr"/>
+      <c r="F159" s="4" t="inlineStr">
+        <is>
+          <t>331.00</t>
+        </is>
+      </c>
+      <c r="G159" s="4" t="inlineStr"/>
+      <c r="H159" s="4" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="I159" s="4" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="J159" s="4" t="inlineStr"/>
+      <c r="K159" s="4" t="inlineStr"/>
+      <c r="L159" s="4" t="inlineStr"/>
+      <c r="M159" s="4" t="inlineStr"/>
+      <c r="N159" s="4" t="inlineStr"/>
+      <c r="O159" s="4" t="inlineStr"/>
+      <c r="P159" s="4" t="inlineStr">
+        <is>
+          <t>Low Strike Check | No signal | No signal</t>
+        </is>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" s="4" t="inlineStr">
+        <is>
+          <t>2026-03-25 09:25:00</t>
+        </is>
+      </c>
+      <c r="B160" s="4" t="inlineStr">
+        <is>
+          <t>09:25:00</t>
+        </is>
+      </c>
+      <c r="C160" s="4" t="inlineStr">
+        <is>
+          <t>09:25</t>
+        </is>
+      </c>
+      <c r="D160" s="4" t="inlineStr">
+        <is>
+          <t>310.00</t>
+        </is>
+      </c>
+      <c r="E160" s="4" t="inlineStr"/>
+      <c r="F160" s="4" t="inlineStr">
+        <is>
+          <t>364.95</t>
+        </is>
+      </c>
+      <c r="G160" s="4" t="inlineStr"/>
+      <c r="H160" s="4" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="I160" s="4" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="J160" s="4" t="inlineStr"/>
+      <c r="K160" s="4" t="inlineStr"/>
+      <c r="L160" s="4" t="inlineStr"/>
+      <c r="M160" s="4" t="inlineStr"/>
+      <c r="N160" s="4" t="inlineStr"/>
+      <c r="O160" s="4" t="inlineStr"/>
+      <c r="P160" s="4" t="inlineStr">
+        <is>
+          <t>High Strike Check | No signal | No signal</t>
+        </is>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" s="4" t="inlineStr">
+        <is>
+          <t>2026-03-25 09:25:00</t>
+        </is>
+      </c>
+      <c r="B161" s="4" t="inlineStr">
+        <is>
+          <t>09:25:00</t>
+        </is>
+      </c>
+      <c r="C161" s="4" t="inlineStr">
+        <is>
+          <t>09:25</t>
+        </is>
+      </c>
+      <c r="D161" s="4" t="inlineStr">
+        <is>
+          <t>368.75</t>
+        </is>
+      </c>
+      <c r="E161" s="4" t="inlineStr"/>
+      <c r="F161" s="4" t="inlineStr">
+        <is>
+          <t>331.00</t>
+        </is>
+      </c>
+      <c r="G161" s="4" t="inlineStr"/>
+      <c r="H161" s="4" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="I161" s="4" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="J161" s="4" t="inlineStr"/>
+      <c r="K161" s="4" t="inlineStr"/>
+      <c r="L161" s="4" t="inlineStr"/>
+      <c r="M161" s="4" t="inlineStr"/>
+      <c r="N161" s="4" t="inlineStr"/>
+      <c r="O161" s="4" t="inlineStr"/>
+      <c r="P161" s="4" t="inlineStr">
+        <is>
+          <t>Low Strike Check | No signal | No signal</t>
+        </is>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" s="4" t="inlineStr">
+        <is>
+          <t>2026-03-25 09:30:00</t>
+        </is>
+      </c>
+      <c r="B162" s="4" t="inlineStr">
+        <is>
+          <t>09:30:00</t>
+        </is>
+      </c>
+      <c r="C162" s="4" t="inlineStr">
+        <is>
+          <t>09:30</t>
+        </is>
+      </c>
+      <c r="D162" s="4" t="inlineStr">
+        <is>
+          <t>310.00</t>
+        </is>
+      </c>
+      <c r="E162" s="4" t="inlineStr"/>
+      <c r="F162" s="4" t="inlineStr">
+        <is>
+          <t>364.95</t>
+        </is>
+      </c>
+      <c r="G162" s="4" t="inlineStr"/>
+      <c r="H162" s="4" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="I162" s="4" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="J162" s="4" t="inlineStr"/>
+      <c r="K162" s="4" t="inlineStr"/>
+      <c r="L162" s="4" t="inlineStr"/>
+      <c r="M162" s="4" t="inlineStr"/>
+      <c r="N162" s="4" t="inlineStr"/>
+      <c r="O162" s="4" t="inlineStr"/>
+      <c r="P162" s="4" t="inlineStr">
+        <is>
+          <t>High Strike Check | No signal | No signal</t>
+        </is>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" s="4" t="inlineStr">
+        <is>
+          <t>2026-03-25 09:30:00</t>
+        </is>
+      </c>
+      <c r="B163" s="4" t="inlineStr">
+        <is>
+          <t>09:30:00</t>
+        </is>
+      </c>
+      <c r="C163" s="4" t="inlineStr">
+        <is>
+          <t>09:30</t>
+        </is>
+      </c>
+      <c r="D163" s="4" t="inlineStr">
+        <is>
+          <t>368.75</t>
+        </is>
+      </c>
+      <c r="E163" s="4" t="inlineStr"/>
+      <c r="F163" s="4" t="inlineStr">
+        <is>
+          <t>331.00</t>
+        </is>
+      </c>
+      <c r="G163" s="4" t="inlineStr"/>
+      <c r="H163" s="4" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="I163" s="4" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="J163" s="4" t="inlineStr"/>
+      <c r="K163" s="4" t="inlineStr"/>
+      <c r="L163" s="4" t="inlineStr"/>
+      <c r="M163" s="4" t="inlineStr"/>
+      <c r="N163" s="4" t="inlineStr"/>
+      <c r="O163" s="4" t="inlineStr"/>
+      <c r="P163" s="4" t="inlineStr">
+        <is>
+          <t>Low Strike Check | No signal | No signal</t>
+        </is>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" s="4" t="inlineStr">
+        <is>
+          <t>2026-03-25 09:35:00</t>
+        </is>
+      </c>
+      <c r="B164" s="4" t="inlineStr">
+        <is>
+          <t>09:35:00</t>
+        </is>
+      </c>
+      <c r="C164" s="4" t="inlineStr">
+        <is>
+          <t>09:35</t>
+        </is>
+      </c>
+      <c r="D164" s="4" t="inlineStr">
+        <is>
+          <t>310.00</t>
+        </is>
+      </c>
+      <c r="E164" s="4" t="inlineStr"/>
+      <c r="F164" s="4" t="inlineStr">
+        <is>
+          <t>364.95</t>
+        </is>
+      </c>
+      <c r="G164" s="4" t="inlineStr"/>
+      <c r="H164" s="4" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="I164" s="4" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="J164" s="4" t="inlineStr"/>
+      <c r="K164" s="4" t="inlineStr"/>
+      <c r="L164" s="4" t="inlineStr"/>
+      <c r="M164" s="4" t="inlineStr"/>
+      <c r="N164" s="4" t="inlineStr"/>
+      <c r="O164" s="4" t="inlineStr"/>
+      <c r="P164" s="4" t="inlineStr">
+        <is>
+          <t>High Strike Check | No signal | No signal</t>
+        </is>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" s="4" t="inlineStr">
+        <is>
+          <t>2026-03-25 09:35:00</t>
+        </is>
+      </c>
+      <c r="B165" s="4" t="inlineStr">
+        <is>
+          <t>09:35:00</t>
+        </is>
+      </c>
+      <c r="C165" s="4" t="inlineStr">
+        <is>
+          <t>09:35</t>
+        </is>
+      </c>
+      <c r="D165" s="4" t="inlineStr">
+        <is>
+          <t>368.75</t>
+        </is>
+      </c>
+      <c r="E165" s="4" t="inlineStr"/>
+      <c r="F165" s="4" t="inlineStr">
+        <is>
+          <t>331.00</t>
+        </is>
+      </c>
+      <c r="G165" s="4" t="inlineStr"/>
+      <c r="H165" s="4" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="I165" s="4" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="J165" s="4" t="inlineStr"/>
+      <c r="K165" s="4" t="inlineStr"/>
+      <c r="L165" s="4" t="inlineStr"/>
+      <c r="M165" s="4" t="inlineStr"/>
+      <c r="N165" s="4" t="inlineStr"/>
+      <c r="O165" s="4" t="inlineStr"/>
+      <c r="P165" s="4" t="inlineStr">
+        <is>
+          <t>Low Strike Check | No signal | No signal</t>
+        </is>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" s="4" t="inlineStr">
+        <is>
+          <t>2026-03-25 09:40:00</t>
+        </is>
+      </c>
+      <c r="B166" s="4" t="inlineStr">
+        <is>
+          <t>09:40:00</t>
+        </is>
+      </c>
+      <c r="C166" s="4" t="inlineStr">
+        <is>
+          <t>09:40</t>
+        </is>
+      </c>
+      <c r="D166" s="4" t="inlineStr">
+        <is>
+          <t>310.00</t>
+        </is>
+      </c>
+      <c r="E166" s="4" t="inlineStr"/>
+      <c r="F166" s="4" t="inlineStr">
+        <is>
+          <t>364.95</t>
+        </is>
+      </c>
+      <c r="G166" s="4" t="inlineStr"/>
+      <c r="H166" s="4" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="I166" s="4" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="J166" s="4" t="inlineStr"/>
+      <c r="K166" s="4" t="inlineStr"/>
+      <c r="L166" s="4" t="inlineStr"/>
+      <c r="M166" s="4" t="inlineStr"/>
+      <c r="N166" s="4" t="inlineStr"/>
+      <c r="O166" s="4" t="inlineStr"/>
+      <c r="P166" s="4" t="inlineStr">
+        <is>
+          <t>High Strike Check | No signal | No signal</t>
+        </is>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" s="4" t="inlineStr">
+        <is>
+          <t>2026-03-25 09:40:00</t>
+        </is>
+      </c>
+      <c r="B167" s="4" t="inlineStr">
+        <is>
+          <t>09:40:00</t>
+        </is>
+      </c>
+      <c r="C167" s="4" t="inlineStr">
+        <is>
+          <t>09:40</t>
+        </is>
+      </c>
+      <c r="D167" s="4" t="inlineStr">
+        <is>
+          <t>368.75</t>
+        </is>
+      </c>
+      <c r="E167" s="4" t="inlineStr"/>
+      <c r="F167" s="4" t="inlineStr">
+        <is>
+          <t>331.00</t>
+        </is>
+      </c>
+      <c r="G167" s="4" t="inlineStr"/>
+      <c r="H167" s="4" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="I167" s="4" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="J167" s="4" t="inlineStr"/>
+      <c r="K167" s="4" t="inlineStr"/>
+      <c r="L167" s="4" t="inlineStr"/>
+      <c r="M167" s="4" t="inlineStr"/>
+      <c r="N167" s="4" t="inlineStr"/>
+      <c r="O167" s="4" t="inlineStr"/>
+      <c r="P167" s="4" t="inlineStr">
+        <is>
+          <t>Low Strike Check | No signal | No signal</t>
+        </is>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" s="4" t="inlineStr">
+        <is>
+          <t>2026-03-26 09:25:00</t>
+        </is>
+      </c>
+      <c r="B168" s="4" t="inlineStr">
+        <is>
+          <t>09:25:00</t>
+        </is>
+      </c>
+      <c r="C168" s="4" t="inlineStr">
+        <is>
+          <t>09:25</t>
+        </is>
+      </c>
+      <c r="D168" s="4" t="inlineStr">
+        <is>
+          <t>310.00</t>
+        </is>
+      </c>
+      <c r="E168" s="4" t="inlineStr"/>
+      <c r="F168" s="4" t="inlineStr">
+        <is>
+          <t>364.95</t>
+        </is>
+      </c>
+      <c r="G168" s="4" t="inlineStr"/>
+      <c r="H168" s="4" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="I168" s="4" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="J168" s="4" t="inlineStr"/>
+      <c r="K168" s="4" t="inlineStr"/>
+      <c r="L168" s="4" t="inlineStr"/>
+      <c r="M168" s="4" t="inlineStr"/>
+      <c r="N168" s="4" t="inlineStr"/>
+      <c r="O168" s="4" t="inlineStr"/>
+      <c r="P168" s="4" t="inlineStr">
+        <is>
+          <t>High Strike Check | No signal | No signal</t>
+        </is>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" s="4" t="inlineStr">
+        <is>
+          <t>2026-03-26 09:25:00</t>
+        </is>
+      </c>
+      <c r="B169" s="4" t="inlineStr">
+        <is>
+          <t>09:25:00</t>
+        </is>
+      </c>
+      <c r="C169" s="4" t="inlineStr">
+        <is>
+          <t>09:25</t>
+        </is>
+      </c>
+      <c r="D169" s="4" t="inlineStr">
+        <is>
+          <t>368.75</t>
+        </is>
+      </c>
+      <c r="E169" s="4" t="inlineStr"/>
+      <c r="F169" s="4" t="inlineStr">
+        <is>
+          <t>331.00</t>
+        </is>
+      </c>
+      <c r="G169" s="4" t="inlineStr"/>
+      <c r="H169" s="4" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="I169" s="4" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="J169" s="4" t="inlineStr"/>
+      <c r="K169" s="4" t="inlineStr"/>
+      <c r="L169" s="4" t="inlineStr"/>
+      <c r="M169" s="4" t="inlineStr"/>
+      <c r="N169" s="4" t="inlineStr"/>
+      <c r="O169" s="4" t="inlineStr"/>
+      <c r="P169" s="4" t="inlineStr">
+        <is>
+          <t>Low Strike Check | No signal | No signal</t>
+        </is>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" s="4" t="inlineStr">
+        <is>
+          <t>2026-03-26 09:30:00</t>
+        </is>
+      </c>
+      <c r="B170" s="4" t="inlineStr">
+        <is>
+          <t>09:30:00</t>
+        </is>
+      </c>
+      <c r="C170" s="4" t="inlineStr">
+        <is>
+          <t>09:30</t>
+        </is>
+      </c>
+      <c r="D170" s="4" t="inlineStr">
+        <is>
+          <t>310.00</t>
+        </is>
+      </c>
+      <c r="E170" s="4" t="inlineStr"/>
+      <c r="F170" s="4" t="inlineStr">
+        <is>
+          <t>364.95</t>
+        </is>
+      </c>
+      <c r="G170" s="4" t="inlineStr"/>
+      <c r="H170" s="4" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="I170" s="4" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="J170" s="4" t="inlineStr"/>
+      <c r="K170" s="4" t="inlineStr"/>
+      <c r="L170" s="4" t="inlineStr"/>
+      <c r="M170" s="4" t="inlineStr"/>
+      <c r="N170" s="4" t="inlineStr"/>
+      <c r="O170" s="4" t="inlineStr"/>
+      <c r="P170" s="4" t="inlineStr">
+        <is>
+          <t>High Strike Check | No signal | No signal</t>
+        </is>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" s="4" t="inlineStr">
+        <is>
+          <t>2026-03-26 09:30:00</t>
+        </is>
+      </c>
+      <c r="B171" s="4" t="inlineStr">
+        <is>
+          <t>09:30:00</t>
+        </is>
+      </c>
+      <c r="C171" s="4" t="inlineStr">
+        <is>
+          <t>09:30</t>
+        </is>
+      </c>
+      <c r="D171" s="4" t="inlineStr">
+        <is>
+          <t>368.75</t>
+        </is>
+      </c>
+      <c r="E171" s="4" t="inlineStr"/>
+      <c r="F171" s="4" t="inlineStr">
+        <is>
+          <t>331.00</t>
+        </is>
+      </c>
+      <c r="G171" s="4" t="inlineStr"/>
+      <c r="H171" s="4" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="I171" s="4" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="J171" s="4" t="inlineStr"/>
+      <c r="K171" s="4" t="inlineStr"/>
+      <c r="L171" s="4" t="inlineStr"/>
+      <c r="M171" s="4" t="inlineStr"/>
+      <c r="N171" s="4" t="inlineStr"/>
+      <c r="O171" s="4" t="inlineStr"/>
+      <c r="P171" s="4" t="inlineStr">
+        <is>
+          <t>Low Strike Check | No signal | No signal</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1808,7 +9147,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L1"/>
+  <dimension ref="A1:L9"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -1883,6 +9222,358 @@
         </is>
       </c>
     </row>
+    <row r="2">
+      <c r="A2" s="4" t="inlineStr">
+        <is>
+          <t>2026-03-24 12:00:23</t>
+        </is>
+      </c>
+      <c r="B2" s="4" t="inlineStr">
+        <is>
+          <t>BUY PE</t>
+        </is>
+      </c>
+      <c r="C2" s="4" t="inlineStr">
+        <is>
+          <t>PE</t>
+        </is>
+      </c>
+      <c r="D2" s="4" t="n">
+        <v>22900</v>
+      </c>
+      <c r="E2" s="4" t="inlineStr">
+        <is>
+          <t>129.70</t>
+        </is>
+      </c>
+      <c r="F2" s="4" t="inlineStr">
+        <is>
+          <t>129.70</t>
+        </is>
+      </c>
+      <c r="G2" s="4" t="inlineStr"/>
+      <c r="H2" s="4" t="inlineStr"/>
+      <c r="I2" s="4" t="inlineStr"/>
+      <c r="J2" s="5" t="inlineStr">
+        <is>
+          <t>BUY PE</t>
+        </is>
+      </c>
+      <c r="K2" s="4" t="inlineStr">
+        <is>
+          <t>2036329758870396930</t>
+        </is>
+      </c>
+      <c r="L2" s="4" t="inlineStr">
+        <is>
+          <t>Mode: LIVE | Details: Order placed successfully via KiteService | Order_type: MARKET</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="4" t="inlineStr">
+        <is>
+          <t>2026-03-24 12:00:23</t>
+        </is>
+      </c>
+      <c r="B3" s="4" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t>PE</t>
+        </is>
+      </c>
+      <c r="D3" s="4" t="n">
+        <v>22900</v>
+      </c>
+      <c r="E3" s="4" t="inlineStr">
+        <is>
+          <t>0.00</t>
+        </is>
+      </c>
+      <c r="F3" s="4" t="inlineStr"/>
+      <c r="G3" s="4" t="inlineStr"/>
+      <c r="H3" s="4" t="inlineStr"/>
+      <c r="I3" s="4" t="inlineStr"/>
+      <c r="J3" s="6" t="inlineStr">
+        <is>
+          <t>FAILED</t>
+        </is>
+      </c>
+      <c r="K3" s="4" t="inlineStr"/>
+      <c r="L3" s="4" t="inlineStr">
+        <is>
+          <t>[ZERODHA_5] BUY Order Failed: Incorrect `api_key` or `access_token`.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="4" t="inlineStr">
+        <is>
+          <t>2026-03-24 12:00:23</t>
+        </is>
+      </c>
+      <c r="B4" s="4" t="inlineStr">
+        <is>
+          <t>SL_ORDER</t>
+        </is>
+      </c>
+      <c r="C4" s="4" t="inlineStr">
+        <is>
+          <t>PE</t>
+        </is>
+      </c>
+      <c r="D4" s="4" t="n">
+        <v>22900</v>
+      </c>
+      <c r="E4" s="4" t="inlineStr">
+        <is>
+          <t>108.95</t>
+        </is>
+      </c>
+      <c r="F4" s="4" t="inlineStr"/>
+      <c r="G4" s="4" t="inlineStr"/>
+      <c r="H4" s="4" t="inlineStr">
+        <is>
+          <t>108.95</t>
+        </is>
+      </c>
+      <c r="I4" s="4" t="inlineStr"/>
+      <c r="J4" s="6" t="inlineStr">
+        <is>
+          <t>FAILED</t>
+        </is>
+      </c>
+      <c r="K4" s="4" t="inlineStr"/>
+      <c r="L4" s="4" t="inlineStr">
+        <is>
+          <t>[ZERODHA_5] SL Order Failed: Incorrect `api_key` or `access_token`.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="4" t="inlineStr">
+        <is>
+          <t>2026-03-24 12:00:24</t>
+        </is>
+      </c>
+      <c r="B5" s="4" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="C5" s="4" t="inlineStr">
+        <is>
+          <t>PE</t>
+        </is>
+      </c>
+      <c r="D5" s="4" t="n">
+        <v>22900</v>
+      </c>
+      <c r="E5" s="4" t="inlineStr">
+        <is>
+          <t>0.00</t>
+        </is>
+      </c>
+      <c r="F5" s="4" t="inlineStr"/>
+      <c r="G5" s="4" t="inlineStr"/>
+      <c r="H5" s="4" t="inlineStr"/>
+      <c r="I5" s="4" t="inlineStr"/>
+      <c r="J5" s="6" t="inlineStr">
+        <is>
+          <t>FAILED</t>
+        </is>
+      </c>
+      <c r="K5" s="4" t="inlineStr"/>
+      <c r="L5" s="4" t="inlineStr">
+        <is>
+          <t>[KOTAK] BUY Order Failed: invalid session token</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="4" t="inlineStr">
+        <is>
+          <t>2026-03-24 12:00:26</t>
+        </is>
+      </c>
+      <c r="B6" s="4" t="inlineStr">
+        <is>
+          <t>SL_ORDER</t>
+        </is>
+      </c>
+      <c r="C6" s="4" t="inlineStr">
+        <is>
+          <t>PE</t>
+        </is>
+      </c>
+      <c r="D6" s="4" t="n">
+        <v>22900</v>
+      </c>
+      <c r="E6" s="4" t="inlineStr">
+        <is>
+          <t>108.95</t>
+        </is>
+      </c>
+      <c r="F6" s="4" t="inlineStr"/>
+      <c r="G6" s="4" t="inlineStr"/>
+      <c r="H6" s="4" t="inlineStr">
+        <is>
+          <t>108.95</t>
+        </is>
+      </c>
+      <c r="I6" s="4" t="inlineStr"/>
+      <c r="J6" s="6" t="inlineStr">
+        <is>
+          <t>FAILED</t>
+        </is>
+      </c>
+      <c r="K6" s="4" t="inlineStr"/>
+      <c r="L6" s="4" t="inlineStr">
+        <is>
+          <t>[KOTAK] SL Order Failed: invalid session token</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="4" t="inlineStr">
+        <is>
+          <t>2026-03-24 12:00:43</t>
+        </is>
+      </c>
+      <c r="B7" s="4" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="C7" s="4" t="inlineStr">
+        <is>
+          <t>PE</t>
+        </is>
+      </c>
+      <c r="D7" s="4" t="n">
+        <v>22900</v>
+      </c>
+      <c r="E7" s="4" t="inlineStr">
+        <is>
+          <t>0.00</t>
+        </is>
+      </c>
+      <c r="F7" s="4" t="inlineStr"/>
+      <c r="G7" s="4" t="inlineStr"/>
+      <c r="H7" s="4" t="inlineStr"/>
+      <c r="I7" s="4" t="inlineStr"/>
+      <c r="J7" s="6" t="inlineStr">
+        <is>
+          <t>FAILED</t>
+        </is>
+      </c>
+      <c r="K7" s="4" t="inlineStr"/>
+      <c r="L7" s="4" t="inlineStr">
+        <is>
+          <t>[DHAN] BUY Order Failed: Missing required fields, bad values for parameters etc.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="4" t="inlineStr">
+        <is>
+          <t>2026-03-24 12:00:47</t>
+        </is>
+      </c>
+      <c r="B8" s="4" t="inlineStr">
+        <is>
+          <t>SL_ORDER</t>
+        </is>
+      </c>
+      <c r="C8" s="4" t="inlineStr">
+        <is>
+          <t>PE</t>
+        </is>
+      </c>
+      <c r="D8" s="4" t="n">
+        <v>22900</v>
+      </c>
+      <c r="E8" s="4" t="inlineStr">
+        <is>
+          <t>108.95</t>
+        </is>
+      </c>
+      <c r="F8" s="4" t="inlineStr"/>
+      <c r="G8" s="4" t="inlineStr"/>
+      <c r="H8" s="4" t="inlineStr">
+        <is>
+          <t>108.95</t>
+        </is>
+      </c>
+      <c r="I8" s="4" t="inlineStr"/>
+      <c r="J8" s="6" t="inlineStr">
+        <is>
+          <t>FAILED</t>
+        </is>
+      </c>
+      <c r="K8" s="4" t="inlineStr"/>
+      <c r="L8" s="4" t="inlineStr">
+        <is>
+          <t>[DHAN] SL Order Failed: Missing required fields, bad values for parameters etc.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="4" t="inlineStr">
+        <is>
+          <t>2026-03-24 12:00:47</t>
+        </is>
+      </c>
+      <c r="B9" s="4" t="inlineStr">
+        <is>
+          <t>SL_ORDER</t>
+        </is>
+      </c>
+      <c r="C9" s="4" t="inlineStr">
+        <is>
+          <t>PE</t>
+        </is>
+      </c>
+      <c r="D9" s="4" t="n">
+        <v>22900</v>
+      </c>
+      <c r="E9" s="4" t="inlineStr">
+        <is>
+          <t>108.95</t>
+        </is>
+      </c>
+      <c r="F9" s="4" t="inlineStr"/>
+      <c r="G9" s="4" t="inlineStr">
+        <is>
+          <t>171.20</t>
+        </is>
+      </c>
+      <c r="H9" s="4" t="inlineStr">
+        <is>
+          <t>108.95</t>
+        </is>
+      </c>
+      <c r="I9" s="4" t="inlineStr"/>
+      <c r="J9" s="6" t="inlineStr">
+        <is>
+          <t>PLACED</t>
+        </is>
+      </c>
+      <c r="K9" s="4" t="inlineStr">
+        <is>
+          <t>2036329763043729408</t>
+        </is>
+      </c>
+      <c r="L9" s="4" t="inlineStr">
+        <is>
+          <t>SL Order Placed | Trigger: 108.95</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" paperSize="9" horizontalDpi="0" verticalDpi="0"/>

--- a/Mine/logs/mine_signal_logs.xlsx
+++ b/Mine/logs/mine_signal_logs.xlsx
@@ -529,7 +529,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P171"/>
+  <dimension ref="A1:P225"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -9136,6 +9136,2742 @@
         </is>
       </c>
     </row>
+    <row r="172">
+      <c r="A172" s="4" t="inlineStr">
+        <is>
+          <t>2026-03-27 09:20:00</t>
+        </is>
+      </c>
+      <c r="B172" s="4" t="inlineStr">
+        <is>
+          <t>09:20:00</t>
+        </is>
+      </c>
+      <c r="C172" s="4" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="D172" s="4" t="inlineStr">
+        <is>
+          <t>283.05</t>
+        </is>
+      </c>
+      <c r="E172" s="4" t="inlineStr"/>
+      <c r="F172" s="4" t="inlineStr">
+        <is>
+          <t>323.60</t>
+        </is>
+      </c>
+      <c r="G172" s="4" t="inlineStr"/>
+      <c r="H172" s="4" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="I172" s="4" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="J172" s="4" t="inlineStr"/>
+      <c r="K172" s="4" t="inlineStr"/>
+      <c r="L172" s="4" t="inlineStr"/>
+      <c r="M172" s="4" t="inlineStr"/>
+      <c r="N172" s="4" t="inlineStr"/>
+      <c r="O172" s="4" t="inlineStr"/>
+      <c r="P172" s="4" t="inlineStr">
+        <is>
+          <t>High Strike Check | No signal | No signal</t>
+        </is>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" s="4" t="inlineStr">
+        <is>
+          <t>2026-03-27 09:20:00</t>
+        </is>
+      </c>
+      <c r="B173" s="4" t="inlineStr">
+        <is>
+          <t>09:20:00</t>
+        </is>
+      </c>
+      <c r="C173" s="4" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="D173" s="4" t="inlineStr">
+        <is>
+          <t>355.90</t>
+        </is>
+      </c>
+      <c r="E173" s="4" t="inlineStr"/>
+      <c r="F173" s="4" t="inlineStr">
+        <is>
+          <t>249.95</t>
+        </is>
+      </c>
+      <c r="G173" s="4" t="inlineStr"/>
+      <c r="H173" s="4" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="I173" s="4" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="J173" s="4" t="inlineStr"/>
+      <c r="K173" s="4" t="inlineStr"/>
+      <c r="L173" s="4" t="inlineStr"/>
+      <c r="M173" s="4" t="inlineStr"/>
+      <c r="N173" s="4" t="inlineStr"/>
+      <c r="O173" s="4" t="inlineStr"/>
+      <c r="P173" s="4" t="inlineStr">
+        <is>
+          <t>Low Strike Check | No signal | No signal</t>
+        </is>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" s="4" t="inlineStr">
+        <is>
+          <t>2026-03-27 09:25:00</t>
+        </is>
+      </c>
+      <c r="B174" s="4" t="inlineStr">
+        <is>
+          <t>09:25:00</t>
+        </is>
+      </c>
+      <c r="C174" s="4" t="inlineStr">
+        <is>
+          <t>09:25</t>
+        </is>
+      </c>
+      <c r="D174" s="4" t="inlineStr">
+        <is>
+          <t>283.05</t>
+        </is>
+      </c>
+      <c r="E174" s="4" t="inlineStr"/>
+      <c r="F174" s="4" t="inlineStr">
+        <is>
+          <t>323.60</t>
+        </is>
+      </c>
+      <c r="G174" s="4" t="inlineStr"/>
+      <c r="H174" s="4" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="I174" s="4" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="J174" s="4" t="inlineStr"/>
+      <c r="K174" s="4" t="inlineStr"/>
+      <c r="L174" s="4" t="inlineStr"/>
+      <c r="M174" s="4" t="inlineStr"/>
+      <c r="N174" s="4" t="inlineStr"/>
+      <c r="O174" s="4" t="inlineStr"/>
+      <c r="P174" s="4" t="inlineStr">
+        <is>
+          <t>High Strike Check | No signal | No signal</t>
+        </is>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" s="4" t="inlineStr">
+        <is>
+          <t>2026-03-27 09:25:00</t>
+        </is>
+      </c>
+      <c r="B175" s="4" t="inlineStr">
+        <is>
+          <t>09:25:00</t>
+        </is>
+      </c>
+      <c r="C175" s="4" t="inlineStr">
+        <is>
+          <t>09:25</t>
+        </is>
+      </c>
+      <c r="D175" s="4" t="inlineStr">
+        <is>
+          <t>355.90</t>
+        </is>
+      </c>
+      <c r="E175" s="4" t="inlineStr"/>
+      <c r="F175" s="4" t="inlineStr">
+        <is>
+          <t>249.95</t>
+        </is>
+      </c>
+      <c r="G175" s="4" t="inlineStr"/>
+      <c r="H175" s="4" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="I175" s="4" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="J175" s="4" t="inlineStr"/>
+      <c r="K175" s="4" t="inlineStr"/>
+      <c r="L175" s="4" t="inlineStr"/>
+      <c r="M175" s="4" t="inlineStr"/>
+      <c r="N175" s="4" t="inlineStr"/>
+      <c r="O175" s="4" t="inlineStr"/>
+      <c r="P175" s="4" t="inlineStr">
+        <is>
+          <t>Low Strike Check | No signal | No signal</t>
+        </is>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" s="4" t="inlineStr">
+        <is>
+          <t>2026-03-27 09:30:00</t>
+        </is>
+      </c>
+      <c r="B176" s="4" t="inlineStr">
+        <is>
+          <t>09:30:00</t>
+        </is>
+      </c>
+      <c r="C176" s="4" t="inlineStr">
+        <is>
+          <t>09:30</t>
+        </is>
+      </c>
+      <c r="D176" s="4" t="inlineStr">
+        <is>
+          <t>283.05</t>
+        </is>
+      </c>
+      <c r="E176" s="4" t="inlineStr"/>
+      <c r="F176" s="4" t="inlineStr">
+        <is>
+          <t>323.60</t>
+        </is>
+      </c>
+      <c r="G176" s="4" t="inlineStr"/>
+      <c r="H176" s="4" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="I176" s="4" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="J176" s="4" t="inlineStr"/>
+      <c r="K176" s="4" t="inlineStr"/>
+      <c r="L176" s="4" t="inlineStr"/>
+      <c r="M176" s="4" t="inlineStr"/>
+      <c r="N176" s="4" t="inlineStr"/>
+      <c r="O176" s="4" t="inlineStr"/>
+      <c r="P176" s="4" t="inlineStr">
+        <is>
+          <t>High Strike Check | No signal | No signal</t>
+        </is>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" s="4" t="inlineStr">
+        <is>
+          <t>2026-03-27 09:30:00</t>
+        </is>
+      </c>
+      <c r="B177" s="4" t="inlineStr">
+        <is>
+          <t>09:30:00</t>
+        </is>
+      </c>
+      <c r="C177" s="4" t="inlineStr">
+        <is>
+          <t>09:30</t>
+        </is>
+      </c>
+      <c r="D177" s="4" t="inlineStr">
+        <is>
+          <t>355.90</t>
+        </is>
+      </c>
+      <c r="E177" s="4" t="inlineStr"/>
+      <c r="F177" s="4" t="inlineStr">
+        <is>
+          <t>249.95</t>
+        </is>
+      </c>
+      <c r="G177" s="4" t="inlineStr"/>
+      <c r="H177" s="4" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="I177" s="4" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="J177" s="4" t="inlineStr"/>
+      <c r="K177" s="4" t="inlineStr"/>
+      <c r="L177" s="4" t="inlineStr"/>
+      <c r="M177" s="4" t="inlineStr"/>
+      <c r="N177" s="4" t="inlineStr"/>
+      <c r="O177" s="4" t="inlineStr"/>
+      <c r="P177" s="4" t="inlineStr">
+        <is>
+          <t>Low Strike Check | No signal | No signal</t>
+        </is>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" s="4" t="inlineStr">
+        <is>
+          <t>2026-03-27 09:35:00</t>
+        </is>
+      </c>
+      <c r="B178" s="4" t="inlineStr">
+        <is>
+          <t>09:35:00</t>
+        </is>
+      </c>
+      <c r="C178" s="4" t="inlineStr">
+        <is>
+          <t>09:35</t>
+        </is>
+      </c>
+      <c r="D178" s="4" t="inlineStr">
+        <is>
+          <t>283.05</t>
+        </is>
+      </c>
+      <c r="E178" s="4" t="inlineStr"/>
+      <c r="F178" s="4" t="inlineStr">
+        <is>
+          <t>323.60</t>
+        </is>
+      </c>
+      <c r="G178" s="4" t="inlineStr"/>
+      <c r="H178" s="4" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="I178" s="4" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="J178" s="4" t="inlineStr"/>
+      <c r="K178" s="4" t="inlineStr"/>
+      <c r="L178" s="4" t="inlineStr"/>
+      <c r="M178" s="4" t="inlineStr"/>
+      <c r="N178" s="4" t="inlineStr"/>
+      <c r="O178" s="4" t="inlineStr"/>
+      <c r="P178" s="4" t="inlineStr">
+        <is>
+          <t>High Strike Check | No signal | No signal</t>
+        </is>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" s="4" t="inlineStr">
+        <is>
+          <t>2026-03-27 09:35:00</t>
+        </is>
+      </c>
+      <c r="B179" s="4" t="inlineStr">
+        <is>
+          <t>09:35:00</t>
+        </is>
+      </c>
+      <c r="C179" s="4" t="inlineStr">
+        <is>
+          <t>09:35</t>
+        </is>
+      </c>
+      <c r="D179" s="4" t="inlineStr">
+        <is>
+          <t>355.90</t>
+        </is>
+      </c>
+      <c r="E179" s="4" t="inlineStr"/>
+      <c r="F179" s="4" t="inlineStr">
+        <is>
+          <t>249.95</t>
+        </is>
+      </c>
+      <c r="G179" s="4" t="inlineStr"/>
+      <c r="H179" s="4" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="I179" s="4" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="J179" s="4" t="inlineStr"/>
+      <c r="K179" s="4" t="inlineStr"/>
+      <c r="L179" s="4" t="inlineStr"/>
+      <c r="M179" s="4" t="inlineStr"/>
+      <c r="N179" s="4" t="inlineStr"/>
+      <c r="O179" s="4" t="inlineStr"/>
+      <c r="P179" s="4" t="inlineStr">
+        <is>
+          <t>Low Strike Check | No signal | No signal</t>
+        </is>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" s="4" t="inlineStr">
+        <is>
+          <t>2026-03-27 09:40:00</t>
+        </is>
+      </c>
+      <c r="B180" s="4" t="inlineStr">
+        <is>
+          <t>09:40:00</t>
+        </is>
+      </c>
+      <c r="C180" s="4" t="inlineStr">
+        <is>
+          <t>09:40</t>
+        </is>
+      </c>
+      <c r="D180" s="4" t="inlineStr">
+        <is>
+          <t>283.05</t>
+        </is>
+      </c>
+      <c r="E180" s="4" t="inlineStr"/>
+      <c r="F180" s="4" t="inlineStr">
+        <is>
+          <t>323.60</t>
+        </is>
+      </c>
+      <c r="G180" s="4" t="inlineStr"/>
+      <c r="H180" s="4" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="I180" s="4" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="J180" s="4" t="inlineStr"/>
+      <c r="K180" s="4" t="inlineStr"/>
+      <c r="L180" s="4" t="inlineStr"/>
+      <c r="M180" s="4" t="inlineStr"/>
+      <c r="N180" s="4" t="inlineStr"/>
+      <c r="O180" s="4" t="inlineStr"/>
+      <c r="P180" s="4" t="inlineStr">
+        <is>
+          <t>High Strike Check | No signal | No signal</t>
+        </is>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" s="4" t="inlineStr">
+        <is>
+          <t>2026-03-27 09:40:00</t>
+        </is>
+      </c>
+      <c r="B181" s="4" t="inlineStr">
+        <is>
+          <t>09:40:00</t>
+        </is>
+      </c>
+      <c r="C181" s="4" t="inlineStr">
+        <is>
+          <t>09:40</t>
+        </is>
+      </c>
+      <c r="D181" s="4" t="inlineStr">
+        <is>
+          <t>355.90</t>
+        </is>
+      </c>
+      <c r="E181" s="4" t="inlineStr"/>
+      <c r="F181" s="4" t="inlineStr">
+        <is>
+          <t>249.95</t>
+        </is>
+      </c>
+      <c r="G181" s="4" t="inlineStr"/>
+      <c r="H181" s="4" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="I181" s="4" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="J181" s="4" t="inlineStr"/>
+      <c r="K181" s="4" t="inlineStr"/>
+      <c r="L181" s="4" t="inlineStr"/>
+      <c r="M181" s="4" t="inlineStr"/>
+      <c r="N181" s="4" t="inlineStr"/>
+      <c r="O181" s="4" t="inlineStr"/>
+      <c r="P181" s="4" t="inlineStr">
+        <is>
+          <t>Low Strike Check | No signal | No signal</t>
+        </is>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" s="4" t="inlineStr">
+        <is>
+          <t>2026-03-27 09:45:00</t>
+        </is>
+      </c>
+      <c r="B182" s="4" t="inlineStr">
+        <is>
+          <t>09:45:00</t>
+        </is>
+      </c>
+      <c r="C182" s="4" t="inlineStr">
+        <is>
+          <t>09:45</t>
+        </is>
+      </c>
+      <c r="D182" s="4" t="inlineStr">
+        <is>
+          <t>283.05</t>
+        </is>
+      </c>
+      <c r="E182" s="4" t="inlineStr"/>
+      <c r="F182" s="4" t="inlineStr">
+        <is>
+          <t>323.60</t>
+        </is>
+      </c>
+      <c r="G182" s="4" t="inlineStr"/>
+      <c r="H182" s="4" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="I182" s="4" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="J182" s="4" t="inlineStr"/>
+      <c r="K182" s="4" t="inlineStr"/>
+      <c r="L182" s="4" t="inlineStr"/>
+      <c r="M182" s="4" t="inlineStr"/>
+      <c r="N182" s="4" t="inlineStr"/>
+      <c r="O182" s="4" t="inlineStr"/>
+      <c r="P182" s="4" t="inlineStr">
+        <is>
+          <t>High Strike Check | No signal | No signal</t>
+        </is>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" s="4" t="inlineStr">
+        <is>
+          <t>2026-03-27 09:45:00</t>
+        </is>
+      </c>
+      <c r="B183" s="4" t="inlineStr">
+        <is>
+          <t>09:45:00</t>
+        </is>
+      </c>
+      <c r="C183" s="4" t="inlineStr">
+        <is>
+          <t>09:45</t>
+        </is>
+      </c>
+      <c r="D183" s="4" t="inlineStr">
+        <is>
+          <t>355.90</t>
+        </is>
+      </c>
+      <c r="E183" s="4" t="inlineStr"/>
+      <c r="F183" s="4" t="inlineStr">
+        <is>
+          <t>249.95</t>
+        </is>
+      </c>
+      <c r="G183" s="4" t="inlineStr"/>
+      <c r="H183" s="4" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="I183" s="4" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="J183" s="4" t="inlineStr"/>
+      <c r="K183" s="4" t="inlineStr"/>
+      <c r="L183" s="4" t="inlineStr"/>
+      <c r="M183" s="4" t="inlineStr"/>
+      <c r="N183" s="4" t="inlineStr"/>
+      <c r="O183" s="4" t="inlineStr"/>
+      <c r="P183" s="4" t="inlineStr">
+        <is>
+          <t>Low Strike Check | No signal | No signal</t>
+        </is>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" s="4" t="inlineStr">
+        <is>
+          <t>2026-03-27 09:50:00</t>
+        </is>
+      </c>
+      <c r="B184" s="4" t="inlineStr">
+        <is>
+          <t>09:50:00</t>
+        </is>
+      </c>
+      <c r="C184" s="4" t="inlineStr">
+        <is>
+          <t>09:50</t>
+        </is>
+      </c>
+      <c r="D184" s="4" t="inlineStr">
+        <is>
+          <t>283.05</t>
+        </is>
+      </c>
+      <c r="E184" s="4" t="inlineStr"/>
+      <c r="F184" s="4" t="inlineStr">
+        <is>
+          <t>323.60</t>
+        </is>
+      </c>
+      <c r="G184" s="4" t="inlineStr"/>
+      <c r="H184" s="4" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="I184" s="4" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="J184" s="4" t="inlineStr"/>
+      <c r="K184" s="4" t="inlineStr"/>
+      <c r="L184" s="4" t="inlineStr"/>
+      <c r="M184" s="4" t="inlineStr"/>
+      <c r="N184" s="4" t="inlineStr"/>
+      <c r="O184" s="4" t="inlineStr"/>
+      <c r="P184" s="4" t="inlineStr">
+        <is>
+          <t>High Strike Check | No signal | No signal</t>
+        </is>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" s="4" t="inlineStr">
+        <is>
+          <t>2026-03-27 09:50:00</t>
+        </is>
+      </c>
+      <c r="B185" s="4" t="inlineStr">
+        <is>
+          <t>09:50:00</t>
+        </is>
+      </c>
+      <c r="C185" s="4" t="inlineStr">
+        <is>
+          <t>09:50</t>
+        </is>
+      </c>
+      <c r="D185" s="4" t="inlineStr">
+        <is>
+          <t>355.90</t>
+        </is>
+      </c>
+      <c r="E185" s="4" t="inlineStr"/>
+      <c r="F185" s="4" t="inlineStr">
+        <is>
+          <t>249.95</t>
+        </is>
+      </c>
+      <c r="G185" s="4" t="inlineStr"/>
+      <c r="H185" s="4" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="I185" s="4" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="J185" s="4" t="inlineStr"/>
+      <c r="K185" s="4" t="inlineStr"/>
+      <c r="L185" s="4" t="inlineStr"/>
+      <c r="M185" s="4" t="inlineStr"/>
+      <c r="N185" s="4" t="inlineStr"/>
+      <c r="O185" s="4" t="inlineStr"/>
+      <c r="P185" s="4" t="inlineStr">
+        <is>
+          <t>Low Strike Check | No signal | No signal</t>
+        </is>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" s="4" t="inlineStr">
+        <is>
+          <t>2026-03-27 09:55:00</t>
+        </is>
+      </c>
+      <c r="B186" s="4" t="inlineStr">
+        <is>
+          <t>09:55:00</t>
+        </is>
+      </c>
+      <c r="C186" s="4" t="inlineStr">
+        <is>
+          <t>09:55</t>
+        </is>
+      </c>
+      <c r="D186" s="4" t="inlineStr">
+        <is>
+          <t>283.05</t>
+        </is>
+      </c>
+      <c r="E186" s="4" t="inlineStr"/>
+      <c r="F186" s="4" t="inlineStr">
+        <is>
+          <t>323.60</t>
+        </is>
+      </c>
+      <c r="G186" s="4" t="inlineStr"/>
+      <c r="H186" s="4" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="I186" s="4" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="J186" s="4" t="inlineStr"/>
+      <c r="K186" s="4" t="inlineStr"/>
+      <c r="L186" s="4" t="inlineStr"/>
+      <c r="M186" s="4" t="inlineStr"/>
+      <c r="N186" s="4" t="inlineStr"/>
+      <c r="O186" s="4" t="inlineStr"/>
+      <c r="P186" s="4" t="inlineStr">
+        <is>
+          <t>High Strike Check | No signal | No signal</t>
+        </is>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" s="4" t="inlineStr">
+        <is>
+          <t>2026-03-27 09:55:00</t>
+        </is>
+      </c>
+      <c r="B187" s="4" t="inlineStr">
+        <is>
+          <t>09:55:00</t>
+        </is>
+      </c>
+      <c r="C187" s="4" t="inlineStr">
+        <is>
+          <t>09:55</t>
+        </is>
+      </c>
+      <c r="D187" s="4" t="inlineStr">
+        <is>
+          <t>355.90</t>
+        </is>
+      </c>
+      <c r="E187" s="4" t="inlineStr"/>
+      <c r="F187" s="4" t="inlineStr">
+        <is>
+          <t>249.95</t>
+        </is>
+      </c>
+      <c r="G187" s="4" t="inlineStr"/>
+      <c r="H187" s="4" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="I187" s="4" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="J187" s="4" t="inlineStr"/>
+      <c r="K187" s="4" t="inlineStr"/>
+      <c r="L187" s="4" t="inlineStr"/>
+      <c r="M187" s="4" t="inlineStr"/>
+      <c r="N187" s="4" t="inlineStr"/>
+      <c r="O187" s="4" t="inlineStr"/>
+      <c r="P187" s="4" t="inlineStr">
+        <is>
+          <t>Low Strike Check | No signal | No signal</t>
+        </is>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" s="4" t="inlineStr">
+        <is>
+          <t>2026-03-27 10:00:00</t>
+        </is>
+      </c>
+      <c r="B188" s="4" t="inlineStr">
+        <is>
+          <t>10:00:00</t>
+        </is>
+      </c>
+      <c r="C188" s="4" t="inlineStr">
+        <is>
+          <t>10:00</t>
+        </is>
+      </c>
+      <c r="D188" s="4" t="inlineStr">
+        <is>
+          <t>283.05</t>
+        </is>
+      </c>
+      <c r="E188" s="4" t="inlineStr"/>
+      <c r="F188" s="4" t="inlineStr">
+        <is>
+          <t>323.60</t>
+        </is>
+      </c>
+      <c r="G188" s="4" t="inlineStr"/>
+      <c r="H188" s="4" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="I188" s="4" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="J188" s="4" t="inlineStr"/>
+      <c r="K188" s="4" t="inlineStr"/>
+      <c r="L188" s="4" t="inlineStr"/>
+      <c r="M188" s="4" t="inlineStr"/>
+      <c r="N188" s="4" t="inlineStr"/>
+      <c r="O188" s="4" t="inlineStr"/>
+      <c r="P188" s="4" t="inlineStr">
+        <is>
+          <t>High Strike Check | No signal | No signal</t>
+        </is>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" s="4" t="inlineStr">
+        <is>
+          <t>2026-03-27 10:00:00</t>
+        </is>
+      </c>
+      <c r="B189" s="4" t="inlineStr">
+        <is>
+          <t>10:00:00</t>
+        </is>
+      </c>
+      <c r="C189" s="4" t="inlineStr">
+        <is>
+          <t>10:00</t>
+        </is>
+      </c>
+      <c r="D189" s="4" t="inlineStr">
+        <is>
+          <t>355.90</t>
+        </is>
+      </c>
+      <c r="E189" s="4" t="inlineStr"/>
+      <c r="F189" s="4" t="inlineStr">
+        <is>
+          <t>249.95</t>
+        </is>
+      </c>
+      <c r="G189" s="4" t="inlineStr"/>
+      <c r="H189" s="4" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="I189" s="4" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="J189" s="4" t="inlineStr"/>
+      <c r="K189" s="4" t="inlineStr"/>
+      <c r="L189" s="4" t="inlineStr"/>
+      <c r="M189" s="4" t="inlineStr"/>
+      <c r="N189" s="4" t="inlineStr"/>
+      <c r="O189" s="4" t="inlineStr"/>
+      <c r="P189" s="4" t="inlineStr">
+        <is>
+          <t>Low Strike Check | No signal | No signal</t>
+        </is>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" s="4" t="inlineStr">
+        <is>
+          <t>2026-03-27 10:05:00</t>
+        </is>
+      </c>
+      <c r="B190" s="4" t="inlineStr">
+        <is>
+          <t>10:05:00</t>
+        </is>
+      </c>
+      <c r="C190" s="4" t="inlineStr">
+        <is>
+          <t>10:05</t>
+        </is>
+      </c>
+      <c r="D190" s="4" t="inlineStr">
+        <is>
+          <t>283.05</t>
+        </is>
+      </c>
+      <c r="E190" s="4" t="inlineStr"/>
+      <c r="F190" s="4" t="inlineStr">
+        <is>
+          <t>323.60</t>
+        </is>
+      </c>
+      <c r="G190" s="4" t="inlineStr"/>
+      <c r="H190" s="4" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="I190" s="4" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="J190" s="4" t="inlineStr"/>
+      <c r="K190" s="4" t="inlineStr"/>
+      <c r="L190" s="4" t="inlineStr"/>
+      <c r="M190" s="4" t="inlineStr"/>
+      <c r="N190" s="4" t="inlineStr"/>
+      <c r="O190" s="4" t="inlineStr"/>
+      <c r="P190" s="4" t="inlineStr">
+        <is>
+          <t>High Strike Check | No signal | No signal</t>
+        </is>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" s="4" t="inlineStr">
+        <is>
+          <t>2026-03-27 10:05:00</t>
+        </is>
+      </c>
+      <c r="B191" s="4" t="inlineStr">
+        <is>
+          <t>10:05:00</t>
+        </is>
+      </c>
+      <c r="C191" s="4" t="inlineStr">
+        <is>
+          <t>10:05</t>
+        </is>
+      </c>
+      <c r="D191" s="4" t="inlineStr">
+        <is>
+          <t>355.90</t>
+        </is>
+      </c>
+      <c r="E191" s="4" t="inlineStr"/>
+      <c r="F191" s="4" t="inlineStr">
+        <is>
+          <t>249.95</t>
+        </is>
+      </c>
+      <c r="G191" s="4" t="inlineStr"/>
+      <c r="H191" s="7" t="inlineStr">
+        <is>
+          <t>✓ YES</t>
+        </is>
+      </c>
+      <c r="I191" s="4" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="J191" s="4" t="inlineStr">
+        <is>
+          <t>262.90</t>
+        </is>
+      </c>
+      <c r="K191" s="4" t="inlineStr"/>
+      <c r="L191" s="4" t="inlineStr">
+        <is>
+          <t>239.95</t>
+        </is>
+      </c>
+      <c r="M191" s="4" t="inlineStr"/>
+      <c r="N191" s="4" t="inlineStr">
+        <is>
+          <t>308.80</t>
+        </is>
+      </c>
+      <c r="O191" s="4" t="inlineStr"/>
+      <c r="P191" s="4" t="inlineStr">
+        <is>
+          <t>Low Strike Check | Low 246.30 &lt; PE High 249.95, Close 262.90 &gt; PE High + 5 | No signal</t>
+        </is>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" s="4" t="inlineStr">
+        <is>
+          <t>2026-03-27 10:10:00</t>
+        </is>
+      </c>
+      <c r="B192" s="4" t="inlineStr">
+        <is>
+          <t>10:10:00</t>
+        </is>
+      </c>
+      <c r="C192" s="4" t="inlineStr">
+        <is>
+          <t>10:10</t>
+        </is>
+      </c>
+      <c r="D192" s="4" t="inlineStr">
+        <is>
+          <t>283.05</t>
+        </is>
+      </c>
+      <c r="E192" s="4" t="inlineStr"/>
+      <c r="F192" s="4" t="inlineStr">
+        <is>
+          <t>323.60</t>
+        </is>
+      </c>
+      <c r="G192" s="4" t="inlineStr"/>
+      <c r="H192" s="4" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="I192" s="4" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="J192" s="4" t="inlineStr"/>
+      <c r="K192" s="4" t="inlineStr"/>
+      <c r="L192" s="4" t="inlineStr"/>
+      <c r="M192" s="4" t="inlineStr"/>
+      <c r="N192" s="4" t="inlineStr"/>
+      <c r="O192" s="4" t="inlineStr"/>
+      <c r="P192" s="4" t="inlineStr">
+        <is>
+          <t>High Strike Check | No signal | No signal</t>
+        </is>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" s="4" t="inlineStr">
+        <is>
+          <t>2026-03-27 10:10:00</t>
+        </is>
+      </c>
+      <c r="B193" s="4" t="inlineStr">
+        <is>
+          <t>10:10:00</t>
+        </is>
+      </c>
+      <c r="C193" s="4" t="inlineStr">
+        <is>
+          <t>10:10</t>
+        </is>
+      </c>
+      <c r="D193" s="4" t="inlineStr">
+        <is>
+          <t>355.90</t>
+        </is>
+      </c>
+      <c r="E193" s="4" t="inlineStr"/>
+      <c r="F193" s="4" t="inlineStr">
+        <is>
+          <t>249.95</t>
+        </is>
+      </c>
+      <c r="G193" s="4" t="inlineStr"/>
+      <c r="H193" s="4" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="I193" s="4" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="J193" s="4" t="inlineStr"/>
+      <c r="K193" s="4" t="inlineStr"/>
+      <c r="L193" s="4" t="inlineStr"/>
+      <c r="M193" s="4" t="inlineStr"/>
+      <c r="N193" s="4" t="inlineStr"/>
+      <c r="O193" s="4" t="inlineStr"/>
+      <c r="P193" s="4" t="inlineStr">
+        <is>
+          <t>Low Strike Check | No signal | No signal</t>
+        </is>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" s="4" t="inlineStr">
+        <is>
+          <t>2026-03-27 10:15:00</t>
+        </is>
+      </c>
+      <c r="B194" s="4" t="inlineStr">
+        <is>
+          <t>10:15:00</t>
+        </is>
+      </c>
+      <c r="C194" s="4" t="inlineStr">
+        <is>
+          <t>10:15</t>
+        </is>
+      </c>
+      <c r="D194" s="4" t="inlineStr">
+        <is>
+          <t>283.05</t>
+        </is>
+      </c>
+      <c r="E194" s="4" t="inlineStr"/>
+      <c r="F194" s="4" t="inlineStr">
+        <is>
+          <t>323.60</t>
+        </is>
+      </c>
+      <c r="G194" s="4" t="inlineStr"/>
+      <c r="H194" s="4" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="I194" s="4" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="J194" s="4" t="inlineStr"/>
+      <c r="K194" s="4" t="inlineStr"/>
+      <c r="L194" s="4" t="inlineStr"/>
+      <c r="M194" s="4" t="inlineStr"/>
+      <c r="N194" s="4" t="inlineStr"/>
+      <c r="O194" s="4" t="inlineStr"/>
+      <c r="P194" s="4" t="inlineStr">
+        <is>
+          <t>High Strike Check | No signal | No signal</t>
+        </is>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" s="4" t="inlineStr">
+        <is>
+          <t>2026-03-27 10:15:00</t>
+        </is>
+      </c>
+      <c r="B195" s="4" t="inlineStr">
+        <is>
+          <t>10:15:00</t>
+        </is>
+      </c>
+      <c r="C195" s="4" t="inlineStr">
+        <is>
+          <t>10:15</t>
+        </is>
+      </c>
+      <c r="D195" s="4" t="inlineStr">
+        <is>
+          <t>355.90</t>
+        </is>
+      </c>
+      <c r="E195" s="4" t="inlineStr"/>
+      <c r="F195" s="4" t="inlineStr">
+        <is>
+          <t>249.95</t>
+        </is>
+      </c>
+      <c r="G195" s="4" t="inlineStr"/>
+      <c r="H195" s="4" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="I195" s="4" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="J195" s="4" t="inlineStr"/>
+      <c r="K195" s="4" t="inlineStr"/>
+      <c r="L195" s="4" t="inlineStr"/>
+      <c r="M195" s="4" t="inlineStr"/>
+      <c r="N195" s="4" t="inlineStr"/>
+      <c r="O195" s="4" t="inlineStr"/>
+      <c r="P195" s="4" t="inlineStr">
+        <is>
+          <t>Low Strike Check | No signal | No signal</t>
+        </is>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" s="4" t="inlineStr">
+        <is>
+          <t>2026-03-27 10:20:00</t>
+        </is>
+      </c>
+      <c r="B196" s="4" t="inlineStr">
+        <is>
+          <t>10:20:00</t>
+        </is>
+      </c>
+      <c r="C196" s="4" t="inlineStr">
+        <is>
+          <t>10:20</t>
+        </is>
+      </c>
+      <c r="D196" s="4" t="inlineStr">
+        <is>
+          <t>283.05</t>
+        </is>
+      </c>
+      <c r="E196" s="4" t="inlineStr"/>
+      <c r="F196" s="4" t="inlineStr">
+        <is>
+          <t>323.60</t>
+        </is>
+      </c>
+      <c r="G196" s="4" t="inlineStr"/>
+      <c r="H196" s="4" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="I196" s="4" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="J196" s="4" t="inlineStr"/>
+      <c r="K196" s="4" t="inlineStr"/>
+      <c r="L196" s="4" t="inlineStr"/>
+      <c r="M196" s="4" t="inlineStr"/>
+      <c r="N196" s="4" t="inlineStr"/>
+      <c r="O196" s="4" t="inlineStr"/>
+      <c r="P196" s="4" t="inlineStr">
+        <is>
+          <t>High Strike Check | No signal | No signal</t>
+        </is>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" s="4" t="inlineStr">
+        <is>
+          <t>2026-03-27 10:20:00</t>
+        </is>
+      </c>
+      <c r="B197" s="4" t="inlineStr">
+        <is>
+          <t>10:20:00</t>
+        </is>
+      </c>
+      <c r="C197" s="4" t="inlineStr">
+        <is>
+          <t>10:20</t>
+        </is>
+      </c>
+      <c r="D197" s="4" t="inlineStr">
+        <is>
+          <t>355.90</t>
+        </is>
+      </c>
+      <c r="E197" s="4" t="inlineStr"/>
+      <c r="F197" s="4" t="inlineStr">
+        <is>
+          <t>249.95</t>
+        </is>
+      </c>
+      <c r="G197" s="4" t="inlineStr"/>
+      <c r="H197" s="4" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="I197" s="4" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="J197" s="4" t="inlineStr"/>
+      <c r="K197" s="4" t="inlineStr"/>
+      <c r="L197" s="4" t="inlineStr"/>
+      <c r="M197" s="4" t="inlineStr"/>
+      <c r="N197" s="4" t="inlineStr"/>
+      <c r="O197" s="4" t="inlineStr"/>
+      <c r="P197" s="4" t="inlineStr">
+        <is>
+          <t>Low Strike Check | No signal | No signal</t>
+        </is>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" s="4" t="inlineStr">
+        <is>
+          <t>2026-03-27 10:25:00</t>
+        </is>
+      </c>
+      <c r="B198" s="4" t="inlineStr">
+        <is>
+          <t>10:25:00</t>
+        </is>
+      </c>
+      <c r="C198" s="4" t="inlineStr">
+        <is>
+          <t>10:25</t>
+        </is>
+      </c>
+      <c r="D198" s="4" t="inlineStr">
+        <is>
+          <t>283.05</t>
+        </is>
+      </c>
+      <c r="E198" s="4" t="inlineStr"/>
+      <c r="F198" s="4" t="inlineStr">
+        <is>
+          <t>323.60</t>
+        </is>
+      </c>
+      <c r="G198" s="4" t="inlineStr"/>
+      <c r="H198" s="4" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="I198" s="4" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="J198" s="4" t="inlineStr"/>
+      <c r="K198" s="4" t="inlineStr"/>
+      <c r="L198" s="4" t="inlineStr"/>
+      <c r="M198" s="4" t="inlineStr"/>
+      <c r="N198" s="4" t="inlineStr"/>
+      <c r="O198" s="4" t="inlineStr"/>
+      <c r="P198" s="4" t="inlineStr">
+        <is>
+          <t>High Strike Check | No signal | No signal</t>
+        </is>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" s="4" t="inlineStr">
+        <is>
+          <t>2026-03-27 10:25:00</t>
+        </is>
+      </c>
+      <c r="B199" s="4" t="inlineStr">
+        <is>
+          <t>10:25:00</t>
+        </is>
+      </c>
+      <c r="C199" s="4" t="inlineStr">
+        <is>
+          <t>10:25</t>
+        </is>
+      </c>
+      <c r="D199" s="4" t="inlineStr">
+        <is>
+          <t>355.90</t>
+        </is>
+      </c>
+      <c r="E199" s="4" t="inlineStr"/>
+      <c r="F199" s="4" t="inlineStr">
+        <is>
+          <t>249.95</t>
+        </is>
+      </c>
+      <c r="G199" s="4" t="inlineStr"/>
+      <c r="H199" s="4" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="I199" s="4" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="J199" s="4" t="inlineStr"/>
+      <c r="K199" s="4" t="inlineStr"/>
+      <c r="L199" s="4" t="inlineStr"/>
+      <c r="M199" s="4" t="inlineStr"/>
+      <c r="N199" s="4" t="inlineStr"/>
+      <c r="O199" s="4" t="inlineStr"/>
+      <c r="P199" s="4" t="inlineStr">
+        <is>
+          <t>Low Strike Check | No signal | No signal</t>
+        </is>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" s="4" t="inlineStr">
+        <is>
+          <t>2026-03-27 10:30:00</t>
+        </is>
+      </c>
+      <c r="B200" s="4" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="C200" s="4" t="inlineStr">
+        <is>
+          <t>10:30</t>
+        </is>
+      </c>
+      <c r="D200" s="4" t="inlineStr">
+        <is>
+          <t>283.05</t>
+        </is>
+      </c>
+      <c r="E200" s="4" t="inlineStr"/>
+      <c r="F200" s="4" t="inlineStr">
+        <is>
+          <t>323.60</t>
+        </is>
+      </c>
+      <c r="G200" s="4" t="inlineStr"/>
+      <c r="H200" s="4" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="I200" s="4" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="J200" s="4" t="inlineStr"/>
+      <c r="K200" s="4" t="inlineStr"/>
+      <c r="L200" s="4" t="inlineStr"/>
+      <c r="M200" s="4" t="inlineStr"/>
+      <c r="N200" s="4" t="inlineStr"/>
+      <c r="O200" s="4" t="inlineStr"/>
+      <c r="P200" s="4" t="inlineStr">
+        <is>
+          <t>High Strike Check | No signal | No signal</t>
+        </is>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" s="4" t="inlineStr">
+        <is>
+          <t>2026-03-27 10:30:00</t>
+        </is>
+      </c>
+      <c r="B201" s="4" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
+      <c r="C201" s="4" t="inlineStr">
+        <is>
+          <t>10:30</t>
+        </is>
+      </c>
+      <c r="D201" s="4" t="inlineStr">
+        <is>
+          <t>355.90</t>
+        </is>
+      </c>
+      <c r="E201" s="4" t="inlineStr"/>
+      <c r="F201" s="4" t="inlineStr">
+        <is>
+          <t>249.95</t>
+        </is>
+      </c>
+      <c r="G201" s="4" t="inlineStr"/>
+      <c r="H201" s="4" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="I201" s="4" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="J201" s="4" t="inlineStr"/>
+      <c r="K201" s="4" t="inlineStr"/>
+      <c r="L201" s="4" t="inlineStr"/>
+      <c r="M201" s="4" t="inlineStr"/>
+      <c r="N201" s="4" t="inlineStr"/>
+      <c r="O201" s="4" t="inlineStr"/>
+      <c r="P201" s="4" t="inlineStr">
+        <is>
+          <t>Low Strike Check | No signal | No signal</t>
+        </is>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" s="4" t="inlineStr">
+        <is>
+          <t>2026-03-27 10:35:00</t>
+        </is>
+      </c>
+      <c r="B202" s="4" t="inlineStr">
+        <is>
+          <t>10:35:00</t>
+        </is>
+      </c>
+      <c r="C202" s="4" t="inlineStr">
+        <is>
+          <t>10:35</t>
+        </is>
+      </c>
+      <c r="D202" s="4" t="inlineStr">
+        <is>
+          <t>283.05</t>
+        </is>
+      </c>
+      <c r="E202" s="4" t="inlineStr"/>
+      <c r="F202" s="4" t="inlineStr">
+        <is>
+          <t>323.60</t>
+        </is>
+      </c>
+      <c r="G202" s="4" t="inlineStr"/>
+      <c r="H202" s="4" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="I202" s="4" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="J202" s="4" t="inlineStr"/>
+      <c r="K202" s="4" t="inlineStr"/>
+      <c r="L202" s="4" t="inlineStr"/>
+      <c r="M202" s="4" t="inlineStr"/>
+      <c r="N202" s="4" t="inlineStr"/>
+      <c r="O202" s="4" t="inlineStr"/>
+      <c r="P202" s="4" t="inlineStr">
+        <is>
+          <t>High Strike Check | No signal | No signal</t>
+        </is>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" s="4" t="inlineStr">
+        <is>
+          <t>2026-03-27 10:35:00</t>
+        </is>
+      </c>
+      <c r="B203" s="4" t="inlineStr">
+        <is>
+          <t>10:35:00</t>
+        </is>
+      </c>
+      <c r="C203" s="4" t="inlineStr">
+        <is>
+          <t>10:35</t>
+        </is>
+      </c>
+      <c r="D203" s="4" t="inlineStr">
+        <is>
+          <t>355.90</t>
+        </is>
+      </c>
+      <c r="E203" s="4" t="inlineStr"/>
+      <c r="F203" s="4" t="inlineStr">
+        <is>
+          <t>249.95</t>
+        </is>
+      </c>
+      <c r="G203" s="4" t="inlineStr"/>
+      <c r="H203" s="7" t="inlineStr">
+        <is>
+          <t>✓ YES</t>
+        </is>
+      </c>
+      <c r="I203" s="4" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="J203" s="4" t="inlineStr">
+        <is>
+          <t>255.55</t>
+        </is>
+      </c>
+      <c r="K203" s="4" t="inlineStr"/>
+      <c r="L203" s="4" t="inlineStr">
+        <is>
+          <t>229.95</t>
+        </is>
+      </c>
+      <c r="M203" s="4" t="inlineStr"/>
+      <c r="N203" s="4" t="inlineStr">
+        <is>
+          <t>306.75</t>
+        </is>
+      </c>
+      <c r="O203" s="4" t="inlineStr"/>
+      <c r="P203" s="4" t="inlineStr">
+        <is>
+          <t>Low Strike Check | Low 249.45 &lt; PE High 249.95, Close 255.55 &gt; PE High + 5 | No signal</t>
+        </is>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" s="4" t="inlineStr">
+        <is>
+          <t>2026-03-27 10:40:00</t>
+        </is>
+      </c>
+      <c r="B204" s="4" t="inlineStr">
+        <is>
+          <t>10:40:00</t>
+        </is>
+      </c>
+      <c r="C204" s="4" t="inlineStr">
+        <is>
+          <t>10:40</t>
+        </is>
+      </c>
+      <c r="D204" s="4" t="inlineStr">
+        <is>
+          <t>283.05</t>
+        </is>
+      </c>
+      <c r="E204" s="4" t="inlineStr"/>
+      <c r="F204" s="4" t="inlineStr">
+        <is>
+          <t>323.60</t>
+        </is>
+      </c>
+      <c r="G204" s="4" t="inlineStr"/>
+      <c r="H204" s="4" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="I204" s="4" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="J204" s="4" t="inlineStr"/>
+      <c r="K204" s="4" t="inlineStr"/>
+      <c r="L204" s="4" t="inlineStr"/>
+      <c r="M204" s="4" t="inlineStr"/>
+      <c r="N204" s="4" t="inlineStr"/>
+      <c r="O204" s="4" t="inlineStr"/>
+      <c r="P204" s="4" t="inlineStr">
+        <is>
+          <t>High Strike Check | No signal | No signal</t>
+        </is>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" s="4" t="inlineStr">
+        <is>
+          <t>2026-03-27 10:40:00</t>
+        </is>
+      </c>
+      <c r="B205" s="4" t="inlineStr">
+        <is>
+          <t>10:40:00</t>
+        </is>
+      </c>
+      <c r="C205" s="4" t="inlineStr">
+        <is>
+          <t>10:40</t>
+        </is>
+      </c>
+      <c r="D205" s="4" t="inlineStr">
+        <is>
+          <t>355.90</t>
+        </is>
+      </c>
+      <c r="E205" s="4" t="inlineStr"/>
+      <c r="F205" s="4" t="inlineStr">
+        <is>
+          <t>249.95</t>
+        </is>
+      </c>
+      <c r="G205" s="4" t="inlineStr"/>
+      <c r="H205" s="7" t="inlineStr">
+        <is>
+          <t>✓ YES</t>
+        </is>
+      </c>
+      <c r="I205" s="4" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="J205" s="4" t="inlineStr">
+        <is>
+          <t>255.05</t>
+        </is>
+      </c>
+      <c r="K205" s="4" t="inlineStr"/>
+      <c r="L205" s="4" t="inlineStr">
+        <is>
+          <t>229.95</t>
+        </is>
+      </c>
+      <c r="M205" s="4" t="inlineStr"/>
+      <c r="N205" s="4" t="inlineStr">
+        <is>
+          <t>305.25</t>
+        </is>
+      </c>
+      <c r="O205" s="4" t="inlineStr"/>
+      <c r="P205" s="4" t="inlineStr">
+        <is>
+          <t>Low Strike Check | Low 243.95 &lt; PE High 249.95, Close 255.05 &gt; PE High + 5 | No signal</t>
+        </is>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" s="4" t="inlineStr">
+        <is>
+          <t>2026-03-27 10:45:00</t>
+        </is>
+      </c>
+      <c r="B206" s="4" t="inlineStr">
+        <is>
+          <t>10:45:00</t>
+        </is>
+      </c>
+      <c r="C206" s="4" t="inlineStr">
+        <is>
+          <t>10:45</t>
+        </is>
+      </c>
+      <c r="D206" s="4" t="inlineStr">
+        <is>
+          <t>283.05</t>
+        </is>
+      </c>
+      <c r="E206" s="4" t="inlineStr"/>
+      <c r="F206" s="4" t="inlineStr">
+        <is>
+          <t>323.60</t>
+        </is>
+      </c>
+      <c r="G206" s="4" t="inlineStr"/>
+      <c r="H206" s="4" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="I206" s="4" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="J206" s="4" t="inlineStr"/>
+      <c r="K206" s="4" t="inlineStr"/>
+      <c r="L206" s="4" t="inlineStr"/>
+      <c r="M206" s="4" t="inlineStr"/>
+      <c r="N206" s="4" t="inlineStr"/>
+      <c r="O206" s="4" t="inlineStr"/>
+      <c r="P206" s="4" t="inlineStr">
+        <is>
+          <t>High Strike Check | No signal | No signal</t>
+        </is>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" s="4" t="inlineStr">
+        <is>
+          <t>2026-03-27 10:45:00</t>
+        </is>
+      </c>
+      <c r="B207" s="4" t="inlineStr">
+        <is>
+          <t>10:45:00</t>
+        </is>
+      </c>
+      <c r="C207" s="4" t="inlineStr">
+        <is>
+          <t>10:45</t>
+        </is>
+      </c>
+      <c r="D207" s="4" t="inlineStr">
+        <is>
+          <t>355.90</t>
+        </is>
+      </c>
+      <c r="E207" s="4" t="inlineStr"/>
+      <c r="F207" s="4" t="inlineStr">
+        <is>
+          <t>249.95</t>
+        </is>
+      </c>
+      <c r="G207" s="4" t="inlineStr"/>
+      <c r="H207" s="4" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="I207" s="4" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="J207" s="4" t="inlineStr"/>
+      <c r="K207" s="4" t="inlineStr"/>
+      <c r="L207" s="4" t="inlineStr"/>
+      <c r="M207" s="4" t="inlineStr"/>
+      <c r="N207" s="4" t="inlineStr"/>
+      <c r="O207" s="4" t="inlineStr"/>
+      <c r="P207" s="4" t="inlineStr">
+        <is>
+          <t>Low Strike Check | No signal | No signal</t>
+        </is>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" s="4" t="inlineStr">
+        <is>
+          <t>2026-03-27 10:50:00</t>
+        </is>
+      </c>
+      <c r="B208" s="4" t="inlineStr">
+        <is>
+          <t>10:50:00</t>
+        </is>
+      </c>
+      <c r="C208" s="4" t="inlineStr">
+        <is>
+          <t>10:50</t>
+        </is>
+      </c>
+      <c r="D208" s="4" t="inlineStr">
+        <is>
+          <t>283.05</t>
+        </is>
+      </c>
+      <c r="E208" s="4" t="inlineStr"/>
+      <c r="F208" s="4" t="inlineStr">
+        <is>
+          <t>323.60</t>
+        </is>
+      </c>
+      <c r="G208" s="4" t="inlineStr"/>
+      <c r="H208" s="4" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="I208" s="4" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="J208" s="4" t="inlineStr"/>
+      <c r="K208" s="4" t="inlineStr"/>
+      <c r="L208" s="4" t="inlineStr"/>
+      <c r="M208" s="4" t="inlineStr"/>
+      <c r="N208" s="4" t="inlineStr"/>
+      <c r="O208" s="4" t="inlineStr"/>
+      <c r="P208" s="4" t="inlineStr">
+        <is>
+          <t>High Strike Check | No signal | No signal</t>
+        </is>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" s="4" t="inlineStr">
+        <is>
+          <t>2026-03-27 10:50:00</t>
+        </is>
+      </c>
+      <c r="B209" s="4" t="inlineStr">
+        <is>
+          <t>10:50:00</t>
+        </is>
+      </c>
+      <c r="C209" s="4" t="inlineStr">
+        <is>
+          <t>10:50</t>
+        </is>
+      </c>
+      <c r="D209" s="4" t="inlineStr">
+        <is>
+          <t>355.90</t>
+        </is>
+      </c>
+      <c r="E209" s="4" t="inlineStr"/>
+      <c r="F209" s="4" t="inlineStr">
+        <is>
+          <t>249.95</t>
+        </is>
+      </c>
+      <c r="G209" s="4" t="inlineStr"/>
+      <c r="H209" s="4" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="I209" s="4" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="J209" s="4" t="inlineStr"/>
+      <c r="K209" s="4" t="inlineStr"/>
+      <c r="L209" s="4" t="inlineStr"/>
+      <c r="M209" s="4" t="inlineStr"/>
+      <c r="N209" s="4" t="inlineStr"/>
+      <c r="O209" s="4" t="inlineStr"/>
+      <c r="P209" s="4" t="inlineStr">
+        <is>
+          <t>Low Strike Check | No signal | No signal</t>
+        </is>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" s="4" t="inlineStr">
+        <is>
+          <t>2026-03-27 10:55:00</t>
+        </is>
+      </c>
+      <c r="B210" s="4" t="inlineStr">
+        <is>
+          <t>10:55:00</t>
+        </is>
+      </c>
+      <c r="C210" s="4" t="inlineStr">
+        <is>
+          <t>10:55</t>
+        </is>
+      </c>
+      <c r="D210" s="4" t="inlineStr">
+        <is>
+          <t>283.05</t>
+        </is>
+      </c>
+      <c r="E210" s="4" t="inlineStr"/>
+      <c r="F210" s="4" t="inlineStr">
+        <is>
+          <t>323.60</t>
+        </is>
+      </c>
+      <c r="G210" s="4" t="inlineStr"/>
+      <c r="H210" s="4" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="I210" s="4" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="J210" s="4" t="inlineStr"/>
+      <c r="K210" s="4" t="inlineStr"/>
+      <c r="L210" s="4" t="inlineStr"/>
+      <c r="M210" s="4" t="inlineStr"/>
+      <c r="N210" s="4" t="inlineStr"/>
+      <c r="O210" s="4" t="inlineStr"/>
+      <c r="P210" s="4" t="inlineStr">
+        <is>
+          <t>High Strike Check | No signal | No signal</t>
+        </is>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" s="4" t="inlineStr">
+        <is>
+          <t>2026-03-27 10:55:00</t>
+        </is>
+      </c>
+      <c r="B211" s="4" t="inlineStr">
+        <is>
+          <t>10:55:00</t>
+        </is>
+      </c>
+      <c r="C211" s="4" t="inlineStr">
+        <is>
+          <t>10:55</t>
+        </is>
+      </c>
+      <c r="D211" s="4" t="inlineStr">
+        <is>
+          <t>355.90</t>
+        </is>
+      </c>
+      <c r="E211" s="4" t="inlineStr"/>
+      <c r="F211" s="4" t="inlineStr">
+        <is>
+          <t>249.95</t>
+        </is>
+      </c>
+      <c r="G211" s="4" t="inlineStr"/>
+      <c r="H211" s="4" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="I211" s="4" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="J211" s="4" t="inlineStr"/>
+      <c r="K211" s="4" t="inlineStr"/>
+      <c r="L211" s="4" t="inlineStr"/>
+      <c r="M211" s="4" t="inlineStr"/>
+      <c r="N211" s="4" t="inlineStr"/>
+      <c r="O211" s="4" t="inlineStr"/>
+      <c r="P211" s="4" t="inlineStr">
+        <is>
+          <t>Low Strike Check | No signal | No signal</t>
+        </is>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" s="4" t="inlineStr">
+        <is>
+          <t>2026-03-27 11:00:00</t>
+        </is>
+      </c>
+      <c r="B212" s="4" t="inlineStr">
+        <is>
+          <t>11:00:00</t>
+        </is>
+      </c>
+      <c r="C212" s="4" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
+      <c r="D212" s="4" t="inlineStr">
+        <is>
+          <t>283.05</t>
+        </is>
+      </c>
+      <c r="E212" s="4" t="inlineStr"/>
+      <c r="F212" s="4" t="inlineStr">
+        <is>
+          <t>323.60</t>
+        </is>
+      </c>
+      <c r="G212" s="4" t="inlineStr"/>
+      <c r="H212" s="4" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="I212" s="4" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="J212" s="4" t="inlineStr"/>
+      <c r="K212" s="4" t="inlineStr"/>
+      <c r="L212" s="4" t="inlineStr"/>
+      <c r="M212" s="4" t="inlineStr"/>
+      <c r="N212" s="4" t="inlineStr"/>
+      <c r="O212" s="4" t="inlineStr"/>
+      <c r="P212" s="4" t="inlineStr">
+        <is>
+          <t>High Strike Check | No signal | No signal</t>
+        </is>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" s="4" t="inlineStr">
+        <is>
+          <t>2026-03-27 11:00:00</t>
+        </is>
+      </c>
+      <c r="B213" s="4" t="inlineStr">
+        <is>
+          <t>11:00:00</t>
+        </is>
+      </c>
+      <c r="C213" s="4" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
+      <c r="D213" s="4" t="inlineStr">
+        <is>
+          <t>355.90</t>
+        </is>
+      </c>
+      <c r="E213" s="4" t="inlineStr"/>
+      <c r="F213" s="4" t="inlineStr">
+        <is>
+          <t>249.95</t>
+        </is>
+      </c>
+      <c r="G213" s="4" t="inlineStr"/>
+      <c r="H213" s="4" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="I213" s="4" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="J213" s="4" t="inlineStr"/>
+      <c r="K213" s="4" t="inlineStr"/>
+      <c r="L213" s="4" t="inlineStr"/>
+      <c r="M213" s="4" t="inlineStr"/>
+      <c r="N213" s="4" t="inlineStr"/>
+      <c r="O213" s="4" t="inlineStr"/>
+      <c r="P213" s="4" t="inlineStr">
+        <is>
+          <t>Low Strike Check | No signal | No signal</t>
+        </is>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" s="4" t="inlineStr">
+        <is>
+          <t>2026-03-27 11:05:00</t>
+        </is>
+      </c>
+      <c r="B214" s="4" t="inlineStr">
+        <is>
+          <t>11:05:00</t>
+        </is>
+      </c>
+      <c r="C214" s="4" t="inlineStr">
+        <is>
+          <t>11:05</t>
+        </is>
+      </c>
+      <c r="D214" s="4" t="inlineStr">
+        <is>
+          <t>283.05</t>
+        </is>
+      </c>
+      <c r="E214" s="4" t="inlineStr"/>
+      <c r="F214" s="4" t="inlineStr">
+        <is>
+          <t>323.60</t>
+        </is>
+      </c>
+      <c r="G214" s="4" t="inlineStr"/>
+      <c r="H214" s="4" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="I214" s="4" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="J214" s="4" t="inlineStr"/>
+      <c r="K214" s="4" t="inlineStr"/>
+      <c r="L214" s="4" t="inlineStr"/>
+      <c r="M214" s="4" t="inlineStr"/>
+      <c r="N214" s="4" t="inlineStr"/>
+      <c r="O214" s="4" t="inlineStr"/>
+      <c r="P214" s="4" t="inlineStr">
+        <is>
+          <t>High Strike Check | No signal | No signal</t>
+        </is>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" s="4" t="inlineStr">
+        <is>
+          <t>2026-03-27 11:05:00</t>
+        </is>
+      </c>
+      <c r="B215" s="4" t="inlineStr">
+        <is>
+          <t>11:05:00</t>
+        </is>
+      </c>
+      <c r="C215" s="4" t="inlineStr">
+        <is>
+          <t>11:05</t>
+        </is>
+      </c>
+      <c r="D215" s="4" t="inlineStr">
+        <is>
+          <t>355.90</t>
+        </is>
+      </c>
+      <c r="E215" s="4" t="inlineStr"/>
+      <c r="F215" s="4" t="inlineStr">
+        <is>
+          <t>249.95</t>
+        </is>
+      </c>
+      <c r="G215" s="4" t="inlineStr"/>
+      <c r="H215" s="4" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="I215" s="4" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="J215" s="4" t="inlineStr"/>
+      <c r="K215" s="4" t="inlineStr"/>
+      <c r="L215" s="4" t="inlineStr"/>
+      <c r="M215" s="4" t="inlineStr"/>
+      <c r="N215" s="4" t="inlineStr"/>
+      <c r="O215" s="4" t="inlineStr"/>
+      <c r="P215" s="4" t="inlineStr">
+        <is>
+          <t>Low Strike Check | No signal | No signal</t>
+        </is>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" s="4" t="inlineStr">
+        <is>
+          <t>2026-03-27 11:10:00</t>
+        </is>
+      </c>
+      <c r="B216" s="4" t="inlineStr">
+        <is>
+          <t>11:10:00</t>
+        </is>
+      </c>
+      <c r="C216" s="4" t="inlineStr">
+        <is>
+          <t>11:10</t>
+        </is>
+      </c>
+      <c r="D216" s="4" t="inlineStr">
+        <is>
+          <t>283.05</t>
+        </is>
+      </c>
+      <c r="E216" s="4" t="inlineStr"/>
+      <c r="F216" s="4" t="inlineStr">
+        <is>
+          <t>323.60</t>
+        </is>
+      </c>
+      <c r="G216" s="4" t="inlineStr"/>
+      <c r="H216" s="4" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="I216" s="4" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="J216" s="4" t="inlineStr"/>
+      <c r="K216" s="4" t="inlineStr"/>
+      <c r="L216" s="4" t="inlineStr"/>
+      <c r="M216" s="4" t="inlineStr"/>
+      <c r="N216" s="4" t="inlineStr"/>
+      <c r="O216" s="4" t="inlineStr"/>
+      <c r="P216" s="4" t="inlineStr">
+        <is>
+          <t>High Strike Check | No signal | No signal</t>
+        </is>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" s="4" t="inlineStr">
+        <is>
+          <t>2026-03-27 11:10:00</t>
+        </is>
+      </c>
+      <c r="B217" s="4" t="inlineStr">
+        <is>
+          <t>11:10:00</t>
+        </is>
+      </c>
+      <c r="C217" s="4" t="inlineStr">
+        <is>
+          <t>11:10</t>
+        </is>
+      </c>
+      <c r="D217" s="4" t="inlineStr">
+        <is>
+          <t>355.90</t>
+        </is>
+      </c>
+      <c r="E217" s="4" t="inlineStr"/>
+      <c r="F217" s="4" t="inlineStr">
+        <is>
+          <t>249.95</t>
+        </is>
+      </c>
+      <c r="G217" s="4" t="inlineStr"/>
+      <c r="H217" s="4" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="I217" s="4" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="J217" s="4" t="inlineStr"/>
+      <c r="K217" s="4" t="inlineStr"/>
+      <c r="L217" s="4" t="inlineStr"/>
+      <c r="M217" s="4" t="inlineStr"/>
+      <c r="N217" s="4" t="inlineStr"/>
+      <c r="O217" s="4" t="inlineStr"/>
+      <c r="P217" s="4" t="inlineStr">
+        <is>
+          <t>Low Strike Check | No signal | No signal</t>
+        </is>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" s="4" t="inlineStr">
+        <is>
+          <t>2026-03-27 11:15:00</t>
+        </is>
+      </c>
+      <c r="B218" s="4" t="inlineStr">
+        <is>
+          <t>11:15:00</t>
+        </is>
+      </c>
+      <c r="C218" s="4" t="inlineStr">
+        <is>
+          <t>11:15</t>
+        </is>
+      </c>
+      <c r="D218" s="4" t="inlineStr">
+        <is>
+          <t>283.05</t>
+        </is>
+      </c>
+      <c r="E218" s="4" t="inlineStr"/>
+      <c r="F218" s="4" t="inlineStr">
+        <is>
+          <t>323.60</t>
+        </is>
+      </c>
+      <c r="G218" s="4" t="inlineStr"/>
+      <c r="H218" s="4" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="I218" s="4" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="J218" s="4" t="inlineStr"/>
+      <c r="K218" s="4" t="inlineStr"/>
+      <c r="L218" s="4" t="inlineStr"/>
+      <c r="M218" s="4" t="inlineStr"/>
+      <c r="N218" s="4" t="inlineStr"/>
+      <c r="O218" s="4" t="inlineStr"/>
+      <c r="P218" s="4" t="inlineStr">
+        <is>
+          <t>High Strike Check | No signal | No signal</t>
+        </is>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" s="4" t="inlineStr">
+        <is>
+          <t>2026-03-27 11:15:00</t>
+        </is>
+      </c>
+      <c r="B219" s="4" t="inlineStr">
+        <is>
+          <t>11:15:00</t>
+        </is>
+      </c>
+      <c r="C219" s="4" t="inlineStr">
+        <is>
+          <t>11:15</t>
+        </is>
+      </c>
+      <c r="D219" s="4" t="inlineStr">
+        <is>
+          <t>355.90</t>
+        </is>
+      </c>
+      <c r="E219" s="4" t="inlineStr"/>
+      <c r="F219" s="4" t="inlineStr">
+        <is>
+          <t>249.95</t>
+        </is>
+      </c>
+      <c r="G219" s="4" t="inlineStr"/>
+      <c r="H219" s="4" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="I219" s="4" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="J219" s="4" t="inlineStr"/>
+      <c r="K219" s="4" t="inlineStr"/>
+      <c r="L219" s="4" t="inlineStr"/>
+      <c r="M219" s="4" t="inlineStr"/>
+      <c r="N219" s="4" t="inlineStr"/>
+      <c r="O219" s="4" t="inlineStr"/>
+      <c r="P219" s="4" t="inlineStr">
+        <is>
+          <t>Low Strike Check | No signal | No signal</t>
+        </is>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" s="4" t="inlineStr">
+        <is>
+          <t>2026-03-27 11:20:00</t>
+        </is>
+      </c>
+      <c r="B220" s="4" t="inlineStr">
+        <is>
+          <t>11:20:00</t>
+        </is>
+      </c>
+      <c r="C220" s="4" t="inlineStr">
+        <is>
+          <t>11:20</t>
+        </is>
+      </c>
+      <c r="D220" s="4" t="inlineStr">
+        <is>
+          <t>283.05</t>
+        </is>
+      </c>
+      <c r="E220" s="4" t="inlineStr"/>
+      <c r="F220" s="4" t="inlineStr">
+        <is>
+          <t>323.60</t>
+        </is>
+      </c>
+      <c r="G220" s="4" t="inlineStr"/>
+      <c r="H220" s="4" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="I220" s="4" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="J220" s="4" t="inlineStr"/>
+      <c r="K220" s="4" t="inlineStr"/>
+      <c r="L220" s="4" t="inlineStr"/>
+      <c r="M220" s="4" t="inlineStr"/>
+      <c r="N220" s="4" t="inlineStr"/>
+      <c r="O220" s="4" t="inlineStr"/>
+      <c r="P220" s="4" t="inlineStr">
+        <is>
+          <t>High Strike Check | No signal | No signal</t>
+        </is>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" s="4" t="inlineStr">
+        <is>
+          <t>2026-03-27 11:20:00</t>
+        </is>
+      </c>
+      <c r="B221" s="4" t="inlineStr">
+        <is>
+          <t>11:20:00</t>
+        </is>
+      </c>
+      <c r="C221" s="4" t="inlineStr">
+        <is>
+          <t>11:20</t>
+        </is>
+      </c>
+      <c r="D221" s="4" t="inlineStr">
+        <is>
+          <t>355.90</t>
+        </is>
+      </c>
+      <c r="E221" s="4" t="inlineStr"/>
+      <c r="F221" s="4" t="inlineStr">
+        <is>
+          <t>249.95</t>
+        </is>
+      </c>
+      <c r="G221" s="4" t="inlineStr"/>
+      <c r="H221" s="4" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="I221" s="4" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="J221" s="4" t="inlineStr"/>
+      <c r="K221" s="4" t="inlineStr"/>
+      <c r="L221" s="4" t="inlineStr"/>
+      <c r="M221" s="4" t="inlineStr"/>
+      <c r="N221" s="4" t="inlineStr"/>
+      <c r="O221" s="4" t="inlineStr"/>
+      <c r="P221" s="4" t="inlineStr">
+        <is>
+          <t>Low Strike Check | No signal | No signal</t>
+        </is>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" s="4" t="inlineStr">
+        <is>
+          <t>2026-03-27 11:25:00</t>
+        </is>
+      </c>
+      <c r="B222" s="4" t="inlineStr">
+        <is>
+          <t>11:25:00</t>
+        </is>
+      </c>
+      <c r="C222" s="4" t="inlineStr">
+        <is>
+          <t>11:25</t>
+        </is>
+      </c>
+      <c r="D222" s="4" t="inlineStr">
+        <is>
+          <t>283.05</t>
+        </is>
+      </c>
+      <c r="E222" s="4" t="inlineStr"/>
+      <c r="F222" s="4" t="inlineStr">
+        <is>
+          <t>323.60</t>
+        </is>
+      </c>
+      <c r="G222" s="4" t="inlineStr"/>
+      <c r="H222" s="4" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="I222" s="4" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="J222" s="4" t="inlineStr"/>
+      <c r="K222" s="4" t="inlineStr"/>
+      <c r="L222" s="4" t="inlineStr"/>
+      <c r="M222" s="4" t="inlineStr"/>
+      <c r="N222" s="4" t="inlineStr"/>
+      <c r="O222" s="4" t="inlineStr"/>
+      <c r="P222" s="4" t="inlineStr">
+        <is>
+          <t>High Strike Check | No signal | No signal</t>
+        </is>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" s="4" t="inlineStr">
+        <is>
+          <t>2026-03-27 11:25:00</t>
+        </is>
+      </c>
+      <c r="B223" s="4" t="inlineStr">
+        <is>
+          <t>11:25:00</t>
+        </is>
+      </c>
+      <c r="C223" s="4" t="inlineStr">
+        <is>
+          <t>11:25</t>
+        </is>
+      </c>
+      <c r="D223" s="4" t="inlineStr">
+        <is>
+          <t>355.90</t>
+        </is>
+      </c>
+      <c r="E223" s="4" t="inlineStr"/>
+      <c r="F223" s="4" t="inlineStr">
+        <is>
+          <t>249.95</t>
+        </is>
+      </c>
+      <c r="G223" s="4" t="inlineStr"/>
+      <c r="H223" s="4" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="I223" s="4" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="J223" s="4" t="inlineStr"/>
+      <c r="K223" s="4" t="inlineStr"/>
+      <c r="L223" s="4" t="inlineStr"/>
+      <c r="M223" s="4" t="inlineStr"/>
+      <c r="N223" s="4" t="inlineStr"/>
+      <c r="O223" s="4" t="inlineStr"/>
+      <c r="P223" s="4" t="inlineStr">
+        <is>
+          <t>Low Strike Check | No signal | No signal</t>
+        </is>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" s="4" t="inlineStr">
+        <is>
+          <t>2026-03-27 11:30:00</t>
+        </is>
+      </c>
+      <c r="B224" s="4" t="inlineStr">
+        <is>
+          <t>11:30:00</t>
+        </is>
+      </c>
+      <c r="C224" s="4" t="inlineStr">
+        <is>
+          <t>11:30</t>
+        </is>
+      </c>
+      <c r="D224" s="4" t="inlineStr">
+        <is>
+          <t>283.05</t>
+        </is>
+      </c>
+      <c r="E224" s="4" t="inlineStr"/>
+      <c r="F224" s="4" t="inlineStr">
+        <is>
+          <t>323.60</t>
+        </is>
+      </c>
+      <c r="G224" s="4" t="inlineStr"/>
+      <c r="H224" s="4" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="I224" s="4" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="J224" s="4" t="inlineStr"/>
+      <c r="K224" s="4" t="inlineStr"/>
+      <c r="L224" s="4" t="inlineStr"/>
+      <c r="M224" s="4" t="inlineStr"/>
+      <c r="N224" s="4" t="inlineStr"/>
+      <c r="O224" s="4" t="inlineStr"/>
+      <c r="P224" s="4" t="inlineStr">
+        <is>
+          <t>High Strike Check | No signal | No signal</t>
+        </is>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" s="4" t="inlineStr">
+        <is>
+          <t>2026-03-27 11:30:00</t>
+        </is>
+      </c>
+      <c r="B225" s="4" t="inlineStr">
+        <is>
+          <t>11:30:00</t>
+        </is>
+      </c>
+      <c r="C225" s="4" t="inlineStr">
+        <is>
+          <t>11:30</t>
+        </is>
+      </c>
+      <c r="D225" s="4" t="inlineStr">
+        <is>
+          <t>355.90</t>
+        </is>
+      </c>
+      <c r="E225" s="4" t="inlineStr"/>
+      <c r="F225" s="4" t="inlineStr">
+        <is>
+          <t>249.95</t>
+        </is>
+      </c>
+      <c r="G225" s="4" t="inlineStr"/>
+      <c r="H225" s="4" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="I225" s="4" t="inlineStr">
+        <is>
+          <t>✗ NO</t>
+        </is>
+      </c>
+      <c r="J225" s="4" t="inlineStr"/>
+      <c r="K225" s="4" t="inlineStr"/>
+      <c r="L225" s="4" t="inlineStr"/>
+      <c r="M225" s="4" t="inlineStr"/>
+      <c r="N225" s="4" t="inlineStr"/>
+      <c r="O225" s="4" t="inlineStr"/>
+      <c r="P225" s="4" t="inlineStr">
+        <is>
+          <t>Low Strike Check | No signal | No signal</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -9147,7 +11883,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L9"/>
+  <dimension ref="A1:L10"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -9574,6 +12310,54 @@
         </is>
       </c>
     </row>
+    <row r="10">
+      <c r="A10" s="4" t="inlineStr">
+        <is>
+          <t>2026-03-27 10:05:22</t>
+        </is>
+      </c>
+      <c r="B10" s="4" t="inlineStr">
+        <is>
+          <t>BUY CE</t>
+        </is>
+      </c>
+      <c r="C10" s="4" t="inlineStr">
+        <is>
+          <t>CE</t>
+        </is>
+      </c>
+      <c r="D10" s="4" t="n">
+        <v>23000</v>
+      </c>
+      <c r="E10" s="4" t="inlineStr">
+        <is>
+          <t>262.90</t>
+        </is>
+      </c>
+      <c r="F10" s="4" t="inlineStr">
+        <is>
+          <t>262.90</t>
+        </is>
+      </c>
+      <c r="G10" s="4" t="inlineStr"/>
+      <c r="H10" s="4" t="inlineStr"/>
+      <c r="I10" s="4" t="inlineStr"/>
+      <c r="J10" s="6" t="inlineStr">
+        <is>
+          <t>EXCEPTION</t>
+        </is>
+      </c>
+      <c r="K10" s="4" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="L10" s="4" t="inlineStr">
+        <is>
+          <t>Mode: LIVE | Error: 'KiteService' object has no attribute 'get_lot_size' | Order_type: MARKET</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" paperSize="9" horizontalDpi="0" verticalDpi="0"/>
